--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 04-Sep-2026  14:45:08    |    Closing Price Date: 04-Sep-2026</t>
+          <t>Scan Run: 07-Sep-2026  16:15:56    |    Closing Price Date: 07-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -591,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>45.2</v>
+        <v>46.4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>56.4</v>
+        <v>56.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>04-Sep-2026  14:45:08</t>
+          <t>07-Sep-2026  16:15:56</t>
         </is>
       </c>
     </row>
@@ -622,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): NEUTRAL — 45.2% stocks above EMA (mixed market)</t>
+          <t>Short-Term  (20 EMA): NEUTRAL — 46.4% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 51.2% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 51.6% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.4% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.8% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -650,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 113 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 116 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 128 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 129 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 141 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 142 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>252.3</v>
+        <v>247.22</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>259.83</v>
+        <v>258.63</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>269.91</v>
+        <v>269.02</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>299.5</v>
+        <v>298.57</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>335.4</v>
+        <v>332.55</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>332.08</v>
+        <v>332.13</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>322.18</v>
+        <v>322.59</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>325.04</v>
+        <v>324.95</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>6298.5</v>
+        <v>6393.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>5323.24</v>
+        <v>5425.17</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>4904.25</v>
+        <v>4962.65</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>4128.66</v>
+        <v>4154.32</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>740.1</v>
+        <v>734.15</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>722.34</v>
+        <v>723.47</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>669.1799999999999</v>
+        <v>671.72</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>532.8099999999999</v>
+        <v>535.1</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>283.15</v>
+        <v>280.95</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>274.13</v>
+        <v>274.78</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>244.03</v>
+        <v>245.48</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>154.8</v>
+        <v>156.08</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>331.8</v>
+        <v>332.6</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>337.89</v>
+        <v>337.38</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>305.47</v>
+        <v>306.53</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>215.48</v>
+        <v>216.49</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7161</v>
+        <v>7519</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>6908.42</v>
+        <v>6966.57</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6782.67</v>
+        <v>6811.54</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>5340.87</v>
+        <v>5361.58</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>842.75</v>
+        <v>870</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>810.59</v>
+        <v>816.25</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>746.9</v>
+        <v>751.73</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>608.14</v>
+        <v>610.75</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1110,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>340.1</v>
+        <v>333.6</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>324.04</v>
+        <v>324.95</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>303.89</v>
+        <v>305.05</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>254.9</v>
+        <v>255.93</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1154,24 +1154,24 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>5332</v>
+        <v>5474</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>5439.37</v>
+        <v>5442.67</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>5501.96</v>
+        <v>5500.86</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4482.5</v>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>4493.08</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -1198,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>172.04</v>
+        <v>171.99</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>172.48</v>
+        <v>172.43</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>170.31</v>
+        <v>170.38</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>164.18</v>
+        <v>164.98</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2777.3</v>
+        <v>2868</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>2732.3</v>
+        <v>2745.23</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>2539.69</v>
+        <v>2552.56</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2093.06</v>
+        <v>2100.63</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>586.1</v>
+        <v>583.6</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>586.34</v>
+        <v>586.08</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>575.0599999999999</v>
+        <v>575.4</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>571.01</v>
+        <v>570.78</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>2196.6</v>
+        <v>2352.5</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>2139.24</v>
+        <v>2159.55</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1945.36</v>
+        <v>1961.32</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1458.46</v>
+        <v>1466.51</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>3367.3</v>
+        <v>3382.6</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3456.09</v>
+        <v>3449.09</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>3487.73</v>
+        <v>3483.61</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>3206.2</v>
+        <v>3209.16</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>388.9</v>
+        <v>403.95</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>387.46</v>
+        <v>389.03</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>387.41</v>
+        <v>388.06</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>328.85</v>
+        <v>330.41</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1462,24 +1462,24 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>764.95</v>
+        <v>779.35</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>768.2</v>
+        <v>769.26</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>716.61</v>
+        <v>719.0700000000001</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>619.25</v>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>620.89</v>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>748.9</v>
+        <v>786.3</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>672.36</v>
+        <v>683.21</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>615.67</v>
+        <v>622.36</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>405.6</v>
+        <v>409.45</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>193.25</v>
+        <v>199.71</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>179.32</v>
+        <v>181.26</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>170.3</v>
+        <v>171.46</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>159.32</v>
+        <v>159.73</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>11.86</v>
+        <v>13.93</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>10.46</v>
+        <v>10.79</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>9.99</v>
+        <v>10.14</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>10.06</v>
+        <v>10.08</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1638,29 +1638,29 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>242.18</v>
+        <v>233.86</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>246.97</v>
+        <v>245.72</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>237.75</v>
+        <v>237.6</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>195.47</v>
+        <v>195.85</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>2005.3</v>
+        <v>2008</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>2010.74</v>
+        <v>2010.48</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1959.34</v>
+        <v>1961.25</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>1673.77</v>
+        <v>1677.53</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1726,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>231.17</v>
+        <v>231.69</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>236.45</v>
+        <v>235.99</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>229.78</v>
+        <v>229.86</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>206.56</v>
+        <v>206.85</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1770,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>64.43000000000001</v>
+        <v>65.09</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>67.90000000000001</v>
+        <v>67.63</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>66.58</v>
+        <v>66.52</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>59.65</v>
+        <v>59.7</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
@@ -1814,29 +1814,29 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>167.81</v>
+        <v>165.48</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>171.24</v>
+        <v>170.7</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>166.67</v>
+        <v>166.62</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>149.05</v>
+        <v>149.18</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>188.49</v>
+        <v>184.53</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>191.16</v>
+        <v>190.53</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>191.69</v>
+        <v>191.41</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>189.88</v>
+        <v>189.89</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>521.15</v>
+        <v>520.2</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>552.11</v>
+        <v>549.0700000000001</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>557.5599999999999</v>
+        <v>556.1</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>542.24</v>
+        <v>542.76</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1946,24 +1946,24 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>354.75</v>
+        <v>339.6</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>350.58</v>
+        <v>349.53</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>318.66</v>
+        <v>319.48</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>259.27</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>259.72</v>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>1414.9</v>
+        <v>1489.4</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1404.25</v>
+        <v>1412.36</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>1307.78</v>
+        <v>1314.9</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1005.17</v>
+        <v>1009.53</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>368.65</v>
+        <v>370.3</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>356.89</v>
+        <v>358.17</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>336.16</v>
+        <v>337.5</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>299.3</v>
+        <v>300.11</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>535.1</v>
+        <v>533.25</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>544.42</v>
+        <v>543.35</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>510.75</v>
+        <v>511.63</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>464.37</v>
+        <v>464.98</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>1625.6</v>
+        <v>1619.5</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1629.55</v>
+        <v>1628.6</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>1527.69</v>
+        <v>1531.29</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>1221.56</v>
+        <v>1225.54</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>781.45</v>
+        <v>788.15</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>772.73</v>
+        <v>774.1900000000001</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>703.54</v>
+        <v>706.86</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>519.74</v>
+        <v>523.1799999999999</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>609.05</v>
+        <v>618.95</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>605.47</v>
+        <v>606.75</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>605.9</v>
+        <v>606.41</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>595.84</v>
+        <v>596.4</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2254,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>535.1</v>
+        <v>538.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>546.02</v>
+        <v>545.3099999999999</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>530.61</v>
+        <v>530.92</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>476.34</v>
+        <v>477.3</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2298,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>197.83</v>
+        <v>195.17</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>201.89</v>
+        <v>201.25</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>204.19</v>
+        <v>203.84</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>204.4</v>
+        <v>203.22</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>798.6</v>
+        <v>786.55</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>845.64</v>
+        <v>840.01</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>909.91</v>
+        <v>905.0700000000001</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>986.71</v>
+        <v>983.17</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>551</v>
+        <v>538.15</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>593.35</v>
+        <v>588.09</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>629.74</v>
+        <v>626.14</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>630.34</v>
+        <v>629.61</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,29 +2430,29 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>358.65</v>
+        <v>365.1</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>358.15</v>
+        <v>358.81</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>359.01</v>
+        <v>359.25</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>343.98</v>
+        <v>344.57</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr">
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>215.72</v>
+        <v>211.38</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>207.48</v>
+        <v>207.85</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>204.14</v>
+        <v>204.42</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>171.6</v>
+        <v>172.05</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>84.20999999999999</v>
+        <v>83.19</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>87.61</v>
+        <v>87.19</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>86.25</v>
+        <v>86.13</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>71.45</v>
+        <v>71.69</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>225.96</v>
+        <v>230.65</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>233.74</v>
+        <v>233.44</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>220.27</v>
+        <v>220.67</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>217.12</v>
+        <v>217.04</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1729</v>
+        <v>1711.6</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1702.69</v>
+        <v>1703.54</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1676.47</v>
+        <v>1677.85</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1370.86</v>
+        <v>1372.91</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>354</v>
+        <v>343.5</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>394.38</v>
+        <v>389.53</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>389.05</v>
+        <v>387.26</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>409.51</v>
+        <v>408.52</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>576.15</v>
+        <v>573.15</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>588.09</v>
+        <v>586.67</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>570.7</v>
+        <v>570.79</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>488.81</v>
+        <v>489.64</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2738,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>168.45</v>
+        <v>165.81</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>171.62</v>
+        <v>171.06</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>178.59</v>
+        <v>178.09</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>215.34</v>
+        <v>214.85</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1222.8</v>
+        <v>1239.8</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1189.73</v>
+        <v>1194.5</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1100.48</v>
+        <v>1105.94</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1014.35</v>
+        <v>1019.33</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>932.45</v>
+        <v>936.45</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>888.27</v>
+        <v>892.86</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>843.84</v>
+        <v>847.47</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>699.74</v>
+        <v>702.36</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2870,24 +2870,24 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>175.1</v>
+        <v>172.28</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>174.64</v>
+        <v>174.41</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>179.94</v>
+        <v>179.64</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>182.48</v>
-      </c>
-      <c r="G50" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>182</v>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>282.55</v>
+        <v>277.15</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>290.49</v>
+        <v>289.22</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>299.32</v>
+        <v>298.46</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>301.93</v>
+        <v>303.22</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
@@ -2958,20 +2958,20 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>499.15</v>
+        <v>513.65</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>528.39</v>
+        <v>526.99</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>548.74</v>
+        <v>547.37</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>542.35</v>
+        <v>542.6799999999999</v>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
@@ -3002,24 +3002,24 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>3782.6</v>
+        <v>3896.3</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>3795.45</v>
+        <v>3805.06</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>3549.27</v>
+        <v>3562.88</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>2715.08</v>
-      </c>
-      <c r="G53" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2726.74</v>
+      </c>
+      <c r="G53" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -3046,20 +3046,20 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>530.6</v>
+        <v>533.05</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>556.97</v>
+        <v>554.6900000000001</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>535.65</v>
+        <v>535.55</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>528.17</v>
+        <v>528.29</v>
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
@@ -3090,20 +3090,20 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>1962.5</v>
+        <v>1932.9</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>2036.21</v>
+        <v>2026.37</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>2034.5</v>
+        <v>2030.51</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>1840.03</v>
+        <v>1840.01</v>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
@@ -3134,24 +3134,24 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>173.74</v>
+        <v>178.24</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>175.01</v>
+        <v>175.32</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>158.2</v>
+        <v>158.98</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>130.21</v>
-      </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>130.96</v>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -3178,20 +3178,20 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>591.1</v>
+        <v>604.4</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>548.03</v>
+        <v>553.48</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>538.35</v>
+        <v>541.03</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>493.07</v>
+        <v>493.92</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
@@ -3222,29 +3222,29 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>1772.9</v>
+        <v>1691.7</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1749.78</v>
+        <v>1744.25</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>1727.95</v>
+        <v>1726.53</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1795.93</v>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1796.48</v>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -3266,20 +3266,20 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>153.99</v>
+        <v>155.77</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>159.38</v>
+        <v>159.04</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>164.22</v>
+        <v>163.89</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>170.61</v>
+        <v>170.73</v>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
@@ -3310,20 +3310,20 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>3278.3</v>
+        <v>3348.7</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>3251.57</v>
+        <v>3260.82</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>3118.32</v>
+        <v>3127.36</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>2651.26</v>
+        <v>2664.16</v>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
@@ -3354,24 +3354,24 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>265.85</v>
+        <v>263.65</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>264.63</v>
+        <v>264.53</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>262.67</v>
+        <v>262.71</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>236.44</v>
-      </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>237.18</v>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -3398,24 +3398,24 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>501.55</v>
+        <v>512.05</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>510.29</v>
+        <v>510.46</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>520.35</v>
+        <v>520.02</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>576.02</v>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>575.02</v>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
@@ -3442,20 +3442,20 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>588.7</v>
+        <v>577.75</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>573.8099999999999</v>
+        <v>574.1799999999999</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>563.5</v>
+        <v>564.0599999999999</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>520.72</v>
+        <v>521.22</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
@@ -3486,20 +3486,20 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>22.98</v>
+        <v>23.54</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>22.56</v>
+        <v>22.65</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>22.4</v>
+        <v>22.44</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>22.5</v>
+        <v>22.62</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
@@ -3530,20 +3530,20 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>199.17</v>
+        <v>198.33</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>200.52</v>
+        <v>200.31</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>205.91</v>
+        <v>205.62</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>206.17</v>
+        <v>205.12</v>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
@@ -3574,20 +3574,20 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>195.56</v>
+        <v>194.45</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>198.79</v>
+        <v>198.37</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>204.03</v>
+        <v>203.65</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>192.47</v>
+        <v>192.23</v>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -3618,20 +3618,20 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>692.85</v>
+        <v>698.75</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>685.13</v>
+        <v>686.4299999999999</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>664.17</v>
+        <v>665.53</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>653.55</v>
+        <v>653.45</v>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
@@ -3662,20 +3662,20 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>1711.6</v>
+        <v>1778</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>1627.23</v>
+        <v>1641.59</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>1635.8</v>
+        <v>1641.38</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1594.54</v>
+        <v>1600.43</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3706,20 +3706,20 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>663.65</v>
+        <v>672.9</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>694.96</v>
+        <v>692.86</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>722.33</v>
+        <v>720.39</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>837.13</v>
+        <v>833.1900000000001</v>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
@@ -3750,20 +3750,20 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>2247.8</v>
+        <v>2231.4</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>2050.42</v>
+        <v>2067.66</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>1950.31</v>
+        <v>1961.34</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1598.04</v>
+        <v>1605.11</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
@@ -3794,20 +3794,20 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>7086.5</v>
+        <v>6951.5</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>7126.29</v>
+        <v>7109.64</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>6897.02</v>
+        <v>6899.15</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>5472.85</v>
+        <v>5489.48</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -3838,20 +3838,20 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>47.29</v>
+        <v>46.54</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>45.99</v>
+        <v>46.04</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>45.45</v>
+        <v>45.49</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>41.34</v>
+        <v>41.43</v>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
@@ -3882,20 +3882,20 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>473</v>
+        <v>466.95</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>494.08</v>
+        <v>491.5</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>514.0599999999999</v>
+        <v>512.22</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>585.1900000000001</v>
+        <v>584.28</v>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
@@ -3926,20 +3926,20 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>151.55</v>
+        <v>155.34</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>141.43</v>
+        <v>142.75</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>135.33</v>
+        <v>136.11</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>150.23</v>
+        <v>150.28</v>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
@@ -3970,20 +3970,20 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>2525.2</v>
+        <v>2566.8</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>2298.26</v>
+        <v>2323.83</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>2183.37</v>
+        <v>2198.4</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1754.82</v>
+        <v>1760.83</v>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
@@ -4014,20 +4014,20 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>344.75</v>
+        <v>338.05</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>370.67</v>
+        <v>367.57</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>377.54</v>
+        <v>375.99</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>372.52</v>
+        <v>372.36</v>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
@@ -4058,20 +4058,20 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>768.35</v>
+        <v>767.45</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>787.8099999999999</v>
+        <v>785.87</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>825.79</v>
+        <v>823.51</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>890.27</v>
+        <v>888.8099999999999</v>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
@@ -4102,20 +4102,20 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>328.55</v>
+        <v>321.15</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>332.51</v>
+        <v>331.43</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>338.57</v>
+        <v>337.89</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>367.43</v>
+        <v>366.77</v>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
@@ -4146,20 +4146,20 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>2727</v>
+        <v>2658.5</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>2546.84</v>
+        <v>2557.47</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>2504.66</v>
+        <v>2510.69</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>2482.18</v>
+        <v>2481.05</v>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
@@ -4190,20 +4190,20 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>186.23</v>
+        <v>185.13</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>195.86</v>
+        <v>194.84</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>204.13</v>
+        <v>203.38</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>214.02</v>
+        <v>214.69</v>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
@@ -4234,20 +4234,20 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>161.62</v>
+        <v>160.98</v>
       </c>
       <c r="D81" s="10" t="n">
-        <v>158.83</v>
+        <v>159.03</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>154.1</v>
+        <v>154.37</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>153.65</v>
+        <v>154.09</v>
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
@@ -4278,20 +4278,20 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>72.95</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>74.59</v>
+        <v>74.47</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>74.95</v>
+        <v>74.88</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>69.76000000000001</v>
+        <v>69.92</v>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
@@ -4322,24 +4322,24 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>199.47</v>
+        <v>205.87</v>
       </c>
       <c r="D83" s="10" t="n">
-        <v>201.81</v>
+        <v>202.2</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>207.51</v>
+        <v>207.45</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>182.68</v>
-      </c>
-      <c r="G83" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>184.09</v>
+      </c>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -4366,20 +4366,20 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>596.7</v>
+        <v>597.9</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>574.33</v>
+        <v>576.5700000000001</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>551.2</v>
+        <v>553.03</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>511.83</v>
+        <v>512.23</v>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
@@ -4410,29 +4410,29 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>15.7</v>
+        <v>15.94</v>
       </c>
       <c r="D85" s="10" t="n">
-        <v>15.56</v>
+        <v>15.59</v>
       </c>
       <c r="E85" s="10" t="n">
         <v>15.77</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>16.1</v>
+        <v>16.09</v>
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H85" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -4454,20 +4454,20 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>858.95</v>
+        <v>852.6</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>881.26</v>
+        <v>878.53</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>915.3</v>
+        <v>912.84</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>958.4400000000001</v>
+        <v>957.25</v>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
@@ -4498,24 +4498,24 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>2137.9</v>
+        <v>2207.1</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>2162.27</v>
+        <v>2166.54</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>2092.58</v>
+        <v>2097.07</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1767.37</v>
-      </c>
-      <c r="G87" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1772.28</v>
+      </c>
+      <c r="G87" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -4542,20 +4542,20 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>649.75</v>
+        <v>643.7</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>653.24</v>
+        <v>652.33</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>657.77</v>
+        <v>657.22</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>621.41</v>
+        <v>620.88</v>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
@@ -4586,20 +4586,20 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
-        <v>1288.4</v>
+        <v>1286.9</v>
       </c>
       <c r="D89" s="10" t="n">
-        <v>1361.06</v>
+        <v>1353.99</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>1383.58</v>
+        <v>1379.79</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>1308.45</v>
+        <v>1308.38</v>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
@@ -4630,20 +4630,20 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>136.08</v>
+        <v>132.72</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>126.35</v>
+        <v>126.96</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>122.58</v>
+        <v>122.97</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>116.22</v>
+        <v>116.52</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -4674,20 +4674,20 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="10" t="n">
-        <v>594.2</v>
+        <v>586.25</v>
       </c>
       <c r="D91" s="10" t="n">
-        <v>534.78</v>
+        <v>539.6799999999999</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>490.35</v>
+        <v>494.11</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>494.84</v>
+        <v>496.69</v>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
@@ -4718,20 +4718,20 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>1768.3</v>
+        <v>1748.4</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1738.3</v>
+        <v>1739.26</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>1588.93</v>
+        <v>1595.18</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1152.33</v>
+        <v>1158.26</v>
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
@@ -4762,20 +4762,20 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="10" t="n">
-        <v>74.23</v>
+        <v>72.28</v>
       </c>
       <c r="D93" s="10" t="n">
-        <v>74.97</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>75.44</v>
+        <v>75.31</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>68.98999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
@@ -4806,20 +4806,20 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>326.75</v>
+        <v>335.05</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>315.74</v>
+        <v>317.58</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>290.52</v>
+        <v>292.27</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>237.4</v>
+        <v>238.56</v>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
@@ -4850,20 +4850,20 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="10" t="n">
-        <v>279.2</v>
+        <v>274.4</v>
       </c>
       <c r="D95" s="10" t="n">
-        <v>300.3</v>
+        <v>297.84</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>330.92</v>
+        <v>328.7</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>415.74</v>
+        <v>414.33</v>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
@@ -4894,20 +4894,20 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>552.95</v>
+        <v>564.5</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>544.6900000000001</v>
+        <v>546.58</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>530.33</v>
+        <v>531.67</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>447.22</v>
+        <v>447.87</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
@@ -4938,24 +4938,24 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>712.25</v>
+        <v>774.25</v>
       </c>
       <c r="D97" s="10" t="n">
-        <v>750.34</v>
+        <v>752.62</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>789.15</v>
+        <v>788.5599999999999</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>715.08</v>
-      </c>
-      <c r="G97" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>718.76</v>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
@@ -4963,9 +4963,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J97" s="12" t="inlineStr">
@@ -4982,20 +4982,20 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>243.46</v>
+        <v>239.02</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>251.42</v>
+        <v>250.24</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>263.75</v>
+        <v>262.78</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>307.2</v>
+        <v>306.45</v>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -5026,20 +5026,20 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>1862</v>
+        <v>1832.4</v>
       </c>
       <c r="D99" s="10" t="n">
-        <v>1896.2</v>
+        <v>1890.12</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>1878.67</v>
+        <v>1876.85</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>1781.2</v>
+        <v>1782.99</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -5070,20 +5070,20 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>220.74</v>
+        <v>221.31</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>206.95</v>
+        <v>208.32</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>196.78</v>
+        <v>197.75</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>180.72</v>
+        <v>181.3</v>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
@@ -5114,20 +5114,20 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>851.15</v>
+        <v>856.5</v>
       </c>
       <c r="D101" s="10" t="n">
-        <v>916.37</v>
+        <v>910.67</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>899.39</v>
+        <v>897.71</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>745.99</v>
+        <v>746.08</v>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -5158,20 +5158,20 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>405.8</v>
+        <v>420.05</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>392.44</v>
+        <v>395.07</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>381.58</v>
+        <v>383.09</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>365.6</v>
+        <v>366.09</v>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
@@ -5202,20 +5202,20 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>676.35</v>
+        <v>659.7</v>
       </c>
       <c r="D103" s="10" t="n">
-        <v>680.47</v>
+        <v>678.5</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>722.4299999999999</v>
+        <v>719.97</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>803.03</v>
+        <v>800.83</v>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
@@ -5246,20 +5246,20 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>11418</v>
+        <v>11067</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>10669.64</v>
+        <v>10707.48</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>10209.65</v>
+        <v>10243.27</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>9291.459999999999</v>
+        <v>9310.709999999999</v>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
@@ -5290,20 +5290,20 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>760.45</v>
+        <v>760.15</v>
       </c>
       <c r="D105" s="10" t="n">
-        <v>746.4400000000001</v>
+        <v>747.74</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>769.02</v>
+        <v>768.67</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>714.4</v>
+        <v>715.53</v>
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
@@ -5334,20 +5334,20 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>89.04000000000001</v>
+        <v>89.67</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>95.43000000000001</v>
+        <v>94.88</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>93.31999999999999</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>85.28</v>
+        <v>85.33</v>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
@@ -5378,20 +5378,20 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="10" t="n">
-        <v>1951.9</v>
+        <v>1935.5</v>
       </c>
       <c r="D107" s="10" t="n">
-        <v>1932.55</v>
+        <v>1932.83</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>1797.78</v>
+        <v>1803.18</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>1577.13</v>
+        <v>1590.3</v>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
@@ -5422,20 +5422,20 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>964.15</v>
+        <v>939.5</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>855.65</v>
+        <v>863.64</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>746.22</v>
+        <v>753.8</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>541.8099999999999</v>
+        <v>545.75</v>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
@@ -5466,20 +5466,20 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="10" t="n">
-        <v>1059.6</v>
+        <v>1178.8</v>
       </c>
       <c r="D109" s="10" t="n">
-        <v>1015.82</v>
+        <v>1031.34</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>1025.38</v>
+        <v>1031.4</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>984.49</v>
+        <v>989.51</v>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
@@ -5510,20 +5510,20 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>689.7</v>
+        <v>668.7</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>711.21</v>
+        <v>707.16</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>751.96</v>
+        <v>748.6900000000001</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>891.66</v>
+        <v>888.88</v>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
@@ -5554,20 +5554,20 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>449.8</v>
+        <v>453.7</v>
       </c>
       <c r="D111" s="10" t="n">
-        <v>430.75</v>
+        <v>432.93</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>410.15</v>
+        <v>411.86</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>342.25</v>
+        <v>341.58</v>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
@@ -5598,20 +5598,20 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>852.85</v>
+        <v>909.1</v>
       </c>
       <c r="D112" s="10" t="n">
-        <v>822.4400000000001</v>
+        <v>830.6900000000001</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>835.55</v>
+        <v>838.4400000000001</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>782.27</v>
+        <v>783.26</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -5642,20 +5642,20 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="10" t="n">
-        <v>409.2</v>
+        <v>439.1</v>
       </c>
       <c r="D113" s="10" t="n">
-        <v>381.71</v>
+        <v>387.18</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>388.88</v>
+        <v>390.85</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>396.2</v>
+        <v>395.74</v>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
@@ -5686,20 +5686,20 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>208.82</v>
+        <v>206.15</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>211.85</v>
+        <v>211.31</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>218.68</v>
+        <v>218.19</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>244.29</v>
+        <v>245.07</v>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
@@ -5730,20 +5730,20 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>74.53</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="D115" s="10" t="n">
-        <v>81.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>89.12</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>96.84</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
@@ -5774,20 +5774,20 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>260.4</v>
+        <v>273.4</v>
       </c>
       <c r="D116" s="10" t="n">
-        <v>907.1900000000001</v>
+        <v>846.83</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>1008.17</v>
+        <v>979.36</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>994.76</v>
+        <v>987.85</v>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
@@ -5818,20 +5818,20 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="10" t="n">
-        <v>331.85</v>
+        <v>321.7</v>
       </c>
       <c r="D117" s="10" t="n">
-        <v>316.85</v>
+        <v>317.31</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>300.96</v>
+        <v>301.77</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>312.91</v>
+        <v>312.99</v>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
@@ -5862,20 +5862,20 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>3347.6</v>
+        <v>3367.7</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>3340.42</v>
+        <v>3343.02</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>3199</v>
+        <v>3205.62</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>2861.38</v>
+        <v>2875.35</v>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
@@ -5906,24 +5906,24 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>4536.9</v>
+        <v>4491.5</v>
       </c>
       <c r="D119" s="10" t="n">
-        <v>4525.03</v>
+        <v>4521.83</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>4329.13</v>
+        <v>4335.49</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>3616.12</v>
-      </c>
-      <c r="G119" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3629.09</v>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H119" s="13" t="inlineStr">
@@ -5950,20 +5950,20 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>677.1</v>
+        <v>672.15</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>671.72</v>
+        <v>671.76</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>705.89</v>
+        <v>704.5599999999999</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>763.7</v>
+        <v>762.27</v>
       </c>
       <c r="G120" s="13" t="inlineStr">
         <is>
@@ -5994,20 +5994,20 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>307</v>
+        <v>302.6</v>
       </c>
       <c r="D121" s="10" t="n">
-        <v>322.96</v>
+        <v>321.02</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>352.94</v>
+        <v>350.96</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>403.23</v>
+        <v>403.15</v>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
@@ -6038,20 +6038,20 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>516.3</v>
+        <v>516.75</v>
       </c>
       <c r="D122" s="10" t="n">
-        <v>520.37</v>
+        <v>520.03</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>547.77</v>
+        <v>546.55</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>674.3200000000001</v>
+        <v>670.5700000000001</v>
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
@@ -6082,24 +6082,24 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="10" t="n">
-        <v>618.85</v>
+        <v>611.5</v>
       </c>
       <c r="D123" s="10" t="n">
-        <v>618.83</v>
+        <v>618.13</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>572.23</v>
+        <v>573.77</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>495.64</v>
-      </c>
-      <c r="G123" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>497.48</v>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H123" s="13" t="inlineStr">
@@ -6126,20 +6126,20 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>1578.7</v>
+        <v>1625.4</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>1475.15</v>
+        <v>1489.46</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>1364.96</v>
+        <v>1375.17</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1119.17</v>
+        <v>1123.7</v>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
@@ -6170,20 +6170,20 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="10" t="n">
-        <v>223.24</v>
+        <v>218.77</v>
       </c>
       <c r="D125" s="10" t="n">
-        <v>223.59</v>
+        <v>223.13</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>225.66</v>
+        <v>225.39</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>241.35</v>
+        <v>241.45</v>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -6214,20 +6214,20 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>490.05</v>
+        <v>473.8</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>503.64</v>
+        <v>500.8</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>509.91</v>
+        <v>508.5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>541.47</v>
+        <v>540.8</v>
       </c>
       <c r="G126" s="11" t="inlineStr">
         <is>
@@ -6258,20 +6258,20 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>421.95</v>
+        <v>427.3</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>410.66</v>
+        <v>412.25</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>389.79</v>
+        <v>391.26</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>370.3</v>
+        <v>370.65</v>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
@@ -6302,24 +6302,24 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>824.2</v>
+        <v>826.2</v>
       </c>
       <c r="D128" s="10" t="n">
-        <v>825.22</v>
+        <v>825.3099999999999</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>791.58</v>
+        <v>792.9400000000001</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>730.15</v>
-      </c>
-      <c r="G128" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>731.0599999999999</v>
+      </c>
+      <c r="G128" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
@@ -6346,20 +6346,20 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>765.75</v>
+        <v>754.65</v>
       </c>
       <c r="D129" s="10" t="n">
-        <v>751.01</v>
+        <v>751.35</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>704.1</v>
+        <v>706.09</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>588.29</v>
+        <v>589.62</v>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
@@ -6390,24 +6390,24 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>170.5</v>
+        <v>171.86</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>171.57</v>
+        <v>171.6</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>167.58</v>
+        <v>167.75</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>156.88</v>
-      </c>
-      <c r="G130" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>156.93</v>
+      </c>
+      <c r="G130" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
@@ -6434,20 +6434,20 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="10" t="n">
-        <v>700.2</v>
+        <v>687.9</v>
       </c>
       <c r="D131" s="10" t="n">
-        <v>706.05</v>
+        <v>704.3200000000001</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>685.64</v>
+        <v>685.73</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>643.21</v>
+        <v>643.58</v>
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
@@ -6478,20 +6478,20 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>436.6</v>
+        <v>433.35</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>437.62</v>
+        <v>437.21</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>438.42</v>
+        <v>438.22</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>474.59</v>
+        <v>473.76</v>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
@@ -6522,24 +6522,24 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="10" t="n">
-        <v>789.2</v>
+        <v>776.95</v>
       </c>
       <c r="D133" s="10" t="n">
-        <v>787.5700000000001</v>
+        <v>786.5599999999999</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>789.47</v>
+        <v>788.97</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>768.97</v>
-      </c>
-      <c r="G133" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>767.9</v>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
@@ -6566,20 +6566,20 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>1881.7</v>
+        <v>1938.1</v>
       </c>
       <c r="D134" s="10" t="n">
-        <v>1763.36</v>
+        <v>1780</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>1719.41</v>
+        <v>1727.99</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1439.8</v>
+        <v>1444.76</v>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
@@ -6610,20 +6610,20 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="10" t="n">
-        <v>251.5</v>
+        <v>249.25</v>
       </c>
       <c r="D135" s="10" t="n">
-        <v>256.88</v>
+        <v>256.15</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>256.28</v>
+        <v>256.01</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>261.56</v>
+        <v>261.44</v>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6654,24 +6654,24 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>97.15000000000001</v>
+        <v>96.41</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>96.78</v>
+        <v>96.75</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>87.72</v>
+        <v>88.06</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>75.42</v>
-      </c>
-      <c r="G136" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -6698,20 +6698,20 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="10" t="n">
-        <v>382.35</v>
+        <v>384.15</v>
       </c>
       <c r="D137" s="10" t="n">
-        <v>367.48</v>
+        <v>369.07</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>354.13</v>
+        <v>355.3</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>365.14</v>
+        <v>365.88</v>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
@@ -6742,20 +6742,20 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>2085.8</v>
+        <v>2068.8</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>2174.5</v>
+        <v>2164.43</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>2233.08</v>
+        <v>2226.64</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2169.25</v>
+        <v>2173.28</v>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
@@ -6786,20 +6786,20 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="10" t="n">
-        <v>600.05</v>
+        <v>599.25</v>
       </c>
       <c r="D139" s="10" t="n">
-        <v>603.3099999999999</v>
+        <v>602.92</v>
       </c>
       <c r="E139" s="10" t="n">
-        <v>604.72</v>
+        <v>604.51</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>552.08</v>
+        <v>552.37</v>
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
@@ -6830,20 +6830,20 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>335.55</v>
+        <v>336.55</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>339.25</v>
+        <v>338.99</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>338.39</v>
+        <v>338.32</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>348.64</v>
+        <v>348.58</v>
       </c>
       <c r="G140" s="11" t="inlineStr">
         <is>
@@ -6874,20 +6874,20 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>429.75</v>
+        <v>417.3</v>
       </c>
       <c r="D141" s="10" t="n">
-        <v>434.3</v>
+        <v>432.68</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>400.69</v>
+        <v>401.34</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>306.14</v>
+        <v>307.25</v>
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
@@ -6918,20 +6918,20 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>1329.3</v>
+        <v>1323.3</v>
       </c>
       <c r="D142" s="10" t="n">
-        <v>1146.11</v>
+        <v>1162.98</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>1014.1</v>
+        <v>1026.23</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>815.9400000000001</v>
+        <v>820.99</v>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
@@ -6962,24 +6962,24 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="10" t="n">
-        <v>120.69</v>
+        <v>126.61</v>
       </c>
       <c r="D143" s="10" t="n">
-        <v>123.45</v>
+        <v>123.75</v>
       </c>
       <c r="E143" s="10" t="n">
         <v>126.62</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>122.55</v>
-      </c>
-      <c r="G143" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>122.47</v>
+      </c>
+      <c r="G143" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
@@ -6987,9 +6987,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I143" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
@@ -7006,29 +7006,29 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>216.5</v>
+        <v>222.42</v>
       </c>
       <c r="D144" s="10" t="n">
-        <v>219.98</v>
+        <v>220.21</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>221.13</v>
+        <v>221.18</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>215.29</v>
-      </c>
-      <c r="G144" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H144" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>215.33</v>
+      </c>
+      <c r="G144" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H144" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I144" s="13" t="inlineStr">
@@ -7050,20 +7050,20 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="10" t="n">
-        <v>286.45</v>
+        <v>285.4</v>
       </c>
       <c r="D145" s="10" t="n">
-        <v>302.42</v>
+        <v>300.8</v>
       </c>
       <c r="E145" s="10" t="n">
-        <v>300.98</v>
+        <v>300.37</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>283.89</v>
+        <v>283.83</v>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -7094,20 +7094,20 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>114.92</v>
+        <v>113.92</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>119.55</v>
+        <v>119.02</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>123.45</v>
+        <v>123.08</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>130.19</v>
+        <v>129.93</v>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -7138,20 +7138,20 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="10" t="n">
-        <v>161.56</v>
+        <v>165.45</v>
       </c>
       <c r="D147" s="10" t="n">
-        <v>156.36</v>
+        <v>157.22</v>
       </c>
       <c r="E147" s="10" t="n">
-        <v>154.64</v>
+        <v>155.06</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>147.18</v>
+        <v>147.61</v>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
@@ -7182,20 +7182,20 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>429.3</v>
+        <v>419.55</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>454.21</v>
+        <v>450.91</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>473.91</v>
+        <v>471.78</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>529.7</v>
+        <v>528.98</v>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
@@ -7226,24 +7226,24 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="10" t="n">
-        <v>95.3</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="D149" s="10" t="n">
-        <v>94.73</v>
+        <v>94.62</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>97.40000000000001</v>
+        <v>97.25</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>104.33</v>
-      </c>
-      <c r="G149" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>104.18</v>
+      </c>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
@@ -7270,24 +7270,24 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>2100.1</v>
+        <v>2071.4</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>2092.19</v>
+        <v>2090.21</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>2039.49</v>
+        <v>2040.74</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1775.44</v>
-      </c>
-      <c r="G150" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1778.39</v>
+      </c>
+      <c r="G150" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H150" s="13" t="inlineStr">
@@ -7314,20 +7314,20 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="10" t="n">
-        <v>2306.1</v>
+        <v>2359.8</v>
       </c>
       <c r="D151" s="10" t="n">
-        <v>2482.11</v>
+        <v>2470.46</v>
       </c>
       <c r="E151" s="10" t="n">
-        <v>2525.74</v>
+        <v>2519.23</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>2517.01</v>
+        <v>2514.25</v>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -7358,20 +7358,20 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>991.1</v>
+        <v>994.8</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>925.16</v>
+        <v>931.8</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>881.58</v>
+        <v>886.02</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>785.88</v>
+        <v>787.7</v>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
@@ -7402,20 +7402,20 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="10" t="n">
-        <v>1993.4</v>
+        <v>2003.6</v>
       </c>
       <c r="D153" s="10" t="n">
-        <v>1846.14</v>
+        <v>1861.13</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>1729.6</v>
+        <v>1740.34</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>1527.49</v>
+        <v>1531.5</v>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
@@ -7446,20 +7446,20 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>1827.6</v>
+        <v>1898.4</v>
       </c>
       <c r="D154" s="10" t="n">
-        <v>1612.39</v>
+        <v>1639.63</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>1432.18</v>
+        <v>1450.46</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1252.7</v>
+        <v>1254.39</v>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
@@ -7490,20 +7490,20 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="10" t="n">
-        <v>286.25</v>
+        <v>286.8</v>
       </c>
       <c r="D155" s="10" t="n">
-        <v>283.21</v>
+        <v>283.55</v>
       </c>
       <c r="E155" s="10" t="n">
-        <v>280.12</v>
+        <v>280.38</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>235.42</v>
+        <v>235.93</v>
       </c>
       <c r="G155" s="13" t="inlineStr">
         <is>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>11654</v>
+        <v>11569</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>11404.22</v>
+        <v>11419.91</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>11059.26</v>
+        <v>11079.25</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10073.1</v>
+        <v>10082.98</v>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
@@ -7578,20 +7578,20 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="10" t="n">
-        <v>2043.2</v>
+        <v>2063.7</v>
       </c>
       <c r="D157" s="10" t="n">
-        <v>2102.87</v>
+        <v>2099.14</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>2183.24</v>
+        <v>2178.56</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>2218.8</v>
+        <v>2230.61</v>
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
@@ -7622,20 +7622,20 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>2278.3</v>
+        <v>2257.2</v>
       </c>
       <c r="D158" s="10" t="n">
-        <v>2320.72</v>
+        <v>2314.67</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>2182.48</v>
+        <v>2185.41</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>1810.05</v>
+        <v>1812.2</v>
       </c>
       <c r="G158" s="11" t="inlineStr">
         <is>
@@ -7666,20 +7666,20 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="10" t="n">
-        <v>646.8</v>
+        <v>642.7</v>
       </c>
       <c r="D159" s="10" t="n">
-        <v>666.66</v>
+        <v>664.38</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>686.58</v>
+        <v>684.86</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>647.49</v>
+        <v>647.28</v>
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
@@ -7710,20 +7710,20 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>504.2</v>
+        <v>509.35</v>
       </c>
       <c r="D160" s="10" t="n">
-        <v>503.28</v>
+        <v>503.86</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>519.04</v>
+        <v>518.66</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>554.9400000000001</v>
+        <v>553.95</v>
       </c>
       <c r="G160" s="13" t="inlineStr">
         <is>
@@ -7754,20 +7754,20 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>115.99</v>
+        <v>119.46</v>
       </c>
       <c r="D161" s="10" t="n">
-        <v>109.95</v>
+        <v>110.85</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>109.63</v>
+        <v>110.02</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>115.34</v>
+        <v>115.45</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
@@ -7798,20 +7798,20 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>418.8</v>
+        <v>419.9</v>
       </c>
       <c r="D162" s="10" t="n">
-        <v>418.73</v>
+        <v>418.84</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>416.17</v>
+        <v>416.31</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>394.48</v>
+        <v>394.61</v>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
@@ -7842,20 +7842,20 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>162.88</v>
+        <v>162.02</v>
       </c>
       <c r="D163" s="10" t="n">
-        <v>160.12</v>
+        <v>160.3</v>
       </c>
       <c r="E163" s="10" t="n">
-        <v>160.85</v>
+        <v>160.89</v>
       </c>
       <c r="F163" s="10" t="n">
-        <v>169.18</v>
+        <v>168.95</v>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
@@ -7886,20 +7886,20 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="10" t="n">
-        <v>515.7</v>
+        <v>507.15</v>
       </c>
       <c r="D164" s="10" t="n">
-        <v>540.84</v>
+        <v>537.63</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>559.48</v>
+        <v>557.4299999999999</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>643.79</v>
+        <v>641.92</v>
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7930,20 +7930,20 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="10" t="n">
-        <v>734.2</v>
+        <v>785.65</v>
       </c>
       <c r="D165" s="10" t="n">
-        <v>697.96</v>
+        <v>706.3099999999999</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>652.7</v>
+        <v>657.91</v>
       </c>
       <c r="F165" s="10" t="n">
-        <v>556.01</v>
+        <v>558.72</v>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="10" t="n">
-        <v>201.54</v>
+        <v>195.1</v>
       </c>
       <c r="D166" s="10" t="n">
-        <v>205.11</v>
+        <v>204.16</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>204.9</v>
+        <v>204.52</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>231.46</v>
+        <v>231.09</v>
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
@@ -8018,20 +8018,20 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="10" t="n">
-        <v>218.74</v>
+        <v>216.49</v>
       </c>
       <c r="D167" s="10" t="n">
-        <v>225.65</v>
+        <v>224.78</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>232.71</v>
+        <v>232.07</v>
       </c>
       <c r="F167" s="10" t="n">
-        <v>230.5</v>
+        <v>230.35</v>
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
@@ -8062,20 +8062,20 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="10" t="n">
-        <v>541.5</v>
+        <v>538.95</v>
       </c>
       <c r="D168" s="10" t="n">
-        <v>520</v>
+        <v>521.8099999999999</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>498</v>
+        <v>499.61</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>470.68</v>
+        <v>471.36</v>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
@@ -8106,20 +8106,20 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="10" t="n">
-        <v>431.65</v>
+        <v>423</v>
       </c>
       <c r="D169" s="10" t="n">
-        <v>419.39</v>
+        <v>419.73</v>
       </c>
       <c r="E169" s="10" t="n">
-        <v>410.17</v>
+        <v>410.67</v>
       </c>
       <c r="F169" s="10" t="n">
-        <v>404.05</v>
+        <v>404.14</v>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
@@ -8150,20 +8150,20 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>826.35</v>
+        <v>827.05</v>
       </c>
       <c r="D170" s="10" t="n">
-        <v>812.76</v>
+        <v>814.12</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>747.65</v>
+        <v>750.76</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>633.4299999999999</v>
+        <v>637.23</v>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
@@ -8194,20 +8194,20 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="10" t="n">
-        <v>446.5</v>
+        <v>439.2</v>
       </c>
       <c r="D171" s="10" t="n">
-        <v>449.94</v>
+        <v>448.92</v>
       </c>
       <c r="E171" s="10" t="n">
-        <v>453.08</v>
+        <v>452.54</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>460.57</v>
+        <v>460.72</v>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
@@ -8238,20 +8238,20 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="10" t="n">
-        <v>1185.8</v>
+        <v>1178</v>
       </c>
       <c r="D172" s="10" t="n">
-        <v>1146.31</v>
+        <v>1149.32</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>1101.03</v>
+        <v>1104.05</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>1039.53</v>
+        <v>1041.24</v>
       </c>
       <c r="G172" s="13" t="inlineStr">
         <is>
@@ -8282,20 +8282,20 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>183.11</v>
+        <v>181.71</v>
       </c>
       <c r="D173" s="10" t="n">
-        <v>202.56</v>
+        <v>200.57</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>215.21</v>
+        <v>213.89</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>229.37</v>
+        <v>228.34</v>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
@@ -8326,24 +8326,24 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="10" t="n">
-        <v>574.1</v>
+        <v>557.6</v>
       </c>
       <c r="D174" s="10" t="n">
-        <v>563.38</v>
+        <v>562.83</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>517.55</v>
+        <v>519.13</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>513.88</v>
-      </c>
-      <c r="G174" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>516.53</v>
+      </c>
+      <c r="G174" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H174" s="13" t="inlineStr">
@@ -8370,20 +8370,20 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="10" t="n">
-        <v>569.3</v>
+        <v>560.45</v>
       </c>
       <c r="D175" s="10" t="n">
-        <v>572.25</v>
+        <v>571.12</v>
       </c>
       <c r="E175" s="10" t="n">
-        <v>553.92</v>
+        <v>554.17</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>506.94</v>
+        <v>508.31</v>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
@@ -8414,20 +8414,20 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="10" t="n">
-        <v>156.29</v>
+        <v>154.78</v>
       </c>
       <c r="D176" s="10" t="n">
-        <v>157.71</v>
+        <v>157.43</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>159.17</v>
+        <v>159</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>157.47</v>
+        <v>157.05</v>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
@@ -8458,20 +8458,20 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="10" t="n">
-        <v>180.77</v>
+        <v>183.49</v>
       </c>
       <c r="D177" s="10" t="n">
-        <v>189.76</v>
+        <v>189.16</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>198.5</v>
+        <v>197.91</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>248.96</v>
+        <v>248.61</v>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
@@ -8502,20 +8502,20 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="10" t="n">
-        <v>1495.3</v>
+        <v>1482.5</v>
       </c>
       <c r="D178" s="10" t="n">
-        <v>1350.85</v>
+        <v>1363.39</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>1263.16</v>
+        <v>1271.77</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>1060.74</v>
+        <v>1066.81</v>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="10" t="n">
-        <v>257.08</v>
+        <v>255.45</v>
       </c>
       <c r="D179" s="10" t="n">
-        <v>242.03</v>
+        <v>243.31</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>244.19</v>
+        <v>244.63</v>
       </c>
       <c r="F179" s="10" t="n">
-        <v>241.2</v>
+        <v>241.17</v>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
@@ -8590,20 +8590,20 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="10" t="n">
-        <v>383.5</v>
+        <v>380.2</v>
       </c>
       <c r="D180" s="10" t="n">
-        <v>388.53</v>
+        <v>387.73</v>
       </c>
       <c r="E180" s="10" t="n">
-        <v>368.13</v>
+        <v>368.6</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>325.48</v>
+        <v>326.02</v>
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
@@ -8634,20 +8634,20 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="10" t="n">
-        <v>28.38</v>
+        <v>27.64</v>
       </c>
       <c r="D181" s="10" t="n">
-        <v>28.84</v>
+        <v>28.72</v>
       </c>
       <c r="E181" s="10" t="n">
-        <v>29.78</v>
+        <v>29.69</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>35.2</v>
+        <v>35.28</v>
       </c>
       <c r="G181" s="11" t="inlineStr">
         <is>
@@ -8678,17 +8678,17 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="10" t="n">
-        <v>7.36</v>
+        <v>7.32</v>
       </c>
       <c r="D182" s="10" t="n">
-        <v>7.87</v>
+        <v>7.82</v>
       </c>
       <c r="E182" s="10" t="n">
-        <v>8.34</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F182" s="10" t="n">
         <v>9.220000000000001</v>
@@ -8722,20 +8722,20 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="10" t="n">
-        <v>615.75</v>
+        <v>617.95</v>
       </c>
       <c r="D183" s="10" t="n">
-        <v>666.1799999999999</v>
+        <v>661.59</v>
       </c>
       <c r="E183" s="10" t="n">
-        <v>672.16</v>
+        <v>670.03</v>
       </c>
       <c r="F183" s="10" t="n">
-        <v>630.61</v>
+        <v>630.48</v>
       </c>
       <c r="G183" s="11" t="inlineStr">
         <is>
@@ -8766,20 +8766,20 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="10" t="n">
-        <v>275.65</v>
+        <v>276.1</v>
       </c>
       <c r="D184" s="10" t="n">
-        <v>282.43</v>
+        <v>281.82</v>
       </c>
       <c r="E184" s="10" t="n">
-        <v>309.53</v>
+        <v>308.22</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>356.36</v>
+        <v>354.73</v>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8810,20 +8810,20 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="10" t="n">
-        <v>744.1</v>
+        <v>732.3</v>
       </c>
       <c r="D185" s="10" t="n">
-        <v>772.0700000000001</v>
+        <v>768.29</v>
       </c>
       <c r="E185" s="10" t="n">
-        <v>805.1900000000001</v>
+        <v>802.33</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>905.42</v>
+        <v>900.92</v>
       </c>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8854,20 +8854,20 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="10" t="n">
-        <v>13602</v>
+        <v>13493</v>
       </c>
       <c r="D186" s="10" t="n">
-        <v>13471.58</v>
+        <v>13473.62</v>
       </c>
       <c r="E186" s="10" t="n">
-        <v>13230.67</v>
+        <v>13240.96</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>13257.87</v>
+        <v>13278.53</v>
       </c>
       <c r="G186" s="13" t="inlineStr">
         <is>
@@ -8898,20 +8898,20 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="10" t="n">
-        <v>341.2</v>
+        <v>340.45</v>
       </c>
       <c r="D187" s="10" t="n">
-        <v>336.67</v>
+        <v>337.03</v>
       </c>
       <c r="E187" s="10" t="n">
-        <v>336.24</v>
+        <v>336.41</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>326.56</v>
+        <v>328.22</v>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
@@ -8942,20 +8942,20 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="10" t="n">
-        <v>57.53</v>
+        <v>59.1</v>
       </c>
       <c r="D188" s="10" t="n">
-        <v>61.34</v>
+        <v>61.13</v>
       </c>
       <c r="E188" s="10" t="n">
-        <v>61.74</v>
+        <v>61.64</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>66.25</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
@@ -8986,20 +8986,20 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="10" t="n">
-        <v>1366.3</v>
+        <v>1388.9</v>
       </c>
       <c r="D189" s="10" t="n">
-        <v>1356.92</v>
+        <v>1359.97</v>
       </c>
       <c r="E189" s="10" t="n">
-        <v>1270.47</v>
+        <v>1275.11</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>1099.96</v>
+        <v>1101.36</v>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
@@ -9030,20 +9030,20 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="10" t="n">
-        <v>887.35</v>
+        <v>868.15</v>
       </c>
       <c r="D190" s="10" t="n">
-        <v>890.79</v>
+        <v>888.64</v>
       </c>
       <c r="E190" s="10" t="n">
-        <v>914.3200000000001</v>
+        <v>912.51</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>992.9400000000001</v>
+        <v>991.98</v>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
@@ -9074,20 +9074,20 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="10" t="n">
-        <v>764.9</v>
+        <v>756.3</v>
       </c>
       <c r="D191" s="10" t="n">
-        <v>803.2</v>
+        <v>798.73</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>814.48</v>
+        <v>812.2</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>790.09</v>
+        <v>789.54</v>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -9118,20 +9118,20 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="10" t="n">
-        <v>858.8</v>
+        <v>862.65</v>
       </c>
       <c r="D192" s="10" t="n">
-        <v>828.24</v>
+        <v>831.52</v>
       </c>
       <c r="E192" s="10" t="n">
-        <v>776.46</v>
+        <v>779.84</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>745.3200000000001</v>
+        <v>747.16</v>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
@@ -9162,20 +9162,20 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="10" t="n">
-        <v>124.66</v>
+        <v>122.75</v>
       </c>
       <c r="D193" s="10" t="n">
-        <v>124.81</v>
+        <v>124.61</v>
       </c>
       <c r="E193" s="10" t="n">
-        <v>126.95</v>
+        <v>126.78</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>140.43</v>
+        <v>139.76</v>
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
@@ -9206,20 +9206,20 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="10" t="n">
-        <v>299.5</v>
+        <v>294</v>
       </c>
       <c r="D194" s="10" t="n">
-        <v>302.27</v>
+        <v>301.48</v>
       </c>
       <c r="E194" s="10" t="n">
-        <v>305.73</v>
+        <v>305.27</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>339.1</v>
+        <v>339.29</v>
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -9250,20 +9250,20 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="10" t="n">
-        <v>3002.5</v>
+        <v>3016.1</v>
       </c>
       <c r="D195" s="10" t="n">
-        <v>2865.23</v>
+        <v>2879.6</v>
       </c>
       <c r="E195" s="10" t="n">
-        <v>2748.27</v>
+        <v>2758.77</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>2567.68</v>
+        <v>2572.14</v>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
@@ -9294,20 +9294,20 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="10" t="n">
-        <v>2792.8</v>
+        <v>2746.6</v>
       </c>
       <c r="D196" s="10" t="n">
-        <v>2825.2</v>
+        <v>2817.71</v>
       </c>
       <c r="E196" s="10" t="n">
-        <v>2722.33</v>
+        <v>2723.28</v>
       </c>
       <c r="F196" s="10" t="n">
-        <v>2605.26</v>
+        <v>2607.85</v>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
@@ -9338,20 +9338,20 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="10" t="n">
-        <v>813.6</v>
+        <v>783.5</v>
       </c>
       <c r="D197" s="10" t="n">
-        <v>670.87</v>
+        <v>681.6</v>
       </c>
       <c r="E197" s="10" t="n">
-        <v>623.0599999999999</v>
+        <v>629.35</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>550.34</v>
+        <v>553.17</v>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
@@ -9382,20 +9382,20 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="10" t="n">
-        <v>666.95</v>
+        <v>675.35</v>
       </c>
       <c r="D198" s="10" t="n">
-        <v>685.6799999999999</v>
+        <v>684.7</v>
       </c>
       <c r="E198" s="10" t="n">
-        <v>684.01</v>
+        <v>683.67</v>
       </c>
       <c r="F198" s="10" t="n">
-        <v>626.9400000000001</v>
+        <v>627.42</v>
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -9426,20 +9426,20 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="10" t="n">
-        <v>342</v>
+        <v>338.95</v>
       </c>
       <c r="D199" s="10" t="n">
-        <v>354.62</v>
+        <v>353.13</v>
       </c>
       <c r="E199" s="10" t="n">
-        <v>362.42</v>
+        <v>361.5</v>
       </c>
       <c r="F199" s="10" t="n">
-        <v>426.73</v>
+        <v>425.93</v>
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
@@ -9470,20 +9470,20 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="10" t="n">
-        <v>1785.8</v>
+        <v>1770.6</v>
       </c>
       <c r="D200" s="10" t="n">
-        <v>1846.84</v>
+        <v>1839.58</v>
       </c>
       <c r="E200" s="10" t="n">
-        <v>1940.19</v>
+        <v>1933.54</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>2048.13</v>
+        <v>2041.96</v>
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
@@ -9514,20 +9514,20 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="10" t="n">
-        <v>166.75</v>
+        <v>167.39</v>
       </c>
       <c r="D201" s="10" t="n">
-        <v>169.9</v>
+        <v>169.66</v>
       </c>
       <c r="E201" s="10" t="n">
-        <v>178.37</v>
+        <v>177.94</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>192.86</v>
+        <v>192.89</v>
       </c>
       <c r="G201" s="11" t="inlineStr">
         <is>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="10" t="n">
-        <v>120.43</v>
+        <v>118.81</v>
       </c>
       <c r="D202" s="10" t="n">
-        <v>123.72</v>
+        <v>123.25</v>
       </c>
       <c r="E202" s="10" t="n">
-        <v>126.76</v>
+        <v>126.45</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>127.64</v>
+        <v>127.25</v>
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
@@ -9602,20 +9602,20 @@
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="10" t="n">
-        <v>194.2</v>
+        <v>194.28</v>
       </c>
       <c r="D203" s="10" t="n">
-        <v>199.41</v>
+        <v>198.92</v>
       </c>
       <c r="E203" s="10" t="n">
-        <v>202.28</v>
+        <v>201.96</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>210.11</v>
+        <v>209.85</v>
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
@@ -9646,24 +9646,24 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="10" t="n">
-        <v>813.55</v>
+        <v>801.45</v>
       </c>
       <c r="D204" s="10" t="n">
-        <v>811.84</v>
+        <v>810.85</v>
       </c>
       <c r="E204" s="10" t="n">
-        <v>834.01</v>
+        <v>832.74</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>830.1</v>
-      </c>
-      <c r="G204" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>829.41</v>
+      </c>
+      <c r="G204" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H204" s="11" t="inlineStr">
@@ -9690,20 +9690,20 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="10" t="n">
-        <v>115.55</v>
+        <v>115.5</v>
       </c>
       <c r="D205" s="10" t="n">
-        <v>116.54</v>
+        <v>116.44</v>
       </c>
       <c r="E205" s="10" t="n">
-        <v>119.81</v>
+        <v>119.64</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>138.5</v>
+        <v>138.38</v>
       </c>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9734,20 +9734,20 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="10" t="n">
-        <v>594.15</v>
+        <v>590.7</v>
       </c>
       <c r="D206" s="10" t="n">
-        <v>577.8200000000001</v>
+        <v>579.04</v>
       </c>
       <c r="E206" s="10" t="n">
-        <v>580.89</v>
+        <v>581.28</v>
       </c>
       <c r="F206" s="10" t="n">
-        <v>611.05</v>
+        <v>610.84</v>
       </c>
       <c r="G206" s="13" t="inlineStr">
         <is>
@@ -9778,20 +9778,20 @@
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="10" t="n">
-        <v>401</v>
+        <v>391.85</v>
       </c>
       <c r="D207" s="10" t="n">
-        <v>411.21</v>
+        <v>409.37</v>
       </c>
       <c r="E207" s="10" t="n">
-        <v>420.95</v>
+        <v>419.81</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>442.03</v>
+        <v>441.38</v>
       </c>
       <c r="G207" s="11" t="inlineStr">
         <is>
@@ -9822,20 +9822,20 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="10" t="n">
-        <v>126.99</v>
+        <v>134.9</v>
       </c>
       <c r="D208" s="10" t="n">
-        <v>123.47</v>
+        <v>124.56</v>
       </c>
       <c r="E208" s="10" t="n">
-        <v>125.51</v>
+        <v>125.88</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>136.45</v>
+        <v>136.36</v>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
@@ -9866,20 +9866,20 @@
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="10" t="n">
-        <v>158.63</v>
+        <v>157.16</v>
       </c>
       <c r="D209" s="10" t="n">
-        <v>160.42</v>
+        <v>160.11</v>
       </c>
       <c r="E209" s="10" t="n">
-        <v>163.98</v>
+        <v>163.71</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>174.78</v>
+        <v>174.36</v>
       </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
@@ -9910,20 +9910,20 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="10" t="n">
-        <v>111.65</v>
+        <v>112.52</v>
       </c>
       <c r="D210" s="10" t="n">
-        <v>107.06</v>
+        <v>107.58</v>
       </c>
       <c r="E210" s="10" t="n">
-        <v>105.34</v>
+        <v>105.63</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>114.15</v>
+        <v>114.67</v>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
@@ -9954,20 +9954,20 @@
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="10" t="n">
-        <v>1305.7</v>
+        <v>1313.6</v>
       </c>
       <c r="D211" s="10" t="n">
-        <v>1347.15</v>
+        <v>1343.95</v>
       </c>
       <c r="E211" s="10" t="n">
-        <v>1332.5</v>
+        <v>1331.76</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>1311.9</v>
+        <v>1320.05</v>
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
@@ -9998,20 +9998,20 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="10" t="n">
-        <v>129.68</v>
+        <v>126.56</v>
       </c>
       <c r="D212" s="10" t="n">
-        <v>131.33</v>
+        <v>130.87</v>
       </c>
       <c r="E212" s="10" t="n">
-        <v>133.77</v>
+        <v>133.49</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>157.33</v>
+        <v>156.86</v>
       </c>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -10042,20 +10042,20 @@
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>293.2</v>
+        <v>297.85</v>
       </c>
       <c r="D213" s="10" t="n">
-        <v>301.1</v>
+        <v>300.79</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>312.73</v>
+        <v>312.15</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>318.71</v>
+        <v>318.35</v>
       </c>
       <c r="G213" s="11" t="inlineStr">
         <is>
@@ -10086,20 +10086,20 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="10" t="n">
-        <v>260.8</v>
+        <v>255.2</v>
       </c>
       <c r="D214" s="10" t="n">
-        <v>265.51</v>
+        <v>264.53</v>
       </c>
       <c r="E214" s="10" t="n">
-        <v>278.45</v>
+        <v>277.54</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>355.65</v>
+        <v>355.45</v>
       </c>
       <c r="G214" s="11" t="inlineStr">
         <is>
@@ -10130,34 +10130,34 @@
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="10" t="n">
-        <v>808.2</v>
+        <v>799.55</v>
       </c>
       <c r="D215" s="10" t="n">
-        <v>819.73</v>
+        <v>817.8</v>
       </c>
       <c r="E215" s="10" t="n">
-        <v>808.1900000000001</v>
+        <v>807.85</v>
       </c>
       <c r="F215" s="10" t="n">
-        <v>802.08</v>
+        <v>802.3200000000001</v>
       </c>
       <c r="G215" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H215" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I215" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H215" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I215" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J215" s="12" t="inlineStr">
@@ -10174,20 +10174,20 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>1147.9</v>
+        <v>1235.7</v>
       </c>
       <c r="D216" s="10" t="n">
-        <v>1022.64</v>
+        <v>1042.93</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>944.29</v>
+        <v>955.72</v>
       </c>
       <c r="F216" s="10" t="n">
-        <v>942.9299999999999</v>
+        <v>945.5</v>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
@@ -10218,20 +10218,20 @@
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="10" t="n">
-        <v>83.70999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="D217" s="10" t="n">
-        <v>78.26000000000001</v>
+        <v>78.48</v>
       </c>
       <c r="E217" s="10" t="n">
-        <v>76.09</v>
+        <v>76.27</v>
       </c>
       <c r="F217" s="10" t="n">
-        <v>78.94</v>
+        <v>78.97</v>
       </c>
       <c r="G217" s="13" t="inlineStr">
         <is>
@@ -10262,20 +10262,20 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="10" t="n">
-        <v>128.85</v>
+        <v>127.77</v>
       </c>
       <c r="D218" s="10" t="n">
-        <v>130.34</v>
+        <v>130.09</v>
       </c>
       <c r="E218" s="10" t="n">
-        <v>139.31</v>
+        <v>138.85</v>
       </c>
       <c r="F218" s="10" t="n">
-        <v>166.39</v>
+        <v>166.4</v>
       </c>
       <c r="G218" s="11" t="inlineStr">
         <is>
@@ -10306,29 +10306,29 @@
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="10" t="n">
-        <v>1047.6</v>
+        <v>1076</v>
       </c>
       <c r="D219" s="10" t="n">
-        <v>1042.29</v>
+        <v>1045.5</v>
       </c>
       <c r="E219" s="10" t="n">
-        <v>1062.65</v>
+        <v>1063.17</v>
       </c>
       <c r="F219" s="10" t="n">
-        <v>1122.14</v>
+        <v>1121.55</v>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H219" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H219" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I219" s="11" t="inlineStr">
@@ -10350,24 +10350,24 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="10" t="n">
-        <v>247.1</v>
+        <v>248.95</v>
       </c>
       <c r="D220" s="10" t="n">
-        <v>247.33</v>
+        <v>247.49</v>
       </c>
       <c r="E220" s="10" t="n">
-        <v>240.7</v>
+        <v>241.03</v>
       </c>
       <c r="F220" s="10" t="n">
         <v>226.73</v>
       </c>
-      <c r="G220" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="G220" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H220" s="13" t="inlineStr">
@@ -10394,20 +10394,20 @@
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="10" t="n">
-        <v>1553.2</v>
+        <v>1546.6</v>
       </c>
       <c r="D221" s="10" t="n">
-        <v>1558.38</v>
+        <v>1557.26</v>
       </c>
       <c r="E221" s="10" t="n">
-        <v>1560.77</v>
+        <v>1560.21</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>1930.56</v>
+        <v>1932.33</v>
       </c>
       <c r="G221" s="11" t="inlineStr">
         <is>
@@ -10438,24 +10438,24 @@
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="10" t="n">
-        <v>623.5</v>
+        <v>626.95</v>
       </c>
       <c r="D222" s="10" t="n">
-        <v>626.66</v>
+        <v>626.6900000000001</v>
       </c>
       <c r="E222" s="10" t="n">
-        <v>635.45</v>
+        <v>635.12</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>633.96</v>
-      </c>
-      <c r="G222" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>634.09</v>
+      </c>
+      <c r="G222" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H222" s="11" t="inlineStr">
@@ -10482,17 +10482,17 @@
       </c>
       <c r="B223" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="10" t="n">
-        <v>24.04</v>
+        <v>25.15</v>
       </c>
       <c r="D223" s="10" t="n">
-        <v>23.82</v>
+        <v>23.95</v>
       </c>
       <c r="E223" s="10" t="n">
-        <v>23.42</v>
+        <v>23.49</v>
       </c>
       <c r="F223" s="10" t="n">
         <v>25.07</v>
@@ -10507,9 +10507,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I223" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I223" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J223" s="12" t="inlineStr">
@@ -10526,20 +10526,20 @@
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="10" t="n">
-        <v>644.85</v>
+        <v>665.5</v>
       </c>
       <c r="D224" s="10" t="n">
-        <v>609.71</v>
+        <v>615.02</v>
       </c>
       <c r="E224" s="10" t="n">
-        <v>585.49</v>
+        <v>588.62</v>
       </c>
       <c r="F224" s="10" t="n">
-        <v>590.34</v>
+        <v>591.78</v>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="10" t="n">
-        <v>423.75</v>
+        <v>406.2</v>
       </c>
       <c r="D225" s="10" t="n">
-        <v>431.06</v>
+        <v>428.69</v>
       </c>
       <c r="E225" s="10" t="n">
-        <v>442.79</v>
+        <v>441.35</v>
       </c>
       <c r="F225" s="10" t="n">
-        <v>489.38</v>
+        <v>488.17</v>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -10614,20 +10614,20 @@
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="10" t="n">
-        <v>216.49</v>
+        <v>215.81</v>
       </c>
       <c r="D226" s="10" t="n">
-        <v>222.24</v>
+        <v>221.62</v>
       </c>
       <c r="E226" s="10" t="n">
-        <v>230.86</v>
+        <v>230.27</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>246.21</v>
+        <v>245.95</v>
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -10658,20 +10658,20 @@
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="10" t="n">
-        <v>514.1</v>
+        <v>518.25</v>
       </c>
       <c r="D227" s="10" t="n">
-        <v>506.82</v>
+        <v>507.91</v>
       </c>
       <c r="E227" s="10" t="n">
-        <v>496.83</v>
+        <v>497.67</v>
       </c>
       <c r="F227" s="10" t="n">
-        <v>470.95</v>
+        <v>470.63</v>
       </c>
       <c r="G227" s="13" t="inlineStr">
         <is>
@@ -10702,29 +10702,29 @@
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="10" t="n">
-        <v>111.12</v>
+        <v>112.21</v>
       </c>
       <c r="D228" s="10" t="n">
-        <v>110.03</v>
+        <v>110.24</v>
       </c>
       <c r="E228" s="10" t="n">
-        <v>111.59</v>
+        <v>111.61</v>
       </c>
       <c r="F228" s="10" t="n">
-        <v>122.86</v>
+        <v>122.66</v>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H228" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H228" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I228" s="11" t="inlineStr">
@@ -10746,20 +10746,20 @@
       </c>
       <c r="B229" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="10" t="n">
-        <v>230.72</v>
+        <v>223.02</v>
       </c>
       <c r="D229" s="10" t="n">
-        <v>216.5</v>
+        <v>217.12</v>
       </c>
       <c r="E229" s="10" t="n">
-        <v>216.46</v>
+        <v>216.71</v>
       </c>
       <c r="F229" s="10" t="n">
-        <v>224.37</v>
+        <v>223.58</v>
       </c>
       <c r="G229" s="13" t="inlineStr">
         <is>
@@ -10771,9 +10771,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I229" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I229" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J229" s="12" t="inlineStr">
@@ -10790,20 +10790,20 @@
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="10" t="n">
-        <v>2020.9</v>
+        <v>1986.3</v>
       </c>
       <c r="D230" s="10" t="n">
-        <v>1983.02</v>
+        <v>1983.33</v>
       </c>
       <c r="E230" s="10" t="n">
-        <v>1906.75</v>
+        <v>1909.87</v>
       </c>
       <c r="F230" s="10" t="n">
-        <v>1766.03</v>
+        <v>1770.66</v>
       </c>
       <c r="G230" s="13" t="inlineStr">
         <is>
@@ -10834,20 +10834,20 @@
       </c>
       <c r="B231" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="10" t="n">
-        <v>688.1</v>
+        <v>688.95</v>
       </c>
       <c r="D231" s="10" t="n">
-        <v>631.12</v>
+        <v>636.63</v>
       </c>
       <c r="E231" s="10" t="n">
-        <v>611.24</v>
+        <v>614.29</v>
       </c>
       <c r="F231" s="10" t="n">
-        <v>599.04</v>
+        <v>599.95</v>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
@@ -10878,20 +10878,20 @@
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="10" t="n">
-        <v>160.29</v>
+        <v>162.15</v>
       </c>
       <c r="D232" s="10" t="n">
-        <v>173.13</v>
+        <v>172.09</v>
       </c>
       <c r="E232" s="10" t="n">
-        <v>184</v>
+        <v>183.15</v>
       </c>
       <c r="F232" s="10" t="n">
-        <v>218.51</v>
+        <v>217.95</v>
       </c>
       <c r="G232" s="11" t="inlineStr">
         <is>
@@ -10922,20 +10922,20 @@
       </c>
       <c r="B233" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="10" t="n">
-        <v>5787.5</v>
+        <v>5743.5</v>
       </c>
       <c r="D233" s="10" t="n">
-        <v>5814</v>
+        <v>5807.28</v>
       </c>
       <c r="E233" s="10" t="n">
-        <v>5906.88</v>
+        <v>5900.48</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>5738.62</v>
+        <v>5740.53</v>
       </c>
       <c r="G233" s="11" t="inlineStr">
         <is>
@@ -10966,29 +10966,29 @@
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="10" t="n">
-        <v>331.15</v>
+        <v>342.1</v>
       </c>
       <c r="D234" s="10" t="n">
-        <v>338.72</v>
+        <v>339.04</v>
       </c>
       <c r="E234" s="10" t="n">
-        <v>339.97</v>
+        <v>340.05</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>389.79</v>
-      </c>
-      <c r="G234" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H234" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>389.42</v>
+      </c>
+      <c r="G234" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H234" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I234" s="11" t="inlineStr">
@@ -11010,20 +11010,20 @@
       </c>
       <c r="B235" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="10" t="n">
-        <v>27.82</v>
+        <v>28.14</v>
       </c>
       <c r="D235" s="10" t="n">
-        <v>29.97</v>
+        <v>29.79</v>
       </c>
       <c r="E235" s="10" t="n">
-        <v>31.28</v>
+        <v>31.15</v>
       </c>
       <c r="F235" s="10" t="n">
-        <v>35.73</v>
+        <v>35.68</v>
       </c>
       <c r="G235" s="11" t="inlineStr">
         <is>
@@ -11054,24 +11054,24 @@
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="10" t="n">
-        <v>190.19</v>
+        <v>194.4</v>
       </c>
       <c r="D236" s="10" t="n">
-        <v>192.37</v>
+        <v>192.57</v>
       </c>
       <c r="E236" s="10" t="n">
-        <v>199.22</v>
+        <v>199.03</v>
       </c>
       <c r="F236" s="10" t="n">
-        <v>213.01</v>
-      </c>
-      <c r="G236" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>212.84</v>
+      </c>
+      <c r="G236" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H236" s="11" t="inlineStr">
@@ -11098,29 +11098,29 @@
       </c>
       <c r="B237" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="10" t="n">
-        <v>130.41</v>
+        <v>129.05</v>
       </c>
       <c r="D237" s="10" t="n">
-        <v>128.83</v>
+        <v>128.85</v>
       </c>
       <c r="E237" s="10" t="n">
-        <v>129.49</v>
+        <v>129.47</v>
       </c>
       <c r="F237" s="10" t="n">
-        <v>123.7</v>
+        <v>123.5</v>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H237" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H237" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I237" s="13" t="inlineStr">
@@ -11142,20 +11142,20 @@
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="10" t="n">
-        <v>7.83</v>
+        <v>7.6</v>
       </c>
       <c r="D238" s="10" t="n">
-        <v>9.960000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="E238" s="10" t="n">
-        <v>11.19</v>
+        <v>11.05</v>
       </c>
       <c r="F238" s="10" t="n">
-        <v>13.57</v>
+        <v>13.49</v>
       </c>
       <c r="G238" s="11" t="inlineStr">
         <is>
@@ -11186,20 +11186,20 @@
       </c>
       <c r="B239" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="10" t="n">
-        <v>102.57</v>
+        <v>100.88</v>
       </c>
       <c r="D239" s="10" t="n">
-        <v>106.66</v>
+        <v>106.11</v>
       </c>
       <c r="E239" s="10" t="n">
-        <v>109.99</v>
+        <v>109.63</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>121.28</v>
+        <v>121.58</v>
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
@@ -11230,20 +11230,20 @@
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="10" t="n">
-        <v>314.05</v>
+        <v>320.5</v>
       </c>
       <c r="D240" s="10" t="n">
-        <v>306.68</v>
+        <v>307.99</v>
       </c>
       <c r="E240" s="10" t="n">
-        <v>306.61</v>
+        <v>307.16</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>330.25</v>
+        <v>330.41</v>
       </c>
       <c r="G240" s="13" t="inlineStr">
         <is>
@@ -11274,20 +11274,20 @@
       </c>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="10" t="n">
-        <v>482</v>
+        <v>488.7</v>
       </c>
       <c r="D241" s="10" t="n">
-        <v>504.38</v>
+        <v>502.89</v>
       </c>
       <c r="E241" s="10" t="n">
-        <v>528.15</v>
+        <v>526.61</v>
       </c>
       <c r="F241" s="10" t="n">
-        <v>630.91</v>
+        <v>630.37</v>
       </c>
       <c r="G241" s="11" t="inlineStr">
         <is>
@@ -11318,20 +11318,20 @@
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="10" t="n">
-        <v>69.73</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="D242" s="10" t="n">
-        <v>68.19</v>
+        <v>68.34</v>
       </c>
       <c r="E242" s="10" t="n">
-        <v>67.29000000000001</v>
+        <v>67.38</v>
       </c>
       <c r="F242" s="10" t="n">
-        <v>72.65000000000001</v>
+        <v>72.58</v>
       </c>
       <c r="G242" s="13" t="inlineStr">
         <is>
@@ -11362,20 +11362,20 @@
       </c>
       <c r="B243" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="10" t="n">
-        <v>1540.4</v>
+        <v>1537.8</v>
       </c>
       <c r="D243" s="10" t="n">
-        <v>1514.82</v>
+        <v>1517.01</v>
       </c>
       <c r="E243" s="10" t="n">
-        <v>1537.51</v>
+        <v>1537.52</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>1710.01</v>
+        <v>1709.99</v>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
@@ -11406,20 +11406,20 @@
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="10" t="n">
-        <v>126.55</v>
+        <v>125.08</v>
       </c>
       <c r="D244" s="10" t="n">
-        <v>130.32</v>
+        <v>129.82</v>
       </c>
       <c r="E244" s="10" t="n">
-        <v>133.51</v>
+        <v>133.18</v>
       </c>
       <c r="F244" s="10" t="n">
-        <v>136.74</v>
+        <v>136.45</v>
       </c>
       <c r="G244" s="11" t="inlineStr">
         <is>
@@ -11450,20 +11450,20 @@
       </c>
       <c r="B245" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="10" t="n">
-        <v>70.51000000000001</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="D245" s="10" t="n">
-        <v>71.04000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="E245" s="10" t="n">
-        <v>72.11</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="F245" s="10" t="n">
-        <v>77.76000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="G245" s="11" t="inlineStr">
         <is>
@@ -11494,20 +11494,20 @@
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="10" t="n">
-        <v>748.45</v>
+        <v>739.3</v>
       </c>
       <c r="D246" s="10" t="n">
-        <v>757.35</v>
+        <v>755.63</v>
       </c>
       <c r="E246" s="10" t="n">
-        <v>763.7</v>
+        <v>762.75</v>
       </c>
       <c r="F246" s="10" t="n">
-        <v>764.42</v>
+        <v>764.4</v>
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -11538,20 +11538,20 @@
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="10" t="n">
-        <v>404.7</v>
+        <v>403.6</v>
       </c>
       <c r="D247" s="10" t="n">
-        <v>414.79</v>
+        <v>413.73</v>
       </c>
       <c r="E247" s="10" t="n">
-        <v>422.86</v>
+        <v>422.1</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>426.51</v>
+        <v>428.15</v>
       </c>
       <c r="G247" s="11" t="inlineStr">
         <is>
@@ -11582,20 +11582,20 @@
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="10" t="n">
-        <v>599.05</v>
+        <v>597.05</v>
       </c>
       <c r="D248" s="10" t="n">
-        <v>679.47</v>
+        <v>671.62</v>
       </c>
       <c r="E248" s="10" t="n">
-        <v>747.33</v>
+        <v>741.4400000000001</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>824.0599999999999</v>
+        <v>822.03</v>
       </c>
       <c r="G248" s="11" t="inlineStr">
         <is>
@@ -11626,20 +11626,20 @@
       </c>
       <c r="B249" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="10" t="n">
-        <v>4201.7</v>
+        <v>4106</v>
       </c>
       <c r="D249" s="10" t="n">
-        <v>4274.12</v>
+        <v>4258.1</v>
       </c>
       <c r="E249" s="10" t="n">
-        <v>4407.89</v>
+        <v>4396.05</v>
       </c>
       <c r="F249" s="10" t="n">
-        <v>4524.65</v>
+        <v>4535.5</v>
       </c>
       <c r="G249" s="11" t="inlineStr">
         <is>
@@ -11670,20 +11670,20 @@
       </c>
       <c r="B250" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="10" t="n">
-        <v>709.6</v>
+        <v>704.75</v>
       </c>
       <c r="D250" s="10" t="n">
-        <v>737.46</v>
+        <v>734.34</v>
       </c>
       <c r="E250" s="10" t="n">
-        <v>760.49</v>
+        <v>758.3</v>
       </c>
       <c r="F250" s="10" t="n">
-        <v>788.9</v>
+        <v>788.46</v>
       </c>
       <c r="G250" s="11" t="inlineStr">
         <is>
@@ -11714,24 +11714,24 @@
       </c>
       <c r="B251" s="10" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="10" t="n">
-        <v>424.4</v>
+        <v>421</v>
       </c>
       <c r="D251" s="10" t="n">
-        <v>422.49</v>
+        <v>422.35</v>
       </c>
       <c r="E251" s="10" t="n">
-        <v>431.45</v>
+        <v>431.04</v>
       </c>
       <c r="F251" s="10" t="n">
-        <v>433.97</v>
-      </c>
-      <c r="G251" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>433.84</v>
+      </c>
+      <c r="G251" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H251" s="11" t="inlineStr">

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 07-Sep-2026  16:15:56    |    Closing Price Date: 07-Sep-2026</t>
+          <t>Scan Run: 08-Sep-2026  14:52:08    |    Closing Price Date: 08-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -591,14 +591,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46.4</v>
+        <v>44.8</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>56.8</v>
@@ -608,7 +608,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>07-Sep-2026  16:15:56</t>
+          <t>08-Sep-2026  14:52:08</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): NEUTRAL — 46.4% stocks above EMA (mixed market)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.8% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 51.6% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 50.4% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -650,14 +650,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 116 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 112 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 129 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 126 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>247.22</v>
+        <v>251.49</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>258.63</v>
+        <v>259.04</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>269.02</v>
+        <v>269.18</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>298.57</v>
+        <v>298.61</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,24 +802,24 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>332.55</v>
+        <v>330.05</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>332.13</v>
+        <v>331.89</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>322.59</v>
+        <v>322.49</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>324.95</v>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>324.92</v>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>6393.5</v>
+        <v>6313.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>5425.17</v>
+        <v>5509.77</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>4962.65</v>
+        <v>5015.62</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>4154.32</v>
+        <v>4175.8</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>734.15</v>
+        <v>768.8</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>723.47</v>
+        <v>727.78</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>671.72</v>
+        <v>675.53</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>535.1</v>
+        <v>537.4299999999999</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>280.95</v>
+        <v>274.8</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>274.78</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>245.48</v>
+        <v>246.63</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>156.08</v>
+        <v>157.27</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>332.6</v>
+        <v>336.25</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>337.38</v>
+        <v>337.73</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>306.53</v>
+        <v>306.68</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>216.49</v>
+        <v>216.52</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7519</v>
+        <v>7799.5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>6966.57</v>
+        <v>6993.29</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6811.54</v>
+        <v>6822.54</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>5361.58</v>
+        <v>5364.37</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>870</v>
+        <v>868.7</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>816.25</v>
+        <v>821.24</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>751.73</v>
+        <v>756.3099999999999</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>610.75</v>
+        <v>613.3200000000001</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1110,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>333.6</v>
+        <v>334.25</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>324.95</v>
+        <v>325.84</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>305.05</v>
+        <v>306.2</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>255.93</v>
+        <v>256.71</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1154,24 +1154,24 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>5474</v>
+        <v>5366.5</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>5442.67</v>
+        <v>5435.41</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>5500.86</v>
+        <v>5495.59</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4493.08</v>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>4501.77</v>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -1198,24 +1198,24 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>171.99</v>
+        <v>184.52</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>172.43</v>
+        <v>173.62</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>170.38</v>
+        <v>170.87</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>164.98</v>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>165.11</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2868</v>
+        <v>2822.1</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>2745.23</v>
+        <v>2752.55</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>2552.56</v>
+        <v>2563.13</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2100.63</v>
+        <v>2107.81</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,29 +1286,29 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>583.6</v>
+        <v>573.4</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>586.08</v>
+        <v>584.87</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>575.4</v>
+        <v>575.3200000000001</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>570.78</v>
+        <v>570.8</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>2352.5</v>
+        <v>2290.3</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>2159.55</v>
+        <v>2153.62</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1961.32</v>
+        <v>1958.88</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1466.51</v>
+        <v>1465.89</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,24 +1374,24 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>3382.6</v>
+        <v>3469.6</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3449.09</v>
+        <v>3457.38</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>3483.61</v>
+        <v>3487.02</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>3209.16</v>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3210.02</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>403.95</v>
+        <v>417.9</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>389.03</v>
+        <v>391.78</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>388.06</v>
+        <v>389.23</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>330.41</v>
+        <v>331.28</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1462,24 +1462,24 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>779.35</v>
+        <v>758.6</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>769.26</v>
+        <v>767.28</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>719.0700000000001</v>
+        <v>718.26</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>620.89</v>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>620.6799999999999</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>786.3</v>
+        <v>824.7</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>683.21</v>
+        <v>686.86</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>622.36</v>
+        <v>623.86</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>409.45</v>
+        <v>409.84</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>199.71</v>
+        <v>198.81</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>181.26</v>
+        <v>182.93</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>171.46</v>
+        <v>172.53</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>159.73</v>
+        <v>160.11</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>13.93</v>
+        <v>13.52</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>10.79</v>
+        <v>11.05</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>10.14</v>
+        <v>10.28</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>10.08</v>
+        <v>10.12</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>233.86</v>
+        <v>231.9</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>245.72</v>
+        <v>244.41</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>237.6</v>
+        <v>237.38</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>195.85</v>
+        <v>196.21</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>2008</v>
+        <v>2008.4</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>2010.48</v>
+        <v>2010.28</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1961.25</v>
+        <v>1963.1</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>1677.53</v>
+        <v>1680.83</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1726,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>231.69</v>
+        <v>233.15</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>235.99</v>
+        <v>236.13</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>229.86</v>
+        <v>229.92</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>206.85</v>
+        <v>206.87</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1770,17 +1770,17 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>65.09</v>
+        <v>64.86</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>67.63</v>
+        <v>67.61</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>66.52</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F25" s="10" t="n">
         <v>59.7</v>
@@ -1814,29 +1814,29 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>165.48</v>
+        <v>167.3</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>170.7</v>
+        <v>170.37</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>166.62</v>
+        <v>166.65</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>149.18</v>
+        <v>149.36</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>184.53</v>
+        <v>186.54</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>190.53</v>
+        <v>190.15</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>191.41</v>
+        <v>191.22</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>189.89</v>
+        <v>189.86</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>520.2</v>
+        <v>512.95</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>549.0700000000001</v>
+        <v>545.63</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>556.1</v>
+        <v>554.4</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>542.76</v>
+        <v>542.46</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>339.6</v>
+        <v>337.5</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>349.53</v>
+        <v>348.39</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>319.48</v>
+        <v>320.19</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>259.72</v>
+        <v>260.49</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>1489.4</v>
+        <v>1504</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1412.36</v>
+        <v>1413.75</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>1314.9</v>
+        <v>1315.48</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1009.53</v>
+        <v>1009.67</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>370.3</v>
+        <v>368.4</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>358.17</v>
+        <v>357.99</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>337.5</v>
+        <v>337.43</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>300.11</v>
+        <v>300.09</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>533.25</v>
+        <v>540.35</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>543.35</v>
+        <v>544.03</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>511.63</v>
+        <v>511.91</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>464.98</v>
+        <v>465.05</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2122,24 +2122,24 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>1619.5</v>
+        <v>1642.9</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1628.6</v>
+        <v>1630.83</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>1531.29</v>
+        <v>1532.21</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>1225.54</v>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1225.77</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>788.15</v>
+        <v>820</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>774.1900000000001</v>
+        <v>778.5599999999999</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>706.86</v>
+        <v>711.29</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>523.1799999999999</v>
+        <v>526.13</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>618.95</v>
+        <v>627.45</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>606.75</v>
+        <v>608.72</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>606.41</v>
+        <v>607.24</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>596.4</v>
+        <v>596.71</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2254,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>538.5</v>
+        <v>539.8</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>545.3099999999999</v>
+        <v>544.78</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>530.92</v>
+        <v>531.27</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>477.3</v>
+        <v>477.93</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2298,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>195.17</v>
+        <v>196.57</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>201.25</v>
+        <v>200.81</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>203.84</v>
+        <v>203.55</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>203.22</v>
+        <v>203.16</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>786.55</v>
+        <v>837.15</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>840.01</v>
+        <v>839.74</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>905.0700000000001</v>
+        <v>902.41</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>983.17</v>
+        <v>981.72</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>538.15</v>
+        <v>549.35</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>588.09</v>
+        <v>584.4</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>626.14</v>
+        <v>623.13</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>629.61</v>
+        <v>628.8099999999999</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>365.1</v>
+        <v>361.85</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>358.81</v>
+        <v>358.5</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>359.25</v>
+        <v>359.12</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>344.57</v>
+        <v>344.54</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>211.38</v>
+        <v>217.81</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>207.85</v>
+        <v>208.47</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>204.42</v>
+        <v>204.67</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>172.05</v>
+        <v>172.12</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>83.19</v>
+        <v>81.81</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>87.19</v>
+        <v>87.06</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>86.13</v>
+        <v>86.08</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>71.69</v>
+        <v>71.67</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,17 +2562,17 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>230.65</v>
+        <v>230.35</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>233.44</v>
+        <v>233.42</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>220.67</v>
+        <v>220.66</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>217.04</v>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1711.6</v>
+        <v>1757.3</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1703.54</v>
+        <v>1708.66</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1677.85</v>
+        <v>1680.97</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1372.91</v>
+        <v>1376.73</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>343.5</v>
+        <v>345.65</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>389.53</v>
+        <v>385.35</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>387.26</v>
+        <v>385.63</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>408.52</v>
+        <v>407.89</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,29 +2694,29 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>573.15</v>
+        <v>569.45</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>586.67</v>
+        <v>586.3200000000001</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>570.79</v>
+        <v>570.65</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>489.64</v>
+        <v>489.6</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
@@ -2738,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>165.81</v>
+        <v>169.28</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>171.06</v>
+        <v>170.89</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>178.09</v>
+        <v>177.75</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>214.85</v>
+        <v>214.39</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1239.8</v>
+        <v>1221.7</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1194.5</v>
+        <v>1197.09</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1105.94</v>
+        <v>1110.48</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1019.33</v>
+        <v>1021.34</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>936.45</v>
+        <v>926.8</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>892.86</v>
+        <v>891.9400000000001</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>847.47</v>
+        <v>847.09</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>702.36</v>
+        <v>702.27</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>172.28</v>
+        <v>174.42</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>174.41</v>
+        <v>174.62</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>179.64</v>
+        <v>179.72</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>182</v>
+        <v>182.02</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>277.15</v>
+        <v>275.85</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>289.22</v>
+        <v>287.94</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>298.46</v>
+        <v>297.57</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>303.22</v>
+        <v>302.95</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
@@ -2958,20 +2958,20 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>513.65</v>
+        <v>503.35</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>526.99</v>
+        <v>524.74</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>547.37</v>
+        <v>545.64</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>542.6799999999999</v>
+        <v>542.28</v>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
@@ -3002,20 +3002,20 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>3896.3</v>
+        <v>4033.6</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>3805.06</v>
+        <v>3818.13</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>3562.88</v>
+        <v>3568.26</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>2726.74</v>
+        <v>2728.1</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
@@ -3046,29 +3046,29 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>533.05</v>
+        <v>538.25</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>554.6900000000001</v>
+        <v>555.1900000000001</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>535.55</v>
+        <v>535.76</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>528.29</v>
+        <v>528.35</v>
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H54" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
@@ -3090,20 +3090,20 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>1932.9</v>
+        <v>1922.8</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>2026.37</v>
+        <v>2025.41</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>2030.51</v>
+        <v>2030.12</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>1840.01</v>
+        <v>1839.91</v>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
@@ -3134,20 +3134,20 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>178.24</v>
+        <v>186.02</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>175.32</v>
+        <v>176.06</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>158.98</v>
+        <v>159.29</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>130.96</v>
+        <v>131.04</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
@@ -3178,20 +3178,20 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>604.4</v>
+        <v>604.7</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>553.48</v>
+        <v>558.28</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>541.03</v>
+        <v>543.4400000000001</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>493.92</v>
+        <v>494.94</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
@@ -3222,20 +3222,20 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>1691.7</v>
+        <v>1654.2</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1744.25</v>
+        <v>1735.67</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>1726.53</v>
+        <v>1723.69</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1796.48</v>
+        <v>1795.07</v>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
@@ -3266,17 +3266,17 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>155.77</v>
+        <v>155.61</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>159.04</v>
+        <v>159.02</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>163.89</v>
+        <v>163.88</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>170.73</v>
@@ -3310,20 +3310,20 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>3348.7</v>
+        <v>3407.8</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>3260.82</v>
+        <v>3274.81</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>3127.36</v>
+        <v>3138.36</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>2664.16</v>
+        <v>2671.56</v>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
@@ -3354,29 +3354,29 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>263.65</v>
+        <v>261.95</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>264.53</v>
+        <v>264.29</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>262.71</v>
+        <v>262.68</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>237.18</v>
+        <v>237.43</v>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H61" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I61" s="13" t="inlineStr">
@@ -3398,24 +3398,24 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>512.05</v>
+        <v>502.55</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>510.46</v>
+        <v>509.55</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>520.02</v>
+        <v>519.65</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>575.02</v>
-      </c>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>574.9299999999999</v>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
@@ -3442,20 +3442,20 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>577.75</v>
+        <v>582.2</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>574.1799999999999</v>
+        <v>574.61</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>564.0599999999999</v>
+        <v>564.24</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>521.22</v>
+        <v>521.27</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
@@ -3486,20 +3486,20 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>23.54</v>
+        <v>23.86</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>22.65</v>
+        <v>22.77</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>22.44</v>
+        <v>22.5</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>22.62</v>
+        <v>22.63</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
@@ -3530,20 +3530,20 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>198.33</v>
+        <v>196.2</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>200.31</v>
+        <v>199.92</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>205.62</v>
+        <v>205.25</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>205.12</v>
+        <v>205.04</v>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
@@ -3574,20 +3574,20 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>194.45</v>
+        <v>193.06</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>198.37</v>
+        <v>197.87</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>203.65</v>
+        <v>203.24</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>192.23</v>
+        <v>192.24</v>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -3618,20 +3618,20 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>698.75</v>
+        <v>694.25</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>686.4299999999999</v>
+        <v>686</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>665.53</v>
+        <v>665.35</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>653.45</v>
+        <v>653.41</v>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
@@ -3662,20 +3662,20 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>1778</v>
+        <v>1848.6</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>1641.59</v>
+        <v>1648.31</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>1641.38</v>
+        <v>1644.14</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1600.43</v>
+        <v>1601.13</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3706,24 +3706,24 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>672.9</v>
+        <v>696.85</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>692.86</v>
+        <v>693.24</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>720.39</v>
+        <v>719.47</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>833.1900000000001</v>
-      </c>
-      <c r="G69" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>831.83</v>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -3750,20 +3750,20 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>2231.4</v>
+        <v>2215.9</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>2067.66</v>
+        <v>2081.78</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>1961.34</v>
+        <v>1971.32</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1605.11</v>
+        <v>1611.19</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
@@ -3794,20 +3794,20 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>6951.5</v>
+        <v>6975.5</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>7109.64</v>
+        <v>7111.93</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>6899.15</v>
+        <v>6900.09</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>5489.48</v>
+        <v>5489.72</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -3838,20 +3838,20 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>46.54</v>
+        <v>46.82</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>46.04</v>
+        <v>46.12</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>45.49</v>
+        <v>45.54</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>41.43</v>
+        <v>41.48</v>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
@@ -3882,20 +3882,20 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>466.95</v>
+        <v>473</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>491.5</v>
+        <v>489.73</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>512.22</v>
+        <v>510.68</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>584.28</v>
+        <v>583.17</v>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
@@ -3926,20 +3926,20 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>155.34</v>
+        <v>153.05</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>142.75</v>
+        <v>143.73</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>136.11</v>
+        <v>136.78</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>150.28</v>
+        <v>150.31</v>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
@@ -3970,20 +3970,20 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>2566.8</v>
+        <v>2475.4</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>2323.83</v>
+        <v>2338.27</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>2198.4</v>
+        <v>2209.26</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1760.83</v>
+        <v>1767.94</v>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
@@ -4014,20 +4014,20 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>338.05</v>
+        <v>333.7</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>367.57</v>
+        <v>367.15</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>375.99</v>
+        <v>375.82</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>372.36</v>
+        <v>372.32</v>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
@@ -4058,24 +4058,24 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>767.45</v>
+        <v>795.9</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>785.87</v>
+        <v>786.83</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>823.51</v>
+        <v>822.42</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>888.8099999999999</v>
-      </c>
-      <c r="G77" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>887.88</v>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
@@ -4102,20 +4102,20 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>321.15</v>
+        <v>312.85</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>331.43</v>
+        <v>330.64</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>337.89</v>
+        <v>337.56</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>366.77</v>
+        <v>366.69</v>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
@@ -4146,20 +4146,20 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>2658.5</v>
+        <v>2803.8</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>2557.47</v>
+        <v>2571.31</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>2510.69</v>
+        <v>2516.39</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>2481.05</v>
+        <v>2482.5</v>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
@@ -4190,20 +4190,20 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>185.13</v>
+        <v>184.08</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>194.84</v>
+        <v>194.74</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>203.38</v>
+        <v>203.34</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>214.69</v>
+        <v>214.68</v>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
@@ -4234,17 +4234,17 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>160.98</v>
+        <v>160.58</v>
       </c>
       <c r="D81" s="10" t="n">
-        <v>159.03</v>
+        <v>158.99</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>154.37</v>
+        <v>154.35</v>
       </c>
       <c r="F81" s="10" t="n">
         <v>154.09</v>
@@ -4278,20 +4278,20 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>73.34999999999999</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>74.47</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>74.88</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>69.92</v>
+        <v>69.91</v>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
@@ -4322,20 +4322,20 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>205.87</v>
+        <v>203.27</v>
       </c>
       <c r="D83" s="10" t="n">
-        <v>202.2</v>
+        <v>202.3</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>207.45</v>
+        <v>207.28</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>184.09</v>
+        <v>184.28</v>
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
@@ -4366,20 +4366,20 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>597.9</v>
+        <v>589.1</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>576.5700000000001</v>
+        <v>577.77</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>553.03</v>
+        <v>554.45</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>512.23</v>
+        <v>512.99</v>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
@@ -4410,29 +4410,29 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>15.94</v>
+        <v>15.36</v>
       </c>
       <c r="D85" s="10" t="n">
-        <v>15.59</v>
+        <v>15.54</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>15.77</v>
+        <v>15.75</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="G85" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H85" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>16.08</v>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -4454,20 +4454,20 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>852.6</v>
+        <v>845.25</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>878.53</v>
+        <v>875.36</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>912.84</v>
+        <v>910.1900000000001</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>957.25</v>
+        <v>956.13</v>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
@@ -4498,20 +4498,20 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>2207.1</v>
+        <v>2213</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>2166.54</v>
+        <v>2167.1</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>2097.07</v>
+        <v>2097.3</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1772.28</v>
+        <v>1772.33</v>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
@@ -4542,20 +4542,20 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>643.7</v>
+        <v>644.9</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>652.33</v>
+        <v>652.45</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>657.22</v>
+        <v>657.27</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>620.88</v>
+        <v>620.9</v>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
@@ -4586,20 +4586,20 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
-        <v>1286.9</v>
+        <v>1306.7</v>
       </c>
       <c r="D89" s="10" t="n">
-        <v>1353.99</v>
+        <v>1355.88</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>1379.79</v>
+        <v>1380.57</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>1308.38</v>
+        <v>1308.58</v>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
@@ -4630,20 +4630,20 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>132.72</v>
+        <v>138.8</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>126.96</v>
+        <v>128.09</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>122.97</v>
+        <v>123.59</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>116.52</v>
+        <v>116.75</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -4674,20 +4674,20 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="10" t="n">
-        <v>586.25</v>
+        <v>579.55</v>
       </c>
       <c r="D91" s="10" t="n">
-        <v>539.6799999999999</v>
+        <v>539.05</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>494.11</v>
+        <v>493.85</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>496.69</v>
+        <v>496.62</v>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
@@ -4718,20 +4718,20 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>1748.4</v>
+        <v>1860.6</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1739.26</v>
+        <v>1750.82</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>1595.18</v>
+        <v>1605.59</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1158.26</v>
+        <v>1165.24</v>
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
@@ -4762,20 +4762,20 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="10" t="n">
-        <v>72.28</v>
+        <v>71.05</v>
       </c>
       <c r="D93" s="10" t="n">
-        <v>74.70999999999999</v>
+        <v>74.36</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>75.31</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>69.23</v>
+        <v>69.25</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
@@ -4806,20 +4806,20 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>335.05</v>
+        <v>335.9</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>317.58</v>
+        <v>317.66</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>292.27</v>
+        <v>292.3</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>238.56</v>
+        <v>238.57</v>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
@@ -4850,20 +4850,20 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="10" t="n">
-        <v>274.4</v>
+        <v>274.8</v>
       </c>
       <c r="D95" s="10" t="n">
-        <v>297.84</v>
+        <v>295.64</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>328.7</v>
+        <v>326.59</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>414.33</v>
+        <v>412.94</v>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
@@ -4894,20 +4894,20 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>564.5</v>
+        <v>581.35</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>546.58</v>
+        <v>549.89</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>531.67</v>
+        <v>533.62</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>447.87</v>
+        <v>449.2</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
@@ -4938,20 +4938,20 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>774.25</v>
+        <v>770.9</v>
       </c>
       <c r="D97" s="10" t="n">
-        <v>752.62</v>
+        <v>754.36</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>788.5599999999999</v>
+        <v>787.87</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>718.76</v>
+        <v>719.28</v>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
@@ -4982,20 +4982,20 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>239.02</v>
+        <v>236.58</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>250.24</v>
+        <v>250</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>262.78</v>
+        <v>262.69</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>306.45</v>
+        <v>306.43</v>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -5026,20 +5026,20 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>1832.4</v>
+        <v>1853.3</v>
       </c>
       <c r="D99" s="10" t="n">
-        <v>1890.12</v>
+        <v>1892.11</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>1876.85</v>
+        <v>1877.67</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>1782.99</v>
+        <v>1783.2</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -5070,20 +5070,20 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>221.31</v>
+        <v>229.55</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>208.32</v>
+        <v>210.34</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>197.75</v>
+        <v>198.99</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>181.3</v>
+        <v>181.78</v>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
@@ -5114,20 +5114,20 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>856.5</v>
+        <v>862.7</v>
       </c>
       <c r="D101" s="10" t="n">
-        <v>910.67</v>
+        <v>911.26</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>897.71</v>
+        <v>897.95</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>746.08</v>
+        <v>746.14</v>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -5158,20 +5158,20 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>420.05</v>
+        <v>415.3</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>395.07</v>
+        <v>397</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>383.09</v>
+        <v>384.35</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>366.09</v>
+        <v>366.58</v>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
@@ -5202,20 +5202,20 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>659.7</v>
+        <v>663.45</v>
       </c>
       <c r="D103" s="10" t="n">
-        <v>678.5</v>
+        <v>678.85</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>719.97</v>
+        <v>720.11</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>800.83</v>
+        <v>800.86</v>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
@@ -5246,20 +5246,20 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>11067</v>
+        <v>11365</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>10707.48</v>
+        <v>10735.86</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>10243.27</v>
+        <v>10254.95</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>9310.709999999999</v>
+        <v>9313.68</v>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
@@ -5290,24 +5290,24 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>760.15</v>
+        <v>745</v>
       </c>
       <c r="D105" s="10" t="n">
-        <v>747.74</v>
+        <v>746.3</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>768.67</v>
+        <v>768.08</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>715.53</v>
-      </c>
-      <c r="G105" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>715.38</v>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -5334,20 +5334,20 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>89.67</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>94.88</v>
+        <v>94.48</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>93.18000000000001</v>
+        <v>93.08</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>85.33</v>
+        <v>85.38</v>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
@@ -5378,20 +5378,20 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="10" t="n">
-        <v>1935.5</v>
+        <v>1955.9</v>
       </c>
       <c r="D107" s="10" t="n">
-        <v>1932.83</v>
+        <v>1935.03</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>1803.18</v>
+        <v>1809.17</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>1590.3</v>
+        <v>1593.94</v>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
@@ -5422,20 +5422,20 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>939.5</v>
+        <v>959.9</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>863.64</v>
+        <v>872.8099999999999</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>753.8</v>
+        <v>761.89</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>545.75</v>
+        <v>549.87</v>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
@@ -5466,20 +5466,20 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="10" t="n">
-        <v>1178.8</v>
+        <v>1187.4</v>
       </c>
       <c r="D109" s="10" t="n">
-        <v>1031.34</v>
+        <v>1046.2</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>1031.4</v>
+        <v>1037.52</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>989.51</v>
+        <v>991.48</v>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
@@ -5510,20 +5510,20 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>668.7</v>
+        <v>672.1</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>707.16</v>
+        <v>703.8200000000001</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>748.6900000000001</v>
+        <v>745.6900000000001</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>888.88</v>
+        <v>886.73</v>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
@@ -5554,20 +5554,20 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>453.7</v>
+        <v>450.85</v>
       </c>
       <c r="D111" s="10" t="n">
-        <v>432.93</v>
+        <v>432.66</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>411.86</v>
+        <v>411.75</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>341.58</v>
+        <v>341.55</v>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
@@ -5598,20 +5598,20 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>909.1</v>
+        <v>915.65</v>
       </c>
       <c r="D112" s="10" t="n">
-        <v>830.6900000000001</v>
+        <v>831.3099999999999</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>838.4400000000001</v>
+        <v>838.6900000000001</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>783.26</v>
+        <v>783.33</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -5642,20 +5642,20 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="10" t="n">
-        <v>439.1</v>
+        <v>431.75</v>
       </c>
       <c r="D113" s="10" t="n">
-        <v>387.18</v>
+        <v>391.42</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>390.85</v>
+        <v>392.45</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>395.74</v>
+        <v>396.09</v>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
@@ -5686,20 +5686,20 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>206.15</v>
+        <v>205.29</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>211.31</v>
+        <v>210.74</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>218.19</v>
+        <v>217.68</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>245.07</v>
+        <v>244.68</v>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
@@ -5730,20 +5730,20 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>75.20999999999999</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="D115" s="10" t="n">
-        <v>80.90000000000001</v>
+        <v>80.34</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>88.56999999999999</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>96.81999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
@@ -5774,20 +5774,20 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>273.4</v>
+        <v>287</v>
       </c>
       <c r="D116" s="10" t="n">
-        <v>846.83</v>
+        <v>848.12</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>979.36</v>
+        <v>979.89</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>987.85</v>
+        <v>987.98</v>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
@@ -5818,20 +5818,20 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="10" t="n">
-        <v>321.7</v>
+        <v>322.8</v>
       </c>
       <c r="D117" s="10" t="n">
-        <v>317.31</v>
+        <v>317.83</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>301.77</v>
+        <v>302.6</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>312.99</v>
+        <v>313.09</v>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
@@ -5862,24 +5862,24 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>3367.7</v>
+        <v>3277.5</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>3343.02</v>
+        <v>3334.43</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>3205.62</v>
+        <v>3202.08</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>2875.35</v>
-      </c>
-      <c r="G118" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2874.46</v>
+      </c>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
@@ -5906,20 +5906,20 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>4491.5</v>
+        <v>4438.2</v>
       </c>
       <c r="D119" s="10" t="n">
-        <v>4521.83</v>
+        <v>4516.76</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>4335.49</v>
+        <v>4333.4</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>3629.09</v>
+        <v>3628.56</v>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
@@ -5950,24 +5950,24 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>672.15</v>
+        <v>671.7</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>671.76</v>
+        <v>671.75</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>704.5599999999999</v>
+        <v>703.28</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>762.27</v>
-      </c>
-      <c r="G120" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>761.36</v>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
@@ -5994,20 +5994,20 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>302.6</v>
+        <v>292.05</v>
       </c>
       <c r="D121" s="10" t="n">
-        <v>321.02</v>
+        <v>320.01</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>350.96</v>
+        <v>350.55</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>403.15</v>
+        <v>403.04</v>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
@@ -6038,20 +6038,20 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>516.75</v>
+        <v>505.45</v>
       </c>
       <c r="D122" s="10" t="n">
-        <v>520.03</v>
+        <v>518.95</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>546.55</v>
+        <v>546.11</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>670.5700000000001</v>
+        <v>670.46</v>
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
@@ -6082,20 +6082,20 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="10" t="n">
-        <v>611.5</v>
+        <v>610.15</v>
       </c>
       <c r="D123" s="10" t="n">
-        <v>618.13</v>
+        <v>617.37</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>573.77</v>
+        <v>575.2</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>497.48</v>
+        <v>498.6</v>
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
@@ -6126,20 +6126,20 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>1625.4</v>
+        <v>1660.2</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>1489.46</v>
+        <v>1505.72</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>1375.17</v>
+        <v>1386.35</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1123.7</v>
+        <v>1129.04</v>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
@@ -6170,20 +6170,20 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="10" t="n">
-        <v>218.77</v>
+        <v>216.81</v>
       </c>
       <c r="D125" s="10" t="n">
-        <v>223.13</v>
+        <v>222.94</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>225.39</v>
+        <v>225.31</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>241.45</v>
+        <v>241.43</v>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -6214,20 +6214,20 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>473.8</v>
+        <v>460.55</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>500.8</v>
+        <v>496.96</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>508.5</v>
+        <v>506.62</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>540.8</v>
+        <v>540</v>
       </c>
       <c r="G126" s="11" t="inlineStr">
         <is>
@@ -6258,20 +6258,20 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>427.3</v>
+        <v>431.05</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>412.25</v>
+        <v>412.61</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>391.26</v>
+        <v>391.41</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>370.65</v>
+        <v>370.69</v>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
@@ -6302,24 +6302,24 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>826.2</v>
+        <v>824.65</v>
       </c>
       <c r="D128" s="10" t="n">
-        <v>825.3099999999999</v>
+        <v>825.16</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>792.9400000000001</v>
+        <v>792.88</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>731.0599999999999</v>
-      </c>
-      <c r="G128" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>731.04</v>
+      </c>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
@@ -6346,24 +6346,24 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>754.65</v>
+        <v>736.6</v>
       </c>
       <c r="D129" s="10" t="n">
-        <v>751.35</v>
+        <v>749.95</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>706.09</v>
+        <v>707.28</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>589.62</v>
-      </c>
-      <c r="G129" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>591.08</v>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
@@ -6390,24 +6390,24 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>171.86</v>
+        <v>170.91</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>171.6</v>
+        <v>171.51</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>167.75</v>
+        <v>167.71</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>156.93</v>
-      </c>
-      <c r="G130" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>156.92</v>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
@@ -6434,20 +6434,20 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="10" t="n">
-        <v>687.9</v>
+        <v>690.6</v>
       </c>
       <c r="D131" s="10" t="n">
-        <v>704.3200000000001</v>
+        <v>704.58</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>685.73</v>
+        <v>685.84</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>643.58</v>
+        <v>643.61</v>
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
@@ -6478,17 +6478,17 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>433.35</v>
+        <v>433.05</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>437.21</v>
+        <v>437.18</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>438.22</v>
+        <v>438.21</v>
       </c>
       <c r="F132" s="10" t="n">
         <v>473.76</v>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="10" t="n">
-        <v>776.95</v>
+        <v>781.3</v>
       </c>
       <c r="D133" s="10" t="n">
-        <v>786.5599999999999</v>
+        <v>786.97</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>788.97</v>
+        <v>789.14</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>767.9</v>
+        <v>767.95</v>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6566,20 +6566,20 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>1938.1</v>
+        <v>1922.3</v>
       </c>
       <c r="D134" s="10" t="n">
-        <v>1780</v>
+        <v>1793.56</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>1727.99</v>
+        <v>1735.61</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1444.76</v>
+        <v>1449.51</v>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
@@ -6610,20 +6610,20 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="10" t="n">
-        <v>249.25</v>
+        <v>242.25</v>
       </c>
       <c r="D135" s="10" t="n">
-        <v>256.15</v>
+        <v>254.83</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>256.01</v>
+        <v>255.47</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>261.44</v>
+        <v>261.25</v>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6654,20 +6654,20 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>96.41</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>96.75</v>
+        <v>96.66</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>88.06</v>
+        <v>88.03</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>75.59999999999999</v>
+        <v>75.59</v>
       </c>
       <c r="G136" s="11" t="inlineStr">
         <is>
@@ -6698,20 +6698,20 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="10" t="n">
-        <v>384.15</v>
+        <v>382.15</v>
       </c>
       <c r="D137" s="10" t="n">
-        <v>369.07</v>
+        <v>368.87</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>355.3</v>
+        <v>355.23</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>365.88</v>
+        <v>365.86</v>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
@@ -6742,20 +6742,20 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>2068.8</v>
+        <v>2038.2</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>2164.43</v>
+        <v>2161.52</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>2226.64</v>
+        <v>2225.44</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2173.28</v>
+        <v>2172.97</v>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
@@ -6786,29 +6786,29 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="10" t="n">
-        <v>599.25</v>
+        <v>614.6</v>
       </c>
       <c r="D139" s="10" t="n">
-        <v>602.92</v>
+        <v>604.03</v>
       </c>
       <c r="E139" s="10" t="n">
-        <v>604.51</v>
+        <v>604.9</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>552.37</v>
-      </c>
-      <c r="G139" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H139" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>552.99</v>
+      </c>
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H139" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I139" s="13" t="inlineStr">
@@ -6830,29 +6830,29 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>336.55</v>
+        <v>338.85</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>338.99</v>
+        <v>339.21</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>338.32</v>
+        <v>338.41</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>348.58</v>
+        <v>348.6</v>
       </c>
       <c r="G140" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H140" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H140" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I140" s="11" t="inlineStr">
@@ -6874,24 +6874,24 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>417.3</v>
+        <v>435.2</v>
       </c>
       <c r="D141" s="10" t="n">
-        <v>432.68</v>
+        <v>432.92</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>401.34</v>
+        <v>402.67</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>307.25</v>
-      </c>
-      <c r="G141" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>308.52</v>
+      </c>
+      <c r="G141" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H141" s="13" t="inlineStr">
@@ -6918,20 +6918,20 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>1323.3</v>
+        <v>1344.2</v>
       </c>
       <c r="D142" s="10" t="n">
-        <v>1162.98</v>
+        <v>1180.24</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>1026.23</v>
+        <v>1038.7</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>820.99</v>
+        <v>826.1900000000001</v>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
@@ -6962,29 +6962,29 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="10" t="n">
-        <v>126.61</v>
+        <v>128.92</v>
       </c>
       <c r="D143" s="10" t="n">
-        <v>123.75</v>
+        <v>123.97</v>
       </c>
       <c r="E143" s="10" t="n">
-        <v>126.62</v>
+        <v>126.71</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>122.47</v>
+        <v>122.49</v>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H143" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H143" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I143" s="13" t="inlineStr">
@@ -7006,29 +7006,29 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>222.42</v>
+        <v>220.17</v>
       </c>
       <c r="D144" s="10" t="n">
-        <v>220.21</v>
+        <v>220</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>221.18</v>
+        <v>221.09</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>215.33</v>
+        <v>215.3</v>
       </c>
       <c r="G144" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H144" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H144" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I144" s="13" t="inlineStr">
@@ -7050,20 +7050,20 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="10" t="n">
-        <v>285.4</v>
+        <v>283.35</v>
       </c>
       <c r="D145" s="10" t="n">
-        <v>300.8</v>
+        <v>300.61</v>
       </c>
       <c r="E145" s="10" t="n">
-        <v>300.37</v>
+        <v>300.29</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>283.83</v>
+        <v>283.81</v>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -7075,9 +7075,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I145" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
@@ -7094,20 +7094,20 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>113.92</v>
+        <v>113.73</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>119.02</v>
+        <v>119</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>123.08</v>
+        <v>123.07</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>129.93</v>
+        <v>129.92</v>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -7138,20 +7138,20 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="10" t="n">
-        <v>165.45</v>
+        <v>162.3</v>
       </c>
       <c r="D147" s="10" t="n">
-        <v>157.22</v>
+        <v>157.71</v>
       </c>
       <c r="E147" s="10" t="n">
-        <v>155.06</v>
+        <v>155.34</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>147.61</v>
+        <v>147.76</v>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
@@ -7182,20 +7182,20 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>419.55</v>
+        <v>419</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>450.91</v>
+        <v>447.87</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>471.78</v>
+        <v>469.71</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>528.98</v>
+        <v>527.88</v>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
@@ -7226,24 +7226,24 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="10" t="n">
-        <v>93.56999999999999</v>
+        <v>95.61</v>
       </c>
       <c r="D149" s="10" t="n">
-        <v>94.62</v>
+        <v>94.81</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>97.25</v>
+        <v>97.33</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>104.18</v>
-      </c>
-      <c r="G149" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>104.2</v>
+      </c>
+      <c r="G149" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
@@ -7270,24 +7270,24 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>2071.4</v>
+        <v>2093.2</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>2090.21</v>
+        <v>2090.5</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>2040.74</v>
+        <v>2042.8</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1778.39</v>
-      </c>
-      <c r="G150" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1781.52</v>
+      </c>
+      <c r="G150" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H150" s="13" t="inlineStr">
@@ -7314,20 +7314,20 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="10" t="n">
-        <v>2359.8</v>
+        <v>2415.1</v>
       </c>
       <c r="D151" s="10" t="n">
-        <v>2470.46</v>
+        <v>2475.73</v>
       </c>
       <c r="E151" s="10" t="n">
-        <v>2519.23</v>
+        <v>2521.4</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>2514.25</v>
+        <v>2514.8</v>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -7358,20 +7358,20 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>994.8</v>
+        <v>969.9</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>931.8</v>
+        <v>929.42</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>886.02</v>
+        <v>885.04</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>787.7</v>
+        <v>787.45</v>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
@@ -7402,20 +7402,20 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="10" t="n">
-        <v>2003.6</v>
+        <v>2132.9</v>
       </c>
       <c r="D153" s="10" t="n">
-        <v>1861.13</v>
+        <v>1873.45</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>1740.34</v>
+        <v>1745.41</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>1531.5</v>
+        <v>1532.78</v>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
@@ -7446,20 +7446,20 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>1898.4</v>
+        <v>1851.8</v>
       </c>
       <c r="D154" s="10" t="n">
-        <v>1639.63</v>
+        <v>1659.83</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>1450.46</v>
+        <v>1466.2</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1254.39</v>
+        <v>1260.34</v>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
@@ -7490,24 +7490,24 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="10" t="n">
-        <v>286.8</v>
+        <v>282.25</v>
       </c>
       <c r="D155" s="10" t="n">
-        <v>283.55</v>
+        <v>283.43</v>
       </c>
       <c r="E155" s="10" t="n">
-        <v>280.38</v>
+        <v>280.46</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>235.93</v>
-      </c>
-      <c r="G155" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>236.39</v>
+      </c>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>11569</v>
+        <v>11584</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>11419.91</v>
+        <v>11435.54</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>11079.25</v>
+        <v>11099.04</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10082.98</v>
+        <v>10097.91</v>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
@@ -7578,24 +7578,24 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="10" t="n">
-        <v>2063.7</v>
+        <v>2114.9</v>
       </c>
       <c r="D157" s="10" t="n">
-        <v>2099.14</v>
+        <v>2104.01</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>2178.56</v>
+        <v>2180.56</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>2230.61</v>
-      </c>
-      <c r="G157" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2231.12</v>
+      </c>
+      <c r="G157" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
@@ -7622,24 +7622,24 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>2257.2</v>
+        <v>2366.8</v>
       </c>
       <c r="D158" s="10" t="n">
-        <v>2314.67</v>
+        <v>2325.11</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>2185.41</v>
+        <v>2189.71</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>1812.2</v>
-      </c>
-      <c r="G158" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1813.29</v>
+      </c>
+      <c r="G158" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
@@ -7666,24 +7666,24 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="10" t="n">
-        <v>642.7</v>
+        <v>675.95</v>
       </c>
       <c r="D159" s="10" t="n">
-        <v>664.38</v>
+        <v>667.54</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>684.86</v>
+        <v>686.16</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>647.28</v>
-      </c>
-      <c r="G159" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>647.62</v>
+      </c>
+      <c r="G159" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
@@ -7691,9 +7691,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I159" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
@@ -7710,24 +7710,24 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>509.35</v>
+        <v>484.7</v>
       </c>
       <c r="D160" s="10" t="n">
-        <v>503.86</v>
+        <v>501.51</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>518.66</v>
+        <v>517.7</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>553.95</v>
-      </c>
-      <c r="G160" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>553.71</v>
+      </c>
+      <c r="G160" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H160" s="11" t="inlineStr">
@@ -7754,20 +7754,20 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>119.46</v>
+        <v>118.26</v>
       </c>
       <c r="D161" s="10" t="n">
-        <v>110.85</v>
+        <v>111.56</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>110.02</v>
+        <v>110.34</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>115.45</v>
+        <v>115.48</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
@@ -7798,20 +7798,20 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>419.9</v>
+        <v>477</v>
       </c>
       <c r="D162" s="10" t="n">
-        <v>418.84</v>
+        <v>424.28</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>416.31</v>
+        <v>418.55</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>394.61</v>
+        <v>395.17</v>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
@@ -7842,29 +7842,29 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>162.02</v>
+        <v>160.81</v>
       </c>
       <c r="D163" s="10" t="n">
-        <v>160.3</v>
+        <v>160.35</v>
       </c>
       <c r="E163" s="10" t="n">
         <v>160.89</v>
       </c>
       <c r="F163" s="10" t="n">
-        <v>168.95</v>
+        <v>168.87</v>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H163" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H163" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I163" s="11" t="inlineStr">
@@ -7886,20 +7886,20 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="10" t="n">
-        <v>507.15</v>
+        <v>498.75</v>
       </c>
       <c r="D164" s="10" t="n">
-        <v>537.63</v>
+        <v>536.83</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>557.4299999999999</v>
+        <v>557.1</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>641.92</v>
+        <v>641.84</v>
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7930,20 +7930,20 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="10" t="n">
-        <v>785.65</v>
+        <v>778.55</v>
       </c>
       <c r="D165" s="10" t="n">
-        <v>706.3099999999999</v>
+        <v>713.1900000000001</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>657.91</v>
+        <v>662.64</v>
       </c>
       <c r="F165" s="10" t="n">
-        <v>558.72</v>
+        <v>560.91</v>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="10" t="n">
-        <v>195.1</v>
+        <v>194.59</v>
       </c>
       <c r="D166" s="10" t="n">
-        <v>204.16</v>
+        <v>203.24</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>204.52</v>
+        <v>204.13</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>231.09</v>
+        <v>230.73</v>
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
@@ -8018,17 +8018,17 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="10" t="n">
-        <v>216.49</v>
+        <v>215.98</v>
       </c>
       <c r="D167" s="10" t="n">
-        <v>224.78</v>
+        <v>224.73</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>232.07</v>
+        <v>232.05</v>
       </c>
       <c r="F167" s="10" t="n">
         <v>230.35</v>
@@ -8062,20 +8062,20 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="10" t="n">
-        <v>538.95</v>
+        <v>552.65</v>
       </c>
       <c r="D168" s="10" t="n">
-        <v>521.8099999999999</v>
+        <v>524.75</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>499.61</v>
+        <v>501.69</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>471.36</v>
+        <v>472.17</v>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
@@ -8106,20 +8106,20 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="10" t="n">
-        <v>423</v>
+        <v>421.5</v>
       </c>
       <c r="D169" s="10" t="n">
-        <v>419.73</v>
+        <v>419.59</v>
       </c>
       <c r="E169" s="10" t="n">
-        <v>410.67</v>
+        <v>410.62</v>
       </c>
       <c r="F169" s="10" t="n">
-        <v>404.14</v>
+        <v>404.12</v>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
@@ -8150,20 +8150,20 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>827.05</v>
+        <v>849.45</v>
       </c>
       <c r="D170" s="10" t="n">
-        <v>814.12</v>
+        <v>816.25</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>750.76</v>
+        <v>751.64</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>637.23</v>
+        <v>637.46</v>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
@@ -8194,20 +8194,20 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="10" t="n">
-        <v>439.2</v>
+        <v>440.35</v>
       </c>
       <c r="D171" s="10" t="n">
-        <v>448.92</v>
+        <v>449.03</v>
       </c>
       <c r="E171" s="10" t="n">
-        <v>452.54</v>
+        <v>452.58</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>460.72</v>
+        <v>460.73</v>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
@@ -8238,24 +8238,24 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="10" t="n">
-        <v>1178</v>
+        <v>1140.3</v>
       </c>
       <c r="D172" s="10" t="n">
-        <v>1149.32</v>
+        <v>1145.73</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>1104.05</v>
+        <v>1102.57</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>1041.24</v>
-      </c>
-      <c r="G172" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1040.87</v>
+      </c>
+      <c r="G172" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H172" s="13" t="inlineStr">
@@ -8282,20 +8282,20 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>181.71</v>
+        <v>177.06</v>
       </c>
       <c r="D173" s="10" t="n">
-        <v>200.57</v>
+        <v>200.13</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>213.89</v>
+        <v>213.71</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>228.34</v>
+        <v>228.29</v>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
@@ -8326,20 +8326,20 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="10" t="n">
-        <v>557.6</v>
+        <v>541.65</v>
       </c>
       <c r="D174" s="10" t="n">
-        <v>562.83</v>
+        <v>560.8099999999999</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>519.13</v>
+        <v>520.01</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>516.53</v>
+        <v>516.78</v>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
@@ -8370,20 +8370,20 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="10" t="n">
-        <v>560.45</v>
+        <v>556.35</v>
       </c>
       <c r="D175" s="10" t="n">
-        <v>571.12</v>
+        <v>570.73</v>
       </c>
       <c r="E175" s="10" t="n">
-        <v>554.17</v>
+        <v>554.01</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>508.31</v>
+        <v>508.27</v>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
@@ -8414,20 +8414,20 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="10" t="n">
-        <v>154.78</v>
+        <v>154.2</v>
       </c>
       <c r="D176" s="10" t="n">
-        <v>157.43</v>
+        <v>157.12</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>159</v>
+        <v>158.81</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>157.05</v>
+        <v>157.02</v>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
@@ -8458,20 +8458,20 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="10" t="n">
-        <v>183.49</v>
+        <v>180.11</v>
       </c>
       <c r="D177" s="10" t="n">
-        <v>189.16</v>
+        <v>188.84</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>197.91</v>
+        <v>197.78</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>248.61</v>
+        <v>248.58</v>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
@@ -8502,20 +8502,20 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="10" t="n">
-        <v>1482.5</v>
+        <v>1519.7</v>
       </c>
       <c r="D178" s="10" t="n">
-        <v>1363.39</v>
+        <v>1378.28</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>1271.77</v>
+        <v>1281.49</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>1066.81</v>
+        <v>1071.31</v>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="10" t="n">
-        <v>255.45</v>
+        <v>254.61</v>
       </c>
       <c r="D179" s="10" t="n">
-        <v>243.31</v>
+        <v>243.23</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>244.63</v>
+        <v>244.6</v>
       </c>
       <c r="F179" s="10" t="n">
-        <v>241.17</v>
+        <v>241.16</v>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
@@ -8590,20 +8590,20 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="10" t="n">
-        <v>380.2</v>
+        <v>383.35</v>
       </c>
       <c r="D180" s="10" t="n">
-        <v>387.73</v>
+        <v>387.32</v>
       </c>
       <c r="E180" s="10" t="n">
-        <v>368.6</v>
+        <v>369.18</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>326.02</v>
+        <v>326.6</v>
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
@@ -8634,20 +8634,20 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="10" t="n">
-        <v>27.64</v>
+        <v>27.3</v>
       </c>
       <c r="D181" s="10" t="n">
-        <v>28.72</v>
+        <v>28.59</v>
       </c>
       <c r="E181" s="10" t="n">
-        <v>29.69</v>
+        <v>29.6</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>35.28</v>
+        <v>35.2</v>
       </c>
       <c r="G181" s="11" t="inlineStr">
         <is>
@@ -8678,20 +8678,20 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="10" t="n">
-        <v>7.32</v>
+        <v>7.28</v>
       </c>
       <c r="D182" s="10" t="n">
-        <v>7.82</v>
+        <v>7.76</v>
       </c>
       <c r="E182" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>9.220000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G182" s="11" t="inlineStr">
         <is>
@@ -8722,20 +8722,20 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="10" t="n">
-        <v>617.95</v>
+        <v>608.3</v>
       </c>
       <c r="D183" s="10" t="n">
-        <v>661.59</v>
+        <v>656.51</v>
       </c>
       <c r="E183" s="10" t="n">
-        <v>670.03</v>
+        <v>667.61</v>
       </c>
       <c r="F183" s="10" t="n">
-        <v>630.48</v>
+        <v>630.26</v>
       </c>
       <c r="G183" s="11" t="inlineStr">
         <is>
@@ -8766,20 +8766,20 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="10" t="n">
-        <v>276.1</v>
+        <v>272.75</v>
       </c>
       <c r="D184" s="10" t="n">
-        <v>281.82</v>
+        <v>281.5</v>
       </c>
       <c r="E184" s="10" t="n">
-        <v>308.22</v>
+        <v>308.09</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>354.73</v>
+        <v>354.7</v>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8810,20 +8810,20 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="10" t="n">
-        <v>732.3</v>
+        <v>728.5</v>
       </c>
       <c r="D185" s="10" t="n">
-        <v>768.29</v>
+        <v>767.92</v>
       </c>
       <c r="E185" s="10" t="n">
-        <v>802.33</v>
+        <v>802.1799999999999</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>900.92</v>
+        <v>900.88</v>
       </c>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8854,24 +8854,24 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="10" t="n">
-        <v>13493</v>
+        <v>13267</v>
       </c>
       <c r="D186" s="10" t="n">
-        <v>13473.62</v>
+        <v>13452.1</v>
       </c>
       <c r="E186" s="10" t="n">
-        <v>13240.96</v>
+        <v>13232.1</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>13278.53</v>
-      </c>
-      <c r="G186" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>13276.28</v>
+      </c>
+      <c r="G186" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H186" s="13" t="inlineStr">
@@ -8879,9 +8879,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I186" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I186" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J186" s="12" t="inlineStr">
@@ -8898,20 +8898,20 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="10" t="n">
-        <v>340.45</v>
+        <v>339.4</v>
       </c>
       <c r="D187" s="10" t="n">
-        <v>337.03</v>
+        <v>336.93</v>
       </c>
       <c r="E187" s="10" t="n">
-        <v>336.41</v>
+        <v>336.36</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>328.22</v>
+        <v>328.21</v>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
@@ -8942,20 +8942,20 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="10" t="n">
-        <v>59.1</v>
+        <v>58.12</v>
       </c>
       <c r="D188" s="10" t="n">
-        <v>61.13</v>
+        <v>61.04</v>
       </c>
       <c r="E188" s="10" t="n">
-        <v>61.64</v>
+        <v>61.6</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>66.45999999999999</v>
+        <v>66.45</v>
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
@@ -8986,20 +8986,20 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="10" t="n">
-        <v>1388.9</v>
+        <v>1372</v>
       </c>
       <c r="D189" s="10" t="n">
-        <v>1359.97</v>
+        <v>1358.36</v>
       </c>
       <c r="E189" s="10" t="n">
-        <v>1275.11</v>
+        <v>1274.45</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>1101.36</v>
+        <v>1101.19</v>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
@@ -9030,20 +9030,20 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="10" t="n">
-        <v>868.15</v>
+        <v>854.3</v>
       </c>
       <c r="D190" s="10" t="n">
-        <v>888.64</v>
+        <v>885.37</v>
       </c>
       <c r="E190" s="10" t="n">
-        <v>912.51</v>
+        <v>910.23</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>991.98</v>
+        <v>990.61</v>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
@@ -9074,20 +9074,20 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="10" t="n">
-        <v>756.3</v>
+        <v>739</v>
       </c>
       <c r="D191" s="10" t="n">
-        <v>798.73</v>
+        <v>793.05</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>812.2</v>
+        <v>809.33</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>789.54</v>
+        <v>789.03</v>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -9118,20 +9118,20 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="10" t="n">
-        <v>862.65</v>
+        <v>867</v>
       </c>
       <c r="D192" s="10" t="n">
-        <v>831.52</v>
+        <v>831.9299999999999</v>
       </c>
       <c r="E192" s="10" t="n">
-        <v>779.84</v>
+        <v>780.01</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>747.16</v>
+        <v>747.21</v>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
@@ -9162,20 +9162,20 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="10" t="n">
-        <v>122.75</v>
+        <v>119.72</v>
       </c>
       <c r="D193" s="10" t="n">
-        <v>124.61</v>
+        <v>124.15</v>
       </c>
       <c r="E193" s="10" t="n">
-        <v>126.78</v>
+        <v>126.51</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>139.76</v>
+        <v>139.56</v>
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
@@ -9206,20 +9206,20 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="10" t="n">
-        <v>294</v>
+        <v>295.9</v>
       </c>
       <c r="D194" s="10" t="n">
-        <v>301.48</v>
+        <v>301.66</v>
       </c>
       <c r="E194" s="10" t="n">
-        <v>305.27</v>
+        <v>305.35</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>339.29</v>
+        <v>339.31</v>
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -9250,20 +9250,20 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="10" t="n">
-        <v>3016.1</v>
+        <v>2953.8</v>
       </c>
       <c r="D195" s="10" t="n">
-        <v>2879.6</v>
+        <v>2886.67</v>
       </c>
       <c r="E195" s="10" t="n">
-        <v>2758.77</v>
+        <v>2766.42</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>2572.14</v>
+        <v>2575.94</v>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
@@ -9294,20 +9294,20 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="10" t="n">
-        <v>2746.6</v>
+        <v>2761.5</v>
       </c>
       <c r="D196" s="10" t="n">
-        <v>2817.71</v>
+        <v>2819.13</v>
       </c>
       <c r="E196" s="10" t="n">
-        <v>2723.28</v>
+        <v>2723.86</v>
       </c>
       <c r="F196" s="10" t="n">
-        <v>2607.85</v>
+        <v>2607.99</v>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
@@ -9338,20 +9338,20 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="10" t="n">
-        <v>783.5</v>
+        <v>790</v>
       </c>
       <c r="D197" s="10" t="n">
-        <v>681.6</v>
+        <v>691.92</v>
       </c>
       <c r="E197" s="10" t="n">
-        <v>629.35</v>
+        <v>635.65</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>553.17</v>
+        <v>555.53</v>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
@@ -9382,20 +9382,20 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="10" t="n">
-        <v>675.35</v>
+        <v>667.35</v>
       </c>
       <c r="D198" s="10" t="n">
-        <v>684.7</v>
+        <v>683.05</v>
       </c>
       <c r="E198" s="10" t="n">
-        <v>683.67</v>
+        <v>683.03</v>
       </c>
       <c r="F198" s="10" t="n">
-        <v>627.42</v>
+        <v>627.8200000000001</v>
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -9426,20 +9426,20 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="10" t="n">
-        <v>338.95</v>
+        <v>343.95</v>
       </c>
       <c r="D199" s="10" t="n">
-        <v>353.13</v>
+        <v>352.25</v>
       </c>
       <c r="E199" s="10" t="n">
-        <v>361.5</v>
+        <v>360.82</v>
       </c>
       <c r="F199" s="10" t="n">
-        <v>425.93</v>
+        <v>425.11</v>
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
@@ -9470,20 +9470,20 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="10" t="n">
-        <v>1770.6</v>
+        <v>1725.6</v>
       </c>
       <c r="D200" s="10" t="n">
-        <v>1839.58</v>
+        <v>1835.29</v>
       </c>
       <c r="E200" s="10" t="n">
-        <v>1933.54</v>
+        <v>1931.77</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>2041.96</v>
+        <v>2041.51</v>
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
@@ -9514,24 +9514,24 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="10" t="n">
-        <v>167.39</v>
+        <v>169.96</v>
       </c>
       <c r="D201" s="10" t="n">
-        <v>169.66</v>
+        <v>169.69</v>
       </c>
       <c r="E201" s="10" t="n">
-        <v>177.94</v>
+        <v>177.63</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>192.89</v>
-      </c>
-      <c r="G201" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>192.66</v>
+      </c>
+      <c r="G201" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H201" s="11" t="inlineStr">
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="10" t="n">
-        <v>118.81</v>
+        <v>115.58</v>
       </c>
       <c r="D202" s="10" t="n">
-        <v>123.25</v>
+        <v>122.94</v>
       </c>
       <c r="E202" s="10" t="n">
-        <v>126.45</v>
+        <v>126.32</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>127.25</v>
+        <v>127.21</v>
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
@@ -9602,17 +9602,17 @@
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="10" t="n">
-        <v>194.28</v>
+        <v>193.4</v>
       </c>
       <c r="D203" s="10" t="n">
-        <v>198.92</v>
+        <v>198.84</v>
       </c>
       <c r="E203" s="10" t="n">
-        <v>201.96</v>
+        <v>201.93</v>
       </c>
       <c r="F203" s="10" t="n">
         <v>209.85</v>
@@ -9646,24 +9646,24 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="10" t="n">
-        <v>801.45</v>
+        <v>824.05</v>
       </c>
       <c r="D204" s="10" t="n">
-        <v>810.85</v>
+        <v>813</v>
       </c>
       <c r="E204" s="10" t="n">
-        <v>832.74</v>
+        <v>833.62</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>829.41</v>
-      </c>
-      <c r="G204" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>829.64</v>
+      </c>
+      <c r="G204" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H204" s="11" t="inlineStr">
@@ -9690,20 +9690,20 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="10" t="n">
-        <v>115.5</v>
+        <v>114.27</v>
       </c>
       <c r="D205" s="10" t="n">
-        <v>116.44</v>
+        <v>116.32</v>
       </c>
       <c r="E205" s="10" t="n">
-        <v>119.64</v>
+        <v>119.59</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>138.38</v>
+        <v>138.37</v>
       </c>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9734,20 +9734,20 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="10" t="n">
-        <v>590.7</v>
+        <v>589.85</v>
       </c>
       <c r="D206" s="10" t="n">
-        <v>579.04</v>
+        <v>580.0700000000001</v>
       </c>
       <c r="E206" s="10" t="n">
-        <v>581.28</v>
+        <v>581.61</v>
       </c>
       <c r="F206" s="10" t="n">
-        <v>610.84</v>
+        <v>610.63</v>
       </c>
       <c r="G206" s="13" t="inlineStr">
         <is>
@@ -9778,20 +9778,20 @@
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="10" t="n">
-        <v>391.85</v>
+        <v>393.55</v>
       </c>
       <c r="D207" s="10" t="n">
-        <v>409.37</v>
+        <v>409.53</v>
       </c>
       <c r="E207" s="10" t="n">
-        <v>419.81</v>
+        <v>419.88</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>441.38</v>
+        <v>441.4</v>
       </c>
       <c r="G207" s="11" t="inlineStr">
         <is>
@@ -9822,20 +9822,20 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="10" t="n">
-        <v>134.9</v>
+        <v>131.53</v>
       </c>
       <c r="D208" s="10" t="n">
-        <v>124.56</v>
+        <v>124.24</v>
       </c>
       <c r="E208" s="10" t="n">
-        <v>125.88</v>
+        <v>125.75</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>136.36</v>
+        <v>136.32</v>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
@@ -9866,20 +9866,20 @@
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="10" t="n">
-        <v>157.16</v>
+        <v>157.86</v>
       </c>
       <c r="D209" s="10" t="n">
-        <v>160.11</v>
+        <v>160.17</v>
       </c>
       <c r="E209" s="10" t="n">
-        <v>163.71</v>
+        <v>163.74</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>174.36</v>
+        <v>174.37</v>
       </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
@@ -9910,20 +9910,20 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="10" t="n">
-        <v>112.52</v>
+        <v>109.91</v>
       </c>
       <c r="D210" s="10" t="n">
-        <v>107.58</v>
+        <v>107.33</v>
       </c>
       <c r="E210" s="10" t="n">
-        <v>105.63</v>
+        <v>105.52</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>114.67</v>
+        <v>114.64</v>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
@@ -9954,20 +9954,20 @@
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="10" t="n">
-        <v>1313.6</v>
+        <v>1296</v>
       </c>
       <c r="D211" s="10" t="n">
-        <v>1343.95</v>
+        <v>1342.27</v>
       </c>
       <c r="E211" s="10" t="n">
-        <v>1331.76</v>
+        <v>1331.07</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>1320.05</v>
+        <v>1319.88</v>
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
@@ -9998,20 +9998,20 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="10" t="n">
-        <v>126.56</v>
+        <v>126.42</v>
       </c>
       <c r="D212" s="10" t="n">
-        <v>130.87</v>
+        <v>130.45</v>
       </c>
       <c r="E212" s="10" t="n">
-        <v>133.49</v>
+        <v>133.21</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>156.86</v>
+        <v>156.56</v>
       </c>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -10042,20 +10042,20 @@
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>297.85</v>
+        <v>298.85</v>
       </c>
       <c r="D213" s="10" t="n">
-        <v>300.79</v>
+        <v>300.89</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>312.15</v>
+        <v>312.19</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>318.35</v>
+        <v>318.36</v>
       </c>
       <c r="G213" s="11" t="inlineStr">
         <is>
@@ -10086,20 +10086,20 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="10" t="n">
-        <v>255.2</v>
+        <v>253</v>
       </c>
       <c r="D214" s="10" t="n">
-        <v>264.53</v>
+        <v>263.43</v>
       </c>
       <c r="E214" s="10" t="n">
-        <v>277.54</v>
+        <v>276.57</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>355.45</v>
+        <v>354.43</v>
       </c>
       <c r="G214" s="11" t="inlineStr">
         <is>
@@ -10130,34 +10130,34 @@
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="10" t="n">
-        <v>799.55</v>
+        <v>808.5</v>
       </c>
       <c r="D215" s="10" t="n">
-        <v>817.8</v>
+        <v>818.66</v>
       </c>
       <c r="E215" s="10" t="n">
-        <v>807.85</v>
+        <v>808.2</v>
       </c>
       <c r="F215" s="10" t="n">
-        <v>802.3200000000001</v>
+        <v>802.41</v>
       </c>
       <c r="G215" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H215" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I215" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H215" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I215" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J215" s="12" t="inlineStr">
@@ -10174,20 +10174,20 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>1235.7</v>
+        <v>1285.2</v>
       </c>
       <c r="D216" s="10" t="n">
-        <v>1042.93</v>
+        <v>1047.65</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>955.72</v>
+        <v>957.66</v>
       </c>
       <c r="F216" s="10" t="n">
-        <v>945.5</v>
+        <v>945.99</v>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
@@ -10218,17 +10218,17 @@
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="10" t="n">
-        <v>80.51000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D217" s="10" t="n">
-        <v>78.48</v>
+        <v>78.42</v>
       </c>
       <c r="E217" s="10" t="n">
-        <v>76.27</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="F217" s="10" t="n">
         <v>78.97</v>
@@ -10262,17 +10262,17 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="10" t="n">
-        <v>127.77</v>
+        <v>127.1</v>
       </c>
       <c r="D218" s="10" t="n">
-        <v>130.09</v>
+        <v>130.03</v>
       </c>
       <c r="E218" s="10" t="n">
-        <v>138.85</v>
+        <v>138.83</v>
       </c>
       <c r="F218" s="10" t="n">
         <v>166.4</v>
@@ -10306,20 +10306,20 @@
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="10" t="n">
-        <v>1076</v>
+        <v>1117.1</v>
       </c>
       <c r="D219" s="10" t="n">
-        <v>1045.5</v>
+        <v>1049.41</v>
       </c>
       <c r="E219" s="10" t="n">
-        <v>1063.17</v>
+        <v>1064.79</v>
       </c>
       <c r="F219" s="10" t="n">
-        <v>1121.55</v>
+        <v>1121.96</v>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
@@ -10350,20 +10350,20 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="10" t="n">
-        <v>248.95</v>
+        <v>248.1</v>
       </c>
       <c r="D220" s="10" t="n">
-        <v>247.49</v>
+        <v>247.55</v>
       </c>
       <c r="E220" s="10" t="n">
-        <v>241.03</v>
+        <v>241.3</v>
       </c>
       <c r="F220" s="10" t="n">
-        <v>226.73</v>
+        <v>226.95</v>
       </c>
       <c r="G220" s="13" t="inlineStr">
         <is>
@@ -10394,20 +10394,20 @@
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="10" t="n">
-        <v>1546.6</v>
+        <v>1534.8</v>
       </c>
       <c r="D221" s="10" t="n">
-        <v>1557.26</v>
+        <v>1555.12</v>
       </c>
       <c r="E221" s="10" t="n">
-        <v>1560.21</v>
+        <v>1559.22</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>1932.33</v>
+        <v>1928.38</v>
       </c>
       <c r="G221" s="11" t="inlineStr">
         <is>
@@ -10438,20 +10438,20 @@
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="10" t="n">
-        <v>626.95</v>
+        <v>628.3</v>
       </c>
       <c r="D222" s="10" t="n">
-        <v>626.6900000000001</v>
+        <v>626.84</v>
       </c>
       <c r="E222" s="10" t="n">
-        <v>635.12</v>
+        <v>634.85</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>634.09</v>
+        <v>634.03</v>
       </c>
       <c r="G222" s="13" t="inlineStr">
         <is>
@@ -10482,17 +10482,17 @@
       </c>
       <c r="B223" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="10" t="n">
-        <v>25.15</v>
+        <v>25.19</v>
       </c>
       <c r="D223" s="10" t="n">
-        <v>23.95</v>
+        <v>24.07</v>
       </c>
       <c r="E223" s="10" t="n">
-        <v>23.49</v>
+        <v>23.55</v>
       </c>
       <c r="F223" s="10" t="n">
         <v>25.07</v>
@@ -10526,20 +10526,20 @@
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="10" t="n">
-        <v>665.5</v>
+        <v>673.6</v>
       </c>
       <c r="D224" s="10" t="n">
-        <v>615.02</v>
+        <v>615.79</v>
       </c>
       <c r="E224" s="10" t="n">
-        <v>588.62</v>
+        <v>588.9400000000001</v>
       </c>
       <c r="F224" s="10" t="n">
-        <v>591.78</v>
+        <v>591.86</v>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="10" t="n">
-        <v>406.2</v>
+        <v>408.55</v>
       </c>
       <c r="D225" s="10" t="n">
-        <v>428.69</v>
+        <v>426.78</v>
       </c>
       <c r="E225" s="10" t="n">
-        <v>441.35</v>
+        <v>440.07</v>
       </c>
       <c r="F225" s="10" t="n">
-        <v>488.17</v>
+        <v>487.38</v>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -10614,20 +10614,20 @@
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="10" t="n">
-        <v>215.81</v>
+        <v>216.02</v>
       </c>
       <c r="D226" s="10" t="n">
-        <v>221.62</v>
+        <v>221.09</v>
       </c>
       <c r="E226" s="10" t="n">
-        <v>230.27</v>
+        <v>229.71</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>245.95</v>
+        <v>245.65</v>
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -10658,20 +10658,20 @@
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="10" t="n">
-        <v>518.25</v>
+        <v>519.7</v>
       </c>
       <c r="D227" s="10" t="n">
-        <v>507.91</v>
+        <v>509.03</v>
       </c>
       <c r="E227" s="10" t="n">
-        <v>497.67</v>
+        <v>498.53</v>
       </c>
       <c r="F227" s="10" t="n">
-        <v>470.63</v>
+        <v>471.12</v>
       </c>
       <c r="G227" s="13" t="inlineStr">
         <is>
@@ -10702,20 +10702,20 @@
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="10" t="n">
-        <v>112.21</v>
+        <v>112.27</v>
       </c>
       <c r="D228" s="10" t="n">
-        <v>110.24</v>
+        <v>110.43</v>
       </c>
       <c r="E228" s="10" t="n">
-        <v>111.61</v>
+        <v>111.64</v>
       </c>
       <c r="F228" s="10" t="n">
-        <v>122.66</v>
+        <v>122.55</v>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
@@ -10746,29 +10746,29 @@
       </c>
       <c r="B229" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="10" t="n">
-        <v>223.02</v>
+        <v>216.39</v>
       </c>
       <c r="D229" s="10" t="n">
-        <v>217.12</v>
+        <v>216.49</v>
       </c>
       <c r="E229" s="10" t="n">
-        <v>216.71</v>
+        <v>216.45</v>
       </c>
       <c r="F229" s="10" t="n">
-        <v>223.58</v>
-      </c>
-      <c r="G229" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H229" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>223.52</v>
+      </c>
+      <c r="G229" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H229" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I229" s="11" t="inlineStr">
@@ -10790,24 +10790,24 @@
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="10" t="n">
-        <v>1986.3</v>
+        <v>1970.7</v>
       </c>
       <c r="D230" s="10" t="n">
-        <v>1983.33</v>
+        <v>1981.85</v>
       </c>
       <c r="E230" s="10" t="n">
-        <v>1909.87</v>
+        <v>1909.26</v>
       </c>
       <c r="F230" s="10" t="n">
-        <v>1770.66</v>
-      </c>
-      <c r="G230" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1770.5</v>
+      </c>
+      <c r="G230" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H230" s="13" t="inlineStr">
@@ -10834,20 +10834,20 @@
       </c>
       <c r="B231" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="10" t="n">
-        <v>688.95</v>
+        <v>680.65</v>
       </c>
       <c r="D231" s="10" t="n">
-        <v>636.63</v>
+        <v>635.84</v>
       </c>
       <c r="E231" s="10" t="n">
-        <v>614.29</v>
+        <v>613.96</v>
       </c>
       <c r="F231" s="10" t="n">
-        <v>599.95</v>
+        <v>599.87</v>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
@@ -10878,20 +10878,20 @@
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="10" t="n">
-        <v>162.15</v>
+        <v>171.94</v>
       </c>
       <c r="D232" s="10" t="n">
-        <v>172.09</v>
+        <v>172.07</v>
       </c>
       <c r="E232" s="10" t="n">
-        <v>183.15</v>
+        <v>182.71</v>
       </c>
       <c r="F232" s="10" t="n">
-        <v>217.95</v>
+        <v>217.5</v>
       </c>
       <c r="G232" s="11" t="inlineStr">
         <is>
@@ -10922,20 +10922,20 @@
       </c>
       <c r="B233" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="10" t="n">
-        <v>5743.5</v>
+        <v>5761.5</v>
       </c>
       <c r="D233" s="10" t="n">
-        <v>5807.28</v>
+        <v>5809</v>
       </c>
       <c r="E233" s="10" t="n">
-        <v>5900.48</v>
+        <v>5901.18</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>5740.53</v>
+        <v>5740.71</v>
       </c>
       <c r="G233" s="11" t="inlineStr">
         <is>
@@ -10966,29 +10966,29 @@
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="10" t="n">
-        <v>342.1</v>
+        <v>339.95</v>
       </c>
       <c r="D234" s="10" t="n">
-        <v>339.04</v>
+        <v>339.13</v>
       </c>
       <c r="E234" s="10" t="n">
         <v>340.05</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>389.42</v>
+        <v>388.93</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H234" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H234" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I234" s="11" t="inlineStr">
@@ -11010,20 +11010,20 @@
       </c>
       <c r="B235" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="10" t="n">
-        <v>28.14</v>
+        <v>28.05</v>
       </c>
       <c r="D235" s="10" t="n">
-        <v>29.79</v>
+        <v>29.63</v>
       </c>
       <c r="E235" s="10" t="n">
-        <v>31.15</v>
+        <v>31.03</v>
       </c>
       <c r="F235" s="10" t="n">
-        <v>35.68</v>
+        <v>35.61</v>
       </c>
       <c r="G235" s="11" t="inlineStr">
         <is>
@@ -11054,17 +11054,17 @@
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="10" t="n">
-        <v>194.4</v>
+        <v>194.83</v>
       </c>
       <c r="D236" s="10" t="n">
-        <v>192.57</v>
+        <v>192.61</v>
       </c>
       <c r="E236" s="10" t="n">
-        <v>199.03</v>
+        <v>199.04</v>
       </c>
       <c r="F236" s="10" t="n">
         <v>212.84</v>
@@ -11098,24 +11098,24 @@
       </c>
       <c r="B237" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="10" t="n">
-        <v>129.05</v>
+        <v>127.23</v>
       </c>
       <c r="D237" s="10" t="n">
-        <v>128.85</v>
+        <v>128.68</v>
       </c>
       <c r="E237" s="10" t="n">
-        <v>129.47</v>
+        <v>129.4</v>
       </c>
       <c r="F237" s="10" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="G237" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>123.48</v>
+      </c>
+      <c r="G237" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H237" s="11" t="inlineStr">
@@ -11142,17 +11142,17 @@
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="10" t="n">
-        <v>7.6</v>
+        <v>7.46</v>
       </c>
       <c r="D238" s="10" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="E238" s="10" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="F238" s="10" t="n">
         <v>13.49</v>
@@ -11186,20 +11186,20 @@
       </c>
       <c r="B239" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="10" t="n">
-        <v>100.88</v>
+        <v>101.19</v>
       </c>
       <c r="D239" s="10" t="n">
-        <v>106.11</v>
+        <v>105.64</v>
       </c>
       <c r="E239" s="10" t="n">
-        <v>109.63</v>
+        <v>109.3</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>121.58</v>
+        <v>121.38</v>
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
@@ -11230,20 +11230,20 @@
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="10" t="n">
-        <v>320.5</v>
+        <v>309.6</v>
       </c>
       <c r="D240" s="10" t="n">
-        <v>307.99</v>
+        <v>308.15</v>
       </c>
       <c r="E240" s="10" t="n">
-        <v>307.16</v>
+        <v>307.25</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>330.41</v>
+        <v>330.2</v>
       </c>
       <c r="G240" s="13" t="inlineStr">
         <is>
@@ -11274,20 +11274,20 @@
       </c>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="10" t="n">
-        <v>488.7</v>
+        <v>484.55</v>
       </c>
       <c r="D241" s="10" t="n">
-        <v>502.89</v>
+        <v>502.49</v>
       </c>
       <c r="E241" s="10" t="n">
-        <v>526.61</v>
+        <v>526.4400000000001</v>
       </c>
       <c r="F241" s="10" t="n">
-        <v>630.37</v>
+        <v>630.33</v>
       </c>
       <c r="G241" s="11" t="inlineStr">
         <is>
@@ -11318,24 +11318,24 @@
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="10" t="n">
-        <v>69.70999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="D242" s="10" t="n">
-        <v>68.34</v>
+        <v>68.16</v>
       </c>
       <c r="E242" s="10" t="n">
-        <v>67.38</v>
+        <v>67.31</v>
       </c>
       <c r="F242" s="10" t="n">
-        <v>72.58</v>
-      </c>
-      <c r="G242" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="G242" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H242" s="13" t="inlineStr">
@@ -11362,29 +11362,29 @@
       </c>
       <c r="B243" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="10" t="n">
-        <v>1537.8</v>
+        <v>1533.7</v>
       </c>
       <c r="D243" s="10" t="n">
-        <v>1517.01</v>
+        <v>1516.62</v>
       </c>
       <c r="E243" s="10" t="n">
-        <v>1537.52</v>
+        <v>1537.36</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>1709.99</v>
+        <v>1709.95</v>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H243" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H243" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I243" s="11" t="inlineStr">
@@ -11406,17 +11406,17 @@
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="10" t="n">
-        <v>125.08</v>
+        <v>124.41</v>
       </c>
       <c r="D244" s="10" t="n">
-        <v>129.82</v>
+        <v>129.76</v>
       </c>
       <c r="E244" s="10" t="n">
-        <v>133.18</v>
+        <v>133.15</v>
       </c>
       <c r="F244" s="10" t="n">
         <v>136.45</v>
@@ -11450,11 +11450,11 @@
       </c>
       <c r="B245" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="10" t="n">
-        <v>70.31999999999999</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="D245" s="10" t="n">
         <v>70.97</v>
@@ -11494,20 +11494,20 @@
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="10" t="n">
-        <v>739.3</v>
+        <v>744.1</v>
       </c>
       <c r="D246" s="10" t="n">
-        <v>755.63</v>
+        <v>756.08</v>
       </c>
       <c r="E246" s="10" t="n">
-        <v>762.75</v>
+        <v>762.9400000000001</v>
       </c>
       <c r="F246" s="10" t="n">
-        <v>764.4</v>
+        <v>764.45</v>
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -11538,24 +11538,24 @@
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="10" t="n">
-        <v>403.6</v>
+        <v>422.3</v>
       </c>
       <c r="D247" s="10" t="n">
-        <v>413.73</v>
+        <v>415.51</v>
       </c>
       <c r="E247" s="10" t="n">
-        <v>422.1</v>
+        <v>422.83</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>428.15</v>
-      </c>
-      <c r="G247" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>428.33</v>
+      </c>
+      <c r="G247" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H247" s="11" t="inlineStr">
@@ -11582,20 +11582,20 @@
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="10" t="n">
-        <v>597.05</v>
+        <v>607.15</v>
       </c>
       <c r="D248" s="10" t="n">
-        <v>671.62</v>
+        <v>672.59</v>
       </c>
       <c r="E248" s="10" t="n">
-        <v>741.4400000000001</v>
+        <v>741.83</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>822.03</v>
+        <v>822.13</v>
       </c>
       <c r="G248" s="11" t="inlineStr">
         <is>
@@ -11626,20 +11626,20 @@
       </c>
       <c r="B249" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="10" t="n">
-        <v>4106</v>
+        <v>4075.6</v>
       </c>
       <c r="D249" s="10" t="n">
-        <v>4258.1</v>
+        <v>4240.72</v>
       </c>
       <c r="E249" s="10" t="n">
-        <v>4396.05</v>
+        <v>4383.48</v>
       </c>
       <c r="F249" s="10" t="n">
-        <v>4535.5</v>
+        <v>4530.93</v>
       </c>
       <c r="G249" s="11" t="inlineStr">
         <is>
@@ -11670,20 +11670,20 @@
       </c>
       <c r="B250" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="10" t="n">
-        <v>704.75</v>
+        <v>697.85</v>
       </c>
       <c r="D250" s="10" t="n">
-        <v>734.34</v>
+        <v>733.6900000000001</v>
       </c>
       <c r="E250" s="10" t="n">
-        <v>758.3</v>
+        <v>758.03</v>
       </c>
       <c r="F250" s="10" t="n">
-        <v>788.46</v>
+        <v>788.39</v>
       </c>
       <c r="G250" s="11" t="inlineStr">
         <is>
@@ -11714,20 +11714,20 @@
       </c>
       <c r="B251" s="10" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="10" t="n">
-        <v>421</v>
+        <v>415.95</v>
       </c>
       <c r="D251" s="10" t="n">
-        <v>422.35</v>
+        <v>421.74</v>
       </c>
       <c r="E251" s="10" t="n">
-        <v>431.04</v>
+        <v>430.45</v>
       </c>
       <c r="F251" s="10" t="n">
-        <v>433.84</v>
+        <v>433.67</v>
       </c>
       <c r="G251" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Sep-2026  14:52:08    |    Closing Price Date: 08-Sep-2026</t>
+          <t>Scan Run: 09-Sep-2026  15:00:29    |    Closing Price Date: 09-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -591,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>44.8</v>
+        <v>42.8</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>50.4</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Sep-2026  14:52:08</t>
+          <t>09-Sep-2026  15:00:29</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.8% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 42.8% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.8% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 112 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 107 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 142 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 140 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>251.49</v>
+        <v>251.95</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>259.04</v>
+        <v>258.36</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>269.18</v>
+        <v>268.51</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>298.61</v>
+        <v>298.15</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>330.05</v>
+        <v>326.95</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>331.89</v>
+        <v>331.42</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>322.49</v>
+        <v>322.67</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>324.92</v>
+        <v>324.94</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>6313.5</v>
+        <v>6570</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>5509.77</v>
+        <v>5610.74</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>5015.62</v>
+        <v>5076.58</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>4175.8</v>
+        <v>4199.63</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>768.8</v>
+        <v>755.1</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>727.78</v>
+        <v>730.39</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>675.53</v>
+        <v>678.65</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>537.4299999999999</v>
+        <v>539.59</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>274.8</v>
+        <v>279.7</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>274.78</v>
+        <v>275.25</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>246.63</v>
+        <v>247.93</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>157.27</v>
+        <v>158.48</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>336.25</v>
+        <v>334.8</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>337.73</v>
+        <v>337.45</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>306.68</v>
+        <v>307.78</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>216.52</v>
+        <v>217.7</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7799.5</v>
+        <v>7501</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>6993.29</v>
+        <v>7041.64</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6822.54</v>
+        <v>6849.15</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>5364.37</v>
+        <v>5385.63</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>868.7</v>
+        <v>874.4</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>821.24</v>
+        <v>826.3099999999999</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>756.3099999999999</v>
+        <v>760.95</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>613.3200000000001</v>
+        <v>615.91</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1110,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>334.25</v>
+        <v>331.25</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>325.84</v>
+        <v>326.35</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>306.2</v>
+        <v>307.18</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>256.71</v>
+        <v>257.45</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>5366.5</v>
+        <v>5118</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>5435.41</v>
+        <v>5405.18</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>5495.59</v>
+        <v>5480.79</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4501.77</v>
+        <v>4507.9</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1198,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>184.52</v>
+        <v>178.56</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>173.62</v>
+        <v>174.09</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>170.87</v>
+        <v>171.17</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>165.11</v>
+        <v>165.24</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2822.1</v>
+        <v>2805</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>2752.55</v>
+        <v>2757.54</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>2563.13</v>
+        <v>2572.62</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2107.81</v>
+        <v>2114.75</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,29 +1286,29 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>573.4</v>
+        <v>580.05</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>584.87</v>
+        <v>584.41</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>575.3200000000001</v>
+        <v>575.51</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>570.8</v>
+        <v>570.9</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>2290.3</v>
+        <v>2293.6</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>2153.62</v>
+        <v>2166.95</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1958.88</v>
+        <v>1972.01</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1465.89</v>
+        <v>1474.12</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,29 +1374,29 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>3469.6</v>
+        <v>3537.9</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3457.38</v>
+        <v>3465.05</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>3487.02</v>
+        <v>3489.02</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>3210.02</v>
+        <v>3213.28</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>417.9</v>
+        <v>422.45</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>391.78</v>
+        <v>394.7</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>389.23</v>
+        <v>390.53</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>331.28</v>
+        <v>332.19</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>758.6</v>
+        <v>745.8</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>767.28</v>
+        <v>765.24</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>718.26</v>
+        <v>719.34</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>620.6799999999999</v>
+        <v>621.9299999999999</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>824.7</v>
+        <v>865.9</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>686.86</v>
+        <v>703.92</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>623.86</v>
+        <v>633.36</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>409.84</v>
+        <v>414.37</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>198.81</v>
+        <v>197.99</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>182.93</v>
+        <v>184.37</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>172.53</v>
+        <v>173.53</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>160.11</v>
+        <v>160.49</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>13.52</v>
+        <v>13.87</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>11.05</v>
+        <v>11.32</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>10.28</v>
+        <v>10.42</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>10.12</v>
+        <v>10.15</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>231.9</v>
+        <v>230.55</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>244.41</v>
+        <v>243.09</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>237.38</v>
+        <v>237.11</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>196.21</v>
+        <v>196.55</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1682,24 +1682,24 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>2008.4</v>
+        <v>2130.9</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>2010.28</v>
+        <v>2021.77</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1963.1</v>
+        <v>1969.68</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>1680.83</v>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1685.3</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -1726,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>233.15</v>
+        <v>230.56</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>236.13</v>
+        <v>235.6</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>229.92</v>
+        <v>229.94</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>206.87</v>
+        <v>207.1</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1770,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>64.86</v>
+        <v>64.12</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>67.61</v>
+        <v>67.28</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>66.51000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>59.7</v>
+        <v>59.74</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
@@ -1814,29 +1814,29 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>167.3</v>
+        <v>166.39</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>170.37</v>
+        <v>169.99</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>166.65</v>
+        <v>166.64</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>149.36</v>
+        <v>149.53</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>186.54</v>
+        <v>184.99</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>190.15</v>
+        <v>189.66</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>191.22</v>
+        <v>190.97</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>189.86</v>
+        <v>189.81</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>512.95</v>
+        <v>509.3</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>545.63</v>
+        <v>542.17</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>554.4</v>
+        <v>552.63</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>542.46</v>
+        <v>542.13</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1946,24 +1946,24 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>337.5</v>
+        <v>355</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>348.39</v>
+        <v>349.02</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>320.19</v>
+        <v>321.56</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>260.49</v>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>261.43</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>1504</v>
+        <v>1470</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1413.75</v>
+        <v>1419.11</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>1315.48</v>
+        <v>1321.53</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1009.67</v>
+        <v>1014.25</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>368.4</v>
+        <v>374.4</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>357.99</v>
+        <v>359.55</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>337.43</v>
+        <v>338.88</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>300.09</v>
+        <v>300.83</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>540.35</v>
+        <v>530.9</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>544.03</v>
+        <v>542.78</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>511.91</v>
+        <v>512.65</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>465.05</v>
+        <v>465.71</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2122,24 +2122,24 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>1642.9</v>
+        <v>1610.9</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1630.83</v>
+        <v>1628.93</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>1532.21</v>
+        <v>1535.3</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>1225.77</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1229.61</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>820</v>
+        <v>832.2</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>778.5599999999999</v>
+        <v>783.67</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>711.29</v>
+        <v>716.03</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>526.13</v>
+        <v>529.1799999999999</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>627.45</v>
+        <v>611.45</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>608.72</v>
+        <v>608.98</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>607.24</v>
+        <v>607.4</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>596.71</v>
+        <v>596.85</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2254,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>539.8</v>
+        <v>533.95</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>544.78</v>
+        <v>543.75</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>531.27</v>
+        <v>531.37</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>477.93</v>
+        <v>478.48</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2298,24 +2298,24 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>196.57</v>
+        <v>201.01</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>200.81</v>
+        <v>200.83</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>203.55</v>
+        <v>203.45</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>203.16</v>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>203.14</v>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>837.15</v>
+        <v>807.15</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>839.74</v>
+        <v>836.64</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>902.41</v>
+        <v>898.67</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>981.72</v>
+        <v>979.98</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>549.35</v>
+        <v>550.6</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>584.4</v>
+        <v>581.1799999999999</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>623.13</v>
+        <v>620.29</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>628.8099999999999</v>
+        <v>628.03</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,29 +2430,29 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>361.85</v>
+        <v>355.8</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>358.5</v>
+        <v>358.24</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>359.12</v>
+        <v>358.99</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>344.54</v>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>344.65</v>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr">
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>217.81</v>
+        <v>222.5</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>208.47</v>
+        <v>209.8</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>204.67</v>
+        <v>205.37</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>172.12</v>
+        <v>172.62</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>81.81</v>
+        <v>81.31</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>87.06</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>86.08</v>
+        <v>85.89</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>71.67</v>
+        <v>71.77</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,24 +2562,24 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>230.35</v>
+        <v>242.05</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>233.42</v>
+        <v>234.24</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>220.66</v>
+        <v>221.5</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>217.04</v>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>217.29</v>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -2606,24 +2606,24 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1757.3</v>
+        <v>1706.1</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1708.66</v>
+        <v>1708.42</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1680.97</v>
+        <v>1681.95</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1376.73</v>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1380.01</v>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>345.65</v>
+        <v>339.5</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>385.35</v>
+        <v>380.99</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>385.63</v>
+        <v>383.82</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>407.89</v>
+        <v>407.21</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>569.45</v>
+        <v>566.85</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>586.3200000000001</v>
+        <v>584.46</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>570.65</v>
+        <v>570.5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>489.6</v>
+        <v>490.37</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2738,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>169.28</v>
+        <v>166.59</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>170.89</v>
+        <v>170.48</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>177.75</v>
+        <v>177.31</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>214.39</v>
+        <v>213.92</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1221.7</v>
+        <v>1262.3</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1197.09</v>
+        <v>1203.3</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1110.48</v>
+        <v>1116.44</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1021.34</v>
+        <v>1023.74</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>926.8</v>
+        <v>922.25</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>891.9400000000001</v>
+        <v>894.83</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>847.09</v>
+        <v>850.04</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>702.27</v>
+        <v>704.45</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2870,24 +2870,24 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>174.42</v>
+        <v>175.76</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>174.62</v>
+        <v>174.73</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>179.72</v>
+        <v>179.56</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>182.02</v>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>181.96</v>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>275.85</v>
+        <v>273.15</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>287.94</v>
+        <v>286.54</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>297.57</v>
+        <v>296.61</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>302.95</v>
+        <v>302.65</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
@@ -2958,20 +2958,20 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>503.35</v>
+        <v>501.95</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>524.74</v>
+        <v>522.5700000000001</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>545.64</v>
+        <v>543.9299999999999</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>542.28</v>
+        <v>541.88</v>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
@@ -3002,20 +3002,20 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>4033.6</v>
+        <v>4135.9</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>3818.13</v>
+        <v>3848.4</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>3568.26</v>
+        <v>3590.52</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>2728.1</v>
+        <v>2742.11</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
@@ -3046,24 +3046,24 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>538.25</v>
+        <v>561.5</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>555.1900000000001</v>
+        <v>555.79</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>535.76</v>
+        <v>536.77</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>528.35</v>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>528.6799999999999</v>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
@@ -3090,20 +3090,20 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>1922.8</v>
+        <v>1893.1</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>2025.41</v>
+        <v>2012.81</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>2030.12</v>
+        <v>2024.74</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>1839.91</v>
+        <v>1840.44</v>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
@@ -3134,20 +3134,20 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>186.02</v>
+        <v>182.65</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>176.06</v>
+        <v>176.69</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>159.29</v>
+        <v>160.2</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>131.04</v>
+        <v>131.55</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
@@ -3178,20 +3178,20 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>604.7</v>
+        <v>593.95</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>558.28</v>
+        <v>561.6799999999999</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>543.4400000000001</v>
+        <v>545.42</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>494.94</v>
+        <v>495.92</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
@@ -3222,20 +3222,20 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>1654.2</v>
+        <v>1623.5</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1735.67</v>
+        <v>1724.99</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>1723.69</v>
+        <v>1719.77</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1795.07</v>
+        <v>1793.36</v>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
@@ -3266,20 +3266,20 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>155.61</v>
+        <v>152.43</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>159.02</v>
+        <v>158.39</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>163.88</v>
+        <v>163.43</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>170.73</v>
+        <v>170.55</v>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
@@ -3310,20 +3310,20 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>3407.8</v>
+        <v>3455</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>3274.81</v>
+        <v>3291.98</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>3138.36</v>
+        <v>3150.77</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>2671.56</v>
+        <v>2679.36</v>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
@@ -3354,20 +3354,20 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>261.95</v>
+        <v>261.9</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>264.29</v>
+        <v>264.06</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>262.68</v>
+        <v>262.65</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>237.43</v>
+        <v>237.67</v>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
@@ -3398,20 +3398,20 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>502.55</v>
+        <v>502.75</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>509.55</v>
+        <v>508.9</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>519.65</v>
+        <v>518.99</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>574.9299999999999</v>
+        <v>574.21</v>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
@@ -3442,20 +3442,20 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>582.2</v>
+        <v>602.1</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>574.61</v>
+        <v>577.23</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>564.24</v>
+        <v>565.72</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>521.27</v>
+        <v>522.0700000000001</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
@@ -3486,20 +3486,20 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>23.86</v>
+        <v>23.43</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>22.77</v>
+        <v>22.83</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>22.5</v>
+        <v>22.54</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>22.63</v>
+        <v>22.64</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
@@ -3530,34 +3530,34 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>196.2</v>
+        <v>206.06</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>199.92</v>
+        <v>200.5</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>205.25</v>
+        <v>205.28</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>205.04</v>
-      </c>
-      <c r="G65" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H65" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>205.05</v>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J65" s="12" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>193.06</v>
+        <v>192.38</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>197.87</v>
+        <v>197.35</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>203.24</v>
+        <v>202.81</v>
       </c>
       <c r="F66" s="10" t="n">
         <v>192.24</v>
@@ -3618,24 +3618,24 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>694.25</v>
+        <v>678.45</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>686</v>
+        <v>685.28</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>665.35</v>
+        <v>665.87</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>653.41</v>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>653.66</v>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -3662,20 +3662,20 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>1848.6</v>
+        <v>1875.7</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>1648.31</v>
+        <v>1669.97</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>1644.14</v>
+        <v>1653.22</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1601.13</v>
+        <v>1603.87</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3706,24 +3706,24 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>696.85</v>
+        <v>670.45</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>693.24</v>
+        <v>691.0700000000001</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>719.47</v>
+        <v>717.55</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>831.83</v>
-      </c>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>830.23</v>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -3750,20 +3750,20 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>2215.9</v>
+        <v>2185.5</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>2081.78</v>
+        <v>2091.66</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>1971.32</v>
+        <v>1979.72</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1611.19</v>
+        <v>1616.91</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
@@ -3794,29 +3794,29 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>6975.5</v>
+        <v>6752.5</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>7111.93</v>
+        <v>7077.7</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>6900.09</v>
+        <v>6894.31</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>5489.72</v>
+        <v>5502.28</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H71" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I71" s="13" t="inlineStr">
@@ -3838,20 +3838,20 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>46.82</v>
+        <v>46.41</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>46.12</v>
+        <v>46.15</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>45.54</v>
+        <v>45.58</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>41.48</v>
+        <v>41.53</v>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
@@ -3882,20 +3882,20 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>473</v>
+        <v>467.8</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>489.73</v>
+        <v>487.65</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>510.68</v>
+        <v>509</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>583.17</v>
+        <v>582.02</v>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
@@ -3926,20 +3926,20 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>153.05</v>
+        <v>152.64</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>143.73</v>
+        <v>144.58</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>136.78</v>
+        <v>137.4</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>150.31</v>
+        <v>150.33</v>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
@@ -3970,20 +3970,20 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>2475.4</v>
+        <v>2359.3</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>2338.27</v>
+        <v>2340.27</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>2209.26</v>
+        <v>2215.15</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1767.94</v>
+        <v>1773.82</v>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
@@ -4014,20 +4014,20 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>333.7</v>
+        <v>326.1</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>367.15</v>
+        <v>363.24</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>375.82</v>
+        <v>373.87</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>372.32</v>
+        <v>371.86</v>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
@@ -4058,24 +4058,24 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>795.9</v>
+        <v>783.5</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>786.83</v>
+        <v>786.51</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>822.42</v>
+        <v>820.9</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>887.88</v>
-      </c>
-      <c r="G77" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>886.84</v>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
@@ -4102,20 +4102,20 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>312.85</v>
+        <v>311.1</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>330.64</v>
+        <v>328.78</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>337.56</v>
+        <v>336.53</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>366.69</v>
+        <v>366.13</v>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
@@ -4146,20 +4146,20 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>2803.8</v>
+        <v>2859.2</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>2571.31</v>
+        <v>2598.73</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>2516.39</v>
+        <v>2529.84</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>2482.5</v>
+        <v>2486.25</v>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
@@ -4190,20 +4190,20 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>184.08</v>
+        <v>182.03</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>194.74</v>
+        <v>193.53</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>203.34</v>
+        <v>202.51</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>214.68</v>
+        <v>214.36</v>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
@@ -4234,24 +4234,24 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>160.58</v>
+        <v>158.59</v>
       </c>
       <c r="D81" s="10" t="n">
-        <v>158.99</v>
+        <v>158.95</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>154.35</v>
+        <v>154.52</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>154.09</v>
-      </c>
-      <c r="G81" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>154.13</v>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
@@ -4278,20 +4278,20 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>72.54000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>74.40000000000001</v>
+        <v>74.23</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>74.84999999999999</v>
+        <v>74.77</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>69.91</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
@@ -4322,24 +4322,24 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>203.27</v>
+        <v>200.58</v>
       </c>
       <c r="D83" s="10" t="n">
-        <v>202.3</v>
+        <v>202.14</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>207.28</v>
+        <v>207.02</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>184.28</v>
-      </c>
-      <c r="G83" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>184.44</v>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -4366,20 +4366,20 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>589.1</v>
+        <v>574.6</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>577.77</v>
+        <v>558.83</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>554.45</v>
+        <v>536.25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>512.99</v>
+        <v>495.5</v>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
@@ -4410,20 +4410,20 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>15.36</v>
+        <v>15.41</v>
       </c>
       <c r="D85" s="10" t="n">
-        <v>15.54</v>
+        <v>15.53</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>15.75</v>
+        <v>15.74</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>16.08</v>
+        <v>16.07</v>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
@@ -4454,20 +4454,20 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>845.25</v>
+        <v>833.5</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>875.36</v>
+        <v>871.38</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>910.1900000000001</v>
+        <v>907.1799999999999</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>956.13</v>
+        <v>954.91</v>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
@@ -4498,20 +4498,20 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>2213</v>
+        <v>2255.2</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>2167.1</v>
+        <v>2175.49</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>2097.3</v>
+        <v>2103.5</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1772.33</v>
+        <v>1777.14</v>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
@@ -4542,20 +4542,20 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>644.9</v>
+        <v>650.8</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>652.45</v>
+        <v>652.29</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>657.27</v>
+        <v>657.01</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>620.9</v>
+        <v>621.1900000000001</v>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
@@ -4586,20 +4586,20 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
-        <v>1306.7</v>
+        <v>1301.2</v>
       </c>
       <c r="D89" s="10" t="n">
-        <v>1355.88</v>
+        <v>1350.67</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>1380.57</v>
+        <v>1377.46</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>1308.58</v>
+        <v>1308.51</v>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
@@ -4630,20 +4630,20 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>138.8</v>
+        <v>133.63</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>128.09</v>
+        <v>128.61</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>123.59</v>
+        <v>123.99</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>116.75</v>
+        <v>116.91</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -4674,20 +4674,20 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="10" t="n">
-        <v>579.55</v>
+        <v>581.35</v>
       </c>
       <c r="D91" s="10" t="n">
-        <v>539.05</v>
+        <v>543.08</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>493.85</v>
+        <v>497.28</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>496.62</v>
+        <v>497.47</v>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
@@ -4718,20 +4718,20 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>1860.6</v>
+        <v>1810.5</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1750.82</v>
+        <v>1756.5</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>1605.59</v>
+        <v>1613.63</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1165.24</v>
+        <v>1171.67</v>
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
@@ -4762,20 +4762,20 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="10" t="n">
-        <v>71.05</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="D93" s="10" t="n">
-        <v>74.36</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>75.15000000000001</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>69.25</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
@@ -4806,20 +4806,20 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>335.9</v>
+        <v>330.15</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>317.66</v>
+        <v>318.85</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>292.3</v>
+        <v>293.78</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>238.57</v>
+        <v>239.48</v>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
@@ -4850,20 +4850,20 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="10" t="n">
-        <v>274.8</v>
+        <v>282.75</v>
       </c>
       <c r="D95" s="10" t="n">
-        <v>295.64</v>
+        <v>294.41</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>326.59</v>
+        <v>324.87</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>412.94</v>
+        <v>411.65</v>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
@@ -4894,20 +4894,20 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>581.35</v>
+        <v>570.8</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>549.89</v>
+        <v>551.88</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>533.62</v>
+        <v>535.08</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>449.2</v>
+        <v>450.41</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
@@ -4938,20 +4938,20 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>770.9</v>
+        <v>763.1</v>
       </c>
       <c r="D97" s="10" t="n">
-        <v>754.36</v>
+        <v>755.1900000000001</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>787.87</v>
+        <v>786.9</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>719.28</v>
+        <v>719.71</v>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
@@ -4982,20 +4982,20 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>236.58</v>
+        <v>231.25</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>250</v>
+        <v>248.22</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>262.69</v>
+        <v>261.45</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>306.43</v>
+        <v>305.68</v>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -5026,20 +5026,20 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>1853.3</v>
+        <v>1850.2</v>
       </c>
       <c r="D99" s="10" t="n">
-        <v>1892.11</v>
+        <v>1888.12</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>1877.67</v>
+        <v>1876.6</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>1783.2</v>
+        <v>1783.86</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -5070,20 +5070,20 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>229.55</v>
+        <v>228.1</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>210.34</v>
+        <v>212.03</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>198.99</v>
+        <v>200.13</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>181.78</v>
+        <v>182.24</v>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
@@ -5114,20 +5114,20 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>862.7</v>
+        <v>841.4</v>
       </c>
       <c r="D101" s="10" t="n">
-        <v>911.26</v>
+        <v>904.61</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>897.95</v>
+        <v>895.73</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>746.14</v>
+        <v>747.09</v>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -5158,20 +5158,20 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>415.3</v>
+        <v>408.85</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>397</v>
+        <v>398.13</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>384.35</v>
+        <v>385.31</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>366.58</v>
+        <v>367</v>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
@@ -5202,20 +5202,20 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>663.45</v>
+        <v>669.95</v>
       </c>
       <c r="D103" s="10" t="n">
-        <v>678.85</v>
+        <v>678.01</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>720.11</v>
+        <v>718.15</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>800.86</v>
+        <v>799.5599999999999</v>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
@@ -5246,20 +5246,20 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>11365</v>
+        <v>11069</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>10735.86</v>
+        <v>10767.59</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>10254.95</v>
+        <v>10286.88</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>9313.68</v>
+        <v>9331.139999999999</v>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
@@ -5290,20 +5290,20 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>745</v>
+        <v>724.85</v>
       </c>
       <c r="D105" s="10" t="n">
-        <v>746.3</v>
+        <v>744.26</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>768.08</v>
+        <v>766.38</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>715.38</v>
+        <v>715.48</v>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -5334,20 +5334,20 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>90.68000000000001</v>
+        <v>91.36</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>94.48</v>
+        <v>94.19</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>93.08</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>85.38</v>
+        <v>85.44</v>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
@@ -5378,20 +5378,20 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="10" t="n">
-        <v>1955.9</v>
+        <v>1990.6</v>
       </c>
       <c r="D107" s="10" t="n">
-        <v>1935.03</v>
+        <v>1940.32</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>1809.17</v>
+        <v>1816.29</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>1593.94</v>
+        <v>1597.89</v>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
@@ -5422,20 +5422,20 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>959.9</v>
+        <v>960.6</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>872.8099999999999</v>
+        <v>881.17</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>761.89</v>
+        <v>769.6799999999999</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>549.87</v>
+        <v>553.96</v>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
@@ -5466,20 +5466,20 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="10" t="n">
-        <v>1187.4</v>
+        <v>1195.7</v>
       </c>
       <c r="D109" s="10" t="n">
-        <v>1046.2</v>
+        <v>1060.44</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>1037.52</v>
+        <v>1043.72</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>991.48</v>
+        <v>993.51</v>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
@@ -5510,20 +5510,20 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>672.1</v>
+        <v>664.95</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>703.8200000000001</v>
+        <v>700.12</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>745.6900000000001</v>
+        <v>742.52</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>886.73</v>
+        <v>884.52</v>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
@@ -5554,20 +5554,20 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>450.85</v>
+        <v>445.55</v>
       </c>
       <c r="D111" s="10" t="n">
-        <v>432.66</v>
+        <v>433.89</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>411.75</v>
+        <v>413.07</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>341.55</v>
+        <v>342.58</v>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
@@ -5598,20 +5598,20 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>915.65</v>
+        <v>911.4</v>
       </c>
       <c r="D112" s="10" t="n">
-        <v>831.3099999999999</v>
+        <v>838.9400000000001</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>838.6900000000001</v>
+        <v>841.54</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>783.33</v>
+        <v>784.6</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -5642,20 +5642,20 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="10" t="n">
-        <v>431.75</v>
+        <v>437.45</v>
       </c>
       <c r="D113" s="10" t="n">
-        <v>391.42</v>
+        <v>395.81</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>392.45</v>
+        <v>394.21</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>396.09</v>
+        <v>396.51</v>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
@@ -5686,20 +5686,20 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>205.29</v>
+        <v>204.01</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>210.74</v>
+        <v>210.1</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>217.68</v>
+        <v>217.14</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>244.68</v>
+        <v>244.27</v>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
@@ -5730,20 +5730,20 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>75.01000000000001</v>
+        <v>78.36</v>
       </c>
       <c r="D115" s="10" t="n">
-        <v>80.34</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>88.04000000000001</v>
+        <v>87.66</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>96.59999999999999</v>
+        <v>96.42</v>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
@@ -5774,20 +5774,20 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>287</v>
+        <v>301.3</v>
       </c>
       <c r="D116" s="10" t="n">
-        <v>848.12</v>
+        <v>796.05</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>979.89</v>
+        <v>953.28</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>987.98</v>
+        <v>981.15</v>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
@@ -5818,20 +5818,20 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="10" t="n">
-        <v>322.8</v>
+        <v>355.05</v>
       </c>
       <c r="D117" s="10" t="n">
-        <v>317.83</v>
+        <v>321.38</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>302.6</v>
+        <v>304.66</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>313.09</v>
+        <v>313.51</v>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
@@ -5862,20 +5862,20 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>3277.5</v>
+        <v>3302.5</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>3334.43</v>
+        <v>3331.39</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>3202.08</v>
+        <v>3206.02</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>2874.46</v>
+        <v>2878.72</v>
       </c>
       <c r="G118" s="11" t="inlineStr">
         <is>
@@ -5906,20 +5906,20 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>4438.2</v>
+        <v>4500.8</v>
       </c>
       <c r="D119" s="10" t="n">
-        <v>4516.76</v>
+        <v>4515.24</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>4333.4</v>
+        <v>4339.97</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>3628.56</v>
+        <v>3637.24</v>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
@@ -5950,20 +5950,20 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>671.7</v>
+        <v>668.2</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>671.75</v>
+        <v>671.42</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>703.28</v>
+        <v>701.9</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>761.36</v>
+        <v>760.4400000000001</v>
       </c>
       <c r="G120" s="11" t="inlineStr">
         <is>
@@ -5994,20 +5994,20 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>292.05</v>
+        <v>291.55</v>
       </c>
       <c r="D121" s="10" t="n">
-        <v>320.01</v>
+        <v>317.3</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>350.55</v>
+        <v>348.23</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>403.04</v>
+        <v>401.93</v>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
@@ -6038,20 +6038,20 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>505.45</v>
+        <v>506.2</v>
       </c>
       <c r="D122" s="10" t="n">
-        <v>518.95</v>
+        <v>517.74</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>546.11</v>
+        <v>544.54</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>670.46</v>
+        <v>668.8200000000001</v>
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
@@ -6082,24 +6082,24 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="10" t="n">
-        <v>610.15</v>
+        <v>627.25</v>
       </c>
       <c r="D123" s="10" t="n">
-        <v>617.37</v>
+        <v>618.3099999999999</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>575.2</v>
+        <v>577.24</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>498.6</v>
-      </c>
-      <c r="G123" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>499.88</v>
+      </c>
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H123" s="13" t="inlineStr">
@@ -6126,20 +6126,20 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>1660.2</v>
+        <v>1597.3</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>1505.72</v>
+        <v>1514.44</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>1386.35</v>
+        <v>1394.62</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1129.04</v>
+        <v>1133.7</v>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
@@ -6170,20 +6170,20 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="10" t="n">
-        <v>216.81</v>
+        <v>214.86</v>
       </c>
       <c r="D125" s="10" t="n">
-        <v>222.94</v>
+        <v>222.17</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>225.31</v>
+        <v>224.9</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>241.43</v>
+        <v>241.17</v>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -6214,20 +6214,20 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>460.55</v>
+        <v>460.3</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>496.96</v>
+        <v>493.47</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>506.62</v>
+        <v>504.8</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>540</v>
+        <v>539.2</v>
       </c>
       <c r="G126" s="11" t="inlineStr">
         <is>
@@ -6258,20 +6258,20 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>431.05</v>
+        <v>434.45</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>412.61</v>
+        <v>414.69</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>391.41</v>
+        <v>393.1</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>370.69</v>
+        <v>371.32</v>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
@@ -6302,20 +6302,20 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>824.65</v>
+        <v>821.2</v>
       </c>
       <c r="D128" s="10" t="n">
-        <v>825.16</v>
+        <v>824.79</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>792.88</v>
+        <v>793.99</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>731.04</v>
+        <v>731.9400000000001</v>
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
@@ -6346,20 +6346,20 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>736.6</v>
+        <v>741.1</v>
       </c>
       <c r="D129" s="10" t="n">
-        <v>749.95</v>
+        <v>749.11</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>707.28</v>
+        <v>708.61</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>591.08</v>
+        <v>592.5700000000001</v>
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
@@ -6390,24 +6390,24 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>170.91</v>
+        <v>189.46</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>171.51</v>
+        <v>172.77</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>167.71</v>
+        <v>168.09</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>156.92</v>
-      </c>
-      <c r="G130" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>156.79</v>
+      </c>
+      <c r="G130" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
@@ -6434,24 +6434,24 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="10" t="n">
-        <v>690.6</v>
+        <v>712.55</v>
       </c>
       <c r="D131" s="10" t="n">
-        <v>704.58</v>
+        <v>705.34</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>685.84</v>
+        <v>686.89</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>643.61</v>
-      </c>
-      <c r="G131" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>644.3</v>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
@@ -6478,20 +6478,20 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>433.05</v>
+        <v>426.3</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>437.18</v>
+        <v>436.15</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>438.21</v>
+        <v>437.74</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>473.76</v>
+        <v>473.28</v>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="10" t="n">
-        <v>781.3</v>
+        <v>785.45</v>
       </c>
       <c r="D133" s="10" t="n">
-        <v>786.97</v>
+        <v>786.83</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>789.14</v>
+        <v>789</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>767.95</v>
+        <v>768.12</v>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6566,20 +6566,20 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>1922.3</v>
+        <v>1848.7</v>
       </c>
       <c r="D134" s="10" t="n">
-        <v>1793.56</v>
+        <v>1798.81</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>1735.61</v>
+        <v>1740.04</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1449.51</v>
+        <v>1453.48</v>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
@@ -6610,20 +6610,20 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="10" t="n">
-        <v>242.25</v>
+        <v>238.7</v>
       </c>
       <c r="D135" s="10" t="n">
-        <v>254.83</v>
+        <v>253.29</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>255.47</v>
+        <v>254.81</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>261.25</v>
+        <v>261.03</v>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6654,24 +6654,24 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>95.54000000000001</v>
+        <v>100.5</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>96.66</v>
+        <v>97.03</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>88.03</v>
+        <v>88.52</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>75.59</v>
-      </c>
-      <c r="G136" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>75.84</v>
+      </c>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -6698,20 +6698,20 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="10" t="n">
-        <v>382.15</v>
+        <v>380.1</v>
       </c>
       <c r="D137" s="10" t="n">
-        <v>368.87</v>
+        <v>369.94</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>355.23</v>
+        <v>356.2</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>365.86</v>
+        <v>366</v>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
@@ -6742,20 +6742,20 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>2038.2</v>
+        <v>2021.6</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>2161.52</v>
+        <v>2148.19</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>2225.44</v>
+        <v>2217.44</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2172.97</v>
+        <v>2171.47</v>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
@@ -6786,20 +6786,20 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="10" t="n">
-        <v>614.6</v>
+        <v>623.1</v>
       </c>
       <c r="D139" s="10" t="n">
-        <v>604.03</v>
+        <v>605.85</v>
       </c>
       <c r="E139" s="10" t="n">
-        <v>604.9</v>
+        <v>605.61</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>552.99</v>
+        <v>553.6900000000001</v>
       </c>
       <c r="G139" s="13" t="inlineStr">
         <is>
@@ -6830,29 +6830,29 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>338.85</v>
+        <v>326.7</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>339.21</v>
+        <v>338.02</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>338.41</v>
+        <v>337.95</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>348.6</v>
+        <v>348.38</v>
       </c>
       <c r="G140" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H140" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I140" s="11" t="inlineStr">
@@ -6874,20 +6874,20 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>435.2</v>
+        <v>451.5</v>
       </c>
       <c r="D141" s="10" t="n">
-        <v>432.92</v>
+        <v>434.69</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>402.67</v>
+        <v>404.58</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>308.52</v>
+        <v>309.95</v>
       </c>
       <c r="G141" s="13" t="inlineStr">
         <is>
@@ -6918,20 +6918,20 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>1344.2</v>
+        <v>1277.3</v>
       </c>
       <c r="D142" s="10" t="n">
-        <v>1180.24</v>
+        <v>1189.49</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>1038.7</v>
+        <v>1048.06</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>826.1900000000001</v>
+        <v>830.6799999999999</v>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
@@ -6962,20 +6962,20 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="10" t="n">
-        <v>128.92</v>
+        <v>128.93</v>
       </c>
       <c r="D143" s="10" t="n">
-        <v>123.97</v>
+        <v>124.44</v>
       </c>
       <c r="E143" s="10" t="n">
-        <v>126.71</v>
+        <v>126.79</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>122.49</v>
+        <v>122.56</v>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
@@ -7006,24 +7006,24 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>220.17</v>
+        <v>219.67</v>
       </c>
       <c r="D144" s="10" t="n">
-        <v>220</v>
+        <v>219.97</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>221.09</v>
+        <v>221.03</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>215.3</v>
-      </c>
-      <c r="G144" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>215.35</v>
+      </c>
+      <c r="G144" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H144" s="11" t="inlineStr">
@@ -7050,20 +7050,20 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="10" t="n">
-        <v>283.35</v>
+        <v>282</v>
       </c>
       <c r="D145" s="10" t="n">
-        <v>300.61</v>
+        <v>298.84</v>
       </c>
       <c r="E145" s="10" t="n">
-        <v>300.29</v>
+        <v>299.57</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>283.81</v>
+        <v>283.8</v>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -7094,20 +7094,20 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>113.73</v>
+        <v>112.64</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>119</v>
+        <v>118.39</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>123.07</v>
+        <v>122.66</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>129.92</v>
+        <v>129.75</v>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -7138,24 +7138,24 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="10" t="n">
-        <v>162.3</v>
+        <v>156.94</v>
       </c>
       <c r="D147" s="10" t="n">
-        <v>157.71</v>
+        <v>157.63</v>
       </c>
       <c r="E147" s="10" t="n">
-        <v>155.34</v>
+        <v>155.41</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="G147" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>147.85</v>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
@@ -7182,20 +7182,20 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>419</v>
+        <v>424.05</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>447.87</v>
+        <v>445.61</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>469.71</v>
+        <v>467.92</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>527.88</v>
+        <v>526.85</v>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
@@ -7226,20 +7226,20 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="10" t="n">
-        <v>95.61</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="D149" s="10" t="n">
         <v>94.81</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>97.33</v>
+        <v>97.23</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>104.2</v>
+        <v>104.11</v>
       </c>
       <c r="G149" s="13" t="inlineStr">
         <is>
@@ -7270,20 +7270,20 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>2093.2</v>
+        <v>2197.2</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>2090.5</v>
+        <v>2100.66</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>2042.8</v>
+        <v>2048.85</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1781.52</v>
+        <v>1785.66</v>
       </c>
       <c r="G150" s="13" t="inlineStr">
         <is>
@@ -7314,20 +7314,20 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="10" t="n">
-        <v>2415.1</v>
+        <v>2430.1</v>
       </c>
       <c r="D151" s="10" t="n">
-        <v>2475.73</v>
+        <v>2471.38</v>
       </c>
       <c r="E151" s="10" t="n">
-        <v>2521.4</v>
+        <v>2517.82</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>2514.8</v>
+        <v>2513.96</v>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -7358,20 +7358,20 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>969.9</v>
+        <v>989.7</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>929.42</v>
+        <v>935.17</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>885.04</v>
+        <v>889.15</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>787.45</v>
+        <v>789.46</v>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
@@ -7402,20 +7402,20 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="10" t="n">
-        <v>2132.9</v>
+        <v>2093.3</v>
       </c>
       <c r="D153" s="10" t="n">
-        <v>1873.45</v>
+        <v>1894.39</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>1745.41</v>
+        <v>1759.06</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>1532.78</v>
+        <v>1538.36</v>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
@@ -7446,20 +7446,20 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>1851.8</v>
+        <v>1828.3</v>
       </c>
       <c r="D154" s="10" t="n">
-        <v>1659.83</v>
+        <v>1675.88</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>1466.2</v>
+        <v>1480.4</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1260.34</v>
+        <v>1265.99</v>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
@@ -7490,20 +7490,20 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="10" t="n">
-        <v>282.25</v>
+        <v>281.85</v>
       </c>
       <c r="D155" s="10" t="n">
-        <v>283.43</v>
+        <v>283.28</v>
       </c>
       <c r="E155" s="10" t="n">
-        <v>280.46</v>
+        <v>280.51</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>236.39</v>
+        <v>236.84</v>
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>11584</v>
+        <v>11625</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>11435.54</v>
+        <v>11453.58</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>11099.04</v>
+        <v>11119.67</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10097.91</v>
+        <v>10113.11</v>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
@@ -7578,20 +7578,20 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="10" t="n">
-        <v>2114.9</v>
+        <v>2146.5</v>
       </c>
       <c r="D157" s="10" t="n">
-        <v>2104.01</v>
+        <v>2108.06</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>2180.56</v>
+        <v>2179.23</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>2231.12</v>
+        <v>2230.27</v>
       </c>
       <c r="G157" s="13" t="inlineStr">
         <is>
@@ -7622,24 +7622,24 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>2366.8</v>
+        <v>2277.9</v>
       </c>
       <c r="D158" s="10" t="n">
-        <v>2325.11</v>
+        <v>2320.61</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>2189.71</v>
+        <v>2193.17</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>1813.29</v>
-      </c>
-      <c r="G158" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1817.92</v>
+      </c>
+      <c r="G158" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
@@ -7666,29 +7666,29 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="10" t="n">
-        <v>675.95</v>
+        <v>687</v>
       </c>
       <c r="D159" s="10" t="n">
-        <v>667.54</v>
+        <v>669.4</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>686.16</v>
+        <v>686.1900000000001</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>647.62</v>
+        <v>648.01</v>
       </c>
       <c r="G159" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H159" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H159" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I159" s="13" t="inlineStr">
@@ -7710,20 +7710,20 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>484.7</v>
+        <v>481.25</v>
       </c>
       <c r="D160" s="10" t="n">
-        <v>501.51</v>
+        <v>499.58</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>517.7</v>
+        <v>516.27</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>553.71</v>
+        <v>552.98</v>
       </c>
       <c r="G160" s="11" t="inlineStr">
         <is>
@@ -7754,17 +7754,17 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>118.26</v>
+        <v>115.16</v>
       </c>
       <c r="D161" s="10" t="n">
-        <v>111.56</v>
+        <v>111.9</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>110.34</v>
+        <v>110.53</v>
       </c>
       <c r="F161" s="10" t="n">
         <v>115.48</v>
@@ -7779,9 +7779,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I161" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I161" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
@@ -7798,20 +7798,20 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>477</v>
+        <v>463.8</v>
       </c>
       <c r="D162" s="10" t="n">
-        <v>424.28</v>
+        <v>428.04</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>418.55</v>
+        <v>420.33</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>395.17</v>
+        <v>395.86</v>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>160.81</v>
+        <v>160.03</v>
       </c>
       <c r="D163" s="10" t="n">
-        <v>160.35</v>
+        <v>160.32</v>
       </c>
       <c r="E163" s="10" t="n">
-        <v>160.89</v>
+        <v>160.85</v>
       </c>
       <c r="F163" s="10" t="n">
-        <v>168.87</v>
-      </c>
-      <c r="G163" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>168.78</v>
+      </c>
+      <c r="G163" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
@@ -7886,20 +7886,20 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="10" t="n">
-        <v>498.75</v>
+        <v>499.2</v>
       </c>
       <c r="D164" s="10" t="n">
-        <v>536.83</v>
+        <v>533.25</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>557.1</v>
+        <v>554.83</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>641.84</v>
+        <v>640.42</v>
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7930,20 +7930,20 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="10" t="n">
-        <v>778.55</v>
+        <v>764.1</v>
       </c>
       <c r="D165" s="10" t="n">
-        <v>713.1900000000001</v>
+        <v>718.04</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>662.64</v>
+        <v>666.62</v>
       </c>
       <c r="F165" s="10" t="n">
-        <v>560.91</v>
+        <v>562.9299999999999</v>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="10" t="n">
-        <v>194.59</v>
+        <v>195.1</v>
       </c>
       <c r="D166" s="10" t="n">
-        <v>203.24</v>
+        <v>202.47</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>204.13</v>
+        <v>203.77</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>230.73</v>
+        <v>230.37</v>
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
@@ -8018,20 +8018,20 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="10" t="n">
-        <v>215.98</v>
+        <v>214.25</v>
       </c>
       <c r="D167" s="10" t="n">
-        <v>224.73</v>
+        <v>223.73</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>232.05</v>
+        <v>231.35</v>
       </c>
       <c r="F167" s="10" t="n">
-        <v>230.35</v>
+        <v>230.19</v>
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
@@ -8062,20 +8062,20 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="10" t="n">
-        <v>552.65</v>
+        <v>547.95</v>
       </c>
       <c r="D168" s="10" t="n">
-        <v>524.75</v>
+        <v>526.96</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>501.69</v>
+        <v>503.5</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>472.17</v>
+        <v>472.92</v>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
@@ -8106,20 +8106,20 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="10" t="n">
-        <v>421.5</v>
+        <v>423.45</v>
       </c>
       <c r="D169" s="10" t="n">
-        <v>419.59</v>
+        <v>419.96</v>
       </c>
       <c r="E169" s="10" t="n">
-        <v>410.62</v>
+        <v>411.12</v>
       </c>
       <c r="F169" s="10" t="n">
-        <v>404.12</v>
+        <v>404.31</v>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
@@ -8150,20 +8150,20 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>849.45</v>
+        <v>839.4</v>
       </c>
       <c r="D170" s="10" t="n">
-        <v>816.25</v>
+        <v>818.46</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>751.64</v>
+        <v>755.08</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>637.46</v>
+        <v>639.47</v>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
@@ -8194,20 +8194,20 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="10" t="n">
-        <v>440.35</v>
+        <v>446.05</v>
       </c>
       <c r="D171" s="10" t="n">
-        <v>449.03</v>
+        <v>448.74</v>
       </c>
       <c r="E171" s="10" t="n">
-        <v>452.58</v>
+        <v>452.33</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>460.73</v>
+        <v>460.59</v>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
@@ -8238,20 +8238,20 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="10" t="n">
-        <v>1140.3</v>
+        <v>1111.2</v>
       </c>
       <c r="D172" s="10" t="n">
-        <v>1145.73</v>
+        <v>1142.44</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>1102.57</v>
+        <v>1102.91</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>1040.87</v>
+        <v>1041.57</v>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
@@ -8282,20 +8282,20 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>177.06</v>
+        <v>179</v>
       </c>
       <c r="D173" s="10" t="n">
-        <v>200.13</v>
+        <v>198.12</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>213.71</v>
+        <v>212.35</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>228.29</v>
+        <v>227.8</v>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
@@ -8326,20 +8326,20 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="10" t="n">
-        <v>541.65</v>
+        <v>541.55</v>
       </c>
       <c r="D174" s="10" t="n">
-        <v>560.8099999999999</v>
+        <v>558.98</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>520.01</v>
+        <v>520.85</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>516.78</v>
+        <v>517.03</v>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
@@ -8370,29 +8370,29 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="10" t="n">
-        <v>556.35</v>
+        <v>541.95</v>
       </c>
       <c r="D175" s="10" t="n">
-        <v>570.73</v>
+        <v>567.99</v>
       </c>
       <c r="E175" s="10" t="n">
-        <v>554.01</v>
+        <v>553.54</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>508.27</v>
+        <v>508.6</v>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H175" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H175" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I175" s="13" t="inlineStr">
@@ -8414,20 +8414,20 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="10" t="n">
-        <v>154.2</v>
+        <v>153.12</v>
       </c>
       <c r="D176" s="10" t="n">
-        <v>157.12</v>
+        <v>156.74</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>158.81</v>
+        <v>158.59</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>157.02</v>
+        <v>156.98</v>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
@@ -8458,20 +8458,20 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="10" t="n">
-        <v>180.11</v>
+        <v>177.06</v>
       </c>
       <c r="D177" s="10" t="n">
-        <v>188.84</v>
+        <v>187.72</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>197.78</v>
+        <v>196.96</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>248.58</v>
+        <v>247.87</v>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
@@ -8502,20 +8502,20 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="10" t="n">
-        <v>1519.7</v>
+        <v>1513.2</v>
       </c>
       <c r="D178" s="10" t="n">
-        <v>1378.28</v>
+        <v>1391.13</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>1281.49</v>
+        <v>1290.58</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>1071.31</v>
+        <v>1075.71</v>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="10" t="n">
-        <v>254.61</v>
+        <v>256.65</v>
       </c>
       <c r="D179" s="10" t="n">
-        <v>243.23</v>
+        <v>244.5</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>244.6</v>
+        <v>245.07</v>
       </c>
       <c r="F179" s="10" t="n">
-        <v>241.16</v>
+        <v>241.31</v>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
@@ -8590,24 +8590,24 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="10" t="n">
-        <v>383.35</v>
+        <v>388.75</v>
       </c>
       <c r="D180" s="10" t="n">
-        <v>387.32</v>
+        <v>387.45</v>
       </c>
       <c r="E180" s="10" t="n">
-        <v>369.18</v>
+        <v>369.95</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>326.6</v>
-      </c>
-      <c r="G180" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>327.21</v>
+      </c>
+      <c r="G180" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -8634,20 +8634,20 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="10" t="n">
-        <v>27.3</v>
+        <v>26.92</v>
       </c>
       <c r="D181" s="10" t="n">
-        <v>28.59</v>
+        <v>28.43</v>
       </c>
       <c r="E181" s="10" t="n">
-        <v>29.6</v>
+        <v>29.49</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>35.2</v>
+        <v>35.12</v>
       </c>
       <c r="G181" s="11" t="inlineStr">
         <is>
@@ -8678,20 +8678,20 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="10" t="n">
-        <v>7.28</v>
+        <v>7.25</v>
       </c>
       <c r="D182" s="10" t="n">
-        <v>7.76</v>
+        <v>7.72</v>
       </c>
       <c r="E182" s="10" t="n">
-        <v>8.26</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="G182" s="11" t="inlineStr">
         <is>
@@ -8722,20 +8722,20 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="10" t="n">
-        <v>608.3</v>
+        <v>599.8</v>
       </c>
       <c r="D183" s="10" t="n">
-        <v>656.51</v>
+        <v>651.11</v>
       </c>
       <c r="E183" s="10" t="n">
-        <v>667.61</v>
+        <v>664.95</v>
       </c>
       <c r="F183" s="10" t="n">
-        <v>630.26</v>
+        <v>629.96</v>
       </c>
       <c r="G183" s="11" t="inlineStr">
         <is>
@@ -8766,20 +8766,20 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="10" t="n">
-        <v>272.75</v>
+        <v>268.8</v>
       </c>
       <c r="D184" s="10" t="n">
-        <v>281.5</v>
+        <v>280.29</v>
       </c>
       <c r="E184" s="10" t="n">
-        <v>308.09</v>
+        <v>306.55</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>354.7</v>
+        <v>353.84</v>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8810,20 +8810,20 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="10" t="n">
-        <v>728.5</v>
+        <v>722.05</v>
       </c>
       <c r="D185" s="10" t="n">
-        <v>767.92</v>
+        <v>763.55</v>
       </c>
       <c r="E185" s="10" t="n">
-        <v>802.1799999999999</v>
+        <v>799.04</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>900.88</v>
+        <v>899.1</v>
       </c>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8854,20 +8854,20 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="10" t="n">
-        <v>13267</v>
+        <v>13270</v>
       </c>
       <c r="D186" s="10" t="n">
-        <v>13452.1</v>
+        <v>13434.76</v>
       </c>
       <c r="E186" s="10" t="n">
-        <v>13232.1</v>
+        <v>13233.59</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>13276.28</v>
+        <v>13276.22</v>
       </c>
       <c r="G186" s="11" t="inlineStr">
         <is>
@@ -8898,20 +8898,20 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="10" t="n">
-        <v>339.4</v>
+        <v>338.05</v>
       </c>
       <c r="D187" s="10" t="n">
-        <v>336.93</v>
+        <v>337.04</v>
       </c>
       <c r="E187" s="10" t="n">
-        <v>336.36</v>
+        <v>336.43</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>328.21</v>
+        <v>328.31</v>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
@@ -8942,20 +8942,20 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="10" t="n">
-        <v>58.12</v>
+        <v>57.34</v>
       </c>
       <c r="D188" s="10" t="n">
-        <v>61.04</v>
+        <v>60.68</v>
       </c>
       <c r="E188" s="10" t="n">
-        <v>61.6</v>
+        <v>61.44</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>66.45</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
@@ -8986,20 +8986,20 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="10" t="n">
-        <v>1372</v>
+        <v>1400.1</v>
       </c>
       <c r="D189" s="10" t="n">
-        <v>1358.36</v>
+        <v>1362.33</v>
       </c>
       <c r="E189" s="10" t="n">
-        <v>1274.45</v>
+        <v>1279.38</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>1101.19</v>
+        <v>1104.16</v>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
@@ -9030,20 +9030,20 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="10" t="n">
-        <v>854.3</v>
+        <v>836.9</v>
       </c>
       <c r="D190" s="10" t="n">
-        <v>885.37</v>
+        <v>880.75</v>
       </c>
       <c r="E190" s="10" t="n">
-        <v>910.23</v>
+        <v>907.35</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>990.61</v>
+        <v>989.08</v>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
@@ -9074,20 +9074,20 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="10" t="n">
-        <v>739</v>
+        <v>773.05</v>
       </c>
       <c r="D191" s="10" t="n">
-        <v>793.05</v>
+        <v>791.14</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>809.33</v>
+        <v>807.91</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>789.03</v>
+        <v>788.88</v>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -9118,24 +9118,24 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="10" t="n">
-        <v>867</v>
+        <v>829.65</v>
       </c>
       <c r="D192" s="10" t="n">
-        <v>831.9299999999999</v>
+        <v>831.72</v>
       </c>
       <c r="E192" s="10" t="n">
-        <v>780.01</v>
+        <v>781.96</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>747.21</v>
-      </c>
-      <c r="G192" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>748.03</v>
+      </c>
+      <c r="G192" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H192" s="13" t="inlineStr">
@@ -9162,20 +9162,20 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="10" t="n">
-        <v>119.72</v>
+        <v>122.9</v>
       </c>
       <c r="D193" s="10" t="n">
-        <v>124.15</v>
+        <v>124.03</v>
       </c>
       <c r="E193" s="10" t="n">
-        <v>126.51</v>
+        <v>126.37</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>139.56</v>
+        <v>139.39</v>
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
@@ -9206,20 +9206,20 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="10" t="n">
-        <v>295.9</v>
+        <v>291.7</v>
       </c>
       <c r="D194" s="10" t="n">
-        <v>301.66</v>
+        <v>300.71</v>
       </c>
       <c r="E194" s="10" t="n">
-        <v>305.35</v>
+        <v>304.81</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>339.31</v>
+        <v>338.83</v>
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -9250,20 +9250,20 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="10" t="n">
-        <v>2953.8</v>
+        <v>2971.7</v>
       </c>
       <c r="D195" s="10" t="n">
-        <v>2886.67</v>
+        <v>2894.77</v>
       </c>
       <c r="E195" s="10" t="n">
-        <v>2766.42</v>
+        <v>2774.47</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>2575.94</v>
+        <v>2579.88</v>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
@@ -9294,20 +9294,20 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="10" t="n">
-        <v>2761.5</v>
+        <v>2744</v>
       </c>
       <c r="D196" s="10" t="n">
-        <v>2819.13</v>
+        <v>2811.98</v>
       </c>
       <c r="E196" s="10" t="n">
-        <v>2723.86</v>
+        <v>2724.65</v>
       </c>
       <c r="F196" s="10" t="n">
-        <v>2607.99</v>
+        <v>2609.35</v>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
@@ -9338,20 +9338,20 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="10" t="n">
-        <v>790</v>
+        <v>782.85</v>
       </c>
       <c r="D197" s="10" t="n">
-        <v>691.92</v>
+        <v>700.58</v>
       </c>
       <c r="E197" s="10" t="n">
-        <v>635.65</v>
+        <v>641.4299999999999</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>555.53</v>
+        <v>557.79</v>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
@@ -9382,20 +9382,20 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="10" t="n">
-        <v>667.35</v>
+        <v>674.7</v>
       </c>
       <c r="D198" s="10" t="n">
-        <v>683.05</v>
+        <v>682.25</v>
       </c>
       <c r="E198" s="10" t="n">
-        <v>683.03</v>
+        <v>682.71</v>
       </c>
       <c r="F198" s="10" t="n">
-        <v>627.8200000000001</v>
+        <v>628.28</v>
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -9426,20 +9426,20 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="10" t="n">
-        <v>343.95</v>
+        <v>337.4</v>
       </c>
       <c r="D199" s="10" t="n">
-        <v>352.25</v>
+        <v>350.84</v>
       </c>
       <c r="E199" s="10" t="n">
-        <v>360.82</v>
+        <v>359.9</v>
       </c>
       <c r="F199" s="10" t="n">
-        <v>425.11</v>
+        <v>424.24</v>
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
@@ -9470,20 +9470,20 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="10" t="n">
-        <v>1725.6</v>
+        <v>1744.5</v>
       </c>
       <c r="D200" s="10" t="n">
-        <v>1835.29</v>
+        <v>1826.64</v>
       </c>
       <c r="E200" s="10" t="n">
-        <v>1931.77</v>
+        <v>1924.43</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>2041.51</v>
+        <v>2038.55</v>
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
@@ -9514,24 +9514,24 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="10" t="n">
-        <v>169.96</v>
+        <v>167.54</v>
       </c>
       <c r="D201" s="10" t="n">
-        <v>169.69</v>
+        <v>169.48</v>
       </c>
       <c r="E201" s="10" t="n">
-        <v>177.63</v>
+        <v>177.23</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>192.66</v>
-      </c>
-      <c r="G201" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>192.41</v>
+      </c>
+      <c r="G201" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H201" s="11" t="inlineStr">
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="10" t="n">
-        <v>115.58</v>
+        <v>116.57</v>
       </c>
       <c r="D202" s="10" t="n">
-        <v>122.94</v>
+        <v>122.33</v>
       </c>
       <c r="E202" s="10" t="n">
-        <v>126.32</v>
+        <v>125.94</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>127.21</v>
+        <v>127.11</v>
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
@@ -9602,20 +9602,20 @@
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="10" t="n">
-        <v>193.4</v>
+        <v>191.2</v>
       </c>
       <c r="D203" s="10" t="n">
-        <v>198.84</v>
+        <v>198.11</v>
       </c>
       <c r="E203" s="10" t="n">
-        <v>201.93</v>
+        <v>201.51</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>209.85</v>
+        <v>209.66</v>
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
@@ -9646,24 +9646,24 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="10" t="n">
-        <v>824.05</v>
+        <v>806.7</v>
       </c>
       <c r="D204" s="10" t="n">
-        <v>813</v>
+        <v>812.4</v>
       </c>
       <c r="E204" s="10" t="n">
-        <v>833.62</v>
+        <v>832.5700000000001</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>829.64</v>
-      </c>
-      <c r="G204" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>829.41</v>
+      </c>
+      <c r="G204" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H204" s="11" t="inlineStr">
@@ -9690,20 +9690,20 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="10" t="n">
-        <v>114.27</v>
+        <v>113.58</v>
       </c>
       <c r="D205" s="10" t="n">
-        <v>116.32</v>
+        <v>116.06</v>
       </c>
       <c r="E205" s="10" t="n">
-        <v>119.59</v>
+        <v>119.36</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>138.37</v>
+        <v>138.12</v>
       </c>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9734,20 +9734,20 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="10" t="n">
-        <v>589.85</v>
+        <v>586.3</v>
       </c>
       <c r="D206" s="10" t="n">
-        <v>580.0700000000001</v>
+        <v>580.67</v>
       </c>
       <c r="E206" s="10" t="n">
-        <v>581.61</v>
+        <v>581.8</v>
       </c>
       <c r="F206" s="10" t="n">
-        <v>610.63</v>
+        <v>610.39</v>
       </c>
       <c r="G206" s="13" t="inlineStr">
         <is>
@@ -9778,20 +9778,20 @@
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="10" t="n">
-        <v>393.55</v>
+        <v>393</v>
       </c>
       <c r="D207" s="10" t="n">
-        <v>409.53</v>
+        <v>407.96</v>
       </c>
       <c r="E207" s="10" t="n">
-        <v>419.88</v>
+        <v>418.83</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>441.4</v>
+        <v>440.92</v>
       </c>
       <c r="G207" s="11" t="inlineStr">
         <is>
@@ -9822,20 +9822,20 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="10" t="n">
-        <v>131.53</v>
+        <v>129.78</v>
       </c>
       <c r="D208" s="10" t="n">
-        <v>124.24</v>
+        <v>124.76</v>
       </c>
       <c r="E208" s="10" t="n">
-        <v>125.75</v>
+        <v>125.91</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>136.32</v>
+        <v>136.26</v>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
@@ -9866,20 +9866,20 @@
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="10" t="n">
-        <v>157.86</v>
+        <v>156.71</v>
       </c>
       <c r="D209" s="10" t="n">
-        <v>160.17</v>
+        <v>159.84</v>
       </c>
       <c r="E209" s="10" t="n">
-        <v>163.74</v>
+        <v>163.46</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>174.37</v>
+        <v>174.19</v>
       </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
@@ -9910,20 +9910,20 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="10" t="n">
-        <v>109.91</v>
+        <v>109.13</v>
       </c>
       <c r="D210" s="10" t="n">
-        <v>107.33</v>
+        <v>107.5</v>
       </c>
       <c r="E210" s="10" t="n">
-        <v>105.52</v>
+        <v>105.67</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>114.64</v>
+        <v>114.58</v>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
@@ -9954,20 +9954,20 @@
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="10" t="n">
-        <v>1296</v>
+        <v>1266.8</v>
       </c>
       <c r="D211" s="10" t="n">
-        <v>1342.27</v>
+        <v>1335.09</v>
       </c>
       <c r="E211" s="10" t="n">
-        <v>1331.07</v>
+        <v>1328.55</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>1319.88</v>
+        <v>1319.35</v>
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
@@ -9998,20 +9998,20 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="10" t="n">
-        <v>126.42</v>
+        <v>126.28</v>
       </c>
       <c r="D212" s="10" t="n">
-        <v>130.45</v>
+        <v>130.05</v>
       </c>
       <c r="E212" s="10" t="n">
-        <v>133.21</v>
+        <v>132.94</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>156.56</v>
+        <v>156.25</v>
       </c>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -10042,20 +10042,20 @@
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>298.85</v>
+        <v>299.5</v>
       </c>
       <c r="D213" s="10" t="n">
-        <v>300.89</v>
+        <v>300.75</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>312.19</v>
+        <v>311.69</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>318.36</v>
+        <v>318.17</v>
       </c>
       <c r="G213" s="11" t="inlineStr">
         <is>
@@ -10086,20 +10086,20 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="10" t="n">
-        <v>253</v>
+        <v>253.9</v>
       </c>
       <c r="D214" s="10" t="n">
-        <v>263.43</v>
+        <v>262.52</v>
       </c>
       <c r="E214" s="10" t="n">
-        <v>276.57</v>
+        <v>275.69</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>354.43</v>
+        <v>353.43</v>
       </c>
       <c r="G214" s="11" t="inlineStr">
         <is>
@@ -10130,20 +10130,20 @@
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="10" t="n">
-        <v>808.5</v>
+        <v>817.4</v>
       </c>
       <c r="D215" s="10" t="n">
-        <v>818.66</v>
+        <v>818.54</v>
       </c>
       <c r="E215" s="10" t="n">
-        <v>808.2</v>
+        <v>808.5599999999999</v>
       </c>
       <c r="F215" s="10" t="n">
-        <v>802.41</v>
+        <v>802.5599999999999</v>
       </c>
       <c r="G215" s="11" t="inlineStr">
         <is>
@@ -10174,20 +10174,20 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>1285.2</v>
+        <v>1305.4</v>
       </c>
       <c r="D216" s="10" t="n">
-        <v>1047.65</v>
+        <v>1072.19</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>957.66</v>
+        <v>971.3</v>
       </c>
       <c r="F216" s="10" t="n">
-        <v>945.99</v>
+        <v>949.5599999999999</v>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
@@ -10218,24 +10218,24 @@
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="10" t="n">
-        <v>79.90000000000001</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="D217" s="10" t="n">
-        <v>78.42</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E217" s="10" t="n">
-        <v>76.23999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F217" s="10" t="n">
-        <v>78.97</v>
-      </c>
-      <c r="G217" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>78.95999999999999</v>
+      </c>
+      <c r="G217" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H217" s="13" t="inlineStr">
@@ -10243,9 +10243,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I217" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I217" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J217" s="12" t="inlineStr">
@@ -10262,20 +10262,20 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="10" t="n">
-        <v>127.1</v>
+        <v>126.68</v>
       </c>
       <c r="D218" s="10" t="n">
-        <v>130.03</v>
+        <v>129.71</v>
       </c>
       <c r="E218" s="10" t="n">
-        <v>138.83</v>
+        <v>138.35</v>
       </c>
       <c r="F218" s="10" t="n">
-        <v>166.4</v>
+        <v>166</v>
       </c>
       <c r="G218" s="11" t="inlineStr">
         <is>
@@ -10306,20 +10306,20 @@
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="10" t="n">
-        <v>1117.1</v>
+        <v>1096.9</v>
       </c>
       <c r="D219" s="10" t="n">
-        <v>1049.41</v>
+        <v>1053.94</v>
       </c>
       <c r="E219" s="10" t="n">
-        <v>1064.79</v>
+        <v>1066.05</v>
       </c>
       <c r="F219" s="10" t="n">
-        <v>1121.96</v>
+        <v>1121.71</v>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
@@ -10350,24 +10350,24 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="10" t="n">
-        <v>248.1</v>
+        <v>246.7</v>
       </c>
       <c r="D220" s="10" t="n">
-        <v>247.55</v>
+        <v>247.47</v>
       </c>
       <c r="E220" s="10" t="n">
-        <v>241.3</v>
+        <v>241.51</v>
       </c>
       <c r="F220" s="10" t="n">
-        <v>226.95</v>
-      </c>
-      <c r="G220" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>227.14</v>
+      </c>
+      <c r="G220" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H220" s="13" t="inlineStr">
@@ -10394,20 +10394,20 @@
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="10" t="n">
-        <v>1534.8</v>
+        <v>1533.5</v>
       </c>
       <c r="D221" s="10" t="n">
-        <v>1555.12</v>
+        <v>1553.06</v>
       </c>
       <c r="E221" s="10" t="n">
-        <v>1559.22</v>
+        <v>1558.21</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>1928.38</v>
+        <v>1924.45</v>
       </c>
       <c r="G221" s="11" t="inlineStr">
         <is>
@@ -10438,34 +10438,34 @@
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="10" t="n">
-        <v>628.3</v>
+        <v>635.15</v>
       </c>
       <c r="D222" s="10" t="n">
-        <v>626.84</v>
+        <v>627.63</v>
       </c>
       <c r="E222" s="10" t="n">
-        <v>634.85</v>
+        <v>634.86</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>634.03</v>
+        <v>634.04</v>
       </c>
       <c r="G222" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H222" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I222" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H222" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I222" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J222" s="12" t="inlineStr">
@@ -10482,17 +10482,17 @@
       </c>
       <c r="B223" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="10" t="n">
-        <v>25.19</v>
+        <v>24.35</v>
       </c>
       <c r="D223" s="10" t="n">
-        <v>24.07</v>
+        <v>24.09</v>
       </c>
       <c r="E223" s="10" t="n">
-        <v>23.55</v>
+        <v>23.58</v>
       </c>
       <c r="F223" s="10" t="n">
         <v>25.07</v>
@@ -10507,9 +10507,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I223" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I223" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J223" s="12" t="inlineStr">
@@ -10526,20 +10526,20 @@
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="10" t="n">
-        <v>673.6</v>
+        <v>674.65</v>
       </c>
       <c r="D224" s="10" t="n">
-        <v>615.79</v>
+        <v>621.4</v>
       </c>
       <c r="E224" s="10" t="n">
-        <v>588.9400000000001</v>
+        <v>592.3</v>
       </c>
       <c r="F224" s="10" t="n">
-        <v>591.86</v>
+        <v>592.6900000000001</v>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="10" t="n">
-        <v>408.55</v>
+        <v>399.35</v>
       </c>
       <c r="D225" s="10" t="n">
-        <v>426.78</v>
+        <v>424.16</v>
       </c>
       <c r="E225" s="10" t="n">
-        <v>440.07</v>
+        <v>438.47</v>
       </c>
       <c r="F225" s="10" t="n">
-        <v>487.38</v>
+        <v>486.5</v>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -10614,20 +10614,20 @@
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="10" t="n">
-        <v>216.02</v>
+        <v>219.57</v>
       </c>
       <c r="D226" s="10" t="n">
-        <v>221.09</v>
+        <v>220.95</v>
       </c>
       <c r="E226" s="10" t="n">
-        <v>229.71</v>
+        <v>229.31</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>245.65</v>
+        <v>245.39</v>
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -10658,20 +10658,20 @@
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="10" t="n">
-        <v>519.7</v>
+        <v>513.7</v>
       </c>
       <c r="D227" s="10" t="n">
-        <v>509.03</v>
+        <v>509.48</v>
       </c>
       <c r="E227" s="10" t="n">
-        <v>498.53</v>
+        <v>499.13</v>
       </c>
       <c r="F227" s="10" t="n">
-        <v>471.12</v>
+        <v>471.55</v>
       </c>
       <c r="G227" s="13" t="inlineStr">
         <is>
@@ -10702,20 +10702,20 @@
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="10" t="n">
-        <v>112.27</v>
+        <v>112.45</v>
       </c>
       <c r="D228" s="10" t="n">
-        <v>110.43</v>
+        <v>110.63</v>
       </c>
       <c r="E228" s="10" t="n">
-        <v>111.64</v>
+        <v>111.67</v>
       </c>
       <c r="F228" s="10" t="n">
-        <v>122.55</v>
+        <v>122.45</v>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
@@ -10746,20 +10746,20 @@
       </c>
       <c r="B229" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="10" t="n">
-        <v>216.39</v>
+        <v>216.25</v>
       </c>
       <c r="D229" s="10" t="n">
-        <v>216.49</v>
+        <v>216.47</v>
       </c>
       <c r="E229" s="10" t="n">
         <v>216.45</v>
       </c>
       <c r="F229" s="10" t="n">
-        <v>223.52</v>
+        <v>223.44</v>
       </c>
       <c r="G229" s="11" t="inlineStr">
         <is>
@@ -10790,20 +10790,20 @@
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="10" t="n">
-        <v>1970.7</v>
+        <v>1944.4</v>
       </c>
       <c r="D230" s="10" t="n">
-        <v>1981.85</v>
+        <v>1978.28</v>
       </c>
       <c r="E230" s="10" t="n">
-        <v>1909.26</v>
+        <v>1910.63</v>
       </c>
       <c r="F230" s="10" t="n">
-        <v>1770.5</v>
+        <v>1772.23</v>
       </c>
       <c r="G230" s="11" t="inlineStr">
         <is>
@@ -10834,20 +10834,20 @@
       </c>
       <c r="B231" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="10" t="n">
-        <v>680.65</v>
+        <v>676.2</v>
       </c>
       <c r="D231" s="10" t="n">
-        <v>635.84</v>
+        <v>639.6799999999999</v>
       </c>
       <c r="E231" s="10" t="n">
-        <v>613.96</v>
+        <v>616.41</v>
       </c>
       <c r="F231" s="10" t="n">
-        <v>599.87</v>
+        <v>600.63</v>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
@@ -10878,24 +10878,24 @@
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="10" t="n">
-        <v>171.94</v>
+        <v>176.04</v>
       </c>
       <c r="D232" s="10" t="n">
-        <v>172.07</v>
+        <v>172.45</v>
       </c>
       <c r="E232" s="10" t="n">
-        <v>182.71</v>
+        <v>182.44</v>
       </c>
       <c r="F232" s="10" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="G232" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>217.08</v>
+      </c>
+      <c r="G232" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H232" s="11" t="inlineStr">
@@ -10922,20 +10922,20 @@
       </c>
       <c r="B233" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="10" t="n">
-        <v>5761.5</v>
+        <v>5698.5</v>
       </c>
       <c r="D233" s="10" t="n">
-        <v>5809</v>
+        <v>5798.47</v>
       </c>
       <c r="E233" s="10" t="n">
-        <v>5901.18</v>
+        <v>5893.23</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>5740.71</v>
+        <v>5740.29</v>
       </c>
       <c r="G233" s="11" t="inlineStr">
         <is>
@@ -10947,9 +10947,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I233" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I233" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J233" s="12" t="inlineStr">
@@ -10966,20 +10966,20 @@
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="10" t="n">
-        <v>339.95</v>
+        <v>339.8</v>
       </c>
       <c r="D234" s="10" t="n">
-        <v>339.13</v>
+        <v>339.19</v>
       </c>
       <c r="E234" s="10" t="n">
-        <v>340.05</v>
+        <v>340.04</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>388.93</v>
+        <v>388.44</v>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
@@ -11010,20 +11010,20 @@
       </c>
       <c r="B235" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="10" t="n">
-        <v>28.05</v>
+        <v>27.61</v>
       </c>
       <c r="D235" s="10" t="n">
-        <v>29.63</v>
+        <v>29.43</v>
       </c>
       <c r="E235" s="10" t="n">
-        <v>31.03</v>
+        <v>30.9</v>
       </c>
       <c r="F235" s="10" t="n">
-        <v>35.61</v>
+        <v>35.53</v>
       </c>
       <c r="G235" s="11" t="inlineStr">
         <is>
@@ -11054,24 +11054,24 @@
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="10" t="n">
-        <v>194.83</v>
+        <v>192.32</v>
       </c>
       <c r="D236" s="10" t="n">
-        <v>192.61</v>
+        <v>192.58</v>
       </c>
       <c r="E236" s="10" t="n">
-        <v>199.04</v>
+        <v>198.78</v>
       </c>
       <c r="F236" s="10" t="n">
-        <v>212.84</v>
-      </c>
-      <c r="G236" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>212.64</v>
+      </c>
+      <c r="G236" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H236" s="11" t="inlineStr">
@@ -11098,20 +11098,20 @@
       </c>
       <c r="B237" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="10" t="n">
-        <v>127.23</v>
+        <v>124.65</v>
       </c>
       <c r="D237" s="10" t="n">
-        <v>128.68</v>
+        <v>128.29</v>
       </c>
       <c r="E237" s="10" t="n">
-        <v>129.4</v>
+        <v>129.21</v>
       </c>
       <c r="F237" s="10" t="n">
-        <v>123.48</v>
+        <v>123.49</v>
       </c>
       <c r="G237" s="11" t="inlineStr">
         <is>
@@ -11142,20 +11142,20 @@
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="10" t="n">
-        <v>7.46</v>
+        <v>7.41</v>
       </c>
       <c r="D238" s="10" t="n">
-        <v>9.720000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E238" s="10" t="n">
-        <v>11.04</v>
+        <v>10.9</v>
       </c>
       <c r="F238" s="10" t="n">
-        <v>13.49</v>
+        <v>13.43</v>
       </c>
       <c r="G238" s="11" t="inlineStr">
         <is>
@@ -11186,20 +11186,20 @@
       </c>
       <c r="B239" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="10" t="n">
-        <v>101.19</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="D239" s="10" t="n">
-        <v>105.64</v>
+        <v>105.03</v>
       </c>
       <c r="E239" s="10" t="n">
-        <v>109.3</v>
+        <v>108.91</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>121.38</v>
+        <v>121.16</v>
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
@@ -11230,29 +11230,29 @@
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="10" t="n">
-        <v>309.6</v>
+        <v>305</v>
       </c>
       <c r="D240" s="10" t="n">
-        <v>308.15</v>
+        <v>307.85</v>
       </c>
       <c r="E240" s="10" t="n">
-        <v>307.25</v>
+        <v>307.16</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>330.2</v>
-      </c>
-      <c r="G240" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H240" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>329.95</v>
+      </c>
+      <c r="G240" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H240" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I240" s="11" t="inlineStr">
@@ -11274,20 +11274,20 @@
       </c>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="10" t="n">
-        <v>484.55</v>
+        <v>478.55</v>
       </c>
       <c r="D241" s="10" t="n">
-        <v>502.49</v>
+        <v>500.21</v>
       </c>
       <c r="E241" s="10" t="n">
-        <v>526.4400000000001</v>
+        <v>524.5700000000001</v>
       </c>
       <c r="F241" s="10" t="n">
-        <v>630.33</v>
+        <v>628.8099999999999</v>
       </c>
       <c r="G241" s="11" t="inlineStr">
         <is>
@@ -11318,24 +11318,24 @@
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="10" t="n">
-        <v>67.86</v>
+        <v>68.7</v>
       </c>
       <c r="D242" s="10" t="n">
-        <v>68.16</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="E242" s="10" t="n">
-        <v>67.31</v>
+        <v>67.36</v>
       </c>
       <c r="F242" s="10" t="n">
-        <v>72.56999999999999</v>
-      </c>
-      <c r="G242" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>72.53</v>
+      </c>
+      <c r="G242" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H242" s="13" t="inlineStr">
@@ -11362,20 +11362,20 @@
       </c>
       <c r="B243" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="10" t="n">
-        <v>1533.7</v>
+        <v>1534.2</v>
       </c>
       <c r="D243" s="10" t="n">
-        <v>1516.62</v>
+        <v>1518.29</v>
       </c>
       <c r="E243" s="10" t="n">
-        <v>1537.36</v>
+        <v>1537.24</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>1709.95</v>
+        <v>1708.2</v>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
@@ -11406,20 +11406,20 @@
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="10" t="n">
-        <v>124.41</v>
+        <v>123.18</v>
       </c>
       <c r="D244" s="10" t="n">
-        <v>129.76</v>
+        <v>129.13</v>
       </c>
       <c r="E244" s="10" t="n">
-        <v>133.15</v>
+        <v>132.76</v>
       </c>
       <c r="F244" s="10" t="n">
-        <v>136.45</v>
+        <v>136.32</v>
       </c>
       <c r="G244" s="11" t="inlineStr">
         <is>
@@ -11450,20 +11450,20 @@
       </c>
       <c r="B245" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="10" t="n">
-        <v>70.34999999999999</v>
+        <v>69.98</v>
       </c>
       <c r="D245" s="10" t="n">
-        <v>70.97</v>
+        <v>70.88</v>
       </c>
       <c r="E245" s="10" t="n">
-        <v>72.04000000000001</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="F245" s="10" t="n">
-        <v>77.65000000000001</v>
+        <v>77.58</v>
       </c>
       <c r="G245" s="11" t="inlineStr">
         <is>
@@ -11494,20 +11494,20 @@
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="10" t="n">
-        <v>744.1</v>
+        <v>738.7</v>
       </c>
       <c r="D246" s="10" t="n">
-        <v>756.08</v>
+        <v>753.51</v>
       </c>
       <c r="E246" s="10" t="n">
-        <v>762.9400000000001</v>
+        <v>761</v>
       </c>
       <c r="F246" s="10" t="n">
-        <v>764.45</v>
+        <v>763.17</v>
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -11538,29 +11538,29 @@
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="10" t="n">
-        <v>422.3</v>
+        <v>422.9</v>
       </c>
       <c r="D247" s="10" t="n">
-        <v>415.51</v>
+        <v>416.21</v>
       </c>
       <c r="E247" s="10" t="n">
-        <v>422.83</v>
+        <v>422.84</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>428.33</v>
+        <v>428.28</v>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H247" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H247" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I247" s="11" t="inlineStr">
@@ -11582,20 +11582,20 @@
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="10" t="n">
-        <v>607.15</v>
+        <v>596.15</v>
       </c>
       <c r="D248" s="10" t="n">
-        <v>672.59</v>
+        <v>665.3099999999999</v>
       </c>
       <c r="E248" s="10" t="n">
-        <v>741.83</v>
+        <v>736.12</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>822.13</v>
+        <v>819.88</v>
       </c>
       <c r="G248" s="11" t="inlineStr">
         <is>
@@ -11626,20 +11626,20 @@
       </c>
       <c r="B249" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="10" t="n">
-        <v>4075.6</v>
+        <v>4049.5</v>
       </c>
       <c r="D249" s="10" t="n">
-        <v>4240.72</v>
+        <v>4222.51</v>
       </c>
       <c r="E249" s="10" t="n">
-        <v>4383.48</v>
+        <v>4370.39</v>
       </c>
       <c r="F249" s="10" t="n">
-        <v>4530.93</v>
+        <v>4526.14</v>
       </c>
       <c r="G249" s="11" t="inlineStr">
         <is>
@@ -11670,20 +11670,20 @@
       </c>
       <c r="B250" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="10" t="n">
-        <v>697.85</v>
+        <v>729</v>
       </c>
       <c r="D250" s="10" t="n">
-        <v>733.6900000000001</v>
+        <v>733.24</v>
       </c>
       <c r="E250" s="10" t="n">
-        <v>758.03</v>
+        <v>756.89</v>
       </c>
       <c r="F250" s="10" t="n">
-        <v>788.39</v>
+        <v>787.8</v>
       </c>
       <c r="G250" s="11" t="inlineStr">
         <is>
@@ -11714,20 +11714,20 @@
       </c>
       <c r="B251" s="10" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="10" t="n">
-        <v>415.95</v>
+        <v>416</v>
       </c>
       <c r="D251" s="10" t="n">
-        <v>421.74</v>
+        <v>421.19</v>
       </c>
       <c r="E251" s="10" t="n">
-        <v>430.45</v>
+        <v>429.88</v>
       </c>
       <c r="F251" s="10" t="n">
-        <v>433.67</v>
+        <v>433.49</v>
       </c>
       <c r="G251" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Sep-2026  15:00:29    |    Closing Price Date: 09-Sep-2026</t>
+          <t>Scan Run: 10-Sep-2026  14:46:11    |    Closing Price Date: 10-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -591,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>42.8</v>
+        <v>44</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>50.4</v>
+        <v>48.8</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>56</v>
+        <v>56.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Sep-2026  15:00:29</t>
+          <t>10-Sep-2026  14:46:11</t>
         </is>
       </c>
     </row>
@@ -622,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 42.8% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 50.4% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 48.8% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.8% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -650,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 107 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 110 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 126 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 122 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 140 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 142 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>251.95</v>
+        <v>250.18</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>258.36</v>
+        <v>257.58</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>268.51</v>
+        <v>267.79</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>298.15</v>
+        <v>297.45</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>326.95</v>
+        <v>328.75</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>331.42</v>
+        <v>331.16</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>322.67</v>
+        <v>322.9</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>324.94</v>
+        <v>324.97</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>6570</v>
+        <v>6278</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>5610.74</v>
+        <v>5674.29</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>5076.58</v>
+        <v>5123.69</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>4199.63</v>
+        <v>4220.85</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>755.1</v>
+        <v>762.75</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>730.39</v>
+        <v>733.47</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>678.65</v>
+        <v>681.95</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>539.59</v>
+        <v>541.75</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>279.7</v>
+        <v>277.45</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>275.25</v>
+        <v>275.46</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>247.93</v>
+        <v>249.09</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>158.48</v>
+        <v>159.69</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -978,24 +978,24 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>334.8</v>
+        <v>351.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>337.45</v>
+        <v>338.79</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>307.78</v>
+        <v>309.49</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>217.7</v>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>218.93</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7501</v>
+        <v>7305</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>7041.64</v>
+        <v>7066.72</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6849.15</v>
+        <v>6867.03</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>5385.63</v>
+        <v>5404.33</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>874.4</v>
+        <v>855.15</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>826.3099999999999</v>
+        <v>829.05</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>760.95</v>
+        <v>764.64</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>615.91</v>
+        <v>618.29</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1110,20 +1110,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>331.25</v>
+        <v>332.55</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>326.35</v>
+        <v>326.94</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>307.18</v>
+        <v>308.18</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>257.45</v>
+        <v>258.05</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>5118</v>
+        <v>5081.5</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>5405.18</v>
+        <v>5374.36</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>5480.79</v>
+        <v>5465.13</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4507.9</v>
+        <v>4513.46</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1198,29 +1198,29 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>178.56</v>
+        <v>170.63</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>174.09</v>
+        <v>173.76</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>171.17</v>
+        <v>171.15</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>165.24</v>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>165.09</v>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2805</v>
+        <v>2773.5</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>2757.54</v>
+        <v>2759.06</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>2572.62</v>
+        <v>2580.49</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2114.75</v>
+        <v>2122.56</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,24 +1286,24 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>580.05</v>
+        <v>585.9</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>584.41</v>
+        <v>584.55</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>575.51</v>
+        <v>575.91</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>570.9</v>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>571.3200000000001</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>2293.6</v>
+        <v>2227</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>2166.95</v>
+        <v>2172.67</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1972.01</v>
+        <v>1982.01</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1474.12</v>
+        <v>1481.53</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>3537.9</v>
+        <v>3495.6</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3465.05</v>
+        <v>3467.96</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>3489.02</v>
+        <v>3489.28</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>3213.28</v>
+        <v>3216.07</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>422.45</v>
+        <v>413.2</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>394.7</v>
+        <v>396.46</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>390.53</v>
+        <v>391.42</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>332.19</v>
+        <v>333.02</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>745.8</v>
+        <v>739.6</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>765.24</v>
+        <v>762.79</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>719.34</v>
+        <v>720.13</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>621.9299999999999</v>
+        <v>622.9</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>865.9</v>
+        <v>854.75</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>703.92</v>
+        <v>718.28</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>633.36</v>
+        <v>642.04</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>414.37</v>
+        <v>418.75</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>197.99</v>
+        <v>207.88</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>184.37</v>
+        <v>186.61</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>173.53</v>
+        <v>174.88</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>160.49</v>
+        <v>160.96</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>13.87</v>
+        <v>13.83</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>11.32</v>
+        <v>11.56</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>10.42</v>
+        <v>10.55</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>230.55</v>
+        <v>229.96</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>243.09</v>
+        <v>241.84</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>237.11</v>
+        <v>236.83</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>196.55</v>
+        <v>196.88</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>2130.9</v>
+        <v>2211.8</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>2021.77</v>
+        <v>2039.87</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1969.68</v>
+        <v>1979.17</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>1685.3</v>
+        <v>1688.78</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -1726,29 +1726,29 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>230.56</v>
+        <v>226.4</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>235.6</v>
+        <v>234.73</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>229.94</v>
+        <v>229.8</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>207.1</v>
+        <v>207.39</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
@@ -1770,29 +1770,29 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>64.12</v>
+        <v>66.52</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>67.28</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>66.42</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>59.74</v>
+        <v>59.77</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -1814,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>166.39</v>
+        <v>164.8</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>169.99</v>
+        <v>169.5</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>166.64</v>
+        <v>166.57</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>149.53</v>
+        <v>149.71</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>184.99</v>
+        <v>184.87</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>189.66</v>
+        <v>189.2</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>190.97</v>
+        <v>190.73</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>189.81</v>
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>509.3</v>
+        <v>503.85</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>542.17</v>
+        <v>538.52</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>552.63</v>
+        <v>550.72</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>542.13</v>
+        <v>541.23</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>355</v>
+        <v>355.1</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>349.02</v>
+        <v>349.6</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>321.56</v>
+        <v>322.87</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>261.43</v>
+        <v>262.39</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>1470</v>
+        <v>1453.3</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1419.11</v>
+        <v>1422.37</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>1321.53</v>
+        <v>1326.7</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1014.25</v>
+        <v>1018.8</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>374.4</v>
+        <v>374.65</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>359.55</v>
+        <v>360.99</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>338.88</v>
+        <v>340.28</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>300.83</v>
+        <v>301.4</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>530.9</v>
+        <v>535.75</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>542.78</v>
+        <v>542.11</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>512.65</v>
+        <v>513.5599999999999</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>465.71</v>
+        <v>466.05</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2122,24 +2122,24 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>1610.9</v>
+        <v>1640.3</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1628.93</v>
+        <v>1630.01</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>1535.3</v>
+        <v>1539.41</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>1229.61</v>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1233.67</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>832.2</v>
+        <v>830.3</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>783.67</v>
+        <v>788.11</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>716.03</v>
+        <v>720.51</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>529.1799999999999</v>
+        <v>531.85</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>611.45</v>
+        <v>611.05</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>608.98</v>
+        <v>609.1799999999999</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>607.4</v>
+        <v>607.55</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>596.85</v>
+        <v>597.24</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2254,29 +2254,29 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>533.95</v>
+        <v>514.75</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>543.75</v>
+        <v>540.99</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>531.37</v>
+        <v>530.72</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>478.48</v>
+        <v>478.62</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I36" s="13" t="inlineStr">
@@ -2298,24 +2298,24 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>201.01</v>
+        <v>196.74</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>200.83</v>
+        <v>200.44</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>203.45</v>
+        <v>203.19</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>203.14</v>
-      </c>
-      <c r="G37" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>202.9</v>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>807.15</v>
+        <v>815.3</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>836.64</v>
+        <v>834.6</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>898.67</v>
+        <v>895.4</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>979.98</v>
+        <v>976.5599999999999</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>550.6</v>
+        <v>542.05</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>581.1799999999999</v>
+        <v>577.46</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>620.29</v>
+        <v>617.22</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>628.03</v>
+        <v>626.37</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>355.8</v>
+        <v>349.9</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>358.24</v>
+        <v>357.45</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>358.99</v>
+        <v>358.63</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>344.65</v>
+        <v>344.67</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>222.5</v>
+        <v>217.28</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>209.8</v>
+        <v>210.52</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>205.37</v>
+        <v>205.84</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>172.62</v>
+        <v>173.15</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>81.31</v>
+        <v>80.55</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>86.51000000000001</v>
+        <v>85.95</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>85.89</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>71.77</v>
+        <v>71.81</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>242.05</v>
+        <v>245.44</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>234.24</v>
+        <v>235.3</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>221.5</v>
+        <v>222.44</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>217.29</v>
+        <v>217.48</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1706.1</v>
+        <v>1696.8</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1708.42</v>
+        <v>1707.31</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1681.95</v>
+        <v>1682.53</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1380.01</v>
+        <v>1383.6</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>339.5</v>
+        <v>332.4</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>380.99</v>
+        <v>376.36</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>383.82</v>
+        <v>381.8</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>407.21</v>
+        <v>406.49</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>566.85</v>
+        <v>557.7</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>584.46</v>
+        <v>581.92</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>570.5</v>
+        <v>570</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>490.37</v>
+        <v>490.8</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2738,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>166.59</v>
+        <v>165.61</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>170.48</v>
+        <v>170.02</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>177.31</v>
+        <v>176.85</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>213.92</v>
+        <v>213.44</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1262.3</v>
+        <v>1270.8</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1203.3</v>
+        <v>1209.73</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1116.44</v>
+        <v>1122.49</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1023.74</v>
+        <v>1026.06</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>922.25</v>
+        <v>923.65</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>894.83</v>
+        <v>897.5700000000001</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>850.04</v>
+        <v>852.92</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>704.45</v>
+        <v>706.61</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>175.76</v>
+        <v>178.12</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>174.73</v>
+        <v>175.05</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>179.56</v>
+        <v>179.51</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>181.96</v>
+        <v>182.07</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>273.15</v>
+        <v>269.95</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>286.54</v>
+        <v>284.96</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>296.61</v>
+        <v>295.57</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>302.65</v>
+        <v>303.29</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
@@ -2958,20 +2958,20 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>501.95</v>
+        <v>502.2</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>522.5700000000001</v>
+        <v>520.63</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>543.9299999999999</v>
+        <v>542.29</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>541.88</v>
+        <v>540.87</v>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
@@ -3002,20 +3002,20 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>4135.9</v>
+        <v>4107.9</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>3848.4</v>
+        <v>3873.11</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>3590.52</v>
+        <v>3610.81</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>2742.11</v>
+        <v>2756.66</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
@@ -3046,20 +3046,20 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>561.5</v>
+        <v>561.95</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>555.79</v>
+        <v>556.38</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>536.77</v>
+        <v>537.75</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>528.6799999999999</v>
+        <v>528.62</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
@@ -3090,20 +3090,20 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>1893.1</v>
+        <v>1907.7</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>2012.81</v>
+        <v>2002.8</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>2024.74</v>
+        <v>2020.15</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>1840.44</v>
+        <v>1842.07</v>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
@@ -3134,20 +3134,20 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>182.65</v>
+        <v>191.82</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>176.69</v>
+        <v>178.13</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>160.2</v>
+        <v>161.44</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>131.55</v>
+        <v>132.07</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
@@ -3178,20 +3178,20 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>593.95</v>
+        <v>583</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>561.6799999999999</v>
+        <v>563.71</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>545.42</v>
+        <v>546.9</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>495.92</v>
+        <v>496.97</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
@@ -3222,20 +3222,20 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>1623.5</v>
+        <v>1610</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1724.99</v>
+        <v>1714.04</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>1719.77</v>
+        <v>1715.46</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1793.36</v>
+        <v>1792.62</v>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
@@ -3266,24 +3266,24 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>152.43</v>
+        <v>160.2</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>158.39</v>
+        <v>158.57</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>163.43</v>
+        <v>163.31</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>170.55</v>
-      </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>170.82</v>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -3310,20 +3310,20 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>3455</v>
+        <v>3383.2</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>3291.98</v>
+        <v>3300.66</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>3150.77</v>
+        <v>3159.89</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>2679.36</v>
+        <v>2682.87</v>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
@@ -3354,20 +3354,20 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>261.9</v>
+        <v>260.45</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>264.06</v>
+        <v>263.72</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>262.65</v>
+        <v>262.57</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>237.67</v>
+        <v>237.69</v>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
@@ -3398,20 +3398,20 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>502.75</v>
+        <v>500.75</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>508.9</v>
+        <v>508.13</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>518.99</v>
+        <v>518.27</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>574.21</v>
+        <v>573.34</v>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
@@ -3442,20 +3442,20 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>602.1</v>
+        <v>595.65</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>577.23</v>
+        <v>578.98</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>565.72</v>
+        <v>566.9</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>522.0700000000001</v>
+        <v>523.28</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
@@ -3486,24 +3486,24 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>23.43</v>
+        <v>22.81</v>
       </c>
       <c r="D64" s="10" t="n">
         <v>22.83</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>22.54</v>
+        <v>22.55</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>22.64</v>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>22.58</v>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
@@ -3530,20 +3530,20 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>206.06</v>
+        <v>211.65</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>200.5</v>
+        <v>201.56</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>205.28</v>
+        <v>205.53</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>205.05</v>
+        <v>205.24</v>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
@@ -3574,20 +3574,20 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>192.38</v>
+        <v>193.6</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>197.35</v>
+        <v>196.99</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>202.81</v>
+        <v>202.45</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>192.24</v>
+        <v>192.3</v>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -3618,20 +3618,20 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>678.45</v>
+        <v>668.75</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>685.28</v>
+        <v>683.71</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>665.87</v>
+        <v>665.98</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>653.66</v>
+        <v>654.27</v>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
@@ -3662,20 +3662,20 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>1875.7</v>
+        <v>1869.7</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>1669.97</v>
+        <v>1688.99</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>1653.22</v>
+        <v>1661.71</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1603.87</v>
+        <v>1606.91</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3706,20 +3706,20 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>670.45</v>
+        <v>687.65</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>691.0700000000001</v>
+        <v>690.74</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>717.55</v>
+        <v>716.37</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>830.23</v>
+        <v>829.36</v>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
@@ -3750,20 +3750,20 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>2185.5</v>
+        <v>2295.8</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>2091.66</v>
+        <v>2111.1</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>1979.72</v>
+        <v>1992.11</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1616.91</v>
+        <v>1623.81</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
@@ -3794,29 +3794,29 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>6752.5</v>
+        <v>6905</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>7077.7</v>
+        <v>7061.25</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>6894.31</v>
+        <v>6894.72</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>5502.28</v>
+        <v>5517.23</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I71" s="13" t="inlineStr">
@@ -3838,24 +3838,24 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>46.41</v>
+        <v>46.08</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>46.15</v>
+        <v>46.14</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>45.58</v>
+        <v>45.6</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>41.53</v>
-      </c>
-      <c r="G72" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>41.57</v>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -3882,24 +3882,24 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>467.8</v>
+        <v>503.2</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>487.65</v>
+        <v>489.13</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>509</v>
+        <v>508.77</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>582.02</v>
-      </c>
-      <c r="G73" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>581.74</v>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
@@ -3926,20 +3926,20 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>152.64</v>
+        <v>152.44</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>144.58</v>
+        <v>145.33</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>137.4</v>
+        <v>137.99</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>150.33</v>
+        <v>150.35</v>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
@@ -3970,20 +3970,20 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>2359.3</v>
+        <v>2342.6</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>2340.27</v>
+        <v>2340.49</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>2215.15</v>
+        <v>2220.15</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1773.82</v>
+        <v>1781.28</v>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
@@ -4014,20 +4014,20 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>326.1</v>
+        <v>326.9</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>363.24</v>
+        <v>359.78</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>373.87</v>
+        <v>372.03</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>371.86</v>
+        <v>371.25</v>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
@@ -4058,20 +4058,20 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>783.5</v>
+        <v>781.35</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>786.51</v>
+        <v>786.02</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>820.9</v>
+        <v>819.35</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>886.84</v>
+        <v>887.41</v>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
@@ -4102,20 +4102,20 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>311.1</v>
+        <v>307.6</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>328.78</v>
+        <v>326.76</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>336.53</v>
+        <v>335.39</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>366.13</v>
+        <v>365.63</v>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
@@ -4146,20 +4146,20 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>2859.2</v>
+        <v>2823</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>2598.73</v>
+        <v>2620.09</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>2529.84</v>
+        <v>2541.33</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>2486.25</v>
+        <v>2488.83</v>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
@@ -4190,20 +4190,20 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>182.03</v>
+        <v>182.65</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>193.53</v>
+        <v>192.49</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>202.51</v>
+        <v>201.73</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>214.36</v>
+        <v>213.96</v>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
@@ -4234,24 +4234,24 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>158.59</v>
+        <v>162.27</v>
       </c>
       <c r="D81" s="10" t="n">
-        <v>158.95</v>
+        <v>159.27</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>154.52</v>
+        <v>154.82</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>154.13</v>
-      </c>
-      <c r="G81" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>154.1</v>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
@@ -4278,20 +4278,20 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>72.7</v>
+        <v>72.63</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>74.23</v>
+        <v>74.08</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>74.77</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>69.93000000000001</v>
+        <v>69.91</v>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
@@ -4322,20 +4322,20 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>200.58</v>
+        <v>196.91</v>
       </c>
       <c r="D83" s="10" t="n">
-        <v>202.14</v>
+        <v>201.64</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>207.02</v>
+        <v>206.63</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>184.44</v>
+        <v>184.43</v>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
@@ -4366,20 +4366,20 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>574.6</v>
+        <v>570.75</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>558.83</v>
+        <v>559.97</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>536.25</v>
+        <v>537.6</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>495.5</v>
+        <v>496.85</v>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
@@ -4410,20 +4410,20 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>15.41</v>
+        <v>15.36</v>
       </c>
       <c r="D85" s="10" t="n">
-        <v>15.53</v>
+        <v>15.51</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>15.74</v>
+        <v>15.72</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>16.07</v>
+        <v>16.06</v>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
@@ -4454,20 +4454,20 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>833.5</v>
+        <v>833.85</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>871.38</v>
+        <v>867.8</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>907.1799999999999</v>
+        <v>904.3</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>954.91</v>
+        <v>954.02</v>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
@@ -4498,20 +4498,20 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>2255.2</v>
+        <v>2388.9</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>2175.49</v>
+        <v>2195.81</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>2103.5</v>
+        <v>2114.69</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1777.14</v>
+        <v>1785.21</v>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
@@ -4542,29 +4542,29 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>650.8</v>
+        <v>658.4</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>652.29</v>
+        <v>652.87</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>657.01</v>
+        <v>657.0700000000001</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>621.1900000000001</v>
-      </c>
-      <c r="G88" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H88" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>621.42</v>
+      </c>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H88" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I88" s="13" t="inlineStr">
@@ -4586,20 +4586,20 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
-        <v>1301.2</v>
+        <v>1279.1</v>
       </c>
       <c r="D89" s="10" t="n">
-        <v>1350.67</v>
+        <v>1343.86</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>1377.46</v>
+        <v>1373.6</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>1308.51</v>
+        <v>1309.95</v>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
@@ -4630,20 +4630,20 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>133.63</v>
+        <v>136.74</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>128.61</v>
+        <v>129.39</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>123.99</v>
+        <v>124.49</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>116.91</v>
+        <v>116.98</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -4674,20 +4674,20 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="10" t="n">
-        <v>581.35</v>
+        <v>576.6</v>
       </c>
       <c r="D91" s="10" t="n">
-        <v>543.08</v>
+        <v>546.27</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>497.28</v>
+        <v>500.39</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>497.47</v>
+        <v>497.73</v>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
@@ -4718,20 +4718,20 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>1810.5</v>
+        <v>1790</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1756.5</v>
+        <v>1759.69</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>1613.63</v>
+        <v>1620.54</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1171.67</v>
+        <v>1177.82</v>
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
@@ -4762,20 +4762,20 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="10" t="n">
-        <v>70.43000000000001</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="D93" s="10" t="n">
-        <v>73.98999999999999</v>
+        <v>73.61</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>74.95999999999999</v>
+        <v>74.77</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>69.26000000000001</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
@@ -4806,20 +4806,20 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>330.15</v>
+        <v>330.4</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>318.85</v>
+        <v>319.95</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>293.78</v>
+        <v>295.22</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>239.48</v>
+        <v>240.64</v>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
@@ -4850,20 +4850,20 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="10" t="n">
-        <v>282.75</v>
+        <v>283.6</v>
       </c>
       <c r="D95" s="10" t="n">
-        <v>294.41</v>
+        <v>293.38</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>324.87</v>
+        <v>323.25</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>411.65</v>
+        <v>410.37</v>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
@@ -4894,20 +4894,20 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>570.8</v>
+        <v>569.8</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>551.88</v>
+        <v>553.59</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>535.08</v>
+        <v>536.4400000000001</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>450.41</v>
+        <v>451.53</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
@@ -4938,24 +4938,24 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>763.1</v>
+        <v>744.85</v>
       </c>
       <c r="D97" s="10" t="n">
-        <v>755.1900000000001</v>
+        <v>754.21</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>786.9</v>
+        <v>785.25</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>719.71</v>
-      </c>
-      <c r="G97" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>720.8099999999999</v>
+      </c>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
@@ -4982,20 +4982,20 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>231.25</v>
+        <v>227.69</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>248.22</v>
+        <v>246.26</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>261.45</v>
+        <v>260.13</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>305.68</v>
+        <v>305.08</v>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -5026,20 +5026,20 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>1850.2</v>
+        <v>1818.3</v>
       </c>
       <c r="D99" s="10" t="n">
-        <v>1888.12</v>
+        <v>1881.47</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>1876.6</v>
+        <v>1874.31</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>1783.86</v>
+        <v>1783.36</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -5070,20 +5070,20 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>228.1</v>
+        <v>227.13</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>212.03</v>
+        <v>213.47</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>200.13</v>
+        <v>201.19</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>182.24</v>
+        <v>182.65</v>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
@@ -5114,20 +5114,20 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>841.4</v>
+        <v>866.45</v>
       </c>
       <c r="D101" s="10" t="n">
-        <v>904.61</v>
+        <v>900.97</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>895.73</v>
+        <v>894.59</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>747.09</v>
+        <v>748.28</v>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -5158,20 +5158,20 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>408.85</v>
+        <v>415.15</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>398.13</v>
+        <v>399.75</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>385.31</v>
+        <v>386.48</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>367</v>
+        <v>367.62</v>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
@@ -5202,20 +5202,20 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>669.95</v>
+        <v>658.05</v>
       </c>
       <c r="D103" s="10" t="n">
-        <v>678.01</v>
+        <v>676.1</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>718.15</v>
+        <v>715.79</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>799.5599999999999</v>
+        <v>796.9299999999999</v>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
@@ -5246,20 +5246,20 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>11069</v>
+        <v>10924</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>10767.59</v>
+        <v>10782.49</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>10286.88</v>
+        <v>10311.87</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>9331.139999999999</v>
+        <v>9375.98</v>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
@@ -5290,20 +5290,20 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>724.85</v>
+        <v>719.7</v>
       </c>
       <c r="D105" s="10" t="n">
-        <v>744.26</v>
+        <v>741.92</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>766.38</v>
+        <v>764.55</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>715.48</v>
+        <v>715.39</v>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -5334,20 +5334,20 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>91.36</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>94.19</v>
+        <v>93.91</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>93.01000000000001</v>
+        <v>92.94</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>85.44</v>
+        <v>85.5</v>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
@@ -5378,20 +5378,20 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="10" t="n">
-        <v>1990.6</v>
+        <v>1942.6</v>
       </c>
       <c r="D107" s="10" t="n">
-        <v>1940.32</v>
+        <v>1940.54</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>1816.29</v>
+        <v>1821.24</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>1597.89</v>
+        <v>1603.02</v>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
@@ -5422,20 +5422,20 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>960.6</v>
+        <v>939.9</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>881.17</v>
+        <v>886.76</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>769.6799999999999</v>
+        <v>776.35</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>553.96</v>
+        <v>557.58</v>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
@@ -5466,20 +5466,20 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="10" t="n">
-        <v>1195.7</v>
+        <v>1217</v>
       </c>
       <c r="D109" s="10" t="n">
-        <v>1060.44</v>
+        <v>1075.35</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>1043.72</v>
+        <v>1050.52</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>993.51</v>
+        <v>995.63</v>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
@@ -5510,20 +5510,20 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>664.95</v>
+        <v>671.15</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>700.12</v>
+        <v>697.36</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>742.52</v>
+        <v>739.72</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>884.52</v>
+        <v>883.74</v>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
@@ -5554,20 +5554,20 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>445.55</v>
+        <v>439.45</v>
       </c>
       <c r="D111" s="10" t="n">
-        <v>433.89</v>
+        <v>434.42</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>413.07</v>
+        <v>414.11</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>342.58</v>
+        <v>343.96</v>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
@@ -5598,20 +5598,20 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>911.4</v>
+        <v>917.45</v>
       </c>
       <c r="D112" s="10" t="n">
-        <v>838.9400000000001</v>
+        <v>846.42</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>841.54</v>
+        <v>844.52</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>784.6</v>
+        <v>785.85</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -5642,20 +5642,20 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="10" t="n">
-        <v>437.45</v>
+        <v>435.45</v>
       </c>
       <c r="D113" s="10" t="n">
-        <v>395.81</v>
+        <v>399.58</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>394.21</v>
+        <v>395.83</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>396.51</v>
+        <v>396.78</v>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
@@ -5686,20 +5686,20 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>204.01</v>
+        <v>203.06</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>210.1</v>
+        <v>209.43</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>217.14</v>
+        <v>216.59</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>244.27</v>
+        <v>243.88</v>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
@@ -5730,20 +5730,20 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>78.36</v>
+        <v>75.39</v>
       </c>
       <c r="D115" s="10" t="n">
-        <v>80.15000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>87.66</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>96.42</v>
+        <v>96.11</v>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
@@ -5774,20 +5774,20 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>301.3</v>
+        <v>310.4</v>
       </c>
       <c r="D116" s="10" t="n">
-        <v>796.05</v>
+        <v>749.79</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>953.28</v>
+        <v>928.0700000000001</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>981.15</v>
+        <v>974.62</v>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
@@ -5818,20 +5818,20 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="10" t="n">
-        <v>355.05</v>
+        <v>373.5</v>
       </c>
       <c r="D117" s="10" t="n">
-        <v>321.38</v>
+        <v>326.34</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>304.66</v>
+        <v>307.36</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>313.51</v>
+        <v>314.1</v>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
@@ -5862,20 +5862,20 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>3302.5</v>
+        <v>3318.8</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>3331.39</v>
+        <v>3330.19</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>3206.02</v>
+        <v>3210.44</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>2878.72</v>
+        <v>2879.67</v>
       </c>
       <c r="G118" s="11" t="inlineStr">
         <is>
@@ -5906,20 +5906,20 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>4500.8</v>
+        <v>4447.4</v>
       </c>
       <c r="D119" s="10" t="n">
-        <v>4515.24</v>
+        <v>4508.78</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>4339.97</v>
+        <v>4344.18</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>3637.24</v>
+        <v>3644.33</v>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
@@ -5950,24 +5950,24 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>668.2</v>
+        <v>672.15</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>671.42</v>
+        <v>671.49</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>701.9</v>
+        <v>700.73</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>760.4400000000001</v>
-      </c>
-      <c r="G120" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>758.97</v>
+      </c>
+      <c r="G120" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
@@ -5994,20 +5994,20 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>291.55</v>
+        <v>287.5</v>
       </c>
       <c r="D121" s="10" t="n">
-        <v>317.3</v>
+        <v>314.46</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>348.23</v>
+        <v>345.85</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>401.93</v>
+        <v>400.41</v>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
@@ -6038,24 +6038,24 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>506.2</v>
+        <v>518.3</v>
       </c>
       <c r="D122" s="10" t="n">
-        <v>517.74</v>
+        <v>517.79</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>544.54</v>
+        <v>543.51</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>668.8200000000001</v>
-      </c>
-      <c r="G122" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>601.29</v>
+      </c>
+      <c r="G122" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
@@ -6082,20 +6082,20 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="10" t="n">
-        <v>627.25</v>
+        <v>622.4</v>
       </c>
       <c r="D123" s="10" t="n">
-        <v>618.3099999999999</v>
+        <v>618.7</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>577.24</v>
+        <v>579.01</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>499.88</v>
+        <v>501.31</v>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
@@ -6126,20 +6126,20 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>1597.3</v>
+        <v>1584.6</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>1514.44</v>
+        <v>1521.12</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>1394.62</v>
+        <v>1402.07</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1133.7</v>
+        <v>1138.08</v>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
@@ -6170,20 +6170,20 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="10" t="n">
-        <v>214.86</v>
+        <v>213.68</v>
       </c>
       <c r="D125" s="10" t="n">
-        <v>222.17</v>
+        <v>221.36</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>224.9</v>
+        <v>224.46</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>241.17</v>
+        <v>240.95</v>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -6214,20 +6214,20 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>460.3</v>
+        <v>459.9</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>493.47</v>
+        <v>490.27</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>504.8</v>
+        <v>503.04</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>539.2</v>
+        <v>538.42</v>
       </c>
       <c r="G126" s="11" t="inlineStr">
         <is>
@@ -6258,20 +6258,20 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>434.45</v>
+        <v>423.25</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>414.69</v>
+        <v>415.5</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>393.1</v>
+        <v>394.28</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>371.32</v>
+        <v>372.01</v>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
@@ -6302,20 +6302,20 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>821.2</v>
+        <v>817.8</v>
       </c>
       <c r="D128" s="10" t="n">
-        <v>824.79</v>
+        <v>824.12</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>793.99</v>
+        <v>794.92</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>731.9400000000001</v>
+        <v>732.47</v>
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
@@ -6346,24 +6346,24 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>741.1</v>
+        <v>749.65</v>
       </c>
       <c r="D129" s="10" t="n">
-        <v>749.11</v>
+        <v>749.16</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>708.61</v>
+        <v>710.22</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>592.5700000000001</v>
-      </c>
-      <c r="G129" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>593.89</v>
+      </c>
+      <c r="G129" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
@@ -6390,20 +6390,20 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>189.46</v>
+        <v>196.32</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>172.77</v>
+        <v>175.01</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>168.09</v>
+        <v>169.2</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>156.79</v>
+        <v>157.08</v>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
@@ -6434,24 +6434,24 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="10" t="n">
-        <v>712.55</v>
+        <v>700.9</v>
       </c>
       <c r="D131" s="10" t="n">
-        <v>705.34</v>
+        <v>704.91</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>686.89</v>
+        <v>687.4400000000001</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>644.3</v>
-      </c>
-      <c r="G131" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>644.7</v>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
@@ -6478,20 +6478,20 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>426.3</v>
+        <v>424.7</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>436.15</v>
+        <v>435.06</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>437.74</v>
+        <v>437.23</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>473.28</v>
+        <v>473.18</v>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="10" t="n">
-        <v>785.45</v>
+        <v>774.2</v>
       </c>
       <c r="D133" s="10" t="n">
-        <v>786.83</v>
+        <v>785.63</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>789</v>
+        <v>788.42</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>768.12</v>
+        <v>768.1900000000001</v>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6566,20 +6566,20 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>1848.7</v>
+        <v>1805.4</v>
       </c>
       <c r="D134" s="10" t="n">
-        <v>1798.81</v>
+        <v>1799.44</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>1740.04</v>
+        <v>1742.61</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1453.48</v>
+        <v>1456.98</v>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
@@ -6610,20 +6610,20 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="10" t="n">
-        <v>238.7</v>
+        <v>240.05</v>
       </c>
       <c r="D135" s="10" t="n">
-        <v>253.29</v>
+        <v>252.03</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>254.81</v>
+        <v>254.23</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>261.03</v>
+        <v>260.82</v>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6654,24 +6654,24 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>100.5</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>97.03</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>88.52</v>
+        <v>88.84</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>75.84</v>
-      </c>
-      <c r="G136" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>76</v>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -6698,20 +6698,20 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="10" t="n">
-        <v>380.1</v>
+        <v>398.05</v>
       </c>
       <c r="D137" s="10" t="n">
-        <v>369.94</v>
+        <v>372.62</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>356.2</v>
+        <v>357.84</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>366</v>
+        <v>366.38</v>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
@@ -6742,20 +6742,20 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>2021.6</v>
+        <v>1986.8</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>2148.19</v>
+        <v>2132.82</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>2217.44</v>
+        <v>2208.4</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2171.47</v>
+        <v>2173.61</v>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
@@ -6786,29 +6786,29 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="10" t="n">
-        <v>623.1</v>
+        <v>603.55</v>
       </c>
       <c r="D139" s="10" t="n">
-        <v>605.85</v>
+        <v>605.63</v>
       </c>
       <c r="E139" s="10" t="n">
-        <v>605.61</v>
+        <v>605.53</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>553.6900000000001</v>
-      </c>
-      <c r="G139" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H139" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>554.11</v>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I139" s="13" t="inlineStr">
@@ -6830,20 +6830,20 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>326.7</v>
+        <v>326.85</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>338.02</v>
+        <v>336.95</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>337.95</v>
+        <v>337.52</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>348.38</v>
+        <v>348.08</v>
       </c>
       <c r="G140" s="11" t="inlineStr">
         <is>
@@ -6874,20 +6874,20 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>451.5</v>
+        <v>441.25</v>
       </c>
       <c r="D141" s="10" t="n">
-        <v>434.69</v>
+        <v>435.31</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>404.58</v>
+        <v>406.02</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>309.95</v>
+        <v>311.25</v>
       </c>
       <c r="G141" s="13" t="inlineStr">
         <is>
@@ -6918,20 +6918,20 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>1277.3</v>
+        <v>1213.5</v>
       </c>
       <c r="D142" s="10" t="n">
-        <v>1189.49</v>
+        <v>1191.77</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>1048.06</v>
+        <v>1054.54</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>830.6799999999999</v>
+        <v>834.49</v>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
@@ -6962,20 +6962,20 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="10" t="n">
-        <v>128.93</v>
+        <v>131.86</v>
       </c>
       <c r="D143" s="10" t="n">
-        <v>124.44</v>
+        <v>125.15</v>
       </c>
       <c r="E143" s="10" t="n">
-        <v>126.79</v>
+        <v>126.99</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>122.56</v>
+        <v>122.6</v>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
@@ -7006,20 +7006,20 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>219.67</v>
+        <v>218.13</v>
       </c>
       <c r="D144" s="10" t="n">
-        <v>219.97</v>
+        <v>219.79</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>221.03</v>
+        <v>220.92</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>215.35</v>
+        <v>215.34</v>
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
@@ -7050,20 +7050,20 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="10" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D145" s="10" t="n">
+        <v>297.14</v>
+      </c>
+      <c r="E145" s="10" t="n">
         <v>298.84</v>
       </c>
-      <c r="E145" s="10" t="n">
-        <v>299.57</v>
-      </c>
       <c r="F145" s="10" t="n">
-        <v>283.8</v>
+        <v>283.84</v>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -7094,20 +7094,20 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>112.64</v>
+        <v>112.57</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>118.39</v>
+        <v>117.84</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>122.66</v>
+        <v>122.26</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>129.75</v>
+        <v>129.98</v>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -7138,24 +7138,24 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="10" t="n">
-        <v>156.94</v>
+        <v>158.88</v>
       </c>
       <c r="D147" s="10" t="n">
-        <v>157.63</v>
+        <v>157.75</v>
       </c>
       <c r="E147" s="10" t="n">
-        <v>155.41</v>
+        <v>155.54</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>147.85</v>
-      </c>
-      <c r="G147" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>147.95</v>
+      </c>
+      <c r="G147" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
@@ -7182,20 +7182,20 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>424.05</v>
+        <v>419.2</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>445.61</v>
+        <v>443.09</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>467.92</v>
+        <v>466.01</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>526.85</v>
+        <v>527.03</v>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
@@ -7226,20 +7226,20 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="10" t="n">
-        <v>94.81999999999999</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="D149" s="10" t="n">
-        <v>94.81</v>
+        <v>94.98</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>97.23</v>
+        <v>97.2</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>104.11</v>
+        <v>104.02</v>
       </c>
       <c r="G149" s="13" t="inlineStr">
         <is>
@@ -7270,20 +7270,20 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>2197.2</v>
+        <v>2200.8</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>2100.66</v>
+        <v>2110.2</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>2048.85</v>
+        <v>2054.81</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1785.66</v>
+        <v>1789.79</v>
       </c>
       <c r="G150" s="13" t="inlineStr">
         <is>
@@ -7314,20 +7314,20 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="10" t="n">
-        <v>2430.1</v>
+        <v>2379.4</v>
       </c>
       <c r="D151" s="10" t="n">
-        <v>2471.38</v>
+        <v>2461.24</v>
       </c>
       <c r="E151" s="10" t="n">
-        <v>2517.82</v>
+        <v>2510.9</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>2513.96</v>
+        <v>2512.39</v>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -7358,20 +7358,20 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>989.7</v>
+        <v>977.2</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>935.17</v>
+        <v>939.17</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>889.15</v>
+        <v>892.6</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>789.46</v>
+        <v>791.26</v>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
@@ -7402,20 +7402,20 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="10" t="n">
-        <v>2093.3</v>
+        <v>2085</v>
       </c>
       <c r="D153" s="10" t="n">
-        <v>1894.39</v>
+        <v>1912.54</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>1759.06</v>
+        <v>1771.84</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>1538.36</v>
+        <v>1545.71</v>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
@@ -7446,20 +7446,20 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>1828.3</v>
+        <v>1792.9</v>
       </c>
       <c r="D154" s="10" t="n">
-        <v>1675.88</v>
+        <v>1687.02</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>1480.4</v>
+        <v>1492.65</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1265.99</v>
+        <v>1270.42</v>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
@@ -7490,20 +7490,20 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="10" t="n">
-        <v>281.85</v>
+        <v>280.8</v>
       </c>
       <c r="D155" s="10" t="n">
-        <v>283.28</v>
+        <v>283.04</v>
       </c>
       <c r="E155" s="10" t="n">
-        <v>280.51</v>
+        <v>280.52</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>236.84</v>
+        <v>237.28</v>
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>11625</v>
+        <v>11543</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>11453.58</v>
+        <v>11462.1</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>11119.67</v>
+        <v>11136.27</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10113.11</v>
+        <v>10129.47</v>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
@@ -7578,20 +7578,20 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="10" t="n">
-        <v>2146.5</v>
+        <v>2142.9</v>
       </c>
       <c r="D157" s="10" t="n">
-        <v>2108.06</v>
+        <v>2111.38</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>2179.23</v>
+        <v>2177.8</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>2230.27</v>
+        <v>2231.07</v>
       </c>
       <c r="G157" s="13" t="inlineStr">
         <is>
@@ -7622,24 +7622,24 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>2277.9</v>
+        <v>2378.4</v>
       </c>
       <c r="D158" s="10" t="n">
-        <v>2320.61</v>
+        <v>2326.11</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>2193.17</v>
+        <v>2200.43</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>1817.92</v>
-      </c>
-      <c r="G158" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1825.32</v>
+      </c>
+      <c r="G158" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
@@ -7666,20 +7666,20 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="10" t="n">
-        <v>687</v>
+        <v>697.95</v>
       </c>
       <c r="D159" s="10" t="n">
-        <v>669.4</v>
+        <v>672.12</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>686.1900000000001</v>
+        <v>686.66</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>648.01</v>
+        <v>648.41</v>
       </c>
       <c r="G159" s="13" t="inlineStr">
         <is>
@@ -7710,20 +7710,20 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>481.25</v>
+        <v>480.55</v>
       </c>
       <c r="D160" s="10" t="n">
-        <v>499.58</v>
+        <v>497.77</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>516.27</v>
+        <v>514.87</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>552.98</v>
+        <v>552.37</v>
       </c>
       <c r="G160" s="11" t="inlineStr">
         <is>
@@ -7754,20 +7754,20 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>115.16</v>
+        <v>117.77</v>
       </c>
       <c r="D161" s="10" t="n">
-        <v>111.9</v>
+        <v>112.46</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>110.53</v>
+        <v>110.81</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>115.48</v>
+        <v>115.46</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
@@ -7779,9 +7779,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I161" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
@@ -7798,20 +7798,20 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>463.8</v>
+        <v>463.35</v>
       </c>
       <c r="D162" s="10" t="n">
-        <v>428.04</v>
+        <v>431.4</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>420.33</v>
+        <v>422.02</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>395.86</v>
+        <v>396.57</v>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>160.03</v>
+        <v>160.38</v>
       </c>
       <c r="D163" s="10" t="n">
         <v>160.32</v>
       </c>
       <c r="E163" s="10" t="n">
-        <v>160.85</v>
+        <v>160.84</v>
       </c>
       <c r="F163" s="10" t="n">
-        <v>168.78</v>
-      </c>
-      <c r="G163" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>169.02</v>
+      </c>
+      <c r="G163" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
@@ -7886,20 +7886,20 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="10" t="n">
-        <v>499.2</v>
+        <v>505.9</v>
       </c>
       <c r="D164" s="10" t="n">
-        <v>533.25</v>
+        <v>530.64</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>554.83</v>
+        <v>552.91</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>640.42</v>
+        <v>638.17</v>
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7930,20 +7930,20 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="10" t="n">
-        <v>764.1</v>
+        <v>737.55</v>
       </c>
       <c r="D165" s="10" t="n">
-        <v>718.04</v>
+        <v>719.9</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>666.62</v>
+        <v>669.4</v>
       </c>
       <c r="F165" s="10" t="n">
-        <v>562.9299999999999</v>
+        <v>564.61</v>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="10" t="n">
-        <v>195.1</v>
+        <v>195.65</v>
       </c>
       <c r="D166" s="10" t="n">
-        <v>202.47</v>
+        <v>201.82</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>203.77</v>
+        <v>203.46</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>230.37</v>
+        <v>229.99</v>
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
@@ -8018,20 +8018,20 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="10" t="n">
-        <v>214.25</v>
+        <v>215.96</v>
       </c>
       <c r="D167" s="10" t="n">
-        <v>223.73</v>
+        <v>222.99</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>231.35</v>
+        <v>230.75</v>
       </c>
       <c r="F167" s="10" t="n">
-        <v>230.19</v>
+        <v>229.9</v>
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
@@ -8062,20 +8062,20 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="10" t="n">
-        <v>547.95</v>
+        <v>535.55</v>
       </c>
       <c r="D168" s="10" t="n">
-        <v>526.96</v>
+        <v>527.77</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>503.5</v>
+        <v>504.76</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>472.92</v>
+        <v>473.54</v>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
@@ -8106,20 +8106,20 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="10" t="n">
-        <v>423.45</v>
+        <v>437</v>
       </c>
       <c r="D169" s="10" t="n">
-        <v>419.96</v>
+        <v>421.58</v>
       </c>
       <c r="E169" s="10" t="n">
-        <v>411.12</v>
+        <v>412.13</v>
       </c>
       <c r="F169" s="10" t="n">
-        <v>404.31</v>
+        <v>404.44</v>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
@@ -8150,20 +8150,20 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>839.4</v>
+        <v>884.4</v>
       </c>
       <c r="D170" s="10" t="n">
-        <v>818.46</v>
+        <v>824.74</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>755.08</v>
+        <v>760.15</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>639.47</v>
+        <v>641.47</v>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
@@ -8194,29 +8194,29 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="10" t="n">
-        <v>446.05</v>
+        <v>453.4</v>
       </c>
       <c r="D171" s="10" t="n">
-        <v>448.74</v>
+        <v>449.19</v>
       </c>
       <c r="E171" s="10" t="n">
-        <v>452.33</v>
+        <v>452.37</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>460.59</v>
-      </c>
-      <c r="G171" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H171" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>460.85</v>
+      </c>
+      <c r="G171" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H171" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I171" s="11" t="inlineStr">
@@ -8238,29 +8238,29 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="10" t="n">
-        <v>1111.2</v>
+        <v>1077.8</v>
       </c>
       <c r="D172" s="10" t="n">
-        <v>1142.44</v>
+        <v>1136.29</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>1102.91</v>
+        <v>1101.93</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>1041.57</v>
+        <v>1041.36</v>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H172" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H172" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I172" s="13" t="inlineStr">
@@ -8282,20 +8282,20 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>179</v>
+        <v>177.41</v>
       </c>
       <c r="D173" s="10" t="n">
-        <v>198.12</v>
+        <v>196.15</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>212.35</v>
+        <v>210.98</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>227.8</v>
+        <v>227.16</v>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
@@ -8326,20 +8326,20 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="10" t="n">
-        <v>541.55</v>
+        <v>536.65</v>
       </c>
       <c r="D174" s="10" t="n">
-        <v>558.98</v>
+        <v>556.85</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>520.85</v>
+        <v>521.47</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>517.03</v>
+        <v>516.48</v>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
@@ -8370,29 +8370,29 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="10" t="n">
-        <v>541.95</v>
+        <v>557.65</v>
       </c>
       <c r="D175" s="10" t="n">
-        <v>567.99</v>
+        <v>567.01</v>
       </c>
       <c r="E175" s="10" t="n">
-        <v>553.54</v>
+        <v>553.7</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>508.6</v>
+        <v>509.1</v>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H175" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H175" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I175" s="13" t="inlineStr">
@@ -8414,20 +8414,20 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="10" t="n">
-        <v>153.12</v>
+        <v>153.69</v>
       </c>
       <c r="D176" s="10" t="n">
-        <v>156.74</v>
+        <v>156.45</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>158.59</v>
+        <v>158.39</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>156.98</v>
+        <v>157.01</v>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
@@ -8458,20 +8458,20 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="10" t="n">
-        <v>177.06</v>
+        <v>183.93</v>
       </c>
       <c r="D177" s="10" t="n">
-        <v>187.72</v>
+        <v>187.36</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>196.96</v>
+        <v>196.45</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>247.87</v>
+        <v>247.23</v>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
@@ -8502,20 +8502,20 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="10" t="n">
-        <v>1513.2</v>
+        <v>1458.2</v>
       </c>
       <c r="D178" s="10" t="n">
-        <v>1391.13</v>
+        <v>1397.52</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>1290.58</v>
+        <v>1297.15</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>1075.71</v>
+        <v>1079.74</v>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="10" t="n">
-        <v>256.65</v>
+        <v>258.78</v>
       </c>
       <c r="D179" s="10" t="n">
-        <v>244.5</v>
+        <v>245.86</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>245.07</v>
+        <v>245.61</v>
       </c>
       <c r="F179" s="10" t="n">
-        <v>241.31</v>
+        <v>241.27</v>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
@@ -8590,24 +8590,24 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="10" t="n">
-        <v>388.75</v>
+        <v>385.9</v>
       </c>
       <c r="D180" s="10" t="n">
-        <v>387.45</v>
+        <v>387.3</v>
       </c>
       <c r="E180" s="10" t="n">
-        <v>369.95</v>
+        <v>370.57</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>327.21</v>
-      </c>
-      <c r="G180" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>327.8</v>
+      </c>
+      <c r="G180" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -8634,20 +8634,20 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="10" t="n">
-        <v>26.92</v>
+        <v>26.83</v>
       </c>
       <c r="D181" s="10" t="n">
-        <v>28.43</v>
+        <v>28.28</v>
       </c>
       <c r="E181" s="10" t="n">
-        <v>29.49</v>
+        <v>29.39</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>35.12</v>
+        <v>34.98</v>
       </c>
       <c r="G181" s="11" t="inlineStr">
         <is>
@@ -8678,20 +8678,20 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="10" t="n">
         <v>7.25</v>
       </c>
       <c r="D182" s="10" t="n">
-        <v>7.72</v>
+        <v>7.67</v>
       </c>
       <c r="E182" s="10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>9.18</v>
+        <v>9.15</v>
       </c>
       <c r="G182" s="11" t="inlineStr">
         <is>
@@ -8722,20 +8722,20 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="10" t="n">
-        <v>599.8</v>
+        <v>600.5</v>
       </c>
       <c r="D183" s="10" t="n">
-        <v>651.11</v>
+        <v>646.29</v>
       </c>
       <c r="E183" s="10" t="n">
-        <v>664.95</v>
+        <v>662.42</v>
       </c>
       <c r="F183" s="10" t="n">
-        <v>629.96</v>
+        <v>629.67</v>
       </c>
       <c r="G183" s="11" t="inlineStr">
         <is>
@@ -8766,20 +8766,20 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="10" t="n">
-        <v>268.8</v>
+        <v>263.95</v>
       </c>
       <c r="D184" s="10" t="n">
-        <v>280.29</v>
+        <v>278.74</v>
       </c>
       <c r="E184" s="10" t="n">
-        <v>306.55</v>
+        <v>304.88</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>353.84</v>
+        <v>353.04</v>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8810,20 +8810,20 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="10" t="n">
-        <v>722.05</v>
+        <v>718.05</v>
       </c>
       <c r="D185" s="10" t="n">
-        <v>763.55</v>
+        <v>759.22</v>
       </c>
       <c r="E185" s="10" t="n">
-        <v>799.04</v>
+        <v>795.86</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>899.1</v>
+        <v>898.37</v>
       </c>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8854,29 +8854,29 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="10" t="n">
-        <v>13270</v>
+        <v>13098</v>
       </c>
       <c r="D186" s="10" t="n">
-        <v>13434.76</v>
+        <v>13402.69</v>
       </c>
       <c r="E186" s="10" t="n">
-        <v>13233.59</v>
+        <v>13228.27</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>13276.22</v>
+        <v>13262.64</v>
       </c>
       <c r="G186" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H186" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H186" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I186" s="11" t="inlineStr">
@@ -8898,20 +8898,20 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="10" t="n">
-        <v>338.05</v>
+        <v>337.3</v>
       </c>
       <c r="D187" s="10" t="n">
-        <v>337.04</v>
+        <v>337.06</v>
       </c>
       <c r="E187" s="10" t="n">
-        <v>336.43</v>
+        <v>336.47</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>328.31</v>
+        <v>328.23</v>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
@@ -8942,20 +8942,20 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="10" t="n">
-        <v>57.34</v>
+        <v>57.6</v>
       </c>
       <c r="D188" s="10" t="n">
-        <v>60.68</v>
+        <v>60.39</v>
       </c>
       <c r="E188" s="10" t="n">
-        <v>61.44</v>
+        <v>61.28</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>66.34999999999999</v>
+        <v>66.23</v>
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
@@ -8986,20 +8986,20 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="10" t="n">
-        <v>1400.1</v>
+        <v>1390.2</v>
       </c>
       <c r="D189" s="10" t="n">
-        <v>1362.33</v>
+        <v>1364.99</v>
       </c>
       <c r="E189" s="10" t="n">
-        <v>1279.38</v>
+        <v>1283.72</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>1104.16</v>
+        <v>1108.11</v>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
@@ -9030,20 +9030,20 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="10" t="n">
-        <v>836.9</v>
+        <v>836.7</v>
       </c>
       <c r="D190" s="10" t="n">
-        <v>880.75</v>
+        <v>876.55</v>
       </c>
       <c r="E190" s="10" t="n">
-        <v>907.35</v>
+        <v>904.58</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>989.08</v>
+        <v>987.02</v>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
@@ -9074,20 +9074,20 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="10" t="n">
-        <v>773.05</v>
+        <v>780.45</v>
       </c>
       <c r="D191" s="10" t="n">
-        <v>791.14</v>
+        <v>790.12</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>807.91</v>
+        <v>806.83</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>788.88</v>
+        <v>788.45</v>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -9118,20 +9118,20 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="10" t="n">
-        <v>829.65</v>
+        <v>825.75</v>
       </c>
       <c r="D192" s="10" t="n">
-        <v>831.72</v>
+        <v>831.15</v>
       </c>
       <c r="E192" s="10" t="n">
-        <v>781.96</v>
+        <v>783.67</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>748.03</v>
+        <v>749.35</v>
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
@@ -9162,20 +9162,20 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="10" t="n">
-        <v>122.9</v>
+        <v>123.68</v>
       </c>
       <c r="D193" s="10" t="n">
-        <v>124.03</v>
+        <v>124</v>
       </c>
       <c r="E193" s="10" t="n">
-        <v>126.37</v>
+        <v>126.26</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>139.39</v>
+        <v>139.2</v>
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
@@ -9206,20 +9206,20 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="10" t="n">
-        <v>291.7</v>
+        <v>289.8</v>
       </c>
       <c r="D194" s="10" t="n">
-        <v>300.71</v>
+        <v>299.67</v>
       </c>
       <c r="E194" s="10" t="n">
-        <v>304.81</v>
+        <v>304.22</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>338.83</v>
+        <v>338.62</v>
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -9250,20 +9250,20 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="10" t="n">
-        <v>2971.7</v>
+        <v>2935.4</v>
       </c>
       <c r="D195" s="10" t="n">
-        <v>2894.77</v>
+        <v>2898.64</v>
       </c>
       <c r="E195" s="10" t="n">
-        <v>2774.47</v>
+        <v>2780.78</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>2579.88</v>
+        <v>2583.41</v>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
@@ -9294,29 +9294,29 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="10" t="n">
-        <v>2744</v>
+        <v>2687.4</v>
       </c>
       <c r="D196" s="10" t="n">
-        <v>2811.98</v>
+        <v>2800.11</v>
       </c>
       <c r="E196" s="10" t="n">
-        <v>2724.65</v>
+        <v>2723.19</v>
       </c>
       <c r="F196" s="10" t="n">
-        <v>2609.35</v>
+        <v>2604.34</v>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H196" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H196" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I196" s="13" t="inlineStr">
@@ -9338,20 +9338,20 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="10" t="n">
-        <v>782.85</v>
+        <v>797.95</v>
       </c>
       <c r="D197" s="10" t="n">
-        <v>700.58</v>
+        <v>709.86</v>
       </c>
       <c r="E197" s="10" t="n">
-        <v>641.4299999999999</v>
+        <v>647.5599999999999</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>557.79</v>
+        <v>559.97</v>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
@@ -9382,20 +9382,20 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="10" t="n">
-        <v>674.7</v>
+        <v>676.95</v>
       </c>
       <c r="D198" s="10" t="n">
-        <v>682.25</v>
+        <v>681.75</v>
       </c>
       <c r="E198" s="10" t="n">
-        <v>682.71</v>
+        <v>682.48</v>
       </c>
       <c r="F198" s="10" t="n">
-        <v>628.28</v>
+        <v>628.77</v>
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -9426,20 +9426,20 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="10" t="n">
-        <v>337.4</v>
+        <v>338.9</v>
       </c>
       <c r="D199" s="10" t="n">
-        <v>350.84</v>
+        <v>349.7</v>
       </c>
       <c r="E199" s="10" t="n">
-        <v>359.9</v>
+        <v>359.07</v>
       </c>
       <c r="F199" s="10" t="n">
-        <v>424.24</v>
+        <v>422.44</v>
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
@@ -9470,20 +9470,20 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="10" t="n">
-        <v>1744.5</v>
+        <v>1719.4</v>
       </c>
       <c r="D200" s="10" t="n">
-        <v>1826.64</v>
+        <v>1816.43</v>
       </c>
       <c r="E200" s="10" t="n">
-        <v>1924.43</v>
+        <v>1916.39</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>2038.55</v>
+        <v>2037.98</v>
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
@@ -9514,20 +9514,20 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="10" t="n">
-        <v>167.54</v>
+        <v>161.92</v>
       </c>
       <c r="D201" s="10" t="n">
-        <v>169.48</v>
+        <v>168.76</v>
       </c>
       <c r="E201" s="10" t="n">
-        <v>177.23</v>
+        <v>176.63</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>192.41</v>
+        <v>191.93</v>
       </c>
       <c r="G201" s="11" t="inlineStr">
         <is>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="10" t="n">
-        <v>116.57</v>
+        <v>115.06</v>
       </c>
       <c r="D202" s="10" t="n">
-        <v>122.33</v>
+        <v>121.64</v>
       </c>
       <c r="E202" s="10" t="n">
-        <v>125.94</v>
+        <v>125.51</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>127.11</v>
+        <v>127.04</v>
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
@@ -9602,20 +9602,20 @@
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="10" t="n">
-        <v>191.2</v>
+        <v>191.11</v>
       </c>
       <c r="D203" s="10" t="n">
-        <v>198.11</v>
+        <v>197.44</v>
       </c>
       <c r="E203" s="10" t="n">
-        <v>201.51</v>
+        <v>201.1</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>209.66</v>
+        <v>209.41</v>
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
@@ -9646,20 +9646,20 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="10" t="n">
-        <v>806.7</v>
+        <v>804.2</v>
       </c>
       <c r="D204" s="10" t="n">
-        <v>812.4</v>
+        <v>811.62</v>
       </c>
       <c r="E204" s="10" t="n">
-        <v>832.5700000000001</v>
+        <v>831.45</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>829.41</v>
+        <v>829.91</v>
       </c>
       <c r="G204" s="11" t="inlineStr">
         <is>
@@ -9690,20 +9690,20 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="10" t="n">
-        <v>113.58</v>
+        <v>113.53</v>
       </c>
       <c r="D205" s="10" t="n">
-        <v>116.06</v>
+        <v>115.82</v>
       </c>
       <c r="E205" s="10" t="n">
-        <v>119.36</v>
+        <v>119.13</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>138.12</v>
+        <v>137.64</v>
       </c>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9734,29 +9734,29 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="10" t="n">
-        <v>586.3</v>
+        <v>578.5</v>
       </c>
       <c r="D206" s="10" t="n">
-        <v>580.67</v>
+        <v>580.46</v>
       </c>
       <c r="E206" s="10" t="n">
-        <v>581.8</v>
+        <v>581.67</v>
       </c>
       <c r="F206" s="10" t="n">
-        <v>610.39</v>
-      </c>
-      <c r="G206" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H206" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>610.08</v>
+      </c>
+      <c r="G206" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H206" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I206" s="11" t="inlineStr">
@@ -9778,20 +9778,20 @@
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="10" t="n">
-        <v>393</v>
+        <v>407.75</v>
       </c>
       <c r="D207" s="10" t="n">
-        <v>407.96</v>
+        <v>407.94</v>
       </c>
       <c r="E207" s="10" t="n">
-        <v>418.83</v>
+        <v>418.39</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>440.92</v>
+        <v>440.69</v>
       </c>
       <c r="G207" s="11" t="inlineStr">
         <is>
@@ -9822,20 +9822,20 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="10" t="n">
-        <v>129.78</v>
+        <v>128.56</v>
       </c>
       <c r="D208" s="10" t="n">
-        <v>124.76</v>
+        <v>125.12</v>
       </c>
       <c r="E208" s="10" t="n">
-        <v>125.91</v>
+        <v>126.01</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>136.26</v>
+        <v>136.31</v>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
@@ -9866,20 +9866,20 @@
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="10" t="n">
-        <v>156.71</v>
+        <v>157.08</v>
       </c>
       <c r="D209" s="10" t="n">
-        <v>159.84</v>
+        <v>159.58</v>
       </c>
       <c r="E209" s="10" t="n">
-        <v>163.46</v>
+        <v>163.21</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>174.19</v>
+        <v>174.03</v>
       </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
@@ -9910,20 +9910,20 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="10" t="n">
-        <v>109.13</v>
+        <v>108.35</v>
       </c>
       <c r="D210" s="10" t="n">
-        <v>107.5</v>
+        <v>107.58</v>
       </c>
       <c r="E210" s="10" t="n">
-        <v>105.67</v>
+        <v>105.77</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>114.58</v>
+        <v>114.42</v>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
@@ -9954,20 +9954,20 @@
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="10" t="n">
-        <v>1266.8</v>
+        <v>1283.2</v>
       </c>
       <c r="D211" s="10" t="n">
-        <v>1335.09</v>
+        <v>1330.14</v>
       </c>
       <c r="E211" s="10" t="n">
-        <v>1328.55</v>
+        <v>1326.77</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>1319.35</v>
+        <v>1319.38</v>
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
@@ -9998,20 +9998,20 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="10" t="n">
-        <v>126.28</v>
+        <v>126.06</v>
       </c>
       <c r="D212" s="10" t="n">
-        <v>130.05</v>
+        <v>129.67</v>
       </c>
       <c r="E212" s="10" t="n">
-        <v>132.94</v>
+        <v>132.67</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>156.25</v>
+        <v>155.92</v>
       </c>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -10042,24 +10042,24 @@
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>299.5</v>
+        <v>303.35</v>
       </c>
       <c r="D213" s="10" t="n">
-        <v>300.75</v>
+        <v>301</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>311.69</v>
+        <v>311.36</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>318.17</v>
-      </c>
-      <c r="G213" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>317.98</v>
+      </c>
+      <c r="G213" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H213" s="11" t="inlineStr">
@@ -10086,20 +10086,20 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="10" t="n">
-        <v>253.9</v>
+        <v>249.6</v>
       </c>
       <c r="D214" s="10" t="n">
-        <v>262.52</v>
+        <v>261.29</v>
       </c>
       <c r="E214" s="10" t="n">
-        <v>275.69</v>
+        <v>274.66</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>353.43</v>
+        <v>353.28</v>
       </c>
       <c r="G214" s="11" t="inlineStr">
         <is>
@@ -10130,20 +10130,20 @@
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="10" t="n">
-        <v>817.4</v>
+        <v>816.4</v>
       </c>
       <c r="D215" s="10" t="n">
-        <v>818.54</v>
+        <v>818.33</v>
       </c>
       <c r="E215" s="10" t="n">
-        <v>808.5599999999999</v>
+        <v>808.87</v>
       </c>
       <c r="F215" s="10" t="n">
-        <v>802.5599999999999</v>
+        <v>801.49</v>
       </c>
       <c r="G215" s="11" t="inlineStr">
         <is>
@@ -10174,20 +10174,20 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>1305.4</v>
+        <v>1319.2</v>
       </c>
       <c r="D216" s="10" t="n">
-        <v>1072.19</v>
+        <v>1095.72</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>971.3</v>
+        <v>984.9400000000001</v>
       </c>
       <c r="F216" s="10" t="n">
-        <v>949.5599999999999</v>
+        <v>952.6799999999999</v>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
@@ -10218,24 +10218,24 @@
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="10" t="n">
-        <v>78.23999999999999</v>
+        <v>79.86</v>
       </c>
       <c r="D217" s="10" t="n">
-        <v>78.40000000000001</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="E217" s="10" t="n">
-        <v>76.31999999999999</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="F217" s="10" t="n">
-        <v>78.95999999999999</v>
-      </c>
-      <c r="G217" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>78.94</v>
+      </c>
+      <c r="G217" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H217" s="13" t="inlineStr">
@@ -10243,9 +10243,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I217" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I217" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J217" s="12" t="inlineStr">
@@ -10262,20 +10262,20 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="10" t="n">
-        <v>126.68</v>
+        <v>125.65</v>
       </c>
       <c r="D218" s="10" t="n">
-        <v>129.71</v>
+        <v>129.32</v>
       </c>
       <c r="E218" s="10" t="n">
-        <v>138.35</v>
+        <v>137.85</v>
       </c>
       <c r="F218" s="10" t="n">
-        <v>166</v>
+        <v>165.29</v>
       </c>
       <c r="G218" s="11" t="inlineStr">
         <is>
@@ -10306,20 +10306,20 @@
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="10" t="n">
-        <v>1096.9</v>
+        <v>1091.2</v>
       </c>
       <c r="D219" s="10" t="n">
-        <v>1053.94</v>
+        <v>1057.48</v>
       </c>
       <c r="E219" s="10" t="n">
-        <v>1066.05</v>
+        <v>1067.03</v>
       </c>
       <c r="F219" s="10" t="n">
-        <v>1121.71</v>
+        <v>1121.21</v>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
@@ -10350,20 +10350,20 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="10" t="n">
-        <v>246.7</v>
+        <v>245.25</v>
       </c>
       <c r="D220" s="10" t="n">
-        <v>247.47</v>
+        <v>247.25</v>
       </c>
       <c r="E220" s="10" t="n">
-        <v>241.51</v>
+        <v>241.66</v>
       </c>
       <c r="F220" s="10" t="n">
-        <v>227.14</v>
+        <v>227.31</v>
       </c>
       <c r="G220" s="11" t="inlineStr">
         <is>
@@ -10394,20 +10394,20 @@
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="10" t="n">
-        <v>1533.5</v>
+        <v>1531.6</v>
       </c>
       <c r="D221" s="10" t="n">
-        <v>1553.06</v>
+        <v>1551.02</v>
       </c>
       <c r="E221" s="10" t="n">
-        <v>1558.21</v>
+        <v>1557.16</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>1924.45</v>
+        <v>1918.67</v>
       </c>
       <c r="G221" s="11" t="inlineStr">
         <is>
@@ -10438,34 +10438,34 @@
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="10" t="n">
-        <v>635.15</v>
+        <v>627.5</v>
       </c>
       <c r="D222" s="10" t="n">
-        <v>627.63</v>
+        <v>627.62</v>
       </c>
       <c r="E222" s="10" t="n">
-        <v>634.86</v>
+        <v>634.58</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>634.04</v>
-      </c>
-      <c r="G222" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H222" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I222" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>633.84</v>
+      </c>
+      <c r="G222" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H222" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I222" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J222" s="12" t="inlineStr">
@@ -10482,20 +10482,20 @@
       </c>
       <c r="B223" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="10" t="n">
-        <v>24.35</v>
+        <v>24.82</v>
       </c>
       <c r="D223" s="10" t="n">
-        <v>24.09</v>
+        <v>24.16</v>
       </c>
       <c r="E223" s="10" t="n">
-        <v>23.58</v>
+        <v>23.63</v>
       </c>
       <c r="F223" s="10" t="n">
-        <v>25.07</v>
+        <v>25.05</v>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
@@ -10526,20 +10526,20 @@
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="10" t="n">
-        <v>674.65</v>
+        <v>673.05</v>
       </c>
       <c r="D224" s="10" t="n">
-        <v>621.4</v>
+        <v>626.3200000000001</v>
       </c>
       <c r="E224" s="10" t="n">
-        <v>592.3</v>
+        <v>595.47</v>
       </c>
       <c r="F224" s="10" t="n">
-        <v>592.6900000000001</v>
+        <v>594.62</v>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="10" t="n">
-        <v>399.35</v>
+        <v>397.35</v>
       </c>
       <c r="D225" s="10" t="n">
-        <v>424.16</v>
+        <v>421.61</v>
       </c>
       <c r="E225" s="10" t="n">
-        <v>438.47</v>
+        <v>436.86</v>
       </c>
       <c r="F225" s="10" t="n">
-        <v>486.5</v>
+        <v>485.34</v>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -10614,20 +10614,20 @@
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="10" t="n">
-        <v>219.57</v>
+        <v>216.05</v>
       </c>
       <c r="D226" s="10" t="n">
-        <v>220.95</v>
+        <v>220.48</v>
       </c>
       <c r="E226" s="10" t="n">
-        <v>229.31</v>
+        <v>228.79</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>245.39</v>
+        <v>245.24</v>
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -10658,24 +10658,24 @@
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="10" t="n">
-        <v>513.7</v>
+        <v>508.35</v>
       </c>
       <c r="D227" s="10" t="n">
-        <v>509.48</v>
+        <v>509.37</v>
       </c>
       <c r="E227" s="10" t="n">
-        <v>499.13</v>
+        <v>499.49</v>
       </c>
       <c r="F227" s="10" t="n">
-        <v>471.55</v>
-      </c>
-      <c r="G227" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>472.02</v>
+      </c>
+      <c r="G227" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H227" s="13" t="inlineStr">
@@ -10702,20 +10702,20 @@
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="10" t="n">
-        <v>112.45</v>
+        <v>115.22</v>
       </c>
       <c r="D228" s="10" t="n">
-        <v>110.63</v>
+        <v>111.06</v>
       </c>
       <c r="E228" s="10" t="n">
-        <v>111.67</v>
+        <v>111.81</v>
       </c>
       <c r="F228" s="10" t="n">
-        <v>122.45</v>
+        <v>122.27</v>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
@@ -10746,20 +10746,20 @@
       </c>
       <c r="B229" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="10" t="n">
+        <v>214.16</v>
+      </c>
+      <c r="D229" s="10" t="n">
         <v>216.25</v>
       </c>
-      <c r="D229" s="10" t="n">
-        <v>216.47</v>
-      </c>
       <c r="E229" s="10" t="n">
-        <v>216.45</v>
+        <v>216.36</v>
       </c>
       <c r="F229" s="10" t="n">
-        <v>223.44</v>
+        <v>223.78</v>
       </c>
       <c r="G229" s="11" t="inlineStr">
         <is>
@@ -10790,20 +10790,20 @@
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="10" t="n">
-        <v>1944.4</v>
+        <v>1920.3</v>
       </c>
       <c r="D230" s="10" t="n">
-        <v>1978.28</v>
+        <v>1972.76</v>
       </c>
       <c r="E230" s="10" t="n">
-        <v>1910.63</v>
+        <v>1911.01</v>
       </c>
       <c r="F230" s="10" t="n">
-        <v>1772.23</v>
+        <v>1773.38</v>
       </c>
       <c r="G230" s="11" t="inlineStr">
         <is>
@@ -10834,20 +10834,20 @@
       </c>
       <c r="B231" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="10" t="n">
-        <v>676.2</v>
+        <v>718.95</v>
       </c>
       <c r="D231" s="10" t="n">
-        <v>639.6799999999999</v>
+        <v>647.23</v>
       </c>
       <c r="E231" s="10" t="n">
-        <v>616.41</v>
+        <v>620.4299999999999</v>
       </c>
       <c r="F231" s="10" t="n">
-        <v>600.63</v>
+        <v>600.83</v>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
@@ -10878,20 +10878,20 @@
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="10" t="n">
-        <v>176.04</v>
+        <v>179.7</v>
       </c>
       <c r="D232" s="10" t="n">
-        <v>172.45</v>
+        <v>173.14</v>
       </c>
       <c r="E232" s="10" t="n">
-        <v>182.44</v>
+        <v>182.34</v>
       </c>
       <c r="F232" s="10" t="n">
-        <v>217.08</v>
+        <v>216.71</v>
       </c>
       <c r="G232" s="13" t="inlineStr">
         <is>
@@ -10922,20 +10922,20 @@
       </c>
       <c r="B233" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="10" t="n">
-        <v>5698.5</v>
+        <v>5614</v>
       </c>
       <c r="D233" s="10" t="n">
-        <v>5798.47</v>
+        <v>5780.91</v>
       </c>
       <c r="E233" s="10" t="n">
-        <v>5893.23</v>
+        <v>5882.28</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>5740.29</v>
+        <v>5743.35</v>
       </c>
       <c r="G233" s="11" t="inlineStr">
         <is>
@@ -10966,24 +10966,24 @@
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="10" t="n">
-        <v>339.8</v>
+        <v>337.75</v>
       </c>
       <c r="D234" s="10" t="n">
-        <v>339.19</v>
+        <v>339.05</v>
       </c>
       <c r="E234" s="10" t="n">
-        <v>340.04</v>
+        <v>339.95</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>388.44</v>
-      </c>
-      <c r="G234" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>387.26</v>
+      </c>
+      <c r="G234" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H234" s="11" t="inlineStr">
@@ -11010,20 +11010,20 @@
       </c>
       <c r="B235" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="10" t="n">
-        <v>27.61</v>
+        <v>27.6</v>
       </c>
       <c r="D235" s="10" t="n">
-        <v>29.43</v>
+        <v>29.26</v>
       </c>
       <c r="E235" s="10" t="n">
-        <v>30.9</v>
+        <v>30.77</v>
       </c>
       <c r="F235" s="10" t="n">
-        <v>35.53</v>
+        <v>35.43</v>
       </c>
       <c r="G235" s="11" t="inlineStr">
         <is>
@@ -11054,24 +11054,24 @@
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="10" t="n">
-        <v>192.32</v>
+        <v>194.68</v>
       </c>
       <c r="D236" s="10" t="n">
-        <v>192.58</v>
+        <v>192.78</v>
       </c>
       <c r="E236" s="10" t="n">
-        <v>198.78</v>
+        <v>198.62</v>
       </c>
       <c r="F236" s="10" t="n">
-        <v>212.64</v>
-      </c>
-      <c r="G236" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>212.54</v>
+      </c>
+      <c r="G236" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H236" s="11" t="inlineStr">
@@ -11098,24 +11098,24 @@
       </c>
       <c r="B237" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="10" t="n">
-        <v>124.65</v>
+        <v>128.73</v>
       </c>
       <c r="D237" s="10" t="n">
-        <v>128.29</v>
+        <v>128.33</v>
       </c>
       <c r="E237" s="10" t="n">
-        <v>129.21</v>
+        <v>129.19</v>
       </c>
       <c r="F237" s="10" t="n">
-        <v>123.49</v>
-      </c>
-      <c r="G237" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>123.52</v>
+      </c>
+      <c r="G237" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H237" s="11" t="inlineStr">
@@ -11142,20 +11142,20 @@
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="10" t="n">
-        <v>7.41</v>
+        <v>7.4</v>
       </c>
       <c r="D238" s="10" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E238" s="10" t="n">
-        <v>10.9</v>
+        <v>10.76</v>
       </c>
       <c r="F238" s="10" t="n">
-        <v>13.43</v>
+        <v>13.35</v>
       </c>
       <c r="G238" s="11" t="inlineStr">
         <is>
@@ -11186,20 +11186,20 @@
       </c>
       <c r="B239" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="10" t="n">
-        <v>99.26000000000001</v>
+        <v>100.19</v>
       </c>
       <c r="D239" s="10" t="n">
-        <v>105.03</v>
+        <v>104.57</v>
       </c>
       <c r="E239" s="10" t="n">
-        <v>108.91</v>
+        <v>108.57</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>121.16</v>
+        <v>121.05</v>
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
@@ -11230,20 +11230,20 @@
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="10" t="n">
-        <v>305</v>
+        <v>301.55</v>
       </c>
       <c r="D240" s="10" t="n">
-        <v>307.85</v>
+        <v>307.25</v>
       </c>
       <c r="E240" s="10" t="n">
-        <v>307.16</v>
+        <v>306.94</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>329.95</v>
+        <v>329.59</v>
       </c>
       <c r="G240" s="11" t="inlineStr">
         <is>
@@ -11274,20 +11274,20 @@
       </c>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="10" t="n">
-        <v>478.55</v>
+        <v>487.25</v>
       </c>
       <c r="D241" s="10" t="n">
-        <v>500.21</v>
+        <v>498.98</v>
       </c>
       <c r="E241" s="10" t="n">
-        <v>524.5700000000001</v>
+        <v>523.1</v>
       </c>
       <c r="F241" s="10" t="n">
-        <v>628.8099999999999</v>
+        <v>625.08</v>
       </c>
       <c r="G241" s="11" t="inlineStr">
         <is>
@@ -11318,24 +11318,24 @@
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="10" t="n">
-        <v>68.7</v>
+        <v>67.53</v>
       </c>
       <c r="D242" s="10" t="n">
-        <v>68.20999999999999</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="E242" s="10" t="n">
-        <v>67.36</v>
+        <v>67.37</v>
       </c>
       <c r="F242" s="10" t="n">
-        <v>72.53</v>
-      </c>
-      <c r="G242" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>72.45999999999999</v>
+      </c>
+      <c r="G242" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H242" s="13" t="inlineStr">
@@ -11362,24 +11362,24 @@
       </c>
       <c r="B243" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="10" t="n">
-        <v>1534.2</v>
+        <v>1501.6</v>
       </c>
       <c r="D243" s="10" t="n">
-        <v>1518.29</v>
+        <v>1516.7</v>
       </c>
       <c r="E243" s="10" t="n">
-        <v>1537.24</v>
+        <v>1535.84</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>1708.2</v>
-      </c>
-      <c r="G243" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1706.22</v>
+      </c>
+      <c r="G243" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H243" s="11" t="inlineStr">
@@ -11406,20 +11406,20 @@
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="10" t="n">
-        <v>123.18</v>
+        <v>120.95</v>
       </c>
       <c r="D244" s="10" t="n">
-        <v>129.13</v>
+        <v>128.35</v>
       </c>
       <c r="E244" s="10" t="n">
-        <v>132.76</v>
+        <v>132.3</v>
       </c>
       <c r="F244" s="10" t="n">
-        <v>136.32</v>
+        <v>136.12</v>
       </c>
       <c r="G244" s="11" t="inlineStr">
         <is>
@@ -11450,20 +11450,20 @@
       </c>
       <c r="B245" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="10" t="n">
-        <v>69.98</v>
+        <v>69.45</v>
       </c>
       <c r="D245" s="10" t="n">
-        <v>70.88</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="E245" s="10" t="n">
-        <v>71.95999999999999</v>
+        <v>71.86</v>
       </c>
       <c r="F245" s="10" t="n">
-        <v>77.58</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="G245" s="11" t="inlineStr">
         <is>
@@ -11494,20 +11494,20 @@
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="10" t="n">
-        <v>738.7</v>
+        <v>734.05</v>
       </c>
       <c r="D246" s="10" t="n">
-        <v>753.51</v>
+        <v>751.66</v>
       </c>
       <c r="E246" s="10" t="n">
-        <v>761</v>
+        <v>759.9400000000001</v>
       </c>
       <c r="F246" s="10" t="n">
-        <v>763.17</v>
+        <v>762.96</v>
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -11538,20 +11538,20 @@
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="10" t="n">
-        <v>422.9</v>
+        <v>441.15</v>
       </c>
       <c r="D247" s="10" t="n">
-        <v>416.21</v>
+        <v>418.59</v>
       </c>
       <c r="E247" s="10" t="n">
-        <v>422.84</v>
+        <v>423.56</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>428.28</v>
+        <v>428.05</v>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
@@ -11563,9 +11563,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I247" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I247" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J247" s="12" t="inlineStr">
@@ -11582,20 +11582,20 @@
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="10" t="n">
-        <v>596.15</v>
+        <v>592.3</v>
       </c>
       <c r="D248" s="10" t="n">
-        <v>665.3099999999999</v>
+        <v>658.35</v>
       </c>
       <c r="E248" s="10" t="n">
-        <v>736.12</v>
+        <v>730.48</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>819.88</v>
+        <v>817.65</v>
       </c>
       <c r="G248" s="11" t="inlineStr">
         <is>
@@ -11626,20 +11626,20 @@
       </c>
       <c r="B249" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="10" t="n">
-        <v>4049.5</v>
+        <v>4089.6</v>
       </c>
       <c r="D249" s="10" t="n">
-        <v>4222.51</v>
+        <v>4209.85</v>
       </c>
       <c r="E249" s="10" t="n">
-        <v>4370.39</v>
+        <v>4359.37</v>
       </c>
       <c r="F249" s="10" t="n">
-        <v>4526.14</v>
+        <v>4516.76</v>
       </c>
       <c r="G249" s="11" t="inlineStr">
         <is>
@@ -11670,20 +11670,20 @@
       </c>
       <c r="B250" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="10" t="n">
-        <v>729</v>
+        <v>712.6</v>
       </c>
       <c r="D250" s="10" t="n">
-        <v>733.24</v>
+        <v>731.27</v>
       </c>
       <c r="E250" s="10" t="n">
-        <v>756.89</v>
+        <v>755.16</v>
       </c>
       <c r="F250" s="10" t="n">
-        <v>787.8</v>
+        <v>786.74</v>
       </c>
       <c r="G250" s="11" t="inlineStr">
         <is>
@@ -11714,20 +11714,20 @@
       </c>
       <c r="B251" s="10" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="10" t="n">
-        <v>416</v>
+        <v>402.05</v>
       </c>
       <c r="D251" s="10" t="n">
-        <v>421.19</v>
+        <v>419.37</v>
       </c>
       <c r="E251" s="10" t="n">
-        <v>429.88</v>
+        <v>428.79</v>
       </c>
       <c r="F251" s="10" t="n">
-        <v>433.49</v>
+        <v>433.18</v>
       </c>
       <c r="G251" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 10-Sep-2026  14:46:11    |    Closing Price Date: 10-Sep-2026</t>
+          <t>Scan Run: 11-Sep-2026  14:50:00    |    Closing Price Date: 11-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -591,24 +591,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>10-Sep-2026  14:46:11</t>
+          <t>11-Sep-2026  14:50:00</t>
         </is>
       </c>
     </row>
@@ -622,21 +622,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 43.6% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 48.8% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.8% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -650,21 +650,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 110 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 109 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 122 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 125 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 142 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 140 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>250.18</v>
+        <v>244.93</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>257.58</v>
+        <v>256.38</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>267.79</v>
+        <v>266.89</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>297.45</v>
+        <v>297.16</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>328.75</v>
+        <v>323.7</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>331.16</v>
+        <v>330.45</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>322.9</v>
+        <v>322.94</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>324.97</v>
+        <v>324.9</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -827,9 +827,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J3" s="12" t="inlineStr">
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>6278</v>
+        <v>6583</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>5674.29</v>
+        <v>5760.84</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>5123.69</v>
+        <v>5180.92</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>4220.85</v>
+        <v>4243.3</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>762.75</v>
+        <v>804.9</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>733.47</v>
+        <v>740.27</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>681.95</v>
+        <v>686.77</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>541.75</v>
+        <v>544.5</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -934,20 +934,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>277.45</v>
+        <v>280</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>275.46</v>
+        <v>275.89</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>249.09</v>
+        <v>250.3</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>159.69</v>
+        <v>160.89</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>351.5</v>
+        <v>369.05</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>338.79</v>
+        <v>341.67</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>309.49</v>
+        <v>311.83</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>218.93</v>
+        <v>220.45</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7305</v>
+        <v>7312.5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>7066.72</v>
+        <v>7090.13</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6867.03</v>
+        <v>6884.5</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>5404.33</v>
+        <v>5425.7</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>855.15</v>
+        <v>890.35</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>829.05</v>
+        <v>834.89</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>764.64</v>
+        <v>769.5700000000001</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>618.29</v>
+        <v>621</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1110,24 +1110,24 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>332.55</v>
+        <v>325.35</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>326.94</v>
+        <v>326.79</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>308.18</v>
+        <v>308.85</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>258.05</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>258.68</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>5081.5</v>
+        <v>5126</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>5374.36</v>
+        <v>5350.7</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>5465.13</v>
+        <v>5451.83</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4513.46</v>
+        <v>4519.59</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1198,29 +1198,29 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>170.63</v>
+        <v>175.56</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>173.76</v>
+        <v>173.93</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>171.15</v>
+        <v>171.32</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>165.09</v>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>165.2</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2773.5</v>
+        <v>2849.1</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>2759.06</v>
+        <v>2767.64</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>2580.49</v>
+        <v>2591.03</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2122.56</v>
+        <v>2130.26</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>585.9</v>
+        <v>628.15</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>584.55</v>
+        <v>588.71</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>575.91</v>
+        <v>577.96</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>571.3200000000001</v>
+        <v>571.8099999999999</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>2227</v>
+        <v>2264.5</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>2172.67</v>
+        <v>2181.42</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1982.01</v>
+        <v>1993.09</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1481.53</v>
+        <v>1489.78</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>3495.6</v>
+        <v>3556.1</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3467.96</v>
+        <v>3476.35</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>3489.28</v>
+        <v>3491.9</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>3216.07</v>
+        <v>3222.73</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>413.2</v>
+        <v>422.25</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>396.46</v>
+        <v>398.92</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>391.42</v>
+        <v>392.63</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>333.02</v>
+        <v>334.12</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1462,20 +1462,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>739.6</v>
+        <v>761.4</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>762.79</v>
+        <v>762.66</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>720.13</v>
+        <v>721.75</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>622.9</v>
+        <v>623.9299999999999</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>854.75</v>
+        <v>897.4</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>718.28</v>
+        <v>735.34</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>642.04</v>
+        <v>652.05</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>418.75</v>
+        <v>423.53</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>207.88</v>
+        <v>209.27</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>186.61</v>
+        <v>188.52</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>174.88</v>
+        <v>175.98</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>160.96</v>
+        <v>161.21</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>13.83</v>
+        <v>13.7</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>11.56</v>
+        <v>11.76</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>10.55</v>
+        <v>10.67</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>10.18</v>
+        <v>10.21</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1638,20 +1638,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>229.96</v>
+        <v>225.97</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>241.84</v>
+        <v>240.33</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>236.83</v>
+        <v>236.4</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>196.88</v>
+        <v>197.17</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1682,20 +1682,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>2211.8</v>
+        <v>2277.9</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>2039.87</v>
+        <v>2062.54</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>1979.17</v>
+        <v>1990.89</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>1688.78</v>
+        <v>1695.31</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -1726,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>226.4</v>
+        <v>226.76</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>234.73</v>
+        <v>233.97</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>229.8</v>
+        <v>229.68</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>207.39</v>
+        <v>208.05</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1770,29 +1770,29 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>66.52</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>67.20999999999999</v>
+        <v>67.05</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>66.42</v>
+        <v>66.39</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>59.77</v>
+        <v>59.82</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -1814,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>164.8</v>
+        <v>163.08</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>169.5</v>
+        <v>168.89</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>166.57</v>
+        <v>166.43</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>149.71</v>
+        <v>149.84</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>184.87</v>
+        <v>180.8</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>189.2</v>
+        <v>188.4</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>190.73</v>
+        <v>190.34</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>189.81</v>
+        <v>189.71</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>503.85</v>
+        <v>502.8</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>538.52</v>
+        <v>535.12</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>550.72</v>
+        <v>548.84</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>541.23</v>
+        <v>541.3</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1946,24 +1946,24 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>355.1</v>
+        <v>348</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>349.6</v>
+        <v>349.44</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>322.87</v>
+        <v>323.86</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>262.39</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>263.35</v>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -1990,20 +1990,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>1453.3</v>
+        <v>1435.6</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1422.37</v>
+        <v>1423.63</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>1326.7</v>
+        <v>1330.97</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1018.8</v>
+        <v>1023.39</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>374.65</v>
+        <v>370.3</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>360.99</v>
+        <v>361.88</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>340.28</v>
+        <v>341.46</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>301.4</v>
+        <v>301.87</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>535.75</v>
+        <v>521.6</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>542.11</v>
+        <v>540.16</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>513.5599999999999</v>
+        <v>513.87</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>466.05</v>
+        <v>466.74</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>1640.3</v>
+        <v>1674.7</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1630.01</v>
+        <v>1634.27</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>1539.41</v>
+        <v>1544.72</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>1233.67</v>
+        <v>1239.25</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>830.3</v>
+        <v>827.4</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>788.11</v>
+        <v>791.85</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>720.51</v>
+        <v>724.71</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>531.85</v>
+        <v>534.63</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>611.05</v>
+        <v>613.2</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>609.1799999999999</v>
+        <v>609.5599999999999</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>607.55</v>
+        <v>607.77</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>597.24</v>
+        <v>597.4400000000001</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2254,17 +2254,17 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>514.75</v>
+        <v>516.85</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>540.99</v>
+        <v>538.6900000000001</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>530.72</v>
+        <v>530.1799999999999</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>478.62</v>
@@ -2298,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>196.74</v>
+        <v>190.35</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>200.44</v>
+        <v>199.48</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>203.19</v>
+        <v>202.68</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>202.9</v>
+        <v>203.11</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>815.3</v>
+        <v>798.6</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>834.6</v>
+        <v>831.17</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>895.4</v>
+        <v>891.61</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>976.5599999999999</v>
+        <v>974.12</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>542.05</v>
+        <v>542.9</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>577.46</v>
+        <v>574.17</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>617.22</v>
+        <v>614.3099999999999</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>626.37</v>
+        <v>626.14</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>349.9</v>
+        <v>346.4</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>357.45</v>
+        <v>356.4</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>358.63</v>
+        <v>358.15</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>344.67</v>
+        <v>344.45</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>217.28</v>
+        <v>215.97</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>210.52</v>
+        <v>211.03</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>205.84</v>
+        <v>206.24</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>173.15</v>
+        <v>173.66</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>80.55</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>85.95</v>
+        <v>85.64</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>85.68000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>71.81</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2562,20 +2562,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>245.44</v>
+        <v>242.5</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>235.3</v>
+        <v>235.38</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>222.44</v>
+        <v>222.62</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>217.48</v>
+        <v>216.87</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1696.8</v>
+        <v>1680.6</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1707.31</v>
+        <v>1702.58</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1682.53</v>
+        <v>1680.17</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1383.6</v>
+        <v>1384.91</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>332.4</v>
+        <v>332.35</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>376.36</v>
+        <v>372.17</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>381.8</v>
+        <v>379.86</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>406.49</v>
+        <v>405.71</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>557.7</v>
+        <v>549.7</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>581.92</v>
+        <v>578.85</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>570</v>
+        <v>569.2</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>490.8</v>
+        <v>491.49</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2738,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>165.61</v>
+        <v>166.86</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>170.02</v>
+        <v>169.72</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>176.85</v>
+        <v>176.46</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>213.44</v>
+        <v>212.97</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1270.8</v>
+        <v>1248.2</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1209.73</v>
+        <v>1213.4</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1122.49</v>
+        <v>1127.42</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1026.06</v>
+        <v>1028.25</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>923.65</v>
+        <v>910.9</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>897.5700000000001</v>
+        <v>898.84</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>852.92</v>
+        <v>855.2</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>706.61</v>
+        <v>708.59</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>178.12</v>
+        <v>178.21</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>175.05</v>
+        <v>175.35</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>179.51</v>
+        <v>179.46</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>182.07</v>
+        <v>182.06</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>269.95</v>
+        <v>273.55</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>284.96</v>
+        <v>283.87</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>295.57</v>
+        <v>294.7</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>303.29</v>
+        <v>302.53</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
@@ -2958,20 +2958,20 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>502.2</v>
+        <v>495.65</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>520.63</v>
+        <v>518.25</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>542.29</v>
+        <v>540.46</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>540.87</v>
+        <v>540.55</v>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
@@ -3002,20 +3002,20 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>4107.9</v>
+        <v>4129.9</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>3873.11</v>
+        <v>3897.57</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>3610.81</v>
+        <v>3631.17</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>2756.66</v>
+        <v>2769.65</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
@@ -3046,20 +3046,20 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>561.95</v>
+        <v>569.6</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>556.38</v>
+        <v>557.64</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>537.75</v>
+        <v>539</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>528.62</v>
+        <v>529.05</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
@@ -3090,20 +3090,20 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>1907.7</v>
+        <v>1885.8</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>2002.8</v>
+        <v>1991.66</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>2020.15</v>
+        <v>2014.88</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>1842.07</v>
+        <v>1842.93</v>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
@@ -3134,20 +3134,20 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>191.82</v>
+        <v>188.38</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>178.13</v>
+        <v>179.11</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>161.44</v>
+        <v>162.5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>132.07</v>
+        <v>132.72</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
@@ -3178,24 +3178,24 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>583</v>
+        <v>551.55</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>563.71</v>
+        <v>562.55</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>546.9</v>
+        <v>547.08</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>496.97</v>
-      </c>
-      <c r="G57" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>497.73</v>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -3222,20 +3222,20 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>1610</v>
+        <v>1626.3</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1714.04</v>
+        <v>1705.68</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>1715.46</v>
+        <v>1711.96</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1792.62</v>
+        <v>1790.54</v>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
@@ -3266,24 +3266,24 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>160.2</v>
+        <v>157.07</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>158.57</v>
+        <v>158.42</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>163.31</v>
+        <v>163.06</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>170.82</v>
-      </c>
-      <c r="G59" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>170.88</v>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -3310,24 +3310,24 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>3383.2</v>
+        <v>3279.5</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>3300.66</v>
+        <v>3296</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>3159.89</v>
+        <v>3161.89</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>2682.87</v>
-      </c>
-      <c r="G60" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2685.28</v>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>260.45</v>
+        <v>257.6</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>263.72</v>
+        <v>263.13</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>262.57</v>
+        <v>262.37</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>237.69</v>
+        <v>237.88</v>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
@@ -3398,20 +3398,20 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>500.75</v>
+        <v>493.55</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>508.13</v>
+        <v>506.74</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>518.27</v>
+        <v>517.3</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>573.34</v>
+        <v>572.37</v>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
@@ -3442,20 +3442,20 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>595.65</v>
+        <v>585.5</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>578.98</v>
+        <v>579.6</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>566.9</v>
+        <v>567.63</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>523.28</v>
+        <v>523.72</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
@@ -3486,20 +3486,20 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>22.81</v>
+        <v>22.73</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>22.83</v>
+        <v>22.82</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>22.55</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>22.58</v>
+        <v>22.64</v>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
@@ -3530,20 +3530,20 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>211.65</v>
+        <v>207.11</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>201.56</v>
+        <v>202.09</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>205.53</v>
+        <v>205.59</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>205.24</v>
+        <v>205.27</v>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
@@ -3574,20 +3574,20 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>193.6</v>
+        <v>192.25</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>196.99</v>
+        <v>196.54</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>202.45</v>
+        <v>202.05</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>192.3</v>
+        <v>192.49</v>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -3599,9 +3599,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J66" s="12" t="inlineStr">
@@ -3618,29 +3618,29 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>668.75</v>
+        <v>665.55</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>683.71</v>
+        <v>681.98</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>665.98</v>
+        <v>665.96</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>654.27</v>
+        <v>654.1</v>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H67" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I67" s="13" t="inlineStr">
@@ -3662,20 +3662,20 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>1869.7</v>
+        <v>1831.8</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>1688.99</v>
+        <v>1702.59</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>1661.71</v>
+        <v>1668.38</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1606.91</v>
+        <v>1608.07</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3706,24 +3706,24 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>687.65</v>
+        <v>692</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>690.74</v>
+        <v>690.86</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>716.37</v>
+        <v>715.42</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>829.36</v>
-      </c>
-      <c r="G69" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>827.35</v>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -3750,20 +3750,20 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>2295.8</v>
+        <v>2246.6</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>2111.1</v>
+        <v>2124</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>1992.11</v>
+        <v>2002.09</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1623.81</v>
+        <v>1629.86</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
@@ -3794,20 +3794,20 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>6905</v>
+        <v>6921.5</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>7061.25</v>
+        <v>7047.94</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>6894.72</v>
+        <v>6895.78</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>5517.23</v>
+        <v>5534.3</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -3838,24 +3838,24 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>46.08</v>
+        <v>46.18</v>
       </c>
       <c r="D72" s="10" t="n">
         <v>46.14</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>45.6</v>
+        <v>45.62</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="G72" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>41.61</v>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -3882,20 +3882,20 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>503.2</v>
+        <v>493.8</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>489.13</v>
+        <v>489.57</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>508.77</v>
+        <v>508.18</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>581.74</v>
+        <v>581.03</v>
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
@@ -3926,20 +3926,20 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>152.44</v>
+        <v>155.13</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>145.33</v>
+        <v>146.26</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>137.99</v>
+        <v>138.66</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>150.35</v>
+        <v>150.4</v>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
@@ -3970,24 +3970,24 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>2342.6</v>
+        <v>2276.5</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>2340.49</v>
+        <v>2334.4</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>2220.15</v>
+        <v>2222.36</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1781.28</v>
-      </c>
-      <c r="G75" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1786.18</v>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
@@ -4014,20 +4014,20 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>326.9</v>
+        <v>324.95</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>359.78</v>
+        <v>356.46</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>372.03</v>
+        <v>370.18</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>371.25</v>
+        <v>370.6</v>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
@@ -4058,20 +4058,20 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>781.35</v>
+        <v>765.55</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>786.02</v>
+        <v>784.0700000000001</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>819.35</v>
+        <v>817.24</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>887.41</v>
+        <v>887.51</v>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
@@ -4102,20 +4102,20 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>307.6</v>
+        <v>305.7</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>326.76</v>
+        <v>324.76</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>335.39</v>
+        <v>334.23</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>365.63</v>
+        <v>365.07</v>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
@@ -4146,20 +4146,20 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>2823</v>
+        <v>2811.4</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>2620.09</v>
+        <v>2638.31</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>2541.33</v>
+        <v>2551.92</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>2488.83</v>
+        <v>2494.16</v>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
@@ -4190,20 +4190,20 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>182.65</v>
+        <v>180.22</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>192.49</v>
+        <v>191.32</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>201.73</v>
+        <v>200.89</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>213.96</v>
+        <v>213.59</v>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
@@ -4234,20 +4234,20 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>162.27</v>
+        <v>161.32</v>
       </c>
       <c r="D81" s="10" t="n">
-        <v>159.27</v>
+        <v>159.47</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>154.82</v>
+        <v>155.08</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>154.1</v>
+        <v>154.23</v>
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
@@ -4278,20 +4278,20 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>72.63</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>74.08</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>74.68000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>69.91</v>
+        <v>69.88</v>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
@@ -4322,20 +4322,20 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>196.91</v>
+        <v>196.01</v>
       </c>
       <c r="D83" s="10" t="n">
-        <v>201.64</v>
+        <v>201.1</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>206.63</v>
+        <v>206.21</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>184.43</v>
+        <v>183</v>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
@@ -4366,20 +4366,20 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>570.75</v>
+        <v>562.4</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>559.97</v>
+        <v>560.2</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>537.6</v>
+        <v>538.5700000000001</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>496.85</v>
+        <v>497.4</v>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
@@ -4410,34 +4410,34 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>15.36</v>
+        <v>16.29</v>
       </c>
       <c r="D85" s="10" t="n">
-        <v>15.51</v>
+        <v>15.58</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>15.72</v>
+        <v>15.75</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>16.06</v>
-      </c>
-      <c r="G85" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H85" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>16.08</v>
+      </c>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J85" s="12" t="inlineStr">
@@ -4454,20 +4454,20 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>833.85</v>
+        <v>831.95</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>867.8</v>
+        <v>864.39</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>904.3</v>
+        <v>901.47</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>954.02</v>
+        <v>955.22</v>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
@@ -4498,20 +4498,20 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>2388.9</v>
+        <v>2373</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>2195.81</v>
+        <v>2212.69</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>2114.69</v>
+        <v>2124.82</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1785.21</v>
+        <v>1789.8</v>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
@@ -4542,20 +4542,20 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>658.4</v>
+        <v>661.55</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>652.87</v>
+        <v>653.7</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>657.0700000000001</v>
+        <v>657.24</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>621.42</v>
+        <v>623.04</v>
       </c>
       <c r="G88" s="13" t="inlineStr">
         <is>
@@ -4586,20 +4586,20 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
-        <v>1279.1</v>
+        <v>1243.5</v>
       </c>
       <c r="D89" s="10" t="n">
-        <v>1343.86</v>
+        <v>1334.3</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>1373.6</v>
+        <v>1368.5</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>1309.95</v>
+        <v>1309.58</v>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
@@ -4630,20 +4630,20 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>136.74</v>
+        <v>132.43</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>129.39</v>
+        <v>128.39</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>124.49</v>
+        <v>123.49</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>116.98</v>
+        <v>115.83</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -4674,20 +4674,20 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="10" t="n">
-        <v>576.6</v>
+        <v>582.35</v>
       </c>
       <c r="D91" s="10" t="n">
-        <v>546.27</v>
+        <v>549.7</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>500.39</v>
+        <v>503.61</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>497.73</v>
+        <v>498.46</v>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
@@ -4718,20 +4718,20 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>1790</v>
+        <v>1835.4</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1759.69</v>
+        <v>1766.9</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>1620.54</v>
+        <v>1628.97</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1177.82</v>
+        <v>1184.36</v>
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
@@ -4762,20 +4762,20 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="10" t="n">
-        <v>70.01000000000001</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="D93" s="10" t="n">
-        <v>73.61</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>74.77</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>69.31999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
@@ -4806,20 +4806,20 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>330.4</v>
+        <v>329.4</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>319.95</v>
+        <v>320.85</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>295.22</v>
+        <v>296.56</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>240.64</v>
+        <v>241.33</v>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
@@ -4850,20 +4850,20 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="10" t="n">
-        <v>283.6</v>
+        <v>282.45</v>
       </c>
       <c r="D95" s="10" t="n">
-        <v>293.38</v>
+        <v>292.34</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>323.25</v>
+        <v>321.65</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>410.37</v>
+        <v>409.1</v>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
@@ -4894,20 +4894,20 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>569.8</v>
+        <v>575.1</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>553.59</v>
+        <v>555.64</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>536.4400000000001</v>
+        <v>537.96</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>451.53</v>
+        <v>452.93</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
@@ -4938,29 +4938,29 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>744.85</v>
+        <v>800.8</v>
       </c>
       <c r="D97" s="10" t="n">
-        <v>754.21</v>
+        <v>758.64</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>785.25</v>
+        <v>785.86</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>720.8099999999999</v>
-      </c>
-      <c r="G97" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H97" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>721.16</v>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I97" s="13" t="inlineStr">
@@ -4982,20 +4982,20 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>227.69</v>
+        <v>224.38</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>246.26</v>
+        <v>241.73</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>260.13</v>
+        <v>255.98</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>305.08</v>
+        <v>301.07</v>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -5026,20 +5026,20 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>1818.3</v>
+        <v>1784</v>
       </c>
       <c r="D99" s="10" t="n">
-        <v>1881.47</v>
+        <v>1872.19</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>1874.31</v>
+        <v>1870.77</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>1783.36</v>
+        <v>1783.81</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -5070,20 +5070,20 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>227.13</v>
+        <v>226.37</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>213.47</v>
+        <v>214.7</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>201.19</v>
+        <v>202.18</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>182.65</v>
+        <v>183.05</v>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
@@ -5114,20 +5114,20 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>866.45</v>
+        <v>878.25</v>
       </c>
       <c r="D101" s="10" t="n">
-        <v>900.97</v>
+        <v>898.8099999999999</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>894.59</v>
+        <v>893.95</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>748.28</v>
+        <v>750.15</v>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -5158,20 +5158,20 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>415.15</v>
+        <v>414.25</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>399.75</v>
+        <v>401.13</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>386.48</v>
+        <v>387.57</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>367.62</v>
+        <v>368.1</v>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
@@ -5202,20 +5202,20 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>658.05</v>
+        <v>660.15</v>
       </c>
       <c r="D103" s="10" t="n">
-        <v>676.1</v>
+        <v>674.59</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>715.79</v>
+        <v>713.61</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>796.9299999999999</v>
+        <v>795.22</v>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
@@ -5246,20 +5246,20 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>10924</v>
+        <v>11217</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>10782.49</v>
+        <v>10823.87</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>10311.87</v>
+        <v>10347.36</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>9375.98</v>
+        <v>9392.209999999999</v>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
@@ -5290,20 +5290,20 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>719.7</v>
+        <v>719.9</v>
       </c>
       <c r="D105" s="10" t="n">
-        <v>741.92</v>
+        <v>739.8200000000001</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>764.55</v>
+        <v>762.8</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>715.39</v>
+        <v>715.9400000000001</v>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -5334,20 +5334,20 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>91.29000000000001</v>
+        <v>89.97</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>93.91</v>
+        <v>93.53</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>92.94</v>
+        <v>92.83</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>85.5</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
@@ -5378,20 +5378,20 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="10" t="n">
-        <v>1942.6</v>
+        <v>1993.7</v>
       </c>
       <c r="D107" s="10" t="n">
-        <v>1940.54</v>
+        <v>1945.6</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>1821.24</v>
+        <v>1828</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>1603.02</v>
+        <v>1608.94</v>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
@@ -5422,20 +5422,20 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>939.9</v>
+        <v>961.15</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>886.76</v>
+        <v>893.85</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>776.35</v>
+        <v>783.6</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>557.58</v>
+        <v>561.77</v>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
@@ -5466,20 +5466,20 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="10" t="n">
-        <v>1217</v>
+        <v>1183.4</v>
       </c>
       <c r="D109" s="10" t="n">
-        <v>1075.35</v>
+        <v>1085.64</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>1050.52</v>
+        <v>1055.73</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>995.63</v>
+        <v>997.54</v>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
@@ -5510,20 +5510,20 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>671.15</v>
+        <v>680.85</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>697.36</v>
+        <v>695.79</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>739.72</v>
+        <v>737.41</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>883.74</v>
+        <v>881.99</v>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
@@ -5554,20 +5554,20 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>439.45</v>
+        <v>443.25</v>
       </c>
       <c r="D111" s="10" t="n">
-        <v>434.42</v>
+        <v>435.26</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>414.11</v>
+        <v>415.25</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>343.96</v>
+        <v>344.5</v>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
@@ -5598,20 +5598,20 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>917.45</v>
+        <v>901.75</v>
       </c>
       <c r="D112" s="10" t="n">
-        <v>846.42</v>
+        <v>851.6900000000001</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>844.52</v>
+        <v>846.77</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>785.85</v>
+        <v>786.38</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -5642,20 +5642,20 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="10" t="n">
-        <v>435.45</v>
+        <v>445.7</v>
       </c>
       <c r="D113" s="10" t="n">
-        <v>399.58</v>
+        <v>403.97</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>395.83</v>
+        <v>397.79</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>396.78</v>
+        <v>397.76</v>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
@@ -5686,20 +5686,20 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>203.06</v>
+        <v>201.99</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>209.43</v>
+        <v>208.72</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>216.59</v>
+        <v>216.02</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>243.88</v>
+        <v>243.72</v>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
@@ -5730,20 +5730,20 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>75.39</v>
+        <v>75.84</v>
       </c>
       <c r="D115" s="10" t="n">
-        <v>79.7</v>
+        <v>79.33</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>87.18000000000001</v>
+        <v>86.73</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>96.11</v>
+        <v>95.97</v>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
@@ -5774,20 +5774,20 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>310.4</v>
+        <v>294.9</v>
       </c>
       <c r="D116" s="10" t="n">
-        <v>749.79</v>
+        <v>706.47</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>928.0700000000001</v>
+        <v>903.24</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>974.62</v>
+        <v>967.72</v>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
@@ -5818,20 +5818,20 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="10" t="n">
-        <v>373.5</v>
+        <v>380.2</v>
       </c>
       <c r="D117" s="10" t="n">
-        <v>326.34</v>
+        <v>331.47</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>307.36</v>
+        <v>310.21</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>314.1</v>
+        <v>314.76</v>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
@@ -5862,24 +5862,24 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>3318.8</v>
+        <v>3385</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>3330.19</v>
+        <v>3335.41</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>3210.44</v>
+        <v>3217.28</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>2879.67</v>
-      </c>
-      <c r="G118" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2883.76</v>
+      </c>
+      <c r="G118" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
@@ -5906,20 +5906,20 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>4447.4</v>
+        <v>4371.5</v>
       </c>
       <c r="D119" s="10" t="n">
-        <v>4508.78</v>
+        <v>4495.7</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>4344.18</v>
+        <v>4345.25</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>3644.33</v>
+        <v>3651.91</v>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
@@ -5950,24 +5950,24 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>672.15</v>
+        <v>652.25</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>671.49</v>
+        <v>669.65</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>700.73</v>
+        <v>698.83</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>758.97</v>
-      </c>
-      <c r="G120" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>758.3200000000001</v>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
@@ -5994,20 +5994,20 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>287.5</v>
+        <v>281.7</v>
       </c>
       <c r="D121" s="10" t="n">
-        <v>314.46</v>
+        <v>311.34</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>345.85</v>
+        <v>343.34</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>400.41</v>
+        <v>400.19</v>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
@@ -6038,24 +6038,24 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>518.3</v>
+        <v>511.85</v>
       </c>
       <c r="D122" s="10" t="n">
-        <v>517.79</v>
+        <v>517.22</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>543.51</v>
+        <v>542.27</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>601.29</v>
-      </c>
-      <c r="G122" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>600.46</v>
+      </c>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
@@ -6082,20 +6082,20 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="10" t="n">
-        <v>622.4</v>
+        <v>624.55</v>
       </c>
       <c r="D123" s="10" t="n">
-        <v>618.7</v>
+        <v>619.26</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>579.01</v>
+        <v>580.8</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>501.31</v>
+        <v>502.23</v>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
@@ -6126,20 +6126,20 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>1584.6</v>
+        <v>1593.6</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>1521.12</v>
+        <v>1528.03</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>1402.07</v>
+        <v>1409.58</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1138.08</v>
+        <v>1142.53</v>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
@@ -6170,20 +6170,20 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="10" t="n">
-        <v>213.68</v>
+        <v>214.36</v>
       </c>
       <c r="D125" s="10" t="n">
-        <v>221.36</v>
+        <v>220.7</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>224.46</v>
+        <v>224.06</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>240.95</v>
+        <v>240.71</v>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -6214,20 +6214,20 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>459.9</v>
+        <v>461.95</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>490.27</v>
+        <v>487.58</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>503.04</v>
+        <v>501.43</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>538.42</v>
+        <v>537.65</v>
       </c>
       <c r="G126" s="11" t="inlineStr">
         <is>
@@ -6258,20 +6258,20 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>423.25</v>
+        <v>421.05</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>415.5</v>
+        <v>416.03</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>394.28</v>
+        <v>395.33</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>372.01</v>
+        <v>372.58</v>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
@@ -6302,20 +6302,20 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>817.8</v>
+        <v>808.95</v>
       </c>
       <c r="D128" s="10" t="n">
-        <v>824.12</v>
+        <v>822.6799999999999</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>794.92</v>
+        <v>795.47</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>732.47</v>
+        <v>733.28</v>
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
@@ -6346,20 +6346,20 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>749.65</v>
+        <v>776.35</v>
       </c>
       <c r="D129" s="10" t="n">
-        <v>749.16</v>
+        <v>751.75</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>710.22</v>
+        <v>712.8099999999999</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>593.89</v>
+        <v>595.36</v>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
@@ -6390,20 +6390,20 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>196.32</v>
+        <v>198.93</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>175.01</v>
+        <v>177.29</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>169.2</v>
+        <v>170.36</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>157.08</v>
+        <v>157.66</v>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
@@ -6434,20 +6434,20 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="10" t="n">
-        <v>700.9</v>
+        <v>693.9</v>
       </c>
       <c r="D131" s="10" t="n">
-        <v>704.91</v>
+        <v>703.86</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>687.4400000000001</v>
+        <v>687.6900000000001</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>644.7</v>
+        <v>645.51</v>
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
@@ -6478,20 +6478,20 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>424.7</v>
+        <v>421.15</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>435.06</v>
+        <v>433.73</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>437.23</v>
+        <v>436.6</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>473.18</v>
+        <v>472.26</v>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="10" t="n">
-        <v>774.2</v>
+        <v>785.5</v>
       </c>
       <c r="D133" s="10" t="n">
-        <v>785.63</v>
+        <v>785.61</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>788.42</v>
+        <v>788.3099999999999</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>768.1900000000001</v>
+        <v>768.74</v>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6566,24 +6566,24 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>1805.4</v>
+        <v>1777.8</v>
       </c>
       <c r="D134" s="10" t="n">
-        <v>1799.44</v>
+        <v>1797.38</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>1742.61</v>
+        <v>1743.99</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1456.98</v>
-      </c>
-      <c r="G134" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1460.18</v>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
@@ -6610,20 +6610,20 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="10" t="n">
-        <v>240.05</v>
+        <v>238.9</v>
       </c>
       <c r="D135" s="10" t="n">
-        <v>252.03</v>
+        <v>250.78</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>254.23</v>
+        <v>253.63</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>260.82</v>
+        <v>260.6</v>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6654,24 +6654,24 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>96.81999999999999</v>
+        <v>98.05</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>97.01000000000001</v>
+        <v>97.11</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>88.84</v>
+        <v>89.2</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="G136" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>76.23</v>
+      </c>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -6698,20 +6698,20 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="10" t="n">
-        <v>398.05</v>
+        <v>417.4</v>
       </c>
       <c r="D137" s="10" t="n">
-        <v>372.62</v>
+        <v>376.89</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>357.84</v>
+        <v>360.18</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>366.38</v>
+        <v>367.9</v>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
@@ -6742,20 +6742,20 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>1986.8</v>
+        <v>2009.5</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>2132.82</v>
+        <v>2121.08</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>2208.4</v>
+        <v>2200.6</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2173.61</v>
+        <v>2172.2</v>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
@@ -6786,29 +6786,29 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="10" t="n">
-        <v>603.55</v>
+        <v>616.45</v>
       </c>
       <c r="D139" s="10" t="n">
-        <v>605.63</v>
+        <v>606.66</v>
       </c>
       <c r="E139" s="10" t="n">
-        <v>605.53</v>
+        <v>605.96</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>554.11</v>
-      </c>
-      <c r="G139" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H139" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>554.54</v>
+      </c>
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H139" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I139" s="13" t="inlineStr">
@@ -6830,20 +6830,20 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>326.85</v>
+        <v>322.15</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>336.95</v>
+        <v>335.54</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>337.52</v>
+        <v>336.91</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>348.08</v>
+        <v>348.14</v>
       </c>
       <c r="G140" s="11" t="inlineStr">
         <is>
@@ -6874,20 +6874,20 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>441.25</v>
+        <v>447.8</v>
       </c>
       <c r="D141" s="10" t="n">
-        <v>435.31</v>
+        <v>436.5</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>406.02</v>
+        <v>407.66</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>311.25</v>
+        <v>312.61</v>
       </c>
       <c r="G141" s="13" t="inlineStr">
         <is>
@@ -6918,20 +6918,20 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>1213.5</v>
+        <v>1202.8</v>
       </c>
       <c r="D142" s="10" t="n">
-        <v>1191.77</v>
+        <v>1192.82</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>1054.54</v>
+        <v>1060.36</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>834.49</v>
+        <v>838.15</v>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
@@ -6962,20 +6962,20 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="10" t="n">
-        <v>131.86</v>
+        <v>135.46</v>
       </c>
       <c r="D143" s="10" t="n">
-        <v>125.15</v>
+        <v>126.13</v>
       </c>
       <c r="E143" s="10" t="n">
-        <v>126.99</v>
+        <v>127.32</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>122.6</v>
+        <v>122.7</v>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
@@ -7006,20 +7006,20 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>218.13</v>
+        <v>218</v>
       </c>
       <c r="D144" s="10" t="n">
-        <v>219.79</v>
+        <v>219.62</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>220.92</v>
+        <v>220.8</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>215.34</v>
+        <v>215.35</v>
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
@@ -7050,20 +7050,20 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="10" t="n">
-        <v>281</v>
+        <v>279.15</v>
       </c>
       <c r="D145" s="10" t="n">
-        <v>297.14</v>
+        <v>295.42</v>
       </c>
       <c r="E145" s="10" t="n">
-        <v>298.84</v>
+        <v>298.07</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>283.84</v>
+        <v>283.93</v>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -7094,20 +7094,20 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>112.57</v>
+        <v>111.45</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>117.84</v>
+        <v>117.23</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>122.26</v>
+        <v>121.84</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>129.98</v>
+        <v>129.78</v>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -7138,20 +7138,20 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="10" t="n">
-        <v>158.88</v>
+        <v>158.53</v>
       </c>
       <c r="D147" s="10" t="n">
-        <v>157.75</v>
+        <v>157.83</v>
       </c>
       <c r="E147" s="10" t="n">
-        <v>155.54</v>
+        <v>155.66</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>147.95</v>
+        <v>148.11</v>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
@@ -7182,20 +7182,20 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>419.2</v>
+        <v>410.35</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>443.09</v>
+        <v>438.06</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>466.01</v>
+        <v>461.69</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>527.03</v>
+        <v>523.34</v>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
@@ -7226,24 +7226,24 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="10" t="n">
-        <v>96.51000000000001</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="D149" s="10" t="n">
-        <v>94.98</v>
+        <v>94.89</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>97.2</v>
+        <v>97.08</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>104.02</v>
-      </c>
-      <c r="G149" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>103.85</v>
+      </c>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
@@ -7270,20 +7270,20 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>2200.8</v>
+        <v>2236.1</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>2110.2</v>
+        <v>2122.19</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>2054.81</v>
+        <v>2061.92</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1789.79</v>
+        <v>1794.23</v>
       </c>
       <c r="G150" s="13" t="inlineStr">
         <is>
@@ -7314,20 +7314,20 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="10" t="n">
-        <v>2379.4</v>
+        <v>2421.3</v>
       </c>
       <c r="D151" s="10" t="n">
-        <v>2461.24</v>
+        <v>2457.44</v>
       </c>
       <c r="E151" s="10" t="n">
-        <v>2510.9</v>
+        <v>2507.38</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>2512.39</v>
+        <v>2511.66</v>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -7358,20 +7358,20 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>977.2</v>
+        <v>966.3</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>939.17</v>
+        <v>941.75</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>892.6</v>
+        <v>895.49</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>791.26</v>
+        <v>792.95</v>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
@@ -7402,20 +7402,20 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="10" t="n">
-        <v>2085</v>
+        <v>2055.7</v>
       </c>
       <c r="D153" s="10" t="n">
-        <v>1912.54</v>
+        <v>1925.51</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>1771.84</v>
+        <v>1782.32</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>1545.71</v>
+        <v>1551.74</v>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
@@ -7446,20 +7446,20 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>1792.9</v>
+        <v>1815.4</v>
       </c>
       <c r="D154" s="10" t="n">
-        <v>1687.02</v>
+        <v>1699.25</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>1492.65</v>
+        <v>1505.31</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1270.42</v>
+        <v>1276.36</v>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
@@ -7490,29 +7490,29 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="10" t="n">
-        <v>280.8</v>
+        <v>279.3</v>
       </c>
       <c r="D155" s="10" t="n">
-        <v>283.04</v>
+        <v>282.69</v>
       </c>
       <c r="E155" s="10" t="n">
-        <v>280.52</v>
+        <v>280.48</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>237.28</v>
+        <v>237.7</v>
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H155" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H155" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I155" s="13" t="inlineStr">
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>11543</v>
+        <v>12097</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>11462.1</v>
+        <v>11522.57</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>11136.27</v>
+        <v>11173.94</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10129.47</v>
+        <v>10151</v>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
@@ -7578,20 +7578,20 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="10" t="n">
-        <v>2142.9</v>
+        <v>2113.1</v>
       </c>
       <c r="D157" s="10" t="n">
-        <v>2111.38</v>
+        <v>2111.54</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>2177.8</v>
+        <v>2175.27</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>2231.07</v>
+        <v>2229.26</v>
       </c>
       <c r="G157" s="13" t="inlineStr">
         <is>
@@ -7622,20 +7622,20 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>2378.4</v>
+        <v>1187.7</v>
       </c>
       <c r="D158" s="10" t="n">
-        <v>2326.11</v>
+        <v>1163.38</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>2200.43</v>
+        <v>1104.89</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>1825.32</v>
+        <v>917.8</v>
       </c>
       <c r="G158" s="13" t="inlineStr">
         <is>
@@ -7666,20 +7666,20 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="10" t="n">
-        <v>697.95</v>
+        <v>691.55</v>
       </c>
       <c r="D159" s="10" t="n">
-        <v>672.12</v>
+        <v>673.97</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>686.66</v>
+        <v>686.85</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>648.41</v>
+        <v>648.96</v>
       </c>
       <c r="G159" s="13" t="inlineStr">
         <is>
@@ -7710,20 +7710,20 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>480.55</v>
+        <v>470.45</v>
       </c>
       <c r="D160" s="10" t="n">
-        <v>497.77</v>
+        <v>495.17</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>514.87</v>
+        <v>513.13</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>552.37</v>
+        <v>551.95</v>
       </c>
       <c r="G160" s="11" t="inlineStr">
         <is>
@@ -7754,20 +7754,20 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>117.77</v>
+        <v>117.81</v>
       </c>
       <c r="D161" s="10" t="n">
-        <v>112.46</v>
+        <v>112.32</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>110.81</v>
+        <v>110.41</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>115.46</v>
+        <v>115.21</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
@@ -7798,20 +7798,20 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>463.35</v>
+        <v>447.4</v>
       </c>
       <c r="D162" s="10" t="n">
-        <v>431.4</v>
+        <v>432.93</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>422.02</v>
+        <v>423.01</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>396.57</v>
+        <v>397.3</v>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
@@ -7842,29 +7842,29 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>160.38</v>
+        <v>155.95</v>
       </c>
       <c r="D163" s="10" t="n">
-        <v>160.32</v>
+        <v>155.38</v>
       </c>
       <c r="E163" s="10" t="n">
-        <v>160.84</v>
+        <v>155.83</v>
       </c>
       <c r="F163" s="10" t="n">
-        <v>169.02</v>
+        <v>163.82</v>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H163" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H163" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I163" s="11" t="inlineStr">
@@ -7886,20 +7886,20 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="10" t="n">
         <v>505.9</v>
       </c>
       <c r="D164" s="10" t="n">
-        <v>530.64</v>
+        <v>528.29</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>552.91</v>
+        <v>551.0599999999999</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>638.17</v>
+        <v>636.55</v>
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7930,20 +7930,20 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="10" t="n">
-        <v>737.55</v>
+        <v>738.55</v>
       </c>
       <c r="D165" s="10" t="n">
-        <v>719.9</v>
+        <v>721.67</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>669.4</v>
+        <v>672.12</v>
       </c>
       <c r="F165" s="10" t="n">
-        <v>564.61</v>
+        <v>566.66</v>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="10" t="n">
-        <v>195.65</v>
+        <v>195.06</v>
       </c>
       <c r="D166" s="10" t="n">
-        <v>201.82</v>
+        <v>201.18</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>203.46</v>
+        <v>203.13</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>229.99</v>
+        <v>229.56</v>
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
@@ -8018,20 +8018,20 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="10" t="n">
-        <v>215.96</v>
+        <v>212.58</v>
       </c>
       <c r="D167" s="10" t="n">
-        <v>222.99</v>
+        <v>222</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>230.75</v>
+        <v>230.04</v>
       </c>
       <c r="F167" s="10" t="n">
-        <v>229.9</v>
+        <v>229.86</v>
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
@@ -8062,20 +8062,20 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="10" t="n">
-        <v>535.55</v>
+        <v>530.75</v>
       </c>
       <c r="D168" s="10" t="n">
-        <v>527.77</v>
+        <v>528.0599999999999</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>504.76</v>
+        <v>505.78</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>473.54</v>
+        <v>474.11</v>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
@@ -8106,20 +8106,20 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="10" t="n">
-        <v>437</v>
+        <v>428.5</v>
       </c>
       <c r="D169" s="10" t="n">
-        <v>421.58</v>
+        <v>422.24</v>
       </c>
       <c r="E169" s="10" t="n">
-        <v>412.13</v>
+        <v>412.78</v>
       </c>
       <c r="F169" s="10" t="n">
-        <v>404.44</v>
+        <v>405.07</v>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
@@ -8150,20 +8150,20 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>884.4</v>
+        <v>872</v>
       </c>
       <c r="D170" s="10" t="n">
-        <v>824.74</v>
+        <v>829.24</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>760.15</v>
+        <v>764.54</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>641.47</v>
+        <v>643.9400000000001</v>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
@@ -8194,29 +8194,29 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="10" t="n">
-        <v>453.4</v>
+        <v>446.5</v>
       </c>
       <c r="D171" s="10" t="n">
-        <v>449.19</v>
+        <v>448.93</v>
       </c>
       <c r="E171" s="10" t="n">
-        <v>452.37</v>
+        <v>452.14</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>460.85</v>
-      </c>
-      <c r="G171" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H171" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>460.86</v>
+      </c>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H171" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I171" s="11" t="inlineStr">
@@ -8238,20 +8238,20 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="10" t="n">
-        <v>1077.8</v>
+        <v>1089.3</v>
       </c>
       <c r="D172" s="10" t="n">
-        <v>1136.29</v>
+        <v>1131.81</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>1101.93</v>
+        <v>1101.43</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>1041.36</v>
+        <v>1042.58</v>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
@@ -8282,20 +8282,20 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>177.41</v>
+        <v>175.4</v>
       </c>
       <c r="D173" s="10" t="n">
-        <v>196.15</v>
+        <v>194.17</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>210.98</v>
+        <v>209.58</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>227.16</v>
+        <v>226.71</v>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
@@ -8326,20 +8326,20 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="10" t="n">
-        <v>536.65</v>
+        <v>533.4</v>
       </c>
       <c r="D174" s="10" t="n">
-        <v>556.85</v>
+        <v>554.62</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>521.47</v>
+        <v>521.9400000000001</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>516.48</v>
+        <v>516.41</v>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
@@ -8370,20 +8370,20 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="10" t="n">
-        <v>557.65</v>
+        <v>566.25</v>
       </c>
       <c r="D175" s="10" t="n">
-        <v>567.01</v>
+        <v>566.9400000000001</v>
       </c>
       <c r="E175" s="10" t="n">
-        <v>553.7</v>
+        <v>554.1900000000001</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>509.1</v>
+        <v>509.02</v>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
@@ -8414,20 +8414,20 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="10" t="n">
-        <v>153.69</v>
+        <v>152.78</v>
       </c>
       <c r="D176" s="10" t="n">
-        <v>156.45</v>
+        <v>156.1</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>158.39</v>
+        <v>158.17</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>157.01</v>
+        <v>156.92</v>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
@@ -8458,20 +8458,20 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="10" t="n">
-        <v>183.93</v>
+        <v>187</v>
       </c>
       <c r="D177" s="10" t="n">
-        <v>187.36</v>
+        <v>187.32</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>196.45</v>
+        <v>196.08</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>247.23</v>
+        <v>246.98</v>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
@@ -8502,20 +8502,20 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="10" t="n">
-        <v>1458.2</v>
+        <v>1426.5</v>
       </c>
       <c r="D178" s="10" t="n">
-        <v>1397.52</v>
+        <v>1400.28</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>1297.15</v>
+        <v>1302.22</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>1079.74</v>
+        <v>1082.96</v>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="10" t="n">
-        <v>258.78</v>
+        <v>256.81</v>
       </c>
       <c r="D179" s="10" t="n">
-        <v>245.86</v>
+        <v>246.91</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>245.61</v>
+        <v>246.05</v>
       </c>
       <c r="F179" s="10" t="n">
-        <v>241.27</v>
+        <v>241.59</v>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
@@ -8590,24 +8590,24 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="10" t="n">
-        <v>385.9</v>
+        <v>387.4</v>
       </c>
       <c r="D180" s="10" t="n">
-        <v>387.3</v>
+        <v>387.31</v>
       </c>
       <c r="E180" s="10" t="n">
-        <v>370.57</v>
+        <v>371.23</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>327.8</v>
-      </c>
-      <c r="G180" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>328.39</v>
+      </c>
+      <c r="G180" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -8634,20 +8634,20 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="10" t="n">
-        <v>26.83</v>
+        <v>26.64</v>
       </c>
       <c r="D181" s="10" t="n">
-        <v>28.28</v>
+        <v>28.12</v>
       </c>
       <c r="E181" s="10" t="n">
-        <v>29.39</v>
+        <v>29.28</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>34.98</v>
+        <v>34.9</v>
       </c>
       <c r="G181" s="11" t="inlineStr">
         <is>
@@ -8678,20 +8678,20 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="10" t="n">
-        <v>7.25</v>
+        <v>7.17</v>
       </c>
       <c r="D182" s="10" t="n">
-        <v>7.67</v>
+        <v>7.62</v>
       </c>
       <c r="E182" s="10" t="n">
-        <v>8.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>9.15</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G182" s="11" t="inlineStr">
         <is>
@@ -8722,20 +8722,20 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="10" t="n">
-        <v>600.5</v>
+        <v>602.15</v>
       </c>
       <c r="D183" s="10" t="n">
-        <v>646.29</v>
+        <v>642.09</v>
       </c>
       <c r="E183" s="10" t="n">
-        <v>662.42</v>
+        <v>660.0599999999999</v>
       </c>
       <c r="F183" s="10" t="n">
-        <v>629.67</v>
+        <v>629.39</v>
       </c>
       <c r="G183" s="11" t="inlineStr">
         <is>
@@ -8766,20 +8766,20 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="10" t="n">
-        <v>263.95</v>
+        <v>255.4</v>
       </c>
       <c r="D184" s="10" t="n">
-        <v>278.74</v>
+        <v>276.52</v>
       </c>
       <c r="E184" s="10" t="n">
-        <v>304.88</v>
+        <v>302.94</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>353.04</v>
+        <v>351.69</v>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8810,20 +8810,20 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="10" t="n">
-        <v>718.05</v>
+        <v>715.85</v>
       </c>
       <c r="D185" s="10" t="n">
-        <v>759.22</v>
+        <v>755.09</v>
       </c>
       <c r="E185" s="10" t="n">
-        <v>795.86</v>
+        <v>792.73</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>898.37</v>
+        <v>897.5700000000001</v>
       </c>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8854,20 +8854,20 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="10" t="n">
-        <v>13098</v>
+        <v>12964</v>
       </c>
       <c r="D186" s="10" t="n">
-        <v>13402.69</v>
+        <v>13360.91</v>
       </c>
       <c r="E186" s="10" t="n">
-        <v>13228.27</v>
+        <v>13217.9</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>13262.64</v>
+        <v>13258.38</v>
       </c>
       <c r="G186" s="11" t="inlineStr">
         <is>
@@ -8898,20 +8898,20 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="10" t="n">
-        <v>337.3</v>
+        <v>339.05</v>
       </c>
       <c r="D187" s="10" t="n">
-        <v>337.06</v>
+        <v>337.25</v>
       </c>
       <c r="E187" s="10" t="n">
-        <v>336.47</v>
+        <v>336.57</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>328.23</v>
+        <v>329.12</v>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
@@ -8942,20 +8942,20 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="10" t="n">
-        <v>57.6</v>
+        <v>55.28</v>
       </c>
       <c r="D188" s="10" t="n">
-        <v>60.39</v>
+        <v>59.9</v>
       </c>
       <c r="E188" s="10" t="n">
-        <v>61.28</v>
+        <v>61.05</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>66.23</v>
+        <v>66.08</v>
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
@@ -8986,20 +8986,20 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="10" t="n">
-        <v>1390.2</v>
+        <v>1386.8</v>
       </c>
       <c r="D189" s="10" t="n">
-        <v>1364.99</v>
+        <v>1367.06</v>
       </c>
       <c r="E189" s="10" t="n">
-        <v>1283.72</v>
+        <v>1287.77</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>1108.11</v>
+        <v>1109.33</v>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
@@ -9030,20 +9030,20 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="10" t="n">
-        <v>836.7</v>
+        <v>825.15</v>
       </c>
       <c r="D190" s="10" t="n">
-        <v>876.55</v>
+        <v>871.66</v>
       </c>
       <c r="E190" s="10" t="n">
-        <v>904.58</v>
+        <v>901.47</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>987.02</v>
+        <v>984.97</v>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
@@ -9074,20 +9074,20 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="10" t="n">
-        <v>780.45</v>
+        <v>760.2</v>
       </c>
       <c r="D191" s="10" t="n">
-        <v>790.12</v>
+        <v>782.6900000000001</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>806.83</v>
+        <v>800.03</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>788.45</v>
+        <v>783.24</v>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -9118,20 +9118,20 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="10" t="n">
-        <v>825.75</v>
+        <v>826.95</v>
       </c>
       <c r="D192" s="10" t="n">
-        <v>831.15</v>
+        <v>830.75</v>
       </c>
       <c r="E192" s="10" t="n">
-        <v>783.67</v>
+        <v>785.37</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>749.35</v>
+        <v>751.25</v>
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
@@ -9162,24 +9162,24 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="10" t="n">
-        <v>123.68</v>
+        <v>125.66</v>
       </c>
       <c r="D193" s="10" t="n">
-        <v>124</v>
+        <v>124.15</v>
       </c>
       <c r="E193" s="10" t="n">
-        <v>126.26</v>
+        <v>126.24</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>139.2</v>
-      </c>
-      <c r="G193" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>139.13</v>
+      </c>
+      <c r="G193" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H193" s="11" t="inlineStr">
@@ -9206,20 +9206,20 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="10" t="n">
-        <v>289.8</v>
+        <v>288</v>
       </c>
       <c r="D194" s="10" t="n">
-        <v>299.67</v>
+        <v>298.56</v>
       </c>
       <c r="E194" s="10" t="n">
-        <v>304.22</v>
+        <v>303.59</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>338.62</v>
+        <v>338.21</v>
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -9250,24 +9250,24 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="10" t="n">
-        <v>2935.4</v>
+        <v>2887.7</v>
       </c>
       <c r="D195" s="10" t="n">
-        <v>2898.64</v>
+        <v>2897.59</v>
       </c>
       <c r="E195" s="10" t="n">
-        <v>2780.78</v>
+        <v>2784.97</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>2583.41</v>
-      </c>
-      <c r="G195" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2586.44</v>
+      </c>
+      <c r="G195" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H195" s="13" t="inlineStr">
@@ -9294,20 +9294,20 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="10" t="n">
-        <v>2687.4</v>
+        <v>2635.4</v>
       </c>
       <c r="D196" s="10" t="n">
-        <v>2800.11</v>
+        <v>2784.43</v>
       </c>
       <c r="E196" s="10" t="n">
-        <v>2723.19</v>
+        <v>2719.75</v>
       </c>
       <c r="F196" s="10" t="n">
-        <v>2604.34</v>
+        <v>2608.69</v>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
@@ -9338,20 +9338,20 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="10" t="n">
-        <v>797.95</v>
+        <v>786.2</v>
       </c>
       <c r="D197" s="10" t="n">
-        <v>709.86</v>
+        <v>717.13</v>
       </c>
       <c r="E197" s="10" t="n">
-        <v>647.5599999999999</v>
+        <v>653</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>559.97</v>
+        <v>562.21</v>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
@@ -9382,20 +9382,20 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="10" t="n">
-        <v>676.95</v>
+        <v>670.25</v>
       </c>
       <c r="D198" s="10" t="n">
-        <v>681.75</v>
+        <v>680.65</v>
       </c>
       <c r="E198" s="10" t="n">
-        <v>682.48</v>
+        <v>682</v>
       </c>
       <c r="F198" s="10" t="n">
-        <v>628.77</v>
+        <v>629.1799999999999</v>
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -9426,20 +9426,20 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="10" t="n">
-        <v>338.9</v>
+        <v>332.8</v>
       </c>
       <c r="D199" s="10" t="n">
-        <v>349.7</v>
+        <v>348.09</v>
       </c>
       <c r="E199" s="10" t="n">
-        <v>359.07</v>
+        <v>358.04</v>
       </c>
       <c r="F199" s="10" t="n">
-        <v>422.44</v>
+        <v>421.58</v>
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
@@ -9470,20 +9470,20 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="10" t="n">
-        <v>1719.4</v>
+        <v>1664.3</v>
       </c>
       <c r="D200" s="10" t="n">
-        <v>1816.43</v>
+        <v>1801.94</v>
       </c>
       <c r="E200" s="10" t="n">
-        <v>1916.39</v>
+        <v>1906.5</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>2037.98</v>
+        <v>2033.65</v>
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
@@ -9514,20 +9514,20 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="10" t="n">
-        <v>161.92</v>
+        <v>158.63</v>
       </c>
       <c r="D201" s="10" t="n">
-        <v>168.76</v>
+        <v>167.8</v>
       </c>
       <c r="E201" s="10" t="n">
-        <v>176.63</v>
+        <v>175.93</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>191.93</v>
+        <v>191.75</v>
       </c>
       <c r="G201" s="11" t="inlineStr">
         <is>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="10" t="n">
-        <v>115.06</v>
+        <v>116.1</v>
       </c>
       <c r="D202" s="10" t="n">
-        <v>121.64</v>
+        <v>121.11</v>
       </c>
       <c r="E202" s="10" t="n">
-        <v>125.51</v>
+        <v>125.14</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>127.04</v>
+        <v>126.86</v>
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
@@ -9602,20 +9602,20 @@
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="10" t="n">
-        <v>191.11</v>
+        <v>188.6</v>
       </c>
       <c r="D203" s="10" t="n">
-        <v>197.44</v>
+        <v>196.6</v>
       </c>
       <c r="E203" s="10" t="n">
-        <v>201.1</v>
+        <v>200.61</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>209.41</v>
+        <v>209.14</v>
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
@@ -9646,20 +9646,20 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="10" t="n">
         <v>804.2</v>
       </c>
       <c r="D204" s="10" t="n">
-        <v>811.62</v>
+        <v>810.91</v>
       </c>
       <c r="E204" s="10" t="n">
-        <v>831.45</v>
+        <v>830.39</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>829.91</v>
+        <v>830.63</v>
       </c>
       <c r="G204" s="11" t="inlineStr">
         <is>
@@ -9690,20 +9690,20 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="10" t="n">
-        <v>113.53</v>
+        <v>113.86</v>
       </c>
       <c r="D205" s="10" t="n">
-        <v>115.82</v>
+        <v>115.63</v>
       </c>
       <c r="E205" s="10" t="n">
-        <v>119.13</v>
+        <v>118.92</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>137.64</v>
+        <v>137.45</v>
       </c>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9734,29 +9734,29 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="10" t="n">
-        <v>578.5</v>
+        <v>591.25</v>
       </c>
       <c r="D206" s="10" t="n">
-        <v>580.46</v>
+        <v>581.49</v>
       </c>
       <c r="E206" s="10" t="n">
-        <v>581.67</v>
+        <v>582.04</v>
       </c>
       <c r="F206" s="10" t="n">
-        <v>610.08</v>
-      </c>
-      <c r="G206" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H206" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>609.89</v>
+      </c>
+      <c r="G206" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H206" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I206" s="11" t="inlineStr">
@@ -9778,20 +9778,20 @@
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="10" t="n">
-        <v>407.75</v>
+        <v>403.35</v>
       </c>
       <c r="D207" s="10" t="n">
-        <v>407.94</v>
+        <v>407.5</v>
       </c>
       <c r="E207" s="10" t="n">
-        <v>418.39</v>
+        <v>417.8</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>440.69</v>
+        <v>440.51</v>
       </c>
       <c r="G207" s="11" t="inlineStr">
         <is>
@@ -9822,20 +9822,20 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="10" t="n">
-        <v>128.56</v>
+        <v>131.39</v>
       </c>
       <c r="D208" s="10" t="n">
-        <v>125.12</v>
+        <v>125.72</v>
       </c>
       <c r="E208" s="10" t="n">
-        <v>126.01</v>
+        <v>126.22</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>136.31</v>
+        <v>136.13</v>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
@@ -9866,20 +9866,20 @@
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="10" t="n">
-        <v>157.08</v>
+        <v>153.45</v>
       </c>
       <c r="D209" s="10" t="n">
-        <v>159.58</v>
+        <v>156.47</v>
       </c>
       <c r="E209" s="10" t="n">
-        <v>163.21</v>
+        <v>160.08</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>174.03</v>
+        <v>170.83</v>
       </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
@@ -9910,20 +9910,20 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="10" t="n">
-        <v>108.35</v>
+        <v>108.63</v>
       </c>
       <c r="D210" s="10" t="n">
-        <v>107.58</v>
+        <v>107.68</v>
       </c>
       <c r="E210" s="10" t="n">
-        <v>105.77</v>
+        <v>105.88</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>114.42</v>
+        <v>114.52</v>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
@@ -9954,20 +9954,20 @@
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="10" t="n">
-        <v>1283.2</v>
+        <v>1300.1</v>
       </c>
       <c r="D211" s="10" t="n">
-        <v>1330.14</v>
+        <v>1327.28</v>
       </c>
       <c r="E211" s="10" t="n">
-        <v>1326.77</v>
+        <v>1325.73</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>1319.38</v>
+        <v>1318.03</v>
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
@@ -9998,20 +9998,20 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="10" t="n">
-        <v>126.06</v>
+        <v>125.58</v>
       </c>
       <c r="D212" s="10" t="n">
-        <v>129.67</v>
+        <v>129.28</v>
       </c>
       <c r="E212" s="10" t="n">
-        <v>132.67</v>
+        <v>132.39</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>155.92</v>
+        <v>155.54</v>
       </c>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -10042,24 +10042,24 @@
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>303.35</v>
+        <v>293.4</v>
       </c>
       <c r="D213" s="10" t="n">
-        <v>301</v>
+        <v>300.28</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>311.36</v>
+        <v>310.66</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>317.98</v>
-      </c>
-      <c r="G213" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>317.89</v>
+      </c>
+      <c r="G213" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H213" s="11" t="inlineStr">
@@ -10086,29 +10086,29 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="10" t="n">
-        <v>249.6</v>
+        <v>293.2</v>
       </c>
       <c r="D214" s="10" t="n">
-        <v>261.29</v>
+        <v>264.33</v>
       </c>
       <c r="E214" s="10" t="n">
-        <v>274.66</v>
+        <v>275.39</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>353.28</v>
-      </c>
-      <c r="G214" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H214" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>351.83</v>
+      </c>
+      <c r="G214" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H214" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I214" s="11" t="inlineStr">
@@ -10130,20 +10130,20 @@
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="10" t="n">
-        <v>816.4</v>
+        <v>810.95</v>
       </c>
       <c r="D215" s="10" t="n">
-        <v>818.33</v>
+        <v>817.63</v>
       </c>
       <c r="E215" s="10" t="n">
-        <v>808.87</v>
+        <v>808.95</v>
       </c>
       <c r="F215" s="10" t="n">
-        <v>801.49</v>
+        <v>802.21</v>
       </c>
       <c r="G215" s="11" t="inlineStr">
         <is>
@@ -10174,20 +10174,20 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>1319.2</v>
+        <v>1307.9</v>
       </c>
       <c r="D216" s="10" t="n">
-        <v>1095.72</v>
+        <v>1115.93</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>984.9400000000001</v>
+        <v>997.6</v>
       </c>
       <c r="F216" s="10" t="n">
-        <v>952.6799999999999</v>
+        <v>955.91</v>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
@@ -10218,24 +10218,24 @@
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="10" t="n">
-        <v>79.86</v>
+        <v>77.62</v>
       </c>
       <c r="D217" s="10" t="n">
-        <v>78.54000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="E217" s="10" t="n">
-        <v>76.45999999999999</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="F217" s="10" t="n">
-        <v>78.94</v>
-      </c>
-      <c r="G217" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>79.04000000000001</v>
+      </c>
+      <c r="G217" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H217" s="13" t="inlineStr">
@@ -10243,9 +10243,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I217" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I217" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J217" s="12" t="inlineStr">
@@ -10262,20 +10262,20 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="10" t="n">
-        <v>125.65</v>
+        <v>123.87</v>
       </c>
       <c r="D218" s="10" t="n">
-        <v>129.32</v>
+        <v>128.8</v>
       </c>
       <c r="E218" s="10" t="n">
-        <v>137.85</v>
+        <v>137.3</v>
       </c>
       <c r="F218" s="10" t="n">
-        <v>165.29</v>
+        <v>165</v>
       </c>
       <c r="G218" s="11" t="inlineStr">
         <is>
@@ -10306,20 +10306,20 @@
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="10" t="n">
-        <v>1091.2</v>
+        <v>1102.2</v>
       </c>
       <c r="D219" s="10" t="n">
-        <v>1057.48</v>
+        <v>1061.74</v>
       </c>
       <c r="E219" s="10" t="n">
-        <v>1067.03</v>
+        <v>1068.41</v>
       </c>
       <c r="F219" s="10" t="n">
-        <v>1121.21</v>
+        <v>1120.56</v>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
@@ -10350,29 +10350,29 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="10" t="n">
-        <v>245.25</v>
+        <v>239.3</v>
       </c>
       <c r="D220" s="10" t="n">
-        <v>247.25</v>
+        <v>246.5</v>
       </c>
       <c r="E220" s="10" t="n">
-        <v>241.66</v>
+        <v>241.57</v>
       </c>
       <c r="F220" s="10" t="n">
-        <v>227.31</v>
+        <v>227.41</v>
       </c>
       <c r="G220" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H220" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H220" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I220" s="13" t="inlineStr">
@@ -10394,20 +10394,20 @@
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="10" t="n">
-        <v>1531.6</v>
+        <v>1527.8</v>
       </c>
       <c r="D221" s="10" t="n">
-        <v>1551.02</v>
+        <v>1548.81</v>
       </c>
       <c r="E221" s="10" t="n">
-        <v>1557.16</v>
+        <v>1556.01</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>1918.67</v>
+        <v>1920.18</v>
       </c>
       <c r="G221" s="11" t="inlineStr">
         <is>
@@ -10438,20 +10438,20 @@
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="10" t="n">
-        <v>627.5</v>
+        <v>615</v>
       </c>
       <c r="D222" s="10" t="n">
-        <v>627.62</v>
+        <v>619.1799999999999</v>
       </c>
       <c r="E222" s="10" t="n">
-        <v>634.58</v>
+        <v>626.03</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>633.84</v>
+        <v>626.53</v>
       </c>
       <c r="G222" s="11" t="inlineStr">
         <is>
@@ -10482,20 +10482,20 @@
       </c>
       <c r="B223" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="10" t="n">
-        <v>24.82</v>
+        <v>24.87</v>
       </c>
       <c r="D223" s="10" t="n">
-        <v>24.16</v>
+        <v>24.23</v>
       </c>
       <c r="E223" s="10" t="n">
-        <v>23.63</v>
+        <v>23.68</v>
       </c>
       <c r="F223" s="10" t="n">
-        <v>25.05</v>
+        <v>25.06</v>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
@@ -10526,20 +10526,20 @@
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="10" t="n">
-        <v>673.05</v>
+        <v>675.85</v>
       </c>
       <c r="D224" s="10" t="n">
-        <v>626.3200000000001</v>
+        <v>631.04</v>
       </c>
       <c r="E224" s="10" t="n">
-        <v>595.47</v>
+        <v>598.62</v>
       </c>
       <c r="F224" s="10" t="n">
-        <v>594.62</v>
+        <v>596.36</v>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="10" t="n">
-        <v>397.35</v>
+        <v>394.15</v>
       </c>
       <c r="D225" s="10" t="n">
-        <v>421.61</v>
+        <v>418.99</v>
       </c>
       <c r="E225" s="10" t="n">
-        <v>436.86</v>
+        <v>435.18</v>
       </c>
       <c r="F225" s="10" t="n">
-        <v>485.34</v>
+        <v>484.78</v>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -10614,20 +10614,20 @@
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="10" t="n">
-        <v>216.05</v>
+        <v>214.27</v>
       </c>
       <c r="D226" s="10" t="n">
-        <v>220.48</v>
+        <v>219.89</v>
       </c>
       <c r="E226" s="10" t="n">
-        <v>228.79</v>
+        <v>228.22</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>245.24</v>
+        <v>244.83</v>
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -10658,20 +10658,20 @@
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="10" t="n">
-        <v>508.35</v>
+        <v>508.4</v>
       </c>
       <c r="D227" s="10" t="n">
-        <v>509.37</v>
+        <v>509.28</v>
       </c>
       <c r="E227" s="10" t="n">
-        <v>499.49</v>
+        <v>499.84</v>
       </c>
       <c r="F227" s="10" t="n">
-        <v>472.02</v>
+        <v>472.75</v>
       </c>
       <c r="G227" s="11" t="inlineStr">
         <is>
@@ -10702,20 +10702,20 @@
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="10" t="n">
-        <v>115.22</v>
+        <v>113.35</v>
       </c>
       <c r="D228" s="10" t="n">
-        <v>111.06</v>
+        <v>111.28</v>
       </c>
       <c r="E228" s="10" t="n">
-        <v>111.81</v>
+        <v>111.87</v>
       </c>
       <c r="F228" s="10" t="n">
-        <v>122.27</v>
+        <v>122.13</v>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
@@ -10746,20 +10746,20 @@
       </c>
       <c r="B229" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="10" t="n">
-        <v>214.16</v>
+        <v>212.06</v>
       </c>
       <c r="D229" s="10" t="n">
-        <v>216.25</v>
+        <v>215.85</v>
       </c>
       <c r="E229" s="10" t="n">
-        <v>216.36</v>
+        <v>216.19</v>
       </c>
       <c r="F229" s="10" t="n">
-        <v>223.78</v>
+        <v>224.7</v>
       </c>
       <c r="G229" s="11" t="inlineStr">
         <is>
@@ -10790,29 +10790,29 @@
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="10" t="n">
-        <v>1920.3</v>
+        <v>1867.5</v>
       </c>
       <c r="D230" s="10" t="n">
-        <v>1972.76</v>
+        <v>1962.74</v>
       </c>
       <c r="E230" s="10" t="n">
-        <v>1911.01</v>
+        <v>1909.31</v>
       </c>
       <c r="F230" s="10" t="n">
-        <v>1773.38</v>
+        <v>1773.47</v>
       </c>
       <c r="G230" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H230" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H230" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I230" s="13" t="inlineStr">
@@ -10834,20 +10834,20 @@
       </c>
       <c r="B231" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="10" t="n">
-        <v>718.95</v>
+        <v>728.9</v>
       </c>
       <c r="D231" s="10" t="n">
-        <v>647.23</v>
+        <v>655.01</v>
       </c>
       <c r="E231" s="10" t="n">
-        <v>620.4299999999999</v>
+        <v>624.6799999999999</v>
       </c>
       <c r="F231" s="10" t="n">
-        <v>600.83</v>
+        <v>601.8099999999999</v>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
@@ -10878,29 +10878,29 @@
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="10" t="n">
-        <v>179.7</v>
+        <v>186.68</v>
       </c>
       <c r="D232" s="10" t="n">
-        <v>173.14</v>
+        <v>174.43</v>
       </c>
       <c r="E232" s="10" t="n">
-        <v>182.34</v>
+        <v>182.51</v>
       </c>
       <c r="F232" s="10" t="n">
-        <v>216.71</v>
+        <v>216.41</v>
       </c>
       <c r="G232" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H232" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H232" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I232" s="11" t="inlineStr">
@@ -10922,20 +10922,20 @@
       </c>
       <c r="B233" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="10" t="n">
-        <v>5614</v>
+        <v>5587.5</v>
       </c>
       <c r="D233" s="10" t="n">
-        <v>5780.91</v>
+        <v>5762.49</v>
       </c>
       <c r="E233" s="10" t="n">
-        <v>5882.28</v>
+        <v>5870.72</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>5743.35</v>
+        <v>5744.62</v>
       </c>
       <c r="G233" s="11" t="inlineStr">
         <is>
@@ -10966,20 +10966,20 @@
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="10" t="n">
-        <v>337.75</v>
+        <v>335.3</v>
       </c>
       <c r="D234" s="10" t="n">
-        <v>339.05</v>
+        <v>338.7</v>
       </c>
       <c r="E234" s="10" t="n">
-        <v>339.95</v>
+        <v>339.77</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>387.26</v>
+        <v>386.65</v>
       </c>
       <c r="G234" s="11" t="inlineStr">
         <is>
@@ -11010,20 +11010,20 @@
       </c>
       <c r="B235" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="10" t="n">
-        <v>27.6</v>
+        <v>27.68</v>
       </c>
       <c r="D235" s="10" t="n">
-        <v>29.26</v>
+        <v>29.11</v>
       </c>
       <c r="E235" s="10" t="n">
-        <v>30.77</v>
+        <v>30.65</v>
       </c>
       <c r="F235" s="10" t="n">
-        <v>35.43</v>
+        <v>35.36</v>
       </c>
       <c r="G235" s="11" t="inlineStr">
         <is>
@@ -11054,20 +11054,20 @@
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="10" t="n">
-        <v>194.68</v>
+        <v>195.14</v>
       </c>
       <c r="D236" s="10" t="n">
-        <v>192.78</v>
+        <v>193.01</v>
       </c>
       <c r="E236" s="10" t="n">
-        <v>198.62</v>
+        <v>198.48</v>
       </c>
       <c r="F236" s="10" t="n">
-        <v>212.54</v>
+        <v>212.27</v>
       </c>
       <c r="G236" s="13" t="inlineStr">
         <is>
@@ -11098,29 +11098,29 @@
       </c>
       <c r="B237" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="10" t="n">
-        <v>128.73</v>
+        <v>130.49</v>
       </c>
       <c r="D237" s="10" t="n">
-        <v>128.33</v>
+        <v>128.54</v>
       </c>
       <c r="E237" s="10" t="n">
-        <v>129.19</v>
+        <v>129.25</v>
       </c>
       <c r="F237" s="10" t="n">
-        <v>123.52</v>
+        <v>123.85</v>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H237" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H237" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I237" s="13" t="inlineStr">
@@ -11142,20 +11142,20 @@
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="10" t="n">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="D238" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E238" s="10" t="n">
-        <v>10.76</v>
+        <v>10.63</v>
       </c>
       <c r="F238" s="10" t="n">
-        <v>13.35</v>
+        <v>13.29</v>
       </c>
       <c r="G238" s="11" t="inlineStr">
         <is>
@@ -11186,20 +11186,20 @@
       </c>
       <c r="B239" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="10" t="n">
-        <v>100.19</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="D239" s="10" t="n">
-        <v>104.57</v>
+        <v>103.93</v>
       </c>
       <c r="E239" s="10" t="n">
-        <v>108.57</v>
+        <v>108.14</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>121.05</v>
+        <v>120.98</v>
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
@@ -11230,20 +11230,20 @@
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="10" t="n">
-        <v>301.55</v>
+        <v>300.1</v>
       </c>
       <c r="D240" s="10" t="n">
-        <v>307.25</v>
+        <v>306.57</v>
       </c>
       <c r="E240" s="10" t="n">
-        <v>306.94</v>
+        <v>306.68</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>329.59</v>
+        <v>329.22</v>
       </c>
       <c r="G240" s="11" t="inlineStr">
         <is>
@@ -11274,20 +11274,20 @@
       </c>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="10" t="n">
-        <v>487.25</v>
+        <v>484</v>
       </c>
       <c r="D241" s="10" t="n">
-        <v>498.98</v>
+        <v>497.55</v>
       </c>
       <c r="E241" s="10" t="n">
-        <v>523.1</v>
+        <v>521.5700000000001</v>
       </c>
       <c r="F241" s="10" t="n">
-        <v>625.08</v>
+        <v>623.11</v>
       </c>
       <c r="G241" s="11" t="inlineStr">
         <is>
@@ -11318,29 +11318,29 @@
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="10" t="n">
-        <v>67.53</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="D242" s="10" t="n">
-        <v>68.15000000000001</v>
+        <v>67.86</v>
       </c>
       <c r="E242" s="10" t="n">
-        <v>67.37</v>
+        <v>67.28</v>
       </c>
       <c r="F242" s="10" t="n">
-        <v>72.45999999999999</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="G242" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H242" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H242" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I242" s="11" t="inlineStr">
@@ -11362,29 +11362,29 @@
       </c>
       <c r="B243" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="10" t="n">
-        <v>1501.6</v>
+        <v>1544.7</v>
       </c>
       <c r="D243" s="10" t="n">
-        <v>1516.7</v>
+        <v>1519.37</v>
       </c>
       <c r="E243" s="10" t="n">
-        <v>1535.84</v>
+        <v>1536.19</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>1706.22</v>
-      </c>
-      <c r="G243" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H243" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1702.79</v>
+      </c>
+      <c r="G243" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H243" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I243" s="11" t="inlineStr">
@@ -11406,20 +11406,20 @@
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="10" t="n">
-        <v>120.95</v>
+        <v>120.62</v>
       </c>
       <c r="D244" s="10" t="n">
-        <v>128.35</v>
+        <v>127.62</v>
       </c>
       <c r="E244" s="10" t="n">
-        <v>132.3</v>
+        <v>131.84</v>
       </c>
       <c r="F244" s="10" t="n">
-        <v>136.12</v>
+        <v>135.96</v>
       </c>
       <c r="G244" s="11" t="inlineStr">
         <is>
@@ -11450,20 +11450,20 @@
       </c>
       <c r="B245" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="10" t="n">
-        <v>69.45</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="D245" s="10" t="n">
-        <v>70.73999999999999</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="E245" s="10" t="n">
-        <v>71.86</v>
+        <v>70.69</v>
       </c>
       <c r="F245" s="10" t="n">
-        <v>77.81999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G245" s="11" t="inlineStr">
         <is>
@@ -11494,20 +11494,20 @@
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="10" t="n">
-        <v>734.05</v>
+        <v>717.05</v>
       </c>
       <c r="D246" s="10" t="n">
-        <v>751.66</v>
+        <v>748.36</v>
       </c>
       <c r="E246" s="10" t="n">
-        <v>759.9400000000001</v>
+        <v>758.26</v>
       </c>
       <c r="F246" s="10" t="n">
-        <v>762.96</v>
+        <v>762.67</v>
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -11538,20 +11538,20 @@
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="10" t="n">
-        <v>441.15</v>
+        <v>437.25</v>
       </c>
       <c r="D247" s="10" t="n">
-        <v>418.59</v>
+        <v>420.36</v>
       </c>
       <c r="E247" s="10" t="n">
-        <v>423.56</v>
+        <v>424.09</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>428.05</v>
+        <v>428.14</v>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
@@ -11582,20 +11582,20 @@
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="10" t="n">
-        <v>592.3</v>
+        <v>601</v>
       </c>
       <c r="D248" s="10" t="n">
-        <v>658.35</v>
+        <v>652.89</v>
       </c>
       <c r="E248" s="10" t="n">
-        <v>730.48</v>
+        <v>725.4</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>817.65</v>
+        <v>815.09</v>
       </c>
       <c r="G248" s="11" t="inlineStr">
         <is>
@@ -11626,20 +11626,20 @@
       </c>
       <c r="B249" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="10" t="n">
-        <v>4089.6</v>
+        <v>4023.4</v>
       </c>
       <c r="D249" s="10" t="n">
-        <v>4209.85</v>
+        <v>4192.1</v>
       </c>
       <c r="E249" s="10" t="n">
-        <v>4359.37</v>
+        <v>4346.2</v>
       </c>
       <c r="F249" s="10" t="n">
-        <v>4516.76</v>
+        <v>4509.35</v>
       </c>
       <c r="G249" s="11" t="inlineStr">
         <is>
@@ -11670,20 +11670,20 @@
       </c>
       <c r="B250" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="10" t="n">
-        <v>712.6</v>
+        <v>703.75</v>
       </c>
       <c r="D250" s="10" t="n">
-        <v>731.27</v>
+        <v>725.87</v>
       </c>
       <c r="E250" s="10" t="n">
-        <v>755.16</v>
+        <v>750.09</v>
       </c>
       <c r="F250" s="10" t="n">
-        <v>786.74</v>
+        <v>782.51</v>
       </c>
       <c r="G250" s="11" t="inlineStr">
         <is>
@@ -11714,20 +11714,20 @@
       </c>
       <c r="B251" s="10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="10" t="n">
-        <v>402.05</v>
+        <v>395.95</v>
       </c>
       <c r="D251" s="10" t="n">
-        <v>419.37</v>
+        <v>417.14</v>
       </c>
       <c r="E251" s="10" t="n">
-        <v>428.79</v>
+        <v>427.51</v>
       </c>
       <c r="F251" s="10" t="n">
-        <v>433.18</v>
+        <v>432.81</v>
       </c>
       <c r="G251" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 11-Sep-2026  14:50:00    |    Closing Price Date: 11-Sep-2026</t>
+          <t>Scan Run: 14-Sep-2026  16:45:59    |    Closing Price Date: 11-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
         <v>50</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>56</v>
+        <v>55.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>11-Sep-2026  14:50:00</t>
+          <t>14-Sep-2026  16:45:59</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 56.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BULLISH — 55.6% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 140 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 139 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         <v>266.89</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>297.16</v>
+        <v>298.07</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>322.94</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>324.9</v>
+        <v>325.06</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>5180.92</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>4243.3</v>
+        <v>4243.14</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>686.77</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>544.5</v>
+        <v>544.3099999999999</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>250.3</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>160.89</v>
+        <v>160.82</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>311.83</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>220.45</v>
+        <v>220.28</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>6884.5</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>5425.7</v>
+        <v>5429.33</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>308.85</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>258.68</v>
+        <v>258.94</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>5451.83</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4519.59</v>
+        <v>4519.81</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>171.32</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>165.2</v>
+        <v>165.14</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>2591.03</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2130.26</v>
+        <v>2125.07</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>577.96</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>571.8099999999999</v>
+        <v>572.54</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>1993.09</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1489.78</v>
+        <v>1489.93</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>3491.9</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>3222.73</v>
+        <v>3218.45</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>392.63</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>334.12</v>
+        <v>333.96</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>721.75</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>623.9299999999999</v>
+        <v>624.49</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>652.05</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>423.53</v>
+        <v>423.61</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>10.67</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>1990.89</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>1695.31</v>
+        <v>1694.07</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>229.68</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>208.05</v>
+        <v>208.26</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>66.39</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>59.82</v>
+        <v>60.04</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>166.43</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>149.84</v>
+        <v>150.01</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>190.34</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>189.71</v>
+        <v>190.9</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>548.84</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>541.3</v>
+        <v>541.33</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>323.86</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>263.35</v>
+        <v>263.26</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>1330.97</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1023.39</v>
+        <v>1023.03</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>341.46</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>301.87</v>
+        <v>301.91</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>513.87</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>466.74</v>
+        <v>466.42</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>1544.72</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>1239.25</v>
+        <v>1240.66</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>724.71</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>534.63</v>
+        <v>534.09</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>607.77</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>597.4400000000001</v>
+        <v>598.12</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>530.1799999999999</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>478.62</v>
+        <v>480.38</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>202.68</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>203.11</v>
+        <v>202.92</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>891.61</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>974.12</v>
+        <v>973.11</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>614.3099999999999</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>626.14</v>
+        <v>626.64</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>358.15</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>344.45</v>
+        <v>344.53</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>206.24</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>173.66</v>
+        <v>173.61</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>85.56999999999999</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>72.01000000000001</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>222.62</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>216.87</v>
+        <v>216.44</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>1680.17</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1384.91</v>
+        <v>1384.17</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>379.86</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>405.71</v>
+        <v>406.61</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>569.2</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>491.49</v>
+        <v>491.17</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>1127.42</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1028.25</v>
+        <v>1033.77</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>855.2</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>708.59</v>
+        <v>708.8</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>179.46</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>182.06</v>
+        <v>182.09</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>294.7</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>302.53</v>
+        <v>303.3</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>540.46</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>540.55</v>
+        <v>541.37</v>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>3631.17</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>2769.65</v>
+        <v>2769.94</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>539</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>529.05</v>
+        <v>532.1</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>2014.88</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>1842.93</v>
+        <v>1843.98</v>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>162.5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>132.72</v>
+        <v>132.94</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>547.08</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>497.73</v>
+        <v>498.92</v>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>1711.96</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1790.54</v>
+        <v>1792.84</v>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>163.06</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>170.88</v>
+        <v>171.23</v>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>3161.89</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>2685.28</v>
+        <v>2680.28</v>
       </c>
       <c r="G60" s="11" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>262.37</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>237.88</v>
+        <v>237.76</v>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>517.3</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>572.37</v>
+        <v>576.21</v>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>567.63</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>523.72</v>
+        <v>523.97</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>22.55</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>22.64</v>
+        <v>22.72</v>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>205.59</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>205.27</v>
+        <v>205.21</v>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>202.05</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>192.49</v>
+        <v>192.85</v>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>665.96</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>654.1</v>
+        <v>655.3200000000001</v>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>1668.38</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1608.07</v>
+        <v>1608.48</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>715.42</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>827.35</v>
+        <v>830.29</v>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>2002.09</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1629.86</v>
+        <v>1630.24</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
@@ -3804,10 +3804,10 @@
         <v>7047.94</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>6895.78</v>
+        <v>6895.77</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>5534.3</v>
+        <v>5527.77</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>45.62</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>41.61</v>
+        <v>41.65</v>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>508.18</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>581.03</v>
+        <v>586.39</v>
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>2222.36</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1786.18</v>
+        <v>1786.92</v>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>370.18</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>370.6</v>
+        <v>371.03</v>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>817.24</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>887.51</v>
+        <v>886.89</v>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>334.23</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>365.07</v>
+        <v>365.91</v>
       </c>
       <c r="G78" s="11" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>2551.92</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>2494.16</v>
+        <v>2496.76</v>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>200.89</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>213.59</v>
+        <v>213.64</v>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>155.08</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>154.23</v>
+        <v>154.33</v>
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>74.62</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>69.88</v>
+        <v>70.06</v>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>206.21</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>183</v>
+        <v>183.41</v>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>538.5700000000001</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>497.4</v>
+        <v>497.6</v>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>15.75</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>16.08</v>
+        <v>16.13</v>
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>901.47</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>955.22</v>
+        <v>952.83</v>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>2124.82</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1789.8</v>
+        <v>1789.46</v>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>657.24</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>623.04</v>
+        <v>623.95</v>
       </c>
       <c r="G88" s="13" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>1368.5</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>1309.58</v>
+        <v>1311.96</v>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>123.49</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>115.83</v>
+        <v>116.18</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>503.61</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>498.46</v>
+        <v>499.47</v>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>74.56999999999999</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>69.5</v>
+        <v>69.67</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>296.56</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>241.33</v>
+        <v>241.19</v>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>537.96</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>452.93</v>
+        <v>453.16</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>785.86</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>721.16</v>
+        <v>721.1900000000001</v>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>255.98</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>301.07</v>
+        <v>300.98</v>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>1870.77</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>1783.81</v>
+        <v>1786.17</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -5051,9 +5051,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
@@ -5083,7 +5083,7 @@
         <v>202.18</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>183.05</v>
+        <v>183.09</v>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>893.95</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>750.15</v>
+        <v>749.91</v>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>387.57</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>368.1</v>
+        <v>368.41</v>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>713.61</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>795.22</v>
+        <v>794.58</v>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>10347.36</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>9392.209999999999</v>
+        <v>9396.309999999999</v>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>762.8</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>715.9400000000001</v>
+        <v>716.51</v>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>92.83</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>85.54000000000001</v>
+        <v>85.62</v>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>1828</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>1608.94</v>
+        <v>1608.62</v>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>783.6</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>561.77</v>
+        <v>562.5599999999999</v>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>1055.73</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>997.54</v>
+        <v>997.6799999999999</v>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>737.41</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>881.99</v>
+        <v>881.53</v>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>415.25</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>344.5</v>
+        <v>344.95</v>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>846.77</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>786.38</v>
+        <v>785.87</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>397.79</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>397.76</v>
+        <v>397.52</v>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>216.02</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>243.72</v>
+        <v>243.83</v>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>86.73</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>95.97</v>
+        <v>95.8</v>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>903.24</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>967.72</v>
+        <v>967.4400000000001</v>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
@@ -5872,10 +5872,10 @@
         <v>3335.41</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>3217.28</v>
+        <v>3217.29</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>2883.76</v>
+        <v>2887.45</v>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>4345.25</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>3651.91</v>
+        <v>3652.57</v>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>698.83</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>758.3200000000001</v>
+        <v>759.3099999999999</v>
       </c>
       <c r="G120" s="11" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>343.34</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>400.19</v>
+        <v>400.54</v>
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>542.27</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>600.46</v>
+        <v>600.41</v>
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>580.8</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>502.23</v>
+        <v>502.72</v>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>1409.58</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1142.53</v>
+        <v>1142.48</v>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>224.06</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>240.71</v>
+        <v>240.49</v>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>395.33</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>372.58</v>
+        <v>372.77</v>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>795.47</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>733.28</v>
+        <v>733.77</v>
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>712.8099999999999</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>595.36</v>
+        <v>595.95</v>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>170.36</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>157.66</v>
+        <v>158.03</v>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>687.6900000000001</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>645.51</v>
+        <v>645.5700000000001</v>
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>436.6</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>472.26</v>
+        <v>473.14</v>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>788.3099999999999</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>768.74</v>
+        <v>768.14</v>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>360.18</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>367.9</v>
+        <v>369.33</v>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>2200.6</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2172.2</v>
+        <v>2173.9</v>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>605.96</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>554.54</v>
+        <v>554.73</v>
       </c>
       <c r="G139" s="13" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>336.91</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>348.14</v>
+        <v>349.72</v>
       </c>
       <c r="G140" s="11" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>127.32</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>122.7</v>
+        <v>122.85</v>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>220.8</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>215.35</v>
+        <v>215.39</v>
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>298.07</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>283.93</v>
+        <v>284.26</v>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>121.84</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>129.78</v>
+        <v>129.95</v>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>155.66</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>148.11</v>
+        <v>148.47</v>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>461.69</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>523.34</v>
+        <v>523.73</v>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>97.08</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>103.85</v>
+        <v>103.93</v>
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>2507.38</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>2511.66</v>
+        <v>2510.09</v>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>895.49</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>792.95</v>
+        <v>794</v>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>1782.32</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>1551.74</v>
+        <v>1548.83</v>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>1505.31</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1276.36</v>
+        <v>1276.34</v>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>11173.94</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10151</v>
+        <v>10150.52</v>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>2175.27</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>2229.26</v>
+        <v>2235.93</v>
       </c>
       <c r="G157" s="13" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>1104.89</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>917.8</v>
+        <v>916.24</v>
       </c>
       <c r="G158" s="13" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>686.85</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>648.96</v>
+        <v>649.9299999999999</v>
       </c>
       <c r="G159" s="13" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>513.13</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>551.95</v>
+        <v>552.83</v>
       </c>
       <c r="G160" s="11" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>110.41</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>115.21</v>
+        <v>115.45</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>423.01</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>397.3</v>
+        <v>397.21</v>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>155.83</v>
       </c>
       <c r="F163" s="10" t="n">
-        <v>163.82</v>
+        <v>163.81</v>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>551.0599999999999</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>636.55</v>
+        <v>637.5</v>
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>672.12</v>
       </c>
       <c r="F165" s="10" t="n">
-        <v>566.66</v>
+        <v>566.77</v>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>203.13</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>229.56</v>
+        <v>229.45</v>
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>412.78</v>
       </c>
       <c r="F169" s="10" t="n">
-        <v>405.07</v>
+        <v>404.86</v>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>764.54</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>643.9400000000001</v>
+        <v>644.2</v>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>452.14</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>460.86</v>
+        <v>460.88</v>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>1101.43</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>1042.58</v>
+        <v>1042.97</v>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>209.58</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>226.71</v>
+        <v>227.88</v>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>521.9400000000001</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>516.41</v>
+        <v>518.6799999999999</v>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>554.1900000000001</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>509.02</v>
+        <v>508.63</v>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>158.17</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>156.92</v>
+        <v>156.99</v>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>196.08</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>246.98</v>
+        <v>247.71</v>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>1302.22</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>1082.96</v>
+        <v>1083.61</v>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>246.05</v>
       </c>
       <c r="F179" s="10" t="n">
-        <v>241.59</v>
+        <v>241.91</v>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>29.28</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>34.9</v>
+        <v>34.87</v>
       </c>
       <c r="G181" s="11" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>8.140000000000001</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>9.119999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="G182" s="11" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>302.94</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>351.69</v>
+        <v>352.09</v>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>792.73</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>897.5700000000001</v>
+        <v>895.1</v>
       </c>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8864,10 +8864,10 @@
         <v>13360.91</v>
       </c>
       <c r="E186" s="10" t="n">
-        <v>13217.9</v>
+        <v>13217.91</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>13258.38</v>
+        <v>13302.6</v>
       </c>
       <c r="G186" s="11" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>336.57</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>329.12</v>
+        <v>329.63</v>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>61.05</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>66.08</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>1287.77</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>1109.33</v>
+        <v>1108.98</v>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>901.47</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>984.97</v>
+        <v>986.53</v>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>800.03</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>783.24</v>
+        <v>784.55</v>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>785.37</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>751.25</v>
+        <v>750.41</v>
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>126.24</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>139.13</v>
+        <v>139.45</v>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>303.59</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>338.21</v>
+        <v>339.41</v>
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>2719.75</v>
       </c>
       <c r="F196" s="10" t="n">
-        <v>2608.69</v>
+        <v>2612.42</v>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>653</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>562.21</v>
+        <v>563.02</v>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>358.04</v>
       </c>
       <c r="F199" s="10" t="n">
-        <v>421.58</v>
+        <v>421.96</v>
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>1906.5</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>2033.65</v>
+        <v>2034.39</v>
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>175.93</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>191.75</v>
+        <v>191.42</v>
       </c>
       <c r="G201" s="11" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>125.14</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>126.86</v>
+        <v>126.89</v>
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>200.61</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>209.14</v>
+        <v>209.19</v>
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>830.39</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>830.63</v>
+        <v>830.99</v>
       </c>
       <c r="G204" s="11" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>118.92</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>137.45</v>
+        <v>137.75</v>
       </c>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>417.8</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>440.51</v>
+        <v>442.29</v>
       </c>
       <c r="G207" s="11" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>126.22</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>136.13</v>
+        <v>137.24</v>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>160.08</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>170.83</v>
+        <v>170.9</v>
       </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>105.88</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>114.52</v>
+        <v>114.26</v>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>1325.73</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>1318.03</v>
+        <v>1318.29</v>
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>132.39</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>155.54</v>
+        <v>155</v>
       </c>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>310.66</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>317.89</v>
+        <v>317.98</v>
       </c>
       <c r="G213" s="11" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>275.39</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>351.83</v>
+        <v>353.43</v>
       </c>
       <c r="G214" s="13" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>808.95</v>
       </c>
       <c r="F215" s="10" t="n">
-        <v>802.21</v>
+        <v>802.5599999999999</v>
       </c>
       <c r="G215" s="11" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>997.6</v>
       </c>
       <c r="F216" s="10" t="n">
-        <v>955.91</v>
+        <v>956.87</v>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>76.51000000000001</v>
       </c>
       <c r="F217" s="10" t="n">
-        <v>79.04000000000001</v>
+        <v>79.23</v>
       </c>
       <c r="G217" s="11" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>1068.41</v>
       </c>
       <c r="F219" s="10" t="n">
-        <v>1120.56</v>
+        <v>1122.25</v>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>241.57</v>
       </c>
       <c r="F220" s="10" t="n">
-        <v>227.41</v>
+        <v>227.47</v>
       </c>
       <c r="G220" s="11" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>1556.01</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>1920.18</v>
+        <v>1917.28</v>
       </c>
       <c r="G221" s="11" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>626.03</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>626.53</v>
+        <v>626.14</v>
       </c>
       <c r="G222" s="11" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>23.68</v>
       </c>
       <c r="F223" s="10" t="n">
-        <v>25.06</v>
+        <v>25.07</v>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>598.62</v>
       </c>
       <c r="F224" s="10" t="n">
-        <v>596.36</v>
+        <v>596.52</v>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>435.18</v>
       </c>
       <c r="F225" s="10" t="n">
-        <v>484.78</v>
+        <v>483.92</v>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>228.22</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>244.83</v>
+        <v>245.16</v>
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>499.84</v>
       </c>
       <c r="F227" s="10" t="n">
-        <v>472.75</v>
+        <v>473.98</v>
       </c>
       <c r="G227" s="11" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>111.87</v>
       </c>
       <c r="F228" s="10" t="n">
-        <v>122.13</v>
+        <v>122.2</v>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>216.19</v>
       </c>
       <c r="F229" s="10" t="n">
-        <v>224.7</v>
+        <v>226.7</v>
       </c>
       <c r="G229" s="11" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>1909.31</v>
       </c>
       <c r="F230" s="10" t="n">
-        <v>1773.47</v>
+        <v>1776.61</v>
       </c>
       <c r="G230" s="11" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>624.6799999999999</v>
       </c>
       <c r="F231" s="10" t="n">
-        <v>601.8099999999999</v>
+        <v>602.37</v>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>5870.72</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>5744.62</v>
+        <v>5763.13</v>
       </c>
       <c r="G233" s="11" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>339.77</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>386.65</v>
+        <v>387.01</v>
       </c>
       <c r="G234" s="11" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>30.65</v>
       </c>
       <c r="F235" s="10" t="n">
-        <v>35.36</v>
+        <v>35.45</v>
       </c>
       <c r="G235" s="11" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>198.48</v>
       </c>
       <c r="F236" s="10" t="n">
-        <v>212.27</v>
+        <v>212.18</v>
       </c>
       <c r="G236" s="13" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>129.25</v>
       </c>
       <c r="F237" s="10" t="n">
-        <v>123.85</v>
+        <v>123.84</v>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>10.63</v>
       </c>
       <c r="F238" s="10" t="n">
-        <v>13.29</v>
+        <v>13.31</v>
       </c>
       <c r="G238" s="11" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>108.14</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>120.98</v>
+        <v>121.3</v>
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>306.68</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>329.22</v>
+        <v>329.01</v>
       </c>
       <c r="G240" s="11" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>521.5700000000001</v>
       </c>
       <c r="F241" s="10" t="n">
-        <v>623.11</v>
+        <v>624.77</v>
       </c>
       <c r="G241" s="11" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>67.28</v>
       </c>
       <c r="F242" s="10" t="n">
-        <v>72.43000000000001</v>
+        <v>72.45</v>
       </c>
       <c r="G242" s="11" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>1536.19</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>1702.79</v>
+        <v>1700.7</v>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>131.84</v>
       </c>
       <c r="F244" s="10" t="n">
-        <v>135.96</v>
+        <v>136.26</v>
       </c>
       <c r="G244" s="11" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>70.69</v>
       </c>
       <c r="F245" s="10" t="n">
-        <v>76.59999999999999</v>
+        <v>76.61</v>
       </c>
       <c r="G245" s="11" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>758.26</v>
       </c>
       <c r="F246" s="10" t="n">
-        <v>762.67</v>
+        <v>762.11</v>
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>424.09</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>428.14</v>
+        <v>429.1</v>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>725.4</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>815.09</v>
+        <v>815.55</v>
       </c>
       <c r="G248" s="11" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>4346.2</v>
       </c>
       <c r="F249" s="10" t="n">
-        <v>4509.35</v>
+        <v>4503.94</v>
       </c>
       <c r="G249" s="11" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>750.09</v>
       </c>
       <c r="F250" s="10" t="n">
-        <v>782.51</v>
+        <v>783.46</v>
       </c>
       <c r="G250" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 15-Sep-2026  15:26:11    |    Closing Price Date: 15-Sep-2026</t>
+          <t>Scan Run: 16-Sep-2026  15:19:14    |    Closing Price Date: 16-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>22</v>
+        <v>22.8</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>36.4</v>
+        <v>34</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50</v>
+        <v>51.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>15-Sep-2026  15:26:11</t>
+          <t>16-Sep-2026  15:19:14</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.8% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 36.4% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 51.6% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 55 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 57 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 91 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 85 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 125 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 129 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>238.54</v>
+        <v>237.36</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>254.68</v>
+        <v>252.14</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>265.78</v>
+        <v>263.87</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>297.48</v>
+        <v>296.36</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,34 +805,34 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>321.9</v>
+        <v>327.15</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>329.64</v>
+        <v>329.4</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>322.89</v>
+        <v>323.06</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>325.03</v>
+        <v>325.05</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J3" s="13" t="inlineStr">
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>6254</v>
+        <v>5971.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>5807.8</v>
+        <v>5887.49</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5223</v>
+        <v>5303.11</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>4263.15</v>
+        <v>4302.97</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>725.5</v>
+        <v>696</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>738.86</v>
+        <v>739.8200000000001</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>688.29</v>
+        <v>692.87</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>546.11</v>
+        <v>550.15</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>284.4</v>
+        <v>280</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>276.7</v>
+        <v>277.34</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>251.63</v>
+        <v>253.82</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>162.04</v>
+        <v>164.38</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>387.5</v>
+        <v>394.75</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>346.04</v>
+        <v>352.81</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>314.8</v>
+        <v>320</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>221.94</v>
+        <v>225.11</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1025,29 +1025,29 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>6947</v>
+        <v>6792</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>7076.5</v>
+        <v>7066.74</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>6886.95</v>
+        <v>6898.72</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5444.43</v>
+        <v>5476.2</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
@@ -1069,24 +1069,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>828.55</v>
+        <v>856</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>834.29</v>
+        <v>840.6799999999999</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>771.88</v>
+        <v>779.55</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>623.0700000000001</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>628.01</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>315.95</v>
+        <v>318.2</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>325.76</v>
+        <v>320.82</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>309.13</v>
+        <v>305.69</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>259.51</v>
+        <v>256.83</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4912</v>
+        <v>4927</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>5308.92</v>
+        <v>5255.03</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>5430.66</v>
+        <v>5399.11</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>4523.71</v>
+        <v>4533.64</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,29 +1201,29 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>167.83</v>
+        <v>171.73</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>173.35</v>
+        <v>173.33</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>171.19</v>
+        <v>171.36</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>165.16</v>
+        <v>165.33</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -1245,29 +1245,29 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2704.9</v>
+        <v>2581.7</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2761.66</v>
+        <v>2750.87</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>2595.49</v>
+        <v>2604.29</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>2130.84</v>
+        <v>2142.39</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>611.9</v>
+        <v>619.05</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>590.92</v>
+        <v>593.59</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>579.29</v>
+        <v>580.85</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>572.9400000000001</v>
+        <v>573.39</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,24 +1333,24 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2160.7</v>
+        <v>2216.1</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>2179.45</v>
+        <v>2182.94</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1999.66</v>
+        <v>2008.15</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1496.61</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1503.77</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
@@ -1377,24 +1377,24 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>3452.2</v>
+        <v>3480.7</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>3474.05</v>
+        <v>3474.68</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>3490.34</v>
+        <v>3489.96</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3220.77</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3223.36</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>386.6</v>
+        <v>370.35</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>397.74</v>
+        <v>396.95</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>392.39</v>
+        <v>392.6</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>334.48</v>
+        <v>335.7</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>740.75</v>
+        <v>744.8</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>760.5700000000001</v>
+        <v>759.0700000000001</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>722.49</v>
+        <v>723.37</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>625.65</v>
+        <v>626.84</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>852.55</v>
+        <v>818.05</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>746.5</v>
+        <v>765.95</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>659.91</v>
+        <v>675</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>427.87</v>
+        <v>436.38</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>213.54</v>
+        <v>216.4</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>190.9</v>
+        <v>194.95</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>177.46</v>
+        <v>180.19</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>161.73</v>
+        <v>162.75</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>12.89</v>
+        <v>12.64</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>11.87</v>
+        <v>12.1</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>10.76</v>
+        <v>10.94</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10.23</v>
+        <v>10.29</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>221.52</v>
+        <v>220.68</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>238.53</v>
+        <v>236.83</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>235.82</v>
+        <v>235.22</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>197.41</v>
+        <v>197.65</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,24 +1685,24 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>2103.4</v>
+        <v>2055.8</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>2066.43</v>
+        <v>2082.21</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1995.3</v>
+        <v>2008.06</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1698.14</v>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1707.39</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>218.69</v>
+        <v>218.43</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>232.51</v>
+        <v>231.17</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>229.25</v>
+        <v>228.83</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>208.36</v>
+        <v>208.46</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>64.06999999999999</v>
+        <v>64.83</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>66.76000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>66.3</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>60.08</v>
+        <v>60.13</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>158.72</v>
+        <v>157.16</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>167.92</v>
+        <v>166.44</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>166.13</v>
+        <v>165.65</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>150.1</v>
+        <v>150.3</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>176.3</v>
+        <v>173.53</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>187.25</v>
+        <v>185.94</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>189.79</v>
+        <v>189.15</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>190.75</v>
+        <v>190.58</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>490.55</v>
+        <v>487.55</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>530.88</v>
+        <v>524.23</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>546.5599999999999</v>
+        <v>542.58</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>540.83</v>
+        <v>539.92</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>342.1</v>
+        <v>342.4</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>348.74</v>
+        <v>348.14</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>324.57</v>
+        <v>325.27</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>264.04</v>
+        <v>264.82</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,29 +1993,29 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1339.2</v>
+        <v>1318.8</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>1415.59</v>
+        <v>1407.3</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>1331.3</v>
+        <v>1334.59</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1026.17</v>
+        <v>1033.11</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>357.4</v>
+        <v>351.15</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>361.45</v>
+        <v>360.47</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>342.08</v>
+        <v>342.44</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>302.46</v>
+        <v>302.95</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,29 +2081,29 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>510.75</v>
+        <v>526.55</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>537.36</v>
+        <v>534.03</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>513.75</v>
+        <v>513.62</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>466.86</v>
+        <v>467.11</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1583.1</v>
+        <v>1603.1</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1629.39</v>
+        <v>1630.04</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>1546.22</v>
+        <v>1553.16</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1244.07</v>
+        <v>1251.87</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>789.4</v>
+        <v>792.6</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>791.62</v>
+        <v>794.48</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>727.24</v>
+        <v>733.52</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>536.63</v>
+        <v>542.04</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,24 +2213,24 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>611.6</v>
+        <v>608.65</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>609.76</v>
+        <v>609.9299999999999</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>607.92</v>
+        <v>608.15</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>598.25</v>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>598.5</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>488.65</v>
+        <v>506.6</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>533.92</v>
+        <v>531.3200000000001</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>528.55</v>
+        <v>527.6900000000001</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>480.46</v>
+        <v>480.72</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>181.98</v>
+        <v>180.6</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>197.81</v>
+        <v>196.17</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>201.87</v>
+        <v>201.04</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>202.71</v>
+        <v>202.49</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>771.95</v>
+        <v>770.35</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>825.53</v>
+        <v>817.74</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>886.91</v>
+        <v>878.98</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>971.11</v>
+        <v>967.41</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>518.4</v>
+        <v>515.7</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>568.86</v>
+        <v>561.36</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>610.54</v>
+        <v>604.24</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>625.5599999999999</v>
+        <v>623.65</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>336.4</v>
+        <v>332.25</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>354.49</v>
+        <v>352.37</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>357.3</v>
+        <v>356.32</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>344.45</v>
+        <v>344.33</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>196.74</v>
+        <v>199.29</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>209.67</v>
+        <v>209.07</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>205.86</v>
+        <v>205.96</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>173.84</v>
+        <v>174.5</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>79.70999999999999</v>
+        <v>80.02</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>85.08</v>
+        <v>84.37</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>85.34</v>
+        <v>85.03</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>72.06999999999999</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,29 +2565,29 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>223.4</v>
+        <v>220.16</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>234.24</v>
+        <v>233.46</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>222.65</v>
+        <v>223.27</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>216.51</v>
+        <v>216.8</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1593.8</v>
+        <v>1621.9</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1692.22</v>
+        <v>1683.81</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1676.78</v>
+        <v>1674.65</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1386.26</v>
+        <v>1391.49</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>325.6</v>
+        <v>327.45</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>367.73</v>
+        <v>360.79</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>377.74</v>
+        <v>374.04</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>405.8</v>
+        <v>404.3</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>544.45</v>
+        <v>541.3</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>575.5700000000001</v>
+        <v>572.3099999999999</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>568.23</v>
+        <v>567.1799999999999</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>491.7</v>
+        <v>492.19</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>163.46</v>
+        <v>163.88</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>169.12</v>
+        <v>168.4</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>175.95</v>
+        <v>175.13</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>212.48</v>
+        <v>211.55</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1183.2</v>
+        <v>1198.7</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1210.52</v>
+        <v>1209.39</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1129.61</v>
+        <v>1132.32</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1035.26</v>
+        <v>1036.89</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,24 +2829,24 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>868.35</v>
+        <v>904.2</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>895.9400000000001</v>
+        <v>897.66</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>855.71</v>
+        <v>859.63</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>710.38</v>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>714.28</v>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>173.22</v>
+        <v>173.11</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>175.15</v>
+        <v>174.95</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>179.21</v>
+        <v>178.97</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>182</v>
+        <v>181.92</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>265.85</v>
+        <v>260.9</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>282.15</v>
+        <v>279.32</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>293.57</v>
+        <v>291.52</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>302.93</v>
+        <v>302.22</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>461.3</v>
+        <v>446</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>512.8200000000001</v>
+        <v>504.7</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>537.36</v>
+        <v>532.15</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>540.5700000000001</v>
+        <v>539.1799999999999</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,24 +3005,24 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>3871.7</v>
+        <v>3971.2</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>3895.1</v>
+        <v>3920.46</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>3640.6</v>
+        <v>3671.62</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2780.9</v>
-      </c>
-      <c r="G53" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2806.01</v>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H53" s="14" t="inlineStr">
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>556.1</v>
+        <v>550.45</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>557.49</v>
+        <v>556.8200000000001</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>539.67</v>
+        <v>540.1</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>532.34</v>
+        <v>532.52</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>1825.9</v>
+        <v>1852.9</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>1975.87</v>
+        <v>1964.16</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>2007.47</v>
+        <v>2001.41</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1843.8</v>
+        <v>1843.89</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3118,9 +3118,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I55" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J55" s="13" t="inlineStr">
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>185.06</v>
+        <v>180.93</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>179.67</v>
+        <v>179.79</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>163.39</v>
+        <v>164.07</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>133.45</v>
+        <v>133.93</v>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>534.15</v>
+        <v>522.65</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>559.84</v>
+        <v>555.4400000000001</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>546.5700000000001</v>
+        <v>545.8</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>499.27</v>
+        <v>500.02</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1652.1</v>
+        <v>1633.1</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>1700.58</v>
+        <v>1687.96</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>1709.62</v>
+        <v>1703.52</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1791.44</v>
+        <v>1788.24</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3269,24 +3269,24 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>152.73</v>
+        <v>160.27</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>157.88</v>
+        <v>158</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>162.66</v>
+        <v>162.35</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>171.05</v>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>170.8</v>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -3313,29 +3313,29 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>3181.8</v>
+        <v>3097.3</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>3285.12</v>
+        <v>3265.95</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>3162.67</v>
+        <v>3164.36</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2685.27</v>
+        <v>2695.22</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H60" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>246.9</v>
+        <v>238.85</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>261.59</v>
+        <v>258.99</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>261.76</v>
+        <v>260.69</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>237.85</v>
+        <v>238.05</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>481.9</v>
+        <v>480.7</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>504.37</v>
+        <v>501.09</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>515.92</v>
+        <v>513.6799999999999</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>575.27</v>
+        <v>573.52</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,24 +3445,24 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>572.5</v>
+        <v>580.85</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>578.92</v>
+        <v>579.11</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>567.8200000000001</v>
+        <v>568.33</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>524.45</v>
-      </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>525.01</v>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>21.32</v>
+        <v>21.04</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>22.68</v>
+        <v>22.51</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>22.51</v>
+        <v>22.45</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>22.7</v>
+        <v>22.69</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>196.91</v>
+        <v>194.87</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>201.6</v>
+        <v>201.35</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>205.25</v>
+        <v>204.9</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>205.13</v>
+        <v>205.05</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>187.13</v>
+        <v>185.64</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>195.64</v>
+        <v>194.35</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>201.47</v>
+        <v>200.49</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>192.79</v>
+        <v>192.71</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3621,29 +3621,29 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>661.85</v>
+        <v>673.7</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>680.0599999999999</v>
+        <v>679.46</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>665.8</v>
+        <v>666.11</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>655.39</v>
+        <v>655.5700000000001</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H67" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr">
@@ -3665,24 +3665,24 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>1717.7</v>
+        <v>1684.5</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>1704.03</v>
+        <v>1702.17</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1670.32</v>
+        <v>1670.87</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1609.57</v>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1610.31</v>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H68" s="14" t="inlineStr">
@@ -3709,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>672.65</v>
+        <v>667.75</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>689.13</v>
+        <v>687.09</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>713.74</v>
+        <v>711.9400000000001</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>828.72</v>
+        <v>827.12</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>1992.8</v>
+        <v>1978.9</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>2111.51</v>
+        <v>2098.88</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>2001.73</v>
+        <v>2000.83</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1633.85</v>
+        <v>1637.28</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>6603.5</v>
+        <v>6431</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>7005.61</v>
+        <v>6939.37</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>6884.31</v>
+        <v>6854.52</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>5538.47</v>
+        <v>5537.39</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>45</v>
+        <v>45.19</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>46.03</v>
+        <v>45.96</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>45.59</v>
+        <v>45.6</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>41.69</v>
+        <v>41.77</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>474.2</v>
+        <v>463.9</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>488.11</v>
+        <v>485.8</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>506.85</v>
+        <v>505.17</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>585.27</v>
+        <v>584.0599999999999</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,24 +3929,24 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>148.61</v>
+        <v>145.61</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>146.49</v>
+        <v>146.4</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>139.05</v>
+        <v>139.31</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>150.38</v>
-      </c>
-      <c r="G74" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>150.34</v>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H74" s="14" t="inlineStr">
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>2105.7</v>
+        <v>2149.8</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>2312.62</v>
+        <v>2292.6</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2217.78</v>
+        <v>2217.08</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1790.09</v>
+        <v>1798.45</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>317.15</v>
+        <v>311.4</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>352.72</v>
+        <v>348.78</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>368.1</v>
+        <v>365.88</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>370.5</v>
+        <v>369.91</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>753.4</v>
+        <v>745.5</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>781.15</v>
+        <v>777.75</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>814.73</v>
+        <v>812.02</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>885.5599999999999</v>
+        <v>884.16</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,24 +4105,24 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>296.35</v>
+        <v>328.75</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>322.05</v>
+        <v>321.2</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>332.74</v>
+        <v>331.55</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>365.22</v>
-      </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>364.27</v>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>2691.4</v>
+        <v>2695</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>2643.36</v>
+        <v>2648.28</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>2557.39</v>
+        <v>2562.79</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2498.69</v>
+        <v>2500.65</v>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>174.3</v>
+        <v>177.94</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>189.7</v>
+        <v>187.72</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>199.84</v>
+        <v>198.24</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>213.25</v>
+        <v>212.57</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>161.18</v>
+        <v>162.24</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>159.63</v>
+        <v>159.88</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>155.32</v>
+        <v>155.59</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>154.4</v>
+        <v>154.48</v>
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>71.34999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>73.73999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>74.48999999999999</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>70.06999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>188</v>
+        <v>185.59</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>199.85</v>
+        <v>198.1</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>205.49</v>
+        <v>204.34</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>183.45</v>
+        <v>183.6</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>540.6</v>
+        <v>539.75</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>558.33</v>
+        <v>556.73</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>538.65</v>
+        <v>539.5599999999999</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>498.03</v>
+        <v>499.07</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
@@ -4413,24 +4413,24 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>15.69</v>
+        <v>15.32</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>15.59</v>
+        <v>15.57</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>15.74</v>
+        <v>15.73</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>16.13</v>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>16.12</v>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>806.55</v>
+        <v>801.05</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>858.88</v>
+        <v>853.37</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>897.74</v>
+        <v>893.95</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>951.37</v>
+        <v>949.87</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>2310.3</v>
+        <v>2302.4</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>2221.98</v>
+        <v>2229.64</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>2132.09</v>
+        <v>2138.77</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1794.64</v>
+        <v>1799.69</v>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
@@ -4545,29 +4545,29 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>659.15</v>
+        <v>654.55</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>654.22</v>
+        <v>654.86</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>657.3200000000001</v>
+        <v>657.36</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>624.3</v>
-      </c>
-      <c r="G88" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H88" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>624.97</v>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>1220.8</v>
+        <v>1246.1</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>1323.49</v>
+        <v>1316.12</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>1362.71</v>
+        <v>1358.13</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1311.05</v>
+        <v>1310.4</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4633,20 +4633,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>127.4</v>
+        <v>126.74</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>128.3</v>
+        <v>128.46</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>123.64</v>
+        <v>124.09</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>116.29</v>
+        <v>116.55</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>566.65</v>
+        <v>554.7</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>551.3200000000001</v>
+        <v>551.64</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>506.08</v>
+        <v>507.99</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>500.14</v>
+        <v>500.69</v>
       </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
@@ -4721,24 +4721,24 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>1815.6</v>
+        <v>1766.7</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>1771.54</v>
+        <v>1771.08</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>1636.29</v>
+        <v>1641.4</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1190.64</v>
-      </c>
-      <c r="G92" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1196.37</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr">
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>67.64</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>72.70999999999999</v>
+        <v>72.16</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>74.3</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>69.65000000000001</v>
+        <v>69.62</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>312.85</v>
+        <v>316.45</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>320.09</v>
+        <v>320.41</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>297.2</v>
+        <v>299.14</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>241.91</v>
+        <v>243.51</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>275.45</v>
+        <v>269.85</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>290.73</v>
+        <v>288.74</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>319.84</v>
+        <v>317.88</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>407.77</v>
+        <v>406.4</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>550.6</v>
+        <v>548.05</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>555.16</v>
+        <v>554.48</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>538.45</v>
+        <v>538.83</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>454.13</v>
+        <v>455.06</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4941,24 +4941,24 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>745.8</v>
+        <v>763.25</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>757.42</v>
+        <v>761.26</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>784.29</v>
+        <v>784</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>721.4400000000001</v>
-      </c>
-      <c r="G97" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>722.63</v>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>222.91</v>
+        <v>232.39</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>239.94</v>
+        <v>237.87</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>254.69</v>
+        <v>252.67</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>300.2</v>
+        <v>298.78</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1728</v>
+        <v>1724.7</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1858.46</v>
+        <v>1845.72</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1865.17</v>
+        <v>1859.66</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1785.59</v>
+        <v>1784.98</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5073,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>221.89</v>
+        <v>219.94</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>215.38</v>
+        <v>216.73</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>202.95</v>
+        <v>204.5</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>183.48</v>
+        <v>184.26</v>
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>878.65</v>
+        <v>860.95</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>896.89</v>
+        <v>893.46</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>893.35</v>
+        <v>892.08</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>751.1900000000001</v>
+        <v>752.28</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>402.1</v>
+        <v>417.35</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>401.22</v>
+        <v>402.76</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>388.14</v>
+        <v>389.29</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>368.75</v>
+        <v>369.23</v>
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>656.3</v>
+        <v>656.1</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>672.84</v>
+        <v>671.25</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>711.36</v>
+        <v>709.1900000000001</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>793.21</v>
+        <v>791.84</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>10596</v>
+        <v>10513</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>10802.17</v>
+        <v>10774.63</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>10357.11</v>
+        <v>10363.22</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>9408.24</v>
+        <v>9419.24</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>698.15</v>
+        <v>695.2</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>735.85</v>
+        <v>731.98</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>760.26</v>
+        <v>757.71</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>716.33</v>
+        <v>716.12</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>88.63</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>93.06999999999999</v>
+        <v>92.25</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>92.66</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>85.65000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,24 +5381,24 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>1991.3</v>
+        <v>1941.8</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>1949.95</v>
+        <v>1952.93</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>1834.41</v>
+        <v>1844.62</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1612.43</v>
-      </c>
-      <c r="G107" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1619.46</v>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H107" s="14" t="inlineStr">
@@ -5425,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>911.9</v>
+        <v>928.05</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>895.5599999999999</v>
+        <v>903.91</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>788.63</v>
+        <v>800.53</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>566.03</v>
+        <v>573.52</v>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
@@ -5469,20 +5469,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>1150.6</v>
+        <v>1183.9</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1091.83</v>
+        <v>1108.22</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>1059.45</v>
+        <v>1068.95</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>999.2</v>
+        <v>1002.85</v>
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
@@ -5513,24 +5513,24 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>698.65</v>
+        <v>688</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>696.0599999999999</v>
+        <v>695.29</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>735.89</v>
+        <v>734.02</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>879.71</v>
-      </c>
-      <c r="G110" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>877.8</v>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
@@ -5557,20 +5557,20 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>427.1</v>
+        <v>431.95</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>434.48</v>
+        <v>434.86</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>415.72</v>
+        <v>417.37</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>345.77</v>
+        <v>347.58</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5601,20 +5601,20 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>874.95</v>
+        <v>877.85</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>853.9</v>
+        <v>856.1799999999999</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>847.87</v>
+        <v>849.05</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>786.75</v>
+        <v>787.66</v>
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>432</v>
+        <v>426.25</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>406.64</v>
+        <v>411.76</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>399.13</v>
+        <v>401.93</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>397.87</v>
+        <v>398.62</v>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>200.82</v>
+        <v>202.65</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>207.97</v>
+        <v>207.46</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>215.42</v>
+        <v>214.92</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>243.4</v>
+        <v>242.99</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>72.75</v>
+        <v>72.11</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>78.7</v>
+        <v>77.59</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>86.18000000000001</v>
+        <v>84.98</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>95.56999999999999</v>
+        <v>94.84</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>280.2</v>
+        <v>266.2</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>665.87</v>
+        <v>627.8099999999999</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>878.8</v>
+        <v>854.78</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>960.6</v>
+        <v>953.6900000000001</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>355.1</v>
+        <v>374.65</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>333.72</v>
+        <v>337.62</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>311.97</v>
+        <v>314.43</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>315.16</v>
+        <v>315.76</v>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>3251.5</v>
+        <v>3326.1</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>3327.42</v>
+        <v>3327.29</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>3218.63</v>
+        <v>3222.84</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>2891.07</v>
+        <v>2895.4</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>4275.4</v>
+        <v>4309.3</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>4474.72</v>
+        <v>4458.97</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>4342.51</v>
+        <v>4341.21</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>3658.76</v>
+        <v>3665.24</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>647.25</v>
+        <v>661.6</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>667.52</v>
+        <v>666.96</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>696.8099999999999</v>
+        <v>695.4299999999999</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>758.2</v>
+        <v>757.24</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>277.15</v>
+        <v>276.35</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>308.09</v>
+        <v>302.75</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>340.74</v>
+        <v>335.98</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>399.31</v>
+        <v>396.93</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>500.25</v>
+        <v>497.05</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>515.61</v>
+        <v>513.42</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>540.62</v>
+        <v>537.8099999999999</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>599.41</v>
+        <v>597.53</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>604.7</v>
+        <v>617.9</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>617.87</v>
+        <v>618.29</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>581.73</v>
+        <v>584.74</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>503.74</v>
+        <v>506.06</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -6129,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1514</v>
+        <v>1438.3</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1526.69</v>
+        <v>1523.38</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1413.68</v>
+        <v>1421.3</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1146.18</v>
+        <v>1153.49</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,20 +6173,20 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>212.9</v>
+        <v>211.47</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>219.95</v>
+        <v>219.15</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>223.63</v>
+        <v>223.15</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>240.22</v>
+        <v>239.93</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>472.2</v>
+        <v>452.05</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>486.11</v>
+        <v>482.87</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>500.28</v>
+        <v>498.39</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>537</v>
+        <v>536.16</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6261,29 +6261,29 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>397.15</v>
+        <v>394.85</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>414.23</v>
+        <v>412.39</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>395.4</v>
+        <v>395.38</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>373.01</v>
+        <v>373.23</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H127" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I127" s="14" t="inlineStr">
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>789.85</v>
+        <v>786.4</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>819.55</v>
+        <v>816.39</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>795.25</v>
+        <v>794.9</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>734.33</v>
+        <v>734.84</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>765.65</v>
+        <v>772</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>753.0700000000001</v>
+        <v>756.79</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>714.88</v>
+        <v>719.42</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>597.64</v>
+        <v>601.13</v>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>197.2</v>
+        <v>196.05</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>179.18</v>
+        <v>182.48</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>171.42</v>
+        <v>173.42</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>158.42</v>
+        <v>159.19</v>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
@@ -6437,20 +6437,20 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>678.3</v>
+        <v>674.15</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>701.4299999999999</v>
+        <v>698.83</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>687.3200000000001</v>
+        <v>686.8</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>645.9</v>
+        <v>646.1799999999999</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>423.15</v>
+        <v>418.85</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>432.72</v>
+        <v>431.4</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>436.07</v>
+        <v>435.39</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>472.64</v>
+        <v>472.1</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>743.3</v>
+        <v>725.35</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>781.58</v>
+        <v>776.22</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>786.54</v>
+        <v>784.04</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>767.9</v>
+        <v>767.64</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6569,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>1660</v>
+        <v>1655</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>1784.29</v>
+        <v>1771.98</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>1740.69</v>
+        <v>1737.33</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1462.16</v>
+        <v>1464.08</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>232.4</v>
+        <v>228.55</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>249.03</v>
+        <v>247.08</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>252.8</v>
+        <v>251.85</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>260.32</v>
+        <v>260</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>95.23</v>
+        <v>95.83</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>96.93000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>89.44</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>76.42</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>393.85</v>
+        <v>408.65</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>378.5</v>
+        <v>384.53</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>361.5</v>
+        <v>365.42</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>369.58</v>
+        <v>370.43</v>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1938.1</v>
+        <v>1927.9</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>2103.65</v>
+        <v>2078.21</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>2190.31</v>
+        <v>2173.1</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>2171.55</v>
+        <v>2167.52</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>611.2</v>
+        <v>620.6</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>607.09</v>
+        <v>608.38</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>606.17</v>
+        <v>606.73</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>555.29</v>
+        <v>555.9400000000001</v>
       </c>
       <c r="G139" s="14" t="inlineStr">
         <is>
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>333.87</v>
+        <v>330.94</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>336.17</v>
+        <v>334.77</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>349.41</v>
+        <v>348.79</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,29 +6877,29 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>421.9</v>
+        <v>405.65</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>435.11</v>
+        <v>433.19</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>408.22</v>
+        <v>409.57</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>313.7</v>
+        <v>315.93</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H141" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I141" s="14" t="inlineStr">
@@ -6921,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>1142.7</v>
+        <v>1107.2</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>1188.05</v>
+        <v>1180.35</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>1063.59</v>
+        <v>1065.3</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>841.1900000000001</v>
+        <v>843.83</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>129.06</v>
+        <v>128.55</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>126.41</v>
+        <v>127.34</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>127.39</v>
+        <v>127.73</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>122.91</v>
+        <v>123.09</v>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>212.12</v>
+        <v>209.18</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>218.91</v>
+        <v>217.98</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>220.46</v>
+        <v>220.02</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>215.36</v>
+        <v>215.3</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>275.55</v>
+        <v>276.85</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>293.53</v>
+        <v>291.94</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>297.19</v>
+        <v>296.39</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>284.18</v>
+        <v>284.1</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>108.59</v>
+        <v>108.77</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>116.41</v>
+        <v>115.23</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>121.32</v>
+        <v>120.45</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>129.74</v>
+        <v>129.35</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>153.51</v>
+        <v>150.76</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>157.42</v>
+        <v>156.78</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>155.58</v>
+        <v>155.39</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>148.52</v>
+        <v>148.54</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>404.9</v>
+        <v>406.85</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>434.9</v>
+        <v>430.07</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>459.46</v>
+        <v>455.54</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>522.54</v>
+        <v>520.29</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7229,20 +7229,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>90.34999999999999</v>
+        <v>93.16</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>94.45999999999999</v>
+        <v>94.33</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>96.81999999999999</v>
+        <v>96.67</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>103.8</v>
+        <v>103.69</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>2217.9</v>
+        <v>2143.6</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>2131.3</v>
+        <v>2141.35</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>2068.04</v>
+        <v>2077.3</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1798.45</v>
+        <v>1806.19</v>
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>2336.4</v>
+        <v>2296.5</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>2445.91</v>
+        <v>2431.68</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>2500.68</v>
+        <v>2492.67</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>2508.36</v>
+        <v>2506.25</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,20 +7361,20 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>981.8</v>
+        <v>982.3</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>945.5700000000001</v>
+        <v>949.0700000000001</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>898.88</v>
+        <v>902.15</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>795.87</v>
+        <v>797.73</v>
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
@@ -7405,24 +7405,24 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>1987.1</v>
+        <v>1916.4</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>1931.38</v>
+        <v>1940.1</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>1790.35</v>
+        <v>1805.19</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1553.19</v>
-      </c>
-      <c r="G153" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1561.74</v>
+      </c>
+      <c r="G153" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H153" s="14" t="inlineStr">
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>1802.1</v>
+        <v>1731.8</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>1709.04</v>
+        <v>1711.21</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>1516.95</v>
+        <v>1525.38</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1281.57</v>
+        <v>1286.05</v>
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
@@ -7493,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>279.15</v>
+        <v>276.4</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>282.35</v>
+        <v>281.78</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>280.42</v>
+        <v>280.27</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>238.11</v>
+        <v>238.49</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>12071</v>
+        <v>12077</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>11574.8</v>
+        <v>11667.41</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>11209.12</v>
+        <v>11276.57</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>10169.62</v>
+        <v>10207.59</v>
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>2034.2</v>
+        <v>2059.7</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>2104.18</v>
+        <v>2099.94</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>2169.74</v>
+        <v>2165.42</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>2233.92</v>
+        <v>2232.18</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,24 +7625,24 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>1141.4</v>
+        <v>1179.9</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>1161.28</v>
+        <v>1163.06</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>1106.33</v>
+        <v>1109.21</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>918.48</v>
-      </c>
-      <c r="G158" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>921.08</v>
+      </c>
+      <c r="G158" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr">
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>668.25</v>
+        <v>663.05</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>673.42</v>
+        <v>673.8099999999999</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>686.12</v>
+        <v>685.38</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>650.11</v>
+        <v>650.65</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>455.25</v>
+        <v>461.45</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>491.37</v>
+        <v>488.52</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>510.86</v>
+        <v>508.92</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>551.86</v>
+        <v>550.96</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,29 +7757,29 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>110.71</v>
+        <v>108.62</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>112.17</v>
+        <v>112.26</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>110.42</v>
+        <v>110.62</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>115.41</v>
+        <v>115.36</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H161" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H161" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>405.85</v>
+        <v>399.25</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>430.35</v>
+        <v>428.52</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>422.34</v>
+        <v>422.32</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>397.3</v>
+        <v>397.81</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>151.55</v>
+        <v>149.16</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>155.02</v>
+        <v>154.5</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>155.66</v>
+        <v>155.41</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>163.68</v>
+        <v>163.46</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>504.9</v>
+        <v>507.65</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>526.0599999999999</v>
+        <v>524.3099999999999</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>549.25</v>
+        <v>547.62</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>636.1900000000001</v>
+        <v>634.91</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7933,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>701.2</v>
+        <v>703.55</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>719.72</v>
+        <v>718.1799999999999</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>673.26</v>
+        <v>674.4400000000001</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>568.11</v>
+        <v>569.46</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>192.22</v>
+        <v>195.41</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>200.32</v>
+        <v>199.38</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>202.7</v>
+        <v>202.12</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>229.08</v>
+        <v>228.41</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>209.3</v>
+        <v>210.66</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>220.79</v>
+        <v>219.83</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>229.22</v>
+        <v>228.49</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>229.65</v>
+        <v>229.47</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>518.7</v>
+        <v>520.2</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>527.17</v>
+        <v>526.71</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>506.28</v>
+        <v>507.73</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>474.56</v>
+        <v>475.56</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>426.35</v>
+        <v>424.3</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>422.63</v>
+        <v>422.79</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>413.31</v>
+        <v>413.74</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>405.08</v>
+        <v>405.27</v>
       </c>
       <c r="G169" s="14" t="inlineStr">
         <is>
@@ -8153,20 +8153,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>836</v>
+        <v>851.15</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>829.88</v>
+        <v>831.91</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>767.34</v>
+        <v>770.63</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>646.11</v>
+        <v>648.15</v>
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
@@ -8197,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>428.5</v>
+        <v>416.35</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>446.99</v>
+        <v>444.07</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>451.21</v>
+        <v>449.84</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>460.56</v>
+        <v>460.12</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>1061.9</v>
+        <v>1081.6</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>1125.15</v>
+        <v>1121.01</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>1099.88</v>
+        <v>1099.16</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>1043.16</v>
+        <v>1043.54</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>140.32</v>
+        <v>134.44</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>189.04</v>
+        <v>182.38</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>206.87</v>
+        <v>202.79</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>227.01</v>
+        <v>225.58</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>498.2</v>
+        <v>483.25</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>549.24</v>
+        <v>541.3</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>521.01</v>
+        <v>519.9400000000001</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>518.48</v>
+        <v>518.27</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>604.95</v>
+        <v>592.85</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>570.5599999999999</v>
+        <v>572.63</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>556.1799999999999</v>
+        <v>558.0599999999999</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>509.58</v>
+        <v>510.97</v>
       </c>
       <c r="G175" s="14" t="inlineStr">
         <is>
@@ -8417,20 +8417,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>152.41</v>
+        <v>151.96</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>155.75</v>
+        <v>155.13</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>157.95</v>
+        <v>157.52</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>156.94</v>
+        <v>156.85</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8461,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>179.41</v>
+        <v>177.81</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>186.57</v>
+        <v>185.71</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>195.43</v>
+        <v>194.41</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>247.03</v>
+        <v>245.75</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8505,24 +8505,24 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>1355.2</v>
+        <v>1422.9</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>1395.98</v>
+        <v>1400.59</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>1304.3</v>
+        <v>1313.45</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1086.31</v>
-      </c>
-      <c r="G178" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1093.01</v>
+      </c>
+      <c r="G178" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H178" s="14" t="inlineStr">
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>247.55</v>
+        <v>247.65</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>246.97</v>
+        <v>247.03</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>246.11</v>
+        <v>246.17</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>241.97</v>
+        <v>242.03</v>
       </c>
       <c r="G179" s="14" t="inlineStr">
         <is>
@@ -8593,20 +8593,20 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>360.2</v>
+        <v>361.2</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>384.73</v>
+        <v>382.49</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>370.8</v>
+        <v>370.42</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>328.71</v>
+        <v>329.03</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>25.95</v>
+        <v>26.12</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>27.91</v>
+        <v>27.63</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>29.15</v>
+        <v>28.94</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>34.78</v>
+        <v>34.61</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>6.99</v>
+        <v>7.03</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>7.56</v>
+        <v>7.48</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>8.1</v>
+        <v>8.02</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>9.140000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>585.65</v>
+        <v>593.05</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>636.71</v>
+        <v>632.55</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>657.14</v>
+        <v>654.63</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>628.96</v>
+        <v>628.6</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>246.45</v>
+        <v>239.45</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>273.65</v>
+        <v>270.39</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>300.72</v>
+        <v>298.32</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>351.04</v>
+        <v>349.93</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8813,20 +8813,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>697.9</v>
+        <v>690.45</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>749.64</v>
+        <v>740.95</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>789.01</v>
+        <v>782.36</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>893.14</v>
+        <v>889.37</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>12882</v>
+        <v>13123</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>13315.3</v>
+        <v>13296.98</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>13204.74</v>
+        <v>13201.53</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>13298.41</v>
+        <v>13296.67</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>336.5</v>
+        <v>335.6</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>337.18</v>
+        <v>337.03</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>336.56</v>
+        <v>336.53</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>329.7</v>
+        <v>329.76</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>55.01</v>
+        <v>53.68</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>59.44</v>
+        <v>58.89</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>60.81</v>
+        <v>60.53</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>66.20999999999999</v>
+        <v>66.08</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -8989,24 +8989,24 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>1347.8</v>
+        <v>1370.6</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>1365.23</v>
+        <v>1365.74</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>1290.12</v>
+        <v>1293.28</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1111.36</v>
-      </c>
-      <c r="G189" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1113.94</v>
+      </c>
+      <c r="G189" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H189" s="14" t="inlineStr">
@@ -9033,20 +9033,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>810.25</v>
+        <v>803.9</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>865.8099999999999</v>
+        <v>856.29</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>897.89</v>
+        <v>891.4400000000001</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>984.77</v>
+        <v>981.4</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9077,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>766.25</v>
+        <v>755.55</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>781.13</v>
+        <v>778.6900000000001</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>798.71</v>
+        <v>797.02</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>784.37</v>
+        <v>784.08</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>789.45</v>
+        <v>813</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>826.8099999999999</v>
+        <v>823.5599999999999</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>785.53</v>
+        <v>786.36</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>750.8</v>
+        <v>750.38</v>
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
@@ -9165,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>121.22</v>
+        <v>121.82</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>123.87</v>
+        <v>123.59</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>126.04</v>
+        <v>125.62</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>139.27</v>
+        <v>138.69</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>276.2</v>
+        <v>281.15</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>296.43</v>
+        <v>294.98</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>302.51</v>
+        <v>301.68</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>338.78</v>
+        <v>338.2</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,24 +9253,24 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>2833.8</v>
+        <v>2943</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>2891.52</v>
+        <v>2896.42</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>2786.89</v>
+        <v>2793.01</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>2588.9</v>
-      </c>
-      <c r="G195" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2592.43</v>
+      </c>
+      <c r="G195" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H195" s="14" t="inlineStr">
@@ -9297,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>2574.1</v>
+        <v>2612.5</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>2764.4</v>
+        <v>2749.93</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>2714.04</v>
+        <v>2710.06</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>2612.04</v>
+        <v>2612.05</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9322,9 +9322,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I196" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I196" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J196" s="13" t="inlineStr">
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>737.6</v>
+        <v>768</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>719.08</v>
+        <v>723.74</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>656.3200000000001</v>
+        <v>660.7</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>564.76</v>
+        <v>566.78</v>
       </c>
       <c r="G197" s="14" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>673.55</v>
+        <v>676.1</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>679.98</v>
+        <v>678.8</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>681.67</v>
+        <v>681.03</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>629.62</v>
+        <v>630.49</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>327.55</v>
+        <v>323.4</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>346.14</v>
+        <v>343.97</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>356.85</v>
+        <v>355.54</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>421.02</v>
+        <v>420.05</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>1616.1</v>
+        <v>1637</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>1784.24</v>
+        <v>1770.22</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>1895.11</v>
+        <v>1884.99</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>2030.22</v>
+        <v>2026.31</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>161.02</v>
+        <v>160.53</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>167.15</v>
+        <v>165.81</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>175.34</v>
+        <v>174.13</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>191.12</v>
+        <v>190.5</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>120.87</v>
+        <v>117.34</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>121.09</v>
+        <v>120.34</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>124.98</v>
+        <v>124.35</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>126.83</v>
+        <v>126.63</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>183.03</v>
+        <v>184.81</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>195.31</v>
+        <v>194.31</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>199.92</v>
+        <v>199.33</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>208.93</v>
+        <v>208.69</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>787.95</v>
+        <v>764.85</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>808.73</v>
+        <v>804.55</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>828.72</v>
+        <v>826.22</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>830.5700000000001</v>
+        <v>829.91</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>111.37</v>
+        <v>108.76</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>115.23</v>
+        <v>114.47</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>118.62</v>
+        <v>118.05</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>137.49</v>
+        <v>136.97</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,29 +9737,29 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
+        <v>579.8</v>
+      </c>
+      <c r="D206" s="11" t="n">
+        <v>582.16</v>
+      </c>
+      <c r="E206" s="11" t="n">
         <v>582.3</v>
       </c>
-      <c r="D206" s="11" t="n">
-        <v>581.5599999999999</v>
-      </c>
-      <c r="E206" s="11" t="n">
-        <v>582.05</v>
-      </c>
       <c r="F206" s="11" t="n">
-        <v>609.61</v>
-      </c>
-      <c r="G206" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H206" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>609.14</v>
+      </c>
+      <c r="G206" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H206" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I206" s="12" t="inlineStr">
@@ -9781,20 +9781,20 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>399.6</v>
+        <v>406.2</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>406.75</v>
+        <v>406.69</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>417.09</v>
+        <v>416.66</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>441.86</v>
+        <v>441.51</v>
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>126.61</v>
+        <v>128.81</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>125.81</v>
+        <v>126.09</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>126.24</v>
+        <v>126.34</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>137.13</v>
+        <v>137.05</v>
       </c>
       <c r="G208" s="14" t="inlineStr">
         <is>
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>151.33</v>
+        <v>151.05</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>155.98</v>
+        <v>155.27</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>159.74</v>
+        <v>159.16</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>170.71</v>
+        <v>170.34</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>103.37</v>
+        <v>102.01</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>107.27</v>
+        <v>106.84</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>105.78</v>
+        <v>105.74</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>114.15</v>
+        <v>113.97</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>1272</v>
+        <v>1241.9</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>1322.02</v>
+        <v>1314.39</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>1323.62</v>
+        <v>1320.41</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>1317.83</v>
+        <v>1317.07</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>121.98</v>
+        <v>121.64</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>128.59</v>
+        <v>127.92</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>131.98</v>
+        <v>131.58</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>154.67</v>
+        <v>154.35</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>287.7</v>
+        <v>287.85</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>299.08</v>
+        <v>298.01</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>309.76</v>
+        <v>308.9</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>317.68</v>
+        <v>317.38</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,20 +10089,20 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>275.15</v>
+        <v>271.1</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>265.36</v>
+        <v>268.16</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>275.38</v>
+        <v>275.86</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>352.65</v>
+        <v>351.25</v>
       </c>
       <c r="G214" s="14" t="inlineStr">
         <is>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>824.75</v>
+        <v>825.3</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>818.3099999999999</v>
+        <v>818.97</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>809.5700000000001</v>
+        <v>810.1900000000001</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>802.78</v>
+        <v>803</v>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1348</v>
+        <v>1335</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>1138.03</v>
+        <v>1156.79</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>1011.35</v>
+        <v>1024.04</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>960.77</v>
+        <v>964.49</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>75.23</v>
+        <v>74.33</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>78.15000000000001</v>
+        <v>77.72</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>76.45999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>79.19</v>
+        <v>79.13</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>119.13</v>
+        <v>118.58</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>127.88</v>
+        <v>127</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>136.59</v>
+        <v>135.89</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>164.54</v>
+        <v>164.09</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10309,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>1087.7</v>
+        <v>1075.6</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>1064.22</v>
+        <v>1065.3</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>1069.17</v>
+        <v>1069.42</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>1121.9</v>
+        <v>1121.44</v>
       </c>
       <c r="G219" s="14" t="inlineStr">
         <is>
@@ -10353,20 +10353,20 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>235.9</v>
+        <v>233.9</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>245.49</v>
+        <v>243.82</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>241.35</v>
+        <v>240.97</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>227.56</v>
+        <v>227.74</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10397,24 +10397,24 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1508.5</v>
+        <v>1546.3</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1544.97</v>
+        <v>1545.09</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1554.15</v>
+        <v>1553.84</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1913.21</v>
-      </c>
-      <c r="G221" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1909.56</v>
+      </c>
+      <c r="G221" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H221" s="12" t="inlineStr">
@@ -10441,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>587.65</v>
+        <v>593.15</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>616.17</v>
+        <v>613.66</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>624.53</v>
+        <v>622.9</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>625.76</v>
+        <v>625.33</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10485,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>23.49</v>
+        <v>23.01</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>24.16</v>
+        <v>24.1</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>23.67</v>
+        <v>23.69</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>25.06</v>
+        <v>25.04</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>645.3</v>
+        <v>647.35</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>632.39</v>
+        <v>637.3099999999999</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>600.45</v>
+        <v>605.09</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>597.01</v>
+        <v>598.28</v>
       </c>
       <c r="G224" s="14" t="inlineStr">
         <is>
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>394.3</v>
+        <v>394.15</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>416.64</v>
+        <v>412.56</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>433.58</v>
+        <v>430.55</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>483.03</v>
+        <v>481.27</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10617,20 +10617,20 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>209.8</v>
+        <v>209.2</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>218.93</v>
+        <v>218</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>227.5</v>
+        <v>226.78</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>244.8</v>
+        <v>244.45</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10661,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>502.05</v>
+        <v>505</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>508.59</v>
+        <v>508.25</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>499.93</v>
+        <v>500.13</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>474.26</v>
+        <v>474.57</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>112.14</v>
+        <v>114.54</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>111.36</v>
+        <v>111.67</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>111.88</v>
+        <v>111.98</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>122.1</v>
+        <v>122.03</v>
       </c>
       <c r="G228" s="14" t="inlineStr">
         <is>
@@ -10749,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>205.56</v>
+        <v>210.23</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>214.87</v>
+        <v>214.43</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>215.77</v>
+        <v>215.55</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>226.49</v>
+        <v>226.33</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>1775.7</v>
+        <v>1823.1</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>1944.92</v>
+        <v>1933.32</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>1904.07</v>
+        <v>1900.89</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>1776.6</v>
+        <v>1777.06</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10818,9 +10818,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I230" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I230" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J230" s="13" t="inlineStr">
@@ -10837,20 +10837,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>701.1</v>
+        <v>692.95</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>659.4</v>
+        <v>668.35</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>627.6799999999999</v>
+        <v>634.01</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>603.36</v>
+        <v>605.48</v>
       </c>
       <c r="G231" s="14" t="inlineStr">
         <is>
@@ -10881,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>179.89</v>
+        <v>176.02</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>174.95</v>
+        <v>176.01</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>182.4</v>
+        <v>182.31</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>216.05</v>
+        <v>215.36</v>
       </c>
       <c r="G232" s="14" t="inlineStr">
         <is>
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>5572</v>
+        <v>5646</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>5744.34</v>
+        <v>5734.98</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>5859.01</v>
+        <v>5850.66</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>5761.23</v>
+        <v>5760.08</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>328.4</v>
+        <v>322.55</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>337.72</v>
+        <v>336.01</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>339.32</v>
+        <v>338.5</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>386.43</v>
+        <v>385.29</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11013,20 +11013,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>27.01</v>
+        <v>26.74</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>28.91</v>
+        <v>28.59</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>30.51</v>
+        <v>30.25</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>35.37</v>
+        <v>35.21</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>184.93</v>
+        <v>187.3</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>192.24</v>
+        <v>191.77</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>197.95</v>
+        <v>197.53</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>211.91</v>
+        <v>211.67</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>127.16</v>
+        <v>126.28</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>128.41</v>
+        <v>128.2</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>129.16</v>
+        <v>129.05</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>123.87</v>
+        <v>123.9</v>
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
@@ -11145,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>7.38</v>
+        <v>7.48</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>8.949999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>10.5</v>
+        <v>10.26</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>13.25</v>
+        <v>13.13</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11189,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>96.95999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>103.26</v>
+        <v>102.02</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>107.71</v>
+        <v>106.84</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>121.06</v>
+        <v>120.57</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11233,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>291.05</v>
+        <v>297.65</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>305.09</v>
+        <v>303.88</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>306.06</v>
+        <v>305.5</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>328.63</v>
+        <v>328.04</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>471.8</v>
+        <v>461.5</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>495.1</v>
+        <v>490.84</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>519.62</v>
+        <v>515.98</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>623.25</v>
+        <v>620.27</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11321,20 +11321,20 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>62.25</v>
+        <v>64.05</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>67.31999999999999</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>67.08</v>
+        <v>66.88</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>72.34999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
@@ -11365,24 +11365,24 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>1532.1</v>
+        <v>1520.5</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>1520.58</v>
+        <v>1520.57</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>1536.03</v>
+        <v>1535.42</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>1699.02</v>
-      </c>
-      <c r="G243" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1697.24</v>
+      </c>
+      <c r="G243" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H243" s="12" t="inlineStr">
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>117.18</v>
+        <v>117.67</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>126.62</v>
+        <v>125.22</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>131.27</v>
+        <v>130.33</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>136.07</v>
+        <v>135.74</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>67.18000000000001</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>69.34</v>
+        <v>68.97</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>70.55</v>
+        <v>70.31</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>76.51000000000001</v>
+        <v>76.33</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>711.05</v>
+        <v>719.9</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>744.8099999999999</v>
+        <v>742.4299999999999</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>756.41</v>
+        <v>754.98</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>761.6</v>
+        <v>761.1900000000001</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,20 +11541,20 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>442.95</v>
+        <v>438.5</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>422.52</v>
+        <v>425.35</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>424.83</v>
+        <v>425.84</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>429.24</v>
+        <v>429.41</v>
       </c>
       <c r="G247" s="14" t="inlineStr">
         <is>
@@ -11585,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>585.85</v>
+        <v>569.3</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>646.51</v>
+        <v>635.11</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>719.9299999999999</v>
+        <v>709.52</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>813.27</v>
+        <v>808.75</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>4055.3</v>
+        <v>3990.4</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>4179.07</v>
+        <v>4161.1</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>4334.79</v>
+        <v>4321.28</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>4499.47</v>
+        <v>4494.41</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11673,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>682.55</v>
+        <v>678</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>721.74</v>
+        <v>715.85</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>747.4400000000001</v>
+        <v>743.04</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>782.45</v>
+        <v>780.64</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11717,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>389.55</v>
+        <v>413.25</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>414.51</v>
+        <v>414.39</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>426.02</v>
+        <v>425.52</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>432.38</v>
+        <v>432.19</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 16-Sep-2026  15:19:14    |    Closing Price Date: 16-Sep-2026</t>
+          <t>Scan Run: 17-Sep-2026  15:25:26    |    Closing Price Date: 17-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>22.8</v>
+        <v>28.8</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>34</v>
+        <v>38.8</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>16-Sep-2026  15:19:14</t>
+          <t>17-Sep-2026  15:25:26</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.8% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 28.8% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 38.8% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 51.6% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 57 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 72 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 85 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 97 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 129 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 130 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>237.36</v>
+        <v>243.06</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>252.14</v>
+        <v>251.27</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>263.87</v>
+        <v>263.05</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>296.36</v>
+        <v>295.84</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,24 +805,24 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>327.15</v>
+        <v>330.15</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>329.4</v>
+        <v>329</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>323.06</v>
+        <v>323.37</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>325.05</v>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>325.11</v>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr">
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>5971.5</v>
+        <v>6220.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>5887.49</v>
+        <v>5919.21</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5303.11</v>
+        <v>5339.09</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>4302.97</v>
+        <v>4322.33</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>696</v>
+        <v>722.1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>739.8200000000001</v>
+        <v>738.13</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>692.87</v>
+        <v>694.01</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>550.15</v>
+        <v>551.79</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>280</v>
+        <v>279.15</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>277.34</v>
+        <v>277.51</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>253.82</v>
+        <v>254.82</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>164.38</v>
+        <v>165.51</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>394.75</v>
+        <v>376.05</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>352.81</v>
+        <v>355.02</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>320</v>
+        <v>322.2</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>225.11</v>
+        <v>226.63</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1025,29 +1025,29 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>6792</v>
+        <v>7060</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>7066.74</v>
+        <v>7066.1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>6898.72</v>
+        <v>6905.04</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5476.2</v>
+        <v>5491.54</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
@@ -1069,24 +1069,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>856</v>
+        <v>831.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>840.6799999999999</v>
+        <v>839.78</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>779.55</v>
+        <v>781.58</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>628.01</v>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>630.03</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>318.2</v>
+        <v>313.9</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>320.82</v>
+        <v>320.16</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>305.69</v>
+        <v>306.01</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>256.83</v>
+        <v>257.38</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4927</v>
+        <v>4811</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>5255.03</v>
+        <v>5212.74</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>5399.11</v>
+        <v>5376.05</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>4533.64</v>
+        <v>4536.02</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,24 +1201,24 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>171.73</v>
+        <v>179.23</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>173.33</v>
+        <v>173.89</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>171.36</v>
+        <v>171.67</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>165.33</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>165.53</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -1245,29 +1245,29 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2581.7</v>
+        <v>2605.3</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2750.87</v>
+        <v>2737.01</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>2604.29</v>
+        <v>2604.33</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>2142.39</v>
+        <v>2145.05</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>619.05</v>
+        <v>611.5</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>593.59</v>
+        <v>595.3</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>580.85</v>
+        <v>582.05</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>573.39</v>
+        <v>573.5599999999999</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2216.1</v>
+        <v>2230</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>2182.94</v>
+        <v>2193.28</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>2008.15</v>
+        <v>2026.29</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1503.77</v>
+        <v>1517.92</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1377,29 +1377,29 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>3480.7</v>
+        <v>3490.8</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>3474.68</v>
+        <v>3476.22</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>3489.96</v>
+        <v>3489.99</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3223.36</v>
+        <v>3225.51</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>370.35</v>
+        <v>378.25</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>396.95</v>
+        <v>395.17</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>392.6</v>
+        <v>392.04</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>335.7</v>
+        <v>336.16</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>744.8</v>
+        <v>752.5</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>759.0700000000001</v>
+        <v>758.36</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>723.37</v>
+        <v>725.89</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>626.84</v>
+        <v>629.62</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>818.05</v>
+        <v>827.45</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>765.95</v>
+        <v>771.8099999999999</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>675</v>
+        <v>680.98</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>436.38</v>
+        <v>440.27</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>216.4</v>
+        <v>213.39</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>194.95</v>
+        <v>196.71</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>180.19</v>
+        <v>181.49</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>162.75</v>
+        <v>163.25</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>12.64</v>
+        <v>12.35</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>12.1</v>
+        <v>12.12</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>10.94</v>
+        <v>11</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10.29</v>
+        <v>10.32</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>220.68</v>
+        <v>229.33</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>236.83</v>
+        <v>235.11</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>235.22</v>
+        <v>234.63</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>197.65</v>
+        <v>198.24</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>2055.8</v>
+        <v>2074.8</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>2082.21</v>
+        <v>2081.5</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>2008.06</v>
+        <v>2010.68</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1707.39</v>
+        <v>1710.7</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>218.43</v>
+        <v>218.17</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>231.17</v>
+        <v>229.93</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>228.83</v>
+        <v>228.41</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>208.46</v>
+        <v>208.48</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>64.83</v>
+        <v>63.97</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>66.58</v>
+        <v>66.33</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>66.23999999999999</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>60.13</v>
+        <v>60.28</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>157.16</v>
+        <v>159.41</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>166.44</v>
+        <v>165.77</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>165.65</v>
+        <v>165.41</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>150.3</v>
+        <v>150.34</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>173.53</v>
+        <v>174.54</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>185.94</v>
+        <v>183.17</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>189.15</v>
+        <v>186.85</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>190.58</v>
+        <v>188.74</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>487.55</v>
+        <v>495.15</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>524.23</v>
+        <v>521.46</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>542.58</v>
+        <v>540.72</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>539.92</v>
+        <v>539.5599999999999</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,24 +1949,24 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>342.4</v>
+        <v>353</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>348.14</v>
+        <v>348.6</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>325.27</v>
+        <v>326.36</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>264.82</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>265.91</v>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -1993,29 +1993,29 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1318.8</v>
+        <v>1370.9</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>1407.3</v>
+        <v>1403.84</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>1334.59</v>
+        <v>1336.02</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1033.11</v>
+        <v>1036.7</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
@@ -2037,24 +2037,24 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>351.15</v>
+        <v>362.55</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>360.47</v>
+        <v>360.67</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>342.44</v>
+        <v>343.23</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>302.95</v>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>303.69</v>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
@@ -2081,24 +2081,24 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>526.55</v>
+        <v>543.85</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>534.03</v>
+        <v>534.97</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>513.62</v>
+        <v>514.8099999999999</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>467.11</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>468.17</v>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1603.1</v>
+        <v>1623.3</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1630.04</v>
+        <v>1629.4</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>1553.16</v>
+        <v>1555.91</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1251.87</v>
+        <v>1255.19</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>792.6</v>
+        <v>793.3</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>794.48</v>
+        <v>794.37</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>733.52</v>
+        <v>735.87</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>542.04</v>
+        <v>544.64</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,29 +2213,29 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>608.65</v>
+        <v>601.15</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>609.9299999999999</v>
+        <v>609.1</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>608.15</v>
+        <v>607.87</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>598.5</v>
+        <v>599.89</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>506.6</v>
+        <v>520.1</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>531.3200000000001</v>
+        <v>530.25</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>527.6900000000001</v>
+        <v>527.39</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>480.72</v>
+        <v>481.13</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>180.6</v>
+        <v>182.53</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>196.17</v>
+        <v>194.23</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>201.04</v>
+        <v>199.88</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>202.49</v>
+        <v>202.2</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>770.35</v>
+        <v>770.85</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>817.74</v>
+        <v>813.27</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>878.98</v>
+        <v>874.74</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>967.41</v>
+        <v>965.8099999999999</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>515.7</v>
+        <v>517.6</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>561.36</v>
+        <v>557.1900000000001</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>604.24</v>
+        <v>600.84</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>623.65</v>
+        <v>622.26</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>332.25</v>
+        <v>342.35</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>352.37</v>
+        <v>350.71</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>356.32</v>
+        <v>355.36</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>344.33</v>
+        <v>344.06</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>199.29</v>
+        <v>203.02</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>209.07</v>
+        <v>208.49</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>205.96</v>
+        <v>205.84</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>174.5</v>
+        <v>174.87</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>80.02</v>
+        <v>80.2</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>84.37</v>
+        <v>83.97</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>85.03</v>
+        <v>84.84</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>72.26000000000001</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>220.16</v>
+        <v>220.81</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>233.46</v>
+        <v>232.25</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>223.27</v>
+        <v>223.17</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>216.8</v>
+        <v>216.88</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1621.9</v>
+        <v>1607.8</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1683.81</v>
+        <v>1676.57</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1674.65</v>
+        <v>1672.03</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1391.49</v>
+        <v>1395.39</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>327.45</v>
+        <v>327.9</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>360.79</v>
+        <v>357.66</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>374.04</v>
+        <v>372.23</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>404.3</v>
+        <v>403.66</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>541.3</v>
+        <v>559.25</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>572.3099999999999</v>
+        <v>571.0599999999999</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>567.1799999999999</v>
+        <v>566.86</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>492.19</v>
+        <v>493.11</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>163.88</v>
+        <v>163.37</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>168.4</v>
+        <v>167.92</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>175.13</v>
+        <v>174.67</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>211.55</v>
+        <v>211.07</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1198.7</v>
+        <v>1205.4</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1209.39</v>
+        <v>1209.01</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1132.32</v>
+        <v>1135.18</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1036.89</v>
+        <v>1037.68</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,24 +2829,24 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>904.2</v>
+        <v>891.45</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>897.66</v>
+        <v>897.0700000000001</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>859.63</v>
+        <v>860.88</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>714.28</v>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>716.09</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>173.11</v>
+        <v>174.64</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>174.95</v>
+        <v>174.92</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>178.97</v>
+        <v>178.8</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>181.92</v>
+        <v>181.76</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>260.9</v>
+        <v>271.75</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>279.32</v>
+        <v>278.6</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>291.52</v>
+        <v>290.75</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>302.22</v>
+        <v>301.38</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>446</v>
+        <v>449.35</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>504.7</v>
+        <v>499.43</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>532.15</v>
+        <v>528.91</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>539.1799999999999</v>
+        <v>539.21</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>3971.2</v>
+        <v>4017.5</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>3920.46</v>
+        <v>3926.13</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>3671.62</v>
+        <v>3681.63</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2806.01</v>
+        <v>2815.36</v>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>550.45</v>
+        <v>549.05</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>556.8200000000001</v>
+        <v>556.08</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>540.1</v>
+        <v>540.45</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>532.52</v>
+        <v>531.5599999999999</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>1852.9</v>
+        <v>1862.2</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>1964.16</v>
+        <v>1954.45</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>2001.41</v>
+        <v>1995.95</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1843.89</v>
+        <v>1843.03</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>180.93</v>
+        <v>185.07</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>179.79</v>
+        <v>180.3</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>164.07</v>
+        <v>164.9</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>133.93</v>
+        <v>134.52</v>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>522.65</v>
+        <v>532.55</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>555.4400000000001</v>
+        <v>553.26</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>545.8</v>
+        <v>545.28</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>500.02</v>
+        <v>500.45</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1633.1</v>
+        <v>1630.1</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>1687.96</v>
+        <v>1682.45</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>1703.52</v>
+        <v>1700.64</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1788.24</v>
+        <v>1788.03</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3269,24 +3269,24 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>160.27</v>
+        <v>156.67</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>158</v>
+        <v>157.88</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>162.35</v>
+        <v>162.12</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>170.8</v>
-      </c>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>170.71</v>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>3097.3</v>
+        <v>3107.2</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>3265.95</v>
+        <v>3250.83</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>3164.36</v>
+        <v>3162.12</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2695.22</v>
+        <v>2700.54</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>238.85</v>
+        <v>244.5</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>258.99</v>
+        <v>257.61</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>260.69</v>
+        <v>260.06</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>238.05</v>
+        <v>238.11</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>480.7</v>
+        <v>492.6</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>501.09</v>
+        <v>500.28</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>513.6799999999999</v>
+        <v>512.85</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>573.52</v>
+        <v>572.0599999999999</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>580.85</v>
+        <v>586.3</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>579.11</v>
+        <v>579.79</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>568.33</v>
+        <v>569.03</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>525.01</v>
+        <v>525.4400000000001</v>
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>21.04</v>
+        <v>21.56</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>22.51</v>
+        <v>22.42</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>22.45</v>
+        <v>22.42</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>22.69</v>
+        <v>22.68</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>194.87</v>
+        <v>199.64</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>201.35</v>
+        <v>201.19</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>204.9</v>
+        <v>204.69</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>205.05</v>
+        <v>204.97</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>185.64</v>
+        <v>191.72</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>194.35</v>
+        <v>194.1</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>200.49</v>
+        <v>200.15</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>192.71</v>
+        <v>192.72</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>673.7</v>
+        <v>674.05</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>679.46</v>
+        <v>677.78</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>666.11</v>
+        <v>666.41</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>655.5700000000001</v>
+        <v>655.9299999999999</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,24 +3665,24 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>1684.5</v>
+        <v>1852.3</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>1702.17</v>
+        <v>1716.47</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1670.87</v>
+        <v>1677.99</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1610.31</v>
-      </c>
-      <c r="G68" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1614.22</v>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H68" s="14" t="inlineStr">
@@ -3709,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>667.75</v>
+        <v>657.25</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>687.09</v>
+        <v>684.33</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>711.9400000000001</v>
+        <v>708.98</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>827.12</v>
+        <v>824.98</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3753,29 +3753,29 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>1978.9</v>
+        <v>2014.8</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>2098.88</v>
+        <v>2090.87</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>2000.83</v>
+        <v>2001.38</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1637.28</v>
+        <v>1640.34</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H70" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>6431</v>
+        <v>6502.5</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>6939.37</v>
+        <v>6897.76</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>6854.52</v>
+        <v>6840.71</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>5537.39</v>
+        <v>5543.63</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3841,29 +3841,29 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>45.19</v>
+        <v>45.88</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>45.96</v>
+        <v>45.95</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>45.6</v>
+        <v>45.61</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>41.77</v>
+        <v>41.82</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H72" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H72" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>463.9</v>
+        <v>464.1</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>485.8</v>
+        <v>484.03</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>505.17</v>
+        <v>503.06</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>584.0599999999999</v>
+        <v>580.77</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>145.61</v>
+        <v>145.59</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>146.4</v>
+        <v>146.95</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>139.31</v>
+        <v>140.13</v>
       </c>
       <c r="F74" s="11" t="n">
         <v>150.34</v>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>2149.8</v>
+        <v>2148.9</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>2292.6</v>
+        <v>2278.91</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2217.08</v>
+        <v>2214.4</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1798.45</v>
+        <v>1801.64</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>311.4</v>
+        <v>313.7</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>348.78</v>
+        <v>345.44</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>365.88</v>
+        <v>363.83</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>369.91</v>
+        <v>369.45</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>745.5</v>
+        <v>741.7</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>777.75</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>812.02</v>
+        <v>809.26</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>884.16</v>
+        <v>883.66</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,20 +4105,20 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>328.75</v>
+        <v>328.35</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>321.2</v>
+        <v>321.88</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>331.55</v>
+        <v>331.43</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>364.27</v>
+        <v>363.83</v>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>2695</v>
+        <v>2702.6</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>2648.28</v>
+        <v>2653.45</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>2562.79</v>
+        <v>2568.27</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2500.65</v>
+        <v>2503.32</v>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>177.94</v>
+        <v>179.22</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>187.72</v>
+        <v>186.91</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>198.24</v>
+        <v>197.49</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>212.57</v>
+        <v>212.39</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>162.24</v>
+        <v>162.59</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>159.88</v>
+        <v>160.14</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>155.59</v>
+        <v>155.86</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>154.48</v>
+        <v>154.71</v>
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>73.5</v>
+        <v>72.13</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>73.72</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>74.45999999999999</v>
+        <v>74.31</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>70.09999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>185.59</v>
+        <v>193.16</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>198.1</v>
+        <v>197.63</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>204.34</v>
+        <v>203.91</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>183.6</v>
+        <v>183.61</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,24 +4369,24 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>539.75</v>
+        <v>584.85</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>556.73</v>
+        <v>559.41</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>539.5599999999999</v>
+        <v>541.33</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>499.07</v>
-      </c>
-      <c r="G84" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>499.87</v>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H84" s="14" t="inlineStr">
@@ -4413,34 +4413,34 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>15.32</v>
+        <v>16.32</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>15.57</v>
+        <v>15.64</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>15.73</v>
+        <v>15.75</v>
       </c>
       <c r="F85" s="11" t="n">
         <v>16.12</v>
       </c>
-      <c r="G85" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H85" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I85" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H85" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I85" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J85" s="13" t="inlineStr">
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>801.05</v>
+        <v>811.05</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>853.37</v>
+        <v>849.34</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>893.95</v>
+        <v>890.7</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>949.87</v>
+        <v>948.34</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>2302.4</v>
+        <v>2395.6</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>2229.64</v>
+        <v>2245.45</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>2138.77</v>
+        <v>2148.84</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1799.69</v>
+        <v>1805.46</v>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
@@ -4545,24 +4545,24 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>654.55</v>
+        <v>656.6</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>654.86</v>
+        <v>655.03</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>657.36</v>
+        <v>657.33</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>624.97</v>
-      </c>
-      <c r="G88" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>625.03</v>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>1246.1</v>
+        <v>1273.7</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>1316.12</v>
+        <v>1312.08</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>1358.13</v>
+        <v>1354.82</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1310.4</v>
+        <v>1309.4</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4633,17 +4633,17 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>126.74</v>
+        <v>128.34</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>128.46</v>
+        <v>128.45</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>124.09</v>
+        <v>124.25</v>
       </c>
       <c r="F90" s="11" t="n">
         <v>116.55</v>
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>554.7</v>
+        <v>567.6</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>551.64</v>
+        <v>553.16</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>507.99</v>
+        <v>510.32</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>500.69</v>
+        <v>501.23</v>
       </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
@@ -4721,24 +4721,24 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>1766.7</v>
+        <v>1778.3</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>1771.08</v>
+        <v>1771.77</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>1641.4</v>
+        <v>1646.77</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1196.37</v>
-      </c>
-      <c r="G92" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1202.16</v>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr">
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>66.95999999999999</v>
+        <v>67</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>72.16</v>
+        <v>71.67</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>74.01000000000001</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>69.62</v>
+        <v>69.61</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>316.45</v>
+        <v>319.7</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>320.41</v>
+        <v>320.34</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>299.14</v>
+        <v>299.95</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>243.51</v>
+        <v>244.13</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>269.85</v>
+        <v>273.3</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>288.74</v>
+        <v>287.27</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>317.88</v>
+        <v>316.13</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>406.4</v>
+        <v>405.08</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>548.05</v>
+        <v>541.6</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>554.48</v>
+        <v>553.25</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>538.83</v>
+        <v>538.9400000000001</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>455.06</v>
+        <v>456.25</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4941,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>763.25</v>
+        <v>766.4</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>761.26</v>
+        <v>761.75</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>784</v>
+        <v>783.3099999999999</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>722.63</v>
+        <v>722.55</v>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>232.39</v>
+        <v>231.04</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>237.87</v>
+        <v>237.22</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>252.67</v>
+        <v>251.82</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>298.78</v>
+        <v>298.05</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1724.7</v>
+        <v>1770.8</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1845.72</v>
+        <v>1838.58</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1859.66</v>
+        <v>1856.18</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1784.98</v>
+        <v>1785.71</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5073,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>219.94</v>
+        <v>218.51</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>216.73</v>
+        <v>216.9</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>204.5</v>
+        <v>205.04</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>184.26</v>
+        <v>184.72</v>
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>860.95</v>
+        <v>865.45</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>893.46</v>
+        <v>890.8</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>892.08</v>
+        <v>891.03</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>752.28</v>
+        <v>753.4</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>417.35</v>
+        <v>418.05</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>402.76</v>
+        <v>404.21</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>389.29</v>
+        <v>390.42</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>369.23</v>
+        <v>369.59</v>
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>656.1</v>
+        <v>654</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>671.25</v>
+        <v>668.59</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>709.1900000000001</v>
+        <v>705.17</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>791.84</v>
+        <v>789.23</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>10513</v>
+        <v>10735</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>10774.63</v>
+        <v>10770.85</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>10363.22</v>
+        <v>10377.8</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>9419.24</v>
+        <v>9427.09</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>695.2</v>
+        <v>693.85</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>731.98</v>
+        <v>728.35</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>757.71</v>
+        <v>755.21</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>716.12</v>
+        <v>716.1799999999999</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>87.34999999999999</v>
+        <v>88.94</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>92.25</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>92.34999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>85.70999999999999</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,24 +5381,24 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>1941.8</v>
+        <v>2018</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>1952.93</v>
+        <v>1959.12</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>1844.62</v>
+        <v>1851.42</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1619.46</v>
-      </c>
-      <c r="G107" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1625.68</v>
+      </c>
+      <c r="G107" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H107" s="14" t="inlineStr">
@@ -5425,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>928.05</v>
+        <v>958.35</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>903.91</v>
+        <v>909.09</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>800.53</v>
+        <v>806.72</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>573.52</v>
+        <v>577.99</v>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
@@ -5469,20 +5469,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>1183.9</v>
+        <v>1200.2</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1108.22</v>
+        <v>1116.98</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>1068.95</v>
+        <v>1074.1</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1002.85</v>
+        <v>1005.84</v>
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
@@ -5513,24 +5513,24 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>688</v>
+        <v>705</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>695.29</v>
+        <v>696.22</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>734.02</v>
+        <v>732.88</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>877.8</v>
-      </c>
-      <c r="G110" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>876.02</v>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
@@ -5557,24 +5557,24 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>431.95</v>
+        <v>435.5</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>434.86</v>
+        <v>434.92</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>417.37</v>
+        <v>418.08</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>347.58</v>
-      </c>
-      <c r="G111" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>348.37</v>
+      </c>
+      <c r="G111" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H111" s="14" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>877.85</v>
+        <v>900.65</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>856.1799999999999</v>
+        <v>863.95</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>849.05</v>
+        <v>852.98</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>787.66</v>
+        <v>789.6</v>
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>426.25</v>
+        <v>424.35</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>411.76</v>
+        <v>412.96</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>401.93</v>
+        <v>402.81</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>398.62</v>
+        <v>399.1</v>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>202.65</v>
+        <v>204.14</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>207.46</v>
+        <v>207.14</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>214.92</v>
+        <v>214.5</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>242.99</v>
+        <v>242.44</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>72.11</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>77.59</v>
+        <v>77.03</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>84.98</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>94.84</v>
+        <v>94.52</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>266.2</v>
+        <v>248.7</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>627.8099999999999</v>
+        <v>562.67</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>854.78</v>
+        <v>809.85</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>953.6900000000001</v>
+        <v>939.71</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>374.65</v>
+        <v>371</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>337.62</v>
+        <v>344.23</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>314.43</v>
+        <v>319.08</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>315.76</v>
+        <v>316.94</v>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>3326.1</v>
+        <v>3320.2</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>3327.29</v>
+        <v>3326.62</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>3222.84</v>
+        <v>3226.66</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>2895.4</v>
+        <v>2899.26</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,29 +5909,29 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>4309.3</v>
+        <v>4385.4</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>4458.97</v>
+        <v>4451.96</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>4341.21</v>
+        <v>4342.94</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>3665.24</v>
+        <v>3673.65</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H119" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H119" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I119" s="14" t="inlineStr">
@@ -5953,24 +5953,24 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>661.6</v>
+        <v>670.2</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>666.96</v>
+        <v>667.26</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>695.4299999999999</v>
+        <v>694.4400000000001</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>757.24</v>
-      </c>
-      <c r="G120" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>756.33</v>
+      </c>
+      <c r="G120" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>276.35</v>
+        <v>278.75</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>302.75</v>
+        <v>300.47</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>335.98</v>
+        <v>333.74</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>396.93</v>
+        <v>395.92</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>497.05</v>
+        <v>490.75</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>513.42</v>
+        <v>511.26</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>537.8099999999999</v>
+        <v>535.96</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>597.53</v>
+        <v>596.83</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,24 +6085,24 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>617.9</v>
+        <v>618.9</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>618.29</v>
+        <v>618.34</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>584.74</v>
+        <v>586.08</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>506.06</v>
-      </c>
-      <c r="G123" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>506.99</v>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H123" s="14" t="inlineStr">
@@ -6129,29 +6129,29 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1438.3</v>
+        <v>1392.8</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1523.38</v>
+        <v>1510.95</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1421.3</v>
+        <v>1420.18</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1153.49</v>
+        <v>1156.57</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H124" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
@@ -6173,20 +6173,20 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>211.47</v>
+        <v>211.98</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>219.15</v>
+        <v>218.02</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>223.15</v>
+        <v>222.37</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>239.93</v>
+        <v>239.25</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>452.05</v>
+        <v>448.95</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>482.87</v>
+        <v>477.83</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>498.39</v>
+        <v>495.08</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>536.16</v>
+        <v>534.5599999999999</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -6261,29 +6261,29 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>394.85</v>
+        <v>395.4</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>412.39</v>
+        <v>410.77</v>
       </c>
       <c r="E127" s="11" t="n">
         <v>395.38</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>373.23</v>
+        <v>373.56</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H127" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H127" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I127" s="14" t="inlineStr">
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>786.4</v>
+        <v>790.05</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>816.39</v>
+        <v>813.88</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>794.9</v>
+        <v>794.71</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>734.84</v>
+        <v>735.73</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>772</v>
+        <v>766.7</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>756.79</v>
+        <v>757.74</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>719.42</v>
+        <v>721.28</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>601.13</v>
+        <v>602.61</v>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>196.05</v>
+        <v>218.44</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>182.48</v>
+        <v>185.9</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>173.42</v>
+        <v>175.18</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>159.19</v>
+        <v>159.92</v>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
@@ -6437,29 +6437,29 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>674.15</v>
+        <v>687.15</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>698.83</v>
+        <v>697.72</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>686.8</v>
+        <v>686.8200000000001</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>646.1799999999999</v>
+        <v>646.23</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H131" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H131" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I131" s="14" t="inlineStr">
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>418.85</v>
+        <v>420.1</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>431.4</v>
+        <v>430.33</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>435.39</v>
+        <v>434.8</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>472.1</v>
+        <v>471.42</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>725.35</v>
+        <v>727.55</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>776.22</v>
+        <v>771.58</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>784.04</v>
+        <v>781.8200000000001</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>767.64</v>
+        <v>767.5</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6569,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>1655</v>
+        <v>1633.3</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>1771.98</v>
+        <v>1758.77</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>1737.33</v>
+        <v>1733.25</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1464.08</v>
+        <v>1465.77</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>228.55</v>
+        <v>234.35</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>247.08</v>
+        <v>245.87</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>251.85</v>
+        <v>251.16</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>260</v>
+        <v>259.75</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>95.83</v>
+        <v>96.12</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>96.90000000000001</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>90.01000000000001</v>
+        <v>90.25</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>76.81999999999999</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>408.65</v>
+        <v>405.45</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>384.53</v>
+        <v>386.52</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>365.42</v>
+        <v>366.99</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>370.43</v>
+        <v>370.38</v>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1927.9</v>
+        <v>1900.9</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>2078.21</v>
+        <v>2061.33</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>2173.1</v>
+        <v>2162.42</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>2167.52</v>
+        <v>2165.1</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>620.6</v>
+        <v>633.25</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>608.38</v>
+        <v>611.4400000000001</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>606.73</v>
+        <v>608.14</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>555.9400000000001</v>
+        <v>557.0700000000001</v>
       </c>
       <c r="G139" s="14" t="inlineStr">
         <is>
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>314</v>
+        <v>317.1</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>330.94</v>
+        <v>329.62</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>334.77</v>
+        <v>334.08</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>348.79</v>
+        <v>348.23</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>405.65</v>
+        <v>408.95</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>433.19</v>
+        <v>430.88</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>409.57</v>
+        <v>409.54</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>315.93</v>
+        <v>316.86</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>1107.2</v>
+        <v>1105.4</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>1180.35</v>
+        <v>1173.21</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>1065.3</v>
+        <v>1066.87</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>843.83</v>
+        <v>846.4299999999999</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6965,29 +6965,29 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>128.55</v>
+        <v>126.96</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>127.34</v>
+        <v>127.31</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>127.73</v>
+        <v>127.7</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>123.09</v>
-      </c>
-      <c r="G143" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H143" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>123.13</v>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I143" s="14" t="inlineStr">
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>209.18</v>
+        <v>210.4</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>217.98</v>
+        <v>217.26</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>220.02</v>
+        <v>219.64</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>215.3</v>
+        <v>215.04</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>276.85</v>
+        <v>277.75</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>291.94</v>
+        <v>290.59</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>296.39</v>
+        <v>295.66</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>284.1</v>
+        <v>284.3</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>108.77</v>
+        <v>109.84</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>115.23</v>
+        <v>114.72</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>120.45</v>
+        <v>120.04</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>129.35</v>
+        <v>129.12</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>150.76</v>
+        <v>152.27</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>156.78</v>
+        <v>156.35</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>155.39</v>
+        <v>155.26</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>148.54</v>
+        <v>148.64</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>406.85</v>
+        <v>410.2</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>430.07</v>
+        <v>428.18</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>455.54</v>
+        <v>453.76</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>520.29</v>
+        <v>519.05</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7229,20 +7229,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>93.16</v>
+        <v>92.13</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>94.33</v>
+        <v>94.12</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>96.67</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>103.69</v>
+        <v>103.6</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>2143.6</v>
+        <v>2169.6</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>2141.35</v>
+        <v>2144.04</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>2077.3</v>
+        <v>2080.92</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1806.19</v>
+        <v>1809.81</v>
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>2296.5</v>
+        <v>2339</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>2431.68</v>
+        <v>2422.85</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>2492.67</v>
+        <v>2486.64</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>2506.25</v>
+        <v>2505.74</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,20 +7361,20 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>982.3</v>
+        <v>1072.4</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>949.0700000000001</v>
+        <v>960.8099999999999</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>902.15</v>
+        <v>908.8200000000001</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>797.73</v>
+        <v>800.3099999999999</v>
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>1916.4</v>
+        <v>1939.1</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>1940.1</v>
+        <v>1940</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>1805.19</v>
+        <v>1810.44</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1561.74</v>
+        <v>1565.21</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,24 +7449,24 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>1731.8</v>
+        <v>1666.6</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>1711.21</v>
+        <v>1706.96</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>1525.38</v>
+        <v>1530.91</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1286.05</v>
-      </c>
-      <c r="G154" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1289.15</v>
+      </c>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr">
@@ -7493,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>276.4</v>
+        <v>277.9</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>281.78</v>
+        <v>281.41</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>280.27</v>
+        <v>280.17</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>238.49</v>
+        <v>238.88</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>12077</v>
+        <v>11819</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>11667.41</v>
+        <v>11681.85</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>11276.57</v>
+        <v>11297.84</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>10207.59</v>
+        <v>10229.24</v>
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>2059.7</v>
+        <v>2065.9</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>2099.94</v>
+        <v>2096.7</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>2165.42</v>
+        <v>2161.52</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>2232.18</v>
+        <v>2232.35</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,24 +7625,24 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>1179.9</v>
+        <v>1143.1</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>1163.06</v>
+        <v>1161.16</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>1109.21</v>
+        <v>1110.54</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>921.08</v>
-      </c>
-      <c r="G158" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>922.6</v>
+      </c>
+      <c r="G158" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr">
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>663.05</v>
+        <v>673</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>673.8099999999999</v>
+        <v>673.73</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>685.38</v>
+        <v>684.9</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>650.65</v>
+        <v>651.1900000000001</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>461.45</v>
+        <v>462.4</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>488.52</v>
+        <v>486.03</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>508.92</v>
+        <v>507.09</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>550.96</v>
+        <v>549.75</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,29 +7757,29 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>108.62</v>
+        <v>111.69</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>112.26</v>
+        <v>112.2</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>110.62</v>
+        <v>110.66</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>115.36</v>
+        <v>115.28</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H161" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H161" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>399.25</v>
+        <v>407.85</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>428.52</v>
+        <v>426.55</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>422.32</v>
+        <v>421.75</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>397.81</v>
+        <v>398.77</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>149.16</v>
+        <v>152.27</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>154.5</v>
+        <v>154.29</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>155.41</v>
+        <v>155.29</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>163.46</v>
+        <v>163.29</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>507.65</v>
+        <v>510.4</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>524.3099999999999</v>
+        <v>522.98</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>547.62</v>
+        <v>546.16</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>634.91</v>
+        <v>634.03</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7933,24 +7933,24 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>703.55</v>
+        <v>715.25</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>718.1799999999999</v>
+        <v>710.42</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>674.4400000000001</v>
+        <v>668.58</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>569.46</v>
-      </c>
-      <c r="G165" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>564.38</v>
+      </c>
+      <c r="G165" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H165" s="14" t="inlineStr">
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>195.41</v>
+        <v>193.84</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>199.38</v>
+        <v>198.85</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>202.12</v>
+        <v>201.8</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>228.41</v>
+        <v>228.34</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>210.66</v>
+        <v>211.35</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>219.83</v>
+        <v>219.02</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>228.49</v>
+        <v>227.82</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>229.47</v>
+        <v>229.44</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>520.2</v>
+        <v>519.9</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>526.71</v>
+        <v>526.0599999999999</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>507.73</v>
+        <v>508.21</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>475.56</v>
+        <v>476</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>424.3</v>
+        <v>428.35</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>422.79</v>
+        <v>423.76</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>413.74</v>
+        <v>414.86</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>405.27</v>
+        <v>405.64</v>
       </c>
       <c r="G169" s="14" t="inlineStr">
         <is>
@@ -8153,20 +8153,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>851.15</v>
+        <v>846.15</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>831.91</v>
+        <v>836.28</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>770.63</v>
+        <v>777.33</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>648.15</v>
+        <v>652.02</v>
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
@@ -8197,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>416.35</v>
+        <v>425.05</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>444.07</v>
+        <v>442.26</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>449.84</v>
+        <v>448.87</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>460.12</v>
+        <v>459.57</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>1081.6</v>
+        <v>1098.9</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>1121.01</v>
+        <v>1118.9</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>1099.16</v>
+        <v>1099.15</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>1043.54</v>
+        <v>1045.59</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>134.44</v>
+        <v>139.55</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>182.38</v>
+        <v>178.3</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>202.79</v>
+        <v>200.31</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>225.58</v>
+        <v>224.8</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>483.25</v>
+        <v>501.6</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>541.3</v>
+        <v>537.52</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>519.9400000000001</v>
+        <v>519.22</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>518.27</v>
+        <v>518.14</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>592.85</v>
+        <v>610</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>572.63</v>
+        <v>576.1799999999999</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>558.0599999999999</v>
+        <v>560.09</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>510.97</v>
+        <v>512.13</v>
       </c>
       <c r="G175" s="14" t="inlineStr">
         <is>
@@ -8417,24 +8417,24 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>151.96</v>
+        <v>155.93</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>155.13</v>
+        <v>155.21</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>157.52</v>
+        <v>157.46</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>156.85</v>
-      </c>
-      <c r="G176" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>156.87</v>
+      </c>
+      <c r="G176" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H176" s="12" t="inlineStr">
@@ -8461,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>177.81</v>
+        <v>181.38</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>185.71</v>
+        <v>185.3</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>194.41</v>
+        <v>193.9</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>245.75</v>
+        <v>245.07</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>1422.9</v>
+        <v>1489.8</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>1400.59</v>
+        <v>1409.09</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>1313.45</v>
+        <v>1320.36</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1093.01</v>
+        <v>1098.43</v>
       </c>
       <c r="G178" s="14" t="inlineStr">
         <is>
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>247.65</v>
+        <v>249.89</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>247.03</v>
+        <v>247.3</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>246.17</v>
+        <v>246.31</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>242.03</v>
+        <v>242.1</v>
       </c>
       <c r="G179" s="14" t="inlineStr">
         <is>
@@ -8593,20 +8593,20 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>361.2</v>
+        <v>365.85</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>382.49</v>
+        <v>380.91</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>370.42</v>
+        <v>370.24</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>329.03</v>
+        <v>329.4</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>26.12</v>
+        <v>26.46</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>27.63</v>
+        <v>27.52</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>28.94</v>
+        <v>28.84</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>34.61</v>
+        <v>34.64</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>7.03</v>
+        <v>7.06</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>7.48</v>
+        <v>7.44</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>8.02</v>
+        <v>7.98</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>9.1</v>
+        <v>9.17</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>593.05</v>
+        <v>600.55</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>632.55</v>
+        <v>629.5</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>654.63</v>
+        <v>652.51</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>628.6</v>
+        <v>628.3200000000001</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>239.45</v>
+        <v>232.45</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>270.39</v>
+        <v>266.78</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>298.32</v>
+        <v>295.74</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>349.93</v>
+        <v>348.87</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8813,20 +8813,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>690.45</v>
+        <v>703.35</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>740.95</v>
+        <v>737.37</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>782.36</v>
+        <v>779.26</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>889.37</v>
+        <v>888.49</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>13123</v>
+        <v>13151</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>13296.98</v>
+        <v>13283.08</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>13201.53</v>
+        <v>13199.55</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>13296.67</v>
+        <v>13296.2</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,29 +8901,29 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>335.6</v>
+        <v>336.95</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>337.03</v>
+        <v>337.02</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>336.53</v>
+        <v>336.54</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>329.76</v>
+        <v>330.16</v>
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H187" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H187" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I187" s="14" t="inlineStr">
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>53.68</v>
+        <v>54.91</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>58.89</v>
+        <v>58.51</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>60.53</v>
+        <v>60.31</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>66.08</v>
+        <v>65.95</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>1370.6</v>
+        <v>1387.8</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>1365.74</v>
+        <v>1367.84</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>1293.28</v>
+        <v>1296.98</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1113.94</v>
+        <v>1116.35</v>
       </c>
       <c r="G189" s="14" t="inlineStr">
         <is>
@@ -9033,20 +9033,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>803.9</v>
+        <v>811.15</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>856.29</v>
+        <v>851.99</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>891.4400000000001</v>
+        <v>888.29</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>981.4</v>
+        <v>979.55</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9077,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>755.55</v>
+        <v>758.35</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>778.6900000000001</v>
+        <v>776.75</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>797.02</v>
+        <v>795.5</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>784.08</v>
+        <v>783.67</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9121,24 +9121,24 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>813</v>
+        <v>826.95</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>823.5599999999999</v>
+        <v>823.88</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>786.36</v>
+        <v>787.95</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>750.38</v>
-      </c>
-      <c r="G192" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>751.64</v>
+      </c>
+      <c r="G192" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H192" s="14" t="inlineStr">
@@ -9165,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>121.82</v>
+        <v>120.86</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>123.59</v>
+        <v>123.33</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>125.62</v>
+        <v>125.44</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>138.69</v>
+        <v>138.66</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>281.15</v>
+        <v>281.25</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>294.98</v>
+        <v>292.25</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>301.68</v>
+        <v>299.33</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>338.2</v>
+        <v>335.42</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,20 +9253,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>2943</v>
+        <v>2940.3</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>2896.42</v>
+        <v>2900.6</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>2793.01</v>
+        <v>2798.79</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>2592.43</v>
+        <v>2595.89</v>
       </c>
       <c r="G195" s="14" t="inlineStr">
         <is>
@@ -9297,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>2612.5</v>
+        <v>2651</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>2749.93</v>
+        <v>2740.51</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>2710.06</v>
+        <v>2707.74</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>2612.05</v>
+        <v>2615.03</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>768</v>
+        <v>778.7</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>723.74</v>
+        <v>728.97</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>660.7</v>
+        <v>665.33</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>566.78</v>
+        <v>569.3</v>
       </c>
       <c r="G197" s="14" t="inlineStr">
         <is>
@@ -9385,29 +9385,29 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>676.1</v>
+        <v>682.85</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>678.8</v>
+        <v>679.1799999999999</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>681.03</v>
+        <v>681.1</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>630.49</v>
-      </c>
-      <c r="G198" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H198" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>631.01</v>
+      </c>
+      <c r="G198" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H198" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I198" s="14" t="inlineStr">
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>323.4</v>
+        <v>327.6</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>343.97</v>
+        <v>342.41</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>355.54</v>
+        <v>354.44</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>420.05</v>
+        <v>419.55</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>1637</v>
+        <v>1646.6</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>1770.22</v>
+        <v>1758.45</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>1884.99</v>
+        <v>1875.64</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>2026.31</v>
+        <v>2021.46</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>160.53</v>
+        <v>160.06</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>165.81</v>
+        <v>165.26</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>174.13</v>
+        <v>173.58</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>190.5</v>
+        <v>190.41</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>117.34</v>
+        <v>118.65</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>120.34</v>
+        <v>120.18</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>124.35</v>
+        <v>124.13</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>126.63</v>
+        <v>126.59</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>184.81</v>
+        <v>184.2</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>194.31</v>
+        <v>193.35</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>199.33</v>
+        <v>198.73</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>208.69</v>
+        <v>208.6</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>764.85</v>
+        <v>777.8</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>804.55</v>
+        <v>801.53</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>826.22</v>
+        <v>823.41</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>829.91</v>
+        <v>828.71</v>
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>108.76</v>
+        <v>108.8</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>114.47</v>
+        <v>113.93</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>118.05</v>
+        <v>117.69</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>136.97</v>
+        <v>136.58</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>579.8</v>
+        <v>578.25</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>582.16</v>
+        <v>581.79</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>582.3</v>
+        <v>582.14</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>609.14</v>
+        <v>608.83</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,24 +9781,24 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>406.2</v>
+        <v>408.35</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>406.69</v>
+        <v>406.85</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>416.66</v>
+        <v>416.33</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>441.51</v>
-      </c>
-      <c r="G207" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>440.97</v>
+      </c>
+      <c r="G207" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>128.81</v>
+        <v>130.69</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>126.09</v>
+        <v>126.53</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>126.34</v>
+        <v>126.51</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>137.05</v>
+        <v>136.83</v>
       </c>
       <c r="G208" s="14" t="inlineStr">
         <is>
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>151.05</v>
+        <v>154.43</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>155.27</v>
+        <v>155.19</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>159.16</v>
+        <v>158.98</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>170.34</v>
+        <v>170.31</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>102.01</v>
+        <v>103.42</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>106.84</v>
+        <v>106.52</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>105.74</v>
+        <v>105.64</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>113.97</v>
+        <v>114</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>1241.9</v>
+        <v>1217.9</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>1314.39</v>
+        <v>1303.28</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>1320.41</v>
+        <v>1315.5</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>1317.07</v>
+        <v>1318.95</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>121.64</v>
+        <v>122.09</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>127.92</v>
+        <v>127.37</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>131.58</v>
+        <v>131.21</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>154.35</v>
+        <v>153.84</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>287.85</v>
+        <v>288.1</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>298.01</v>
+        <v>297.07</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>308.9</v>
+        <v>308.08</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>317.38</v>
+        <v>317.67</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,24 +10089,24 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>271.1</v>
+        <v>264.7</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>268.16</v>
+        <v>267.83</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>275.86</v>
+        <v>275.42</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>351.25</v>
-      </c>
-      <c r="G214" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>350.31</v>
+      </c>
+      <c r="G214" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H214" s="12" t="inlineStr">
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>825.3</v>
+        <v>826</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>818.97</v>
+        <v>819.64</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>810.1900000000001</v>
+        <v>810.8099999999999</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>803</v>
+        <v>802.9400000000001</v>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1335</v>
+        <v>1363.4</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>1156.79</v>
+        <v>1176.47</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>1024.04</v>
+        <v>1037.35</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>964.49</v>
+        <v>968.5599999999999</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>74.33</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>77.72</v>
+        <v>77.37</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>76.41</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>79.13</v>
+        <v>79.27</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>118.58</v>
+        <v>120.58</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>127</v>
+        <v>126.39</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>135.89</v>
+        <v>135.28</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>164.09</v>
+        <v>163.77</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10309,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>1075.6</v>
+        <v>1081.5</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>1065.3</v>
+        <v>1066.84</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>1069.42</v>
+        <v>1069.89</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>1121.44</v>
+        <v>1123.83</v>
       </c>
       <c r="G219" s="14" t="inlineStr">
         <is>
@@ -10353,20 +10353,20 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>233.9</v>
+        <v>231.4</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>243.82</v>
+        <v>242.64</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>240.97</v>
+        <v>240.6</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>227.74</v>
+        <v>227.79</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10397,24 +10397,24 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1546.3</v>
+        <v>1541</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1545.09</v>
+        <v>1543.22</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1553.84</v>
+        <v>1552.36</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1909.56</v>
-      </c>
-      <c r="G221" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1903.69</v>
+      </c>
+      <c r="G221" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H221" s="12" t="inlineStr">
@@ -10441,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>593.15</v>
+        <v>593.05</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>613.66</v>
+        <v>611.6900000000001</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>622.9</v>
+        <v>621.73</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>625.33</v>
+        <v>626.65</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10485,17 +10485,17 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>23.01</v>
+        <v>22.81</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>24.1</v>
+        <v>23.98</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>23.69</v>
+        <v>23.66</v>
       </c>
       <c r="F223" s="11" t="n">
         <v>25.04</v>
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>647.35</v>
+        <v>653.6</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>637.3099999999999</v>
+        <v>638.86</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>605.09</v>
+        <v>606.99</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>598.28</v>
+        <v>598.39</v>
       </c>
       <c r="G224" s="14" t="inlineStr">
         <is>
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>394.15</v>
+        <v>391.1</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>412.56</v>
+        <v>410.52</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>430.55</v>
+        <v>429</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>481.27</v>
+        <v>480.32</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10617,20 +10617,20 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>209.2</v>
+        <v>209.97</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>218</v>
+        <v>217.24</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>226.78</v>
+        <v>226.12</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>244.45</v>
+        <v>244.25</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10661,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>505</v>
+        <v>500.15</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>508.25</v>
+        <v>507.48</v>
       </c>
       <c r="E227" s="11" t="n">
         <v>500.13</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>474.57</v>
+        <v>474.83</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>114.54</v>
+        <v>113.44</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>111.67</v>
+        <v>111.83</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>111.98</v>
+        <v>112.04</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>122.03</v>
+        <v>122.44</v>
       </c>
       <c r="G228" s="14" t="inlineStr">
         <is>
@@ -10749,29 +10749,29 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>210.23</v>
+        <v>218.23</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>214.43</v>
+        <v>214.79</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>215.55</v>
+        <v>215.66</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>226.33</v>
-      </c>
-      <c r="G229" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H229" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>225.9</v>
+      </c>
+      <c r="G229" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H229" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I229" s="12" t="inlineStr">
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>1823.1</v>
+        <v>1843.8</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>1933.32</v>
+        <v>1924.79</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>1900.89</v>
+        <v>1898.65</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>1777.06</v>
+        <v>1777.78</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10837,20 +10837,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>692.95</v>
+        <v>720.2</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>668.35</v>
+        <v>673.29</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>634.01</v>
+        <v>637.39</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>605.48</v>
+        <v>607.0599999999999</v>
       </c>
       <c r="G231" s="14" t="inlineStr">
         <is>
@@ -10881,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>176.02</v>
+        <v>176.56</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>176.01</v>
+        <v>176.06</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>182.31</v>
+        <v>182.08</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>215.36</v>
+        <v>214.97</v>
       </c>
       <c r="G232" s="14" t="inlineStr">
         <is>
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>5646</v>
+        <v>5592</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>5734.98</v>
+        <v>5709.02</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>5850.66</v>
+        <v>5830.66</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>5760.08</v>
+        <v>5756.76</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>322.55</v>
+        <v>325.3</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>336.01</v>
+        <v>334.99</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>338.5</v>
+        <v>337.98</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>385.29</v>
+        <v>384.69</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11013,20 +11013,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>26.74</v>
+        <v>26.37</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>28.59</v>
+        <v>28.38</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>30.25</v>
+        <v>30.1</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>35.21</v>
+        <v>35.48</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>187.3</v>
+        <v>188.33</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>191.77</v>
+        <v>191.44</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>197.53</v>
+        <v>197.17</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>211.67</v>
+        <v>211.61</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,29 +11101,29 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>126.28</v>
+        <v>130.09</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>128.2</v>
+        <v>128.52</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>129.05</v>
+        <v>129.13</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>123.9</v>
-      </c>
-      <c r="G237" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H237" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>124.17</v>
+      </c>
+      <c r="G237" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H237" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I237" s="14" t="inlineStr">
@@ -11145,17 +11145,17 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>7.48</v>
+        <v>7.05</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>8.67</v>
+        <v>8.52</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>10.26</v>
+        <v>10.14</v>
       </c>
       <c r="F238" s="11" t="n">
         <v>13.13</v>
@@ -11189,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>95.2</v>
+        <v>94.73</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>102.02</v>
+        <v>101.32</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>106.84</v>
+        <v>106.37</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>120.57</v>
+        <v>120.63</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11233,24 +11233,24 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>297.65</v>
+        <v>304.25</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>303.88</v>
+        <v>303.91</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>305.5</v>
+        <v>305.45</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>328.04</v>
-      </c>
-      <c r="G240" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>328.51</v>
+      </c>
+      <c r="G240" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H240" s="12" t="inlineStr">
@@ -11277,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>461.5</v>
+        <v>460.65</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>490.84</v>
+        <v>487.97</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>515.98</v>
+        <v>513.8099999999999</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>620.27</v>
+        <v>618.8099999999999</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11321,20 +11321,20 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>64.05</v>
+        <v>63.81</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>66.79000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>66.88</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>72.2</v>
+        <v>72.06</v>
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
@@ -11365,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>1520.5</v>
+        <v>1511.4</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>1520.57</v>
+        <v>1519.7</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>1535.42</v>
+        <v>1534.48</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>1697.24</v>
+        <v>1695.03</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>117.67</v>
+        <v>120.81</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>125.22</v>
+        <v>124.8</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>130.33</v>
+        <v>129.95</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>135.74</v>
+        <v>135.56</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>66.29000000000001</v>
+        <v>66.84</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>68.97</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>70.31</v>
+        <v>70.17</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>76.33</v>
+        <v>76.22</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>719.9</v>
+        <v>718.95</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>742.4299999999999</v>
+        <v>737.99</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>754.98</v>
+        <v>752.13</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>761.1900000000001</v>
+        <v>760.35</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,20 +11541,20 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>438.5</v>
+        <v>445.95</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>425.35</v>
+        <v>427.32</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>425.84</v>
+        <v>426.63</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>429.41</v>
+        <v>429.54</v>
       </c>
       <c r="G247" s="14" t="inlineStr">
         <is>
@@ -11585,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>569.3</v>
+        <v>567.6</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>635.11</v>
+        <v>628.6799999999999</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>709.52</v>
+        <v>703.95</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>808.75</v>
+        <v>806.9299999999999</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>3990.4</v>
+        <v>3989.5</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>4161.1</v>
+        <v>4144.76</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>4321.28</v>
+        <v>4308.27</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>4494.41</v>
+        <v>4486.77</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11673,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>678</v>
+        <v>689.6</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>715.85</v>
+        <v>713.35</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>743.04</v>
+        <v>740.9400000000001</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>780.64</v>
+        <v>780.91</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11717,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>413.25</v>
+        <v>404.5</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>414.39</v>
+        <v>411.96</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>425.52</v>
+        <v>423.59</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>432.19</v>
+        <v>431.56</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 17-Sep-2026  15:25:26    |    Closing Price Date: 17-Sep-2026</t>
+          <t>Scan Run: 18-Sep-2026  14:46:12    |    Closing Price Date: 18-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="C5" s="5" t="n">
         <v>38.8</v>
       </c>
+      <c r="C5" s="6" t="n">
+        <v>43.6</v>
+      </c>
       <c r="D5" s="6" t="n">
-        <v>52</v>
+        <v>53.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>17-Sep-2026  15:25:26</t>
+          <t>18-Sep-2026  14:46:12</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 28.8% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 38.8% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 38.8% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 43.6% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 53.6% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 72 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 97 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 97 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 109 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 130 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 134 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>243.06</v>
+        <v>243.88</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>251.27</v>
+        <v>250.08</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>263.05</v>
+        <v>261.68</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>295.84</v>
+        <v>294.89</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,24 +805,24 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>330.15</v>
+        <v>325.4</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>329</v>
+        <v>328.56</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>323.37</v>
+        <v>323.48</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>325.11</v>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>325.26</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr">
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>6220.5</v>
+        <v>6292.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>5919.21</v>
+        <v>5954.76</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5339.09</v>
+        <v>5376.48</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>4322.33</v>
+        <v>4341.76</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -893,24 +893,24 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>722.1</v>
+        <v>763.75</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>738.13</v>
+        <v>740.5700000000001</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>694.01</v>
+        <v>696.75</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>551.79</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>554.24</v>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
@@ -937,24 +937,24 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>279.15</v>
+        <v>265</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>277.51</v>
+        <v>276.32</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>254.82</v>
+        <v>255.21</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>165.51</v>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>166.47</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>376.05</v>
+        <v>366.8</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>355.02</v>
+        <v>353.92</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>322.2</v>
+        <v>322.61</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>226.63</v>
+        <v>227.51</v>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>7060</v>
+        <v>7202</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>7066.1</v>
+        <v>7102.67</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>6905.04</v>
+        <v>6936.83</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5491.54</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>5526.79</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>831.2</v>
+        <v>827.5</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>839.78</v>
+        <v>838.61</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>781.58</v>
+        <v>783.38</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>630.03</v>
+        <v>632</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>313.9</v>
+        <v>313.8</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>320.16</v>
+        <v>320.15</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>306.01</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>257.38</v>
+        <v>257.65</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4811</v>
+        <v>5044.5</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>5212.74</v>
+        <v>5234.98</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>5376.05</v>
+        <v>5385.21</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>4536.02</v>
+        <v>4538.13</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>179.23</v>
+        <v>178.24</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>173.89</v>
+        <v>174.28</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>171.67</v>
+        <v>171.97</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>165.53</v>
+        <v>165.95</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,24 +1245,24 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2605.3</v>
+        <v>2790.3</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2737.01</v>
+        <v>2742.08</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>2604.33</v>
+        <v>2611.63</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>2145.05</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2152.13</v>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>611.5</v>
+        <v>632.4</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>595.3</v>
+        <v>601.35</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>582.05</v>
+        <v>585.71</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>573.5599999999999</v>
+        <v>575.0700000000001</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2230</v>
+        <v>2537.7</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>2193.28</v>
+        <v>2231.7</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>2026.29</v>
+        <v>2049.95</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1517.92</v>
+        <v>1529.04</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1377,29 +1377,29 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>3490.8</v>
+        <v>3444.9</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>3476.22</v>
+        <v>3468.37</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>3489.99</v>
+        <v>3485.08</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3225.51</v>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3225.43</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>378.25</v>
+        <v>370.7</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>395.17</v>
+        <v>394.45</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>392.04</v>
+        <v>391.74</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>336.16</v>
+        <v>335.76</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,24 +1465,24 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>752.5</v>
+        <v>767.5</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>758.36</v>
+        <v>760.26</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>725.89</v>
+        <v>728.27</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>629.62</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>631.16</v>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>827.45</v>
+        <v>818.8</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>771.8099999999999</v>
+        <v>780.6900000000001</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>680.98</v>
+        <v>691.05</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>440.27</v>
+        <v>447.56</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>213.39</v>
+        <v>215.13</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>196.71</v>
+        <v>198.46</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>181.49</v>
+        <v>182.81</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>163.25</v>
+        <v>163.77</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>12.35</v>
+        <v>12.72</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>12.12</v>
+        <v>12.18</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10.32</v>
+        <v>10.36</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>229.33</v>
+        <v>231.67</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>235.11</v>
+        <v>234.78</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>234.63</v>
+        <v>234.51</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>198.24</v>
+        <v>198.57</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,24 +1685,24 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>2074.8</v>
+        <v>2132.6</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>2081.5</v>
+        <v>2086.37</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>2010.68</v>
+        <v>2015.46</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1710.7</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1714.78</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>218.17</v>
+        <v>224.24</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>229.93</v>
+        <v>230.29</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>228.41</v>
+        <v>228.7</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>208.48</v>
+        <v>208.67</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>63.97</v>
+        <v>65.02</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>66.33</v>
+        <v>66.3</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>66.15000000000001</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>60.28</v>
+        <v>60.24</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>159.41</v>
+        <v>156.95</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>165.77</v>
+        <v>165.54</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>165.41</v>
+        <v>165.31</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>150.34</v>
+        <v>150.4</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>174.54</v>
+        <v>179.24</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>183.17</v>
+        <v>183.62</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>186.85</v>
+        <v>187.04</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>188.74</v>
+        <v>188.82</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>495.15</v>
+        <v>489.25</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>521.46</v>
+        <v>520.9</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>540.72</v>
+        <v>540.48</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>539.5599999999999</v>
+        <v>539.24</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>353</v>
+        <v>351.65</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>348.6</v>
+        <v>348.8</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>326.36</v>
+        <v>328.16</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>265.91</v>
+        <v>267.4</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1370.9</v>
+        <v>1372.7</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>1403.84</v>
+        <v>1404.16</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>1336.02</v>
+        <v>1342.42</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1036.7</v>
+        <v>1044.19</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
+        <v>369.35</v>
+      </c>
+      <c r="D31" s="11" t="n">
         <v>362.55</v>
       </c>
-      <c r="D31" s="11" t="n">
-        <v>360.67</v>
-      </c>
       <c r="E31" s="11" t="n">
-        <v>343.23</v>
+        <v>346.15</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>303.69</v>
+        <v>305.72</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>543.85</v>
+        <v>568.7</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>534.97</v>
+        <v>537.75</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>514.8099999999999</v>
+        <v>517.54</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>468.17</v>
+        <v>469.12</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,24 +2125,24 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1623.3</v>
+        <v>1630</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1629.4</v>
+        <v>1629.61</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>1555.91</v>
+        <v>1558.79</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1255.19</v>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1258.81</v>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>793.3</v>
+        <v>783.7</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>794.37</v>
+        <v>793.45</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>735.87</v>
+        <v>735.49</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>544.64</v>
+        <v>544.63</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,17 +2213,17 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>601.15</v>
+        <v>604.75</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>609.1</v>
+        <v>608.6799999999999</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>607.87</v>
+        <v>607.75</v>
       </c>
       <c r="F35" s="11" t="n">
         <v>599.89</v>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>520.1</v>
+        <v>527.3</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>530.25</v>
+        <v>530.9400000000001</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>527.39</v>
+        <v>527.67</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>481.13</v>
+        <v>481.27</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>182.53</v>
+        <v>185.4</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>194.23</v>
+        <v>194.5</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>199.88</v>
+        <v>200</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>202.2</v>
+        <v>202.4</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>770.85</v>
+        <v>774.45</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>813.27</v>
+        <v>813.62</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>874.74</v>
+        <v>874.88</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>965.8099999999999</v>
+        <v>966.2</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>517.6</v>
+        <v>525.35</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>557.1900000000001</v>
+        <v>557.9299999999999</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>600.84</v>
+        <v>601.15</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>622.26</v>
+        <v>622.23</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>342.35</v>
+        <v>348</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>350.71</v>
+        <v>351.55</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>355.36</v>
+        <v>355.75</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>344.06</v>
+        <v>343.98</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2458,9 +2458,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr">
@@ -2477,29 +2477,29 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>203.02</v>
+        <v>206.92</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>208.49</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>205.84</v>
+        <v>206.08</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>174.87</v>
+        <v>175.8</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>80.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>83.97</v>
+        <v>83.66</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>84.84</v>
+        <v>84.66</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>72.48999999999999</v>
+        <v>72.69</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>220.81</v>
+        <v>221.55</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>232.25</v>
+        <v>232.19</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>223.17</v>
+        <v>223.5</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>216.88</v>
+        <v>216.92</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1607.8</v>
+        <v>1631.2</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1676.57</v>
+        <v>1672.25</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1672.03</v>
+        <v>1670.43</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1395.39</v>
+        <v>1397.38</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>327.9</v>
+        <v>321.55</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>357.66</v>
+        <v>354.22</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>372.23</v>
+        <v>370.25</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>403.66</v>
+        <v>402.87</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>559.25</v>
+        <v>555.8</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>571.0599999999999</v>
+        <v>567.17</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>566.86</v>
+        <v>565.85</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>493.11</v>
+        <v>494.95</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>163.37</v>
+        <v>165.42</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>167.92</v>
+        <v>167.68</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>174.67</v>
+        <v>174.3</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>211.07</v>
+        <v>210.61</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,24 +2785,24 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1205.4</v>
+        <v>1263.5</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1209.01</v>
+        <v>1216.42</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1135.18</v>
+        <v>1144.25</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1037.68</v>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1041.59</v>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>891.45</v>
+        <v>895.75</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>897.0700000000001</v>
+        <v>899.54</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>860.88</v>
+        <v>863.6799999999999</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>716.09</v>
+        <v>718.29</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>174.64</v>
+        <v>171.32</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>174.92</v>
+        <v>174.5</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>178.8</v>
+        <v>178.45</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>181.76</v>
+        <v>181.54</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>271.75</v>
+        <v>271.85</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>278.6</v>
+        <v>277.96</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>290.75</v>
+        <v>290.01</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>301.38</v>
+        <v>300.45</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>449.35</v>
+        <v>459.5</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>499.43</v>
+        <v>500.39</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>528.91</v>
+        <v>529.3</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>539.21</v>
+        <v>538.8099999999999</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4017.5</v>
+        <v>4259.9</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>3926.13</v>
+        <v>3953.53</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>3681.63</v>
+        <v>3701.01</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2815.36</v>
+        <v>2829.35</v>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
@@ -3049,24 +3049,24 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>549.05</v>
+        <v>564.4</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>556.08</v>
+        <v>556.71</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>540.45</v>
+        <v>542.34</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>531.5599999999999</v>
-      </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>532.08</v>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr">
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>1862.2</v>
+        <v>1895.6</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>1954.45</v>
+        <v>1938.09</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>1995.95</v>
+        <v>1984.92</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1843.03</v>
+        <v>1844.58</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>185.07</v>
+        <v>196.28</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>180.3</v>
+        <v>182.53</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>164.9</v>
+        <v>167.54</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>134.52</v>
+        <v>136.18</v>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
@@ -3181,29 +3181,29 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>532.55</v>
+        <v>566.2</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>553.26</v>
+        <v>554.5</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>545.28</v>
+        <v>546.1</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>500.45</v>
-      </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>500.6</v>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr">
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1630.1</v>
+        <v>1588.2</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>1682.45</v>
+        <v>1678.46</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>1700.64</v>
+        <v>1698.99</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1788.03</v>
+        <v>1790.39</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3269,24 +3269,24 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>156.67</v>
+        <v>161.98</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>157.88</v>
+        <v>158.23</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>162.12</v>
+        <v>162.09</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>170.71</v>
-      </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>170.54</v>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>3107.2</v>
+        <v>3149.8</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>3250.83</v>
+        <v>3254.89</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>3162.12</v>
+        <v>3163.79</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2700.54</v>
+        <v>2700.71</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>244.5</v>
+        <v>249.65</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>257.61</v>
+        <v>258.1</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>260.06</v>
+        <v>260.26</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>238.11</v>
+        <v>238.6</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>492.6</v>
+        <v>464.4</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>500.28</v>
+        <v>496.93</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>512.85</v>
+        <v>510.72</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>572.0599999999999</v>
+        <v>570.35</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>586.3</v>
+        <v>597.45</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>579.79</v>
+        <v>582</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>569.03</v>
+        <v>571.13</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>525.4400000000001</v>
+        <v>527.15</v>
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>21.56</v>
+        <v>21.77</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>22.42</v>
+        <v>22.36</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>22.42</v>
+        <v>22.39</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>22.68</v>
+        <v>22.67</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>199.64</v>
+        <v>200.01</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>201.19</v>
+        <v>201.07</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>204.69</v>
+        <v>204.51</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>204.97</v>
+        <v>204.87</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,24 +3577,24 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>191.72</v>
+        <v>197.35</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>194.1</v>
+        <v>194.41</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>200.15</v>
+        <v>200.04</v>
       </c>
       <c r="F66" s="11" t="n">
         <v>192.72</v>
       </c>
-      <c r="G66" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
@@ -3602,9 +3602,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I66" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J66" s="13" t="inlineStr">
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>674.05</v>
+        <v>669</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>677.78</v>
+        <v>677.88</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>666.41</v>
+        <v>667.2</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>655.9299999999999</v>
+        <v>656.41</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>1852.3</v>
+        <v>1811.2</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>1716.47</v>
+        <v>1719.68</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1677.99</v>
+        <v>1680.59</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1614.22</v>
+        <v>1617.17</v>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
@@ -3709,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>657.25</v>
+        <v>648.35</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>684.33</v>
+        <v>680.9</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>708.98</v>
+        <v>706.6</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>824.98</v>
+        <v>823.64</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>2014.8</v>
+        <v>2098.8</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>2090.87</v>
+        <v>2098.87</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>2001.38</v>
+        <v>2004.68</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1640.34</v>
+        <v>1641.04</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>6502.5</v>
+        <v>6724.5</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>6897.76</v>
+        <v>6910.66</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>6840.71</v>
+        <v>6851.03</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>5543.63</v>
+        <v>5557.97</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3841,24 +3841,24 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>45.88</v>
+        <v>46.07</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>45.95</v>
+        <v>45.97</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>45.61</v>
+        <v>45.62</v>
       </c>
       <c r="F72" s="11" t="n">
         <v>41.82</v>
       </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H72" s="14" t="inlineStr">
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>464.1</v>
+        <v>460.95</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>484.03</v>
+        <v>483.73</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>503.06</v>
+        <v>502.93</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>580.77</v>
+        <v>580.25</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>145.59</v>
+        <v>146.85</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>146.95</v>
+        <v>146.94</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>140.13</v>
+        <v>140.39</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>150.34</v>
+        <v>150.3</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>2148.9</v>
+        <v>2171.5</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>2278.91</v>
+        <v>2281.06</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2214.4</v>
+        <v>2215.29</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1801.64</v>
+        <v>1801.94</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>313.7</v>
+        <v>291.25</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>345.44</v>
+        <v>333.56</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>363.83</v>
+        <v>354.52</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>369.45</v>
+        <v>363.84</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>741.7</v>
+        <v>743.1</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>774.3200000000001</v>
+        <v>770.16</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>809.26</v>
+        <v>804.9400000000001</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>883.66</v>
+        <v>881.8099999999999</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,29 +4105,29 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>328.35</v>
+        <v>336.15</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>321.88</v>
+        <v>322.8</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>331.43</v>
+        <v>331.14</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>363.83</v>
+        <v>363.14</v>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I78" s="12" t="inlineStr">
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>2702.6</v>
+        <v>2859.1</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>2653.45</v>
+        <v>2673.64</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>2568.27</v>
+        <v>2578.97</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2503.32</v>
+        <v>2506.16</v>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>179.22</v>
+        <v>176.06</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>186.91</v>
+        <v>185.46</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>197.49</v>
+        <v>196.13</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>212.39</v>
+        <v>212.33</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,24 +4237,24 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>162.59</v>
+        <v>160.35</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>160.14</v>
+        <v>160.36</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>155.86</v>
+        <v>156.44</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>154.71</v>
-      </c>
-      <c r="G81" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>154.9</v>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H81" s="14" t="inlineStr">
@@ -4281,24 +4281,24 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>72.13</v>
+        <v>74.09</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>73.51000000000001</v>
+        <v>73.52</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>74.31</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>70.23</v>
-      </c>
-      <c r="G82" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>70.26000000000001</v>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
@@ -4325,20 +4325,20 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>193.16</v>
+        <v>193.92</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>197.63</v>
+        <v>197.7</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>203.91</v>
+        <v>203.94</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>183.61</v>
+        <v>183.66</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>584.85</v>
+        <v>588.9</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>559.41</v>
+        <v>562.22</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>541.33</v>
+        <v>543.2</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>499.87</v>
+        <v>500.77</v>
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
@@ -4413,20 +4413,20 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>16.32</v>
+        <v>16.08</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>15.64</v>
+        <v>15.74</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>15.75</v>
+        <v>15.79</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>16.12</v>
+        <v>16.13</v>
       </c>
       <c r="G85" s="14" t="inlineStr">
         <is>
@@ -4438,9 +4438,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I85" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I85" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J85" s="13" t="inlineStr">
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>811.05</v>
+        <v>819.65</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>849.34</v>
+        <v>844.4400000000001</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>890.7</v>
+        <v>885.59</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>948.34</v>
+        <v>945.62</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>2395.6</v>
+        <v>2488.4</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>2245.45</v>
+        <v>2280.55</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>2148.84</v>
+        <v>2173.59</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1805.46</v>
+        <v>1824.4</v>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
@@ -4545,29 +4545,29 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>656.6</v>
+        <v>657.7</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>655.03</v>
+        <v>654.72</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>657.33</v>
+        <v>656.98</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>625.03</v>
+        <v>625.2</v>
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H88" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>1273.7</v>
+        <v>1252.2</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>1312.08</v>
+        <v>1306.53</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>1354.82</v>
+        <v>1351.11</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1309.4</v>
+        <v>1308.87</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4633,24 +4633,24 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>128.34</v>
+        <v>136.25</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>128.45</v>
+        <v>129.21</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>124.25</v>
+        <v>124.56</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>116.55</v>
-      </c>
-      <c r="G90" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>116.58</v>
+      </c>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr">
@@ -4677,24 +4677,24 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>567.6</v>
+        <v>544.25</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>553.16</v>
+        <v>553.37</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>510.32</v>
+        <v>512.25</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>501.23</v>
-      </c>
-      <c r="G91" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>501.95</v>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H91" s="14" t="inlineStr">
@@ -4721,24 +4721,24 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>1778.3</v>
+        <v>1751.1</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>1771.77</v>
+        <v>1769.8</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>1646.77</v>
+        <v>1650.86</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1202.16</v>
-      </c>
-      <c r="G92" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1207.63</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr">
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>67</v>
+        <v>68.84</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>71.67</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>73.73999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>69.61</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>319.7</v>
+        <v>320.15</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>320.34</v>
+        <v>321.07</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>299.95</v>
+        <v>301.96</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>244.13</v>
+        <v>246.32</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>273.3</v>
+        <v>278.1</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>287.27</v>
+        <v>286.4</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>316.13</v>
+        <v>314.64</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>405.08</v>
+        <v>403.81</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>541.6</v>
+        <v>552.6</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>553.25</v>
+        <v>554.4299999999999</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>538.9400000000001</v>
+        <v>540.71</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>456.25</v>
+        <v>458.21</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4941,29 +4941,29 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>766.4</v>
+        <v>801.15</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>761.75</v>
+        <v>765.5</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>783.3099999999999</v>
+        <v>784.01</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>722.55</v>
+        <v>723.24</v>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H97" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H97" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I97" s="14" t="inlineStr">
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>231.04</v>
+        <v>230.93</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>237.22</v>
+        <v>236.68</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>251.82</v>
+        <v>251.12</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>298.05</v>
+        <v>297.55</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1770.8</v>
+        <v>1811.4</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1838.58</v>
+        <v>1839.43</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1856.18</v>
+        <v>1856.4</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1785.71</v>
+        <v>1785.69</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5054,9 +5054,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I99" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J99" s="13" t="inlineStr">
@@ -5073,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>218.51</v>
+        <v>218.35</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>216.9</v>
+        <v>217.03</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>205.04</v>
+        <v>205.57</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>184.72</v>
+        <v>184.92</v>
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>865.45</v>
+        <v>858.4</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>890.8</v>
+        <v>887.3</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>891.03</v>
+        <v>889.48</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>753.4</v>
+        <v>754.47</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>418.05</v>
+        <v>430.6</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>404.21</v>
+        <v>405.41</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>390.42</v>
+        <v>390.91</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>369.59</v>
+        <v>370.06</v>
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>654</v>
+        <v>659.65</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>668.59</v>
+        <v>666.9299999999999</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>705.17</v>
+        <v>701.67</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>789.23</v>
+        <v>786.33</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,24 +5249,24 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>10735</v>
+        <v>10879</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>10770.85</v>
+        <v>10803.35</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>10377.8</v>
+        <v>10408.86</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>9427.09</v>
-      </c>
-      <c r="G104" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>9440.200000000001</v>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr">
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>693.85</v>
+        <v>698.65</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>728.35</v>
+        <v>729.46</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>755.21</v>
+        <v>755.13</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>716.1799999999999</v>
+        <v>716.08</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>88.94</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>91.93000000000001</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>92.22</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>85.68000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,20 +5381,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>2018</v>
+        <v>2102.7</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>1959.12</v>
+        <v>1967.19</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>1851.42</v>
+        <v>1854.74</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1625.68</v>
+        <v>1625.05</v>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
@@ -5425,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>958.35</v>
+        <v>1021.1</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>909.09</v>
+        <v>915.0700000000001</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>806.72</v>
+        <v>809.1799999999999</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>577.99</v>
+        <v>579.0599999999999</v>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
@@ -5469,20 +5469,20 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>1200.2</v>
+        <v>1219.8</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1116.98</v>
+        <v>1126.77</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>1074.1</v>
+        <v>1079.81</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1005.84</v>
+        <v>1009.89</v>
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
@@ -5513,24 +5513,24 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>705</v>
+        <v>685.6</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>696.22</v>
+        <v>694.37</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>732.88</v>
+        <v>732.12</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>876.02</v>
-      </c>
-      <c r="G110" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>877.63</v>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
@@ -5557,20 +5557,20 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>435.5</v>
+        <v>447.35</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>434.92</v>
+        <v>437.03</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>418.08</v>
+        <v>419.78</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>348.37</v>
+        <v>349.59</v>
       </c>
       <c r="G111" s="14" t="inlineStr">
         <is>
@@ -5601,20 +5601,20 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>900.65</v>
+        <v>906.3</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>863.95</v>
+        <v>868.1900000000001</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>852.98</v>
+        <v>855.3</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>789.6</v>
+        <v>790.86</v>
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>424.35</v>
+        <v>442.3</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>412.96</v>
+        <v>414.67</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>402.81</v>
+        <v>403.51</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>399.1</v>
+        <v>399.13</v>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>204.14</v>
+        <v>203.8</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>207.14</v>
+        <v>207.11</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>214.5</v>
+        <v>214.49</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>242.44</v>
+        <v>242.51</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>71.73999999999999</v>
+        <v>72.94</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>77.03</v>
+        <v>76.64</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>84.45999999999999</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>94.52</v>
+        <v>94.42</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>248.7</v>
+        <v>263.7</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>562.67</v>
+        <v>537</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>809.85</v>
+        <v>789.52</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>939.71</v>
+        <v>932.42</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>371</v>
+        <v>373.1</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>344.23</v>
+        <v>346.98</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>319.08</v>
+        <v>321.2</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>316.94</v>
+        <v>317.5</v>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
@@ -5865,24 +5865,24 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>3320.2</v>
+        <v>3501.6</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>3326.62</v>
+        <v>3345.18</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>3226.66</v>
+        <v>3238.77</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>2899.26</v>
-      </c>
-      <c r="G118" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2905.23</v>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H118" s="14" t="inlineStr">
@@ -5909,24 +5909,24 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>4385.4</v>
+        <v>4576.6</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>4451.96</v>
+        <v>4468.59</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>4342.94</v>
+        <v>4355.25</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>3673.65</v>
-      </c>
-      <c r="G119" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3684.72</v>
+      </c>
+      <c r="G119" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H119" s="14" t="inlineStr">
@@ -5953,17 +5953,17 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>670.2</v>
+        <v>681.85</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>667.26</v>
+        <v>668.37</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>694.4400000000001</v>
+        <v>694.9</v>
       </c>
       <c r="F120" s="11" t="n">
         <v>756.33</v>
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>278.75</v>
+        <v>284.45</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>300.47</v>
+        <v>300.14</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>333.74</v>
+        <v>332.53</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>395.92</v>
+        <v>395.49</v>
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>490.75</v>
+        <v>510.4</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>511.26</v>
+        <v>511.04</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>535.96</v>
+        <v>534.11</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>596.83</v>
+        <v>594.8099999999999</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>618.9</v>
+        <v>656.25</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>618.34</v>
+        <v>621.9</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>586.08</v>
+        <v>587.54</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>506.99</v>
+        <v>507.03</v>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
@@ -6129,29 +6129,29 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1392.8</v>
+        <v>1446.2</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1510.95</v>
+        <v>1504.78</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1420.18</v>
+        <v>1421.2</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1156.57</v>
+        <v>1159.32</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H124" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H124" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
@@ -6173,20 +6173,20 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>211.98</v>
+        <v>212.12</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>218.02</v>
+        <v>217.27</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>222.37</v>
+        <v>221.78</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>239.25</v>
+        <v>238.73</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6217,24 +6217,24 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>448.95</v>
+        <v>484.05</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>477.83</v>
+        <v>478.42</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>495.08</v>
+        <v>494.65</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>534.5599999999999</v>
-      </c>
-      <c r="G126" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>534.0599999999999</v>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
@@ -6261,29 +6261,29 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>395.4</v>
+        <v>392.45</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>410.77</v>
+        <v>411.27</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>395.38</v>
+        <v>396.38</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>373.56</v>
+        <v>374.31</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H127" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I127" s="14" t="inlineStr">
@@ -6305,29 +6305,29 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>790.05</v>
+        <v>808.15</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>813.88</v>
+        <v>815.65</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>794.71</v>
+        <v>796.45</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>735.73</v>
+        <v>738.9</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H128" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H128" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>766.7</v>
+        <v>783.7</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>757.74</v>
+        <v>760.21</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>721.28</v>
+        <v>723.73</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>602.61</v>
+        <v>604.97</v>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>218.44</v>
+        <v>228.15</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>185.9</v>
+        <v>189.94</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>175.18</v>
+        <v>177.38</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>159.92</v>
+        <v>160.8</v>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
@@ -6437,24 +6437,24 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>687.15</v>
+        <v>708.25</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>697.72</v>
+        <v>698.87</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>686.8200000000001</v>
+        <v>687.71</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>646.23</v>
-      </c>
-      <c r="G131" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>646.97</v>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H131" s="14" t="inlineStr">
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>420.1</v>
+        <v>421.7</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>430.33</v>
+        <v>428.54</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>434.8</v>
+        <v>433.63</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>471.42</v>
+        <v>470.23</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>727.55</v>
+        <v>727.75</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>771.58</v>
+        <v>771.15</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>781.8200000000001</v>
+        <v>781.48</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>767.5</v>
+        <v>767.87</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6569,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>1633.3</v>
+        <v>1666.1</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>1758.77</v>
+        <v>1749.95</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>1733.25</v>
+        <v>1730.62</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1465.77</v>
+        <v>1467.76</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>234.35</v>
+        <v>234</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>245.87</v>
+        <v>244.74</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>251.16</v>
+        <v>250.49</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>259.75</v>
+        <v>259.49</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>96.12</v>
+        <v>95.12</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>96.81999999999999</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>90.25</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>76.98999999999999</v>
+        <v>77.22</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>405.45</v>
+        <v>418.1</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>386.52</v>
+        <v>388.44</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>366.99</v>
+        <v>368.34</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>370.38</v>
+        <v>370.46</v>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1900.9</v>
+        <v>1937.3</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>2061.33</v>
+        <v>2060.27</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>2162.42</v>
+        <v>2159.17</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>2165.1</v>
+        <v>2164.46</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>633.25</v>
+        <v>636.95</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>611.4400000000001</v>
+        <v>613.87</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>608.14</v>
+        <v>609.27</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>557.0700000000001</v>
+        <v>557.8</v>
       </c>
       <c r="G139" s="14" t="inlineStr">
         <is>
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>317.1</v>
+        <v>316.05</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>329.62</v>
+        <v>329.4</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>334.08</v>
+        <v>333.98</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>348.23</v>
+        <v>347.69</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,29 +6877,29 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>408.95</v>
+        <v>418.65</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>430.88</v>
+        <v>429.71</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>409.54</v>
+        <v>409.9</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>316.86</v>
+        <v>317.87</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H141" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H141" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I141" s="14" t="inlineStr">
@@ -6921,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>1105.4</v>
+        <v>1155</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>1173.21</v>
+        <v>1171.48</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>1066.87</v>
+        <v>1070.33</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>846.4299999999999</v>
+        <v>849.51</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>126.96</v>
+        <v>125.03</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>127.31</v>
+        <v>127.21</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>127.7</v>
+        <v>127.6</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>123.13</v>
+        <v>123.18</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>210.4</v>
+        <v>214.03</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>217.26</v>
+        <v>217.72</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>219.64</v>
+        <v>219.82</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>215.04</v>
+        <v>215.22</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>277.75</v>
+        <v>280.05</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>290.59</v>
+        <v>290.01</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>295.66</v>
+        <v>295.29</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>284.3</v>
+        <v>284.38</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>109.84</v>
+        <v>109.08</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>114.72</v>
+        <v>112.7</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>120.04</v>
+        <v>117.94</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>129.12</v>
+        <v>127.24</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>152.27</v>
+        <v>155.25</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>156.35</v>
+        <v>156.64</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>155.26</v>
+        <v>155.38</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>148.64</v>
+        <v>148.75</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>410.2</v>
+        <v>408.75</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>428.18</v>
+        <v>426.33</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>453.76</v>
+        <v>452</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>519.05</v>
+        <v>517.34</v>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
@@ -7229,20 +7229,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>92.13</v>
+        <v>92.31</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>94.12</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>96.48999999999999</v>
+        <v>96.13</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>103.6</v>
+        <v>103.23</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>2169.6</v>
+        <v>2201.8</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>2144.04</v>
+        <v>2149.55</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>2080.92</v>
+        <v>2085.66</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1809.81</v>
+        <v>1813.71</v>
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>2339</v>
+        <v>2371.4</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>2422.85</v>
+        <v>2420.16</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>2486.64</v>
+        <v>2483</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>2505.74</v>
+        <v>2503.23</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,20 +7361,20 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>1072.4</v>
+        <v>1139.5</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>960.8099999999999</v>
+        <v>982.09</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>908.8200000000001</v>
+        <v>923.33</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>800.3099999999999</v>
+        <v>807.25</v>
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
@@ -7405,24 +7405,24 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>1939.1</v>
+        <v>1966.9</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>1940</v>
+        <v>1949.38</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>1810.44</v>
+        <v>1819.33</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1565.21</v>
-      </c>
-      <c r="G153" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1569.95</v>
+      </c>
+      <c r="G153" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H153" s="14" t="inlineStr">
@@ -7449,24 +7449,24 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>1666.6</v>
+        <v>1732.3</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>1706.96</v>
+        <v>1713.22</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>1530.91</v>
+        <v>1533.49</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1289.15</v>
-      </c>
-      <c r="G154" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1290</v>
+      </c>
+      <c r="G154" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr">
@@ -7493,29 +7493,29 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>277.9</v>
+        <v>282.05</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>281.41</v>
+        <v>281.47</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>280.17</v>
+        <v>280.25</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>238.88</v>
-      </c>
-      <c r="G155" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H155" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>239.31</v>
+      </c>
+      <c r="G155" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H155" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I155" s="14" t="inlineStr">
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>11819</v>
+        <v>12061</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>11681.85</v>
+        <v>11717.96</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>11297.84</v>
+        <v>11327.77</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>10229.24</v>
+        <v>10237.41</v>
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>2065.9</v>
+        <v>2067.9</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>2096.7</v>
+        <v>2095.04</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>2161.52</v>
+        <v>2158.05</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>2232.35</v>
+        <v>2229.03</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,20 +7625,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>1143.1</v>
+        <v>1146.1</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>1161.16</v>
+        <v>1159.72</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>1110.54</v>
+        <v>1111.93</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>922.6</v>
+        <v>925.98</v>
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>673</v>
+        <v>657.3</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>673.73</v>
+        <v>671.21</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>684.9</v>
+        <v>683.03</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>651.1900000000001</v>
+        <v>651.29</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>462.4</v>
+        <v>467.15</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>486.03</v>
+        <v>486.77</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>507.09</v>
+        <v>506.99</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>549.75</v>
+        <v>549.0700000000001</v>
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
@@ -7757,24 +7757,24 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>111.69</v>
+        <v>114.66</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>112.2</v>
+        <v>112.44</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>110.66</v>
+        <v>110.82</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>115.28</v>
-      </c>
-      <c r="G161" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>115.37</v>
+      </c>
+      <c r="G161" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H161" s="14" t="inlineStr">
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>407.85</v>
+        <v>417.3</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>426.55</v>
+        <v>425.71</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>421.75</v>
+        <v>421.68</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>398.77</v>
+        <v>399.01</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>152.27</v>
+        <v>151.92</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>154.29</v>
+        <v>154.07</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>155.29</v>
+        <v>155.15</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>163.29</v>
+        <v>163.23</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,24 +7889,24 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>510.4</v>
+        <v>530.2</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>522.98</v>
+        <v>520.9400000000001</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>546.16</v>
+        <v>542.6</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>634.03</v>
-      </c>
-      <c r="G164" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>630.73</v>
+      </c>
+      <c r="G164" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H164" s="12" t="inlineStr">
@@ -7933,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>715.25</v>
+        <v>724.05</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>710.42</v>
+        <v>711.26</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>668.58</v>
+        <v>668.9299999999999</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>564.38</v>
+        <v>564.3</v>
       </c>
       <c r="G165" s="14" t="inlineStr">
         <is>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>193.84</v>
+        <v>195.07</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>198.85</v>
+        <v>198.97</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>201.8</v>
+        <v>201.84</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>228.34</v>
+        <v>228.46</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>211.35</v>
+        <v>209.9</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>219.02</v>
+        <v>218.45</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>227.82</v>
+        <v>227.28</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>229.44</v>
+        <v>229.38</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,24 +8065,24 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>519.9</v>
+        <v>547.35</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>526.0599999999999</v>
+        <v>528.09</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>508.21</v>
+        <v>509.75</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>476</v>
-      </c>
-      <c r="G168" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>476.71</v>
+      </c>
+      <c r="G168" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr">
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>428.35</v>
+        <v>431.8</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>423.76</v>
+        <v>424.67</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>414.86</v>
+        <v>415.87</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>405.64</v>
+        <v>406.32</v>
       </c>
       <c r="G169" s="14" t="inlineStr">
         <is>
@@ -8153,20 +8153,20 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>846.15</v>
+        <v>861.55</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>836.28</v>
+        <v>838.36</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>777.33</v>
+        <v>780.1900000000001</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>652.02</v>
+        <v>654.29</v>
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
@@ -8197,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>425.05</v>
+        <v>428.1</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>442.26</v>
+        <v>442.04</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>448.87</v>
+        <v>448.58</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>459.57</v>
+        <v>459.63</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>1098.9</v>
+        <v>1099.7</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>1118.9</v>
+        <v>1120.48</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>1099.15</v>
+        <v>1101.47</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>1045.59</v>
+        <v>1047.17</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>139.55</v>
+        <v>138.87</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>178.3</v>
+        <v>173.74</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>200.31</v>
+        <v>196.98</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>224.8</v>
+        <v>223.56</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,34 +8329,34 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>501.6</v>
+        <v>522.15</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>537.52</v>
+        <v>535.91</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>519.22</v>
+        <v>519.1900000000001</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>518.14</v>
+        <v>518.11</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H174" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I174" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H174" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I174" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J174" s="13" t="inlineStr">
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>610</v>
+        <v>590.1</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>576.1799999999999</v>
+        <v>577.05</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>560.09</v>
+        <v>561.45</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>512.13</v>
+        <v>513.5700000000001</v>
       </c>
       <c r="G175" s="14" t="inlineStr">
         <is>
@@ -8417,20 +8417,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>155.93</v>
+        <v>156.23</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>155.21</v>
+        <v>155.3</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>157.46</v>
+        <v>157.41</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>156.87</v>
+        <v>156.98</v>
       </c>
       <c r="G176" s="14" t="inlineStr">
         <is>
@@ -8461,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>181.38</v>
+        <v>178.56</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>185.3</v>
+        <v>184.76</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>193.9</v>
+        <v>193.36</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>245.07</v>
+        <v>243.95</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>1489.8</v>
+        <v>1536.1</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>1409.09</v>
+        <v>1421.18</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>1320.36</v>
+        <v>1328.82</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1098.43</v>
+        <v>1102.05</v>
       </c>
       <c r="G178" s="14" t="inlineStr">
         <is>
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>249.89</v>
+        <v>253.02</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>247.3</v>
+        <v>249</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>246.31</v>
+        <v>247.24</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>242.1</v>
+        <v>242.47</v>
       </c>
       <c r="G179" s="14" t="inlineStr">
         <is>
@@ -8593,20 +8593,20 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>365.85</v>
+        <v>360.35</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>380.91</v>
+        <v>378.95</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>370.24</v>
+        <v>369.85</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>329.4</v>
+        <v>329.7</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>26.46</v>
+        <v>27</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>27.52</v>
+        <v>27.57</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>28.84</v>
+        <v>28.86</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>34.64</v>
+        <v>34.63</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>7.06</v>
+        <v>7.14</v>
       </c>
       <c r="D182" s="11" t="n">
         <v>7.44</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>7.98</v>
+        <v>7.99</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>9.17</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>600.55</v>
+        <v>589.4</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>629.5</v>
+        <v>624.74</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>652.51</v>
+        <v>648.99</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>628.3200000000001</v>
+        <v>626.9</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>232.45</v>
+        <v>238.8</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>266.78</v>
+        <v>267.09</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>295.74</v>
+        <v>295</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>348.87</v>
+        <v>348.07</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8813,20 +8813,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>703.35</v>
+        <v>696.35</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>737.37</v>
+        <v>731.92</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>779.26</v>
+        <v>774.01</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>888.49</v>
+        <v>883.27</v>
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
@@ -8857,34 +8857,34 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>13151</v>
+        <v>13729</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>13283.08</v>
+        <v>13339.14</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>13199.55</v>
+        <v>13229.99</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>13296.2</v>
-      </c>
-      <c r="G186" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H186" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I186" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>13312.8</v>
+      </c>
+      <c r="G186" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H186" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I186" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J186" s="13" t="inlineStr">
@@ -8901,24 +8901,24 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>336.95</v>
+        <v>345.1</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>337.02</v>
+        <v>337.98</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>336.54</v>
+        <v>336.99</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>330.16</v>
-      </c>
-      <c r="G187" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>330.11</v>
+      </c>
+      <c r="G187" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H187" s="14" t="inlineStr">
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>54.91</v>
+        <v>53.88</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>58.51</v>
+        <v>57.69</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>60.31</v>
+        <v>59.79</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>65.95</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>1387.8</v>
+        <v>1430.8</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>1367.84</v>
+        <v>1373.45</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>1296.98</v>
+        <v>1302.18</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1116.35</v>
+        <v>1120.25</v>
       </c>
       <c r="G189" s="14" t="inlineStr">
         <is>
@@ -9033,20 +9033,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>811.15</v>
+        <v>823.6</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>851.99</v>
+        <v>849.29</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>888.29</v>
+        <v>885.76</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>979.55</v>
+        <v>977.6</v>
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
@@ -9077,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>758.35</v>
+        <v>765.95</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>776.75</v>
+        <v>774.29</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>795.5</v>
+        <v>793.01</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>783.67</v>
+        <v>783.7</v>
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
@@ -9121,24 +9121,24 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>826.95</v>
+        <v>820.4</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>823.88</v>
+        <v>824.73</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>787.95</v>
+        <v>790.14</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>751.64</v>
-      </c>
-      <c r="G192" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>752.36</v>
+      </c>
+      <c r="G192" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H192" s="14" t="inlineStr">
@@ -9165,24 +9165,24 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>120.86</v>
+        <v>124.8</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>123.33</v>
+        <v>123.71</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>125.44</v>
+        <v>125.59</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>138.66</v>
-      </c>
-      <c r="G193" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>138.72</v>
+      </c>
+      <c r="G193" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H193" s="12" t="inlineStr">
@@ -9209,24 +9209,24 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>281.25</v>
+        <v>294.05</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>292.25</v>
+        <v>293.08</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>299.33</v>
+        <v>299.48</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>335.42</v>
-      </c>
-      <c r="G194" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>335.46</v>
+      </c>
+      <c r="G194" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H194" s="12" t="inlineStr">
@@ -9253,20 +9253,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>2940.3</v>
+        <v>2984.2</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>2900.6</v>
+        <v>2908.56</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>2798.79</v>
+        <v>2806.06</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>2595.89</v>
+        <v>2599.75</v>
       </c>
       <c r="G195" s="14" t="inlineStr">
         <is>
@@ -9297,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>2651</v>
+        <v>2661.5</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>2740.51</v>
+        <v>2737.79</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>2707.74</v>
+        <v>2708.87</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>2615.03</v>
+        <v>2616.12</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>778.7</v>
+        <v>823.35</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>728.97</v>
+        <v>733.22</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>665.33</v>
+        <v>667.08</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>569.3</v>
+        <v>570.12</v>
       </c>
       <c r="G197" s="14" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>682.85</v>
+        <v>681.2</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>679.1799999999999</v>
+        <v>679.37</v>
       </c>
       <c r="E198" s="11" t="n">
         <v>681.1</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>631.01</v>
+        <v>631.51</v>
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>327.6</v>
+        <v>322.45</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>342.41</v>
+        <v>341.92</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>354.44</v>
+        <v>354.24</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>419.55</v>
+        <v>419.64</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>1646.6</v>
+        <v>1638.3</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>1758.45</v>
+        <v>1754.05</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>1875.64</v>
+        <v>1870.29</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>2021.46</v>
+        <v>2018.33</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,24 +9517,24 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>160.06</v>
+        <v>165.65</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>165.26</v>
+        <v>165.3</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>173.58</v>
+        <v>173.27</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>190.41</v>
-      </c>
-      <c r="G201" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>190.61</v>
+      </c>
+      <c r="G201" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H201" s="12" t="inlineStr">
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>118.65</v>
+        <v>117.35</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>120.18</v>
+        <v>119.85</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>124.13</v>
+        <v>123.85</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>126.59</v>
+        <v>126.46</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>184.2</v>
+        <v>183.96</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>193.35</v>
+        <v>193.08</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>198.73</v>
+        <v>198.49</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>208.6</v>
+        <v>208.33</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,24 +9649,24 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>777.8</v>
+        <v>813.1</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>801.53</v>
+        <v>804.4400000000001</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>823.41</v>
+        <v>823.86</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>828.71</v>
-      </c>
-      <c r="G204" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>828.36</v>
+      </c>
+      <c r="G204" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H204" s="12" t="inlineStr">
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>108.8</v>
+        <v>113.43</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>113.93</v>
+        <v>113.84</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>117.69</v>
+        <v>117.41</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>136.58</v>
+        <v>136.03</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,29 +9737,29 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>578.25</v>
+        <v>595.65</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>581.79</v>
+        <v>583.11</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>582.14</v>
+        <v>582.67</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>608.83</v>
-      </c>
-      <c r="G206" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H206" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>608.7</v>
+      </c>
+      <c r="G206" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H206" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I206" s="12" t="inlineStr">
@@ -9781,29 +9781,29 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>408.35</v>
+        <v>425.5</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>406.85</v>
+        <v>407.57</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>416.33</v>
+        <v>416.14</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>440.97</v>
+        <v>441.05</v>
       </c>
       <c r="G207" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H207" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H207" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I207" s="12" t="inlineStr">
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>130.69</v>
+        <v>133.09</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>126.53</v>
+        <v>127.3</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>126.51</v>
+        <v>126.88</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>136.83</v>
+        <v>136.7</v>
       </c>
       <c r="G208" s="14" t="inlineStr">
         <is>
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>154.43</v>
+        <v>154.63</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>155.19</v>
+        <v>155.02</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>158.98</v>
+        <v>158.62</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>170.31</v>
+        <v>170.12</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,29 +9913,29 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>103.42</v>
+        <v>106.04</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>106.52</v>
+        <v>107</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>105.64</v>
+        <v>105.95</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>114</v>
+        <v>113.93</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H210" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H210" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I210" s="12" t="inlineStr">
@@ -9957,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>1217.9</v>
+        <v>1225.1</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>1303.28</v>
+        <v>1302.53</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>1315.5</v>
+        <v>1315.25</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>1318.95</v>
+        <v>1320.93</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>122.09</v>
+        <v>124.55</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>127.37</v>
+        <v>126.86</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>131.21</v>
+        <v>130.72</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>153.84</v>
+        <v>152.72</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>288.1</v>
+        <v>287.8</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>297.07</v>
+        <v>295.62</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>308.08</v>
+        <v>306.3</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>317.67</v>
+        <v>317.29</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,29 +10089,29 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>264.7</v>
+        <v>275.75</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>267.83</v>
+        <v>268.58</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>275.42</v>
+        <v>275.43</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>350.31</v>
-      </c>
-      <c r="G214" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H214" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>348.57</v>
+      </c>
+      <c r="G214" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H214" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I214" s="12" t="inlineStr">
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>826</v>
+        <v>845.75</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>819.64</v>
+        <v>820.5700000000001</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>810.8099999999999</v>
+        <v>811.3200000000001</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>802.9400000000001</v>
+        <v>803.67</v>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1363.4</v>
+        <v>1467</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>1176.47</v>
+        <v>1224.63</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>1037.35</v>
+        <v>1072.54</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>968.5599999999999</v>
+        <v>979.66</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>74.06999999999999</v>
+        <v>73.38</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>77.37</v>
+        <v>77.08</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>76.31999999999999</v>
+        <v>76.33</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>79.27</v>
+        <v>79.61</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>120.58</v>
+        <v>119.5</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>126.39</v>
+        <v>126.16</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>135.28</v>
+        <v>134.9</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>163.77</v>
+        <v>163.17</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10309,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>1081.5</v>
+        <v>1111.3</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>1066.84</v>
+        <v>1071.27</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>1069.89</v>
+        <v>1071.46</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>1123.83</v>
+        <v>1123.82</v>
       </c>
       <c r="G219" s="14" t="inlineStr">
         <is>
@@ -10353,20 +10353,20 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>231.4</v>
+        <v>239.35</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>242.64</v>
+        <v>243.4</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>240.6</v>
+        <v>240.91</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>227.79</v>
+        <v>227.84</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10397,24 +10397,24 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1541</v>
+        <v>1552.6</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1543.22</v>
+        <v>1544.33</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1552.36</v>
+        <v>1552.81</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1903.69</v>
-      </c>
-      <c r="G221" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1903.5</v>
+      </c>
+      <c r="G221" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H221" s="12" t="inlineStr">
@@ -10441,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>593.05</v>
+        <v>604</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>611.6900000000001</v>
+        <v>612.74</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>621.73</v>
+        <v>622.16</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>626.65</v>
+        <v>626.54</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10485,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>22.81</v>
+        <v>23.06</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>23.98</v>
+        <v>24</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>23.66</v>
+        <v>23.67</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>25.04</v>
+        <v>25.07</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>653.6</v>
+        <v>661.6</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>638.86</v>
+        <v>642.01</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>606.99</v>
+        <v>609.58</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>598.39</v>
+        <v>598.52</v>
       </c>
       <c r="G224" s="14" t="inlineStr">
         <is>
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>391.1</v>
+        <v>385.3</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>410.52</v>
+        <v>408.12</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>429</v>
+        <v>427.29</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>480.32</v>
+        <v>479.26</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10617,20 +10617,20 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>209.97</v>
+        <v>210.62</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>217.24</v>
+        <v>217.3</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>226.12</v>
+        <v>226.15</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>244.25</v>
+        <v>244.2</v>
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
@@ -10661,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>500.15</v>
+        <v>500.45</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>507.48</v>
+        <v>506.81</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>500.13</v>
+        <v>500.14</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>474.83</v>
+        <v>474.64</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>113.44</v>
+        <v>117.05</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>111.83</v>
+        <v>112.46</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>112.04</v>
+        <v>112.29</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>122.44</v>
+        <v>122.66</v>
       </c>
       <c r="G228" s="14" t="inlineStr">
         <is>
@@ -10749,29 +10749,29 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>218.23</v>
+        <v>213.43</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>214.79</v>
+        <v>214.64</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>215.66</v>
+        <v>215.67</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>225.9</v>
-      </c>
-      <c r="G229" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H229" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>225.65</v>
+      </c>
+      <c r="G229" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H229" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I229" s="12" t="inlineStr">
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>1843.8</v>
+        <v>1863</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>1924.79</v>
+        <v>1926.78</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>1898.65</v>
+        <v>1901.76</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>1777.78</v>
+        <v>1780.09</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10837,20 +10837,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>720.2</v>
+        <v>717.55</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>673.29</v>
+        <v>679.75</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>637.39</v>
+        <v>642.66</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>607.0599999999999</v>
+        <v>609.92</v>
       </c>
       <c r="G231" s="14" t="inlineStr">
         <is>
@@ -10881,24 +10881,24 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>176.56</v>
+        <v>173.73</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>176.06</v>
+        <v>175.84</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>182.08</v>
+        <v>181.75</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>214.97</v>
-      </c>
-      <c r="G232" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>214.56</v>
+      </c>
+      <c r="G232" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H232" s="12" t="inlineStr">
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>5592</v>
+        <v>5645</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>5709.02</v>
+        <v>5711.05</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>5830.66</v>
+        <v>5828.09</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>5756.76</v>
+        <v>5754.85</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>325.3</v>
+        <v>323.05</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>334.99</v>
+        <v>334.77</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>337.98</v>
+        <v>337.9</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>384.69</v>
+        <v>385.15</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11013,20 +11013,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>26.37</v>
+        <v>26.54</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>28.38</v>
+        <v>28.2</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>30.1</v>
+        <v>29.96</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>35.48</v>
+        <v>35.66</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11057,24 +11057,24 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>188.33</v>
+        <v>194.25</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>191.44</v>
+        <v>192.1</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>197.17</v>
+        <v>197.26</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>211.61</v>
-      </c>
-      <c r="G236" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>211.4</v>
+      </c>
+      <c r="G236" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H236" s="12" t="inlineStr">
@@ -11101,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>130.09</v>
+        <v>133.85</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>128.52</v>
+        <v>128.89</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>129.13</v>
+        <v>129.27</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>124.17</v>
+        <v>124.28</v>
       </c>
       <c r="G237" s="14" t="inlineStr">
         <is>
@@ -11145,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
         <v>7.05</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>8.52</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>10.14</v>
+        <v>9.92</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>13.13</v>
+        <v>13.04</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11189,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>94.73</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>101.32</v>
+        <v>101.41</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>106.37</v>
+        <v>106.4</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>120.63</v>
+        <v>120.73</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11233,24 +11233,24 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>304.25</v>
+        <v>299.1</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>303.91</v>
+        <v>303.42</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>305.45</v>
+        <v>305.24</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>328.51</v>
-      </c>
-      <c r="G240" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>330.24</v>
+      </c>
+      <c r="G240" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H240" s="12" t="inlineStr">
@@ -11277,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>460.65</v>
+        <v>442.45</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>487.97</v>
+        <v>483.03</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>513.8099999999999</v>
+        <v>509.93</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>618.8099999999999</v>
+        <v>615.77</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11321,20 +11321,20 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>63.81</v>
+        <v>64.48</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>66.51000000000001</v>
+        <v>66.64</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>66.76000000000001</v>
+        <v>66.86</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>72.06</v>
+        <v>72.11</v>
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
@@ -11365,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>1511.4</v>
+        <v>1501</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>1519.7</v>
+        <v>1519.8</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>1534.48</v>
+        <v>1534.08</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>1695.03</v>
+        <v>1692.75</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>120.81</v>
+        <v>120.77</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>124.8</v>
+        <v>124.58</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>129.95</v>
+        <v>129.71</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>135.56</v>
+        <v>135.54</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>66.84</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>68.76000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>70.17</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>76.22</v>
+        <v>76.03</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>718.95</v>
+        <v>722.65</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>737.99</v>
+        <v>737.5700000000001</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>752.13</v>
+        <v>751.58</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>760.35</v>
+        <v>760.0599999999999</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,20 +11541,20 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>445.95</v>
+        <v>455.65</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>427.32</v>
+        <v>427.76</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>426.63</v>
+        <v>426.46</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>429.54</v>
+        <v>430.3</v>
       </c>
       <c r="G247" s="14" t="inlineStr">
         <is>
@@ -11585,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>567.6</v>
+        <v>584.7</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>628.6799999999999</v>
+        <v>626.78</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>703.95</v>
+        <v>700.35</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>806.9299999999999</v>
+        <v>804.42</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>3989.5</v>
+        <v>4033.4</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>4144.76</v>
+        <v>4134.15</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>4308.27</v>
+        <v>4297.49</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>4486.77</v>
+        <v>4486.42</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11673,24 +11673,24 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>689.6</v>
+        <v>720.3</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>713.35</v>
+        <v>714.88</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>740.9400000000001</v>
+        <v>740.5700000000001</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>780.91</v>
-      </c>
-      <c r="G250" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>779.52</v>
+      </c>
+      <c r="G250" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H250" s="12" t="inlineStr">
@@ -11717,20 +11717,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>404.5</v>
+        <v>411.8</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>411.96</v>
+        <v>411.94</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>423.59</v>
+        <v>423.13</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>431.56</v>
+        <v>431.36</v>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 21-Sep-2026  16:46:09    |    Closing Price Date: 21-Sep-2026</t>
+          <t>Scan Run: 22-Sep-2026  15:23:56    |    Closing Price Date: 22-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -591,11 +591,11 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>44.4</v>
@@ -608,7 +608,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>21-Sep-2026  16:46:09</t>
+          <t>22-Sep-2026  15:23:56</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 43.6% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 44.4% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 109 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 111 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -758,20 +758,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>241.35</v>
+        <v>243.2</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>249.25</v>
+        <v>248.67</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>260.88</v>
+        <v>260.19</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>293.9</v>
+        <v>293.39</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -802,29 +802,29 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>324.95</v>
+        <v>320.5</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>328.32</v>
+        <v>327.57</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>323.78</v>
+        <v>323.65</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>325.13</v>
+        <v>325.09</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -846,20 +846,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>6464</v>
+        <v>6719.5</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>6003.26</v>
+        <v>6071.47</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>5419.12</v>
+        <v>5470.12</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>4363.15</v>
+        <v>4386.59</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -890,20 +890,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>747.3</v>
+        <v>756.4</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>741.21</v>
+        <v>742.66</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>698.73</v>
+        <v>700.99</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>556.15</v>
+        <v>558.14</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -934,29 +934,29 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>251.3</v>
+        <v>258.2</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>273.94</v>
+        <v>272.44</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>255.06</v>
+        <v>255.18</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>167.28</v>
+        <v>168.18</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>376.05</v>
+        <v>370.85</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>357.86</v>
+        <v>359.09</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>326.71</v>
+        <v>328.44</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>230.45</v>
+        <v>231.85</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
@@ -1022,24 +1022,24 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>7015.5</v>
+        <v>7176</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>7094.36</v>
+        <v>7102.14</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6939.92</v>
+        <v>6949.18</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>5540.34</v>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>5556.62</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -1066,20 +1066,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>845.45</v>
+        <v>930.4</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>839.26</v>
+        <v>847.9400000000001</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>785.8099999999999</v>
+        <v>791.48</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>634.12</v>
+        <v>637.0700000000001</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1110,24 +1110,24 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>314.55</v>
+        <v>331.5</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>319.08</v>
+        <v>320.26</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>306.64</v>
+        <v>307.62</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>258.61</v>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>259.33</v>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -1154,20 +1154,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>4930.5</v>
+        <v>5119.5</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>5171.36</v>
+        <v>5166.43</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>5346.09</v>
+        <v>5337.2</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4544.31</v>
+        <v>4550.03</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1198,20 +1198,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>177.62</v>
+        <v>178.01</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>174.6</v>
+        <v>174.93</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>172.19</v>
+        <v>172.42</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>165.51</v>
+        <v>165.63</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1242,20 +1242,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2764.9</v>
+        <v>2776.2</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>2744.26</v>
+        <v>2747.3</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>2617.64</v>
+        <v>2623.86</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2158.52</v>
+        <v>2164.67</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>629.95</v>
+        <v>620.35</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>604.0700000000001</v>
+        <v>605.62</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>587.4400000000001</v>
+        <v>588.73</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>574.75</v>
+        <v>575.2</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1330,20 +1330,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>2485.9</v>
+        <v>2468.5</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>2258.29</v>
+        <v>2278.31</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>2074.28</v>
+        <v>2089.74</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1544.85</v>
+        <v>1554.04</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1374,20 +1374,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>3525.6</v>
+        <v>3515.2</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3475.38</v>
+        <v>3479.17</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>3486.82</v>
+        <v>3487.93</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>3238.85</v>
+        <v>3241.6</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1418,29 +1418,29 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>385.45</v>
+        <v>406.75</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>392.14</v>
+        <v>393.53</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>390.98</v>
+        <v>391.59</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>336.78</v>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>337.48</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
@@ -1462,24 +1462,24 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>756.5</v>
+        <v>768.1</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>759.36</v>
+        <v>760.1900000000001</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>730.3099999999999</v>
+        <v>731.79</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>633.25</v>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>634.59</v>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
@@ -1506,20 +1506,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>813.65</v>
+        <v>839.55</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>783.83</v>
+        <v>789.14</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>695.86</v>
+        <v>701.49</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>452.12</v>
+        <v>455.97</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>214.42</v>
+        <v>213.84</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>199.98</v>
+        <v>201.3</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>184.05</v>
+        <v>185.22</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>164.27</v>
+        <v>164.76</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>12.79</v>
+        <v>13.58</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>12.24</v>
+        <v>12.36</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>11.13</v>
+        <v>11.23</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>10.37</v>
+        <v>10.4</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1638,29 +1638,29 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>231.57</v>
+        <v>242.87</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>234.47</v>
+        <v>235.27</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>234.4</v>
+        <v>234.73</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>198.9</v>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>199.34</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
@@ -1682,24 +1682,24 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>2099.5</v>
+        <v>2072.1</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>2087.62</v>
+        <v>2086.14</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>2018.75</v>
+        <v>2020.85</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>1717.78</v>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1721.3</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -1726,20 +1726,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>221.16</v>
+        <v>221.15</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>228.42</v>
+        <v>227.73</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>228.02</v>
+        <v>227.75</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>208.99</v>
+        <v>209.11</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1770,20 +1770,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>64.79000000000001</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="D25" s="10" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="E25" s="10" t="n">
         <v>65.95999999999999</v>
       </c>
-      <c r="E25" s="10" t="n">
-        <v>66.01000000000001</v>
-      </c>
       <c r="F25" s="10" t="n">
-        <v>60.3</v>
+        <v>60.34</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
@@ -1814,20 +1814,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>161.25</v>
+        <v>157.08</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>164.58</v>
+        <v>163.87</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>164.93</v>
+        <v>164.62</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>150.43</v>
+        <v>150.49</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1858,20 +1858,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>180.23</v>
+        <v>180.59</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>182.55</v>
+        <v>182.36</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>186.3</v>
+        <v>186.08</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>188.56</v>
+        <v>188.49</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1902,20 +1902,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>493.4</v>
+        <v>485.35</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>516.01</v>
+        <v>513.09</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>536.92</v>
+        <v>534.9</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>539.7</v>
+        <v>539.16</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1946,20 +1946,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>363.1</v>
+        <v>360.45</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>350.16</v>
+        <v>351.14</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>329.53</v>
+        <v>330.74</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>268.2</v>
+        <v>269.12</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -1990,24 +1990,24 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>1406.5</v>
+        <v>1375.5</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1404.39</v>
+        <v>1401.64</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>1344.94</v>
+        <v>1346.14</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1048.34</v>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1051.59</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -2034,20 +2034,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>367.25</v>
+        <v>370.45</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>363</v>
+        <v>363.71</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>346.98</v>
+        <v>347.9</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>306.93</v>
+        <v>307.56</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>579.55</v>
+        <v>574.65</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>541.73</v>
+        <v>544.87</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>519.97</v>
+        <v>522.11</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>471.87</v>
+        <v>472.89</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>1639.6</v>
+        <v>1643.5</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1630.07</v>
+        <v>1631.35</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>1564.4</v>
+        <v>1567.5</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>1265.94</v>
+        <v>1269.69</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2166,20 +2166,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>794.75</v>
+        <v>802.55</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>793.49</v>
+        <v>794.35</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>739.98</v>
+        <v>742.4299999999999</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>549.86</v>
+        <v>552.38</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>601.55</v>
+        <v>598.4</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>608</v>
+        <v>607.09</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>607.51</v>
+        <v>607.15</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>599.05</v>
+        <v>599.04</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2235,9 +2235,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
@@ -2254,20 +2254,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>531.3</v>
+        <v>533.7</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>530.1</v>
+        <v>530.4400000000001</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>527.54</v>
+        <v>527.78</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>481.08</v>
+        <v>481.6</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
@@ -2298,20 +2298,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>183.15</v>
+        <v>183.24</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>192.41</v>
+        <v>191.54</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>198.68</v>
+        <v>198.08</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>201.86</v>
+        <v>201.67</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2342,20 +2342,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>767</v>
+        <v>753.15</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>805.52</v>
+        <v>800.53</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>866.73</v>
+        <v>862.28</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>962.4299999999999</v>
+        <v>960.35</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2386,20 +2386,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>532.25</v>
+        <v>537.35</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>552.0700000000001</v>
+        <v>548.79</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>595.3099999999999</v>
+        <v>590.89</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>619.96</v>
+        <v>616.83</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2430,20 +2430,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>341.9</v>
+        <v>337.35</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>349.88</v>
+        <v>348.69</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>354.71</v>
+        <v>354.03</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>343.98</v>
+        <v>343.91</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>212.18</v>
+        <v>219.54</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>208.85</v>
+        <v>209.86</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>206.32</v>
+        <v>206.84</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>175.88</v>
+        <v>176.32</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2518,20 +2518,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>85.01000000000001</v>
+        <v>85.73</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>83.78</v>
+        <v>83.97</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>84.67</v>
+        <v>84.72</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>72.64</v>
+        <v>72.77</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2562,17 +2562,17 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>225.68</v>
+        <v>217.81</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>230.6</v>
+        <v>229.38</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>223.48</v>
+        <v>223.26</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>217.14</v>
@@ -2582,9 +2582,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I43" s="13" t="inlineStr">
@@ -2606,20 +2606,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1657.9</v>
+        <v>1616.3</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1670.88</v>
+        <v>1665.69</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1669.93</v>
+        <v>1667.83</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1399.38</v>
+        <v>1401.54</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>317.8</v>
+        <v>313.4</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>350.75</v>
+        <v>347.19</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>368.19</v>
+        <v>366.04</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>401.31</v>
+        <v>400.43</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2694,20 +2694,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>571.45</v>
+        <v>577.5</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>567.58</v>
+        <v>568.52</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>566.0700000000001</v>
+        <v>566.51</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>496.15</v>
+        <v>496.96</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2738,20 +2738,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>163.75</v>
+        <v>162.35</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>167.31</v>
+        <v>166.84</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>173.89</v>
+        <v>173.44</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>210.15</v>
+        <v>209.67</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2782,20 +2782,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1257.9</v>
+        <v>1230.3</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1220.37</v>
+        <v>1221.32</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1148.71</v>
+        <v>1151.91</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1044.87</v>
+        <v>1046.71</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2826,20 +2826,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>886.35</v>
+        <v>883.75</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>897.62</v>
+        <v>896.3</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>865.63</v>
+        <v>866.34</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>721.3099999999999</v>
+        <v>722.9299999999999</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2870,20 +2870,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>172.34</v>
+        <v>171.41</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>174.28</v>
+        <v>174</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>178.06</v>
+        <v>177.8</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>180.97</v>
+        <v>180.87</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>293.2</v>
+        <v>291</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>279.41</v>
+        <v>280.52</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>290.13</v>
+        <v>290.17</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>299.64</v>
+        <v>299.55</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
@@ -2958,20 +2958,20 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>473.75</v>
+        <v>474.7</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>493.54</v>
+        <v>491.75</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>524.13</v>
+        <v>522.1900000000001</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>536.1900000000001</v>
+        <v>535.58</v>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
@@ -3002,20 +3002,20 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>4297</v>
+        <v>4586.5</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>3993.74</v>
+        <v>4050.19</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>3736.66</v>
+        <v>3769.99</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>2853.32</v>
+        <v>2870.56</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
@@ -3046,20 +3046,20 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>564.1</v>
+        <v>574</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>557.41</v>
+        <v>558.99</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>543.1900000000001</v>
+        <v>544.4</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>532.13</v>
+        <v>532.55</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
@@ -3090,20 +3090,20 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>1966.8</v>
+        <v>1941.9</v>
       </c>
       <c r="D55" s="10" t="n">
-        <v>1940.82</v>
+        <v>1940.93</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>1984.21</v>
+        <v>1982.55</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>1843.58</v>
+        <v>1844.55</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
@@ -3134,20 +3134,20 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>191.28</v>
+        <v>192.61</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>183.37</v>
+        <v>184.25</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>168.47</v>
+        <v>169.42</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>136.62</v>
+        <v>137.18</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
@@ -3178,20 +3178,20 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>560.35</v>
+        <v>561.55</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>555.05</v>
+        <v>555.67</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>546.66</v>
+        <v>547.24</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>501.25</v>
+        <v>501.85</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
@@ -3222,20 +3222,20 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>1589.2</v>
+        <v>1567.9</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1665.45</v>
+        <v>1656.16</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>1692.03</v>
+        <v>1687.16</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1788.14</v>
+        <v>1785.94</v>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
@@ -3266,20 +3266,20 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>160.26</v>
+        <v>159.52</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>158.33</v>
+        <v>158.44</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>161.82</v>
+        <v>161.73</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>170.4</v>
+        <v>170.29</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -3310,24 +3310,24 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>3265.1</v>
+        <v>3168.8</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>3243.48</v>
+        <v>3236.37</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>3165.69</v>
+        <v>3165.82</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>2708.96</v>
-      </c>
-      <c r="G60" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2713.54</v>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>251.65</v>
+        <v>251.5</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>256.36</v>
+        <v>255.89</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>259.34</v>
+        <v>259.03</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>238.72</v>
+        <v>238.85</v>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
@@ -3398,20 +3398,20 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>469.2</v>
+        <v>463.95</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>494.29</v>
+        <v>491.4</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>509.09</v>
+        <v>507.32</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>570.71</v>
+        <v>569.65</v>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
@@ -3442,20 +3442,20 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>593.4</v>
+        <v>592.4</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>583.09</v>
+        <v>583.98</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>572.01</v>
+        <v>572.8099999999999</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>528.05</v>
+        <v>528.6900000000001</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
@@ -3486,20 +3486,20 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>21.83</v>
+        <v>21.67</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>22.31</v>
+        <v>22.25</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>22.37</v>
+        <v>22.34</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>22.54</v>
+        <v>22.53</v>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
@@ -3530,24 +3530,24 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>203.89</v>
+        <v>201.07</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>201.34</v>
+        <v>201.32</v>
       </c>
       <c r="E65" s="10" t="n">
+        <v>204.35</v>
+      </c>
+      <c r="F65" s="10" t="n">
         <v>204.48</v>
       </c>
-      <c r="F65" s="10" t="n">
-        <v>204.51</v>
-      </c>
-      <c r="G65" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -3574,20 +3574,20 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>198.58</v>
+        <v>199.67</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>194.81</v>
+        <v>195.27</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>199.98</v>
+        <v>199.97</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>192.48</v>
+        <v>192.55</v>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
@@ -3618,20 +3618,20 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>682.7</v>
+        <v>682.6</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>677.97</v>
+        <v>678.41</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>668.05</v>
+        <v>668.62</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>655.23</v>
+        <v>655.5</v>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
@@ -3662,20 +3662,20 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>1839.7</v>
+        <v>1891.1</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>1749.11</v>
+        <v>1762.63</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>1698.33</v>
+        <v>1705.89</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1625.91</v>
+        <v>1628.55</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
@@ -3706,20 +3706,20 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>646.15</v>
+        <v>652.8</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>677.59</v>
+        <v>675.23</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>704.23</v>
+        <v>702.21</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>820.79</v>
+        <v>819.12</v>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
@@ -3750,24 +3750,24 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>2089.2</v>
+        <v>2133.7</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>2098.47</v>
+        <v>2101.83</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>2016.35</v>
+        <v>2020.95</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1654</v>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1658.78</v>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
@@ -3794,20 +3794,20 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>6454.5</v>
+        <v>6366.5</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>6833.87</v>
+        <v>6789.36</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>6822.67</v>
+        <v>6804.79</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>5573.63</v>
+        <v>5581.51</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -3838,20 +3838,20 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>45.52</v>
+        <v>45.23</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>45.92</v>
+        <v>45.85</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>45.62</v>
+        <v>45.61</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>41.86</v>
+        <v>41.89</v>
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
@@ -3882,20 +3882,20 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>470.95</v>
+        <v>469.1</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>480.8</v>
+        <v>479.68</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>500.21</v>
+        <v>498.99</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>579.27</v>
+        <v>578.1799999999999</v>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
@@ -3926,20 +3926,20 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>146.66</v>
+        <v>146.86</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>146.92</v>
+        <v>146.91</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>140.64</v>
+        <v>140.88</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>150.26</v>
+        <v>150.23</v>
       </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
@@ -3970,20 +3970,20 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>2130.7</v>
+        <v>2138.9</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>2255.54</v>
+        <v>2244.43</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>2209.5</v>
+        <v>2206.73</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>1806.6</v>
+        <v>1809.91</v>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
@@ -4014,20 +4014,20 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>293.55</v>
+        <v>292.65</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>329.75</v>
+        <v>326.21</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>352.13</v>
+        <v>349.8</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>362.11</v>
+        <v>361.42</v>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
@@ -4058,20 +4058,20 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>745.75</v>
+        <v>747.35</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>767.84</v>
+        <v>765.89</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>802.62</v>
+        <v>800.45</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>880.52</v>
+        <v>879.1900000000001</v>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
@@ -4102,20 +4102,20 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>334.8</v>
+        <v>334.95</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>323.95</v>
+        <v>324.99</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>331.28</v>
+        <v>331.42</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>362.68</v>
+        <v>362.41</v>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
@@ -4146,20 +4146,20 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>2776.9</v>
+        <v>2781.7</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>2687.25</v>
+        <v>2696.25</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>2591.62</v>
+        <v>2599.07</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>2509.05</v>
+        <v>2511.76</v>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
@@ -4190,20 +4190,20 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>173.27</v>
+        <v>178.42</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>184.3</v>
+        <v>183.74</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>195.23</v>
+        <v>194.57</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>211.96</v>
+        <v>211.63</v>
       </c>
       <c r="G80" s="11" t="inlineStr">
         <is>
@@ -4234,20 +4234,20 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>164.99</v>
+        <v>164.41</v>
       </c>
       <c r="D81" s="10" t="n">
-        <v>160.8</v>
+        <v>161.14</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>156.77</v>
+        <v>157.07</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>154.87</v>
+        <v>154.97</v>
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
@@ -4278,20 +4278,20 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>72.43000000000001</v>
+        <v>72.91</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>73.41</v>
+        <v>73.36</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>74.19</v>
+        <v>74.14</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>70.20999999999999</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
@@ -4322,24 +4322,24 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>196.1</v>
+        <v>197.96</v>
       </c>
       <c r="D83" s="10" t="n">
-        <v>197.16</v>
+        <v>197.24</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>203.22</v>
+        <v>203.02</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="G83" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>183.9</v>
+      </c>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -4366,20 +4366,20 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>589.9</v>
+        <v>598.7</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>564.86</v>
+        <v>568.08</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>545.03</v>
+        <v>547.14</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>501.16</v>
+        <v>502.13</v>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
@@ -4410,17 +4410,17 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>16</v>
+        <v>16.11</v>
       </c>
       <c r="D85" s="10" t="n">
-        <v>15.77</v>
+        <v>15.8</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>15.79</v>
+        <v>15.81</v>
       </c>
       <c r="F85" s="10" t="n">
         <v>16.1</v>
@@ -4435,9 +4435,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J85" s="12" t="inlineStr">
@@ -4454,20 +4454,20 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>813.9</v>
+        <v>816.95</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>841.53</v>
+        <v>839.1900000000001</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>882.78</v>
+        <v>880.2</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>943.15</v>
+        <v>941.9</v>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
@@ -4498,20 +4498,20 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>2359.8</v>
+        <v>2379.2</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>2288.1</v>
+        <v>2296.78</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>2180.89</v>
+        <v>2188.66</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1826.01</v>
+        <v>1831.52</v>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
@@ -4542,20 +4542,20 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>660</v>
+        <v>661.8</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>655.4</v>
+        <v>656.01</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>657.08</v>
+        <v>657.27</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>625.1799999999999</v>
+        <v>625.54</v>
       </c>
       <c r="G88" s="13" t="inlineStr">
         <is>
@@ -4586,20 +4586,20 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
-        <v>1238</v>
+        <v>1252.8</v>
       </c>
       <c r="D89" s="10" t="n">
-        <v>1296.99</v>
+        <v>1292.79</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>1343.73</v>
+        <v>1340.16</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>1308.22</v>
+        <v>1307.67</v>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
@@ -4630,20 +4630,20 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>139.52</v>
+        <v>141.16</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>130.18</v>
+        <v>131.22</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>125.3</v>
+        <v>125.93</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>116.84</v>
+        <v>117.08</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -4674,20 +4674,20 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="10" t="n">
-        <v>536.7</v>
+        <v>535.35</v>
       </c>
       <c r="D91" s="10" t="n">
-        <v>547.34</v>
+        <v>546.2</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>510.61</v>
+        <v>511.58</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>495.88</v>
+        <v>496.28</v>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
@@ -4718,20 +4718,20 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>1732.6</v>
+        <v>1671.2</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1766.26</v>
+        <v>1757.2</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>1654.07</v>
+        <v>1654.74</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1212.85</v>
+        <v>1217.41</v>
       </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
@@ -4762,20 +4762,20 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="10" t="n">
-        <v>70.48999999999999</v>
+        <v>70.41</v>
       </c>
       <c r="D93" s="10" t="n">
-        <v>71.12</v>
+        <v>71.05</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>73.27</v>
+        <v>73.16</v>
       </c>
       <c r="F93" s="10" t="n">
-        <v>69.69</v>
+        <v>69.7</v>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
@@ -4806,20 +4806,20 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>338.1</v>
+        <v>332.95</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>322.69</v>
+        <v>323.67</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>303.38</v>
+        <v>304.54</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>247.01</v>
+        <v>247.86</v>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
@@ -4850,20 +4850,20 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="10" t="n">
-        <v>276.2</v>
+        <v>273.6</v>
       </c>
       <c r="D95" s="10" t="n">
-        <v>284.86</v>
+        <v>283.79</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>311.87</v>
+        <v>310.37</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>401.34</v>
+        <v>400.07</v>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
@@ -4894,20 +4894,20 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>538.55</v>
+        <v>533.55</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>552.92</v>
+        <v>551.08</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>540.63</v>
+        <v>540.35</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>458.36</v>
+        <v>459.11</v>
       </c>
       <c r="G96" s="11" t="inlineStr">
         <is>
@@ -4938,20 +4938,20 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>831.35</v>
+        <v>810.05</v>
       </c>
       <c r="D97" s="10" t="n">
-        <v>771.78</v>
+        <v>775.42</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>785.87</v>
+        <v>786.8200000000001</v>
       </c>
       <c r="F97" s="10" t="n">
-        <v>723.1799999999999</v>
+        <v>724.04</v>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
@@ -4982,20 +4982,20 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>232.14</v>
+        <v>234.62</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>235.76</v>
+        <v>235.65</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>249.62</v>
+        <v>249.03</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>295.91</v>
+        <v>295.3</v>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -5026,20 +5026,20 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>1797</v>
+        <v>1775.3</v>
       </c>
       <c r="D99" s="10" t="n">
-        <v>1824.95</v>
+        <v>1820.23</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>1848.17</v>
+        <v>1845.31</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>1785.42</v>
+        <v>1785.32</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -5051,9 +5051,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
@@ -5070,20 +5070,20 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>218.77</v>
+        <v>218.58</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>217.2</v>
+        <v>217.33</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>206.08</v>
+        <v>206.57</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>185.13</v>
+        <v>185.47</v>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
@@ -5114,20 +5114,20 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>842.3</v>
+        <v>837.5</v>
       </c>
       <c r="D101" s="10" t="n">
-        <v>881.0700000000001</v>
+        <v>876.92</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>886.72</v>
+        <v>884.79</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>755.45</v>
+        <v>756.27</v>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -5158,20 +5158,20 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>422.9</v>
+        <v>416.4</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>409.03</v>
+        <v>409.73</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>394.06</v>
+        <v>394.94</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>370.79</v>
+        <v>371.25</v>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
@@ -5202,20 +5202,20 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>660.7</v>
+        <v>655.55</v>
       </c>
       <c r="D103" s="10" t="n">
-        <v>666.34</v>
+        <v>665.3099999999999</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>700.0599999999999</v>
+        <v>698.3200000000001</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>785.03</v>
+        <v>783.74</v>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
@@ -5246,24 +5246,24 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>10802</v>
+        <v>10747</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>10798.51</v>
+        <v>10793.61</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>10436.78</v>
+        <v>10448.94</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>9466.43</v>
-      </c>
-      <c r="G104" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>9479.17</v>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H104" s="13" t="inlineStr">
@@ -5290,20 +5290,20 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>714.45</v>
+        <v>706.8</v>
       </c>
       <c r="D105" s="10" t="n">
-        <v>725</v>
+        <v>723.26</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>751.24</v>
+        <v>749.49</v>
       </c>
       <c r="F105" s="10" t="n">
-        <v>715.9400000000001</v>
+        <v>715.84</v>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -5334,20 +5334,20 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>91.59999999999999</v>
+        <v>90.28</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>91.67</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>92.08</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>85.75</v>
+        <v>85.8</v>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
@@ -5378,20 +5378,20 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="10" t="n">
-        <v>2068.8</v>
+        <v>2116.4</v>
       </c>
       <c r="D107" s="10" t="n">
-        <v>1981.94</v>
+        <v>1994.75</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>1869.41</v>
+        <v>1879.09</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>1633.9</v>
+        <v>1638.7</v>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
@@ -5422,20 +5422,20 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>1070.8</v>
+        <v>1033.15</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>934.14</v>
+        <v>943.5700000000001</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>825.15</v>
+        <v>833.3099999999999</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>587.86</v>
+        <v>592.29</v>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
@@ -5466,20 +5466,20 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="10" t="n">
-        <v>1235.1</v>
+        <v>1217.4</v>
       </c>
       <c r="D109" s="10" t="n">
-        <v>1137.09</v>
+        <v>1144.74</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>1085.9</v>
+        <v>1091.06</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>1013.11</v>
+        <v>1015.14</v>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
@@ -5510,20 +5510,20 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>687.05</v>
+        <v>681.9</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>694.4299999999999</v>
+        <v>691.41</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>729.3</v>
+        <v>725.4</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>872.9400000000001</v>
+        <v>868.52</v>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
@@ -5554,24 +5554,24 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>436.15</v>
+        <v>448.9</v>
       </c>
       <c r="D111" s="10" t="n">
-        <v>436.92</v>
+        <v>438.06</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>421.03</v>
+        <v>422.13</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>350.85</v>
-      </c>
-      <c r="G111" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>351.82</v>
+      </c>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
@@ -5598,20 +5598,20 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>957.7</v>
+        <v>939.1</v>
       </c>
       <c r="D112" s="10" t="n">
-        <v>879.5599999999999</v>
+        <v>885.23</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>861.03</v>
+        <v>864.09</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>794.0599999999999</v>
+        <v>795.5</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -5642,20 +5642,20 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="10" t="n">
-        <v>432.25</v>
+        <v>429.8</v>
       </c>
       <c r="D113" s="10" t="n">
-        <v>417.33</v>
+        <v>418.51</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>405.45</v>
+        <v>406.4</v>
       </c>
       <c r="F113" s="10" t="n">
-        <v>399.34</v>
+        <v>399.64</v>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
@@ -5686,20 +5686,20 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>202.15</v>
+        <v>201.95</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>205.99</v>
+        <v>205.61</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>213.16</v>
+        <v>212.72</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>241.29</v>
+        <v>240.89</v>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
@@ -5730,20 +5730,20 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>72.03</v>
+        <v>71.8</v>
       </c>
       <c r="D115" s="10" t="n">
-        <v>76.2</v>
+        <v>75.78</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>83.54000000000001</v>
+        <v>83.08</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>93.84</v>
+        <v>93.62</v>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
@@ -5774,20 +5774,20 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>255.8</v>
+        <v>253.6</v>
       </c>
       <c r="D116" s="10" t="n">
-        <v>485.5</v>
+        <v>463.41</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>748.24</v>
+        <v>728.84</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>920.54</v>
+        <v>913.91</v>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
@@ -5818,20 +5818,20 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="10" t="n">
-        <v>373.45</v>
+        <v>357.1</v>
       </c>
       <c r="D117" s="10" t="n">
-        <v>349.5</v>
+        <v>350.23</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>323.25</v>
+        <v>324.58</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>318.05</v>
+        <v>318.44</v>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
@@ -5862,20 +5862,20 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>3426.8</v>
+        <v>3403.7</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>3355.05</v>
+        <v>3359.69</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>3254.69</v>
+        <v>3260.53</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>2915.7</v>
+        <v>2920.56</v>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
@@ -5906,20 +5906,20 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>4508.7</v>
+        <v>4512.6</v>
       </c>
       <c r="D119" s="10" t="n">
-        <v>4459.76</v>
+        <v>4464.79</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>4363.36</v>
+        <v>4369.21</v>
       </c>
       <c r="F119" s="10" t="n">
-        <v>3703.51</v>
+        <v>3711.57</v>
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
@@ -5950,24 +5950,24 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>674.6</v>
+        <v>662.15</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>669.22</v>
+        <v>668.55</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>693.1900000000001</v>
+        <v>691.97</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>754.63</v>
-      </c>
-      <c r="G120" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>753.71</v>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
@@ -5994,29 +5994,29 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>321.4</v>
+        <v>346.45</v>
       </c>
       <c r="D121" s="10" t="n">
-        <v>300.37</v>
+        <v>304.42</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>330.08</v>
+        <v>330.32</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>392.3</v>
+        <v>391.36</v>
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H121" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H121" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -6038,20 +6038,20 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>508.1</v>
+        <v>515.4</v>
       </c>
       <c r="D122" s="10" t="n">
-        <v>506.68</v>
+        <v>507.51</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>528.5700000000001</v>
+        <v>528.05</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>587.8099999999999</v>
+        <v>587.09</v>
       </c>
       <c r="G122" s="13" t="inlineStr">
         <is>
@@ -6082,20 +6082,20 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="10" t="n">
-        <v>655.1</v>
+        <v>663.4</v>
       </c>
       <c r="D123" s="10" t="n">
-        <v>625.11</v>
+        <v>628.76</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>591.4299999999999</v>
+        <v>594.25</v>
       </c>
       <c r="F123" s="10" t="n">
-        <v>509.95</v>
+        <v>511.48</v>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
@@ -6126,20 +6126,20 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>1416.5</v>
+        <v>1420.1</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>1496.37</v>
+        <v>1489.11</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>1421.02</v>
+        <v>1420.98</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1160.35</v>
+        <v>1162.93</v>
       </c>
       <c r="G124" s="11" t="inlineStr">
         <is>
@@ -6170,20 +6170,20 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="10" t="n">
-        <v>211.16</v>
+        <v>211.35</v>
       </c>
       <c r="D125" s="10" t="n">
-        <v>216.69</v>
+        <v>216.18</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>221.37</v>
+        <v>220.97</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>238.24</v>
+        <v>237.97</v>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -6214,20 +6214,20 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>510.15</v>
+        <v>547.1</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>481.44</v>
+        <v>487.7</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>495.25</v>
+        <v>497.29</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>533.8200000000001</v>
+        <v>533.95</v>
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
@@ -6239,9 +6239,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I126" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J126" s="12" t="inlineStr">
@@ -6258,29 +6258,29 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>393.15</v>
+        <v>389.9</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>404.32</v>
+        <v>402.95</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>392.04</v>
+        <v>391.96</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>369.72</v>
+        <v>369.92</v>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H127" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I127" s="13" t="inlineStr">
@@ -6302,29 +6302,29 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>808.8</v>
+        <v>795.6</v>
       </c>
       <c r="D128" s="10" t="n">
-        <v>812.15</v>
+        <v>810.5700000000001</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>797.12</v>
+        <v>797.0599999999999</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>740.99</v>
+        <v>741.54</v>
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H128" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I128" s="13" t="inlineStr">
@@ -6346,20 +6346,20 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>821.45</v>
+        <v>807.9</v>
       </c>
       <c r="D129" s="10" t="n">
-        <v>766.04</v>
+        <v>770.03</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>727.5599999999999</v>
+        <v>730.71</v>
       </c>
       <c r="F129" s="10" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
@@ -6390,20 +6390,20 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>227.11</v>
+        <v>223.32</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>193.48</v>
+        <v>196.32</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>179.33</v>
+        <v>181.05</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>161.25</v>
+        <v>161.86</v>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
@@ -6434,20 +6434,20 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="10" t="n">
-        <v>701.35</v>
+        <v>713.1</v>
       </c>
       <c r="D131" s="10" t="n">
-        <v>698.27</v>
+        <v>699.6799999999999</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>688.26</v>
+        <v>689.23</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>647.96</v>
+        <v>648.61</v>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
@@ -6478,20 +6478,20 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>421.55</v>
+        <v>420.3</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>427.87</v>
+        <v>427.15</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>433.15</v>
+        <v>432.65</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>469.22</v>
+        <v>468.73</v>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="10" t="n">
-        <v>694.7</v>
+        <v>695.05</v>
       </c>
       <c r="D133" s="10" t="n">
-        <v>760.11</v>
+        <v>753.92</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>776.04</v>
+        <v>772.86</v>
       </c>
       <c r="F133" s="10" t="n">
-        <v>765.35</v>
+        <v>764.65</v>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6566,20 +6566,20 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>1695.4</v>
+        <v>1664.9</v>
       </c>
       <c r="D134" s="10" t="n">
-        <v>1744.75</v>
+        <v>1737.15</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>1729.24</v>
+        <v>1726.72</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1470.02</v>
+        <v>1471.96</v>
       </c>
       <c r="G134" s="11" t="inlineStr">
         <is>
@@ -6610,20 +6610,20 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="10" t="n">
-        <v>231.1</v>
+        <v>227.9</v>
       </c>
       <c r="D135" s="10" t="n">
-        <v>243.44</v>
+        <v>241.96</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>249.73</v>
+        <v>248.87</v>
       </c>
       <c r="F135" s="10" t="n">
-        <v>259.21</v>
+        <v>258.9</v>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6654,20 +6654,20 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>95.22</v>
+        <v>93.64</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>96.51000000000001</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>90.86</v>
+        <v>90.97</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>77.45999999999999</v>
+        <v>77.62</v>
       </c>
       <c r="G136" s="11" t="inlineStr">
         <is>
@@ -6698,20 +6698,20 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="10" t="n">
-        <v>421.5</v>
+        <v>414.7</v>
       </c>
       <c r="D137" s="10" t="n">
-        <v>393.16</v>
+        <v>395.21</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>371.84</v>
+        <v>373.52</v>
       </c>
       <c r="F137" s="10" t="n">
-        <v>370.92</v>
+        <v>371.36</v>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
@@ -6742,20 +6742,20 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>1901.1</v>
+        <v>1906.7</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>2031.68</v>
+        <v>2019.78</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>2139.37</v>
+        <v>2130.25</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2161.08</v>
+        <v>2158.55</v>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
@@ -6786,20 +6786,20 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="10" t="n">
-        <v>629.3</v>
+        <v>627.1</v>
       </c>
       <c r="D139" s="10" t="n">
-        <v>615.34</v>
+        <v>616.46</v>
       </c>
       <c r="E139" s="10" t="n">
-        <v>610.05</v>
+        <v>610.72</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>557.83</v>
+        <v>558.52</v>
       </c>
       <c r="G139" s="13" t="inlineStr">
         <is>
@@ -6830,20 +6830,20 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>312.15</v>
+        <v>317.55</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>326.69</v>
+        <v>325.82</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>332.49</v>
+        <v>331.9</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>346.26</v>
+        <v>345.97</v>
       </c>
       <c r="G140" s="11" t="inlineStr">
         <is>
@@ -6874,24 +6874,24 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>422.05</v>
+        <v>434.6</v>
       </c>
       <c r="D141" s="10" t="n">
-        <v>428.98</v>
+        <v>429.52</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>410.38</v>
+        <v>411.33</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>318.91</v>
-      </c>
-      <c r="G141" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>320.06</v>
+      </c>
+      <c r="G141" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H141" s="13" t="inlineStr">
@@ -6918,24 +6918,24 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>1144</v>
+        <v>1197.1</v>
       </c>
       <c r="D142" s="10" t="n">
-        <v>1168.86</v>
+        <v>1171.55</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>1073.21</v>
+        <v>1078.07</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>852.4400000000001</v>
-      </c>
-      <c r="G142" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>855.86</v>
+      </c>
+      <c r="G142" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
@@ -6962,20 +6962,20 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="10" t="n">
-        <v>129.24</v>
+        <v>127.99</v>
       </c>
       <c r="D143" s="10" t="n">
-        <v>127.4</v>
+        <v>126.12</v>
       </c>
       <c r="E143" s="10" t="n">
-        <v>127.66</v>
+        <v>126.25</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>123.12</v>
+        <v>121.75</v>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
@@ -7006,20 +7006,20 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>210.85</v>
+        <v>213.18</v>
       </c>
       <c r="D144" s="10" t="n">
-        <v>216.36</v>
+        <v>216.06</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>219.03</v>
+        <v>218.8</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>215.15</v>
+        <v>215.13</v>
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
@@ -7050,20 +7050,20 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="10" t="n">
-        <v>275.55</v>
+        <v>274.8</v>
       </c>
       <c r="D145" s="10" t="n">
-        <v>286.71</v>
+        <v>285.58</v>
       </c>
       <c r="E145" s="10" t="n">
-        <v>293.27</v>
+        <v>292.54</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>283.97</v>
+        <v>283.88</v>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
@@ -7094,20 +7094,20 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>108.74</v>
+        <v>107.63</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>112.32</v>
+        <v>111.87</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>117.58</v>
+        <v>117.19</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>126.84</v>
+        <v>126.65</v>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -7138,20 +7138,20 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="10" t="n">
-        <v>151.74</v>
+        <v>152.14</v>
       </c>
       <c r="D147" s="10" t="n">
-        <v>155.82</v>
+        <v>155.47</v>
       </c>
       <c r="E147" s="10" t="n">
-        <v>155.13</v>
+        <v>155.01</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>148.83</v>
+        <v>148.86</v>
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
@@ -7182,29 +7182,29 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>414.2</v>
+        <v>477.15</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>425.17</v>
+        <v>430.12</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>450.51</v>
+        <v>451.56</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>515.75</v>
-      </c>
-      <c r="G148" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H148" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>515.36</v>
+      </c>
+      <c r="G148" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H148" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I148" s="11" t="inlineStr">
@@ -7226,24 +7226,24 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="10" t="n">
-        <v>92.43000000000001</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="D149" s="10" t="n">
-        <v>93.72</v>
+        <v>93.86</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>95.98</v>
+        <v>95.95</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>103</v>
-      </c>
-      <c r="G149" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>102.92</v>
+      </c>
+      <c r="G149" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
@@ -7270,20 +7270,20 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>2212.9</v>
+        <v>2181.5</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>2155.58</v>
+        <v>2158.05</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>2090.65</v>
+        <v>2094.22</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1817.68</v>
+        <v>1821.3</v>
       </c>
       <c r="G150" s="13" t="inlineStr">
         <is>
@@ -7314,20 +7314,20 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="10" t="n">
-        <v>2444.2</v>
+        <v>2443.1</v>
       </c>
       <c r="D151" s="10" t="n">
-        <v>2414.09</v>
+        <v>2416.85</v>
       </c>
       <c r="E151" s="10" t="n">
-        <v>2473.52</v>
+        <v>2472.32</v>
       </c>
       <c r="F151" s="10" t="n">
-        <v>2499.78</v>
+        <v>2499.22</v>
       </c>
       <c r="G151" s="13" t="inlineStr">
         <is>
@@ -7358,20 +7358,20 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>1125.3</v>
+        <v>1129.1</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>995.73</v>
+        <v>1008.43</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>931.25</v>
+        <v>939.01</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>810.5700000000001</v>
+        <v>813.74</v>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
@@ -7402,20 +7402,20 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="10" t="n">
-        <v>1923</v>
+        <v>1911</v>
       </c>
       <c r="D153" s="10" t="n">
-        <v>1946.21</v>
+        <v>1942.86</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>1827.95</v>
+        <v>1831.21</v>
       </c>
       <c r="F153" s="10" t="n">
-        <v>1578.67</v>
+        <v>1581.98</v>
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
@@ -7446,20 +7446,20 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>1795.5</v>
+        <v>1841.8</v>
       </c>
       <c r="D154" s="10" t="n">
-        <v>1717.58</v>
+        <v>1729.41</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>1548.88</v>
+        <v>1560.36</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1296.84</v>
+        <v>1302.27</v>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
@@ -7490,20 +7490,20 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="10" t="n">
-        <v>284.7</v>
+        <v>285.1</v>
       </c>
       <c r="D155" s="10" t="n">
-        <v>281.58</v>
+        <v>281.92</v>
       </c>
       <c r="E155" s="10" t="n">
-        <v>280.38</v>
+        <v>280.57</v>
       </c>
       <c r="F155" s="10" t="n">
-        <v>240.16</v>
+        <v>240.6</v>
       </c>
       <c r="G155" s="13" t="inlineStr">
         <is>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>12169</v>
+        <v>12516</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>11760.91</v>
+        <v>11832.83</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>11360.76</v>
+        <v>11406.06</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10276.87</v>
+        <v>10299.15</v>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
@@ -7578,24 +7578,24 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="10" t="n">
-        <v>2096.1</v>
+        <v>2078.3</v>
       </c>
       <c r="D157" s="10" t="n">
-        <v>2092.88</v>
+        <v>2091.49</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>2150.29</v>
+        <v>2147.46</v>
       </c>
       <c r="F157" s="10" t="n">
-        <v>2220.88</v>
-      </c>
-      <c r="G157" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2219.47</v>
+      </c>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
@@ -7622,24 +7622,24 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>1138.4</v>
+        <v>1194.9</v>
       </c>
       <c r="D158" s="10" t="n">
-        <v>1157.69</v>
+        <v>1161.24</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>1112.97</v>
+        <v>1116.19</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>927.99</v>
-      </c>
-      <c r="G158" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>930.64</v>
+      </c>
+      <c r="G158" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
@@ -7666,20 +7666,20 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="10" t="n">
-        <v>643.5</v>
+        <v>648.25</v>
       </c>
       <c r="D159" s="10" t="n">
-        <v>668.6</v>
+        <v>666.66</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>681.08</v>
+        <v>679.79</v>
       </c>
       <c r="F159" s="10" t="n">
-        <v>653.12</v>
+        <v>653.0700000000001</v>
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
@@ -7710,20 +7710,20 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>466.25</v>
+        <v>463.05</v>
       </c>
       <c r="D160" s="10" t="n">
-        <v>482.75</v>
+        <v>480.88</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>503.72</v>
+        <v>502.13</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>547.38</v>
+        <v>546.54</v>
       </c>
       <c r="G160" s="11" t="inlineStr">
         <is>
@@ -7754,20 +7754,20 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>114.43</v>
+        <v>119.2</v>
       </c>
       <c r="D161" s="10" t="n">
-        <v>112.63</v>
+        <v>113.25</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>110.96</v>
+        <v>111.28</v>
       </c>
       <c r="F161" s="10" t="n">
-        <v>114.97</v>
+        <v>115.01</v>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
@@ -7779,9 +7779,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I161" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
@@ -7798,20 +7798,20 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>418.55</v>
+        <v>415.2</v>
       </c>
       <c r="D162" s="10" t="n">
-        <v>425.03</v>
+        <v>424.09</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>421.55</v>
+        <v>421.3</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>399.54</v>
+        <v>399.7</v>
       </c>
       <c r="G162" s="11" t="inlineStr">
         <is>
@@ -7842,20 +7842,20 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>150.75</v>
+        <v>152.19</v>
       </c>
       <c r="D163" s="10" t="n">
-        <v>153.75</v>
+        <v>153.6</v>
       </c>
       <c r="E163" s="10" t="n">
-        <v>154.98</v>
+        <v>154.87</v>
       </c>
       <c r="F163" s="10" t="n">
-        <v>162.78</v>
+        <v>162.67</v>
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
@@ -7886,20 +7886,20 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="10" t="n">
-        <v>515.75</v>
+        <v>507.8</v>
       </c>
       <c r="D164" s="10" t="n">
-        <v>520.4400000000001</v>
+        <v>519.24</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>541.54</v>
+        <v>540.22</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>628.9400000000001</v>
+        <v>627.73</v>
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7930,20 +7930,20 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="10" t="n">
-        <v>729.85</v>
+        <v>746.95</v>
       </c>
       <c r="D165" s="10" t="n">
-        <v>713.45</v>
+        <v>716.64</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>673.08</v>
+        <v>675.97</v>
       </c>
       <c r="F165" s="10" t="n">
-        <v>566.04</v>
+        <v>567.84</v>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="10" t="n">
-        <v>194.67</v>
+        <v>193.97</v>
       </c>
       <c r="D166" s="10" t="n">
-        <v>198.13</v>
+        <v>197.73</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>201.26</v>
+        <v>200.98</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>227.18</v>
+        <v>226.84</v>
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
@@ -8018,20 +8018,20 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="10" t="n">
-        <v>208.01</v>
+        <v>208.18</v>
       </c>
       <c r="D167" s="10" t="n">
-        <v>216.83</v>
+        <v>216.01</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>225.93</v>
+        <v>225.23</v>
       </c>
       <c r="F167" s="10" t="n">
-        <v>228.47</v>
+        <v>228.27</v>
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
@@ -8062,20 +8062,20 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="10" t="n">
-        <v>540.25</v>
+        <v>543.9</v>
       </c>
       <c r="D168" s="10" t="n">
-        <v>529.25</v>
+        <v>530.64</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>510.94</v>
+        <v>512.23</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>477.35</v>
+        <v>478.01</v>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
@@ -8106,20 +8106,20 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="10" t="n">
-        <v>435.5</v>
+        <v>425.75</v>
       </c>
       <c r="D169" s="10" t="n">
         <v>425.7</v>
       </c>
       <c r="E169" s="10" t="n">
-        <v>416.64</v>
+        <v>417</v>
       </c>
       <c r="F169" s="10" t="n">
-        <v>406.19</v>
+        <v>406.38</v>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
@@ -8150,20 +8150,20 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>872.55</v>
+        <v>864.5</v>
       </c>
       <c r="D170" s="10" t="n">
-        <v>842.41</v>
+        <v>844.52</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>786.3200000000001</v>
+        <v>789.39</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>658.16</v>
+        <v>660.21</v>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
@@ -8194,20 +8194,20 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="10" t="n">
-        <v>427.6</v>
+        <v>419.4</v>
       </c>
       <c r="D171" s="10" t="n">
-        <v>439.23</v>
+        <v>437.34</v>
       </c>
       <c r="E171" s="10" t="n">
-        <v>446.87</v>
+        <v>445.8</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>460.01</v>
+        <v>459.61</v>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
@@ -8238,20 +8238,20 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="10" t="n">
-        <v>1130.5</v>
+        <v>1142</v>
       </c>
       <c r="D172" s="10" t="n">
-        <v>1119.58</v>
+        <v>1121.71</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>1102.51</v>
+        <v>1104.06</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>1046.32</v>
+        <v>1047.27</v>
       </c>
       <c r="G172" s="13" t="inlineStr">
         <is>
@@ -8282,20 +8282,20 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="10" t="n">
-        <v>140.47</v>
+        <v>139.62</v>
       </c>
       <c r="D173" s="10" t="n">
-        <v>170.57</v>
+        <v>167.62</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>194.77</v>
+        <v>192.6</v>
       </c>
       <c r="F173" s="10" t="n">
-        <v>222.17</v>
+        <v>221.35</v>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
@@ -8326,20 +8326,20 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="10" t="n">
-        <v>518.65</v>
+        <v>505.25</v>
       </c>
       <c r="D174" s="10" t="n">
-        <v>534.27</v>
+        <v>531.51</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>519.17</v>
+        <v>518.62</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>514.41</v>
+        <v>514.3200000000001</v>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
@@ -8351,9 +8351,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I174" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J174" s="12" t="inlineStr">
@@ -8370,20 +8370,20 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="10" t="n">
-        <v>590.75</v>
+        <v>708.9</v>
       </c>
       <c r="D175" s="10" t="n">
-        <v>578.36</v>
+        <v>590.79</v>
       </c>
       <c r="E175" s="10" t="n">
-        <v>562.6</v>
+        <v>568.34</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>514.0700000000001</v>
+        <v>516.01</v>
       </c>
       <c r="G175" s="13" t="inlineStr">
         <is>
@@ -8414,20 +8414,20 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="10" t="n">
-        <v>156.28</v>
+        <v>155.63</v>
       </c>
       <c r="D176" s="10" t="n">
-        <v>155.4</v>
+        <v>155.42</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>157.36</v>
+        <v>157.29</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>156.9</v>
+        <v>156.89</v>
       </c>
       <c r="G176" s="13" t="inlineStr">
         <is>
@@ -8458,20 +8458,20 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="10" t="n">
-        <v>180.01</v>
+        <v>179.95</v>
       </c>
       <c r="D177" s="10" t="n">
-        <v>183.99</v>
+        <v>183.61</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>192.38</v>
+        <v>191.89</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>242.02</v>
+        <v>241.4</v>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
@@ -8502,20 +8502,20 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="10" t="n">
-        <v>1486.4</v>
+        <v>1491.6</v>
       </c>
       <c r="D178" s="10" t="n">
-        <v>1427.39</v>
+        <v>1432.64</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>1335</v>
+        <v>1340.28</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>1106.74</v>
+        <v>1109.83</v>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
@@ -8546,24 +8546,24 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="10" t="n">
-        <v>253.21</v>
+        <v>249.17</v>
       </c>
       <c r="D179" s="10" t="n">
-        <v>249.4</v>
+        <v>249.38</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>247.48</v>
+        <v>247.54</v>
       </c>
       <c r="F179" s="10" t="n">
-        <v>242.56</v>
-      </c>
-      <c r="G179" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>242.63</v>
+      </c>
+      <c r="G179" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H179" s="13" t="inlineStr">
@@ -8590,20 +8590,20 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="10" t="n">
-        <v>350.15</v>
+        <v>361.25</v>
       </c>
       <c r="D180" s="10" t="n">
-        <v>376.21</v>
+        <v>374.79</v>
       </c>
       <c r="E180" s="10" t="n">
-        <v>369.6</v>
+        <v>369.27</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>330.47</v>
+        <v>330.77</v>
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
@@ -8634,20 +8634,20 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="10" t="n">
-        <v>26.79</v>
+        <v>26.91</v>
       </c>
       <c r="D181" s="10" t="n">
-        <v>27.4</v>
+        <v>27.36</v>
       </c>
       <c r="E181" s="10" t="n">
-        <v>28.69</v>
+        <v>28.62</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>34.39</v>
+        <v>34.31</v>
       </c>
       <c r="G181" s="11" t="inlineStr">
         <is>
@@ -8678,20 +8678,20 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="10" t="n">
-        <v>7.11</v>
+        <v>7.06</v>
       </c>
       <c r="D182" s="10" t="n">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
       <c r="E182" s="10" t="n">
-        <v>7.92</v>
+        <v>7.88</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>9.119999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="G182" s="11" t="inlineStr">
         <is>
@@ -8722,20 +8722,20 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="10" t="n">
-        <v>591.2</v>
+        <v>614.8</v>
       </c>
       <c r="D183" s="10" t="n">
-        <v>621.54</v>
+        <v>620.9</v>
       </c>
       <c r="E183" s="10" t="n">
-        <v>646.72</v>
+        <v>645.47</v>
       </c>
       <c r="F183" s="10" t="n">
-        <v>626.54</v>
+        <v>626.4299999999999</v>
       </c>
       <c r="G183" s="11" t="inlineStr">
         <is>
@@ -8766,20 +8766,20 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="10" t="n">
-        <v>238.75</v>
+        <v>239.55</v>
       </c>
       <c r="D184" s="10" t="n">
-        <v>261.46</v>
+        <v>259.37</v>
       </c>
       <c r="E184" s="10" t="n">
-        <v>290.44</v>
+        <v>288.45</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>345.03</v>
+        <v>343.98</v>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8810,20 +8810,20 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="10" t="n">
-        <v>710.65</v>
+        <v>699.7</v>
       </c>
       <c r="D185" s="10" t="n">
-        <v>729.9</v>
+        <v>727.02</v>
       </c>
       <c r="E185" s="10" t="n">
-        <v>771.53</v>
+        <v>768.71</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>878.59</v>
+        <v>876.8099999999999</v>
       </c>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8854,20 +8854,20 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="10" t="n">
-        <v>13609</v>
+        <v>13313</v>
       </c>
       <c r="D186" s="10" t="n">
-        <v>13212.85</v>
+        <v>13222.39</v>
       </c>
       <c r="E186" s="10" t="n">
-        <v>13094.62</v>
+        <v>13103.18</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>13178.18</v>
+        <v>13179.52</v>
       </c>
       <c r="G186" s="13" t="inlineStr">
         <is>
@@ -8898,20 +8898,20 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="10" t="n">
-        <v>344.4</v>
+        <v>345.05</v>
       </c>
       <c r="D187" s="10" t="n">
-        <v>338.57</v>
+        <v>339.19</v>
       </c>
       <c r="E187" s="10" t="n">
-        <v>337.29</v>
+        <v>337.59</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>329.89</v>
+        <v>330.04</v>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
@@ -8942,20 +8942,20 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="10" t="n">
-        <v>58.89</v>
+        <v>58.43</v>
       </c>
       <c r="D188" s="10" t="n">
-        <v>57.8</v>
+        <v>57.86</v>
       </c>
       <c r="E188" s="10" t="n">
-        <v>59.76</v>
+        <v>59.71</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>65.59</v>
+        <v>65.52</v>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
@@ -8986,24 +8986,24 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="10" t="n">
-        <v>1400.4</v>
+        <v>1374.2</v>
       </c>
       <c r="D189" s="10" t="n">
-        <v>1377.6</v>
+        <v>1377.28</v>
       </c>
       <c r="E189" s="10" t="n">
-        <v>1309.32</v>
+        <v>1311.87</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>1125.35</v>
-      </c>
-      <c r="G189" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1127.83</v>
+      </c>
+      <c r="G189" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H189" s="13" t="inlineStr">
@@ -9030,20 +9030,20 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="10" t="n">
-        <v>825.05</v>
+        <v>817.6</v>
       </c>
       <c r="D190" s="10" t="n">
-        <v>846.98</v>
+        <v>844.1799999999999</v>
       </c>
       <c r="E190" s="10" t="n">
-        <v>883.38</v>
+        <v>880.8</v>
       </c>
       <c r="F190" s="10" t="n">
-        <v>975.09</v>
+        <v>973.53</v>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
@@ -9074,20 +9074,20 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="10" t="n">
-        <v>773.85</v>
+        <v>765.3</v>
       </c>
       <c r="D191" s="10" t="n">
-        <v>774.25</v>
+        <v>773.4</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>792.26</v>
+        <v>791.2</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>783.02</v>
+        <v>782.84</v>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -9118,20 +9118,20 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="10" t="n">
-        <v>846.45</v>
+        <v>883.75</v>
       </c>
       <c r="D192" s="10" t="n">
-        <v>826.9299999999999</v>
+        <v>832.34</v>
       </c>
       <c r="E192" s="10" t="n">
-        <v>793.72</v>
+        <v>797.25</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>752.3099999999999</v>
+        <v>753.62</v>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
@@ -9162,20 +9162,20 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="10" t="n">
-        <v>121.93</v>
+        <v>120.04</v>
       </c>
       <c r="D193" s="10" t="n">
-        <v>123.33</v>
+        <v>123.01</v>
       </c>
       <c r="E193" s="10" t="n">
-        <v>125.27</v>
+        <v>125.07</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>138.06</v>
+        <v>137.88</v>
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
@@ -9206,20 +9206,20 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="10" t="n">
-        <v>290</v>
+        <v>287.9</v>
       </c>
       <c r="D194" s="10" t="n">
-        <v>291.87</v>
+        <v>291.49</v>
       </c>
       <c r="E194" s="10" t="n">
-        <v>298.44</v>
+        <v>298.03</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>333.85</v>
+        <v>333.39</v>
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -9250,29 +9250,29 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="10" t="n">
-        <v>2880</v>
+        <v>2790.8</v>
       </c>
       <c r="D195" s="10" t="n">
-        <v>2905.84</v>
+        <v>2894.89</v>
       </c>
       <c r="E195" s="10" t="n">
-        <v>2808.96</v>
+        <v>2808.25</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>2602.54</v>
+        <v>2604.41</v>
       </c>
       <c r="G195" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H195" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H195" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I195" s="13" t="inlineStr">
@@ -9294,20 +9294,20 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="10" t="n">
-        <v>2593.8</v>
+        <v>2613.3</v>
       </c>
       <c r="D196" s="10" t="n">
-        <v>2716.69</v>
+        <v>2706.84</v>
       </c>
       <c r="E196" s="10" t="n">
-        <v>2702.19</v>
+        <v>2698.71</v>
       </c>
       <c r="F196" s="10" t="n">
-        <v>2619.27</v>
+        <v>2619.22</v>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
@@ -9338,20 +9338,20 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="10" t="n">
-        <v>784.7</v>
+        <v>783.75</v>
       </c>
       <c r="D197" s="10" t="n">
-        <v>742.41</v>
+        <v>746.35</v>
       </c>
       <c r="E197" s="10" t="n">
-        <v>675.96</v>
+        <v>680.1900000000001</v>
       </c>
       <c r="F197" s="10" t="n">
-        <v>573.92</v>
+        <v>576.01</v>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
@@ -9382,20 +9382,20 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="10" t="n">
-        <v>672.35</v>
+        <v>671.15</v>
       </c>
       <c r="D198" s="10" t="n">
-        <v>678.71</v>
+        <v>677.99</v>
       </c>
       <c r="E198" s="10" t="n">
-        <v>680.76</v>
+        <v>680.38</v>
       </c>
       <c r="F198" s="10" t="n">
-        <v>631.91</v>
+        <v>632.3</v>
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -9426,20 +9426,20 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="10" t="n">
-        <v>321.95</v>
+        <v>320.3</v>
       </c>
       <c r="D199" s="10" t="n">
-        <v>337.86</v>
+        <v>336.19</v>
       </c>
       <c r="E199" s="10" t="n">
-        <v>351.15</v>
+        <v>349.94</v>
       </c>
       <c r="F199" s="10" t="n">
-        <v>416.17</v>
+        <v>415.22</v>
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
@@ -9470,20 +9470,20 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="10" t="n">
-        <v>1632.1</v>
+        <v>1663</v>
       </c>
       <c r="D200" s="10" t="n">
-        <v>1725.44</v>
+        <v>1719.5</v>
       </c>
       <c r="E200" s="10" t="n">
-        <v>1844.92</v>
+        <v>1837.78</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>2005.79</v>
+        <v>2002.38</v>
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
@@ -9514,20 +9514,20 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="10" t="n">
-        <v>160.98</v>
+        <v>163.28</v>
       </c>
       <c r="D201" s="10" t="n">
-        <v>164.89</v>
+        <v>164.73</v>
       </c>
       <c r="E201" s="10" t="n">
-        <v>172.79</v>
+        <v>172.42</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>190.27</v>
+        <v>190</v>
       </c>
       <c r="G201" s="11" t="inlineStr">
         <is>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="10" t="n">
-        <v>116.41</v>
+        <v>118.8</v>
       </c>
       <c r="D202" s="10" t="n">
-        <v>119.41</v>
+        <v>119.35</v>
       </c>
       <c r="E202" s="10" t="n">
-        <v>123.36</v>
+        <v>123.18</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>126.15</v>
+        <v>126.08</v>
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
@@ -9602,20 +9602,20 @@
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="10" t="n">
-        <v>182.27</v>
+        <v>180.98</v>
       </c>
       <c r="D203" s="10" t="n">
-        <v>190.84</v>
+        <v>189.9</v>
       </c>
       <c r="E203" s="10" t="n">
-        <v>196.94</v>
+        <v>196.31</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>207.28</v>
+        <v>207.02</v>
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
@@ -9646,20 +9646,20 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="10" t="n">
-        <v>802.6</v>
+        <v>820.15</v>
       </c>
       <c r="D204" s="10" t="n">
-        <v>802.26</v>
+        <v>803.97</v>
       </c>
       <c r="E204" s="10" t="n">
-        <v>821.35</v>
+        <v>821.3</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>826.3099999999999</v>
+        <v>826.24</v>
       </c>
       <c r="G204" s="13" t="inlineStr">
         <is>
@@ -9690,20 +9690,20 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="10" t="n">
-        <v>112.66</v>
+        <v>111.96</v>
       </c>
       <c r="D205" s="10" t="n">
-        <v>113.73</v>
+        <v>113.56</v>
       </c>
       <c r="E205" s="10" t="n">
-        <v>117.22</v>
+        <v>117.01</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>135.32</v>
+        <v>135.08</v>
       </c>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9734,20 +9734,20 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="10" t="n">
-        <v>579.05</v>
+        <v>569.25</v>
       </c>
       <c r="D206" s="10" t="n">
-        <v>582.72</v>
+        <v>581.4400000000001</v>
       </c>
       <c r="E206" s="10" t="n">
-        <v>582.53</v>
+        <v>582.01</v>
       </c>
       <c r="F206" s="10" t="n">
-        <v>608.4</v>
+        <v>608.01</v>
       </c>
       <c r="G206" s="11" t="inlineStr">
         <is>
@@ -9778,20 +9778,20 @@
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="10" t="n">
-        <v>421.3</v>
+        <v>423.1</v>
       </c>
       <c r="D207" s="10" t="n">
-        <v>409.09</v>
+        <v>410.42</v>
       </c>
       <c r="E207" s="10" t="n">
-        <v>416.08</v>
+        <v>416.35</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>440.07</v>
+        <v>439.9</v>
       </c>
       <c r="G207" s="13" t="inlineStr">
         <is>
@@ -9822,20 +9822,20 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="10" t="n">
-        <v>129.97</v>
+        <v>130.66</v>
       </c>
       <c r="D208" s="10" t="n">
-        <v>127.87</v>
+        <v>128.13</v>
       </c>
       <c r="E208" s="10" t="n">
-        <v>127.15</v>
+        <v>127.29</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>136.64</v>
+        <v>136.58</v>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
@@ -9866,20 +9866,20 @@
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="10" t="n">
-        <v>152.16</v>
+        <v>152.94</v>
       </c>
       <c r="D209" s="10" t="n">
-        <v>154.74</v>
+        <v>154.57</v>
       </c>
       <c r="E209" s="10" t="n">
-        <v>158.37</v>
+        <v>158.16</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>169.85</v>
+        <v>169.68</v>
       </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
@@ -9910,20 +9910,20 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="10" t="n">
-        <v>105.03</v>
+        <v>104.85</v>
       </c>
       <c r="D210" s="10" t="n">
-        <v>106.53</v>
+        <v>106.37</v>
       </c>
       <c r="E210" s="10" t="n">
-        <v>105.82</v>
+        <v>105.79</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>113.43</v>
+        <v>113.35</v>
       </c>
       <c r="G210" s="11" t="inlineStr">
         <is>
@@ -9954,20 +9954,20 @@
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="10" t="n">
-        <v>1222.3</v>
+        <v>1213.1</v>
       </c>
       <c r="D211" s="10" t="n">
-        <v>1287.66</v>
+        <v>1280.56</v>
       </c>
       <c r="E211" s="10" t="n">
-        <v>1307.95</v>
+        <v>1304.23</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>1316.92</v>
+        <v>1315.88</v>
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
@@ -9998,20 +9998,20 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="10" t="n">
-        <v>125.07</v>
+        <v>123.19</v>
       </c>
       <c r="D212" s="10" t="n">
-        <v>126.69</v>
+        <v>126.36</v>
       </c>
       <c r="E212" s="10" t="n">
-        <v>130.5</v>
+        <v>130.21</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>151.35</v>
+        <v>151.07</v>
       </c>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -10042,24 +10042,24 @@
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="10" t="n">
-        <v>294.05</v>
+        <v>296.6</v>
       </c>
       <c r="D213" s="10" t="n">
-        <v>295.47</v>
+        <v>295.58</v>
       </c>
       <c r="E213" s="10" t="n">
-        <v>305.82</v>
+        <v>305.46</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>317.23</v>
-      </c>
-      <c r="G213" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>317.03</v>
+      </c>
+      <c r="G213" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H213" s="11" t="inlineStr">
@@ -10086,24 +10086,24 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="10" t="n">
-        <v>271.35</v>
+        <v>266.55</v>
       </c>
       <c r="D214" s="10" t="n">
-        <v>268.85</v>
+        <v>268.63</v>
       </c>
       <c r="E214" s="10" t="n">
-        <v>275.27</v>
+        <v>274.93</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>348.32</v>
-      </c>
-      <c r="G214" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>347.51</v>
+      </c>
+      <c r="G214" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H214" s="11" t="inlineStr">
@@ -10130,20 +10130,20 @@
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="10" t="n">
-        <v>848.75</v>
+        <v>840.15</v>
       </c>
       <c r="D215" s="10" t="n">
-        <v>823.5700000000001</v>
+        <v>825.15</v>
       </c>
       <c r="E215" s="10" t="n">
-        <v>813.45</v>
+        <v>814.49</v>
       </c>
       <c r="F215" s="10" t="n">
-        <v>803.4</v>
+        <v>803.76</v>
       </c>
       <c r="G215" s="13" t="inlineStr">
         <is>
@@ -10174,20 +10174,20 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="10" t="n">
-        <v>1507.2</v>
+        <v>1462.3</v>
       </c>
       <c r="D216" s="10" t="n">
-        <v>1251.54</v>
+        <v>1271.61</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>1089.58</v>
+        <v>1104.2</v>
       </c>
       <c r="F216" s="10" t="n">
-        <v>983.9</v>
+        <v>988.66</v>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
@@ -10218,20 +10218,20 @@
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="10" t="n">
-        <v>73.63</v>
+        <v>72.88</v>
       </c>
       <c r="D217" s="10" t="n">
-        <v>76.75</v>
+        <v>76.38</v>
       </c>
       <c r="E217" s="10" t="n">
-        <v>76.22</v>
+        <v>76.09</v>
       </c>
       <c r="F217" s="10" t="n">
-        <v>79.54000000000001</v>
+        <v>79.47</v>
       </c>
       <c r="G217" s="11" t="inlineStr">
         <is>
@@ -10262,20 +10262,20 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="10" t="n">
-        <v>116.12</v>
+        <v>119.48</v>
       </c>
       <c r="D218" s="10" t="n">
-        <v>124.29</v>
+        <v>123.83</v>
       </c>
       <c r="E218" s="10" t="n">
-        <v>133.11</v>
+        <v>132.57</v>
       </c>
       <c r="F218" s="10" t="n">
-        <v>160.78</v>
+        <v>160.37</v>
       </c>
       <c r="G218" s="11" t="inlineStr">
         <is>
@@ -10306,29 +10306,29 @@
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="10" t="n">
-        <v>1081.9</v>
+        <v>1069</v>
       </c>
       <c r="D219" s="10" t="n">
-        <v>1073.41</v>
+        <v>1072.99</v>
       </c>
       <c r="E219" s="10" t="n">
-        <v>1072.29</v>
+        <v>1072.16</v>
       </c>
       <c r="F219" s="10" t="n">
-        <v>1122.28</v>
-      </c>
-      <c r="G219" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H219" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1121.75</v>
+      </c>
+      <c r="G219" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H219" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I219" s="11" t="inlineStr">
@@ -10350,20 +10350,20 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="10" t="n">
-        <v>239.65</v>
+        <v>236.65</v>
       </c>
       <c r="D220" s="10" t="n">
-        <v>242.07</v>
+        <v>241.56</v>
       </c>
       <c r="E220" s="10" t="n">
-        <v>240.51</v>
+        <v>240.36</v>
       </c>
       <c r="F220" s="10" t="n">
-        <v>227.88</v>
+        <v>227.97</v>
       </c>
       <c r="G220" s="11" t="inlineStr">
         <is>
@@ -10394,20 +10394,20 @@
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="10" t="n">
-        <v>1532.5</v>
+        <v>1507.2</v>
       </c>
       <c r="D221" s="10" t="n">
-        <v>1543.01</v>
+        <v>1539.6</v>
       </c>
       <c r="E221" s="10" t="n">
-        <v>1551.59</v>
+        <v>1549.85</v>
       </c>
       <c r="F221" s="10" t="n">
-        <v>1891.46</v>
+        <v>1887.64</v>
       </c>
       <c r="G221" s="11" t="inlineStr">
         <is>
@@ -10438,20 +10438,20 @@
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="10" t="n">
-        <v>599.3</v>
+        <v>605.65</v>
       </c>
       <c r="D222" s="10" t="n">
-        <v>609.85</v>
+        <v>609.45</v>
       </c>
       <c r="E222" s="10" t="n">
-        <v>620.1799999999999</v>
+        <v>619.61</v>
       </c>
       <c r="F222" s="10" t="n">
-        <v>626.15</v>
+        <v>625.95</v>
       </c>
       <c r="G222" s="11" t="inlineStr">
         <is>
@@ -10482,20 +10482,20 @@
       </c>
       <c r="B223" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="10" t="n">
-        <v>22.98</v>
+        <v>22.82</v>
       </c>
       <c r="D223" s="10" t="n">
-        <v>23.8</v>
+        <v>23.71</v>
       </c>
       <c r="E223" s="10" t="n">
-        <v>23.61</v>
+        <v>23.58</v>
       </c>
       <c r="F223" s="10" t="n">
-        <v>24.95</v>
+        <v>24.93</v>
       </c>
       <c r="G223" s="11" t="inlineStr">
         <is>
@@ -10526,20 +10526,20 @@
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="10" t="n">
-        <v>660.65</v>
+        <v>653.9</v>
       </c>
       <c r="D224" s="10" t="n">
-        <v>644.85</v>
+        <v>645.71</v>
       </c>
       <c r="E224" s="10" t="n">
-        <v>613.25</v>
+        <v>614.85</v>
       </c>
       <c r="F224" s="10" t="n">
-        <v>598.98</v>
+        <v>599.53</v>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="10" t="n">
-        <v>378.45</v>
+        <v>377.3</v>
       </c>
       <c r="D225" s="10" t="n">
-        <v>405.29</v>
+        <v>402.63</v>
       </c>
       <c r="E225" s="10" t="n">
-        <v>425.37</v>
+        <v>423.49</v>
       </c>
       <c r="F225" s="10" t="n">
-        <v>477.62</v>
+        <v>476.62</v>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -10614,20 +10614,20 @@
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="10" t="n">
-        <v>211.18</v>
+        <v>212.05</v>
       </c>
       <c r="D226" s="10" t="n">
-        <v>215.76</v>
+        <v>215.41</v>
       </c>
       <c r="E226" s="10" t="n">
-        <v>224.51</v>
+        <v>224.02</v>
       </c>
       <c r="F226" s="10" t="n">
-        <v>243.28</v>
+        <v>242.97</v>
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -10658,20 +10658,20 @@
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="10" t="n">
-        <v>490.3</v>
+        <v>493.05</v>
       </c>
       <c r="D227" s="10" t="n">
-        <v>505.23</v>
+        <v>504.07</v>
       </c>
       <c r="E227" s="10" t="n">
-        <v>499.75</v>
+        <v>499.49</v>
       </c>
       <c r="F227" s="10" t="n">
-        <v>475.66</v>
+        <v>475.83</v>
       </c>
       <c r="G227" s="11" t="inlineStr">
         <is>
@@ -10702,20 +10702,20 @@
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="10" t="n">
-        <v>116.44</v>
+        <v>116.08</v>
       </c>
       <c r="D228" s="10" t="n">
-        <v>112.84</v>
+        <v>113.15</v>
       </c>
       <c r="E228" s="10" t="n">
-        <v>112.45</v>
+        <v>112.59</v>
       </c>
       <c r="F228" s="10" t="n">
-        <v>122.41</v>
+        <v>122.34</v>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
@@ -10746,29 +10746,29 @@
       </c>
       <c r="B229" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="10" t="n">
-        <v>214.94</v>
+        <v>216.69</v>
       </c>
       <c r="D229" s="10" t="n">
-        <v>214.7</v>
+        <v>214.89</v>
       </c>
       <c r="E229" s="10" t="n">
-        <v>215.59</v>
+        <v>215.63</v>
       </c>
       <c r="F229" s="10" t="n">
-        <v>224.6</v>
+        <v>224.52</v>
       </c>
       <c r="G229" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H229" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H229" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I229" s="11" t="inlineStr">
@@ -10790,20 +10790,20 @@
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="10" t="n">
-        <v>1867.9</v>
+        <v>1863.8</v>
       </c>
       <c r="D230" s="10" t="n">
-        <v>1914.18</v>
+        <v>1909.38</v>
       </c>
       <c r="E230" s="10" t="n">
-        <v>1898.28</v>
+        <v>1896.93</v>
       </c>
       <c r="F230" s="10" t="n">
-        <v>1780.62</v>
+        <v>1781.45</v>
       </c>
       <c r="G230" s="11" t="inlineStr">
         <is>
@@ -10834,20 +10834,20 @@
       </c>
       <c r="B231" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="10" t="n">
-        <v>706.95</v>
+        <v>697.35</v>
       </c>
       <c r="D231" s="10" t="n">
-        <v>682.34</v>
+        <v>683.77</v>
       </c>
       <c r="E231" s="10" t="n">
-        <v>645.1799999999999</v>
+        <v>647.23</v>
       </c>
       <c r="F231" s="10" t="n">
-        <v>609.78</v>
+        <v>610.65</v>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
@@ -10878,20 +10878,20 @@
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="10" t="n">
-        <v>176.49</v>
+        <v>177.03</v>
       </c>
       <c r="D232" s="10" t="n">
-        <v>175.9</v>
+        <v>176.01</v>
       </c>
       <c r="E232" s="10" t="n">
-        <v>181.55</v>
+        <v>181.37</v>
       </c>
       <c r="F232" s="10" t="n">
-        <v>214.19</v>
+        <v>213.82</v>
       </c>
       <c r="G232" s="13" t="inlineStr">
         <is>
@@ -10922,20 +10922,20 @@
       </c>
       <c r="B233" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="10" t="n">
-        <v>5528</v>
+        <v>5501</v>
       </c>
       <c r="D233" s="10" t="n">
-        <v>5683.79</v>
+        <v>5666.39</v>
       </c>
       <c r="E233" s="10" t="n">
-        <v>5807.5</v>
+        <v>5795.48</v>
       </c>
       <c r="F233" s="10" t="n">
-        <v>5752.56</v>
+        <v>5750.05</v>
       </c>
       <c r="G233" s="11" t="inlineStr">
         <is>
@@ -10966,20 +10966,20 @@
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="10" t="n">
-        <v>326</v>
+        <v>323.45</v>
       </c>
       <c r="D234" s="10" t="n">
-        <v>333.1</v>
+        <v>332.18</v>
       </c>
       <c r="E234" s="10" t="n">
-        <v>336.95</v>
+        <v>336.42</v>
       </c>
       <c r="F234" s="10" t="n">
-        <v>383.14</v>
+        <v>382.55</v>
       </c>
       <c r="G234" s="11" t="inlineStr">
         <is>
@@ -11010,20 +11010,20 @@
       </c>
       <c r="B235" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="10" t="n">
-        <v>27.08</v>
+        <v>27.22</v>
       </c>
       <c r="D235" s="10" t="n">
-        <v>28.1</v>
+        <v>28.01</v>
       </c>
       <c r="E235" s="10" t="n">
-        <v>29.85</v>
+        <v>29.74</v>
       </c>
       <c r="F235" s="10" t="n">
-        <v>35.34</v>
+        <v>35.26</v>
       </c>
       <c r="G235" s="11" t="inlineStr">
         <is>
@@ -11054,24 +11054,24 @@
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="10" t="n">
-        <v>193.5</v>
+        <v>189.51</v>
       </c>
       <c r="D236" s="10" t="n">
-        <v>191.96</v>
+        <v>191.72</v>
       </c>
       <c r="E236" s="10" t="n">
-        <v>196.79</v>
+        <v>196.5</v>
       </c>
       <c r="F236" s="10" t="n">
-        <v>210.86</v>
-      </c>
-      <c r="G236" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>210.64</v>
+      </c>
+      <c r="G236" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H236" s="11" t="inlineStr">
@@ -11098,20 +11098,20 @@
       </c>
       <c r="B237" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="10" t="n">
-        <v>132.85</v>
+        <v>132.31</v>
       </c>
       <c r="D237" s="10" t="n">
-        <v>129.4</v>
+        <v>129.68</v>
       </c>
       <c r="E237" s="10" t="n">
-        <v>129.45</v>
+        <v>129.56</v>
       </c>
       <c r="F237" s="10" t="n">
-        <v>124.72</v>
+        <v>124.8</v>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
@@ -11142,20 +11142,20 @@
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="10" t="n">
-        <v>7.13</v>
+        <v>7.34</v>
       </c>
       <c r="D238" s="10" t="n">
-        <v>8.18</v>
+        <v>8.1</v>
       </c>
       <c r="E238" s="10" t="n">
-        <v>9.81</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F238" s="10" t="n">
-        <v>12.92</v>
+        <v>12.87</v>
       </c>
       <c r="G238" s="11" t="inlineStr">
         <is>
@@ -11186,20 +11186,20 @@
       </c>
       <c r="B239" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="10" t="n">
-        <v>95.29000000000001</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="D239" s="10" t="n">
-        <v>100.26</v>
+        <v>99.92</v>
       </c>
       <c r="E239" s="10" t="n">
-        <v>105.53</v>
+        <v>105.18</v>
       </c>
       <c r="F239" s="10" t="n">
-        <v>120.43</v>
+        <v>120.19</v>
       </c>
       <c r="G239" s="11" t="inlineStr">
         <is>
@@ -11230,20 +11230,20 @@
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="10" t="n">
-        <v>295.9</v>
+        <v>297.2</v>
       </c>
       <c r="D240" s="10" t="n">
-        <v>302.73</v>
+        <v>302.21</v>
       </c>
       <c r="E240" s="10" t="n">
-        <v>304.83</v>
+        <v>304.53</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>330.06</v>
+        <v>329.73</v>
       </c>
       <c r="G240" s="11" t="inlineStr">
         <is>
@@ -11274,20 +11274,20 @@
       </c>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="10" t="n">
-        <v>442.65</v>
+        <v>444.45</v>
       </c>
       <c r="D241" s="10" t="n">
-        <v>479.18</v>
+        <v>475.87</v>
       </c>
       <c r="E241" s="10" t="n">
-        <v>507.29</v>
+        <v>504.83</v>
       </c>
       <c r="F241" s="10" t="n">
-        <v>611.99</v>
+        <v>610.3200000000001</v>
       </c>
       <c r="G241" s="11" t="inlineStr">
         <is>
@@ -11318,20 +11318,20 @@
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="10" t="n">
-        <v>63.56</v>
+        <v>64.33</v>
       </c>
       <c r="D242" s="10" t="n">
-        <v>66.11</v>
+        <v>65.94</v>
       </c>
       <c r="E242" s="10" t="n">
-        <v>66.61</v>
+        <v>66.53</v>
       </c>
       <c r="F242" s="10" t="n">
-        <v>71.97</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G242" s="11" t="inlineStr">
         <is>
@@ -11362,20 +11362,20 @@
       </c>
       <c r="B243" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="10" t="n">
-        <v>1485.7</v>
+        <v>1498.5</v>
       </c>
       <c r="D243" s="10" t="n">
-        <v>1515.74</v>
+        <v>1514.1</v>
       </c>
       <c r="E243" s="10" t="n">
-        <v>1531.31</v>
+        <v>1530.02</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>1687.06</v>
+        <v>1685.19</v>
       </c>
       <c r="G243" s="11" t="inlineStr">
         <is>
@@ -11406,20 +11406,20 @@
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="10" t="n">
-        <v>120.02</v>
+        <v>119.16</v>
       </c>
       <c r="D244" s="10" t="n">
-        <v>123.82</v>
+        <v>123.37</v>
       </c>
       <c r="E244" s="10" t="n">
-        <v>129</v>
+        <v>128.61</v>
       </c>
       <c r="F244" s="10" t="n">
-        <v>135.04</v>
+        <v>134.89</v>
       </c>
       <c r="G244" s="11" t="inlineStr">
         <is>
@@ -11450,20 +11450,20 @@
       </c>
       <c r="B245" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="10" t="n">
-        <v>66.83</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D245" s="10" t="n">
-        <v>68.38</v>
+        <v>68.23</v>
       </c>
       <c r="E245" s="10" t="n">
-        <v>69.87</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="F245" s="10" t="n">
-        <v>75.72</v>
+        <v>75.63</v>
       </c>
       <c r="G245" s="11" t="inlineStr">
         <is>
@@ -11494,20 +11494,20 @@
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="10" t="n">
-        <v>703.35</v>
+        <v>695.6</v>
       </c>
       <c r="D246" s="10" t="n">
-        <v>732.74</v>
+        <v>729.2</v>
       </c>
       <c r="E246" s="10" t="n">
-        <v>748.47</v>
+        <v>746.39</v>
       </c>
       <c r="F246" s="10" t="n">
-        <v>758.59</v>
+        <v>757.96</v>
       </c>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -11538,20 +11538,20 @@
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="10" t="n">
-        <v>460.35</v>
+        <v>461.35</v>
       </c>
       <c r="D247" s="10" t="n">
-        <v>432.51</v>
+        <v>435.26</v>
       </c>
       <c r="E247" s="10" t="n">
-        <v>428.54</v>
+        <v>429.83</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>431.94</v>
+        <v>432.23</v>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
@@ -11582,20 +11582,20 @@
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="10" t="n">
-        <v>580.2</v>
+        <v>582.4</v>
       </c>
       <c r="D248" s="10" t="n">
-        <v>617.39</v>
+        <v>613.38</v>
       </c>
       <c r="E248" s="10" t="n">
-        <v>690.66</v>
+        <v>685.61</v>
       </c>
       <c r="F248" s="10" t="n">
-        <v>799.59</v>
+        <v>796.48</v>
       </c>
       <c r="G248" s="11" t="inlineStr">
         <is>
@@ -11626,20 +11626,20 @@
       </c>
       <c r="B249" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="10" t="n">
-        <v>3997.6</v>
+        <v>3993</v>
       </c>
       <c r="D249" s="10" t="n">
-        <v>4121.15</v>
+        <v>4108.94</v>
       </c>
       <c r="E249" s="10" t="n">
-        <v>4285.73</v>
+        <v>4274.25</v>
       </c>
       <c r="F249" s="10" t="n">
-        <v>4479.21</v>
+        <v>4474.37</v>
       </c>
       <c r="G249" s="11" t="inlineStr">
         <is>
@@ -11670,20 +11670,20 @@
       </c>
       <c r="B250" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="10" t="n">
-        <v>714.9</v>
+        <v>720.65</v>
       </c>
       <c r="D250" s="10" t="n">
-        <v>712.96</v>
+        <v>713.6900000000001</v>
       </c>
       <c r="E250" s="10" t="n">
-        <v>737.6799999999999</v>
+        <v>737.02</v>
       </c>
       <c r="F250" s="10" t="n">
-        <v>786.53</v>
+        <v>785.87</v>
       </c>
       <c r="G250" s="13" t="inlineStr">
         <is>
@@ -11714,20 +11714,20 @@
       </c>
       <c r="B251" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="10" t="n">
-        <v>431.6</v>
+        <v>446.75</v>
       </c>
       <c r="D251" s="10" t="n">
-        <v>413.81</v>
+        <v>416.95</v>
       </c>
       <c r="E251" s="10" t="n">
-        <v>423.46</v>
+        <v>424.38</v>
       </c>
       <c r="F251" s="10" t="n">
-        <v>431.36</v>
+        <v>431.51</v>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 25-Sep-2026  15:43:30    |    Closing Price Date: 25-Sep-2026</t>
+          <t>Scan Run: 28-Sep-2026  18:23:49    |    Closing Price Date: 28-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>46.4</v>
+        <v>27.2</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>35.6</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>25-Sep-2026  15:43:30</t>
+          <t>28-Sep-2026  18:23:49</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 39.2% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 27.2% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): NEUTRAL — 46.4% stocks above EMA (mixed market)</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 35.6% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 51.2% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.8% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 98 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 68 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 116 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 89 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 128 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 127 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>241.88</v>
+        <v>242.05</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>247.74</v>
+        <v>247.2</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>258.5</v>
+        <v>257.85</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>291.4</v>
+        <v>291.07</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>304.35</v>
+        <v>307.25</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>322.86</v>
+        <v>321.37</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>322.06</v>
+        <v>321.48</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>324.62</v>
+        <v>324.46</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>6825.5</v>
+        <v>6515.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>6245.41</v>
+        <v>6271.14</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5613.88</v>
+        <v>5649.24</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>4455.38</v>
+        <v>4473.01</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -893,24 +893,24 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>751.55</v>
+        <v>722</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>745.23</v>
+        <v>743.02</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>706.86</v>
+        <v>707.45</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>564.1900000000001</v>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>565.61</v>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>270</v>
+        <v>264.5</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>271.79</v>
+        <v>271.09</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>256.86</v>
+        <v>257.16</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>171.18</v>
+        <v>172.12</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>354.5</v>
+        <v>339.25</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>360.23</v>
+        <v>358.24</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>332.45</v>
+        <v>332.72</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>235.83</v>
+        <v>237.02</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,29 +1025,29 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>6900</v>
+        <v>7072.5</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>7092.77</v>
+        <v>7090.84</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>6963.26</v>
+        <v>6967.54</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5601.67</v>
+        <v>5615.8</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
@@ -1069,29 +1069,29 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>809.3</v>
+        <v>786.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>841.33</v>
+        <v>836.08</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>795.09</v>
+        <v>794.74</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>642.59</v>
+        <v>644.02</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -1113,24 +1113,24 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>335.5</v>
+        <v>321.85</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>325.03</v>
+        <v>324.73</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>311.14</v>
+        <v>311.56</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>261.59</v>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>262.24</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>5134.5</v>
+        <v>5011.5</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>5169.14</v>
+        <v>5154.13</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>5319.47</v>
+        <v>5307.39</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>4569.4</v>
+        <v>4572.14</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>181.42</v>
+        <v>177.47</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>177.09</v>
+        <v>177.12</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>173.66</v>
+        <v>173.81</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>165.95</v>
+        <v>166</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2728</v>
+        <v>2723.2</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2736.86</v>
+        <v>2735.56</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>2633.22</v>
+        <v>2636.75</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>2179.57</v>
+        <v>2184.26</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>598.95</v>
+        <v>601.2</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>604.71</v>
+        <v>604.38</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>590.28</v>
+        <v>590.71</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>575.36</v>
+        <v>575.95</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2328.5</v>
+        <v>2310.2</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>2299.39</v>
+        <v>2300.42</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>2120.52</v>
+        <v>2127.95</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1578.17</v>
+        <v>1584.72</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>3594.1</v>
+        <v>3605.3</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>3495.54</v>
+        <v>3505.99</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>3493.83</v>
+        <v>3498.2</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3250.76</v>
+        <v>3248.38</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>395.6</v>
+        <v>408.3</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>394.89</v>
+        <v>396.16</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>392.29</v>
+        <v>392.92</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>339.2</v>
+        <v>340.59</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>759.4</v>
+        <v>753.1</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>760.7</v>
+        <v>759.97</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>735.23</v>
+        <v>735.9299999999999</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>638.33</v>
+        <v>638.87</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>837.2</v>
+        <v>825.35</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>802.78</v>
+        <v>804.9299999999999</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>717.42</v>
+        <v>721.65</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>467.6</v>
+        <v>471.02</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>217.99</v>
+        <v>208.05</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>205.8</v>
+        <v>206.02</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>188.79</v>
+        <v>189.54</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>166.04</v>
+        <v>166.45</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>14.11</v>
+        <v>13.52</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>12.86</v>
+        <v>12.92</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>11.57</v>
+        <v>11.65</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10.52</v>
+        <v>10.54</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>246.05</v>
+        <v>260.1</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>237.62</v>
+        <v>239.76</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>235.81</v>
+        <v>236.76</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>200.67</v>
+        <v>201.26</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>2008.4</v>
+        <v>1977.2</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>2070.91</v>
+        <v>2061.99</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>2021.68</v>
+        <v>2019.94</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1728.98</v>
+        <v>1729.78</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>221.89</v>
+        <v>216.16</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>226.52</v>
+        <v>225.53</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>227.27</v>
+        <v>226.83</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>210.1</v>
+        <v>209.89</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>64.70999999999999</v>
+        <v>63.09</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>65.43000000000001</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>65.77</v>
+        <v>65.67</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>60.53</v>
+        <v>60.54</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,24 +1817,24 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>163.87</v>
+        <v>160.47</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>163.7</v>
+        <v>163.4</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>164.46</v>
+        <v>164.31</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>150.78</v>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>150.79</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>181.22</v>
+        <v>183.44</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>181.96</v>
+        <v>182.1</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>185.49</v>
+        <v>185.41</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>188.38</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>188.35</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>494.75</v>
+        <v>497.3</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>508.33</v>
+        <v>507.28</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>530.37</v>
+        <v>529.0700000000001</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>538.13</v>
+        <v>536.97</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
         <v>340.9</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>350.97</v>
+        <v>350.01</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>333.02</v>
+        <v>333.32</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>271.38</v>
+        <v>271.81</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>1387.34</v>
+        <v>1380.45</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>1346.32</v>
+        <v>1345.09</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1060.36</v>
+        <v>1064.99</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>376.45</v>
+        <v>379.65</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>366.56</v>
+        <v>367.8</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>350.92</v>
+        <v>352.05</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>309.43</v>
+        <v>310.12</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>581.7</v>
+        <v>561.65</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>556.47</v>
+        <v>556.96</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>529.79</v>
+        <v>531.04</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>475.54</v>
+        <v>476.13</v>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1767</v>
+        <v>1739.2</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1646.86</v>
+        <v>1655.66</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>1581.21</v>
+        <v>1587.41</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1281.12</v>
+        <v>1285.49</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>793.55</v>
+        <v>796.95</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>793.25</v>
+        <v>793.6</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>747.83</v>
+        <v>749.75</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>557.95</v>
+        <v>558.9400000000001</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,24 +2213,24 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>605.5</v>
+        <v>585.35</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>605.41</v>
+        <v>603.5</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>606.4</v>
+        <v>605.58</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>598.77</v>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>597.66</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -2238,9 +2238,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J35" s="13" t="inlineStr">
@@ -2257,29 +2257,29 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>535.25</v>
+        <v>499.2</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>531.49</v>
+        <v>528.42</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>528.5599999999999</v>
+        <v>527.41</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>483.11</v>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>483.73</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>184.79</v>
+        <v>181.51</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>189.9</v>
+        <v>189.1</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>196.63</v>
+        <v>196.04</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>200.99</v>
+        <v>200.92</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>753.15</v>
+        <v>741.5</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>789.05</v>
+        <v>784.52</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>850.3200000000001</v>
+        <v>846.05</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>954.0700000000001</v>
+        <v>950.1900000000001</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>506.5</v>
+        <v>502.6</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>540.24</v>
+        <v>536.66</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>582.46</v>
+        <v>579.3200000000001</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>613.9299999999999</v>
+        <v>613.74</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>331.1</v>
+        <v>318.3</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>345.42</v>
+        <v>342.84</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>352.03</v>
+        <v>350.71</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>343.24</v>
+        <v>342.44</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>219.35</v>
+        <v>215.45</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>212.42</v>
+        <v>212.71</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>208.3</v>
+        <v>208.58</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>177.52</v>
+        <v>177.78</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>98.56</v>
+        <v>95.97</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>86.55</v>
+        <v>87.44</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>85.73999999999999</v>
+        <v>86.14</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>73.36</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>215.58</v>
+        <v>211.52</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>226.1</v>
+        <v>224.71</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>222.53</v>
+        <v>222.1</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>217.19</v>
+        <v>216.69</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1622.4</v>
+        <v>1590.1</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1650.62</v>
+        <v>1644.86</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1660.97</v>
+        <v>1658.19</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1406.75</v>
+        <v>1409.04</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>310.5</v>
+        <v>307.15</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>338.33</v>
+        <v>335.36</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>360.06</v>
+        <v>357.99</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>399.66</v>
+        <v>397.68</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,29 +2697,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>566.85</v>
+        <v>548.3</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>568.62</v>
+        <v>566.6799999999999</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>566.8</v>
+        <v>566.0700000000001</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>498.79</v>
+        <v>499.18</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>160.31</v>
+        <v>160.08</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>165.39</v>
+        <v>164.88</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>172.07</v>
+        <v>171.6</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>208.24</v>
+        <v>207.77</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1218.9</v>
+        <v>1199.6</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1222.02</v>
+        <v>1219.88</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1160.1</v>
+        <v>1161.65</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1050.42</v>
+        <v>1051.99</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,29 +2829,29 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>881.9</v>
+        <v>861.75</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>896.65</v>
+        <v>893.33</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>869.97</v>
+        <v>869.64</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>728.05</v>
+        <v>728.99</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>172.32</v>
+        <v>170</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>174.08</v>
+        <v>173.69</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>177.33</v>
+        <v>177.04</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>180.29</v>
+        <v>179.9</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,24 +2917,24 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>285.8</v>
+        <v>275.8</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>281.74</v>
+        <v>281.18</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>289.61</v>
+        <v>289.07</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>298.8</v>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>297.98</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>455.15</v>
+        <v>452.25</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>484.2</v>
+        <v>481.16</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>515.5</v>
+        <v>513.02</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>532.91</v>
+        <v>531.9</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4662.4</v>
+        <v>4457.2</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>4200.89</v>
+        <v>4225.3</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>3867.29</v>
+        <v>3890.42</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2923.26</v>
+        <v>2938.31</v>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>578.1</v>
+        <v>579.85</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>564.79</v>
+        <v>566.23</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>548.62</v>
+        <v>549.85</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>534.0700000000001</v>
+        <v>535.77</v>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
@@ -3093,24 +3093,24 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>1972.7</v>
+        <v>1918.2</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>1950.27</v>
+        <v>1947.21</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>1981.93</v>
+        <v>1979.43</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1846.52</v>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1844.7</v>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>200.22</v>
+        <v>192.89</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>186.74</v>
+        <v>187.33</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>172.16</v>
+        <v>172.98</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>139.94</v>
+        <v>139.99</v>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
@@ -3181,29 +3181,29 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>551.15</v>
+        <v>535.65</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>555.88</v>
+        <v>553.95</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>548.3200000000001</v>
+        <v>547.8200000000001</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>502.47</v>
+        <v>502.88</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr">
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1582.8</v>
+        <v>1555.9</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>1633.01</v>
+        <v>1625.67</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>1673.54</v>
+        <v>1668.93</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1777.56</v>
+        <v>1775.12</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3269,24 +3269,24 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>159.19</v>
+        <v>150.16</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>158.68</v>
+        <v>157.87</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>161.46</v>
+        <v>161.02</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>169.92</v>
-      </c>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>169.45</v>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>3142.3</v>
+        <v>3033.5</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>3214.73</v>
+        <v>3197.47</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>3164.51</v>
+        <v>3159.37</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2727.64</v>
+        <v>2728.92</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>244.35</v>
+        <v>241</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>253.77</v>
+        <v>252.56</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>257.77</v>
+        <v>257.11</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>238.95</v>
+        <v>238.58</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>463</v>
+        <v>453.45</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>484.95</v>
+        <v>481.95</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>502.73</v>
+        <v>500.8</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>565.95</v>
+        <v>562.4400000000001</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,29 +3445,29 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>582.6</v>
+        <v>572.3</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>583.88</v>
+        <v>582.77</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>574.03</v>
+        <v>573.96</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>530.1900000000001</v>
+        <v>530.62</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H63" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H63" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr">
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>21.26</v>
+        <v>20.55</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>22.1</v>
+        <v>21.95</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>22.27</v>
+        <v>22.2</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>22.43</v>
+        <v>22.36</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>198.85</v>
+        <v>193</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>201.26</v>
+        <v>200.48</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>203.99</v>
+        <v>203.56</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>204.24</v>
+        <v>203.94</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>234.78</v>
+        <v>230.4</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>202.16</v>
+        <v>204.85</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>202.38</v>
+        <v>203.47</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>193.18</v>
+        <v>193.36</v>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
@@ -3621,29 +3621,29 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>672.2</v>
+        <v>658.95</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>678.48</v>
+        <v>676.62</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>669.8099999999999</v>
+        <v>669.38</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>656</v>
+        <v>655.6900000000001</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H67" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr">
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>1892.1</v>
+        <v>1879.5</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>1802.63</v>
+        <v>1809.95</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1729.86</v>
+        <v>1735.73</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1642.12</v>
+        <v>1647.42</v>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
@@ -3709,24 +3709,24 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>687.6</v>
+        <v>672</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>677.76</v>
+        <v>677.21</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>700.24</v>
+        <v>699.13</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>813.77</v>
-      </c>
-      <c r="G69" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>812.21</v>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
@@ -3753,24 +3753,24 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>2156.8</v>
+        <v>2051.1</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>2109.1</v>
+        <v>2103.58</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>2033.28</v>
+        <v>2033.98</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1672.3</v>
-      </c>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1676.13</v>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H70" s="14" t="inlineStr">
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>6640</v>
+        <v>6653.5</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>6712.54</v>
+        <v>6706.92</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>6771.88</v>
+        <v>6767.24</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>5616.39</v>
+        <v>5619.32</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>49.95</v>
+        <v>48.64</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>46.69</v>
+        <v>46.87</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>45.99</v>
+        <v>46.1</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>42.1</v>
+        <v>42.14</v>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>466.9</v>
+        <v>465.15</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>477.59</v>
+        <v>476.41</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>495.92</v>
+        <v>494.71</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>575.4400000000001</v>
+        <v>572.37</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,29 +3929,29 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>141.35</v>
+        <v>138.57</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>146.02</v>
+        <v>145.31</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>141.19</v>
+        <v>141.08</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>150.04</v>
+        <v>149.92</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H74" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr">
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>2189.6</v>
+        <v>2153.9</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>2239.71</v>
+        <v>2231.54</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2209.12</v>
+        <v>2206.96</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1822.27</v>
+        <v>1825.31</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>297</v>
+        <v>290.75</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>318.28</v>
+        <v>315.66</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>343.68</v>
+        <v>341.6</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>359.33</v>
+        <v>358.34</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>749.6</v>
+        <v>729.1</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>761.5700000000001</v>
+        <v>758.48</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>794.6799999999999</v>
+        <v>792.11</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>874.71</v>
+        <v>873.23</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,29 +4105,29 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>333.7</v>
+        <v>323.75</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>327.47</v>
+        <v>327.11</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>331.78</v>
+        <v>331.47</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>361.76</v>
-      </c>
-      <c r="G78" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H78" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>361.23</v>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I78" s="12" t="inlineStr">
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>2778.3</v>
+        <v>2748.4</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>2729.66</v>
+        <v>2731.44</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>2628.85</v>
+        <v>2633.53</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2522.34</v>
+        <v>2523.09</v>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>176.65</v>
+        <v>170.74</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>182.28</v>
+        <v>181.18</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>192.72</v>
+        <v>191.86</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>210.65</v>
+        <v>209.61</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,24 +4237,24 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>163.2</v>
+        <v>159.88</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>161.75</v>
+        <v>161.58</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>157.8</v>
+        <v>157.88</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>155.18</v>
-      </c>
-      <c r="G81" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>155.31</v>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H81" s="14" t="inlineStr">
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>67.03</v>
+        <v>66.02</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>72.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>73.64</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>70.18000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,29 +4325,29 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>209.05</v>
+        <v>202.85</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>199.6</v>
+        <v>199.91</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>203.39</v>
+        <v>203.36</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>184.33</v>
+        <v>184.49</v>
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H83" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I83" s="14" t="inlineStr">
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>630.3</v>
+        <v>620.65</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>583.2</v>
+        <v>586.77</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>556.08</v>
+        <v>558.62</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>505.5</v>
+        <v>506.54</v>
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
@@ -4413,29 +4413,29 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>15.89</v>
+        <v>15.41</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>15.85</v>
+        <v>15.81</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>15.83</v>
+        <v>15.81</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>15.97</v>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H85" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>15.9</v>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>832.9</v>
+        <v>826.05</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>838.6900000000001</v>
+        <v>837.48</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>875.37</v>
+        <v>873.4400000000001</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>937.88</v>
+        <v>937.49</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>2385.2</v>
+        <v>2396.3</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>2315.16</v>
+        <v>2322.88</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>2208.91</v>
+        <v>2216.26</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1845.96</v>
+        <v>1851.13</v>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
@@ -4545,29 +4545,29 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>668.95</v>
+        <v>657.35</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>658.89</v>
+        <v>658.74</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>658.39</v>
+        <v>658.34</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>626.65</v>
-      </c>
-      <c r="G88" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H88" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>626.63</v>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>1230.4</v>
+        <v>1207.8</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>1276.97</v>
+        <v>1270.38</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>1326.11</v>
+        <v>1321.47</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1304.79</v>
+        <v>1303.6</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4633,20 +4633,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>136.83</v>
+        <v>135.45</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>133.27</v>
+        <v>133.48</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>127.43</v>
+        <v>127.74</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>117.72</v>
+        <v>117.73</v>
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
@@ -4677,17 +4677,17 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>532.5</v>
+        <v>541.3</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>541.85</v>
+        <v>541.8</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>513.6</v>
+        <v>514.6799999999999</v>
       </c>
       <c r="F91" s="11" t="n">
         <v>498.27</v>
@@ -4721,29 +4721,29 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>1676.3</v>
+        <v>1592.8</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>1738.74</v>
+        <v>1724.84</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>1662.76</v>
+        <v>1660.02</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1236.88</v>
+        <v>1240.42</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H92" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>79.67</v>
+        <v>76.33</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>72.5</v>
+        <v>72.87</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>73.54000000000001</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>69.81999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="G93" s="14" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>336.95</v>
+        <v>331.55</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>327.98</v>
+        <v>328.32</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>308.61</v>
+        <v>309.51</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>250.29</v>
+        <v>250.72</v>
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>274.95</v>
+        <v>268.55</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>282.68</v>
+        <v>281.33</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>306.9</v>
+        <v>305.4</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>396.52</v>
+        <v>395.03</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>549.05</v>
+        <v>543.6</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>551.92</v>
+        <v>551.13</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>541.9299999999999</v>
+        <v>542</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>461.59</v>
+        <v>463.06</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4941,29 +4941,29 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>799.75</v>
+        <v>783.15</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>782.14</v>
+        <v>782.24</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>788.48</v>
+        <v>788.27</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>725.23</v>
+        <v>725.8</v>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H97" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H97" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I97" s="14" t="inlineStr">
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>233.17</v>
+        <v>228.01</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>235.01</v>
+        <v>234.34</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>247.24</v>
+        <v>246.48</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>293.03</v>
+        <v>292.57</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,20 +5029,20 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1771.9</v>
+        <v>1732.3</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1809.14</v>
+        <v>1801.82</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1837.69</v>
+        <v>1833.55</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1784.3</v>
+        <v>1788.72</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
@@ -5073,29 +5073,29 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>214.09</v>
+        <v>207.46</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>217.18</v>
+        <v>216.25</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>207.74</v>
+        <v>207.73</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>186.42</v>
+        <v>186.66</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H100" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>827.75</v>
+        <v>828.7</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>865.0700000000001</v>
+        <v>861.61</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>878.6799999999999</v>
+        <v>876.72</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>760.0599999999999</v>
+        <v>760.46</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>408.45</v>
+        <v>398.15</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>410.16</v>
+        <v>409.02</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>396.81</v>
+        <v>396.87</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>372.24</v>
+        <v>372.16</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>654.9</v>
+        <v>653</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>663.11</v>
+        <v>662.15</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>693.64</v>
+        <v>692.04</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>779.46</v>
+        <v>778.08</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>10709</v>
+        <v>10513</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>10782.4</v>
+        <v>10756.74</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>10500.02</v>
+        <v>10500.53</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>9525.76</v>
+        <v>9534.110000000001</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>691.95</v>
+        <v>678.65</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>717.2</v>
+        <v>713.53</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>743.9299999999999</v>
+        <v>741.37</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>715.0700000000001</v>
+        <v>716.08</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>88.55</v>
+        <v>87.98</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>91.06999999999999</v>
+        <v>90.77</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>91.76000000000001</v>
+        <v>91.61</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>85.91</v>
+        <v>85.89</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -5381,20 +5381,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>2026.8</v>
+        <v>2032</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>2008.09</v>
+        <v>2010.37</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>1898.04</v>
+        <v>1903.29</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1653.58</v>
+        <v>1658.62</v>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
@@ -5425,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>1013.45</v>
+        <v>1025.25</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>963.0599999999999</v>
+        <v>968.98</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>854.33</v>
+        <v>861.03</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>603.61</v>
+        <v>607.0599999999999</v>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
@@ -5469,24 +5469,24 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>1184.9</v>
+        <v>1151.4</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1159.69</v>
+        <v>1158.9</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>1103.74</v>
+        <v>1105.6</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1019.2</v>
-      </c>
-      <c r="G109" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1019.55</v>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H109" s="14" t="inlineStr">
@@ -5513,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>669.7</v>
+        <v>642.5</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>687.84</v>
+        <v>683.53</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>718.76</v>
+        <v>715.76</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>860.42</v>
+        <v>855.4299999999999</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5557,24 +5557,24 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>445.75</v>
+        <v>440.2</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>442.9</v>
+        <v>442.64</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>426.11</v>
+        <v>426.66</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>354.98</v>
-      </c>
-      <c r="G111" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>356.05</v>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H111" s="14" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>985.2</v>
+        <v>984.75</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>910.36</v>
+        <v>917.45</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>877.47</v>
+        <v>881.6799999999999</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>800.1799999999999</v>
+        <v>802.08</v>
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>420.15</v>
+        <v>422.9</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>419.75</v>
+        <v>420.05</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>408.33</v>
+        <v>408.9</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>399.78</v>
+        <v>399.93</v>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>200.38</v>
+        <v>199.42</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>204.42</v>
+        <v>203.95</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>211.41</v>
+        <v>210.94</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>239.62</v>
+        <v>238.91</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>73.23</v>
+        <v>71.75</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>75.25</v>
+        <v>74.92</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>82.02</v>
+        <v>81.62</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>92.84999999999999</v>
+        <v>92.53</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>309.9</v>
+        <v>297.5</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>419.19</v>
+        <v>407.6</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>679.42</v>
+        <v>664.4400000000001</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>895.12</v>
+        <v>888.4</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>368.5</v>
+        <v>359.05</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>354.25</v>
+        <v>354.71</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>329.24</v>
+        <v>330.41</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>319.84</v>
+        <v>320.23</v>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>3097.9</v>
+        <v>3171.3</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>3322.14</v>
+        <v>3307.77</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>3255.95</v>
+        <v>3252.63</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>2926.44</v>
+        <v>2927.55</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>4746.8</v>
+        <v>4645.3</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>4498.93</v>
+        <v>4512.87</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>4394.32</v>
+        <v>4404.16</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>3735.49</v>
+        <v>3742.01</v>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>654.3</v>
+        <v>647.3</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>665.75</v>
+        <v>663.99</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>688.13</v>
+        <v>686.53</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>750.5599999999999</v>
+        <v>749.75</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>339.75</v>
+        <v>357.35</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>313.82</v>
+        <v>317.97</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>331.52</v>
+        <v>332.53</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>389.21</v>
+        <v>388.81</v>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>508.25</v>
+        <v>501.9</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>509.21</v>
+        <v>508.51</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>526.5</v>
+        <v>525.54</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>584.9</v>
+        <v>584.03</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
@@ -6085,20 +6085,20 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>645.15</v>
+        <v>650.35</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>633.28</v>
+        <v>634.9</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>600.14</v>
+        <v>602.11</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>515.59</v>
+        <v>517.86</v>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
@@ -6129,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1381.8</v>
+        <v>1387.4</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1465.38</v>
+        <v>1457.96</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1418.41</v>
+        <v>1417.2</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1171.96</v>
+        <v>1175.2</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,20 +6173,20 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>209.99</v>
+        <v>211.04</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>214.74</v>
+        <v>214.39</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>219.81</v>
+        <v>219.46</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>237.15</v>
+        <v>236.84</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>599.45</v>
+        <v>576.35</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>509.73</v>
+        <v>516.08</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>505.69</v>
+        <v>508.46</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>535.05</v>
+        <v>535.46</v>
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
@@ -6261,29 +6261,29 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>398.65</v>
+        <v>382.95</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>402.43</v>
+        <v>400.57</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>393.59</v>
+        <v>393.17</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>370.87</v>
+        <v>370.29</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H127" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I127" s="14" t="inlineStr">
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>760.1</v>
+        <v>766.5</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>800.72</v>
+        <v>797.46</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>794.35</v>
+        <v>793.26</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>741.6900000000001</v>
+        <v>742.71</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>819.55</v>
+        <v>799.95</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>783</v>
+        <v>784.61</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>740.8200000000001</v>
+        <v>743.14</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>614.39</v>
+        <v>615.46</v>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>209.62</v>
+        <v>206.1</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>200.77</v>
+        <v>201.28</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>184.74</v>
+        <v>185.58</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>162.98</v>
+        <v>163.37</v>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
@@ -6437,20 +6437,20 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>698.65</v>
+        <v>691.2</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>700.38</v>
+        <v>699.5</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>691.0599999999999</v>
+        <v>691.0700000000001</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>650.27</v>
+        <v>650.24</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>419.8</v>
+        <v>410.6</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>425.7</v>
+        <v>424.26</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>431.4</v>
+        <v>430.59</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>466.77</v>
+        <v>465.14</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>689.6</v>
+        <v>671.85</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>739.13</v>
+        <v>732.72</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>764.3200000000001</v>
+        <v>760.6900000000001</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>763.35</v>
+        <v>759.59</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6569,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>1625.9</v>
+        <v>1613.3</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>1706.57</v>
+        <v>1697.69</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>1715.88</v>
+        <v>1711.86</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1479.32</v>
+        <v>1480.65</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>230.45</v>
+        <v>225.4</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>238.36</v>
+        <v>237.13</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>246.32</v>
+        <v>245.5</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>257.84</v>
+        <v>257.52</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>92.51000000000001</v>
+        <v>91.61</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>95.29000000000001</v>
+        <v>94.94</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>91.16</v>
+        <v>91.17</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>77.98</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>407.4</v>
+        <v>402.05</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>400.25</v>
+        <v>400.42</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>378.21</v>
+        <v>379.14</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>372.05</v>
+        <v>372.39</v>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1965.5</v>
+        <v>1926</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1998.34</v>
+        <v>1991.45</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>2108.31</v>
+        <v>2101.16</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>2151.27</v>
+        <v>2145.74</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,29 +6789,29 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>619.5</v>
+        <v>595.15</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>618.37</v>
+        <v>616.15</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>612.21</v>
+        <v>611.54</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>559.17</v>
-      </c>
-      <c r="G139" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H139" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>560.7</v>
+      </c>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I139" s="14" t="inlineStr">
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>315.9</v>
+        <v>311.95</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>323.6</v>
+        <v>322.49</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>330.25</v>
+        <v>329.54</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>344.79</v>
+        <v>344.56</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,29 +6877,29 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>422.1</v>
+        <v>409.05</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>430.44</v>
+        <v>428.4</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>413.84</v>
+        <v>413.65</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>323.42</v>
+        <v>324.27</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H141" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I141" s="14" t="inlineStr">
@@ -6921,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>1164.9</v>
+        <v>1138.8</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>1171.06</v>
+        <v>1167.99</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>1092.24</v>
+        <v>1094.06</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>868.4400000000001</v>
+        <v>871.13</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>138.2</v>
+        <v>139.68</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>128.6</v>
+        <v>129.65</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>127.3</v>
+        <v>127.78</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>122.29</v>
+        <v>122.35</v>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>214.72</v>
+        <v>211.22</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>215.76</v>
+        <v>215.33</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>218.36</v>
+        <v>218.08</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>215.2</v>
+        <v>215.23</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>265.65</v>
+        <v>263.85</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>281.25</v>
+        <v>279.59</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>289.89</v>
+        <v>288.86</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>283.36</v>
+        <v>282.96</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>108.58</v>
+        <v>109.95</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>111.09</v>
+        <v>110.98</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>116.25</v>
+        <v>116</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>126.04</v>
+        <v>125.78</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>151.68</v>
+        <v>150.72</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>154.71</v>
+        <v>154.33</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>154.73</v>
+        <v>154.58</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>149.01</v>
+        <v>148.93</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7185,29 +7185,29 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>469.25</v>
+        <v>449.65</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>441.35</v>
+        <v>442.14</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>454.07</v>
+        <v>453.9</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>513.5</v>
+        <v>512.65</v>
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H148" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H148" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I148" s="12" t="inlineStr">
@@ -7229,20 +7229,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>102.68</v>
+        <v>101.9</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>95.69</v>
+        <v>96.28</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>96.5</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>102.74</v>
+        <v>102.7</v>
       </c>
       <c r="G149" s="14" t="inlineStr">
         <is>
@@ -7273,29 +7273,29 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>2117.7</v>
+        <v>2053.3</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>2150.57</v>
+        <v>2141.3</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>2098.27</v>
+        <v>2096.51</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1830.44</v>
+        <v>1832.66</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H150" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H150" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I150" s="14" t="inlineStr">
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>2407.3</v>
+        <v>2364.3</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>2419.89</v>
+        <v>2414.59</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>2467.48</v>
+        <v>2463.43</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>2496.98</v>
+        <v>2491.13</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,20 +7361,20 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>1121.4</v>
+        <v>1100.4</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>1043.98</v>
+        <v>1049.35</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>962.46</v>
+        <v>967.87</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>822.92</v>
+        <v>824.99</v>
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>1872.8</v>
+        <v>1865.1</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>1929.95</v>
+        <v>1923.78</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>1838.33</v>
+        <v>1839.38</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1591.06</v>
+        <v>1589.9</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>1821.8</v>
+        <v>1790.1</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>1757.61</v>
+        <v>1760.7</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>1591.83</v>
+        <v>1599.6</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1317.31</v>
+        <v>1321.32</v>
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
@@ -7493,29 +7493,29 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>286.35</v>
+        <v>276.5</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>282.97</v>
+        <v>282.35</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>281.18</v>
+        <v>281</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>241.95</v>
-      </c>
-      <c r="G155" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H155" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>242.29</v>
+      </c>
+      <c r="G155" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H155" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I155" s="14" t="inlineStr">
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>13153</v>
+        <v>13139</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>12077.21</v>
+        <v>12178.33</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>11559.52</v>
+        <v>11621.46</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>10372.06</v>
+        <v>10388.59</v>
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>2067</v>
+        <v>2036.4</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>2091.88</v>
+        <v>2086.6</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>2141.45</v>
+        <v>2137.33</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>2215.75</v>
+        <v>2212.52</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,20 +7625,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>1329.1</v>
+        <v>1296.1</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>1198.73</v>
+        <v>1208</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>1139.41</v>
+        <v>1145.56</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>946.3200000000001</v>
+        <v>950.49</v>
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>634.6</v>
+        <v>629.3</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>659.6799999999999</v>
+        <v>656.78</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>675.28</v>
+        <v>673.48</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>654.25</v>
+        <v>654.03</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>482.55</v>
+        <v>482.75</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>480.48</v>
+        <v>480.7</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>498.8</v>
+        <v>498.17</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>543.35</v>
+        <v>542.74</v>
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
@@ -7757,17 +7757,17 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>125.67</v>
+        <v>123.14</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>116.5</v>
+        <v>117.13</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>112.92</v>
+        <v>113.32</v>
       </c>
       <c r="F161" s="11" t="n">
         <v>115.14</v>
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>405.05</v>
+        <v>416</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>419.24</v>
+        <v>418.93</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>418.81</v>
+        <v>418.7</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>397.92</v>
+        <v>399.76</v>
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
@@ -7845,29 +7845,29 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>156.8</v>
+        <v>153.04</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>154.19</v>
+        <v>154.08</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>154.98</v>
+        <v>154.91</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>162.31</v>
-      </c>
-      <c r="G163" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H163" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>162.1</v>
+      </c>
+      <c r="G163" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H163" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I163" s="12" t="inlineStr">
@@ -7889,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>510.35</v>
+        <v>494.8</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>516.92</v>
+        <v>514.8200000000001</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>536.84</v>
+        <v>535.1900000000001</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>623.9400000000001</v>
+        <v>622.76</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7933,24 +7933,24 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>740.8</v>
+        <v>710.4</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>724.21</v>
+        <v>722.89</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>685.41</v>
+        <v>686.39</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>574.02</v>
-      </c>
-      <c r="G165" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>575.2</v>
+      </c>
+      <c r="G165" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H165" s="14" t="inlineStr">
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>191.07</v>
+        <v>189.66</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>196.39</v>
+        <v>195.75</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>200.03</v>
+        <v>199.63</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>225.92</v>
+        <v>225.05</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>206.38</v>
+        <v>199.72</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>213.65</v>
+        <v>212.33</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>223.17</v>
+        <v>222.25</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>227.32</v>
+        <v>226.77</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,29 +8065,29 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>529.9</v>
+        <v>511.65</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>532.1</v>
+        <v>530.15</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>514.98</v>
+        <v>514.85</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>479.74</v>
+        <v>480.06</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H168" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H168" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I168" s="14" t="inlineStr">
@@ -8109,24 +8109,24 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>427.4</v>
+        <v>429.65</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>427.68</v>
+        <v>427.87</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>418.87</v>
+        <v>419.29</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>406.56</v>
-      </c>
-      <c r="G169" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>406.24</v>
+      </c>
+      <c r="G169" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H169" s="14" t="inlineStr">
@@ -8153,24 +8153,24 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>834.85</v>
+        <v>848.35</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>842.01</v>
+        <v>842.62</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>794.54</v>
+        <v>796.65</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>665.71</v>
-      </c>
-      <c r="G170" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>667.05</v>
+      </c>
+      <c r="G170" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr">
@@ -8197,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>417.2</v>
+        <v>413.75</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>432.5</v>
+        <v>430.72</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>442.75</v>
+        <v>441.61</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>458.07</v>
+        <v>457.45</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8241,24 +8241,24 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>1128.6</v>
+        <v>1110</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>1121.73</v>
+        <v>1120.62</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>1106.44</v>
+        <v>1106.58</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>1051.14</v>
-      </c>
-      <c r="G172" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1054.16</v>
+      </c>
+      <c r="G172" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr">
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>135.45</v>
+        <v>131.26</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>159.14</v>
+        <v>156.49</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>185.59</v>
+        <v>183.46</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>217.8</v>
+        <v>216.82</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>506.8</v>
+        <v>495.1</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>524.3099999999999</v>
+        <v>521.52</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>516.9400000000001</v>
+        <v>516.08</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>512.71</v>
+        <v>512.79</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>758.55</v>
+        <v>809.95</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>641.72</v>
+        <v>657.74</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>593.24</v>
+        <v>601.74</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>527.55</v>
+        <v>529.34</v>
       </c>
       <c r="G175" s="14" t="inlineStr">
         <is>
@@ -8417,20 +8417,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>155.09</v>
+        <v>154.88</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>155.56</v>
+        <v>155.49</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>157.15</v>
+        <v>157.06</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>156.73</v>
+        <v>156.65</v>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
@@ -8461,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>178.84</v>
+        <v>175.55</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>182.4</v>
+        <v>181.75</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>190.43</v>
+        <v>189.85</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>239.21</v>
+        <v>238.1</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>1517.8</v>
+        <v>1592.7</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>1456.15</v>
+        <v>1469.15</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>1361.06</v>
+        <v>1370.14</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1122.56</v>
+        <v>1130.32</v>
       </c>
       <c r="G178" s="14" t="inlineStr">
         <is>
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>242.27</v>
+        <v>234.32</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>248.11</v>
+        <v>246.79</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>247.22</v>
+        <v>246.71</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>242.36</v>
+        <v>242.14</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8593,24 +8593,24 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>381.85</v>
+        <v>370.35</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>373.91</v>
+        <v>373.57</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>369.46</v>
+        <v>369.5</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>331.95</v>
-      </c>
-      <c r="G180" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>332.34</v>
+      </c>
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H180" s="14" t="inlineStr">
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>26.75</v>
+        <v>25.98</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>27.25</v>
+        <v>27.13</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>28.43</v>
+        <v>28.34</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>34.02</v>
+        <v>34</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>7.27</v>
+        <v>7.23</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>7.79</v>
+        <v>7.75</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>9.01</v>
+        <v>9</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>613</v>
+        <v>600.5</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>616.99</v>
+        <v>615.42</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>640.1</v>
+        <v>638.54</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>625.75</v>
+        <v>625.5</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>247.55</v>
+        <v>242.4</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>255.26</v>
+        <v>254.04</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>283.36</v>
+        <v>281.75</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>340.54</v>
+        <v>339.15</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8813,20 +8813,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>804.55</v>
+        <v>769.5</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>738.03</v>
+        <v>741.03</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>768.59</v>
+        <v>768.62</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>871.84</v>
+        <v>869.17</v>
       </c>
       <c r="G185" s="14" t="inlineStr">
         <is>
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>13052</v>
+        <v>12804</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>13212.61</v>
+        <v>13173.69</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>13112.9</v>
+        <v>13100.78</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>13143.5</v>
+        <v>13116.83</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>346.7</v>
+        <v>343.7</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>341.78</v>
+        <v>341.96</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>338.95</v>
+        <v>339.14</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>330.67</v>
+        <v>330.91</v>
       </c>
       <c r="G187" s="14" t="inlineStr">
         <is>
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>58.07</v>
+        <v>56.03</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>58.23</v>
+        <v>58.02</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>59.66</v>
+        <v>59.52</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>65.40000000000001</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>1365.6</v>
+        <v>1345.5</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>1376.68</v>
+        <v>1373.71</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>1321.34</v>
+        <v>1322.29</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1137.04</v>
+        <v>1138.84</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9033,24 +9033,24 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>850.3</v>
+        <v>839.1</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>844.15</v>
+        <v>843.67</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>876.62</v>
+        <v>875.15</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>968.8200000000001</v>
-      </c>
-      <c r="G190" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>964.95</v>
+      </c>
+      <c r="G190" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
@@ -9077,29 +9077,29 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>807.6</v>
+        <v>784.2</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>778.85</v>
+        <v>779.36</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>791.52</v>
+        <v>791.24</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>782.6799999999999</v>
+        <v>782.47</v>
       </c>
       <c r="G191" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H191" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H191" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I191" s="14" t="inlineStr">
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>939.55</v>
+        <v>914</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>859.74</v>
+        <v>864.9</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>813.17</v>
+        <v>817.12</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>759.33</v>
+        <v>760.5700000000001</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9165,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>120.27</v>
+        <v>117.39</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>122.4</v>
+        <v>121.92</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>124.57</v>
+        <v>124.29</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>137.35</v>
+        <v>137.02</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>283</v>
+        <v>276.75</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>289.55</v>
+        <v>288.33</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>296.21</v>
+        <v>295.45</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>331.51</v>
+        <v>330.45</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,24 +9253,24 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>2918</v>
+        <v>2881.7</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>2899.87</v>
+        <v>2898.14</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>2823.12</v>
+        <v>2825.42</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>2616.32</v>
-      </c>
-      <c r="G195" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2618.96</v>
+      </c>
+      <c r="G195" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H195" s="14" t="inlineStr">
@@ -9297,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>2552.8</v>
+        <v>2518.2</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>2679.82</v>
+        <v>2664.43</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>2688.09</v>
+        <v>2681.42</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>2613.75</v>
+        <v>2605.23</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9341,24 +9341,24 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>754.5</v>
+        <v>749.5</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>752.1900000000001</v>
+        <v>751.9400000000001</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>692.74</v>
+        <v>694.97</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>583.08</v>
-      </c>
-      <c r="G197" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>583.99</v>
+      </c>
+      <c r="G197" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H197" s="14" t="inlineStr">
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>652.55</v>
+        <v>650.65</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>672.5599999999999</v>
+        <v>670.47</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>677.78</v>
+        <v>676.72</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>633.05</v>
+        <v>633.22</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,24 +9429,24 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>338.5</v>
+        <v>332.6</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>335.78</v>
+        <v>335.47</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>348.17</v>
+        <v>347.56</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>412.7</v>
-      </c>
-      <c r="G199" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>410.83</v>
+      </c>
+      <c r="G199" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H199" s="12" t="inlineStr">
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>1677.1</v>
+        <v>1632</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>1709.56</v>
+        <v>1702.17</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>1820.12</v>
+        <v>1812.74</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>1989.86</v>
+        <v>1983.81</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>156.8</v>
+        <v>155.08</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>163.45</v>
+        <v>162.65</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>171</v>
+        <v>170.38</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>188.86</v>
+        <v>188.12</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>121.05</v>
+        <v>119.97</v>
       </c>
       <c r="D202" s="11" t="n">
         <v>119.89</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>122.98</v>
+        <v>122.86</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>125.83</v>
+        <v>125.72</v>
       </c>
       <c r="G202" s="14" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>180.63</v>
+        <v>177.48</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>187.54</v>
+        <v>186.59</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>194.56</v>
+        <v>193.89</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>206.32</v>
+        <v>205.99</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,24 +9649,24 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>819.1</v>
+        <v>801.25</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>806.75</v>
+        <v>806.23</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>820.5599999999999</v>
+        <v>819.8</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>827.24</v>
-      </c>
-      <c r="G204" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>825.35</v>
+      </c>
+      <c r="G204" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H204" s="12" t="inlineStr">
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>113.12</v>
+        <v>110.17</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>113.42</v>
+        <v>113.11</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>116.56</v>
+        <v>116.31</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>134.39</v>
+        <v>133.98</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>555.95</v>
+        <v>554.3</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>574.08</v>
+        <v>572.2</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>578.74</v>
+        <v>577.78</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>606.39</v>
+        <v>605.87</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,24 +9781,24 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>412.45</v>
+        <v>406.9</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>410.52</v>
+        <v>410.18</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>414.87</v>
+        <v>414.56</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>436.87</v>
-      </c>
-      <c r="G207" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>435.72</v>
+      </c>
+      <c r="G207" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -9825,29 +9825,29 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>129.36</v>
+        <v>126.53</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>128.47</v>
+        <v>128.29</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>127.53</v>
+        <v>127.49</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>136.37</v>
-      </c>
-      <c r="G208" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H208" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>136.28</v>
+      </c>
+      <c r="G208" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H208" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I208" s="12" t="inlineStr">
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>154.16</v>
+        <v>151.61</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>154.46</v>
+        <v>154.18</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>157.7</v>
+        <v>157.46</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>169.62</v>
+        <v>168.67</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>103.47</v>
+        <v>102.18</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>105.79</v>
+        <v>105.44</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>105.6</v>
+        <v>105.47</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>113.12</v>
+        <v>112.65</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>1225.2</v>
+        <v>1214.2</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>1268.56</v>
+        <v>1263.38</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>1296.39</v>
+        <v>1293.17</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>1312.33</v>
+        <v>1310.07</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>122.16</v>
+        <v>119.43</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>125.5</v>
+        <v>124.92</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>129.4</v>
+        <v>129.01</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>148.83</v>
+        <v>147.41</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>291.15</v>
+        <v>283.15</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>295.02</v>
+        <v>293.89</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>304.11</v>
+        <v>303.29</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>316.34</v>
+        <v>316</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,20 +10089,20 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>257.2</v>
+        <v>250.2</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>267.04</v>
+        <v>265.43</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>273.55</v>
+        <v>272.63</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>344.28</v>
+        <v>343.47</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>863.75</v>
+        <v>854.35</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>832.47</v>
+        <v>834.55</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>818.85</v>
+        <v>820.24</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>804.73</v>
+        <v>804.48</v>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1505.2</v>
+        <v>1480.1</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>1323.97</v>
+        <v>1338.84</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>1145.8</v>
+        <v>1158.91</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>1004.97</v>
+        <v>1010.26</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10221,20 +10221,20 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>72.34</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>75.5</v>
+        <v>75.2</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>75.73999999999999</v>
+        <v>75.61</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>79.27</v>
+        <v>79.09</v>
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>117.68</v>
+        <v>116.13</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>122.42</v>
+        <v>121.82</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>130.7</v>
+        <v>130.13</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>158.84</v>
+        <v>157.96</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10309,29 +10309,29 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>1070.3</v>
+        <v>1086.4</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>1074.69</v>
+        <v>1075.81</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>1073.28</v>
+        <v>1073.79</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>1120.56</v>
-      </c>
-      <c r="G219" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H219" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1120.15</v>
+      </c>
+      <c r="G219" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H219" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I219" s="12" t="inlineStr">
@@ -10353,20 +10353,20 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>238.1</v>
+        <v>235</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>240.73</v>
+        <v>240.19</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>240.14</v>
+        <v>239.94</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>228.29</v>
+        <v>228.21</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10397,24 +10397,24 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1539.8</v>
+        <v>1511.8</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1538.28</v>
+        <v>1535.76</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1548.07</v>
+        <v>1546.65</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1877.62</v>
-      </c>
-      <c r="G221" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1873.15</v>
+      </c>
+      <c r="G221" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H221" s="12" t="inlineStr">
@@ -10441,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>599.85</v>
+        <v>594.2</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>608.1</v>
+        <v>606.78</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>617.9</v>
+        <v>616.97</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>624.45</v>
+        <v>623.4299999999999</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10485,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>23.31</v>
+        <v>22.91</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>23.55</v>
+        <v>23.49</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>23.52</v>
+        <v>23.5</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>24.83</v>
+        <v>24.79</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10529,24 +10529,24 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>657.8</v>
+        <v>642.5</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>651.38</v>
+        <v>650.53</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>620.84</v>
+        <v>621.6900000000001</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>601.15</v>
-      </c>
-      <c r="G224" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>600.89</v>
+      </c>
+      <c r="G224" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H224" s="14" t="inlineStr">
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>370.85</v>
+        <v>361.3</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>395.34</v>
+        <v>392.1</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>417.97</v>
+        <v>415.75</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>473.67</v>
+        <v>472.84</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10617,29 +10617,29 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>227.45</v>
+        <v>220.1</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>216.68</v>
+        <v>217</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>223.57</v>
+        <v>223.43</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>242.14</v>
+        <v>241.56</v>
       </c>
       <c r="G226" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H226" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H226" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I226" s="12" t="inlineStr">
@@ -10661,24 +10661,24 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>500</v>
+        <v>503.6</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>502.79</v>
+        <v>502.87</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>499.44</v>
+        <v>499.6</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>477.09</v>
-      </c>
-      <c r="G227" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>477.08</v>
+      </c>
+      <c r="G227" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H227" s="14" t="inlineStr">
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>116.31</v>
+        <v>115.15</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>113.89</v>
+        <v>114.01</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>112.98</v>
+        <v>113.06</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>121.99</v>
+        <v>121.76</v>
       </c>
       <c r="G228" s="14" t="inlineStr">
         <is>
@@ -10749,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>213.87</v>
+        <v>209.99</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>214.95</v>
+        <v>214.48</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>215.58</v>
+        <v>215.36</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>223.58</v>
+        <v>223.63</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>1847.7</v>
+        <v>1799.8</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>1893.72</v>
+        <v>1884.77</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>1891.98</v>
+        <v>1888.37</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>1782.46</v>
+        <v>1791.69</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10837,20 +10837,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>715.65</v>
+        <v>714.35</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>690.42</v>
+        <v>692.7</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>654.23</v>
+        <v>656.59</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>613.16</v>
+        <v>614.0599999999999</v>
       </c>
       <c r="G231" s="14" t="inlineStr">
         <is>
@@ -10881,29 +10881,29 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>182.79</v>
+        <v>177.14</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>177.56</v>
+        <v>177.52</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>181.43</v>
+        <v>181.26</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>212.87</v>
-      </c>
-      <c r="G232" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H232" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>212.51</v>
+      </c>
+      <c r="G232" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H232" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I232" s="12" t="inlineStr">
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>5396.5</v>
+        <v>5196</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>5614.29</v>
+        <v>5574.45</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>5758.45</v>
+        <v>5736.39</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>5739.03</v>
+        <v>5724.29</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>318.95</v>
+        <v>314.65</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>329.78</v>
+        <v>328.34</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>334.92</v>
+        <v>334.12</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>381.21</v>
+        <v>380.8</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11013,20 +11013,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>26.96</v>
+        <v>26.2</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>27.75</v>
+        <v>27.6</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>29.43</v>
+        <v>29.3</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>34.89</v>
+        <v>34.83</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>186.61</v>
+        <v>182.42</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>190.73</v>
+        <v>189.94</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>195.41</v>
+        <v>194.91</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>209.74</v>
+        <v>209.38</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,29 +11101,29 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>130.26</v>
+        <v>128.5</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>130.02</v>
+        <v>129.88</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>129.73</v>
+        <v>129.68</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>124.94</v>
-      </c>
-      <c r="G237" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H237" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>124.55</v>
+      </c>
+      <c r="G237" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H237" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I237" s="14" t="inlineStr">
@@ -11145,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>7.5</v>
+        <v>7.22</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>7.95</v>
+        <v>7.88</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>12.69</v>
+        <v>12.62</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11189,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>100.08</v>
+        <v>96.28</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>100.08</v>
+        <v>99.72</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>104.66</v>
+        <v>104.33</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>119.16</v>
+        <v>118.71</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11233,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>301.2</v>
+        <v>296.25</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>301.74</v>
+        <v>301.22</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>304.06</v>
+        <v>303.76</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>328.53</v>
+        <v>328.81</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>453.1</v>
+        <v>444.55</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>471.07</v>
+        <v>468.54</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>499.45</v>
+        <v>497.3</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>604.78</v>
+        <v>602.64</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11321,20 +11321,20 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>64.95999999999999</v>
+        <v>63.51</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>65.87</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>66.43000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>71.56</v>
+        <v>71.48</v>
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
@@ -11365,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>1464.2</v>
+        <v>1453.2</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>1504.76</v>
+        <v>1499.85</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>1524.21</v>
+        <v>1521.43</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>1678.54</v>
+        <v>1676.93</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>120.36</v>
+        <v>115.95</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>122.5</v>
+        <v>121.88</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>127.64</v>
+        <v>127.18</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>134.28</v>
+        <v>133.99</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>66.67</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>67.92</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>69.44</v>
+        <v>69.3</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>75.28</v>
+        <v>75.17</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>694.45</v>
+        <v>679.05</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>721.53</v>
+        <v>717.49</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>741.14</v>
+        <v>738.71</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>755.87</v>
+        <v>754.49</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,24 +11541,24 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>456.85</v>
+        <v>434.7</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>441.27</v>
+        <v>440.64</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>433.07</v>
+        <v>433.14</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>432.98</v>
-      </c>
-      <c r="G247" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>433.26</v>
+      </c>
+      <c r="G247" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H247" s="14" t="inlineStr">
@@ -11585,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>585.55</v>
+        <v>572.4</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>605.54</v>
+        <v>602.38</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>674.01</v>
+        <v>670.03</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>789.5</v>
+        <v>788.48</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>3945.3</v>
+        <v>3976.2</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>4073.42</v>
+        <v>4064.16</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>4240.21</v>
+        <v>4229.85</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>4459.26</v>
+        <v>4450.19</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11673,24 +11673,24 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>720.9</v>
+        <v>700.3</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>716.3200000000001</v>
+        <v>714.79</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>735.55</v>
+        <v>734.16</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>782.1799999999999</v>
-      </c>
-      <c r="G250" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>780.17</v>
+      </c>
+      <c r="G250" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H250" s="12" t="inlineStr">
@@ -11717,29 +11717,29 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>427.45</v>
+        <v>422.4</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>422.15</v>
+        <v>422.17</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>425.85</v>
+        <v>425.71</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>431.69</v>
+        <v>431.6</v>
       </c>
       <c r="G251" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H251" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H251" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I251" s="12" t="inlineStr">

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 28-Sep-2026  18:23:49    |    Closing Price Date: 28-Sep-2026</t>
+          <t>Scan Run: 29-Sep-2026  16:46:42    |    Closing Price Date: 29-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>27.2</v>
+        <v>32.4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>35.6</v>
+        <v>37.6</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50.8</v>
+        <v>49.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>28-Sep-2026  18:23:49</t>
+          <t>29-Sep-2026  16:46:42</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 27.2% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 32.4% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 35.6% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 37.6% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 50.8% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 49.6% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 68 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 81 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 89 of 250 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 94 of 250 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 127 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 124 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>242.05</v>
+        <v>243.96</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>247.2</v>
+        <v>246.89</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>257.85</v>
+        <v>257.31</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>291.07</v>
+        <v>290.6</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>307.25</v>
+        <v>307.05</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>321.37</v>
+        <v>320.01</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>321.48</v>
+        <v>320.92</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>324.46</v>
+        <v>324.29</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>6515.5</v>
+        <v>6616.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>6271.14</v>
+        <v>6304.03</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5649.24</v>
+        <v>5687.17</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>4473.01</v>
+        <v>4494.34</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -893,24 +893,24 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>722</v>
+        <v>777.35</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>743.02</v>
+        <v>746.29</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>707.45</v>
+        <v>710.1900000000001</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>565.61</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>567.72</v>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
@@ -937,24 +937,24 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>264.5</v>
+        <v>288</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>271.09</v>
+        <v>272.7</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>257.16</v>
+        <v>258.37</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>172.12</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>173.27</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>339.25</v>
+        <v>352.05</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>358.24</v>
+        <v>357.65</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>332.72</v>
+        <v>333.48</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>237.02</v>
+        <v>238.16</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>7072.5</v>
+        <v>7426</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>7090.84</v>
+        <v>7122.76</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>6967.54</v>
+        <v>6985.52</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5615.8</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>5633.82</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -1069,29 +1069,29 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>786.2</v>
+        <v>806.05</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>836.08</v>
+        <v>833.22</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>794.74</v>
+        <v>795.1900000000001</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>644.02</v>
+        <v>645.63</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>321.85</v>
+        <v>324.25</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>324.73</v>
+        <v>324.68</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>311.56</v>
+        <v>312.06</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>262.24</v>
+        <v>262.86</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>5011.5</v>
+        <v>5204.5</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>5154.13</v>
+        <v>5158.93</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>5307.39</v>
+        <v>5303.36</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>4572.14</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>4578.43</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -1201,24 +1201,24 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>177.47</v>
+        <v>176.49</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>177.12</v>
+        <v>177.06</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>173.81</v>
+        <v>173.92</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>166</v>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>166.11</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -1245,24 +1245,24 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2723.2</v>
+        <v>2914.2</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2735.56</v>
+        <v>2752.57</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>2636.75</v>
+        <v>2647.63</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>2184.26</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2191.52</v>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>601.2</v>
+        <v>622.4</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>604.38</v>
+        <v>606.09</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>590.71</v>
+        <v>591.95</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>575.95</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>576.41</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2310.2</v>
+        <v>2302</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>2300.42</v>
+        <v>2300.57</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>2127.95</v>
+        <v>2134.78</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1584.72</v>
+        <v>1591.86</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>3605.3</v>
+        <v>3605.5</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>3505.99</v>
+        <v>3515.47</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>3498.2</v>
+        <v>3502.4</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3248.38</v>
+        <v>3251.93</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>408.3</v>
+        <v>402.6</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>396.16</v>
+        <v>396.78</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>392.92</v>
+        <v>393.3</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>340.59</v>
+        <v>341.21</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>753.1</v>
+        <v>749.35</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>759.97</v>
+        <v>758.96</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>735.9299999999999</v>
+        <v>736.46</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>638.87</v>
+        <v>639.97</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>825.35</v>
+        <v>866.6</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>804.9299999999999</v>
+        <v>810.8</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>721.65</v>
+        <v>727.33</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>471.02</v>
+        <v>474.96</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>208.05</v>
+        <v>214.15</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>206.02</v>
+        <v>206.79</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>189.54</v>
+        <v>190.51</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>166.45</v>
+        <v>166.93</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>13.52</v>
+        <v>13.23</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>12.92</v>
+        <v>12.95</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>11.65</v>
+        <v>11.71</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10.54</v>
+        <v>10.57</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>260.1</v>
+        <v>271.63</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>239.76</v>
+        <v>242.8</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>236.76</v>
+        <v>238.13</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>201.26</v>
+        <v>201.96</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,29 +1685,29 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1977.2</v>
+        <v>2093.8</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>2061.99</v>
+        <v>2065.02</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>2019.94</v>
+        <v>2022.83</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1729.78</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1733.4</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>216.16</v>
+        <v>215.23</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>225.53</v>
+        <v>224.55</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>226.83</v>
+        <v>226.37</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>209.89</v>
+        <v>209.94</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,24 +1773,24 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>63.09</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>65.20999999999999</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>65.67</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>60.54</v>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>60.58</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>160.47</v>
+        <v>161.75</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>163.4</v>
+        <v>163.24</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>164.31</v>
+        <v>164.21</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>150.79</v>
+        <v>150.9</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>183.44</v>
+        <v>183.92</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>182.1</v>
+        <v>182.27</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>185.41</v>
+        <v>185.35</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>188.35</v>
+        <v>188.31</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>497.3</v>
+        <v>490.65</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>507.28</v>
+        <v>505.7</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>529.0700000000001</v>
+        <v>527.5700000000001</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>536.97</v>
+        <v>536.51</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>340.9</v>
+        <v>342.1</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>350.01</v>
+        <v>349.26</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>333.32</v>
+        <v>333.67</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>271.81</v>
+        <v>272.51</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1315</v>
+        <v>1325</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>1380.45</v>
+        <v>1375.17</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>1345.09</v>
+        <v>1344.3</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1064.99</v>
+        <v>1067.58</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>379.65</v>
+        <v>388.4</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>367.8</v>
+        <v>369.77</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>352.05</v>
+        <v>353.47</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>310.12</v>
+        <v>310.9</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2081,24 +2081,24 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>561.65</v>
+        <v>550.85</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>556.96</v>
+        <v>556.38</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>531.04</v>
+        <v>531.8200000000001</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>476.13</v>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>476.87</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1739.2</v>
+        <v>1749.9</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1655.66</v>
+        <v>1664.63</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>1587.41</v>
+        <v>1593.78</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1285.49</v>
+        <v>1290.12</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>796.95</v>
+        <v>820.85</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>793.6</v>
+        <v>796.2</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>749.75</v>
+        <v>752.54</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>558.9400000000001</v>
+        <v>561.54</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>585.35</v>
+        <v>585.05</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>603.5</v>
+        <v>601.74</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>605.58</v>
+        <v>604.77</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>597.66</v>
+        <v>597.53</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>499.2</v>
+        <v>503.7</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>528.42</v>
+        <v>526.0599999999999</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>527.41</v>
+        <v>526.48</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>483.73</v>
+        <v>483.93</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>181.51</v>
+        <v>182.69</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>189.1</v>
+        <v>188.49</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>196.04</v>
+        <v>195.51</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>200.92</v>
+        <v>200.74</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>741.5</v>
+        <v>747.5</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>784.52</v>
+        <v>780.99</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>846.05</v>
+        <v>842.1900000000001</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>950.1900000000001</v>
+        <v>948.17</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>502.6</v>
+        <v>518.8</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>536.66</v>
+        <v>534.96</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>579.3200000000001</v>
+        <v>576.95</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>613.74</v>
+        <v>612.79</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>318.3</v>
+        <v>328.3</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>342.84</v>
+        <v>341.45</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>350.71</v>
+        <v>349.83</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>342.44</v>
+        <v>342.3</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>215.45</v>
+        <v>215.41</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>212.71</v>
+        <v>212.97</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>208.58</v>
+        <v>208.85</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>177.78</v>
+        <v>178.15</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>95.97</v>
+        <v>102.19</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>87.44</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>86.14</v>
+        <v>86.77</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>73.54000000000001</v>
+        <v>73.83</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>211.52</v>
+        <v>208.7</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>224.71</v>
+        <v>223.18</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>222.1</v>
+        <v>221.57</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>216.69</v>
+        <v>216.61</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,24 +2609,24 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1590.1</v>
+        <v>1652.6</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1644.86</v>
+        <v>1645.59</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1658.19</v>
+        <v>1657.97</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1409.04</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1411.47</v>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>307.15</v>
+        <v>308.7</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>335.36</v>
+        <v>332.82</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>357.99</v>
+        <v>356.05</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>397.68</v>
+        <v>396.79</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>548.3</v>
+        <v>547.1</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>566.6799999999999</v>
+        <v>564.8200000000001</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>566.0700000000001</v>
+        <v>565.33</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>499.18</v>
+        <v>499.66</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>160.08</v>
+        <v>160.05</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>164.88</v>
+        <v>164.42</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>171.6</v>
+        <v>171.14</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>207.77</v>
+        <v>207.29</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1199.6</v>
+        <v>1197.3</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1219.88</v>
+        <v>1217.73</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1161.65</v>
+        <v>1163.05</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1051.99</v>
+        <v>1053.44</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>861.75</v>
+        <v>863.55</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>893.33</v>
+        <v>890.49</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>869.64</v>
+        <v>869.4</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>728.99</v>
+        <v>730.33</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>170</v>
+        <v>163.96</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>173.69</v>
+        <v>172.76</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>177.04</v>
+        <v>176.53</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>179.9</v>
+        <v>179.74</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>275.8</v>
+        <v>272.05</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>281.18</v>
+        <v>280.31</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>289.07</v>
+        <v>288.4</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>297.98</v>
+        <v>297.72</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>452.25</v>
+        <v>452.5</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>481.16</v>
+        <v>478.43</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>513.02</v>
+        <v>510.65</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>531.9</v>
+        <v>531.11</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4457.2</v>
+        <v>4362.2</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>4225.3</v>
+        <v>4238.34</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>3890.42</v>
+        <v>3908.93</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2938.31</v>
+        <v>2952.48</v>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>579.85</v>
+        <v>596.6</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>566.23</v>
+        <v>569.12</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>549.85</v>
+        <v>551.6799999999999</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>535.77</v>
+        <v>536.38</v>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>1918.2</v>
+        <v>1916.7</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>1947.21</v>
+        <v>1944.31</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>1979.43</v>
+        <v>1976.97</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1844.7</v>
+        <v>1845.42</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>192.89</v>
+        <v>191.71</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>187.33</v>
+        <v>187.75</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>172.98</v>
+        <v>173.71</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>139.99</v>
+        <v>140.51</v>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>535.65</v>
+        <v>541.55</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>553.95</v>
+        <v>552.77</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>547.8200000000001</v>
+        <v>547.58</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>502.88</v>
+        <v>503.26</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1555.9</v>
+        <v>1523.4</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>1625.67</v>
+        <v>1615.93</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>1668.93</v>
+        <v>1663.22</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1775.12</v>
+        <v>1772.62</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3269,20 +3269,20 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>150.16</v>
+        <v>149.34</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>157.87</v>
+        <v>157.06</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>161.02</v>
+        <v>160.56</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>169.45</v>
+        <v>169.25</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>3033.5</v>
+        <v>3040.8</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>3197.47</v>
+        <v>3182.55</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>3159.37</v>
+        <v>3154.72</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2728.92</v>
+        <v>2732.02</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,17 +3357,17 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>241</v>
+        <v>238.05</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>252.56</v>
+        <v>251.18</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>257.11</v>
+        <v>256.37</v>
       </c>
       <c r="F61" s="11" t="n">
         <v>238.58</v>
@@ -3382,9 +3382,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I61" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J61" s="13" t="inlineStr">
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>453.45</v>
+        <v>447.2</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>481.95</v>
+        <v>478.64</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>500.8</v>
+        <v>498.7</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>562.4400000000001</v>
+        <v>561.29</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>572.3</v>
+        <v>562.3</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>582.77</v>
+        <v>580.8200000000001</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>573.96</v>
+        <v>573.51</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>530.62</v>
+        <v>530.9299999999999</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>20.55</v>
+        <v>20.71</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>21.95</v>
+        <v>21.83</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>22.2</v>
+        <v>22.14</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>22.36</v>
+        <v>22.34</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>193</v>
+        <v>191.48</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>200.48</v>
+        <v>199.62</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>203.56</v>
+        <v>203.09</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>203.94</v>
+        <v>203.82</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>230.4</v>
+        <v>234.99</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>204.85</v>
+        <v>207.72</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>203.47</v>
+        <v>204.71</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>193.36</v>
+        <v>193.77</v>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>658.95</v>
+        <v>656.5</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>676.62</v>
+        <v>674.7</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>669.38</v>
+        <v>668.88</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>655.6900000000001</v>
+        <v>655.7</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>1879.5</v>
+        <v>2067.4</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>1809.95</v>
+        <v>1834.47</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1735.73</v>
+        <v>1748.74</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1647.42</v>
+        <v>1651.6</v>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
@@ -3709,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>672</v>
+        <v>660.55</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>677.21</v>
+        <v>675.62</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>699.13</v>
+        <v>697.62</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>812.21</v>
+        <v>810.7</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>2051.1</v>
+        <v>2070.4</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>2103.58</v>
+        <v>2100.42</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>2033.98</v>
+        <v>2035.41</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1676.13</v>
+        <v>1680.05</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,29 +3797,29 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>6653.5</v>
+        <v>7016.5</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>6706.92</v>
+        <v>6736.4</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>6767.24</v>
+        <v>6777.01</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>5619.32</v>
-      </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H71" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>5633.22</v>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I71" s="14" t="inlineStr">
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>48.64</v>
+        <v>48.71</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>46.87</v>
+        <v>47.05</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>42.14</v>
+        <v>42.21</v>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>465.15</v>
+        <v>458</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>476.41</v>
+        <v>474.65</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>494.71</v>
+        <v>493.27</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>572.37</v>
+        <v>571.23</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,29 +3929,29 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>138.57</v>
+        <v>144.06</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>145.31</v>
+        <v>145.19</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>141.08</v>
+        <v>141.2</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>149.92</v>
+        <v>149.86</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H74" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr">
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>2153.9</v>
+        <v>2142.1</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>2231.54</v>
+        <v>2223.02</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2206.96</v>
+        <v>2204.41</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1825.31</v>
+        <v>1828.46</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>290.75</v>
+        <v>291.5</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>315.66</v>
+        <v>313.36</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>341.6</v>
+        <v>339.64</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>358.34</v>
+        <v>357.68</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>729.1</v>
+        <v>721.45</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>758.48</v>
+        <v>754.95</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>792.11</v>
+        <v>789.33</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>873.23</v>
+        <v>871.72</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,20 +4105,20 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>323.75</v>
+        <v>316.2</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>327.11</v>
+        <v>326.07</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>331.47</v>
+        <v>330.87</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>361.23</v>
+        <v>360.78</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4149,20 +4149,20 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>2748.4</v>
+        <v>2833.3</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>2731.44</v>
+        <v>2741.14</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>2633.53</v>
+        <v>2641.37</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2523.09</v>
+        <v>2526.17</v>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>170.74</v>
+        <v>171.08</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>181.18</v>
+        <v>180.22</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>191.86</v>
+        <v>191.05</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>209.61</v>
+        <v>209.23</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,20 +4237,20 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>159.88</v>
+        <v>160.54</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>161.58</v>
+        <v>161.48</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>157.88</v>
+        <v>157.99</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>155.31</v>
+        <v>155.36</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>66.02</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>71.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>73.34999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>70.19</v>
+        <v>70.16</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,29 +4325,29 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>202.85</v>
+        <v>208.85</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>199.91</v>
+        <v>200.76</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>203.36</v>
+        <v>203.58</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>184.49</v>
+        <v>184.73</v>
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H83" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I83" s="14" t="inlineStr">
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>620.65</v>
+        <v>611.5</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>586.77</v>
+        <v>589.13</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>558.62</v>
+        <v>560.6900000000001</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>506.54</v>
+        <v>507.59</v>
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
@@ -4413,17 +4413,17 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>15.41</v>
+        <v>15.36</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>15.81</v>
+        <v>15.76</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>15.81</v>
+        <v>15.79</v>
       </c>
       <c r="F85" s="11" t="n">
         <v>15.9</v>
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>826.05</v>
+        <v>821.4</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>837.48</v>
+        <v>835.95</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>873.4400000000001</v>
+        <v>871.4</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>937.49</v>
+        <v>936.34</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>2396.3</v>
+        <v>2435.3</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>2322.88</v>
+        <v>2333.59</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>2216.26</v>
+        <v>2224.85</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1851.13</v>
+        <v>1856.94</v>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
@@ -4545,20 +4545,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>657.35</v>
+        <v>647.2</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>658.74</v>
+        <v>657.64</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>658.34</v>
+        <v>657.91</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>626.63</v>
+        <v>626.83</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>1207.8</v>
+        <v>1206.5</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>1270.38</v>
+        <v>1264.3</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>1321.47</v>
+        <v>1316.96</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1303.6</v>
+        <v>1302.64</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4633,20 +4633,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>135.45</v>
+        <v>137.77</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>133.48</v>
+        <v>133.89</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>127.74</v>
+        <v>128.14</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>117.73</v>
+        <v>117.93</v>
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>541.3</v>
+        <v>531.7</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>541.8</v>
+        <v>540.83</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>514.6799999999999</v>
+        <v>515.35</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>498.27</v>
+        <v>498.6</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4721,20 +4721,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>1592.8</v>
+        <v>1609</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>1724.84</v>
+        <v>1713.8</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>1660.02</v>
+        <v>1658.02</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1240.42</v>
+        <v>1244.09</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>76.33</v>
+        <v>79.13</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>72.87</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>73.65000000000001</v>
+        <v>73.87</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>69.95</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="G93" s="14" t="inlineStr">
         <is>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>331.55</v>
+        <v>342.75</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>328.32</v>
+        <v>329.7</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>309.51</v>
+        <v>310.81</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>250.72</v>
+        <v>251.63</v>
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>268.55</v>
+        <v>266.25</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>281.33</v>
+        <v>279.89</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>305.4</v>
+        <v>303.86</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>395.03</v>
+        <v>393.74</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,20 +4897,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>543.6</v>
+        <v>545.45</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>551.13</v>
+        <v>550.59</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>542</v>
+        <v>542.13</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>463.06</v>
+        <v>463.88</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -4941,29 +4941,29 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>783.15</v>
+        <v>812.8</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>782.24</v>
+        <v>785.15</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>788.27</v>
+        <v>789.23</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>725.8</v>
+        <v>726.67</v>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H97" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H97" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I97" s="14" t="inlineStr">
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>228.01</v>
+        <v>229.17</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>234.34</v>
+        <v>233.85</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>246.48</v>
+        <v>245.81</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>292.57</v>
+        <v>291.94</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,34 +5029,34 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1732.3</v>
+        <v>1848.3</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1801.82</v>
+        <v>1806.25</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1833.55</v>
+        <v>1834.13</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1788.72</v>
-      </c>
-      <c r="G99" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H99" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I99" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1789.32</v>
+      </c>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J99" s="13" t="inlineStr">
@@ -5073,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>207.46</v>
+        <v>202.37</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>216.25</v>
+        <v>214.93</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>207.73</v>
+        <v>207.52</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>186.66</v>
+        <v>186.82</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>828.7</v>
+        <v>830</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>861.61</v>
+        <v>858.6</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>876.72</v>
+        <v>874.88</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>760.46</v>
+        <v>761.15</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,29 +5161,29 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>398.15</v>
+        <v>391.35</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>409.02</v>
+        <v>407.33</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>396.87</v>
+        <v>396.65</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>372.16</v>
+        <v>372.35</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H102" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H102" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>662.15</v>
+        <v>661.37</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>692.04</v>
+        <v>690.55</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>778.08</v>
+        <v>776.85</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,20 +5249,20 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>10513</v>
+        <v>10624</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>10756.74</v>
+        <v>10744.1</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>10500.53</v>
+        <v>10505.37</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>9534.110000000001</v>
+        <v>9544.959999999999</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>678.65</v>
+        <v>684.4</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>713.53</v>
+        <v>710.76</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>741.37</v>
+        <v>739.13</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>716.08</v>
+        <v>715.76</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5337,29 +5337,29 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>87.98</v>
+        <v>92.66</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>90.77</v>
+        <v>90.95</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>91.61</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>85.89</v>
-      </c>
-      <c r="G106" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H106" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>85.95</v>
+      </c>
+      <c r="G106" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H106" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
@@ -5381,20 +5381,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>2032</v>
+        <v>2011.7</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>2010.37</v>
+        <v>2010.49</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>1903.29</v>
+        <v>1907.54</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1658.62</v>
+        <v>1662.13</v>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
@@ -5425,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>1025.25</v>
+        <v>1055.75</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>968.98</v>
+        <v>977.24</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>861.03</v>
+        <v>868.66</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>607.0599999999999</v>
+        <v>611.53</v>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
@@ -5469,24 +5469,24 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>1151.4</v>
+        <v>1172.6</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1158.9</v>
+        <v>1160.21</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>1105.6</v>
+        <v>1108.23</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1019.55</v>
-      </c>
-      <c r="G109" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1021.08</v>
+      </c>
+      <c r="G109" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H109" s="14" t="inlineStr">
@@ -5513,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>642.5</v>
+        <v>634.2</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>683.53</v>
+        <v>678.83</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>715.76</v>
+        <v>712.5700000000001</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>855.4299999999999</v>
+        <v>853.23</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5557,20 +5557,20 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>440.2</v>
+        <v>434.95</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>442.64</v>
+        <v>441.91</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>426.66</v>
+        <v>426.99</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>356.05</v>
+        <v>356.83</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -5601,20 +5601,20 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>984.75</v>
+        <v>985.05</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>917.45</v>
+        <v>923.89</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>881.6799999999999</v>
+        <v>885.73</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>802.08</v>
+        <v>803.9</v>
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
@@ -5645,24 +5645,24 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>422.9</v>
+        <v>410.2</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>420.05</v>
+        <v>419.11</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>408.9</v>
+        <v>408.96</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>399.93</v>
-      </c>
-      <c r="G113" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>400.03</v>
+      </c>
+      <c r="G113" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H113" s="14" t="inlineStr">
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>199.42</v>
+        <v>199.96</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>203.95</v>
+        <v>203.57</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>210.94</v>
+        <v>210.51</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>238.91</v>
+        <v>238.52</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>71.75</v>
+        <v>70.62</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>74.92</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>81.62</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>92.53</v>
+        <v>92.31</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>297.5</v>
+        <v>304.5</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>407.6</v>
+        <v>397.78</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>664.4400000000001</v>
+        <v>650.33</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>888.4</v>
+        <v>882.59</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>359.05</v>
+        <v>369.35</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>354.71</v>
+        <v>356.11</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>330.41</v>
+        <v>331.94</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>320.23</v>
+        <v>320.72</v>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>3171.3</v>
+        <v>3098.7</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>3307.77</v>
+        <v>3287.86</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>3252.63</v>
+        <v>3246.59</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>2927.55</v>
+        <v>2929.25</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>4645.3</v>
+        <v>4749.2</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>4512.87</v>
+        <v>4535.38</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>4404.16</v>
+        <v>4417.69</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>3742.01</v>
+        <v>3752.03</v>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>647.3</v>
+        <v>639.75</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>663.99</v>
+        <v>661.6799999999999</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>686.53</v>
+        <v>684.6900000000001</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>749.75</v>
+        <v>748.66</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>357.35</v>
+        <v>371.25</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>317.97</v>
+        <v>323.04</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>332.53</v>
+        <v>334.05</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>388.81</v>
+        <v>388.63</v>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
@@ -6041,24 +6041,24 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>501.9</v>
+        <v>509.45</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>508.51</v>
+        <v>508.6</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>525.54</v>
+        <v>524.91</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>584.03</v>
-      </c>
-      <c r="G122" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>583.29</v>
+      </c>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -6085,24 +6085,24 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>650.35</v>
+        <v>619.85</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>634.9</v>
+        <v>633.47</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>602.11</v>
+        <v>602.8</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>517.86</v>
-      </c>
-      <c r="G123" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>518.87</v>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H123" s="14" t="inlineStr">
@@ -6129,29 +6129,29 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1387.4</v>
+        <v>1443.1</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1457.96</v>
+        <v>1456.54</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1417.2</v>
+        <v>1418.21</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1175.2</v>
+        <v>1177.87</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H124" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H124" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
@@ -6173,20 +6173,20 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>211.04</v>
+        <v>209.76</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>214.39</v>
+        <v>213.95</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>219.46</v>
+        <v>219.08</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>236.84</v>
+        <v>236.57</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>576.35</v>
+        <v>568.05</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>516.08</v>
+        <v>521.03</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>508.46</v>
+        <v>510.8</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>535.46</v>
+        <v>535.78</v>
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
@@ -6261,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>382.95</v>
+        <v>386.2</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>400.57</v>
+        <v>399.21</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>393.17</v>
+        <v>392.9</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>370.29</v>
+        <v>370.44</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>766.5</v>
+        <v>760.05</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>797.46</v>
+        <v>793.9</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>793.26</v>
+        <v>791.95</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>742.71</v>
+        <v>742.88</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>799.95</v>
+        <v>819.55</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>784.61</v>
+        <v>787.9400000000001</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>743.14</v>
+        <v>746.13</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>615.46</v>
+        <v>617.49</v>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>206.1</v>
+        <v>205.68</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>201.28</v>
+        <v>201.7</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>185.58</v>
+        <v>186.37</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>163.37</v>
+        <v>163.79</v>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
@@ -6437,24 +6437,24 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>691.2</v>
+        <v>703.6</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>699.5</v>
+        <v>699.89</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>691.0700000000001</v>
+        <v>691.5599999999999</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>650.24</v>
-      </c>
-      <c r="G131" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>650.77</v>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H131" s="14" t="inlineStr">
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>410.6</v>
+        <v>404.55</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>424.26</v>
+        <v>422.39</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>430.59</v>
+        <v>429.57</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>465.14</v>
+        <v>464.54</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>671.85</v>
+        <v>678.55</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>732.72</v>
+        <v>727.5599999999999</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>760.6900000000001</v>
+        <v>757.47</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>759.59</v>
+        <v>758.79</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6569,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>1613.3</v>
+        <v>1634.2</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>1697.69</v>
+        <v>1691.64</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>1711.86</v>
+        <v>1708.81</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1480.65</v>
+        <v>1482.18</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>225.4</v>
+        <v>223.55</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>237.13</v>
+        <v>235.84</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>245.5</v>
+        <v>244.64</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>257.52</v>
+        <v>257.18</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>91.61</v>
+        <v>91.98</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>94.94</v>
+        <v>94.66</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>91.17</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>78.31999999999999</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>402.05</v>
+        <v>401.2</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>400.42</v>
+        <v>400.49</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>379.14</v>
+        <v>380.01</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>372.39</v>
+        <v>372.68</v>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1926</v>
+        <v>1921.1</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1991.45</v>
+        <v>1984.75</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>2101.16</v>
+        <v>2094.1</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>2145.74</v>
+        <v>2143.51</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>595.15</v>
+        <v>585.8</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>616.15</v>
+        <v>613.26</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>611.54</v>
+        <v>610.54</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>560.7</v>
+        <v>560.95</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>311.95</v>
+        <v>307.75</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>322.49</v>
+        <v>321.08</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>329.54</v>
+        <v>328.68</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>344.56</v>
+        <v>344.2</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>409.05</v>
+        <v>407.7</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>428.4</v>
+        <v>426.43</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>413.65</v>
+        <v>413.42</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>324.27</v>
+        <v>325.1</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,24 +6921,24 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>1138.8</v>
+        <v>1195.2</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>1167.99</v>
+        <v>1170.58</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>1094.06</v>
+        <v>1098.03</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>871.13</v>
-      </c>
-      <c r="G142" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>874.36</v>
+      </c>
+      <c r="G142" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr">
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>139.68</v>
+        <v>136.27</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>129.65</v>
+        <v>130.28</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>127.78</v>
+        <v>128.11</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>122.35</v>
+        <v>122.49</v>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>211.22</v>
+        <v>209.43</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>215.33</v>
+        <v>214.77</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>218.08</v>
+        <v>217.74</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>215.23</v>
+        <v>215.17</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>263.85</v>
+        <v>262.05</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>279.59</v>
+        <v>277.92</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>288.86</v>
+        <v>287.81</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>282.96</v>
+        <v>282.75</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>109.95</v>
+        <v>108.11</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>110.98</v>
+        <v>110.7</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>116</v>
+        <v>115.69</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>125.78</v>
+        <v>125.6</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,17 +7141,17 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>150.72</v>
+        <v>148.86</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>154.33</v>
+        <v>153.81</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>154.58</v>
+        <v>154.35</v>
       </c>
       <c r="F147" s="11" t="n">
         <v>148.93</v>
@@ -7166,9 +7166,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I147" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I147" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J147" s="13" t="inlineStr">
@@ -7185,20 +7185,20 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>449.65</v>
+        <v>451.65</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>442.14</v>
+        <v>443.05</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>453.9</v>
+        <v>453.81</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>512.65</v>
+        <v>512.04</v>
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
@@ -7229,20 +7229,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>101.9</v>
+        <v>100.72</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>96.28</v>
+        <v>96.7</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>96.70999999999999</v>
+        <v>96.87</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>102.7</v>
+        <v>102.68</v>
       </c>
       <c r="G149" s="14" t="inlineStr">
         <is>
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>2053.3</v>
+        <v>2078.4</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>2141.3</v>
+        <v>2135.31</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>2096.51</v>
+        <v>2095.8</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1832.66</v>
+        <v>1835.1</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7317,20 +7317,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>2364.3</v>
+        <v>2397.2</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>2414.59</v>
+        <v>2412.94</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>2463.43</v>
+        <v>2460.83</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>2491.13</v>
+        <v>2490.2</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
@@ -7361,20 +7361,20 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>1100.4</v>
+        <v>1108</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>1049.35</v>
+        <v>1054.94</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>967.87</v>
+        <v>973.36</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>824.99</v>
+        <v>827.8099999999999</v>
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>1865.1</v>
+        <v>1863.5</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>1923.78</v>
+        <v>1918.04</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>1839.38</v>
+        <v>1840.33</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1589.9</v>
+        <v>1592.63</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,20 +7449,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>1790.1</v>
+        <v>1764.9</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>1760.7</v>
+        <v>1761.1</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>1599.6</v>
+        <v>1606.08</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1321.32</v>
+        <v>1325.73</v>
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
@@ -7493,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>276.5</v>
+        <v>275.45</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>282.35</v>
+        <v>281.69</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>281</v>
+        <v>280.78</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>242.29</v>
+        <v>242.62</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>13139</v>
+        <v>13065</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>12178.33</v>
+        <v>12262.78</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>11621.46</v>
+        <v>11678.07</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>10388.59</v>
+        <v>10415.22</v>
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>2036.4</v>
+        <v>2000.8</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>2086.6</v>
+        <v>2078.43</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>2137.33</v>
+        <v>2131.97</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>2212.52</v>
+        <v>2210.41</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,20 +7625,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>1296.1</v>
+        <v>1290.4</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>1208</v>
+        <v>1215.85</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>1145.56</v>
+        <v>1151.24</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>950.49</v>
+        <v>953.88</v>
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>629.3</v>
+        <v>631.5</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>656.78</v>
+        <v>654.38</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>673.48</v>
+        <v>671.84</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>654.03</v>
+        <v>653.8099999999999</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>482.75</v>
+        <v>490.6</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>480.7</v>
+        <v>481.64</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>498.17</v>
+        <v>497.87</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>542.74</v>
+        <v>542.22</v>
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
@@ -7757,20 +7757,20 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>123.14</v>
+        <v>125.67</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>117.13</v>
+        <v>117.94</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>113.32</v>
+        <v>113.8</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>115.14</v>
+        <v>115.25</v>
       </c>
       <c r="G161" s="14" t="inlineStr">
         <is>
@@ -7801,29 +7801,29 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>416</v>
+        <v>419.1</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>418.93</v>
+        <v>418.95</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>418.7</v>
+        <v>418.72</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>399.76</v>
-      </c>
-      <c r="G162" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H162" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>399.95</v>
+      </c>
+      <c r="G162" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H162" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I162" s="14" t="inlineStr">
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>153.04</v>
+        <v>151.65</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>154.08</v>
+        <v>153.85</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>154.91</v>
+        <v>154.78</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>162.1</v>
+        <v>162</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>494.8</v>
+        <v>490.15</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>514.8200000000001</v>
+        <v>512.47</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>535.1900000000001</v>
+        <v>533.42</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>622.76</v>
+        <v>621.4400000000001</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7933,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>710.4</v>
+        <v>713.05</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>722.89</v>
+        <v>721.95</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>686.39</v>
+        <v>687.4400000000001</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>575.2</v>
+        <v>576.5700000000001</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>189.66</v>
+        <v>184.26</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>195.75</v>
+        <v>194.66</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>199.63</v>
+        <v>199.02</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>225.05</v>
+        <v>224.64</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>199.72</v>
+        <v>202.89</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>212.33</v>
+        <v>211.43</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>222.25</v>
+        <v>221.49</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>226.77</v>
+        <v>226.54</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,20 +8065,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>511.65</v>
+        <v>514.25</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>530.15</v>
+        <v>528.64</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>514.85</v>
+        <v>514.8200000000001</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>480.06</v>
+        <v>480.4</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>429.65</v>
+        <v>428.6</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>427.87</v>
+        <v>427.94</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>419.29</v>
+        <v>419.66</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>406.24</v>
+        <v>406.46</v>
       </c>
       <c r="G169" s="14" t="inlineStr">
         <is>
@@ -8153,24 +8153,24 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>848.35</v>
+        <v>837.4</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>842.62</v>
+        <v>842.12</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>796.65</v>
+        <v>798.24</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>667.05</v>
-      </c>
-      <c r="G170" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>668.74</v>
+      </c>
+      <c r="G170" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr">
@@ -8197,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>413.75</v>
+        <v>410.15</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>430.72</v>
+        <v>428.76</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>441.61</v>
+        <v>440.38</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>457.45</v>
+        <v>456.98</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8241,29 +8241,29 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>1110</v>
+        <v>1078.9</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>1120.62</v>
+        <v>1116.64</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>1106.58</v>
+        <v>1105.49</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>1054.16</v>
+        <v>1054.41</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H172" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H172" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I172" s="14" t="inlineStr">
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>131.26</v>
+        <v>129.8</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>156.49</v>
+        <v>153.95</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>183.46</v>
+        <v>181.35</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>216.82</v>
+        <v>215.95</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>495.1</v>
+        <v>501.15</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>521.52</v>
+        <v>519.58</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>516.08</v>
+        <v>515.5</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>512.79</v>
+        <v>512.67</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>809.95</v>
+        <v>796.2</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>657.74</v>
+        <v>670.9299999999999</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>601.74</v>
+        <v>609.36</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>529.34</v>
+        <v>532</v>
       </c>
       <c r="G175" s="14" t="inlineStr">
         <is>
@@ -8417,24 +8417,24 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>154.88</v>
+        <v>155.75</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>155.49</v>
+        <v>155.52</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>157.06</v>
+        <v>157.01</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>156.65</v>
-      </c>
-      <c r="G176" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>156.64</v>
+      </c>
+      <c r="G176" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H176" s="12" t="inlineStr">
@@ -8461,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>175.55</v>
+        <v>173.84</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>181.75</v>
+        <v>180.99</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>189.85</v>
+        <v>189.22</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>238.1</v>
+        <v>237.46</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>1592.7</v>
+        <v>1614.3</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>1469.15</v>
+        <v>1482.98</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>1370.14</v>
+        <v>1379.72</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1130.32</v>
+        <v>1135.14</v>
       </c>
       <c r="G178" s="14" t="inlineStr">
         <is>
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>234.32</v>
+        <v>232.05</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>246.79</v>
+        <v>245.39</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>246.71</v>
+        <v>246.14</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>242.14</v>
+        <v>242.04</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8593,29 +8593,29 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>370.35</v>
+        <v>368.8</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>373.57</v>
+        <v>373.11</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>369.5</v>
+        <v>369.47</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>332.34</v>
+        <v>332.7</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H180" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H180" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I180" s="14" t="inlineStr">
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>25.98</v>
+        <v>25.88</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>27.13</v>
+        <v>27.01</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>28.34</v>
+        <v>28.24</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>34</v>
+        <v>33.92</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>7.23</v>
+        <v>7.2</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>9</v>
+        <v>8.98</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>600.5</v>
+        <v>602.85</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>615.42</v>
+        <v>614.22</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>638.54</v>
+        <v>637.14</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>625.5</v>
+        <v>625.28</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>242.4</v>
+        <v>239.15</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>254.04</v>
+        <v>252.62</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>281.75</v>
+        <v>280.08</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>339.15</v>
+        <v>338.16</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8813,29 +8813,29 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>769.5</v>
+        <v>742.1</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>741.03</v>
+        <v>741.13</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>768.62</v>
+        <v>767.58</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>869.17</v>
+        <v>867.91</v>
       </c>
       <c r="G185" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H185" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H185" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I185" s="12" t="inlineStr">
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>12804</v>
+        <v>12341</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>13173.69</v>
+        <v>13094.39</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>13100.78</v>
+        <v>13070.99</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>13116.83</v>
+        <v>13109.11</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>343.7</v>
+        <v>344.95</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>341.96</v>
+        <v>342.24</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>339.14</v>
+        <v>339.37</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>330.91</v>
+        <v>331.05</v>
       </c>
       <c r="G187" s="14" t="inlineStr">
         <is>
@@ -8945,20 +8945,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>56.03</v>
+        <v>56.33</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>58.02</v>
+        <v>57.86</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>59.52</v>
+        <v>59.4</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>65.48999999999999</v>
+        <v>65.39</v>
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
@@ -8989,20 +8989,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>1345.5</v>
+        <v>1356.8</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>1373.71</v>
+        <v>1372.1</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>1322.29</v>
+        <v>1323.64</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1138.84</v>
+        <v>1141.01</v>
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
@@ -9033,24 +9033,24 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>839.1</v>
+        <v>849.9</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>843.67</v>
+        <v>844.26</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>875.15</v>
+        <v>874.16</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>964.95</v>
-      </c>
-      <c r="G190" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>963.8</v>
+      </c>
+      <c r="G190" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
@@ -9077,29 +9077,29 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>784.2</v>
+        <v>821.4</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>779.36</v>
+        <v>783.36</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>791.24</v>
+        <v>792.42</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>782.47</v>
+        <v>782.86</v>
       </c>
       <c r="G191" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H191" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H191" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I191" s="14" t="inlineStr">
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>914</v>
+        <v>972.8</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>864.9</v>
+        <v>875.1799999999999</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>817.12</v>
+        <v>823.23</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>760.5700000000001</v>
+        <v>762.6900000000001</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9165,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>117.39</v>
+        <v>119.33</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>121.92</v>
+        <v>121.67</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>124.29</v>
+        <v>124.1</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>137.02</v>
+        <v>136.84</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>276.75</v>
+        <v>280.3</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>288.33</v>
+        <v>287.56</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>295.45</v>
+        <v>294.86</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>330.45</v>
+        <v>329.96</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,29 +9253,29 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>2881.7</v>
+        <v>2789</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>2898.14</v>
+        <v>2887.74</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>2825.42</v>
+        <v>2823.99</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>2618.96</v>
+        <v>2620.65</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H195" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H195" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I195" s="14" t="inlineStr">
@@ -9297,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>2518.2</v>
+        <v>2489.8</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>2664.43</v>
+        <v>2647.79</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>2681.42</v>
+        <v>2673.91</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>2605.23</v>
+        <v>2604.08</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>749.5</v>
+        <v>744.3</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>751.9400000000001</v>
+        <v>751.21</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>694.97</v>
+        <v>696.9</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>583.99</v>
+        <v>585.59</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>650.65</v>
+        <v>667.15</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>670.47</v>
+        <v>670.16</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>676.72</v>
+        <v>676.34</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>633.22</v>
+        <v>633.5599999999999</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>332.6</v>
+        <v>333.35</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>335.47</v>
+        <v>335.27</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>347.56</v>
+        <v>347.01</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>410.83</v>
+        <v>410.06</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>1632</v>
+        <v>1591.2</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>1702.17</v>
+        <v>1691.6</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>1812.74</v>
+        <v>1804.05</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>1983.81</v>
+        <v>1979.91</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,20 +9517,20 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>155.08</v>
+        <v>160.24</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>162.65</v>
+        <v>162.42</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>170.38</v>
+        <v>169.98</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>188.12</v>
+        <v>187.84</v>
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
@@ -9561,24 +9561,24 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>119.97</v>
+        <v>117.48</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>119.89</v>
+        <v>119.66</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>122.86</v>
+        <v>122.65</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>125.72</v>
-      </c>
-      <c r="G202" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>125.64</v>
+      </c>
+      <c r="G202" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H202" s="12" t="inlineStr">
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>177.48</v>
+        <v>181.33</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>186.59</v>
+        <v>186.08</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>193.89</v>
+        <v>193.4</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>205.99</v>
+        <v>205.74</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,29 +9649,29 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>801.25</v>
+        <v>824.8</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>806.23</v>
+        <v>808</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>819.8</v>
+        <v>820</v>
       </c>
       <c r="F204" s="11" t="n">
         <v>825.35</v>
       </c>
-      <c r="G204" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H204" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="G204" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H204" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I204" s="12" t="inlineStr">
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>110.17</v>
+        <v>108.53</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>113.11</v>
+        <v>112.67</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>116.31</v>
+        <v>116</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>133.98</v>
+        <v>133.73</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>554.3</v>
+        <v>540.05</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>572.2</v>
+        <v>569.14</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>577.78</v>
+        <v>576.3</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>605.87</v>
+        <v>605.22</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,24 +9781,24 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>406.9</v>
+        <v>410.9</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>410.18</v>
+        <v>410.25</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>414.56</v>
+        <v>414.41</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>435.72</v>
-      </c>
-      <c r="G207" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>435.47</v>
+      </c>
+      <c r="G207" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>126.53</v>
+        <v>127.02</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>128.29</v>
+        <v>128.17</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>127.49</v>
+        <v>127.47</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>136.28</v>
+        <v>136.19</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>151.61</v>
+        <v>151.15</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>154.18</v>
+        <v>153.9</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>157.46</v>
+        <v>157.21</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>168.67</v>
+        <v>168.5</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>102.18</v>
+        <v>103.92</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>105.44</v>
+        <v>105.3</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>105.47</v>
+        <v>105.41</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>112.65</v>
+        <v>112.56</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
-        <v>1214.2</v>
+        <v>1201</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>1263.38</v>
+        <v>1257.44</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>1293.17</v>
+        <v>1289.55</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>1310.07</v>
+        <v>1308.98</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>119.43</v>
+        <v>118.42</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>124.92</v>
+        <v>124.3</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>129.01</v>
+        <v>128.6</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>147.41</v>
+        <v>147.13</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>283.15</v>
+        <v>282.15</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>293.89</v>
+        <v>292.77</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>303.29</v>
+        <v>302.46</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>316</v>
+        <v>315.66</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,20 +10089,20 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>250.2</v>
+        <v>247.1</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>265.43</v>
+        <v>263.69</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>272.63</v>
+        <v>271.63</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>343.47</v>
+        <v>342.51</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>854.35</v>
+        <v>861.5</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>834.55</v>
+        <v>837.12</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>820.24</v>
+        <v>821.86</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>804.48</v>
+        <v>805.04</v>
       </c>
       <c r="G215" s="14" t="inlineStr">
         <is>
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1480.1</v>
+        <v>1477.1</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>1338.84</v>
+        <v>1352.01</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>1158.91</v>
+        <v>1171.39</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>1010.26</v>
+        <v>1014.9</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10221,29 +10221,29 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>72.34999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>75.2</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>75.61</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>79.09</v>
-      </c>
-      <c r="G217" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H217" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="G217" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H217" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I217" s="12" t="inlineStr">
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>116.13</v>
+        <v>115.56</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>121.82</v>
+        <v>121.22</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>130.13</v>
+        <v>129.56</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>157.96</v>
+        <v>157.54</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10309,29 +10309,29 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>1086.4</v>
+        <v>1040.5</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>1075.81</v>
+        <v>1072.44</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>1073.79</v>
+        <v>1072.49</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>1120.15</v>
-      </c>
-      <c r="G219" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H219" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1119.36</v>
+      </c>
+      <c r="G219" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H219" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I219" s="12" t="inlineStr">
@@ -10353,20 +10353,20 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>235</v>
+        <v>233.05</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>240.19</v>
+        <v>239.51</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>239.94</v>
+        <v>239.67</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>228.21</v>
+        <v>228.26</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10397,20 +10397,20 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1511.8</v>
+        <v>1514</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1535.76</v>
+        <v>1533.69</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1546.65</v>
+        <v>1545.37</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1873.15</v>
+        <v>1869.57</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10441,20 +10441,20 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>594.2</v>
+        <v>595.65</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>606.78</v>
+        <v>605.72</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>616.97</v>
+        <v>616.14</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>623.4299999999999</v>
+        <v>623.15</v>
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
@@ -10485,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>22.91</v>
+        <v>22.54</v>
       </c>
       <c r="D223" s="11" t="n">
-        <v>23.49</v>
+        <v>23.4</v>
       </c>
       <c r="E223" s="11" t="n">
-        <v>23.5</v>
+        <v>23.46</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>24.79</v>
+        <v>24.77</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>642.5</v>
+        <v>631.7</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>650.53</v>
+        <v>648.74</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>621.6900000000001</v>
+        <v>622.08</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>600.89</v>
+        <v>601.1900000000001</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>361.3</v>
+        <v>362.95</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>392.1</v>
+        <v>389.32</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>415.75</v>
+        <v>413.68</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>472.84</v>
+        <v>471.74</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10617,20 +10617,20 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>220.1</v>
+        <v>220.75</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>217</v>
+        <v>217.36</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>223.43</v>
+        <v>223.33</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>241.56</v>
+        <v>241.35</v>
       </c>
       <c r="G226" s="14" t="inlineStr">
         <is>
@@ -10661,29 +10661,29 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>503.6</v>
+        <v>495.25</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>502.87</v>
+        <v>502.14</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>499.6</v>
+        <v>499.43</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>477.08</v>
-      </c>
-      <c r="G227" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H227" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>477.26</v>
+      </c>
+      <c r="G227" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H227" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I227" s="14" t="inlineStr">
@@ -10705,29 +10705,29 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>115.15</v>
+        <v>109.27</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>114.01</v>
+        <v>113.56</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>113.06</v>
+        <v>112.91</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>121.76</v>
-      </c>
-      <c r="G228" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H228" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>121.63</v>
+      </c>
+      <c r="G228" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H228" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I228" s="12" t="inlineStr">
@@ -10749,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>209.99</v>
+        <v>204.84</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>214.48</v>
+        <v>213.56</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>215.36</v>
+        <v>214.95</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>223.63</v>
+        <v>223.44</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>1799.8</v>
+        <v>1781.3</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>1884.77</v>
+        <v>1874.92</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>1888.37</v>
+        <v>1884.17</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>1791.69</v>
+        <v>1791.59</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10818,9 +10818,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I230" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I230" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J230" s="13" t="inlineStr">
@@ -10837,20 +10837,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>714.35</v>
+        <v>721.85</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>692.7</v>
+        <v>695.47</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>656.59</v>
+        <v>659.15</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>614.0599999999999</v>
+        <v>615.13</v>
       </c>
       <c r="G231" s="14" t="inlineStr">
         <is>
@@ -10881,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>177.14</v>
+        <v>169.08</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>177.52</v>
+        <v>176.72</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>181.26</v>
+        <v>180.78</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>212.51</v>
+        <v>212.08</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>5196</v>
+        <v>5124.5</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>5574.45</v>
+        <v>5531.6</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>5736.39</v>
+        <v>5712.4</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>5724.29</v>
+        <v>5718.32</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>314.65</v>
+        <v>309.85</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>328.34</v>
+        <v>326.58</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>334.12</v>
+        <v>333.17</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>380.8</v>
+        <v>380.09</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11013,20 +11013,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>26.2</v>
+        <v>25.66</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>27.6</v>
+        <v>27.41</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>29.3</v>
+        <v>29.16</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>34.83</v>
+        <v>34.74</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>182.42</v>
+        <v>178.1</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>189.94</v>
+        <v>188.81</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>194.91</v>
+        <v>194.25</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>209.38</v>
+        <v>209.07</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,29 +11101,29 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>128.5</v>
+        <v>131.3</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>129.88</v>
+        <v>130.01</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>129.68</v>
+        <v>129.74</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>124.55</v>
-      </c>
-      <c r="G237" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H237" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>124.62</v>
+      </c>
+      <c r="G237" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H237" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I237" s="14" t="inlineStr">
@@ -11145,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>7.22</v>
+        <v>7.06</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>7.88</v>
+        <v>7.8</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>9.380000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>12.62</v>
+        <v>12.56</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11189,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>96.28</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>99.72</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>104.33</v>
+        <v>104.08</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>118.71</v>
+        <v>118.5</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11233,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>296.25</v>
+        <v>293.2</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>301.22</v>
+        <v>300.46</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>303.76</v>
+        <v>303.34</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>328.81</v>
+        <v>328.46</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>444.55</v>
+        <v>438.25</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>468.54</v>
+        <v>465.66</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>497.3</v>
+        <v>494.99</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>602.64</v>
+        <v>601.01</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11321,20 +11321,20 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>63.51</v>
+        <v>63.35</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>65.65000000000001</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>66.31999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>71.48</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
@@ -11365,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>1453.2</v>
+        <v>1430.9</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>1499.85</v>
+        <v>1493.28</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>1521.43</v>
+        <v>1517.88</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>1676.93</v>
+        <v>1674.48</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>115.95</v>
+        <v>114.94</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>121.88</v>
+        <v>121.22</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>127.18</v>
+        <v>126.7</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>133.99</v>
+        <v>133.8</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>65.76000000000001</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>67.70999999999999</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>69.3</v>
+        <v>69.12</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>75.17</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>679.05</v>
+        <v>665</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>717.49</v>
+        <v>712.49</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>738.71</v>
+        <v>735.8200000000001</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>754.49</v>
+        <v>753.6</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,34 +11541,34 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>434.7</v>
+        <v>421.45</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>440.64</v>
+        <v>438.81</v>
       </c>
       <c r="E247" s="11" t="n">
+        <v>432.68</v>
+      </c>
+      <c r="F247" s="11" t="n">
         <v>433.14</v>
       </c>
-      <c r="F247" s="11" t="n">
-        <v>433.26</v>
-      </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H247" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I247" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H247" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I247" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J247" s="13" t="inlineStr">
@@ -11585,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>572.4</v>
+        <v>551.55</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>602.38</v>
+        <v>597.54</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>670.03</v>
+        <v>665.38</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>788.48</v>
+        <v>786.12</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>3976.2</v>
+        <v>3867</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>4064.16</v>
+        <v>4045.39</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>4229.85</v>
+        <v>4215.62</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>4450.19</v>
+        <v>4444.39</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11673,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C250" s="11" t="n">
-        <v>700.3</v>
+        <v>702.2</v>
       </c>
       <c r="D250" s="11" t="n">
-        <v>714.79</v>
+        <v>713.59</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>734.16</v>
+        <v>732.91</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>780.17</v>
+        <v>779.39</v>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
@@ -11717,24 +11717,24 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C251" s="11" t="n">
-        <v>422.4</v>
+        <v>414.5</v>
       </c>
       <c r="D251" s="11" t="n">
-        <v>422.17</v>
+        <v>421.44</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>425.71</v>
+        <v>425.27</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>431.6</v>
-      </c>
-      <c r="G251" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>431.43</v>
+      </c>
+      <c r="G251" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H251" s="12" t="inlineStr">

--- a/Report/EMAReport/Micro_250_ema_breadth.xlsx
+++ b/Report/EMAReport/Micro_250_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 29-Sep-2026  16:46:42    |    Closing Price Date: 29-Sep-2026</t>
+          <t>Scan Run: 30-Sep-2026  16:38:54    |    Closing Price Date: 30-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>32.4</v>
+        <v>30.4</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>37.6</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>49.6</v>
+        <v>50.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>250</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>29-Sep-2026  16:46:42</t>
+          <t>30-Sep-2026  16:38:54</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 32.4% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 30.4% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 49.6% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): NEUTRAL — 50.8% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 81 of 250 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 76 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 124 of 250 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 127 of 250 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>243.96</v>
+        <v>237.76</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>246.89</v>
+        <v>246.02</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>257.31</v>
+        <v>256.54</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>290.6</v>
+        <v>290.08</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>307.05</v>
+        <v>296.45</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>320.01</v>
+        <v>317.76</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>320.92</v>
+        <v>319.96</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>324.29</v>
+        <v>324.01</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>6616.5</v>
+        <v>6578</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>6304.03</v>
+        <v>6330.12</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>5687.17</v>
+        <v>5722.1</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>4494.34</v>
+        <v>4515.07</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>777.35</v>
+        <v>786.05</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>746.29</v>
+        <v>750.0700000000001</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>710.1900000000001</v>
+        <v>713.17</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>567.72</v>
+        <v>569.89</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>288</v>
+        <v>311.65</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>272.7</v>
+        <v>276.41</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>258.37</v>
+        <v>260.46</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>173.27</v>
+        <v>174.65</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>352.05</v>
+        <v>354.2</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>357.65</v>
+        <v>357.32</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>333.48</v>
+        <v>334.29</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>238.16</v>
+        <v>239.31</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>7426</v>
+        <v>7797</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>7122.76</v>
+        <v>7186.97</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>6985.52</v>
+        <v>7017.34</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5633.82</v>
+        <v>5655.34</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,29 +1069,29 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>806.05</v>
+        <v>794.85</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>833.22</v>
+        <v>829.5700000000001</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>795.1900000000001</v>
+        <v>795.17</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>645.63</v>
+        <v>647.12</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -1113,24 +1113,24 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>324.25</v>
+        <v>329</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>324.68</v>
+        <v>325.09</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>312.06</v>
+        <v>312.72</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>262.86</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>263.52</v>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>5204.5</v>
+        <v>5062</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>5158.93</v>
+        <v>5149.69</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>5303.36</v>
+        <v>5293.89</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>4578.43</v>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>4583.24</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -1201,24 +1201,24 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>176.49</v>
+        <v>177.36</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>177.06</v>
+        <v>177.09</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>173.92</v>
+        <v>174.05</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>166.11</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>166.22</v>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2914.2</v>
+        <v>2963.2</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2752.57</v>
+        <v>2772.63</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>2647.63</v>
+        <v>2660.01</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>2191.52</v>
+        <v>2199.2</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>622.4</v>
+        <v>607.9</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>606.09</v>
+        <v>606.26</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>591.95</v>
+        <v>592.58</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>576.41</v>
+        <v>576.72</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,24 +1333,24 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2302</v>
+        <v>2296.7</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>2300.57</v>
+        <v>2300.2</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>2134.78</v>
+        <v>2141.13</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1591.86</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1598.87</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>3605.5</v>
+        <v>3586.6</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>3515.47</v>
+        <v>3522.24</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>3502.4</v>
+        <v>3505.71</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3251.93</v>
+        <v>3255.26</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>402.6</v>
+        <v>403.45</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>396.78</v>
+        <v>397.41</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>393.3</v>
+        <v>393.7</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>341.21</v>
+        <v>341.83</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>749.35</v>
+        <v>747.6</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>758.96</v>
+        <v>757.88</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>736.46</v>
+        <v>736.9</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>639.97</v>
+        <v>641.04</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>866.6</v>
+        <v>909.9</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>810.8</v>
+        <v>820.24</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>727.33</v>
+        <v>734.49</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>474.96</v>
+        <v>479.28</v>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>214.15</v>
+        <v>224.53</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>206.79</v>
+        <v>208.48</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>190.51</v>
+        <v>191.84</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>166.93</v>
+        <v>167.5</v>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>13.23</v>
+        <v>13.2</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>12.95</v>
+        <v>12.97</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>11.71</v>
+        <v>11.77</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10.57</v>
+        <v>10.59</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>271.63</v>
+        <v>279.48</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>242.8</v>
+        <v>246.29</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>238.13</v>
+        <v>239.75</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>201.96</v>
+        <v>202.73</v>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
@@ -1685,24 +1685,24 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>2093.8</v>
+        <v>2061.4</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>2065.02</v>
+        <v>2064.67</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>2022.83</v>
+        <v>2024.35</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1733.4</v>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1736.66</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>215.23</v>
+        <v>212.98</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>224.55</v>
+        <v>223.45</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>226.37</v>
+        <v>225.85</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>209.94</v>
+        <v>209.97</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,29 +1773,29 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>65.26000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>65.20999999999999</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>65.65000000000001</v>
+        <v>65.72</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>60.58</v>
+        <v>60.65</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>161.75</v>
+        <v>160.21</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>163.24</v>
+        <v>162.95</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>164.21</v>
+        <v>164.05</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>150.9</v>
+        <v>150.99</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>183.92</v>
+        <v>182.36</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>182.27</v>
+        <v>182.28</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>185.35</v>
+        <v>185.23</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>188.31</v>
+        <v>188.25</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>490.65</v>
+        <v>492.15</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>505.7</v>
+        <v>504.41</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>527.5700000000001</v>
+        <v>526.1799999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>536.51</v>
+        <v>536.0700000000001</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>342.1</v>
+        <v>334.95</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>349.26</v>
+        <v>347.9</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>333.67</v>
+        <v>333.72</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>272.51</v>
+        <v>273.13</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1325</v>
+        <v>1311</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>1375.17</v>
+        <v>1369.06</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>1344.3</v>
+        <v>1342.99</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1067.58</v>
+        <v>1070</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>388.4</v>
+        <v>392.85</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>369.77</v>
+        <v>371.96</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>353.47</v>
+        <v>355.02</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>310.9</v>
+        <v>311.72</v>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>550.85</v>
+        <v>540.65</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>556.38</v>
+        <v>554.88</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>531.8200000000001</v>
+        <v>532.16</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>476.87</v>
+        <v>477.51</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1749.9</v>
+        <v>1699.3</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1664.63</v>
+        <v>1667.93</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>1593.78</v>
+        <v>1597.92</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1290.12</v>
+        <v>1294.19</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>820.85</v>
+        <v>810.7</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>796.2</v>
+        <v>797.58</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>752.54</v>
+        <v>754.8200000000001</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>561.54</v>
+        <v>564.02</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>585.05</v>
+        <v>590.15</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>601.74</v>
+        <v>600.64</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>604.77</v>
+        <v>604.2</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>597.53</v>
+        <v>597.46</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>503.7</v>
+        <v>489.3</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>526.0599999999999</v>
+        <v>522.5599999999999</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>526.48</v>
+        <v>525.02</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>483.93</v>
+        <v>483.98</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>182.69</v>
+        <v>182.18</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>188.49</v>
+        <v>187.89</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>195.51</v>
+        <v>194.99</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>200.74</v>
+        <v>200.55</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>747.5</v>
+        <v>717.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>780.99</v>
+        <v>774.97</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>842.1900000000001</v>
+        <v>837.3099999999999</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>948.17</v>
+        <v>945.88</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>518.8</v>
+        <v>504.15</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>534.96</v>
+        <v>532.02</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>576.95</v>
+        <v>574.1</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>612.79</v>
+        <v>611.71</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>328.3</v>
+        <v>320.95</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>341.45</v>
+        <v>339.5</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>349.83</v>
+        <v>348.69</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>342.3</v>
+        <v>342.09</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>215.41</v>
+        <v>213.94</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>212.97</v>
+        <v>213.06</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>208.85</v>
+        <v>209.05</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>178.15</v>
+        <v>178.51</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>102.19</v>
+        <v>98.64</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>88.84999999999999</v>
+        <v>89.78</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>86.77</v>
+        <v>87.23</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>73.83</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>208.7</v>
+        <v>206.74</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>223.18</v>
+        <v>221.62</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>221.57</v>
+        <v>220.99</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>216.61</v>
+        <v>216.51</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,24 +2609,24 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1652.6</v>
+        <v>1636.7</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1645.59</v>
+        <v>1644.75</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1657.97</v>
+        <v>1657.14</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1411.47</v>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1413.71</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>308.7</v>
+        <v>310.6</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>332.82</v>
+        <v>330.71</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>356.05</v>
+        <v>354.27</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>396.79</v>
+        <v>395.93</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>547.1</v>
+        <v>534.15</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>564.8200000000001</v>
+        <v>561.9</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>565.33</v>
+        <v>564.11</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>499.66</v>
+        <v>500</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>160.05</v>
+        <v>160.01</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>164.42</v>
+        <v>164</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>171.14</v>
+        <v>170.71</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>207.29</v>
+        <v>206.82</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1197.3</v>
+        <v>1203.9</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1217.73</v>
+        <v>1216.41</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1163.05</v>
+        <v>1164.65</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1053.44</v>
+        <v>1054.94</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,29 +2829,29 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>863.55</v>
+        <v>871.3</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>890.49</v>
+        <v>888.66</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>869.4</v>
+        <v>869.48</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>730.33</v>
+        <v>731.73</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>163.96</v>
+        <v>161.07</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>172.76</v>
+        <v>171.65</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>176.53</v>
+        <v>175.92</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>179.74</v>
+        <v>179.56</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>272.05</v>
+        <v>265.25</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>280.31</v>
+        <v>278.87</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>288.4</v>
+        <v>287.49</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>297.72</v>
+        <v>297.4</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -2961,20 +2961,20 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>452.5</v>
+        <v>458.15</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>478.43</v>
+        <v>476.5</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>510.65</v>
+        <v>508.59</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>531.11</v>
+        <v>530.38</v>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
@@ -3005,20 +3005,20 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4362.2</v>
+        <v>4537.5</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>4238.34</v>
+        <v>4266.83</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>3908.93</v>
+        <v>3933.58</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2952.48</v>
+        <v>2968.25</v>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>596.6</v>
+        <v>589.85</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>569.12</v>
+        <v>571.09</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>551.6799999999999</v>
+        <v>553.1799999999999</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>536.38</v>
+        <v>536.91</v>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
@@ -3093,29 +3093,29 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>1916.7</v>
+        <v>1994.1</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>1944.31</v>
+        <v>1949.05</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>1976.97</v>
+        <v>1977.64</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1845.42</v>
-      </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1846.9</v>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
@@ -3137,20 +3137,20 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>191.71</v>
+        <v>205.36</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>187.75</v>
+        <v>189.42</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>173.71</v>
+        <v>174.95</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>140.51</v>
+        <v>141.15</v>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>541.55</v>
+        <v>531.15</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>552.77</v>
+        <v>550.71</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>547.58</v>
+        <v>546.9299999999999</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>503.26</v>
+        <v>503.54</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -3225,20 +3225,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1523.4</v>
+        <v>1562.8</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>1615.93</v>
+        <v>1610.87</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>1663.22</v>
+        <v>1659.28</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1772.62</v>
+        <v>1770.53</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -3269,20 +3269,20 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>149.34</v>
+        <v>153.68</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>157.06</v>
+        <v>156.73</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>160.56</v>
+        <v>160.29</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>169.25</v>
+        <v>169.1</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -3313,20 +3313,20 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>3040.8</v>
+        <v>3063</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>3182.55</v>
+        <v>3171.16</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>3154.72</v>
+        <v>3151.12</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2732.02</v>
+        <v>2735.32</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>238.05</v>
+        <v>235.8</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>251.18</v>
+        <v>249.71</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>256.37</v>
+        <v>255.56</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>238.58</v>
+        <v>238.55</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
@@ -3401,20 +3401,20 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>447.2</v>
+        <v>445</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>478.64</v>
+        <v>475.43</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>498.7</v>
+        <v>496.59</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>561.29</v>
+        <v>560.13</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>562.3</v>
+        <v>541.7</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>580.8200000000001</v>
+        <v>577.1</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>573.51</v>
+        <v>572.26</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>530.9299999999999</v>
+        <v>531.04</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -3489,20 +3489,20 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>20.71</v>
+        <v>20.41</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>21.83</v>
+        <v>21.69</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>22.14</v>
+        <v>22.07</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>22.34</v>
+        <v>22.32</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -3533,20 +3533,20 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>191.48</v>
+        <v>189.62</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>199.62</v>
+        <v>198.67</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>203.09</v>
+        <v>202.56</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>203.82</v>
+        <v>203.67</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>234.99</v>
+        <v>230.28</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>207.72</v>
+        <v>209.87</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>204.71</v>
+        <v>205.71</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>193.77</v>
+        <v>194.14</v>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
@@ -3621,20 +3621,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>656.5</v>
+        <v>666.15</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>674.7</v>
+        <v>673.89</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>668.88</v>
+        <v>668.77</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>655.7</v>
+        <v>655.8</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>2067.4</v>
+        <v>2231.2</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>1834.47</v>
+        <v>1872.25</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1748.74</v>
+        <v>1767.66</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1651.6</v>
+        <v>1657.36</v>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
@@ -3709,20 +3709,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>660.55</v>
+        <v>642.05</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>675.62</v>
+        <v>672.42</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>697.62</v>
+        <v>695.4400000000001</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>810.7</v>
+        <v>809.02</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -3753,20 +3753,20 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>2070.4</v>
+        <v>2052.5</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>2100.42</v>
+        <v>2095.85</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>2035.41</v>
+        <v>2036.08</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1680.05</v>
+        <v>1683.76</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>7016.5</v>
+        <v>7015.5</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>6736.4</v>
+        <v>6762.98</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>6777.01</v>
+        <v>6786.37</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>5633.22</v>
+        <v>5646.98</v>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
@@ -3841,20 +3841,20 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>48.71</v>
+        <v>48.24</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>47.05</v>
+        <v>47.16</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>46.2</v>
+        <v>46.28</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>42.21</v>
+        <v>42.27</v>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
@@ -3885,20 +3885,20 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>458</v>
+        <v>461.35</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>474.65</v>
+        <v>473.39</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>493.27</v>
+        <v>492.02</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>571.23</v>
+        <v>570.14</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -3929,20 +3929,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>144.06</v>
+        <v>143.82</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>145.19</v>
+        <v>145.06</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>141.2</v>
+        <v>141.3</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>149.86</v>
+        <v>149.8</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>2142.1</v>
+        <v>2118.5</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>2223.02</v>
+        <v>2213.06</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>2204.41</v>
+        <v>2201.04</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1828.46</v>
+        <v>1831.35</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
@@ -4017,20 +4017,20 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>291.5</v>
+        <v>291.2</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>313.36</v>
+        <v>311.25</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>339.64</v>
+        <v>337.74</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>357.68</v>
+        <v>357.02</v>
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4061,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
-        <v>721.45</v>
+        <v>723.5</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>754.95</v>
+        <v>751.96</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>789.33</v>
+        <v>786.75</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>871.72</v>
+        <v>870.25</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -4105,20 +4105,20 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
-        <v>316.2</v>
+        <v>311</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>326.07</v>
+        <v>324.64</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>330.87</v>
+        <v>330.09</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>360.78</v>
+        <v>360.28</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -4149,24 +4149,24 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>2833.3</v>
+        <v>2725.5</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>2741.14</v>
+        <v>2739.65</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>2641.37</v>
+        <v>2644.67</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2526.17</v>
-      </c>
-      <c r="G79" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2528.16</v>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H79" s="14" t="inlineStr">
@@ -4193,20 +4193,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>171.08</v>
+        <v>171.18</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>180.22</v>
+        <v>179.36</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>191.05</v>
+        <v>190.27</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>209.23</v>
+        <v>208.85</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -4237,24 +4237,24 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>160.54</v>
+        <v>166.75</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>161.48</v>
+        <v>161.98</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>157.99</v>
+        <v>158.33</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>155.36</v>
-      </c>
-      <c r="G81" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>155.47</v>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H81" s="14" t="inlineStr">
@@ -4281,20 +4281,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>67.06999999999999</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>71.34999999999999</v>
+        <v>71.12</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>73.09999999999999</v>
+        <v>72.94</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>70.16</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -4325,29 +4325,29 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>208.85</v>
+        <v>197.19</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>200.76</v>
+        <v>200.42</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>203.58</v>
+        <v>203.33</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>184.73</v>
-      </c>
-      <c r="G83" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H83" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>184.86</v>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I83" s="14" t="inlineStr">
@@ -4369,20 +4369,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
-        <v>611.5</v>
+        <v>604.4</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>589.13</v>
+        <v>590.58</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>560.6900000000001</v>
+        <v>562.4</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>507.59</v>
+        <v>508.55</v>
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
@@ -4413,20 +4413,20 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>15.36</v>
+        <v>15.12</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>15.76</v>
+        <v>15.7</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>15.79</v>
+        <v>15.77</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>15.9</v>
+        <v>15.89</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -4457,20 +4457,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>821.4</v>
+        <v>819.95</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>835.95</v>
+        <v>834.4299999999999</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>871.4</v>
+        <v>869.38</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>936.34</v>
+        <v>935.1799999999999</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -4501,20 +4501,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>2435.3</v>
+        <v>2451.6</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>2333.59</v>
+        <v>2344.83</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>2224.85</v>
+        <v>2233.74</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1856.94</v>
+        <v>1862.86</v>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
@@ -4545,24 +4545,24 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>647.2</v>
+        <v>657.85</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>657.64</v>
+        <v>657.66</v>
       </c>
       <c r="E88" s="11" t="n">
         <v>657.91</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>626.83</v>
-      </c>
-      <c r="G88" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>627.14</v>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
@@ -4589,20 +4589,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>1206.5</v>
+        <v>1190.9</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>1264.3</v>
+        <v>1257.31</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>1316.96</v>
+        <v>1312.02</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1302.64</v>
+        <v>1301.53</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -4633,20 +4633,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>137.77</v>
+        <v>142.73</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>133.89</v>
+        <v>134.73</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>128.14</v>
+        <v>128.71</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>117.93</v>
+        <v>118.18</v>
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
@@ -4677,20 +4677,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>531.7</v>
+        <v>535.1</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>540.83</v>
+        <v>540.29</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>515.35</v>
+        <v>516.13</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>498.6</v>
+        <v>498.96</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -4721,20 +4721,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>1609</v>
+        <v>1619.4</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>1713.8</v>
+        <v>1704.81</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>1658.02</v>
+        <v>1656.51</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1244.09</v>
+        <v>1247.82</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
-        <v>79.13</v>
+        <v>79.23</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>73.45999999999999</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>73.87</v>
+        <v>74.08</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>70.04000000000001</v>
+        <v>70.13</v>
       </c>
       <c r="G93" s="14" t="inlineStr">
         <is>
@@ -4809,24 +4809,24 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
-        <v>342.75</v>
+        <v>322.3</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>329.7</v>
+        <v>328.99</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>310.81</v>
+        <v>311.26</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>251.63</v>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>252.34</v>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H94" s="14" t="inlineStr">
@@ -4853,20 +4853,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
-        <v>266.25</v>
+        <v>266.75</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>279.89</v>
+        <v>278.64</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>303.86</v>
+        <v>302.41</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>393.74</v>
+        <v>392.48</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -4897,29 +4897,29 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
-        <v>545.45</v>
+        <v>539.9</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>550.59</v>
+        <v>549.5700000000001</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>542.13</v>
+        <v>542.05</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>463.88</v>
+        <v>464.63</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H96" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H96" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
@@ -4941,20 +4941,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>812.8</v>
+        <v>804.8</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>785.15</v>
+        <v>787.02</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>789.23</v>
+        <v>789.85</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>726.67</v>
+        <v>727.45</v>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
@@ -4985,20 +4985,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>229.17</v>
+        <v>221.45</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>233.85</v>
+        <v>232.67</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>245.81</v>
+        <v>244.85</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>291.94</v>
+        <v>291.24</v>
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
@@ -5029,34 +5029,34 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>1848.3</v>
+        <v>1774.9</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1806.25</v>
+        <v>1803.26</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1834.13</v>
+        <v>1831.81</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1789.32</v>
-      </c>
-      <c r="G99" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H99" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I99" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1789.17</v>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I99" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J99" s="13" t="inlineStr">
@@ -5073,20 +5073,20 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>202.37</v>
+        <v>203.54</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>214.93</v>
+        <v>213.84</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>207.52</v>
+        <v>207.37</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>186.82</v>
+        <v>186.98</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -5117,20 +5117,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
-        <v>830</v>
+        <v>851.55</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>858.6</v>
+        <v>857.9299999999999</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>874.88</v>
+        <v>873.97</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>761.15</v>
+        <v>762.05</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -5161,20 +5161,20 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>391.35</v>
+        <v>393.7</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>407.33</v>
+        <v>406.03</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>396.65</v>
+        <v>396.53</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>372.35</v>
+        <v>372.56</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -5205,20 +5205,20 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>654</v>
+        <v>654.9</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>661.37</v>
+        <v>660.75</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>690.55</v>
+        <v>689.15</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>776.85</v>
+        <v>775.64</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -5249,29 +5249,29 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
-        <v>10624</v>
+        <v>10500</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>10744.1</v>
+        <v>10720.85</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>10505.37</v>
+        <v>10505.16</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>9544.959999999999</v>
+        <v>9554.459999999999</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H104" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H104" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
@@ -5293,20 +5293,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>684.4</v>
+        <v>676.7</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>710.76</v>
+        <v>707.51</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>739.13</v>
+        <v>736.6900000000001</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>715.76</v>
+        <v>715.37</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -5337,20 +5337,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>92.66</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>90.95</v>
+        <v>91.13</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>91.65000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>85.95</v>
+        <v>86.02</v>
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
@@ -5381,20 +5381,20 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>2011.7</v>
+        <v>2076.7</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>2010.49</v>
+        <v>2016.8</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>1907.54</v>
+        <v>1914.18</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1662.13</v>
+        <v>1666.25</v>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
@@ -5425,20 +5425,20 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>1055.75</v>
+        <v>1047.2</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>977.24</v>
+        <v>983.91</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>868.66</v>
+        <v>875.67</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>611.53</v>
+        <v>615.86</v>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
@@ -5469,24 +5469,24 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>1172.6</v>
+        <v>1120</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1160.21</v>
+        <v>1156.38</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>1108.23</v>
+        <v>1108.69</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1021.08</v>
-      </c>
-      <c r="G109" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1022.06</v>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H109" s="14" t="inlineStr">
@@ -5513,20 +5513,20 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>634.2</v>
+        <v>622.1</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>678.83</v>
+        <v>673.4299999999999</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>712.5700000000001</v>
+        <v>709.02</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>853.23</v>
+        <v>850.9299999999999</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -5557,24 +5557,24 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>434.95</v>
+        <v>460.4</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>441.91</v>
+        <v>443.67</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>426.99</v>
+        <v>428.3</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>356.83</v>
-      </c>
-      <c r="G111" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>357.86</v>
+      </c>
+      <c r="G111" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H111" s="14" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>985.05</v>
+        <v>950.25</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>923.89</v>
+        <v>926.4</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>885.73</v>
+        <v>888.26</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>803.9</v>
+        <v>805.36</v>
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
@@ -5645,20 +5645,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>410.2</v>
+        <v>411.15</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>419.11</v>
+        <v>418.35</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>408.96</v>
+        <v>409.04</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>400.03</v>
+        <v>400.14</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -5689,20 +5689,20 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>199.96</v>
+        <v>199.73</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>203.57</v>
+        <v>203.2</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>210.51</v>
+        <v>210.08</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>238.52</v>
+        <v>238.14</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -5733,20 +5733,20 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
-        <v>70.62</v>
+        <v>70.56</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>74.51000000000001</v>
+        <v>74.13</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>81.18000000000001</v>
+        <v>80.77</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>92.31</v>
+        <v>92.09</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -5777,20 +5777,20 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>304.5</v>
+        <v>307.4</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>397.78</v>
+        <v>389.17</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>650.33</v>
+        <v>636.88</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>882.59</v>
+        <v>876.87</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -5821,20 +5821,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>369.35</v>
+        <v>356.9</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>356.11</v>
+        <v>356.18</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>331.94</v>
+        <v>332.91</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>320.72</v>
+        <v>321.08</v>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
@@ -5865,20 +5865,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>3098.7</v>
+        <v>3129.2</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>3287.86</v>
+        <v>3272.75</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>3246.59</v>
+        <v>3241.99</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>2929.25</v>
+        <v>2931.24</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -5909,20 +5909,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>4749.2</v>
+        <v>4653.7</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>4535.38</v>
+        <v>4546.65</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>4417.69</v>
+        <v>4426.95</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>3752.03</v>
+        <v>3761</v>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
@@ -5953,20 +5953,20 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>639.75</v>
+        <v>635.6</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>661.6799999999999</v>
+        <v>659.2</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>684.6900000000001</v>
+        <v>682.77</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>748.66</v>
+        <v>747.53</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -5997,20 +5997,20 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>371.25</v>
+        <v>358.95</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>323.04</v>
+        <v>326.46</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>334.05</v>
+        <v>335.02</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>388.63</v>
+        <v>388.34</v>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
@@ -6041,24 +6041,24 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>509.45</v>
+        <v>500.8</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>508.6</v>
+        <v>507.86</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>524.91</v>
+        <v>523.96</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>583.29</v>
-      </c>
-      <c r="G122" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>582.47</v>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -6085,24 +6085,24 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>619.85</v>
+        <v>640.1</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>633.47</v>
+        <v>634.1</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>602.8</v>
+        <v>604.26</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>518.87</v>
-      </c>
-      <c r="G123" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>520.08</v>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H123" s="14" t="inlineStr">
@@ -6129,20 +6129,20 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1443.1</v>
+        <v>1436.5</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1456.54</v>
+        <v>1454.63</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>1418.21</v>
+        <v>1418.93</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1177.87</v>
+        <v>1180.44</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -6173,20 +6173,20 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>209.76</v>
+        <v>208.83</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>213.95</v>
+        <v>213.46</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>219.08</v>
+        <v>218.68</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>236.57</v>
+        <v>236.3</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -6217,20 +6217,20 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>568.05</v>
+        <v>560.45</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>521.03</v>
+        <v>524.78</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>510.8</v>
+        <v>512.74</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>535.78</v>
+        <v>536.03</v>
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
@@ -6261,20 +6261,20 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>386.2</v>
+        <v>381.6</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>399.21</v>
+        <v>397.53</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>392.9</v>
+        <v>392.45</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>370.44</v>
+        <v>370.56</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -6305,20 +6305,20 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>760.05</v>
+        <v>753.7</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>793.9</v>
+        <v>790.0700000000001</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>791.95</v>
+        <v>790.45</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>742.88</v>
+        <v>742.99</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -6349,20 +6349,20 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>819.55</v>
+        <v>818.5</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>787.9400000000001</v>
+        <v>790.85</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>746.13</v>
+        <v>748.97</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>617.49</v>
+        <v>619.49</v>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
@@ -6393,20 +6393,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>205.68</v>
+        <v>205.01</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>201.7</v>
+        <v>202.01</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>186.37</v>
+        <v>187.1</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>163.79</v>
+        <v>164.2</v>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
@@ -6437,29 +6437,29 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>703.6</v>
+        <v>666.05</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>699.89</v>
+        <v>696.67</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>691.5599999999999</v>
+        <v>690.5599999999999</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>650.77</v>
-      </c>
-      <c r="G131" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H131" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>650.9299999999999</v>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I131" s="14" t="inlineStr">
@@ -6481,20 +6481,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>404.55</v>
+        <v>405.5</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>422.39</v>
+        <v>420.78</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>429.57</v>
+        <v>428.62</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>464.54</v>
+        <v>463.95</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
@@ -6525,20 +6525,20 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>678.55</v>
+        <v>687.8</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>727.5599999999999</v>
+        <v>723.77</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>757.47</v>
+        <v>754.74</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>758.79</v>
+        <v>758.08</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
@@ -6569,20 +6569,20 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>1634.2</v>
+        <v>1608.1</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>1691.64</v>
+        <v>1683.68</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>1708.81</v>
+        <v>1704.86</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1482.18</v>
+        <v>1483.43</v>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
@@ -6613,20 +6613,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>223.55</v>
+        <v>224.7</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>235.84</v>
+        <v>234.78</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>244.64</v>
+        <v>243.86</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>257.18</v>
+        <v>256.86</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
@@ -6657,20 +6657,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C136" s="11" t="n">
-        <v>91.98</v>
+        <v>91.58</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>94.66</v>
+        <v>94.37</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>91.20999999999999</v>
+        <v>91.22</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>78.45999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C137" s="11" t="n">
-        <v>401.2</v>
+        <v>402</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>400.49</v>
+        <v>400.64</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>380.01</v>
+        <v>380.87</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>372.68</v>
+        <v>372.97</v>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
@@ -6745,20 +6745,20 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1921.1</v>
+        <v>1877.6</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1984.75</v>
+        <v>1974.55</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>2094.1</v>
+        <v>2085.61</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>2143.51</v>
+        <v>2140.86</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
@@ -6789,20 +6789,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>585.8</v>
+        <v>594.35</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>613.26</v>
+        <v>611.46</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>610.54</v>
+        <v>609.9</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>560.95</v>
+        <v>561.28</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
@@ -6833,20 +6833,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
-        <v>307.75</v>
+        <v>305.85</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>321.08</v>
+        <v>319.63</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>328.68</v>
+        <v>327.79</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>344.2</v>
+        <v>343.82</v>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
@@ -6877,20 +6877,20 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>407.7</v>
+        <v>398.45</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>426.43</v>
+        <v>423.77</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>413.42</v>
+        <v>412.83</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>325.1</v>
+        <v>325.83</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
@@ -6921,20 +6921,20 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C142" s="11" t="n">
-        <v>1195.2</v>
+        <v>1205.8</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>1170.58</v>
+        <v>1173.94</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>1098.03</v>
+        <v>1102.25</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>874.36</v>
+        <v>877.65</v>
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
@@ -6965,20 +6965,20 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C143" s="11" t="n">
-        <v>136.27</v>
+        <v>136.35</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>130.28</v>
+        <v>130.86</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>128.11</v>
+        <v>128.44</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>122.49</v>
+        <v>122.63</v>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
@@ -7009,20 +7009,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C144" s="11" t="n">
-        <v>209.43</v>
+        <v>208.74</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>214.77</v>
+        <v>214.19</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>217.74</v>
+        <v>217.39</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>215.17</v>
+        <v>215.11</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
@@ -7053,20 +7053,20 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C145" s="11" t="n">
-        <v>262.05</v>
+        <v>253.6</v>
       </c>
       <c r="D145" s="11" t="n">
-        <v>277.92</v>
+        <v>275.61</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>287.81</v>
+        <v>286.47</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>282.75</v>
+        <v>282.46</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C146" s="11" t="n">
-        <v>108.11</v>
+        <v>109.97</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>110.7</v>
+        <v>110.63</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>115.69</v>
+        <v>115.47</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>125.6</v>
+        <v>125.45</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
@@ -7141,20 +7141,20 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C147" s="11" t="n">
-        <v>148.86</v>
+        <v>150.96</v>
       </c>
       <c r="D147" s="11" t="n">
-        <v>153.81</v>
+        <v>153.54</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>154.35</v>
+        <v>154.22</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>148.93</v>
+        <v>148.95</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
@@ -7166,9 +7166,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I147" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I147" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J147" s="13" t="inlineStr">
@@ -7185,29 +7185,29 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C148" s="11" t="n">
-        <v>451.65</v>
+        <v>476.4</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>443.05</v>
+        <v>446.22</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>453.81</v>
+        <v>454.7</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>512.04</v>
+        <v>511.69</v>
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H148" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H148" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I148" s="12" t="inlineStr">
@@ -7229,20 +7229,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>100.72</v>
+        <v>105.38</v>
       </c>
       <c r="D149" s="11" t="n">
-        <v>96.7</v>
+        <v>97.53</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>96.87</v>
+        <v>97.2</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>102.68</v>
+        <v>102.7</v>
       </c>
       <c r="G149" s="14" t="inlineStr">
         <is>
@@ -7254,9 +7254,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I149" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I149" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J149" s="13" t="inlineStr">
@@ -7273,20 +7273,20 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>2078.4</v>
+        <v>2093.4</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>2135.31</v>
+        <v>2131.32</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>2095.8</v>
+        <v>2095.71</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1835.1</v>
+        <v>1837.67</v>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
@@ -7317,34 +7317,34 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
-        <v>2397.2</v>
+        <v>2490.5</v>
       </c>
       <c r="D151" s="11" t="n">
-        <v>2412.94</v>
+        <v>2420.32</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>2460.83</v>
+        <v>2462</v>
       </c>
       <c r="F151" s="11" t="n">
         <v>2490.2</v>
       </c>
-      <c r="G151" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H151" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I151" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="G151" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H151" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I151" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J151" s="13" t="inlineStr">
@@ -7361,24 +7361,24 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>1108</v>
+        <v>1032.5</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>1054.94</v>
+        <v>1052.8</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>973.36</v>
+        <v>975.6799999999999</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>827.8099999999999</v>
-      </c>
-      <c r="G152" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>829.85</v>
+      </c>
+      <c r="G152" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr">
@@ -7405,20 +7405,20 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C153" s="11" t="n">
-        <v>1863.5</v>
+        <v>1852.8</v>
       </c>
       <c r="D153" s="11" t="n">
-        <v>1918.04</v>
+        <v>1911.82</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>1840.33</v>
+        <v>1840.82</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1592.63</v>
+        <v>1595.21</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
@@ -7449,24 +7449,24 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C154" s="11" t="n">
-        <v>1764.9</v>
+        <v>1708.9</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>1761.1</v>
+        <v>1756.13</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>1606.08</v>
+        <v>1610.12</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1325.73</v>
-      </c>
-      <c r="G154" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1329.54</v>
+      </c>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr">
@@ -7493,20 +7493,20 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C155" s="11" t="n">
-        <v>275.45</v>
+        <v>274.95</v>
       </c>
       <c r="D155" s="11" t="n">
-        <v>281.69</v>
+        <v>281.05</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>280.78</v>
+        <v>280.55</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>242.62</v>
+        <v>242.94</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
@@ -7537,20 +7537,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C156" s="11" t="n">
-        <v>13065</v>
+        <v>13611</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>12262.78</v>
+        <v>12391.18</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>11678.07</v>
+        <v>11753.87</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>10415.22</v>
+        <v>10447.02</v>
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
@@ -7581,20 +7581,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C157" s="11" t="n">
-        <v>2000.8</v>
+        <v>2015.5</v>
       </c>
       <c r="D157" s="11" t="n">
-        <v>2078.43</v>
+        <v>2072.44</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>2131.97</v>
+        <v>2127.41</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>2210.41</v>
+        <v>2208.47</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
@@ -7625,20 +7625,20 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C158" s="11" t="n">
-        <v>1290.4</v>
+        <v>1282.1</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>1215.85</v>
+        <v>1222.16</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>1151.24</v>
+        <v>1156.37</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>953.88</v>
+        <v>957.14</v>
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
@@ -7669,20 +7669,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C159" s="11" t="n">
-        <v>631.5</v>
+        <v>634.1</v>
       </c>
       <c r="D159" s="11" t="n">
-        <v>654.38</v>
+        <v>652.45</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>671.84</v>
+        <v>670.36</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>653.8099999999999</v>
+        <v>653.61</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
-        <v>490.6</v>
+        <v>485.85</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>481.64</v>
+        <v>482.04</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>497.87</v>
+        <v>497.4</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>542.22</v>
+        <v>541.66</v>
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
@@ -7757,20 +7757,20 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>125.67</v>
+        <v>131.73</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>117.94</v>
+        <v>119.26</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>113.8</v>
+        <v>114.51</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>115.25</v>
+        <v>115.41</v>
       </c>
       <c r="G161" s="14" t="inlineStr">
         <is>
@@ -7801,20 +7801,20 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
-        <v>419.1</v>
+        <v>437.65</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>418.95</v>
+        <v>420.73</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>418.72</v>
+        <v>419.46</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>399.95</v>
+        <v>400.33</v>
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
@@ -7845,20 +7845,20 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>151.65</v>
+        <v>150.79</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>153.85</v>
+        <v>153.56</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>154.78</v>
+        <v>154.62</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>162</v>
+        <v>161.89</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
@@ -7889,20 +7889,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>490.15</v>
+        <v>492.3</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>512.47</v>
+        <v>510.55</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>533.42</v>
+        <v>531.8099999999999</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>621.4400000000001</v>
+        <v>620.15</v>
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
@@ -7933,20 +7933,20 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C165" s="11" t="n">
-        <v>713.05</v>
+        <v>714.75</v>
       </c>
       <c r="D165" s="11" t="n">
-        <v>721.95</v>
+        <v>721.27</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>687.4400000000001</v>
+        <v>688.51</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>576.5700000000001</v>
+        <v>577.9400000000001</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
@@ -7977,20 +7977,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C166" s="11" t="n">
-        <v>184.26</v>
+        <v>186.7</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>194.66</v>
+        <v>193.9</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>199.02</v>
+        <v>198.54</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>224.64</v>
+        <v>224.26</v>
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C167" s="11" t="n">
-        <v>202.89</v>
+        <v>204.32</v>
       </c>
       <c r="D167" s="11" t="n">
-        <v>211.43</v>
+        <v>210.75</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>221.49</v>
+        <v>220.82</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>226.54</v>
+        <v>226.31</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
@@ -8065,29 +8065,29 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C168" s="11" t="n">
-        <v>514.25</v>
+        <v>519.85</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>528.64</v>
+        <v>527.8</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>514.8200000000001</v>
+        <v>515.02</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>480.4</v>
+        <v>480.79</v>
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H168" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H168" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I168" s="14" t="inlineStr">
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C169" s="11" t="n">
-        <v>428.6</v>
+        <v>430.9</v>
       </c>
       <c r="D169" s="11" t="n">
-        <v>427.94</v>
+        <v>428.22</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>419.66</v>
+        <v>420.1</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>406.46</v>
+        <v>406.71</v>
       </c>
       <c r="G169" s="14" t="inlineStr">
         <is>
@@ -8153,24 +8153,24 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C170" s="11" t="n">
-        <v>837.4</v>
+        <v>862.95</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>842.12</v>
+        <v>844.1</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>798.24</v>
+        <v>800.78</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>668.74</v>
-      </c>
-      <c r="G170" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>670.67</v>
+      </c>
+      <c r="G170" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr">
@@ -8197,20 +8197,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C171" s="11" t="n">
-        <v>410.15</v>
+        <v>387.45</v>
       </c>
       <c r="D171" s="11" t="n">
-        <v>428.76</v>
+        <v>424.82</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>440.38</v>
+        <v>438.3</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>456.98</v>
+        <v>456.28</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
@@ -8241,20 +8241,20 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C172" s="11" t="n">
-        <v>1078.9</v>
+        <v>1091</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>1116.64</v>
+        <v>1114.2</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>1105.49</v>
+        <v>1104.92</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>1054.41</v>
+        <v>1054.77</v>
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
@@ -8285,20 +8285,20 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>129.8</v>
+        <v>133.18</v>
       </c>
       <c r="D173" s="11" t="n">
-        <v>153.95</v>
+        <v>151.97</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>181.35</v>
+        <v>179.47</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>215.95</v>
+        <v>215.13</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
@@ -8329,20 +8329,20 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C174" s="11" t="n">
-        <v>501.15</v>
+        <v>496.35</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>519.58</v>
+        <v>517.37</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>515.5</v>
+        <v>514.75</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>512.67</v>
+        <v>512.51</v>
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
@@ -8373,20 +8373,20 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C175" s="11" t="n">
-        <v>796.2</v>
+        <v>767.75</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>670.9299999999999</v>
+        <v>680.15</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>609.36</v>
+        <v>615.58</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>532</v>
+        <v>534.34</v>
       </c>
       <c r="G175" s="14" t="inlineStr">
         <is>
@@ -8417,20 +8417,20 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>155.75</v>
+        <v>155.56</v>
       </c>
       <c r="D176" s="11" t="n">
         <v>155.52</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>157.01</v>
+        <v>156.95</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>156.64</v>
+        <v>156.63</v>
       </c>
       <c r="G176" s="14" t="inlineStr">
         <is>
@@ -8461,20 +8461,20 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C177" s="11" t="n">
-        <v>173.84</v>
+        <v>173.18</v>
       </c>
       <c r="D177" s="11" t="n">
-        <v>180.99</v>
+        <v>180.25</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>189.22</v>
+        <v>188.59</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>237.46</v>
+        <v>236.82</v>
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
@@ -8505,20 +8505,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C178" s="11" t="n">
-        <v>1614.3</v>
+        <v>1584.8</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>1482.98</v>
+        <v>1492.68</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>1379.72</v>
+        <v>1387.76</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1135.14</v>
+        <v>1139.61</v>
       </c>
       <c r="G178" s="14" t="inlineStr">
         <is>
@@ -8549,20 +8549,20 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>232.05</v>
+        <v>228.91</v>
       </c>
       <c r="D179" s="11" t="n">
-        <v>245.39</v>
+        <v>243.82</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>246.14</v>
+        <v>245.46</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>242.04</v>
+        <v>241.91</v>
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
@@ -8593,29 +8593,29 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>368.8</v>
+        <v>369.95</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>373.11</v>
+        <v>372.81</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>369.47</v>
+        <v>369.49</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>332.7</v>
+        <v>333.07</v>
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H180" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H180" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I180" s="14" t="inlineStr">
@@ -8637,20 +8637,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>25.88</v>
+        <v>25.87</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>27.01</v>
+        <v>26.9</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>28.24</v>
+        <v>28.15</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>33.92</v>
+        <v>33.84</v>
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
@@ -8681,20 +8681,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C182" s="11" t="n">
-        <v>6.87</v>
+        <v>6.89</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>7.2</v>
+        <v>7.17</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>7.72</v>
+        <v>7.68</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>8.98</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
@@ -8725,20 +8725,20 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C183" s="11" t="n">
-        <v>602.85</v>
+        <v>592.35</v>
       </c>
       <c r="D183" s="11" t="n">
-        <v>614.22</v>
+        <v>612.14</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>637.14</v>
+        <v>635.39</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>625.28</v>
+        <v>624.95</v>
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
@@ -8769,20 +8769,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C184" s="11" t="n">
-        <v>239.15</v>
+        <v>235.7</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>252.62</v>
+        <v>251.01</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>280.08</v>
+        <v>278.34</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>338.16</v>
+        <v>337.14</v>
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
@@ -8813,24 +8813,24 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C185" s="11" t="n">
-        <v>742.1</v>
+        <v>725.65</v>
       </c>
       <c r="D185" s="11" t="n">
-        <v>741.13</v>
+        <v>739.65</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>767.58</v>
+        <v>765.9400000000001</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>867.91</v>
-      </c>
-      <c r="G185" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>866.49</v>
+      </c>
+      <c r="G185" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H185" s="12" t="inlineStr">
@@ -8857,20 +8857,20 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C186" s="11" t="n">
-        <v>12341</v>
+        <v>12576</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>13094.39</v>
+        <v>13045.02</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>13070.99</v>
+        <v>13051.57</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>13109.11</v>
+        <v>13103.8</v>
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
@@ -8901,20 +8901,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C187" s="11" t="n">
-        <v>344.95</v>
+        <v>346</v>
       </c>
       <c r="D187" s="11" t="n">
-        <v>342.24</v>
+        <v>342.6</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>339.37</v>
+        <v>339.63</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>331.05</v>
+        <v>331.2</v>
       </c>
       <c r="G187" s="14" t="inlineStr">
         <is>
@@ -8945,24 +8945,24 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C188" s="11" t="n">
-        <v>56.33</v>
+        <v>58.51</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>57.86</v>
+        <v>57.92</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>59.4</v>
+        <v>59.36</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>65.39</v>
-      </c>
-      <c r="G188" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>65.33</v>
+      </c>
+      <c r="G188" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H188" s="12" t="inlineStr">
@@ -8989,24 +8989,24 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C189" s="11" t="n">
-        <v>1356.8</v>
+        <v>1379.3</v>
       </c>
       <c r="D189" s="11" t="n">
-        <v>1372.1</v>
+        <v>1372.79</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>1323.64</v>
+        <v>1325.83</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1141.01</v>
-      </c>
-      <c r="G189" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1143.38</v>
+      </c>
+      <c r="G189" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H189" s="14" t="inlineStr">
@@ -9033,24 +9033,24 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C190" s="11" t="n">
-        <v>849.9</v>
+        <v>840.05</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>844.26</v>
+        <v>843.86</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>874.16</v>
+        <v>872.8200000000001</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>963.8</v>
-      </c>
-      <c r="G190" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>962.5700000000001</v>
+      </c>
+      <c r="G190" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
@@ -9077,20 +9077,20 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C191" s="11" t="n">
-        <v>821.4</v>
+        <v>805.55</v>
       </c>
       <c r="D191" s="11" t="n">
-        <v>783.36</v>
+        <v>785.47</v>
       </c>
       <c r="E191" s="11" t="n">
-        <v>792.42</v>
+        <v>792.9299999999999</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>782.86</v>
+        <v>783.09</v>
       </c>
       <c r="G191" s="14" t="inlineStr">
         <is>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C192" s="11" t="n">
-        <v>972.8</v>
+        <v>953.75</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>875.1799999999999</v>
+        <v>882.66</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>823.23</v>
+        <v>828.35</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>762.6900000000001</v>
+        <v>764.59</v>
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
@@ -9165,20 +9165,20 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C193" s="11" t="n">
-        <v>119.33</v>
+        <v>118.58</v>
       </c>
       <c r="D193" s="11" t="n">
-        <v>121.67</v>
+        <v>121.38</v>
       </c>
       <c r="E193" s="11" t="n">
-        <v>124.1</v>
+        <v>123.88</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>136.84</v>
+        <v>136.66</v>
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
@@ -9209,20 +9209,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C194" s="11" t="n">
-        <v>280.3</v>
+        <v>277.4</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>287.56</v>
+        <v>286.6</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>294.86</v>
+        <v>294.17</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>329.96</v>
+        <v>329.43</v>
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
@@ -9253,20 +9253,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C195" s="11" t="n">
-        <v>2789</v>
+        <v>2767.9</v>
       </c>
       <c r="D195" s="11" t="n">
-        <v>2887.74</v>
+        <v>2876.33</v>
       </c>
       <c r="E195" s="11" t="n">
-        <v>2823.99</v>
+        <v>2821.79</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>2620.65</v>
+        <v>2622.12</v>
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
@@ -9297,20 +9297,20 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C196" s="11" t="n">
-        <v>2489.8</v>
+        <v>2537.2</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>2647.79</v>
+        <v>2637.26</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>2673.91</v>
+        <v>2668.55</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>2604.08</v>
+        <v>2603.41</v>
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
@@ -9341,20 +9341,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C197" s="11" t="n">
-        <v>744.3</v>
+        <v>742.7</v>
       </c>
       <c r="D197" s="11" t="n">
-        <v>751.21</v>
+        <v>750.4</v>
       </c>
       <c r="E197" s="11" t="n">
-        <v>696.9</v>
+        <v>698.7</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>585.59</v>
+        <v>587.15</v>
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
@@ -9385,20 +9385,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C198" s="11" t="n">
-        <v>667.15</v>
+        <v>660.45</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>670.16</v>
+        <v>669.23</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>676.34</v>
+        <v>675.72</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>633.5599999999999</v>
+        <v>633.83</v>
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C199" s="11" t="n">
-        <v>333.35</v>
+        <v>325.55</v>
       </c>
       <c r="D199" s="11" t="n">
-        <v>335.27</v>
+        <v>334.35</v>
       </c>
       <c r="E199" s="11" t="n">
-        <v>347.01</v>
+        <v>346.16</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>410.06</v>
+        <v>409.22</v>
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
@@ -9473,20 +9473,20 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C200" s="11" t="n">
-        <v>1591.2</v>
+        <v>1596.3</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>1691.6</v>
+        <v>1682.53</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>1804.05</v>
+        <v>1795.9</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>1979.91</v>
+        <v>1976.09</v>
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
@@ -9517,24 +9517,24 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C201" s="11" t="n">
-        <v>160.24</v>
+        <v>162.89</v>
       </c>
       <c r="D201" s="11" t="n">
-        <v>162.42</v>
+        <v>162.46</v>
       </c>
       <c r="E201" s="11" t="n">
-        <v>169.98</v>
+        <v>169.7</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>187.84</v>
-      </c>
-      <c r="G201" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>187.59</v>
+      </c>
+      <c r="G201" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H201" s="12" t="inlineStr">
@@ -9561,20 +9561,20 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C202" s="11" t="n">
-        <v>117.48</v>
+        <v>117.6</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>119.66</v>
+        <v>119.47</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>122.65</v>
+        <v>122.45</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>125.64</v>
+        <v>125.56</v>
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
@@ -9605,20 +9605,20 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C203" s="11" t="n">
-        <v>181.33</v>
+        <v>177.99</v>
       </c>
       <c r="D203" s="11" t="n">
-        <v>186.08</v>
+        <v>185.31</v>
       </c>
       <c r="E203" s="11" t="n">
-        <v>193.4</v>
+        <v>192.8</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>205.74</v>
+        <v>205.47</v>
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
@@ -9649,20 +9649,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C204" s="11" t="n">
-        <v>824.8</v>
+        <v>856.1</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>808</v>
+        <v>812.58</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>820</v>
+        <v>821.42</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>825.35</v>
+        <v>825.65</v>
       </c>
       <c r="G204" s="14" t="inlineStr">
         <is>
@@ -9674,9 +9674,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I204" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I204" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J204" s="13" t="inlineStr">
@@ -9693,20 +9693,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C205" s="11" t="n">
-        <v>108.53</v>
+        <v>107.75</v>
       </c>
       <c r="D205" s="11" t="n">
-        <v>112.67</v>
+        <v>112.2</v>
       </c>
       <c r="E205" s="11" t="n">
-        <v>116</v>
+        <v>115.68</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>133.73</v>
+        <v>133.47</v>
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
@@ -9737,20 +9737,20 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C206" s="11" t="n">
-        <v>540.05</v>
+        <v>543</v>
       </c>
       <c r="D206" s="11" t="n">
-        <v>569.14</v>
+        <v>566.65</v>
       </c>
       <c r="E206" s="11" t="n">
-        <v>576.3</v>
+        <v>574.99</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>605.22</v>
+        <v>604.6</v>
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
@@ -9781,24 +9781,24 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C207" s="11" t="n">
-        <v>410.9</v>
+        <v>406.2</v>
       </c>
       <c r="D207" s="11" t="n">
-        <v>410.25</v>
+        <v>409.86</v>
       </c>
       <c r="E207" s="11" t="n">
-        <v>414.41</v>
+        <v>414.09</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>435.47</v>
-      </c>
-      <c r="G207" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>435.18</v>
+      </c>
+      <c r="G207" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -9825,20 +9825,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
-        <v>127.02</v>
+        <v>125.96</v>
       </c>
       <c r="D208" s="11" t="n">
-        <v>128.17</v>
+        <v>127.96</v>
       </c>
       <c r="E208" s="11" t="n">
-        <v>127.47</v>
+        <v>127.41</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>136.19</v>
+        <v>136.08</v>
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
@@ -9869,20 +9869,20 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C209" s="11" t="n">
-        <v>151.15</v>
+        <v>151.48</v>
       </c>
       <c r="D209" s="11" t="n">
-        <v>153.9</v>
+        <v>153.67</v>
       </c>
       <c r="E209" s="11" t="n">
-        <v>157.21</v>
+        <v>156.99</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>168.5</v>
+        <v>168.33</v>
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
@@ -9913,20 +9913,20 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
-        <v>103.92</v>
+        <v>102.39</v>
       </c>
       <c r="D210" s="11" t="n">
-        <v>105.3</v>
+        <v>105.02</v>
       </c>
       <c r="E210" s="11" t="n">
-        <v>105.41</v>
+        <v>105.29</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>112.56</v>
+        <v>112.46</v>
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
@@ -9957,20 +9957,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C211" s="11" t="n">
         <v>1201</v>
       </c>
       <c r="D211" s="11" t="n">
-        <v>1257.44</v>
+        <v>1252.07</v>
       </c>
       <c r="E211" s="11" t="n">
-        <v>1289.55</v>
+        <v>1286.08</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>1308.98</v>
+        <v>1307.91</v>
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
-        <v>118.42</v>
+        <v>118.77</v>
       </c>
       <c r="D212" s="11" t="n">
-        <v>124.3</v>
+        <v>123.77</v>
       </c>
       <c r="E212" s="11" t="n">
-        <v>128.6</v>
+        <v>128.21</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>147.13</v>
+        <v>146.84</v>
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
@@ -10045,20 +10045,20 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C213" s="11" t="n">
-        <v>282.15</v>
+        <v>281.6</v>
       </c>
       <c r="D213" s="11" t="n">
-        <v>292.77</v>
+        <v>291.71</v>
       </c>
       <c r="E213" s="11" t="n">
-        <v>302.46</v>
+        <v>301.64</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>315.66</v>
+        <v>315.32</v>
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
@@ -10089,20 +10089,20 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
-        <v>247.1</v>
+        <v>244.1</v>
       </c>
       <c r="D214" s="11" t="n">
-        <v>263.69</v>
+        <v>261.82</v>
       </c>
       <c r="E214" s="11" t="n">
-        <v>271.63</v>
+        <v>270.55</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>342.51</v>
+        <v>341.53</v>
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
@@ -10133,24 +10133,24 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C215" s="11" t="n">
-        <v>861.5</v>
+        <v>825.45</v>
       </c>
       <c r="D215" s="11" t="n">
-        <v>837.12</v>
+        <v>836.01</v>
       </c>
       <c r="E215" s="11" t="n">
-        <v>821.86</v>
+        <v>822</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>805.04</v>
-      </c>
-      <c r="G215" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>805.25</v>
+      </c>
+      <c r="G215" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H215" s="14" t="inlineStr">
@@ -10177,20 +10177,20 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
-        <v>1477.1</v>
+        <v>1466.7</v>
       </c>
       <c r="D216" s="11" t="n">
-        <v>1352.01</v>
+        <v>1362.93</v>
       </c>
       <c r="E216" s="11" t="n">
-        <v>1171.39</v>
+        <v>1182.97</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>1014.9</v>
+        <v>1019.4</v>
       </c>
       <c r="G216" s="14" t="inlineStr">
         <is>
@@ -10221,29 +10221,29 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C217" s="11" t="n">
-        <v>76.53</v>
+        <v>74.37</v>
       </c>
       <c r="D217" s="11" t="n">
-        <v>75.31999999999999</v>
+        <v>75.23</v>
       </c>
       <c r="E217" s="11" t="n">
-        <v>75.65000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="G217" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H217" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>79.02</v>
+      </c>
+      <c r="G217" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H217" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I217" s="12" t="inlineStr">
@@ -10265,20 +10265,20 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
-        <v>115.56</v>
+        <v>119.55</v>
       </c>
       <c r="D218" s="11" t="n">
-        <v>121.22</v>
+        <v>121.06</v>
       </c>
       <c r="E218" s="11" t="n">
-        <v>129.56</v>
+        <v>129.17</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>157.54</v>
+        <v>157.16</v>
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
@@ -10309,20 +10309,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C219" s="11" t="n">
-        <v>1040.5</v>
+        <v>1046.9</v>
       </c>
       <c r="D219" s="11" t="n">
-        <v>1072.44</v>
+        <v>1070.01</v>
       </c>
       <c r="E219" s="11" t="n">
-        <v>1072.49</v>
+        <v>1071.49</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>1119.36</v>
+        <v>1118.64</v>
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
@@ -10353,20 +10353,20 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
-        <v>233.05</v>
+        <v>237</v>
       </c>
       <c r="D220" s="11" t="n">
-        <v>239.51</v>
+        <v>239.27</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>239.67</v>
+        <v>239.56</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>228.26</v>
+        <v>228.35</v>
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
@@ -10397,20 +10397,20 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C221" s="11" t="n">
-        <v>1514</v>
+        <v>1509.9</v>
       </c>
       <c r="D221" s="11" t="n">
-        <v>1533.69</v>
+        <v>1531.42</v>
       </c>
       <c r="E221" s="11" t="n">
-        <v>1545.37</v>
+        <v>1543.98</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>1869.57</v>
+        <v>1865.99</v>
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
@@ -10441,24 +10441,24 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C222" s="11" t="n">
-        <v>595.65</v>
+        <v>606.3</v>
       </c>
       <c r="D222" s="11" t="n">
-        <v>605.72</v>
+        <v>605.77</v>
       </c>
       <c r="E222" s="11" t="n">
-        <v>616.14</v>
+        <v>615.75</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>623.15</v>
-      </c>
-      <c r="G222" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>622.99</v>
+      </c>
+      <c r="G222" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H222" s="12" t="inlineStr">
@@ -10485,20 +10485,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C223" s="11" t="n">
-        <v>22.54</v>
+        <v>21.89</v>
       </c>
       <c r="D223" s="11" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="E223" s="11" t="n">
         <v>23.4</v>
       </c>
-      <c r="E223" s="11" t="n">
-        <v>23.46</v>
-      </c>
       <c r="F223" s="11" t="n">
-        <v>24.77</v>
+        <v>24.74</v>
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
@@ -10529,20 +10529,20 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C224" s="11" t="n">
-        <v>631.7</v>
+        <v>623.55</v>
       </c>
       <c r="D224" s="11" t="n">
-        <v>648.74</v>
+        <v>646.34</v>
       </c>
       <c r="E224" s="11" t="n">
-        <v>622.08</v>
+        <v>622.14</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>601.1900000000001</v>
+        <v>601.42</v>
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
@@ -10573,20 +10573,20 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C225" s="11" t="n">
-        <v>362.95</v>
+        <v>361</v>
       </c>
       <c r="D225" s="11" t="n">
-        <v>389.32</v>
+        <v>386.63</v>
       </c>
       <c r="E225" s="11" t="n">
-        <v>413.68</v>
+        <v>411.61</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>471.74</v>
+        <v>470.64</v>
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
@@ -10617,20 +10617,20 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C226" s="11" t="n">
-        <v>220.75</v>
+        <v>221.37</v>
       </c>
       <c r="D226" s="11" t="n">
-        <v>217.36</v>
+        <v>217.74</v>
       </c>
       <c r="E226" s="11" t="n">
-        <v>223.33</v>
+        <v>223.25</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>241.35</v>
+        <v>241.15</v>
       </c>
       <c r="G226" s="14" t="inlineStr">
         <is>
@@ -10661,20 +10661,20 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C227" s="11" t="n">
-        <v>495.25</v>
+        <v>479.3</v>
       </c>
       <c r="D227" s="11" t="n">
-        <v>502.14</v>
+        <v>499.97</v>
       </c>
       <c r="E227" s="11" t="n">
-        <v>499.43</v>
+        <v>498.64</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>477.26</v>
+        <v>477.28</v>
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
@@ -10705,20 +10705,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C228" s="11" t="n">
-        <v>109.27</v>
+        <v>108.74</v>
       </c>
       <c r="D228" s="11" t="n">
-        <v>113.56</v>
+        <v>113.1</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>112.91</v>
+        <v>112.75</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>121.63</v>
+        <v>121.5</v>
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
@@ -10749,20 +10749,20 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C229" s="11" t="n">
-        <v>204.84</v>
+        <v>206.34</v>
       </c>
       <c r="D229" s="11" t="n">
-        <v>213.56</v>
+        <v>212.88</v>
       </c>
       <c r="E229" s="11" t="n">
-        <v>214.95</v>
+        <v>214.61</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>223.44</v>
+        <v>223.27</v>
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
@@ -10793,20 +10793,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C230" s="11" t="n">
-        <v>1781.3</v>
+        <v>1761.7</v>
       </c>
       <c r="D230" s="11" t="n">
-        <v>1874.92</v>
+        <v>1864.14</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>1884.17</v>
+        <v>1879.36</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>1791.59</v>
+        <v>1791.29</v>
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
@@ -10837,20 +10837,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C231" s="11" t="n">
-        <v>721.85</v>
+        <v>737.65</v>
       </c>
       <c r="D231" s="11" t="n">
-        <v>695.47</v>
+        <v>699.49</v>
       </c>
       <c r="E231" s="11" t="n">
-        <v>659.15</v>
+        <v>662.23</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>615.13</v>
+        <v>616.35</v>
       </c>
       <c r="G231" s="14" t="inlineStr">
         <is>
@@ -10881,20 +10881,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C232" s="11" t="n">
-        <v>169.08</v>
+        <v>170.12</v>
       </c>
       <c r="D232" s="11" t="n">
-        <v>176.72</v>
+        <v>176.09</v>
       </c>
       <c r="E232" s="11" t="n">
-        <v>180.78</v>
+        <v>180.36</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>212.08</v>
+        <v>211.66</v>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
@@ -10925,20 +10925,20 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>5124.5</v>
+        <v>5088</v>
       </c>
       <c r="D233" s="11" t="n">
-        <v>5531.6</v>
+        <v>5489.35</v>
       </c>
       <c r="E233" s="11" t="n">
-        <v>5712.4</v>
+        <v>5687.91</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>5718.32</v>
+        <v>5712.05</v>
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
@@ -10969,20 +10969,20 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>309.85</v>
+        <v>303.4</v>
       </c>
       <c r="D234" s="11" t="n">
-        <v>326.58</v>
+        <v>324.37</v>
       </c>
       <c r="E234" s="11" t="n">
-        <v>333.17</v>
+        <v>332</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>380.09</v>
+        <v>379.33</v>
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
@@ -11013,20 +11013,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>25.66</v>
+        <v>26.06</v>
       </c>
       <c r="D235" s="11" t="n">
-        <v>27.41</v>
+        <v>27.28</v>
       </c>
       <c r="E235" s="11" t="n">
-        <v>29.16</v>
+        <v>29.04</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>34.74</v>
+        <v>34.65</v>
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
@@ -11057,20 +11057,20 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>178.1</v>
+        <v>181.96</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>188.81</v>
+        <v>188.16</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>194.25</v>
+        <v>193.76</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>209.07</v>
+        <v>208.8</v>
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
@@ -11101,20 +11101,20 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>131.3</v>
+        <v>130.57</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>130.01</v>
+        <v>130.06</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>129.74</v>
+        <v>129.77</v>
       </c>
       <c r="F237" s="11" t="n">
-        <v>124.62</v>
+        <v>124.68</v>
       </c>
       <c r="G237" s="14" t="inlineStr">
         <is>
@@ -11145,20 +11145,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>7.06</v>
+        <v>7.09</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>7.8</v>
+        <v>7.74</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>12.56</v>
+        <v>12.51</v>
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
@@ -11189,20 +11189,20 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
-        <v>97.81999999999999</v>
+        <v>96.52</v>
       </c>
       <c r="D239" s="11" t="n">
-        <v>99.54000000000001</v>
+        <v>99.25</v>
       </c>
       <c r="E239" s="11" t="n">
-        <v>104.08</v>
+        <v>103.78</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>118.5</v>
+        <v>118.29</v>
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
@@ -11233,20 +11233,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>293.2</v>
+        <v>290.95</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>300.46</v>
+        <v>299.55</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>303.34</v>
+        <v>302.86</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>328.46</v>
+        <v>328.09</v>
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
@@ -11277,20 +11277,20 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>438.25</v>
+        <v>432.75</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>465.66</v>
+        <v>462.52</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>494.99</v>
+        <v>492.54</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>601.01</v>
+        <v>599.33</v>
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
@@ -11321,20 +11321,20 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C242" s="11" t="n">
-        <v>63.35</v>
+        <v>62.24</v>
       </c>
       <c r="D242" s="11" t="n">
-        <v>65.43000000000001</v>
+        <v>65.12</v>
       </c>
       <c r="E242" s="11" t="n">
-        <v>66.2</v>
+        <v>66.05</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>71.40000000000001</v>
+        <v>71.31</v>
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
@@ -11365,20 +11365,20 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C243" s="11" t="n">
-        <v>1430.9</v>
+        <v>1429.6</v>
       </c>
       <c r="D243" s="11" t="n">
-        <v>1493.28</v>
+        <v>1487.22</v>
       </c>
       <c r="E243" s="11" t="n">
-        <v>1517.88</v>
+        <v>1514.42</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>1674.48</v>
+        <v>1672.05</v>
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
@@ -11409,20 +11409,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>114.94</v>
+        <v>114.07</v>
       </c>
       <c r="D244" s="11" t="n">
-        <v>121.22</v>
+        <v>120.54</v>
       </c>
       <c r="E244" s="11" t="n">
-        <v>126.7</v>
+        <v>126.21</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>133.8</v>
+        <v>133.6</v>
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
@@ -11453,20 +11453,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C245" s="11" t="n">
-        <v>64.79000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="D245" s="11" t="n">
-        <v>67.43000000000001</v>
+        <v>67.22</v>
       </c>
       <c r="E245" s="11" t="n">
-        <v>69.12</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>75.06999999999999</v>
+        <v>74.97</v>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
@@ -11497,20 +11497,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C246" s="11" t="n">
-        <v>665</v>
+        <v>681.85</v>
       </c>
       <c r="D246" s="11" t="n">
-        <v>712.49</v>
+        <v>709.5700000000001</v>
       </c>
       <c r="E246" s="11" t="n">
-        <v>735.8200000000001</v>
+        <v>733.7</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>753.6</v>
+        <v>752.88</v>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
@@ -11541,20 +11541,20 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>421.45</v>
+        <v>417.15</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>438.81</v>
+        <v>436.75</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>432.68</v>
+        <v>432.07</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>433.14</v>
+        <v>432.98</v>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
@@ -11585,20 +11585,20 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C248" s="11" t="n">
-        <v>551.55</v>
+        <v>550.05</v>
       </c>
       <c r="D248" s="11" t="n">
-        <v>597.54</v>
+        <v>593.02</v>
       </c>
       <c r="E248" s="11" t="n">
-        <v>665.38</v>
+        <v>660.86</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>786.12</v>
+        <v>783.77</v>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
@@ -11629,20 +11629,20 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C249" s="11" t="n">
-        <v>3867</v>
+        <v>3802.8</v>
       </c>
       <c r="D249" s="11" t="n">
-        <v>4045.39</v>
+        <v>4022.28</v>
       </c>
       <c r="E249" s="11" t="n">
-        <v>4215.62</v>
+        <v>4199.43</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>4444.39</v>
+        <v>4438.01</v>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
@@ -11673,20 +11673,20 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
  